--- a/TAZA/_документы/ШР ЦАКФ.xlsx
+++ b/TAZA/_документы/ШР ЦАКФ.xlsx
@@ -1654,21 +1654,6 @@
     <t>Бухгалтер</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Эксперт по отходам/воде/воздуху </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="204"/>
-      </rPr>
-      <t>/вакансия</t>
-    </r>
-  </si>
-  <si>
     <t>Юрист (МФЦА) / аутсорс</t>
   </si>
   <si>
@@ -2042,9 +2027,6 @@
   </si>
   <si>
     <t>poiskraboty.kz – индекс зарплат в вакансиях, Астана 370 000 ₸: https://poiskraboty.kz/zarplaty</t>
-  </si>
-  <si>
-    <t>Менеджер проектов</t>
   </si>
   <si>
     <t>Проекты и международные партнёры Проектного офиса для Центральной Азии, гранты, заявки и переписка на английском языке</t>
@@ -2266,21 +2248,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Эксперт-эколог / </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="204"/>
-      </rPr>
-      <t>Загирова Анастасия</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">Директор / </t>
     </r>
     <r>
@@ -2445,13 +2412,22 @@
     <t>Общее руководство Фондом и проектом, представительство, утверждение планов, бюджета и отчётов; руководство Проектным офисом для Центральной Азии</t>
   </si>
   <si>
-    <t>Эксперт / Абулхан А.</t>
-  </si>
-  <si>
     <t>Молодёжь, волонтёры, НПО, школы и вузы; экспертиза молодёжных и общественных проектов</t>
   </si>
   <si>
     <t>Центрально-Азиатского климатического фонда с 01.11.2026 года</t>
+  </si>
+  <si>
+    <t>Заместитель руководителя Проектного офиса для Центральной Азии</t>
+  </si>
+  <si>
+    <t>Менеджер проектов – эколог / Загирова Анастасия</t>
+  </si>
+  <si>
+    <t>Менеджер проектов – эколог / Абулхан А.</t>
+  </si>
+  <si>
+    <t>Менеджер проектов – эколог (отходы, вода, воздух) / вакансия</t>
   </si>
 </sst>
 </file>
@@ -21111,7 +21087,7 @@
     </row>
     <row r="3" spans="1:10" ht="15.75">
       <c r="A3" s="242" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="B3" s="236"/>
       <c r="C3" s="236"/>
@@ -21141,22 +21117,22 @@
         <v>265</v>
       </c>
       <c r="E5" s="218" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F5" s="220" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="G5" s="219" t="s">
         <v>282</v>
       </c>
       <c r="H5" s="219" t="s">
+        <v>299</v>
+      </c>
+      <c r="I5" s="219" t="s">
         <v>300</v>
       </c>
-      <c r="I5" s="219" t="s">
+      <c r="J5" s="219" t="s">
         <v>301</v>
-      </c>
-      <c r="J5" s="219" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -21164,7 +21140,7 @@
         <v>262</v>
       </c>
       <c r="B6" s="201" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C6" s="200"/>
       <c r="D6" s="181">
@@ -21192,7 +21168,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="206" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="C7" s="207" t="s">
         <v>269</v>
@@ -21212,13 +21188,13 @@
         <v>19200</v>
       </c>
       <c r="H7" s="177" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I7" s="264" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="J7" s="270" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="30">
@@ -21226,7 +21202,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="206" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C8" s="207" t="s">
         <v>274</v>
@@ -21246,13 +21222,13 @@
         <v>16800</v>
       </c>
       <c r="H8" s="177" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I8" s="264" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="J8" s="270" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="45">
@@ -21260,7 +21236,7 @@
         <v>2</v>
       </c>
       <c r="B9" s="206" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="C9" s="207" t="s">
         <v>274</v>
@@ -21280,21 +21256,21 @@
         <v>16800</v>
       </c>
       <c r="H9" s="177" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I9" s="264" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="J9" s="270" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="200" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B10" s="201" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C10" s="200"/>
       <c r="D10" s="181">
@@ -21322,7 +21298,7 @@
         <v>1</v>
       </c>
       <c r="B11" s="206" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C11" s="207" t="s">
         <v>274</v>
@@ -21342,13 +21318,13 @@
         <v>16800</v>
       </c>
       <c r="H11" s="177" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I11" s="264" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="J11" s="270" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="28.5">
@@ -21384,7 +21360,7 @@
         <v>1</v>
       </c>
       <c r="B13" s="210" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C13" s="213" t="s">
         <v>270</v>
@@ -21404,13 +21380,13 @@
         <v>15600</v>
       </c>
       <c r="H13" s="281" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I13" s="284" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="J13" s="285" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -21418,7 +21394,7 @@
         <v>2</v>
       </c>
       <c r="B14" s="210" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C14" s="194" t="s">
         <v>272</v>
@@ -21438,13 +21414,13 @@
         <v>12000</v>
       </c>
       <c r="H14" s="177" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I14" s="264" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="J14" s="270" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="15" spans="1:10" s="214" customFormat="1" ht="29.25">
@@ -21452,7 +21428,7 @@
         <v>3</v>
       </c>
       <c r="B15" s="210" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C15" s="213" t="s">
         <v>272</v>
@@ -21472,13 +21448,13 @@
         <v>12000</v>
       </c>
       <c r="H15" s="281" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I15" s="284" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="J15" s="285" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="16" spans="1:10" s="214" customFormat="1">
@@ -21486,7 +21462,7 @@
         <v>4</v>
       </c>
       <c r="B16" s="255" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C16" s="249"/>
       <c r="D16" s="251"/>
@@ -21494,13 +21470,13 @@
       <c r="F16" s="253"/>
       <c r="G16" s="251"/>
       <c r="H16" s="251" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="I16" s="263" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="J16" s="272" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="17" spans="1:10" s="214" customFormat="1" ht="30">
@@ -21508,7 +21484,7 @@
         <v>5</v>
       </c>
       <c r="B17" s="244" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C17" s="243" t="s">
         <v>271</v>
@@ -21528,19 +21504,19 @@
         <v>8400</v>
       </c>
       <c r="H17" s="245" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I17" s="266" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="J17" s="271" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="42.75">
       <c r="A18" s="202"/>
       <c r="B18" s="203" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C18" s="204"/>
       <c r="D18" s="181">
@@ -21549,15 +21525,15 @@
       </c>
       <c r="E18" s="221">
         <f>SUM(E19:E22)</f>
-        <v>3400000</v>
+        <v>3030000</v>
       </c>
       <c r="F18" s="222">
         <f>SUM(F19:F22)</f>
-        <v>2744700</v>
+        <v>2451660</v>
       </c>
       <c r="G18" s="181">
         <f>SUM(G19:G22)</f>
-        <v>40800</v>
+        <v>36360</v>
       </c>
       <c r="H18" s="181"/>
       <c r="I18" s="181"/>
@@ -21568,7 +21544,7 @@
         <v>1</v>
       </c>
       <c r="B19" s="211" t="s">
-        <v>411</v>
+        <v>451</v>
       </c>
       <c r="C19" s="194" t="s">
         <v>272</v>
@@ -21588,81 +21564,81 @@
         <v>12000</v>
       </c>
       <c r="H19" s="177" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I19" s="264" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="J19" s="270" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="20" spans="1:10" s="214" customFormat="1" ht="30">
-      <c r="A20" s="243">
+      <c r="A20" s="213">
         <v>2</v>
       </c>
-      <c r="B20" s="244" t="s">
-        <v>436</v>
-      </c>
-      <c r="C20" s="243" t="s">
+      <c r="B20" s="210" t="s">
+        <v>452</v>
+      </c>
+      <c r="C20" s="213" t="s">
         <v>272</v>
       </c>
-      <c r="D20" s="245">
+      <c r="D20" s="281">
         <v>1</v>
       </c>
-      <c r="E20" s="246">
-        <v>800000</v>
-      </c>
-      <c r="F20" s="247">
+      <c r="E20" s="282">
+        <v>615000</v>
+      </c>
+      <c r="F20" s="283">
         <f>IF(E20&gt;0,E20-MIN(E20,4250000)*10%-MIN(E20,1700000)*2%-MAX(0,E20-MIN(E20,4250000)*10%-MIN(E20,1700000)*2%-129750)*10%,0)</f>
-        <v>646575</v>
-      </c>
-      <c r="G20" s="245">
+        <v>500055</v>
+      </c>
+      <c r="G20" s="281">
         <f>D20*E20*12/1000</f>
-        <v>9600</v>
-      </c>
-      <c r="H20" s="245" t="s">
-        <v>306</v>
-      </c>
-      <c r="I20" s="266" t="s">
-        <v>319</v>
-      </c>
-      <c r="J20" s="271" t="s">
-        <v>325</v>
+        <v>7380</v>
+      </c>
+      <c r="H20" s="281" t="s">
+        <v>305</v>
+      </c>
+      <c r="I20" s="284" t="s">
+        <v>309</v>
+      </c>
+      <c r="J20" s="285" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="21" spans="1:10" s="214" customFormat="1" ht="30">
-      <c r="A21" s="243">
+      <c r="A21" s="213">
         <v>3</v>
       </c>
-      <c r="B21" s="244" t="s">
-        <v>452</v>
-      </c>
-      <c r="C21" s="243" t="s">
+      <c r="B21" s="210" t="s">
+        <v>453</v>
+      </c>
+      <c r="C21" s="213" t="s">
         <v>272</v>
       </c>
-      <c r="D21" s="245">
+      <c r="D21" s="281">
         <v>1</v>
       </c>
-      <c r="E21" s="246">
-        <v>800000</v>
-      </c>
-      <c r="F21" s="247">
+      <c r="E21" s="282">
+        <v>615000</v>
+      </c>
+      <c r="F21" s="283">
         <f>IF(E21&gt;0,E21-MIN(E21,4250000)*10%-MIN(E21,1700000)*2%-MAX(0,E21-MIN(E21,4250000)*10%-MIN(E21,1700000)*2%-129750)*10%,0)</f>
-        <v>646575</v>
-      </c>
-      <c r="G21" s="245">
+        <v>500055</v>
+      </c>
+      <c r="G21" s="281">
         <f>D21*E21*12/1000</f>
-        <v>9600</v>
-      </c>
-      <c r="H21" s="245" t="s">
-        <v>306</v>
-      </c>
-      <c r="I21" s="266" t="s">
-        <v>319</v>
-      </c>
-      <c r="J21" s="271" t="s">
-        <v>453</v>
+        <v>7380</v>
+      </c>
+      <c r="H21" s="281" t="s">
+        <v>305</v>
+      </c>
+      <c r="I21" s="284" t="s">
+        <v>309</v>
+      </c>
+      <c r="J21" s="285" t="s">
+        <v>449</v>
       </c>
     </row>
     <row r="22" spans="1:10" s="214" customFormat="1" ht="30">
@@ -21670,7 +21646,7 @@
         <v>4</v>
       </c>
       <c r="B22" s="244" t="s">
-        <v>285</v>
+        <v>454</v>
       </c>
       <c r="C22" s="243" t="s">
         <v>272</v>
@@ -21690,13 +21666,13 @@
         <v>9600</v>
       </c>
       <c r="H22" s="245" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I22" s="266" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="J22" s="271" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="28.5">
@@ -21732,7 +21708,7 @@
         <v>1</v>
       </c>
       <c r="B24" s="248" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="C24" s="243" t="s">
         <v>270</v>
@@ -21752,13 +21728,13 @@
         <v>15600</v>
       </c>
       <c r="H24" s="245" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I24" s="266" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="J24" s="271" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="30">
@@ -21766,7 +21742,7 @@
         <v>2</v>
       </c>
       <c r="B25" s="183" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="C25" s="194" t="s">
         <v>272</v>
@@ -21786,13 +21762,13 @@
         <v>13200</v>
       </c>
       <c r="H25" s="177" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I25" s="264" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="J25" s="270" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="30">
@@ -21800,7 +21776,7 @@
         <v>3</v>
       </c>
       <c r="B26" s="183" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C26" s="194" t="s">
         <v>272</v>
@@ -21820,13 +21796,13 @@
         <v>12000</v>
       </c>
       <c r="H26" s="177" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I26" s="264" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="J26" s="270" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="27" spans="1:10" s="214" customFormat="1" ht="30">
@@ -21834,7 +21810,7 @@
         <v>4</v>
       </c>
       <c r="B27" s="287" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="C27" s="286" t="s">
         <v>272</v>
@@ -21854,13 +21830,13 @@
         <v>12000</v>
       </c>
       <c r="H27" s="288" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I27" s="291" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="J27" s="292" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="30">
@@ -21868,7 +21844,7 @@
         <v>5</v>
       </c>
       <c r="B28" s="183" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C28" s="194" t="s">
         <v>272</v>
@@ -21888,13 +21864,13 @@
         <v>12000</v>
       </c>
       <c r="H28" s="177" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I28" s="264" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="J28" s="270" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="30">
@@ -21902,7 +21878,7 @@
         <v>6</v>
       </c>
       <c r="B29" s="183" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C29" s="194" t="s">
         <v>272</v>
@@ -21922,13 +21898,13 @@
         <v>12000</v>
       </c>
       <c r="H29" s="177" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I29" s="264" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="J29" s="270" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="30">
@@ -21936,7 +21912,7 @@
         <v>7</v>
       </c>
       <c r="B30" s="293" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C30" s="213" t="s">
         <v>271</v>
@@ -21956,13 +21932,13 @@
         <v>8400</v>
       </c>
       <c r="H30" s="281" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I30" s="284" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="J30" s="285" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="31" spans="1:10" s="214" customFormat="1" ht="30">
@@ -21970,7 +21946,7 @@
         <v>8</v>
       </c>
       <c r="B31" s="294" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="C31" s="286" t="s">
         <v>271</v>
@@ -21990,13 +21966,13 @@
         <v>8400</v>
       </c>
       <c r="H31" s="288" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I31" s="291" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="J31" s="292" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="32" spans="1:10" s="214" customFormat="1" ht="30">
@@ -22004,7 +21980,7 @@
         <v>9</v>
       </c>
       <c r="B32" s="244" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="C32" s="243" t="s">
         <v>271</v>
@@ -22024,13 +22000,13 @@
         <v>8400</v>
       </c>
       <c r="H32" s="245" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I32" s="266" t="s">
+        <v>318</v>
+      </c>
+      <c r="J32" s="271" t="s">
         <v>319</v>
-      </c>
-      <c r="J32" s="271" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="33" spans="1:10" s="214" customFormat="1" ht="30">
@@ -22038,7 +22014,7 @@
         <v>10</v>
       </c>
       <c r="B33" s="244" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="C33" s="243" t="s">
         <v>271</v>
@@ -22058,13 +22034,13 @@
         <v>8400</v>
       </c>
       <c r="H33" s="245" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I33" s="266" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="J33" s="271" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="34" spans="1:10" s="166" customFormat="1">
@@ -22100,7 +22076,7 @@
         <v>1</v>
       </c>
       <c r="B35" s="183" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C35" s="192" t="s">
         <v>270</v>
@@ -22120,13 +22096,13 @@
         <v>15600</v>
       </c>
       <c r="H35" s="177" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I35" s="264" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="J35" s="270" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="30">
@@ -22134,7 +22110,7 @@
         <v>2</v>
       </c>
       <c r="B36" s="250" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C36" s="249"/>
       <c r="D36" s="251"/>
@@ -22142,13 +22118,13 @@
       <c r="F36" s="253"/>
       <c r="G36" s="251"/>
       <c r="H36" s="251" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="I36" s="263" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="J36" s="272" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="37" spans="1:10">
@@ -22184,7 +22160,7 @@
         <v>1</v>
       </c>
       <c r="B38" s="176" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="C38" s="193" t="s">
         <v>270</v>
@@ -22204,13 +22180,13 @@
         <v>15600</v>
       </c>
       <c r="H38" s="170" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I38" s="265" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="J38" s="273" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="30">
@@ -22218,7 +22194,7 @@
         <v>2</v>
       </c>
       <c r="B39" s="210" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C39" s="194" t="s">
         <v>272</v>
@@ -22238,13 +22214,13 @@
         <v>12000</v>
       </c>
       <c r="H39" s="170" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I39" s="265" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="J39" s="273" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="40" spans="1:10" s="212" customFormat="1" ht="30">
@@ -22252,7 +22228,7 @@
         <v>3</v>
       </c>
       <c r="B40" s="255" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C40" s="249" t="s">
         <v>272</v>
@@ -22262,13 +22238,13 @@
       <c r="F40" s="258"/>
       <c r="G40" s="256"/>
       <c r="H40" s="256" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="I40" s="262" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="J40" s="274" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="41" spans="1:10" s="212" customFormat="1" ht="30">
@@ -22276,7 +22252,7 @@
         <v>4</v>
       </c>
       <c r="B41" s="255" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C41" s="249" t="s">
         <v>271</v>
@@ -22286,13 +22262,13 @@
       <c r="F41" s="258"/>
       <c r="G41" s="256"/>
       <c r="H41" s="256" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="I41" s="262" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="J41" s="274" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="42" spans="1:10" s="212" customFormat="1">
@@ -22300,7 +22276,7 @@
         <v>5</v>
       </c>
       <c r="B42" s="210" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="C42" s="213" t="s">
         <v>271</v>
@@ -22320,13 +22296,13 @@
         <v>8400</v>
       </c>
       <c r="H42" s="296" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I42" s="299" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="J42" s="300" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="43" spans="1:10" ht="30">
@@ -22334,7 +22310,7 @@
         <v>6</v>
       </c>
       <c r="B43" s="176" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="C43" s="194" t="s">
         <v>272</v>
@@ -22354,13 +22330,13 @@
         <v>12000</v>
       </c>
       <c r="H43" s="170" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I43" s="265" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="J43" s="273" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="44" spans="1:10" ht="30">
@@ -22368,7 +22344,7 @@
         <v>7</v>
       </c>
       <c r="B44" s="176" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="C44" s="195" t="s">
         <v>271</v>
@@ -22388,13 +22364,13 @@
         <v>8400</v>
       </c>
       <c r="H44" s="177" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I44" s="264" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="J44" s="270" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="45" spans="1:10" s="212" customFormat="1" ht="30">
@@ -22402,7 +22378,7 @@
         <v>8</v>
       </c>
       <c r="B45" s="255" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C45" s="249" t="s">
         <v>271</v>
@@ -22414,13 +22390,13 @@
       <c r="F45" s="258"/>
       <c r="G45" s="256"/>
       <c r="H45" s="256" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="I45" s="262" t="s">
+        <v>309</v>
+      </c>
+      <c r="J45" s="274" t="s">
         <v>310</v>
-      </c>
-      <c r="J45" s="274" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="46" spans="1:10">
@@ -22428,7 +22404,7 @@
         <v>267</v>
       </c>
       <c r="B46" s="167" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C46" s="167"/>
       <c r="D46" s="167">
@@ -22476,13 +22452,13 @@
         <v>16800</v>
       </c>
       <c r="H47" s="170" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I47" s="265" t="s">
+        <v>307</v>
+      </c>
+      <c r="J47" s="273" t="s">
         <v>308</v>
-      </c>
-      <c r="J47" s="273" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="48" spans="1:10">
@@ -22510,13 +22486,13 @@
         <v>8400</v>
       </c>
       <c r="H48" s="177" t="s">
+        <v>305</v>
+      </c>
+      <c r="I48" s="264" t="s">
+        <v>309</v>
+      </c>
+      <c r="J48" s="270" t="s">
         <v>306</v>
-      </c>
-      <c r="I48" s="264" t="s">
-        <v>310</v>
-      </c>
-      <c r="J48" s="270" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="49" spans="1:10">
@@ -22524,7 +22500,7 @@
         <v>3</v>
       </c>
       <c r="B49" s="260" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C49" s="249"/>
       <c r="D49" s="256"/>
@@ -22537,13 +22513,13 @@
       </c>
       <c r="G49" s="251"/>
       <c r="H49" s="251" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="I49" s="263" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="J49" s="272" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="50" spans="1:10" ht="30">
@@ -22551,7 +22527,7 @@
         <v>4</v>
       </c>
       <c r="B50" s="260" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C50" s="249"/>
       <c r="D50" s="251"/>
@@ -22564,19 +22540,19 @@
       </c>
       <c r="G50" s="256"/>
       <c r="H50" s="256" t="s">
+        <v>302</v>
+      </c>
+      <c r="I50" s="262" t="s">
+        <v>309</v>
+      </c>
+      <c r="J50" s="274" t="s">
         <v>303</v>
-      </c>
-      <c r="I50" s="262" t="s">
-        <v>310</v>
-      </c>
-      <c r="J50" s="274" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="51" spans="1:10" ht="15.75" thickBot="1">
       <c r="A51" s="197"/>
       <c r="B51" s="198" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C51" s="189"/>
       <c r="D51" s="174">
@@ -22585,15 +22561,15 @@
       </c>
       <c r="E51" s="233">
         <f>E6+E10+E12+E18+E23+E34+E37+E46</f>
-        <v>31793100</v>
+        <v>31423100</v>
       </c>
       <c r="F51" s="235">
         <f>F6+F10+F12+F18+F23+F34+F37+F46</f>
-        <v>25595335.199999999</v>
+        <v>25302295.199999999</v>
       </c>
       <c r="G51" s="234">
         <f>G6+G10+G12+G18+G23+G34+G37+G46</f>
-        <v>366000</v>
+        <v>361560</v>
       </c>
       <c r="H51" s="234"/>
       <c r="I51" s="234"/>
@@ -22602,7 +22578,7 @@
     <row r="52" spans="1:10" ht="45">
       <c r="A52" s="241"/>
       <c r="B52" s="217" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C52" s="186"/>
       <c r="D52" s="1"/>
@@ -22612,7 +22588,7 @@
     <row r="53" spans="1:10">
       <c r="A53" s="241"/>
       <c r="B53" s="261" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C53" s="190"/>
       <c r="D53" s="129"/>
@@ -29707,12 +29683,12 @@
   <sheetData>
     <row r="1" spans="1:6" ht="16.5">
       <c r="A1" s="277" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="30" customHeight="1">
       <c r="A3" s="450" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B3" s="450"/>
       <c r="C3" s="450"/>
@@ -29722,7 +29698,7 @@
     </row>
     <row r="4" spans="1:6" ht="44.1" customHeight="1">
       <c r="A4" s="450" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B4" s="450"/>
       <c r="C4" s="450"/>
@@ -29732,7 +29708,7 @@
     </row>
     <row r="5" spans="1:6" ht="44.1" customHeight="1">
       <c r="A5" s="450" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B5" s="450"/>
       <c r="C5" s="450"/>
@@ -29742,7 +29718,7 @@
     </row>
     <row r="6" spans="1:6" ht="30" customHeight="1">
       <c r="A6" s="450" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B6" s="450"/>
       <c r="C6" s="450"/>
@@ -29752,7 +29728,7 @@
     </row>
     <row r="7" spans="1:6" ht="30" customHeight="1">
       <c r="A7" s="450" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B7" s="450"/>
       <c r="C7" s="450"/>
@@ -29762,272 +29738,272 @@
     </row>
     <row r="9" spans="1:6" ht="25.5">
       <c r="A9" s="279" t="s">
+        <v>337</v>
+      </c>
+      <c r="B9" s="279" t="s">
         <v>338</v>
       </c>
-      <c r="B9" s="279" t="s">
+      <c r="C9" s="279" t="s">
         <v>339</v>
       </c>
-      <c r="C9" s="279" t="s">
+      <c r="D9" s="279" t="s">
         <v>340</v>
       </c>
-      <c r="D9" s="279" t="s">
+      <c r="E9" s="279" t="s">
         <v>341</v>
       </c>
-      <c r="E9" s="279" t="s">
+      <c r="F9" s="279" t="s">
         <v>342</v>
-      </c>
-      <c r="F9" s="279" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="51">
       <c r="A10" s="278" t="s">
+        <v>343</v>
+      </c>
+      <c r="B10" s="280" t="s">
         <v>344</v>
       </c>
-      <c r="B10" s="280" t="s">
+      <c r="C10" s="280" t="s">
         <v>345</v>
       </c>
-      <c r="C10" s="280" t="s">
+      <c r="D10" s="278" t="s">
         <v>346</v>
       </c>
-      <c r="D10" s="278" t="s">
+      <c r="E10" s="278" t="s">
         <v>347</v>
       </c>
-      <c r="E10" s="278" t="s">
+      <c r="F10" s="278" t="s">
         <v>348</v>
-      </c>
-      <c r="F10" s="278" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="76.5">
       <c r="A11" s="278" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B11" s="280" t="s">
+        <v>349</v>
+      </c>
+      <c r="C11" s="280" t="s">
         <v>350</v>
       </c>
-      <c r="C11" s="280" t="s">
+      <c r="D11" s="278" t="s">
         <v>351</v>
       </c>
-      <c r="D11" s="278" t="s">
+      <c r="E11" s="278" t="s">
         <v>352</v>
       </c>
-      <c r="E11" s="278" t="s">
+      <c r="F11" s="278" t="s">
         <v>353</v>
-      </c>
-      <c r="F11" s="278" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="51">
       <c r="A12" s="278" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B12" s="280" t="s">
+        <v>354</v>
+      </c>
+      <c r="C12" s="280" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="280" t="s">
+      <c r="D12" s="278" t="s">
         <v>356</v>
       </c>
-      <c r="D12" s="278" t="s">
+      <c r="E12" s="278" t="s">
         <v>357</v>
       </c>
-      <c r="E12" s="278" t="s">
+      <c r="F12" s="278" t="s">
         <v>358</v>
-      </c>
-      <c r="F12" s="278" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="63.75">
       <c r="A13" s="278" t="s">
+        <v>359</v>
+      </c>
+      <c r="B13" s="280" t="s">
         <v>360</v>
       </c>
-      <c r="B13" s="280" t="s">
+      <c r="C13" s="280" t="s">
         <v>361</v>
       </c>
-      <c r="C13" s="280" t="s">
+      <c r="D13" s="278" t="s">
         <v>362</v>
       </c>
-      <c r="D13" s="278" t="s">
+      <c r="E13" s="278" t="s">
         <v>363</v>
       </c>
-      <c r="E13" s="278" t="s">
+      <c r="F13" s="278" t="s">
         <v>364</v>
-      </c>
-      <c r="F13" s="278" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="51">
       <c r="A14" s="278" t="s">
+        <v>365</v>
+      </c>
+      <c r="B14" s="280" t="s">
         <v>366</v>
       </c>
-      <c r="B14" s="280" t="s">
+      <c r="C14" s="280" t="s">
         <v>367</v>
       </c>
-      <c r="C14" s="280" t="s">
+      <c r="D14" s="278" t="s">
         <v>368</v>
       </c>
-      <c r="D14" s="278" t="s">
+      <c r="E14" s="278" t="s">
         <v>369</v>
       </c>
-      <c r="E14" s="278" t="s">
+      <c r="F14" s="278" t="s">
         <v>370</v>
-      </c>
-      <c r="F14" s="278" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="51">
       <c r="A15" s="278" t="s">
+        <v>371</v>
+      </c>
+      <c r="B15" s="280" t="s">
         <v>372</v>
       </c>
-      <c r="B15" s="280" t="s">
+      <c r="C15" s="280" t="s">
         <v>373</v>
       </c>
-      <c r="C15" s="280" t="s">
+      <c r="D15" s="278" t="s">
         <v>374</v>
       </c>
-      <c r="D15" s="278" t="s">
+      <c r="E15" s="278" t="s">
         <v>375</v>
       </c>
-      <c r="E15" s="278" t="s">
+      <c r="F15" s="278" t="s">
         <v>376</v>
-      </c>
-      <c r="F15" s="278" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="51">
       <c r="A16" s="278" t="s">
+        <v>377</v>
+      </c>
+      <c r="B16" s="280" t="s">
+        <v>360</v>
+      </c>
+      <c r="C16" s="280" t="s">
         <v>378</v>
       </c>
-      <c r="B16" s="280" t="s">
-        <v>361</v>
-      </c>
-      <c r="C16" s="280" t="s">
+      <c r="D16" s="278" t="s">
         <v>379</v>
       </c>
-      <c r="D16" s="278" t="s">
+      <c r="E16" s="278" t="s">
         <v>380</v>
       </c>
-      <c r="E16" s="278" t="s">
+      <c r="F16" s="278" t="s">
         <v>381</v>
-      </c>
-      <c r="F16" s="278" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="25.5">
       <c r="A17" s="278" t="s">
+        <v>382</v>
+      </c>
+      <c r="B17" s="280" t="s">
+        <v>360</v>
+      </c>
+      <c r="C17" s="280" t="s">
+        <v>378</v>
+      </c>
+      <c r="D17" s="278" t="s">
         <v>383</v>
       </c>
-      <c r="B17" s="280" t="s">
-        <v>361</v>
-      </c>
-      <c r="C17" s="280" t="s">
-        <v>379</v>
-      </c>
-      <c r="D17" s="278" t="s">
+      <c r="E17" s="278" t="s">
+        <v>357</v>
+      </c>
+      <c r="F17" s="278" t="s">
         <v>384</v>
-      </c>
-      <c r="E17" s="278" t="s">
-        <v>358</v>
-      </c>
-      <c r="F17" s="278" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="38.25">
       <c r="A18" s="278" t="s">
+        <v>385</v>
+      </c>
+      <c r="B18" s="280" t="s">
+        <v>360</v>
+      </c>
+      <c r="C18" s="280" t="s">
+        <v>378</v>
+      </c>
+      <c r="D18" s="278" t="s">
         <v>386</v>
       </c>
-      <c r="B18" s="280" t="s">
-        <v>361</v>
-      </c>
-      <c r="C18" s="280" t="s">
-        <v>379</v>
-      </c>
-      <c r="D18" s="278" t="s">
+      <c r="E18" s="278" t="s">
         <v>387</v>
       </c>
-      <c r="E18" s="278" t="s">
+      <c r="F18" s="278" t="s">
         <v>388</v>
-      </c>
-      <c r="F18" s="278" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="38.25">
       <c r="A19" s="278" t="s">
+        <v>389</v>
+      </c>
+      <c r="B19" s="280" t="s">
+        <v>372</v>
+      </c>
+      <c r="C19" s="280" t="s">
+        <v>378</v>
+      </c>
+      <c r="D19" s="278" t="s">
         <v>390</v>
       </c>
-      <c r="B19" s="280" t="s">
-        <v>373</v>
-      </c>
-      <c r="C19" s="280" t="s">
-        <v>379</v>
-      </c>
-      <c r="D19" s="278" t="s">
+      <c r="E19" s="278" t="s">
         <v>391</v>
       </c>
-      <c r="E19" s="278" t="s">
+      <c r="F19" s="278" t="s">
         <v>392</v>
-      </c>
-      <c r="F19" s="278" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="51">
       <c r="A20" s="278" t="s">
+        <v>393</v>
+      </c>
+      <c r="B20" s="280" t="s">
+        <v>372</v>
+      </c>
+      <c r="C20" s="280" t="s">
+        <v>378</v>
+      </c>
+      <c r="D20" s="278" t="s">
         <v>394</v>
       </c>
-      <c r="B20" s="280" t="s">
-        <v>373</v>
-      </c>
-      <c r="C20" s="280" t="s">
-        <v>379</v>
-      </c>
-      <c r="D20" s="278" t="s">
+      <c r="E20" s="278" t="s">
         <v>395</v>
       </c>
-      <c r="E20" s="278" t="s">
+      <c r="F20" s="278" t="s">
         <v>396</v>
-      </c>
-      <c r="F20" s="278" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="25.5">
       <c r="A21" s="278" t="s">
+        <v>397</v>
+      </c>
+      <c r="B21" s="280" t="s">
+        <v>372</v>
+      </c>
+      <c r="C21" s="280" t="s">
+        <v>378</v>
+      </c>
+      <c r="D21" s="278" t="s">
         <v>398</v>
       </c>
-      <c r="B21" s="280" t="s">
-        <v>373</v>
-      </c>
-      <c r="C21" s="280" t="s">
-        <v>379</v>
-      </c>
-      <c r="D21" s="278" t="s">
+      <c r="E21" s="278" t="s">
         <v>399</v>
       </c>
-      <c r="E21" s="278" t="s">
+      <c r="F21" s="278" t="s">
         <v>400</v>
-      </c>
-      <c r="F21" s="278" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="276" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="27" customHeight="1">
       <c r="A24" s="449" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B24" s="449"/>
       <c r="C24" s="449"/>
@@ -30037,7 +30013,7 @@
     </row>
     <row r="25" spans="1:6" ht="27" customHeight="1">
       <c r="A25" s="449" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B25" s="449"/>
       <c r="C25" s="449"/>
@@ -30047,7 +30023,7 @@
     </row>
     <row r="26" spans="1:6" ht="27" customHeight="1">
       <c r="A26" s="449" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B26" s="449"/>
       <c r="C26" s="449"/>
@@ -30057,7 +30033,7 @@
     </row>
     <row r="27" spans="1:6" ht="27" customHeight="1">
       <c r="A27" s="449" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B27" s="449"/>
       <c r="C27" s="449"/>
@@ -30067,7 +30043,7 @@
     </row>
     <row r="28" spans="1:6" ht="27" customHeight="1">
       <c r="A28" s="449" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B28" s="449"/>
       <c r="C28" s="449"/>
@@ -30077,7 +30053,7 @@
     </row>
     <row r="29" spans="1:6" ht="27" customHeight="1">
       <c r="A29" s="449" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B29" s="449"/>
       <c r="C29" s="449"/>
@@ -30087,7 +30063,7 @@
     </row>
     <row r="30" spans="1:6" ht="27" customHeight="1">
       <c r="A30" s="449" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B30" s="449"/>
       <c r="C30" s="449"/>
@@ -30097,7 +30073,7 @@
     </row>
     <row r="31" spans="1:6" ht="27" customHeight="1">
       <c r="A31" s="449" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B31" s="449"/>
       <c r="C31" s="449"/>

--- a/TAZA/_документы/ШР ЦАКФ.xlsx
+++ b/TAZA/_документы/ШР ЦАКФ.xlsx
@@ -2153,9 +2153,6 @@
     <t>12.2026</t>
   </si>
   <si>
-    <t>*приход с 12.2026 и в 2027 году выделен сиреневым (с 12.2026 – Арманов, Мирам; остальные – с 02.2027)</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">Заместитель Главного исполнительного директора Фонда / </t>
     </r>
@@ -2428,6 +2425,9 @@
   </si>
   <si>
     <t>Менеджер проектов – эколог (отходы, вода, воздух) / вакансия</t>
+  </si>
+  <si>
+    <t>*приход с 12.2026 и в 2027 году выделен сиреневым (с 12.2026 – Өміртай А.; остальные – с 02.2027)</t>
   </si>
 </sst>
 </file>
@@ -4736,7 +4736,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="451">
+  <cellXfs count="450">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -5534,9 +5534,6 @@
     <xf numFmtId="0" fontId="4" fillId="71" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="71" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="4" fillId="71" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5579,60 +5576,174 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="37" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="38" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="36" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="32" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="37" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="38" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="36" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="33" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="34" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="35" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="32" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="39" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="1" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="39" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="37" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="38" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="37" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="38" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="36" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="10" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="2" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="17" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="39" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="3" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="39" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="3" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="1" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="10" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="33" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="34" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="35" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="177" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -5684,119 +5795,29 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="37" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="38" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="36" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="39" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="33" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="35" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="39" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="3" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="37" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="36" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="10" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="37" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="38" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="36" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="33" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="34" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="35" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="1" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="32" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="37" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="38" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="36" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="37" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="38" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="39" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="3" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="10" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="2" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="17" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="32" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="33" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="34" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="35" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="39" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="1" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="25" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -5807,47 +5828,98 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="36" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="33" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="35" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="37" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="36" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="0" xfId="177" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="3" borderId="38" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="37" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="36" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="46" fillId="2" borderId="37" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="46" fillId="2" borderId="38" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="37" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="36" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="0" xfId="177" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="46" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -5858,15 +5930,6 @@
     <xf numFmtId="49" fontId="46" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -5879,13 +5942,67 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5896,126 +6013,6 @@
     </xf>
     <xf numFmtId="0" fontId="46" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -6357,7 +6354,7 @@
         <xdr:cNvPr id="2" name="TextBox 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6415,7 +6412,7 @@
         <xdr:cNvPr id="3" name="TextBox 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000003000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6470,7 +6467,7 @@
         <xdr:cNvPr id="4" name="TextBox 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000004000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000004000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10247,49 +10244,49 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="302" t="s">
+      <c r="A2" s="309" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="302"/>
+      <c r="B2" s="309"/>
       <c r="C2" s="132" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="303" t="s">
+      <c r="A3" s="314" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="304"/>
+      <c r="B3" s="315"/>
       <c r="C3" s="133"/>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="303" t="s">
+      <c r="A4" s="314" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="304" t="s">
+      <c r="B4" s="315" t="s">
         <v>27</v>
       </c>
       <c r="C4" s="133"/>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="301" t="s">
+      <c r="A5" s="300" t="s">
         <v>242</v>
       </c>
-      <c r="B5" s="301"/>
+      <c r="B5" s="300"/>
       <c r="C5" s="133"/>
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1">
-      <c r="A6" s="303" t="s">
+      <c r="A6" s="314" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="304"/>
+      <c r="B6" s="315"/>
       <c r="C6" s="134"/>
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1">
-      <c r="A7" s="303" t="s">
+      <c r="A7" s="314" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="304"/>
+      <c r="B7" s="315"/>
       <c r="C7" s="135"/>
     </row>
     <row r="8" spans="1:4">
@@ -10306,40 +10303,40 @@
       <c r="C9" s="2"/>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="307" t="s">
+      <c r="A10" s="316" t="s">
         <v>31</v>
       </c>
-      <c r="B10" s="307"/>
-      <c r="C10" s="307"/>
+      <c r="B10" s="316"/>
+      <c r="C10" s="316"/>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="302" t="s">
+      <c r="A11" s="309" t="s">
         <v>2</v>
       </c>
-      <c r="B11" s="302"/>
+      <c r="B11" s="309"/>
       <c r="C11" s="132" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="301" t="s">
+      <c r="A12" s="300" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="301"/>
+      <c r="B12" s="300"/>
       <c r="C12" s="136"/>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="301" t="s">
+      <c r="A13" s="300" t="s">
         <v>33</v>
       </c>
-      <c r="B13" s="301"/>
+      <c r="B13" s="300"/>
       <c r="C13" s="136"/>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="301" t="s">
+      <c r="A14" s="300" t="s">
         <v>34</v>
       </c>
-      <c r="B14" s="301"/>
+      <c r="B14" s="300"/>
       <c r="C14" s="136"/>
     </row>
     <row r="15" spans="1:4">
@@ -10357,10 +10354,10 @@
       <c r="D16" s="3"/>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="308" t="s">
+      <c r="A17" s="307" t="s">
         <v>36</v>
       </c>
-      <c r="B17" s="309"/>
+      <c r="B17" s="308"/>
       <c r="C17" s="137">
         <f>C8-C15</f>
         <v>0</v>
@@ -10376,42 +10373,42 @@
       <c r="C19" s="4"/>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="302" t="s">
+      <c r="A20" s="309" t="s">
         <v>2</v>
       </c>
-      <c r="B20" s="302"/>
+      <c r="B20" s="309"/>
       <c r="C20" s="132" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="301" t="s">
+      <c r="A21" s="300" t="s">
         <v>26</v>
       </c>
-      <c r="B21" s="301"/>
+      <c r="B21" s="300"/>
       <c r="C21" s="138"/>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="301" t="s">
+      <c r="A22" s="300" t="s">
         <v>3</v>
       </c>
-      <c r="B22" s="301" t="s">
+      <c r="B22" s="300" t="s">
         <v>27</v>
       </c>
       <c r="C22" s="138"/>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" s="301" t="s">
+      <c r="A23" s="300" t="s">
         <v>28</v>
       </c>
-      <c r="B23" s="301"/>
+      <c r="B23" s="300"/>
       <c r="C23" s="138"/>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="301" t="s">
+      <c r="A24" s="300" t="s">
         <v>243</v>
       </c>
-      <c r="B24" s="301"/>
+      <c r="B24" s="300"/>
       <c r="C24" s="138"/>
       <c r="D24" s="4"/>
     </row>
@@ -10431,10 +10428,10 @@
       <c r="C26" s="312"/>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="302" t="s">
+      <c r="A27" s="309" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="302"/>
+      <c r="B27" s="309"/>
       <c r="C27" s="138"/>
     </row>
     <row r="28" spans="1:4">
@@ -10458,48 +10455,48 @@
       <c r="C30" s="2"/>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="302" t="s">
+      <c r="A31" s="309" t="s">
         <v>2</v>
       </c>
-      <c r="B31" s="302"/>
+      <c r="B31" s="309"/>
       <c r="C31" s="132" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="301" t="s">
+      <c r="A32" s="300" t="s">
         <v>26</v>
       </c>
-      <c r="B32" s="301"/>
+      <c r="B32" s="300"/>
       <c r="C32" s="143"/>
     </row>
     <row r="33" spans="1:4">
-      <c r="A33" s="301" t="s">
+      <c r="A33" s="300" t="s">
         <v>3</v>
       </c>
-      <c r="B33" s="301" t="s">
+      <c r="B33" s="300" t="s">
         <v>27</v>
       </c>
       <c r="C33" s="143"/>
     </row>
     <row r="34" spans="1:4">
-      <c r="A34" s="301" t="s">
+      <c r="A34" s="300" t="s">
         <v>28</v>
       </c>
-      <c r="B34" s="301"/>
+      <c r="B34" s="300"/>
       <c r="C34" s="143"/>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="301" t="s">
+      <c r="A35" s="300" t="s">
         <v>41</v>
       </c>
-      <c r="B35" s="301"/>
+      <c r="B35" s="300"/>
       <c r="C35" s="143"/>
       <c r="D35" s="3"/>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="314"/>
-      <c r="B36" s="315"/>
+      <c r="A36" s="301"/>
+      <c r="B36" s="302"/>
       <c r="C36" s="144">
         <f>SUM(C32:C35)</f>
         <v>0</v>
@@ -10511,10 +10508,10 @@
       <c r="C37" s="8"/>
     </row>
     <row r="38" spans="1:4">
-      <c r="A38" s="316" t="s">
+      <c r="A38" s="303" t="s">
         <v>42</v>
       </c>
-      <c r="B38" s="317"/>
+      <c r="B38" s="304"/>
       <c r="C38" s="145">
         <f>C28-C36</f>
         <v>0</v>
@@ -10537,11 +10534,18 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A13:B13"/>
     <mergeCell ref="A32:B32"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="A17:B17"/>
@@ -10554,18 +10558,11 @@
     <mergeCell ref="A27:B27"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A38:B38"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -10586,38 +10583,38 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:7" ht="33" customHeight="1">
-      <c r="A3" s="318" t="s">
+      <c r="A3" s="317" t="s">
         <v>244</v>
       </c>
-      <c r="B3" s="318" t="s">
+      <c r="B3" s="317" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="318" t="s">
+      <c r="C3" s="317" t="s">
         <v>246</v>
       </c>
-      <c r="D3" s="318" t="s">
+      <c r="D3" s="317" t="s">
         <v>247</v>
       </c>
-      <c r="E3" s="318" t="s">
+      <c r="E3" s="317" t="s">
         <v>245</v>
       </c>
-      <c r="F3" s="318"/>
-      <c r="G3" s="318" t="s">
+      <c r="F3" s="317"/>
+      <c r="G3" s="317" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="53.25" customHeight="1">
-      <c r="A4" s="318"/>
-      <c r="B4" s="318"/>
-      <c r="C4" s="318"/>
-      <c r="D4" s="318"/>
+      <c r="A4" s="317"/>
+      <c r="B4" s="317"/>
+      <c r="C4" s="317"/>
+      <c r="D4" s="317"/>
       <c r="E4" s="146" t="s">
         <v>248</v>
       </c>
       <c r="F4" s="146" t="s">
         <v>249</v>
       </c>
-      <c r="G4" s="318"/>
+      <c r="G4" s="317"/>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="132">
@@ -10733,11 +10730,11 @@
     </row>
     <row r="13" spans="1:7" ht="18">
       <c r="A13" s="1"/>
-      <c r="B13" s="319" t="s">
+      <c r="B13" s="318" t="s">
         <v>258</v>
       </c>
-      <c r="C13" s="319"/>
-      <c r="D13" s="319"/>
+      <c r="C13" s="318"/>
+      <c r="D13" s="318"/>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
@@ -10833,11 +10830,11 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="1"/>
-      <c r="B19" s="302" t="s">
+      <c r="B19" s="309" t="s">
         <v>259</v>
       </c>
-      <c r="C19" s="302"/>
-      <c r="D19" s="302"/>
+      <c r="C19" s="309"/>
+      <c r="D19" s="309"/>
       <c r="E19" s="162" t="e">
         <f>E15/E18</f>
         <v>#REF!</v>
@@ -10914,17 +10911,17 @@
       <c r="A1" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="320" t="s">
+      <c r="B1" s="357" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="320"/>
-      <c r="D1" s="320"/>
-      <c r="E1" s="320"/>
-      <c r="F1" s="320"/>
-      <c r="G1" s="320"/>
-      <c r="H1" s="320"/>
-      <c r="I1" s="320"/>
-      <c r="J1" s="320"/>
+      <c r="C1" s="357"/>
+      <c r="D1" s="357"/>
+      <c r="E1" s="357"/>
+      <c r="F1" s="357"/>
+      <c r="G1" s="357"/>
+      <c r="H1" s="357"/>
+      <c r="I1" s="357"/>
+      <c r="J1" s="357"/>
       <c r="K1" s="85"/>
       <c r="O1" s="51"/>
     </row>
@@ -10962,17 +10959,17 @@
       <c r="A3" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="321" t="s">
+      <c r="B3" s="358" t="s">
         <v>201</v>
       </c>
-      <c r="C3" s="321"/>
-      <c r="D3" s="321"/>
-      <c r="E3" s="321"/>
-      <c r="F3" s="321"/>
-      <c r="G3" s="321"/>
-      <c r="H3" s="321"/>
-      <c r="I3" s="321"/>
-      <c r="J3" s="321"/>
+      <c r="C3" s="358"/>
+      <c r="D3" s="358"/>
+      <c r="E3" s="358"/>
+      <c r="F3" s="358"/>
+      <c r="G3" s="358"/>
+      <c r="H3" s="358"/>
+      <c r="I3" s="358"/>
+      <c r="J3" s="358"/>
       <c r="K3" s="88"/>
       <c r="O3" s="51"/>
     </row>
@@ -10980,17 +10977,17 @@
       <c r="A4" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="322" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="322"/>
-      <c r="D4" s="322"/>
-      <c r="E4" s="322"/>
-      <c r="F4" s="322"/>
-      <c r="G4" s="322"/>
-      <c r="H4" s="322"/>
-      <c r="I4" s="322"/>
-      <c r="J4" s="322"/>
+      <c r="B4" s="359" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="359"/>
+      <c r="D4" s="359"/>
+      <c r="E4" s="359"/>
+      <c r="F4" s="359"/>
+      <c r="G4" s="359"/>
+      <c r="H4" s="359"/>
+      <c r="I4" s="359"/>
+      <c r="J4" s="359"/>
       <c r="K4" s="89"/>
       <c r="O4" s="51"/>
     </row>
@@ -10998,17 +10995,17 @@
       <c r="A5" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="323" t="s">
+      <c r="B5" s="360" t="s">
         <v>47</v>
       </c>
-      <c r="C5" s="323"/>
-      <c r="D5" s="323"/>
-      <c r="E5" s="323"/>
-      <c r="F5" s="323"/>
-      <c r="G5" s="323"/>
-      <c r="H5" s="323"/>
-      <c r="I5" s="323"/>
-      <c r="J5" s="323"/>
+      <c r="C5" s="360"/>
+      <c r="D5" s="360"/>
+      <c r="E5" s="360"/>
+      <c r="F5" s="360"/>
+      <c r="G5" s="360"/>
+      <c r="H5" s="360"/>
+      <c r="I5" s="360"/>
+      <c r="J5" s="360"/>
       <c r="K5" s="90"/>
       <c r="O5" s="51"/>
     </row>
@@ -11016,17 +11013,17 @@
       <c r="A6" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B6" s="323" t="s">
+      <c r="B6" s="360" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="323"/>
-      <c r="D6" s="323"/>
-      <c r="E6" s="323"/>
-      <c r="F6" s="323"/>
-      <c r="G6" s="323"/>
-      <c r="H6" s="323"/>
-      <c r="I6" s="323"/>
-      <c r="J6" s="323"/>
+      <c r="C6" s="360"/>
+      <c r="D6" s="360"/>
+      <c r="E6" s="360"/>
+      <c r="F6" s="360"/>
+      <c r="G6" s="360"/>
+      <c r="H6" s="360"/>
+      <c r="I6" s="360"/>
+      <c r="J6" s="360"/>
       <c r="K6" s="90"/>
       <c r="O6" s="51"/>
     </row>
@@ -11034,15 +11031,15 @@
       <c r="A7" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B7" s="324" t="s">
+      <c r="B7" s="361" t="s">
         <v>183</v>
       </c>
-      <c r="C7" s="324"/>
-      <c r="D7" s="324"/>
-      <c r="E7" s="324"/>
-      <c r="F7" s="324"/>
-      <c r="G7" s="324"/>
-      <c r="H7" s="324"/>
+      <c r="C7" s="361"/>
+      <c r="D7" s="361"/>
+      <c r="E7" s="361"/>
+      <c r="F7" s="361"/>
+      <c r="G7" s="361"/>
+      <c r="H7" s="361"/>
       <c r="I7" s="91"/>
       <c r="J7" s="71" t="s">
         <v>50</v>
@@ -11068,51 +11065,51 @@
       <c r="A22" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B22" s="325" t="s">
+      <c r="B22" s="362" t="s">
         <v>0</v>
       </c>
-      <c r="C22" s="328" t="s">
+      <c r="C22" s="365" t="s">
         <v>51</v>
       </c>
-      <c r="D22" s="329"/>
-      <c r="E22" s="329"/>
-      <c r="F22" s="329"/>
-      <c r="G22" s="330"/>
+      <c r="D22" s="366"/>
+      <c r="E22" s="366"/>
+      <c r="F22" s="366"/>
+      <c r="G22" s="367"/>
       <c r="H22" s="93"/>
-      <c r="I22" s="329" t="s">
+      <c r="I22" s="366" t="s">
         <v>52</v>
       </c>
-      <c r="J22" s="330"/>
+      <c r="J22" s="367"/>
       <c r="K22" s="94"/>
     </row>
     <row r="23" spans="1:16" ht="12" customHeight="1">
       <c r="A23" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="326"/>
-      <c r="C23" s="331"/>
-      <c r="D23" s="332"/>
-      <c r="E23" s="332"/>
-      <c r="F23" s="332"/>
-      <c r="G23" s="333"/>
+      <c r="B23" s="363"/>
+      <c r="C23" s="368"/>
+      <c r="D23" s="369"/>
+      <c r="E23" s="369"/>
+      <c r="F23" s="369"/>
+      <c r="G23" s="370"/>
       <c r="H23" s="95"/>
-      <c r="I23" s="332"/>
-      <c r="J23" s="333"/>
+      <c r="I23" s="369"/>
+      <c r="J23" s="370"/>
       <c r="K23" s="94"/>
     </row>
     <row r="24" spans="1:16" ht="24" customHeight="1">
       <c r="A24" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B24" s="327"/>
-      <c r="C24" s="334"/>
-      <c r="D24" s="335"/>
-      <c r="E24" s="335"/>
-      <c r="F24" s="335"/>
-      <c r="G24" s="336"/>
+      <c r="B24" s="364"/>
+      <c r="C24" s="371"/>
+      <c r="D24" s="372"/>
+      <c r="E24" s="372"/>
+      <c r="F24" s="372"/>
+      <c r="G24" s="373"/>
       <c r="H24" s="96"/>
-      <c r="I24" s="335"/>
-      <c r="J24" s="336"/>
+      <c r="I24" s="372"/>
+      <c r="J24" s="373"/>
       <c r="K24" s="94"/>
     </row>
     <row r="25" spans="1:16" ht="15.75" hidden="1" customHeight="1"/>
@@ -11154,13 +11151,13 @@
       <c r="B29" s="58">
         <v>1</v>
       </c>
-      <c r="C29" s="337" t="s">
+      <c r="C29" s="323" t="s">
         <v>202</v>
       </c>
-      <c r="D29" s="338"/>
-      <c r="E29" s="338"/>
-      <c r="F29" s="338"/>
-      <c r="G29" s="339"/>
+      <c r="D29" s="324"/>
+      <c r="E29" s="324"/>
+      <c r="F29" s="324"/>
+      <c r="G29" s="325"/>
       <c r="H29" s="97"/>
       <c r="I29" s="97" t="e">
         <f>I35+I44+I46+I47+I50+#REF!+I68+I71+I72+I73+I77+I89+I97+I101+I106+I108+I116+I131+I142+I146+I147+I154+I32+I34+#REF!+#REF!+I151+#REF!+I98+I113+I155</f>
@@ -11177,15 +11174,15 @@
       <c r="B30" s="58">
         <v>2</v>
       </c>
-      <c r="C30" s="340" t="s">
+      <c r="C30" s="332" t="s">
         <v>54</v>
       </c>
-      <c r="D30" s="337" t="s">
+      <c r="D30" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E30" s="338"/>
-      <c r="F30" s="338"/>
-      <c r="G30" s="339"/>
+      <c r="E30" s="324"/>
+      <c r="F30" s="324"/>
+      <c r="G30" s="325"/>
       <c r="H30" s="97"/>
       <c r="I30" s="97"/>
       <c r="J30" s="99" t="e">
@@ -11205,15 +11202,15 @@
       <c r="B31" s="58">
         <v>3</v>
       </c>
-      <c r="C31" s="341"/>
-      <c r="D31" s="343" t="s">
+      <c r="C31" s="333"/>
+      <c r="D31" s="342" t="s">
         <v>55</v>
       </c>
-      <c r="E31" s="346" t="s">
+      <c r="E31" s="319" t="s">
         <v>56</v>
       </c>
-      <c r="F31" s="347"/>
-      <c r="G31" s="348"/>
+      <c r="F31" s="320"/>
+      <c r="G31" s="321"/>
       <c r="H31" s="72"/>
       <c r="I31" s="72"/>
       <c r="J31" s="100"/>
@@ -11230,13 +11227,13 @@
       <c r="B32" s="58">
         <v>4</v>
       </c>
-      <c r="C32" s="341"/>
-      <c r="D32" s="344"/>
-      <c r="E32" s="346" t="s">
+      <c r="C32" s="333"/>
+      <c r="D32" s="343"/>
+      <c r="E32" s="319" t="s">
         <v>57</v>
       </c>
-      <c r="F32" s="347"/>
-      <c r="G32" s="348"/>
+      <c r="F32" s="320"/>
+      <c r="G32" s="321"/>
       <c r="H32" s="72"/>
       <c r="I32" s="72"/>
       <c r="J32" s="81" t="e">
@@ -11256,13 +11253,13 @@
       <c r="B33" s="58">
         <v>5</v>
       </c>
-      <c r="C33" s="341"/>
-      <c r="D33" s="344"/>
-      <c r="E33" s="349" t="s">
+      <c r="C33" s="333"/>
+      <c r="D33" s="343"/>
+      <c r="E33" s="352" t="s">
         <v>58</v>
       </c>
-      <c r="F33" s="350"/>
-      <c r="G33" s="351"/>
+      <c r="F33" s="353"/>
+      <c r="G33" s="354"/>
       <c r="H33" s="72"/>
       <c r="I33" s="72"/>
       <c r="J33" s="81"/>
@@ -11275,13 +11272,13 @@
       <c r="B34" s="58">
         <v>6</v>
       </c>
-      <c r="C34" s="342"/>
-      <c r="D34" s="345"/>
-      <c r="E34" s="353" t="s">
+      <c r="C34" s="349"/>
+      <c r="D34" s="351"/>
+      <c r="E34" s="329" t="s">
         <v>170</v>
       </c>
-      <c r="F34" s="353"/>
-      <c r="G34" s="353"/>
+      <c r="F34" s="329"/>
+      <c r="G34" s="329"/>
       <c r="H34" s="72"/>
       <c r="I34" s="72"/>
       <c r="J34" s="81" t="e">
@@ -11297,15 +11294,15 @@
       <c r="B35" s="58">
         <v>7</v>
       </c>
-      <c r="C35" s="340" t="s">
+      <c r="C35" s="332" t="s">
         <v>171</v>
       </c>
-      <c r="D35" s="337" t="s">
+      <c r="D35" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E35" s="354"/>
-      <c r="F35" s="354"/>
-      <c r="G35" s="355"/>
+      <c r="E35" s="355"/>
+      <c r="F35" s="355"/>
+      <c r="G35" s="356"/>
       <c r="H35" s="97"/>
       <c r="I35" s="101">
         <f>I36+I37</f>
@@ -11321,15 +11318,15 @@
       <c r="B36" s="58">
         <v>8</v>
       </c>
-      <c r="C36" s="341"/>
-      <c r="D36" s="343" t="s">
+      <c r="C36" s="333"/>
+      <c r="D36" s="342" t="s">
         <v>55</v>
       </c>
-      <c r="E36" s="356" t="s">
+      <c r="E36" s="336" t="s">
         <v>172</v>
       </c>
-      <c r="F36" s="357"/>
-      <c r="G36" s="358"/>
+      <c r="F36" s="337"/>
+      <c r="G36" s="338"/>
       <c r="H36" s="72"/>
       <c r="I36" s="72"/>
       <c r="J36" s="81" t="e">
@@ -11346,13 +11343,13 @@
       <c r="B37" s="58">
         <v>9</v>
       </c>
-      <c r="C37" s="342"/>
-      <c r="D37" s="352"/>
-      <c r="E37" s="356" t="s">
+      <c r="C37" s="349"/>
+      <c r="D37" s="350"/>
+      <c r="E37" s="336" t="s">
         <v>173</v>
       </c>
-      <c r="F37" s="357"/>
-      <c r="G37" s="358"/>
+      <c r="F37" s="337"/>
+      <c r="G37" s="338"/>
       <c r="H37" s="72"/>
       <c r="I37" s="72"/>
       <c r="J37" s="81" t="e">
@@ -11369,13 +11366,13 @@
       <c r="B38" s="58">
         <v>10</v>
       </c>
-      <c r="C38" s="337" t="s">
+      <c r="C38" s="323" t="s">
         <v>203</v>
       </c>
-      <c r="D38" s="338"/>
-      <c r="E38" s="338"/>
-      <c r="F38" s="338"/>
-      <c r="G38" s="339"/>
+      <c r="D38" s="324"/>
+      <c r="E38" s="324"/>
+      <c r="F38" s="324"/>
+      <c r="G38" s="325"/>
       <c r="H38" s="97"/>
       <c r="I38" s="97"/>
       <c r="J38" s="102"/>
@@ -11388,15 +11385,15 @@
       <c r="B39" s="58">
         <v>11</v>
       </c>
-      <c r="C39" s="340" t="s">
+      <c r="C39" s="332" t="s">
         <v>186</v>
       </c>
-      <c r="D39" s="337" t="s">
+      <c r="D39" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E39" s="338"/>
-      <c r="F39" s="338"/>
-      <c r="G39" s="339"/>
+      <c r="E39" s="324"/>
+      <c r="F39" s="324"/>
+      <c r="G39" s="325"/>
       <c r="H39" s="97"/>
       <c r="I39" s="97"/>
       <c r="J39" s="102"/>
@@ -11409,15 +11406,15 @@
       <c r="B40" s="58">
         <v>12</v>
       </c>
-      <c r="C40" s="341"/>
-      <c r="D40" s="343" t="s">
+      <c r="C40" s="333"/>
+      <c r="D40" s="342" t="s">
         <v>55</v>
       </c>
-      <c r="E40" s="346" t="s">
+      <c r="E40" s="319" t="s">
         <v>128</v>
       </c>
-      <c r="F40" s="347"/>
-      <c r="G40" s="348"/>
+      <c r="F40" s="320"/>
+      <c r="G40" s="321"/>
       <c r="H40" s="72"/>
       <c r="I40" s="72"/>
       <c r="J40" s="81" t="e">
@@ -11433,13 +11430,13 @@
       <c r="B41" s="58">
         <v>13</v>
       </c>
-      <c r="C41" s="342"/>
-      <c r="D41" s="352"/>
-      <c r="E41" s="346" t="s">
+      <c r="C41" s="349"/>
+      <c r="D41" s="350"/>
+      <c r="E41" s="319" t="s">
         <v>129</v>
       </c>
-      <c r="F41" s="347"/>
-      <c r="G41" s="348"/>
+      <c r="F41" s="320"/>
+      <c r="G41" s="321"/>
       <c r="H41" s="72"/>
       <c r="I41" s="72"/>
       <c r="J41" s="81" t="e">
@@ -11455,15 +11452,15 @@
       <c r="B42" s="58">
         <v>14</v>
       </c>
-      <c r="C42" s="340" t="s">
+      <c r="C42" s="332" t="s">
         <v>204</v>
       </c>
-      <c r="D42" s="337" t="s">
+      <c r="D42" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E42" s="338"/>
-      <c r="F42" s="338"/>
-      <c r="G42" s="339"/>
+      <c r="E42" s="324"/>
+      <c r="F42" s="324"/>
+      <c r="G42" s="325"/>
       <c r="H42" s="97"/>
       <c r="I42" s="97"/>
       <c r="J42" s="102"/>
@@ -11476,15 +11473,15 @@
       <c r="B43" s="58">
         <v>15</v>
       </c>
-      <c r="C43" s="341"/>
-      <c r="D43" s="343" t="s">
+      <c r="C43" s="333"/>
+      <c r="D43" s="342" t="s">
         <v>55</v>
       </c>
-      <c r="E43" s="346" t="s">
+      <c r="E43" s="319" t="s">
         <v>128</v>
       </c>
-      <c r="F43" s="347"/>
-      <c r="G43" s="348"/>
+      <c r="F43" s="320"/>
+      <c r="G43" s="321"/>
       <c r="H43" s="72"/>
       <c r="I43" s="72"/>
       <c r="J43" s="81" t="e">
@@ -11500,13 +11497,13 @@
       <c r="B44" s="58">
         <v>16</v>
       </c>
-      <c r="C44" s="342"/>
-      <c r="D44" s="352"/>
-      <c r="E44" s="346" t="s">
+      <c r="C44" s="349"/>
+      <c r="D44" s="350"/>
+      <c r="E44" s="319" t="s">
         <v>129</v>
       </c>
-      <c r="F44" s="347"/>
-      <c r="G44" s="348"/>
+      <c r="F44" s="320"/>
+      <c r="G44" s="321"/>
       <c r="H44" s="72"/>
       <c r="I44" s="72"/>
       <c r="J44" s="81" t="e">
@@ -11522,15 +11519,15 @@
       <c r="B45" s="58">
         <v>17</v>
       </c>
-      <c r="C45" s="340" t="s">
+      <c r="C45" s="332" t="s">
         <v>62</v>
       </c>
-      <c r="D45" s="337" t="s">
+      <c r="D45" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E45" s="338"/>
-      <c r="F45" s="338"/>
-      <c r="G45" s="339"/>
+      <c r="E45" s="324"/>
+      <c r="F45" s="324"/>
+      <c r="G45" s="325"/>
       <c r="H45" s="97"/>
       <c r="I45" s="97"/>
       <c r="J45" s="102"/>
@@ -11543,15 +11540,15 @@
       <c r="B46" s="58">
         <v>18</v>
       </c>
-      <c r="C46" s="341"/>
-      <c r="D46" s="343" t="s">
+      <c r="C46" s="333"/>
+      <c r="D46" s="342" t="s">
         <v>55</v>
       </c>
-      <c r="E46" s="346" t="s">
+      <c r="E46" s="319" t="s">
         <v>63</v>
       </c>
-      <c r="F46" s="347"/>
-      <c r="G46" s="348"/>
+      <c r="F46" s="320"/>
+      <c r="G46" s="321"/>
       <c r="H46" s="72"/>
       <c r="I46" s="72"/>
       <c r="J46" s="81" t="e">
@@ -11567,13 +11564,13 @@
       <c r="B47" s="58">
         <v>19</v>
       </c>
-      <c r="C47" s="342"/>
-      <c r="D47" s="352"/>
-      <c r="E47" s="346" t="s">
+      <c r="C47" s="349"/>
+      <c r="D47" s="350"/>
+      <c r="E47" s="319" t="s">
         <v>64</v>
       </c>
-      <c r="F47" s="347"/>
-      <c r="G47" s="348"/>
+      <c r="F47" s="320"/>
+      <c r="G47" s="321"/>
       <c r="H47" s="72"/>
       <c r="I47" s="72"/>
       <c r="J47" s="81" t="e">
@@ -11589,15 +11586,15 @@
       <c r="B48" s="58">
         <v>20</v>
       </c>
-      <c r="C48" s="340" t="s">
+      <c r="C48" s="332" t="s">
         <v>205</v>
       </c>
-      <c r="D48" s="337" t="s">
+      <c r="D48" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E48" s="338"/>
-      <c r="F48" s="338"/>
-      <c r="G48" s="339"/>
+      <c r="E48" s="324"/>
+      <c r="F48" s="324"/>
+      <c r="G48" s="325"/>
       <c r="H48" s="97"/>
       <c r="I48" s="97"/>
       <c r="J48" s="102"/>
@@ -11610,15 +11607,15 @@
       <c r="B49" s="58">
         <v>21</v>
       </c>
-      <c r="C49" s="341"/>
+      <c r="C49" s="333"/>
       <c r="D49" s="103" t="s">
         <v>55</v>
       </c>
-      <c r="E49" s="359" t="s">
-        <v>44</v>
-      </c>
-      <c r="F49" s="360"/>
-      <c r="G49" s="360"/>
+      <c r="E49" s="334" t="s">
+        <v>44</v>
+      </c>
+      <c r="F49" s="335"/>
+      <c r="G49" s="335"/>
       <c r="H49" s="104"/>
       <c r="I49" s="104"/>
       <c r="J49" s="81"/>
@@ -11637,11 +11634,11 @@
       <c r="D50" s="106" t="s">
         <v>44</v>
       </c>
-      <c r="E50" s="346" t="s">
+      <c r="E50" s="319" t="s">
         <v>206</v>
       </c>
-      <c r="F50" s="347"/>
-      <c r="G50" s="348"/>
+      <c r="F50" s="320"/>
+      <c r="G50" s="321"/>
       <c r="H50" s="72"/>
       <c r="I50" s="72"/>
       <c r="J50" s="81" t="e">
@@ -11664,11 +11661,11 @@
       <c r="D51" s="106" t="s">
         <v>44</v>
       </c>
-      <c r="E51" s="346" t="s">
-        <v>44</v>
-      </c>
-      <c r="F51" s="347"/>
-      <c r="G51" s="348"/>
+      <c r="E51" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="F51" s="320"/>
+      <c r="G51" s="321"/>
       <c r="H51" s="72"/>
       <c r="I51" s="72"/>
       <c r="J51" s="81"/>
@@ -11682,15 +11679,15 @@
       <c r="B52" s="58">
         <v>24</v>
       </c>
-      <c r="C52" s="340" t="s">
+      <c r="C52" s="332" t="s">
         <v>102</v>
       </c>
-      <c r="D52" s="337" t="s">
+      <c r="D52" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E52" s="338"/>
-      <c r="F52" s="338"/>
-      <c r="G52" s="339"/>
+      <c r="E52" s="324"/>
+      <c r="F52" s="324"/>
+      <c r="G52" s="325"/>
       <c r="H52" s="97"/>
       <c r="I52" s="97"/>
       <c r="J52" s="102"/>
@@ -11703,15 +11700,15 @@
       <c r="B53" s="58">
         <v>25</v>
       </c>
-      <c r="C53" s="341"/>
+      <c r="C53" s="333"/>
       <c r="D53" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E53" s="346" t="s">
+      <c r="E53" s="319" t="s">
         <v>13</v>
       </c>
-      <c r="F53" s="347"/>
-      <c r="G53" s="348"/>
+      <c r="F53" s="320"/>
+      <c r="G53" s="321"/>
       <c r="H53" s="72"/>
       <c r="I53" s="72"/>
       <c r="J53" s="81"/>
@@ -11730,11 +11727,11 @@
       <c r="D54" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E54" s="346" t="s">
+      <c r="E54" s="319" t="s">
         <v>207</v>
       </c>
-      <c r="F54" s="347"/>
-      <c r="G54" s="348"/>
+      <c r="F54" s="320"/>
+      <c r="G54" s="321"/>
       <c r="H54" s="72"/>
       <c r="I54" s="72"/>
       <c r="J54" s="81" t="e">
@@ -11751,15 +11748,15 @@
       <c r="B55" s="58">
         <v>30</v>
       </c>
-      <c r="C55" s="340" t="s">
+      <c r="C55" s="332" t="s">
         <v>16</v>
       </c>
-      <c r="D55" s="337" t="s">
+      <c r="D55" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E55" s="338"/>
-      <c r="F55" s="338"/>
-      <c r="G55" s="339"/>
+      <c r="E55" s="324"/>
+      <c r="F55" s="324"/>
+      <c r="G55" s="325"/>
       <c r="H55" s="97"/>
       <c r="I55" s="97"/>
       <c r="J55" s="102"/>
@@ -11772,15 +11769,15 @@
       <c r="B56" s="58">
         <v>31</v>
       </c>
-      <c r="C56" s="341"/>
+      <c r="C56" s="333"/>
       <c r="D56" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E56" s="346" t="s">
+      <c r="E56" s="319" t="s">
         <v>146</v>
       </c>
-      <c r="F56" s="347"/>
-      <c r="G56" s="348"/>
+      <c r="F56" s="320"/>
+      <c r="G56" s="321"/>
       <c r="H56" s="72"/>
       <c r="I56" s="72"/>
       <c r="J56" s="81"/>
@@ -11793,15 +11790,15 @@
       <c r="B57" s="58">
         <v>32</v>
       </c>
-      <c r="C57" s="341"/>
+      <c r="C57" s="333"/>
       <c r="D57" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E57" s="346" t="s">
+      <c r="E57" s="319" t="s">
         <v>147</v>
       </c>
-      <c r="F57" s="347"/>
-      <c r="G57" s="348"/>
+      <c r="F57" s="320"/>
+      <c r="G57" s="321"/>
       <c r="H57" s="72"/>
       <c r="I57" s="72"/>
       <c r="J57" s="81"/>
@@ -11820,11 +11817,11 @@
       <c r="D58" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E58" s="346" t="s">
+      <c r="E58" s="319" t="s">
         <v>148</v>
       </c>
-      <c r="F58" s="347"/>
-      <c r="G58" s="348"/>
+      <c r="F58" s="320"/>
+      <c r="G58" s="321"/>
       <c r="H58" s="72"/>
       <c r="I58" s="72"/>
       <c r="J58" s="81"/>
@@ -11843,11 +11840,11 @@
       <c r="D59" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E59" s="346" t="s">
-        <v>44</v>
-      </c>
-      <c r="F59" s="347"/>
-      <c r="G59" s="348"/>
+      <c r="E59" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="F59" s="320"/>
+      <c r="G59" s="321"/>
       <c r="H59" s="72"/>
       <c r="I59" s="72"/>
       <c r="J59" s="81"/>
@@ -11861,15 +11858,15 @@
       <c r="B60" s="58">
         <v>35</v>
       </c>
-      <c r="C60" s="340" t="s">
+      <c r="C60" s="332" t="s">
         <v>190</v>
       </c>
-      <c r="D60" s="337" t="s">
+      <c r="D60" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E60" s="338"/>
-      <c r="F60" s="338"/>
-      <c r="G60" s="339"/>
+      <c r="E60" s="324"/>
+      <c r="F60" s="324"/>
+      <c r="G60" s="325"/>
       <c r="H60" s="97"/>
       <c r="I60" s="97"/>
       <c r="J60" s="102"/>
@@ -11882,15 +11879,15 @@
       <c r="B61" s="58">
         <v>36</v>
       </c>
-      <c r="C61" s="341"/>
+      <c r="C61" s="333"/>
       <c r="D61" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E61" s="346" t="s">
+      <c r="E61" s="319" t="s">
         <v>128</v>
       </c>
-      <c r="F61" s="347"/>
-      <c r="G61" s="348"/>
+      <c r="F61" s="320"/>
+      <c r="G61" s="321"/>
       <c r="H61" s="72"/>
       <c r="I61" s="72"/>
       <c r="J61" s="81"/>
@@ -11903,15 +11900,15 @@
       <c r="B62" s="58">
         <v>37</v>
       </c>
-      <c r="C62" s="341"/>
+      <c r="C62" s="333"/>
       <c r="D62" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E62" s="346" t="s">
+      <c r="E62" s="319" t="s">
         <v>154</v>
       </c>
-      <c r="F62" s="347"/>
-      <c r="G62" s="348"/>
+      <c r="F62" s="320"/>
+      <c r="G62" s="321"/>
       <c r="H62" s="72"/>
       <c r="I62" s="72"/>
       <c r="J62" s="81"/>
@@ -11930,11 +11927,11 @@
       <c r="D63" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E63" s="346" t="s">
+      <c r="E63" s="319" t="s">
         <v>208</v>
       </c>
-      <c r="F63" s="347"/>
-      <c r="G63" s="348"/>
+      <c r="F63" s="320"/>
+      <c r="G63" s="321"/>
       <c r="H63" s="72"/>
       <c r="I63" s="72"/>
       <c r="J63" s="81"/>
@@ -11953,11 +11950,11 @@
       <c r="D64" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E64" s="346" t="s">
-        <v>44</v>
-      </c>
-      <c r="F64" s="347"/>
-      <c r="G64" s="348"/>
+      <c r="E64" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="F64" s="320"/>
+      <c r="G64" s="321"/>
       <c r="H64" s="72"/>
       <c r="I64" s="72"/>
       <c r="J64" s="81"/>
@@ -11971,15 +11968,15 @@
       <c r="B65" s="58">
         <v>40</v>
       </c>
-      <c r="C65" s="340" t="s">
+      <c r="C65" s="332" t="s">
         <v>14</v>
       </c>
-      <c r="D65" s="337" t="s">
+      <c r="D65" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E65" s="338"/>
-      <c r="F65" s="338"/>
-      <c r="G65" s="339"/>
+      <c r="E65" s="324"/>
+      <c r="F65" s="324"/>
+      <c r="G65" s="325"/>
       <c r="H65" s="97"/>
       <c r="I65" s="97"/>
       <c r="J65" s="102"/>
@@ -11992,17 +11989,17 @@
       <c r="B66" s="58">
         <v>41</v>
       </c>
-      <c r="C66" s="341"/>
+      <c r="C66" s="333"/>
       <c r="D66" s="66" t="s">
         <v>55</v>
       </c>
       <c r="E66" s="103" t="s">
         <v>209</v>
       </c>
-      <c r="F66" s="337" t="s">
+      <c r="F66" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="G66" s="339"/>
+      <c r="G66" s="325"/>
       <c r="H66" s="97"/>
       <c r="I66" s="97"/>
       <c r="J66" s="102"/>
@@ -12015,7 +12012,7 @@
       <c r="B67" s="58">
         <v>42</v>
       </c>
-      <c r="C67" s="341"/>
+      <c r="C67" s="333"/>
       <c r="D67" s="67" t="s">
         <v>44</v>
       </c>
@@ -12108,10 +12105,10 @@
       <c r="E70" s="103" t="s">
         <v>210</v>
       </c>
-      <c r="F70" s="337" t="s">
+      <c r="F70" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="G70" s="339"/>
+      <c r="G70" s="325"/>
       <c r="H70" s="97"/>
       <c r="I70" s="97"/>
       <c r="J70" s="102"/>
@@ -12280,10 +12277,10 @@
       <c r="E76" s="103" t="s">
         <v>214</v>
       </c>
-      <c r="F76" s="337" t="s">
+      <c r="F76" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="G76" s="339"/>
+      <c r="G76" s="325"/>
       <c r="H76" s="97"/>
       <c r="I76" s="97"/>
       <c r="J76" s="102"/>
@@ -12385,13 +12382,13 @@
       <c r="D80" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E80" s="361" t="s">
+      <c r="E80" s="344" t="s">
         <v>216</v>
       </c>
-      <c r="F80" s="337" t="s">
+      <c r="F80" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="G80" s="339"/>
+      <c r="G80" s="325"/>
       <c r="H80" s="97"/>
       <c r="I80" s="97"/>
       <c r="J80" s="102"/>
@@ -12411,15 +12408,15 @@
       <c r="D81" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E81" s="362"/>
+      <c r="E81" s="345"/>
       <c r="F81" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="G81" s="363" t="s">
+      <c r="G81" s="346" t="s">
         <v>136</v>
       </c>
-      <c r="H81" s="364"/>
-      <c r="I81" s="365"/>
+      <c r="H81" s="347"/>
+      <c r="I81" s="348"/>
       <c r="J81" s="81" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -12498,13 +12495,13 @@
       <c r="D84" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E84" s="361" t="s">
-        <v>44</v>
-      </c>
-      <c r="F84" s="337" t="s">
+      <c r="E84" s="344" t="s">
+        <v>44</v>
+      </c>
+      <c r="F84" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="G84" s="339"/>
+      <c r="G84" s="325"/>
       <c r="H84" s="97"/>
       <c r="I84" s="97"/>
       <c r="J84" s="102"/>
@@ -12524,7 +12521,7 @@
       <c r="D85" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E85" s="362"/>
+      <c r="E85" s="345"/>
       <c r="F85" s="66" t="s">
         <v>55</v>
       </c>
@@ -12573,15 +12570,15 @@
       <c r="B87" s="58">
         <v>62</v>
       </c>
-      <c r="C87" s="340" t="s">
+      <c r="C87" s="332" t="s">
         <v>144</v>
       </c>
-      <c r="D87" s="337" t="s">
+      <c r="D87" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E87" s="338"/>
-      <c r="F87" s="338"/>
-      <c r="G87" s="339"/>
+      <c r="E87" s="324"/>
+      <c r="F87" s="324"/>
+      <c r="G87" s="325"/>
       <c r="H87" s="97"/>
       <c r="I87" s="110"/>
       <c r="J87" s="102"/>
@@ -12594,15 +12591,15 @@
       <c r="B88" s="58">
         <v>63</v>
       </c>
-      <c r="C88" s="341"/>
+      <c r="C88" s="333"/>
       <c r="D88" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E88" s="359" t="s">
-        <v>44</v>
-      </c>
-      <c r="F88" s="360"/>
-      <c r="G88" s="360"/>
+      <c r="E88" s="334" t="s">
+        <v>44</v>
+      </c>
+      <c r="F88" s="335"/>
+      <c r="G88" s="335"/>
       <c r="H88" s="104"/>
       <c r="I88" s="104"/>
       <c r="J88" s="81" t="e">
@@ -12624,11 +12621,11 @@
       <c r="D89" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E89" s="346" t="s">
-        <v>44</v>
-      </c>
-      <c r="F89" s="347"/>
-      <c r="G89" s="348"/>
+      <c r="E89" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="F89" s="320"/>
+      <c r="G89" s="321"/>
       <c r="H89" s="72"/>
       <c r="I89" s="109"/>
       <c r="J89" s="81"/>
@@ -12648,11 +12645,11 @@
       <c r="D90" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E90" s="346" t="s">
-        <v>44</v>
-      </c>
-      <c r="F90" s="347"/>
-      <c r="G90" s="348"/>
+      <c r="E90" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="F90" s="320"/>
+      <c r="G90" s="321"/>
       <c r="H90" s="72"/>
       <c r="I90" s="109"/>
       <c r="J90" s="81"/>
@@ -12666,15 +12663,15 @@
       <c r="B91" s="58">
         <v>66</v>
       </c>
-      <c r="C91" s="340" t="s">
+      <c r="C91" s="332" t="s">
         <v>189</v>
       </c>
-      <c r="D91" s="337" t="s">
+      <c r="D91" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E91" s="338"/>
-      <c r="F91" s="338"/>
-      <c r="G91" s="339"/>
+      <c r="E91" s="324"/>
+      <c r="F91" s="324"/>
+      <c r="G91" s="325"/>
       <c r="H91" s="97"/>
       <c r="I91" s="110"/>
       <c r="J91" s="102"/>
@@ -12687,15 +12684,15 @@
       <c r="B92" s="58">
         <v>67</v>
       </c>
-      <c r="C92" s="341"/>
+      <c r="C92" s="333"/>
       <c r="D92" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E92" s="359" t="s">
-        <v>44</v>
-      </c>
-      <c r="F92" s="360"/>
-      <c r="G92" s="360"/>
+      <c r="E92" s="334" t="s">
+        <v>44</v>
+      </c>
+      <c r="F92" s="335"/>
+      <c r="G92" s="335"/>
       <c r="H92" s="104"/>
       <c r="I92" s="104"/>
       <c r="J92" s="81"/>
@@ -12714,11 +12711,11 @@
       <c r="D93" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E93" s="346" t="s">
-        <v>44</v>
-      </c>
-      <c r="F93" s="347"/>
-      <c r="G93" s="348"/>
+      <c r="E93" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="F93" s="320"/>
+      <c r="G93" s="321"/>
       <c r="H93" s="72"/>
       <c r="I93" s="109"/>
       <c r="J93" s="81"/>
@@ -12738,11 +12735,11 @@
       <c r="D94" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E94" s="346" t="s">
-        <v>44</v>
-      </c>
-      <c r="F94" s="347"/>
-      <c r="G94" s="348"/>
+      <c r="E94" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="F94" s="320"/>
+      <c r="G94" s="321"/>
       <c r="H94" s="72"/>
       <c r="I94" s="109"/>
       <c r="J94" s="81"/>
@@ -12756,15 +12753,15 @@
       <c r="B95" s="58">
         <v>70</v>
       </c>
-      <c r="C95" s="340" t="s">
+      <c r="C95" s="332" t="s">
         <v>137</v>
       </c>
-      <c r="D95" s="337" t="s">
+      <c r="D95" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E95" s="338"/>
-      <c r="F95" s="338"/>
-      <c r="G95" s="339"/>
+      <c r="E95" s="324"/>
+      <c r="F95" s="324"/>
+      <c r="G95" s="325"/>
       <c r="H95" s="97"/>
       <c r="I95" s="110"/>
       <c r="J95" s="102"/>
@@ -12777,15 +12774,15 @@
       <c r="B96" s="58">
         <v>71</v>
       </c>
-      <c r="C96" s="341"/>
+      <c r="C96" s="333"/>
       <c r="D96" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E96" s="359" t="s">
-        <v>44</v>
-      </c>
-      <c r="F96" s="360"/>
-      <c r="G96" s="360"/>
+      <c r="E96" s="334" t="s">
+        <v>44</v>
+      </c>
+      <c r="F96" s="335"/>
+      <c r="G96" s="335"/>
       <c r="H96" s="104"/>
       <c r="I96" s="104"/>
       <c r="J96" s="81"/>
@@ -12804,11 +12801,11 @@
       <c r="D97" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E97" s="346" t="s">
+      <c r="E97" s="319" t="s">
         <v>217</v>
       </c>
-      <c r="F97" s="347"/>
-      <c r="G97" s="348"/>
+      <c r="F97" s="320"/>
+      <c r="G97" s="321"/>
       <c r="H97" s="72"/>
       <c r="I97" s="109"/>
       <c r="J97" s="81" t="e">
@@ -12823,11 +12820,11 @@
       <c r="B98" s="58"/>
       <c r="C98" s="77"/>
       <c r="D98" s="70"/>
-      <c r="E98" s="346" t="s">
+      <c r="E98" s="319" t="s">
         <v>218</v>
       </c>
-      <c r="F98" s="347"/>
-      <c r="G98" s="348"/>
+      <c r="F98" s="320"/>
+      <c r="G98" s="321"/>
       <c r="H98" s="72"/>
       <c r="I98" s="109"/>
       <c r="J98" s="81"/>
@@ -12839,9 +12836,9 @@
       <c r="B99" s="58"/>
       <c r="C99" s="77"/>
       <c r="D99" s="70"/>
-      <c r="E99" s="346"/>
-      <c r="F99" s="347"/>
-      <c r="G99" s="348"/>
+      <c r="E99" s="319"/>
+      <c r="F99" s="320"/>
+      <c r="G99" s="321"/>
       <c r="H99" s="72"/>
       <c r="I99" s="109"/>
       <c r="J99" s="81"/>
@@ -12861,11 +12858,11 @@
       <c r="D100" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E100" s="346" t="s">
-        <v>44</v>
-      </c>
-      <c r="F100" s="347"/>
-      <c r="G100" s="348"/>
+      <c r="E100" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="F100" s="320"/>
+      <c r="G100" s="321"/>
       <c r="H100" s="72"/>
       <c r="I100" s="109"/>
       <c r="J100" s="81"/>
@@ -12879,15 +12876,15 @@
       <c r="B101" s="58">
         <v>75</v>
       </c>
-      <c r="C101" s="340" t="s">
+      <c r="C101" s="332" t="s">
         <v>17</v>
       </c>
-      <c r="D101" s="337" t="s">
+      <c r="D101" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E101" s="338"/>
-      <c r="F101" s="338"/>
-      <c r="G101" s="339"/>
+      <c r="E101" s="324"/>
+      <c r="F101" s="324"/>
+      <c r="G101" s="325"/>
       <c r="H101" s="97"/>
       <c r="I101" s="111">
         <f>I102+I103+I104</f>
@@ -12903,15 +12900,15 @@
       <c r="B102" s="58">
         <v>76</v>
       </c>
-      <c r="C102" s="341"/>
+      <c r="C102" s="333"/>
       <c r="D102" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E102" s="356" t="s">
+      <c r="E102" s="336" t="s">
         <v>219</v>
       </c>
-      <c r="F102" s="357"/>
-      <c r="G102" s="358"/>
+      <c r="F102" s="337"/>
+      <c r="G102" s="338"/>
       <c r="H102" s="72"/>
       <c r="I102" s="109"/>
       <c r="J102" s="81">
@@ -12927,15 +12924,15 @@
       <c r="B103" s="58">
         <v>77</v>
       </c>
-      <c r="C103" s="341"/>
+      <c r="C103" s="333"/>
       <c r="D103" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E103" s="356" t="s">
+      <c r="E103" s="336" t="s">
         <v>220</v>
       </c>
-      <c r="F103" s="357"/>
-      <c r="G103" s="358"/>
+      <c r="F103" s="337"/>
+      <c r="G103" s="338"/>
       <c r="H103" s="72"/>
       <c r="I103" s="72"/>
       <c r="J103" s="81">
@@ -12957,11 +12954,11 @@
       <c r="D104" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E104" s="356" t="s">
+      <c r="E104" s="336" t="s">
         <v>221</v>
       </c>
-      <c r="F104" s="357"/>
-      <c r="G104" s="358"/>
+      <c r="F104" s="337"/>
+      <c r="G104" s="338"/>
       <c r="H104" s="72"/>
       <c r="I104" s="72"/>
       <c r="J104" s="81">
@@ -12977,13 +12974,13 @@
       <c r="B105" s="58">
         <v>83</v>
       </c>
-      <c r="C105" s="337" t="s">
+      <c r="C105" s="323" t="s">
         <v>7</v>
       </c>
-      <c r="D105" s="338"/>
-      <c r="E105" s="338"/>
-      <c r="F105" s="338"/>
-      <c r="G105" s="339"/>
+      <c r="D105" s="324"/>
+      <c r="E105" s="324"/>
+      <c r="F105" s="324"/>
+      <c r="G105" s="325"/>
       <c r="H105" s="97"/>
       <c r="I105" s="97"/>
       <c r="J105" s="102" t="e">
@@ -12999,13 +12996,13 @@
       <c r="B106" s="58">
         <v>84</v>
       </c>
-      <c r="C106" s="337" t="s">
+      <c r="C106" s="323" t="s">
         <v>222</v>
       </c>
-      <c r="D106" s="338"/>
-      <c r="E106" s="338"/>
-      <c r="F106" s="338"/>
-      <c r="G106" s="339"/>
+      <c r="D106" s="324"/>
+      <c r="E106" s="324"/>
+      <c r="F106" s="324"/>
+      <c r="G106" s="325"/>
       <c r="H106" s="97"/>
       <c r="I106" s="101"/>
       <c r="J106" s="102" t="e">
@@ -13021,15 +13018,15 @@
       <c r="B107" s="58">
         <v>85</v>
       </c>
-      <c r="C107" s="340" t="s">
+      <c r="C107" s="332" t="s">
         <v>223</v>
       </c>
-      <c r="D107" s="337" t="s">
+      <c r="D107" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E107" s="338"/>
-      <c r="F107" s="338"/>
-      <c r="G107" s="339"/>
+      <c r="E107" s="324"/>
+      <c r="F107" s="324"/>
+      <c r="G107" s="325"/>
       <c r="H107" s="97"/>
       <c r="I107" s="97"/>
       <c r="J107" s="102"/>
@@ -13042,15 +13039,15 @@
       <c r="B108" s="58">
         <v>86</v>
       </c>
-      <c r="C108" s="341"/>
+      <c r="C108" s="333"/>
       <c r="D108" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E108" s="356" t="s">
+      <c r="E108" s="336" t="s">
         <v>224</v>
       </c>
-      <c r="F108" s="357"/>
-      <c r="G108" s="358"/>
+      <c r="F108" s="337"/>
+      <c r="G108" s="338"/>
       <c r="H108" s="72"/>
       <c r="I108" s="63"/>
       <c r="J108" s="81" t="e">
@@ -13072,11 +13069,11 @@
       <c r="D109" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E109" s="346" t="s">
+      <c r="E109" s="319" t="s">
         <v>225</v>
       </c>
-      <c r="F109" s="347"/>
-      <c r="G109" s="348"/>
+      <c r="F109" s="320"/>
+      <c r="G109" s="321"/>
       <c r="H109" s="72"/>
       <c r="I109" s="63"/>
       <c r="J109" s="81"/>
@@ -13096,11 +13093,11 @@
       <c r="D110" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E110" s="346" t="s">
-        <v>44</v>
-      </c>
-      <c r="F110" s="347"/>
-      <c r="G110" s="348"/>
+      <c r="E110" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="F110" s="320"/>
+      <c r="G110" s="321"/>
       <c r="H110" s="72"/>
       <c r="I110" s="72"/>
       <c r="J110" s="81"/>
@@ -13114,15 +13111,15 @@
       <c r="B111" s="58">
         <v>89</v>
       </c>
-      <c r="C111" s="340" t="s">
+      <c r="C111" s="332" t="s">
         <v>192</v>
       </c>
-      <c r="D111" s="337" t="s">
+      <c r="D111" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E111" s="338"/>
-      <c r="F111" s="338"/>
-      <c r="G111" s="339"/>
+      <c r="E111" s="324"/>
+      <c r="F111" s="324"/>
+      <c r="G111" s="325"/>
       <c r="H111" s="97"/>
       <c r="I111" s="97"/>
       <c r="J111" s="102"/>
@@ -13135,15 +13132,15 @@
       <c r="B112" s="58">
         <v>90</v>
       </c>
-      <c r="C112" s="341"/>
+      <c r="C112" s="333"/>
       <c r="D112" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E112" s="356" t="s">
+      <c r="E112" s="336" t="s">
         <v>226</v>
       </c>
-      <c r="F112" s="357"/>
-      <c r="G112" s="358"/>
+      <c r="F112" s="337"/>
+      <c r="G112" s="338"/>
       <c r="H112" s="72"/>
       <c r="I112" s="72"/>
       <c r="J112" s="81"/>
@@ -13162,11 +13159,11 @@
       <c r="D113" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E113" s="346" t="s">
-        <v>44</v>
-      </c>
-      <c r="F113" s="347"/>
-      <c r="G113" s="348"/>
+      <c r="E113" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="F113" s="320"/>
+      <c r="G113" s="321"/>
       <c r="H113" s="72"/>
       <c r="I113" s="72"/>
       <c r="J113" s="81"/>
@@ -13179,15 +13176,15 @@
       <c r="B114" s="58">
         <v>92</v>
       </c>
-      <c r="C114" s="340" t="s">
+      <c r="C114" s="332" t="s">
         <v>191</v>
       </c>
-      <c r="D114" s="337" t="s">
+      <c r="D114" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E114" s="338"/>
-      <c r="F114" s="338"/>
-      <c r="G114" s="339"/>
+      <c r="E114" s="324"/>
+      <c r="F114" s="324"/>
+      <c r="G114" s="325"/>
       <c r="H114" s="97"/>
       <c r="I114" s="97"/>
       <c r="J114" s="102"/>
@@ -13200,15 +13197,15 @@
       <c r="B115" s="58">
         <v>93</v>
       </c>
-      <c r="C115" s="341"/>
+      <c r="C115" s="333"/>
       <c r="D115" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E115" s="359" t="s">
-        <v>44</v>
-      </c>
-      <c r="F115" s="360"/>
-      <c r="G115" s="360"/>
+      <c r="E115" s="334" t="s">
+        <v>44</v>
+      </c>
+      <c r="F115" s="335"/>
+      <c r="G115" s="335"/>
       <c r="H115" s="104"/>
       <c r="I115" s="104"/>
       <c r="J115" s="112"/>
@@ -13227,11 +13224,11 @@
       <c r="D116" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E116" s="346" t="s">
-        <v>44</v>
-      </c>
-      <c r="F116" s="347"/>
-      <c r="G116" s="348"/>
+      <c r="E116" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="F116" s="320"/>
+      <c r="G116" s="321"/>
       <c r="H116" s="72"/>
       <c r="I116" s="63"/>
       <c r="J116" s="81"/>
@@ -13251,11 +13248,11 @@
       <c r="D117" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E117" s="346" t="s">
-        <v>44</v>
-      </c>
-      <c r="F117" s="347"/>
-      <c r="G117" s="348"/>
+      <c r="E117" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="F117" s="320"/>
+      <c r="G117" s="321"/>
       <c r="H117" s="72"/>
       <c r="I117" s="72"/>
       <c r="J117" s="81"/>
@@ -13269,15 +13266,15 @@
       <c r="B118" s="58">
         <v>96</v>
       </c>
-      <c r="C118" s="340" t="s">
+      <c r="C118" s="332" t="s">
         <v>149</v>
       </c>
-      <c r="D118" s="337" t="s">
+      <c r="D118" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E118" s="338"/>
-      <c r="F118" s="338"/>
-      <c r="G118" s="339"/>
+      <c r="E118" s="324"/>
+      <c r="F118" s="324"/>
+      <c r="G118" s="325"/>
       <c r="H118" s="97"/>
       <c r="I118" s="97"/>
       <c r="J118" s="102"/>
@@ -13290,15 +13287,15 @@
       <c r="B119" s="58">
         <v>97</v>
       </c>
-      <c r="C119" s="341"/>
+      <c r="C119" s="333"/>
       <c r="D119" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E119" s="356" t="s">
+      <c r="E119" s="336" t="s">
         <v>227</v>
       </c>
-      <c r="F119" s="357"/>
-      <c r="G119" s="358"/>
+      <c r="F119" s="337"/>
+      <c r="G119" s="338"/>
       <c r="H119" s="72"/>
       <c r="I119" s="72"/>
       <c r="J119" s="81"/>
@@ -13317,11 +13314,11 @@
       <c r="D120" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E120" s="356" t="s">
+      <c r="E120" s="336" t="s">
         <v>228</v>
       </c>
-      <c r="F120" s="357"/>
-      <c r="G120" s="358"/>
+      <c r="F120" s="337"/>
+      <c r="G120" s="338"/>
       <c r="H120" s="72"/>
       <c r="I120" s="72"/>
       <c r="J120" s="81"/>
@@ -13340,11 +13337,11 @@
       <c r="D121" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E121" s="356" t="s">
+      <c r="E121" s="336" t="s">
         <v>229</v>
       </c>
-      <c r="F121" s="357"/>
-      <c r="G121" s="358"/>
+      <c r="F121" s="337"/>
+      <c r="G121" s="338"/>
       <c r="H121" s="72"/>
       <c r="I121" s="72"/>
       <c r="J121" s="81"/>
@@ -13363,11 +13360,11 @@
       <c r="D122" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E122" s="346" t="s">
-        <v>44</v>
-      </c>
-      <c r="F122" s="347"/>
-      <c r="G122" s="348"/>
+      <c r="E122" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="F122" s="320"/>
+      <c r="G122" s="321"/>
       <c r="H122" s="72"/>
       <c r="I122" s="72"/>
       <c r="J122" s="81"/>
@@ -13381,15 +13378,15 @@
       <c r="B123" s="58">
         <v>101</v>
       </c>
-      <c r="C123" s="340" t="s">
+      <c r="C123" s="332" t="s">
         <v>230</v>
       </c>
-      <c r="D123" s="337" t="s">
+      <c r="D123" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E123" s="338"/>
-      <c r="F123" s="338"/>
-      <c r="G123" s="339"/>
+      <c r="E123" s="324"/>
+      <c r="F123" s="324"/>
+      <c r="G123" s="325"/>
       <c r="H123" s="97"/>
       <c r="I123" s="97"/>
       <c r="J123" s="102"/>
@@ -13402,17 +13399,17 @@
       <c r="B124" s="58">
         <v>102</v>
       </c>
-      <c r="C124" s="341"/>
+      <c r="C124" s="333"/>
       <c r="D124" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E124" s="343" t="s">
+      <c r="E124" s="342" t="s">
         <v>231</v>
       </c>
-      <c r="F124" s="337" t="s">
+      <c r="F124" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="G124" s="339"/>
+      <c r="G124" s="325"/>
       <c r="H124" s="97"/>
       <c r="I124" s="97"/>
       <c r="J124" s="102"/>
@@ -13425,11 +13422,11 @@
       <c r="B125" s="58">
         <v>103</v>
       </c>
-      <c r="C125" s="341"/>
+      <c r="C125" s="333"/>
       <c r="D125" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E125" s="344"/>
+      <c r="E125" s="343"/>
       <c r="F125" s="66" t="s">
         <v>55</v>
       </c>
@@ -13448,7 +13445,7 @@
       <c r="B126" s="58">
         <v>104</v>
       </c>
-      <c r="C126" s="341"/>
+      <c r="C126" s="333"/>
       <c r="D126" s="67" t="s">
         <v>44</v>
       </c>
@@ -13534,11 +13531,11 @@
       <c r="D129" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E129" s="356" t="s">
+      <c r="E129" s="336" t="s">
         <v>234</v>
       </c>
-      <c r="F129" s="357"/>
-      <c r="G129" s="358"/>
+      <c r="F129" s="337"/>
+      <c r="G129" s="338"/>
       <c r="H129" s="72"/>
       <c r="I129" s="72"/>
       <c r="J129" s="81"/>
@@ -13557,11 +13554,11 @@
       <c r="D130" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E130" s="346" t="s">
-        <v>44</v>
-      </c>
-      <c r="F130" s="347"/>
-      <c r="G130" s="348"/>
+      <c r="E130" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="F130" s="320"/>
+      <c r="G130" s="321"/>
       <c r="H130" s="72"/>
       <c r="I130" s="72"/>
       <c r="J130" s="81"/>
@@ -13575,15 +13572,15 @@
       <c r="B131" s="58">
         <v>109</v>
       </c>
-      <c r="C131" s="340" t="s">
+      <c r="C131" s="332" t="s">
         <v>175</v>
       </c>
-      <c r="D131" s="337" t="s">
+      <c r="D131" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E131" s="338"/>
-      <c r="F131" s="338"/>
-      <c r="G131" s="339"/>
+      <c r="E131" s="324"/>
+      <c r="F131" s="324"/>
+      <c r="G131" s="325"/>
       <c r="H131" s="97"/>
       <c r="I131" s="101">
         <f>SUM(I132:I136)</f>
@@ -13599,15 +13596,15 @@
       <c r="B132" s="58">
         <v>110</v>
       </c>
-      <c r="C132" s="341"/>
+      <c r="C132" s="333"/>
       <c r="D132" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E132" s="356" t="s">
+      <c r="E132" s="336" t="s">
         <v>91</v>
       </c>
-      <c r="F132" s="357"/>
-      <c r="G132" s="358"/>
+      <c r="F132" s="337"/>
+      <c r="G132" s="338"/>
       <c r="H132" s="72"/>
       <c r="I132" s="72"/>
       <c r="J132" s="81" t="e">
@@ -13623,15 +13620,15 @@
       <c r="B133" s="58">
         <v>111</v>
       </c>
-      <c r="C133" s="341"/>
+      <c r="C133" s="333"/>
       <c r="D133" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E133" s="356" t="s">
+      <c r="E133" s="336" t="s">
         <v>235</v>
       </c>
-      <c r="F133" s="357"/>
-      <c r="G133" s="358"/>
+      <c r="F133" s="337"/>
+      <c r="G133" s="338"/>
       <c r="H133" s="72"/>
       <c r="I133" s="72"/>
       <c r="J133" s="81" t="e">
@@ -13653,11 +13650,11 @@
       <c r="D134" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E134" s="356" t="s">
+      <c r="E134" s="336" t="s">
         <v>11</v>
       </c>
-      <c r="F134" s="357"/>
-      <c r="G134" s="358"/>
+      <c r="F134" s="337"/>
+      <c r="G134" s="338"/>
       <c r="H134" s="72"/>
       <c r="I134" s="72"/>
       <c r="J134" s="81" t="e">
@@ -13679,11 +13676,11 @@
       <c r="D135" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E135" s="356" t="s">
+      <c r="E135" s="336" t="s">
         <v>9</v>
       </c>
-      <c r="F135" s="357"/>
-      <c r="G135" s="358"/>
+      <c r="F135" s="337"/>
+      <c r="G135" s="338"/>
       <c r="H135" s="72"/>
       <c r="I135" s="72"/>
       <c r="J135" s="81" t="e">
@@ -13705,11 +13702,11 @@
       <c r="D136" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="E136" s="353" t="s">
+      <c r="E136" s="329" t="s">
         <v>236</v>
       </c>
-      <c r="F136" s="353"/>
-      <c r="G136" s="353"/>
+      <c r="F136" s="329"/>
+      <c r="G136" s="329"/>
       <c r="H136" s="72"/>
       <c r="I136" s="72"/>
       <c r="J136" s="81" t="e">
@@ -13732,11 +13729,11 @@
       <c r="D137" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E137" s="366" t="s">
-        <v>44</v>
-      </c>
-      <c r="F137" s="367"/>
-      <c r="G137" s="368"/>
+      <c r="E137" s="339" t="s">
+        <v>44</v>
+      </c>
+      <c r="F137" s="340"/>
+      <c r="G137" s="341"/>
       <c r="H137" s="115"/>
       <c r="I137" s="115"/>
       <c r="J137" s="116"/>
@@ -13750,15 +13747,15 @@
       <c r="B138" s="58">
         <v>118</v>
       </c>
-      <c r="C138" s="340" t="s">
+      <c r="C138" s="332" t="s">
         <v>237</v>
       </c>
-      <c r="D138" s="337" t="s">
+      <c r="D138" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E138" s="338"/>
-      <c r="F138" s="338"/>
-      <c r="G138" s="339"/>
+      <c r="E138" s="324"/>
+      <c r="F138" s="324"/>
+      <c r="G138" s="325"/>
       <c r="H138" s="97"/>
       <c r="I138" s="117"/>
       <c r="J138" s="118"/>
@@ -13771,15 +13768,15 @@
       <c r="B139" s="58">
         <v>119</v>
       </c>
-      <c r="C139" s="341"/>
+      <c r="C139" s="333"/>
       <c r="D139" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E139" s="356" t="s">
+      <c r="E139" s="336" t="s">
         <v>19</v>
       </c>
-      <c r="F139" s="357"/>
-      <c r="G139" s="358"/>
+      <c r="F139" s="337"/>
+      <c r="G139" s="338"/>
       <c r="H139" s="109"/>
       <c r="I139" s="113"/>
       <c r="J139" s="81" t="e">
@@ -13804,10 +13801,10 @@
       <c r="E140" s="66" t="s">
         <v>95</v>
       </c>
-      <c r="F140" s="337" t="s">
+      <c r="F140" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="G140" s="339"/>
+      <c r="G140" s="325"/>
       <c r="H140" s="110"/>
       <c r="I140" s="97"/>
       <c r="J140" s="102"/>
@@ -13829,7 +13826,7 @@
       <c r="E141" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="F141" s="373" t="s">
+      <c r="F141" s="330" t="s">
         <v>55</v>
       </c>
       <c r="G141" s="108" t="s">
@@ -13856,7 +13853,7 @@
       <c r="E142" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F142" s="374"/>
+      <c r="F142" s="331"/>
       <c r="G142" s="60" t="s">
         <v>238</v>
       </c>
@@ -13907,10 +13904,10 @@
       <c r="E144" s="66" t="s">
         <v>97</v>
       </c>
-      <c r="F144" s="337" t="s">
+      <c r="F144" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="G144" s="339"/>
+      <c r="G144" s="325"/>
       <c r="H144" s="97"/>
       <c r="I144" s="110"/>
       <c r="J144" s="102"/>
@@ -13932,7 +13929,7 @@
       <c r="E145" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="F145" s="373" t="s">
+      <c r="F145" s="330" t="s">
         <v>55</v>
       </c>
       <c r="G145" s="108" t="s">
@@ -13959,7 +13956,7 @@
       <c r="E146" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F146" s="374"/>
+      <c r="F146" s="331"/>
       <c r="G146" s="60" t="s">
         <v>18</v>
       </c>
@@ -14029,15 +14026,15 @@
       <c r="B149" s="58">
         <v>129</v>
       </c>
-      <c r="C149" s="340" t="s">
+      <c r="C149" s="332" t="s">
         <v>239</v>
       </c>
-      <c r="D149" s="337" t="s">
+      <c r="D149" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E149" s="338"/>
-      <c r="F149" s="338"/>
-      <c r="G149" s="339"/>
+      <c r="E149" s="324"/>
+      <c r="F149" s="324"/>
+      <c r="G149" s="325"/>
       <c r="H149" s="97"/>
       <c r="I149" s="110"/>
       <c r="J149" s="102"/>
@@ -14050,15 +14047,15 @@
       <c r="B150" s="121">
         <v>130</v>
       </c>
-      <c r="C150" s="341"/>
+      <c r="C150" s="333"/>
       <c r="D150" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E150" s="359" t="s">
-        <v>44</v>
-      </c>
-      <c r="F150" s="360"/>
-      <c r="G150" s="360"/>
+      <c r="E150" s="334" t="s">
+        <v>44</v>
+      </c>
+      <c r="F150" s="335"/>
+      <c r="G150" s="335"/>
       <c r="H150" s="104"/>
       <c r="I150" s="104"/>
       <c r="J150" s="81"/>
@@ -14077,11 +14074,11 @@
       <c r="D151" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E151" s="346" t="s">
-        <v>44</v>
-      </c>
-      <c r="F151" s="347"/>
-      <c r="G151" s="348"/>
+      <c r="E151" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="F151" s="320"/>
+      <c r="G151" s="321"/>
       <c r="H151" s="72"/>
       <c r="I151" s="109"/>
       <c r="J151" s="81"/>
@@ -14095,15 +14092,15 @@
       <c r="B152" s="58">
         <v>132</v>
       </c>
-      <c r="C152" s="369" t="s">
+      <c r="C152" s="322" t="s">
         <v>240</v>
       </c>
-      <c r="D152" s="337" t="s">
+      <c r="D152" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E152" s="338"/>
-      <c r="F152" s="338"/>
-      <c r="G152" s="339"/>
+      <c r="E152" s="324"/>
+      <c r="F152" s="324"/>
+      <c r="G152" s="325"/>
       <c r="H152" s="97"/>
       <c r="I152" s="110"/>
       <c r="J152" s="102"/>
@@ -14116,15 +14113,15 @@
       <c r="B153" s="58">
         <v>133</v>
       </c>
-      <c r="C153" s="369"/>
+      <c r="C153" s="322"/>
       <c r="D153" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E153" s="370" t="s">
+      <c r="E153" s="326" t="s">
         <v>241</v>
       </c>
-      <c r="F153" s="371"/>
-      <c r="G153" s="372"/>
+      <c r="F153" s="327"/>
+      <c r="G153" s="328"/>
       <c r="H153" s="122"/>
       <c r="I153" s="123"/>
       <c r="J153" s="81"/>
@@ -14143,11 +14140,11 @@
       <c r="D154" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="E154" s="353" t="s">
+      <c r="E154" s="329" t="s">
         <v>198</v>
       </c>
-      <c r="F154" s="353"/>
-      <c r="G154" s="353"/>
+      <c r="F154" s="329"/>
+      <c r="G154" s="329"/>
       <c r="H154" s="72"/>
       <c r="I154" s="120" t="e">
         <f>SUM(#REF!)</f>
@@ -14173,120 +14170,15 @@
     </row>
   </sheetData>
   <mergeCells count="142">
-    <mergeCell ref="E151:G151"/>
-    <mergeCell ref="C152:C153"/>
-    <mergeCell ref="D152:G152"/>
-    <mergeCell ref="E153:G153"/>
-    <mergeCell ref="E154:G154"/>
-    <mergeCell ref="F140:G140"/>
-    <mergeCell ref="F141:F142"/>
-    <mergeCell ref="F144:G144"/>
-    <mergeCell ref="F145:F146"/>
-    <mergeCell ref="C149:C150"/>
-    <mergeCell ref="D149:G149"/>
-    <mergeCell ref="E150:G150"/>
-    <mergeCell ref="E134:G134"/>
-    <mergeCell ref="E135:G135"/>
-    <mergeCell ref="E136:G136"/>
-    <mergeCell ref="E137:G137"/>
-    <mergeCell ref="C138:C139"/>
-    <mergeCell ref="D138:G138"/>
-    <mergeCell ref="E139:G139"/>
-    <mergeCell ref="E129:G129"/>
-    <mergeCell ref="E130:G130"/>
-    <mergeCell ref="C131:C133"/>
-    <mergeCell ref="D131:G131"/>
-    <mergeCell ref="E132:G132"/>
-    <mergeCell ref="E133:G133"/>
-    <mergeCell ref="E121:G121"/>
-    <mergeCell ref="E122:G122"/>
-    <mergeCell ref="C123:C126"/>
-    <mergeCell ref="D123:G123"/>
-    <mergeCell ref="E124:E125"/>
-    <mergeCell ref="F124:G124"/>
-    <mergeCell ref="E116:G116"/>
-    <mergeCell ref="E117:G117"/>
-    <mergeCell ref="C118:C119"/>
-    <mergeCell ref="D118:G118"/>
-    <mergeCell ref="E119:G119"/>
-    <mergeCell ref="E120:G120"/>
-    <mergeCell ref="C111:C112"/>
-    <mergeCell ref="D111:G111"/>
-    <mergeCell ref="E112:G112"/>
-    <mergeCell ref="E113:G113"/>
-    <mergeCell ref="C114:C115"/>
-    <mergeCell ref="D114:G114"/>
-    <mergeCell ref="E115:G115"/>
-    <mergeCell ref="C106:G106"/>
-    <mergeCell ref="C107:C108"/>
-    <mergeCell ref="D107:G107"/>
-    <mergeCell ref="E108:G108"/>
-    <mergeCell ref="E109:G109"/>
-    <mergeCell ref="E110:G110"/>
-    <mergeCell ref="E104:G104"/>
-    <mergeCell ref="C105:G105"/>
-    <mergeCell ref="E98:G98"/>
-    <mergeCell ref="E99:G99"/>
-    <mergeCell ref="E100:G100"/>
-    <mergeCell ref="C101:C103"/>
-    <mergeCell ref="D101:G101"/>
-    <mergeCell ref="E102:G102"/>
-    <mergeCell ref="E103:G103"/>
-    <mergeCell ref="E93:G93"/>
-    <mergeCell ref="E94:G94"/>
-    <mergeCell ref="C95:C96"/>
-    <mergeCell ref="D95:G95"/>
-    <mergeCell ref="E96:G96"/>
-    <mergeCell ref="E97:G97"/>
-    <mergeCell ref="C87:C88"/>
-    <mergeCell ref="D87:G87"/>
-    <mergeCell ref="E88:G88"/>
-    <mergeCell ref="E89:G89"/>
-    <mergeCell ref="E90:G90"/>
-    <mergeCell ref="C91:C92"/>
-    <mergeCell ref="D91:G91"/>
-    <mergeCell ref="E92:G92"/>
-    <mergeCell ref="F76:G76"/>
-    <mergeCell ref="E80:E81"/>
-    <mergeCell ref="F80:G80"/>
-    <mergeCell ref="G81:I81"/>
-    <mergeCell ref="E84:E85"/>
-    <mergeCell ref="F84:G84"/>
-    <mergeCell ref="E63:G63"/>
-    <mergeCell ref="E64:G64"/>
-    <mergeCell ref="C65:C67"/>
-    <mergeCell ref="D65:G65"/>
-    <mergeCell ref="F66:G66"/>
-    <mergeCell ref="F70:G70"/>
-    <mergeCell ref="E58:G58"/>
-    <mergeCell ref="E59:G59"/>
-    <mergeCell ref="C60:C62"/>
-    <mergeCell ref="D60:G60"/>
-    <mergeCell ref="E61:G61"/>
-    <mergeCell ref="E62:G62"/>
-    <mergeCell ref="E54:G54"/>
-    <mergeCell ref="C55:C57"/>
-    <mergeCell ref="D55:G55"/>
-    <mergeCell ref="E56:G56"/>
-    <mergeCell ref="E57:G57"/>
-    <mergeCell ref="C48:C49"/>
-    <mergeCell ref="D48:G48"/>
-    <mergeCell ref="E49:G49"/>
-    <mergeCell ref="E50:G50"/>
-    <mergeCell ref="E51:G51"/>
-    <mergeCell ref="C52:C53"/>
-    <mergeCell ref="D52:G52"/>
-    <mergeCell ref="E53:G53"/>
-    <mergeCell ref="C42:C44"/>
-    <mergeCell ref="D42:G42"/>
-    <mergeCell ref="D43:D44"/>
-    <mergeCell ref="E43:G43"/>
-    <mergeCell ref="E44:G44"/>
-    <mergeCell ref="C45:C47"/>
-    <mergeCell ref="D45:G45"/>
-    <mergeCell ref="D46:D47"/>
-    <mergeCell ref="E46:G46"/>
-    <mergeCell ref="E47:G47"/>
+    <mergeCell ref="B1:J1"/>
+    <mergeCell ref="B3:J3"/>
+    <mergeCell ref="B4:J4"/>
+    <mergeCell ref="B5:J5"/>
+    <mergeCell ref="B6:J6"/>
+    <mergeCell ref="B7:H7"/>
+    <mergeCell ref="B22:B24"/>
+    <mergeCell ref="C22:G24"/>
+    <mergeCell ref="I22:J24"/>
     <mergeCell ref="C29:G29"/>
     <mergeCell ref="C30:C34"/>
     <mergeCell ref="D30:G30"/>
@@ -14306,15 +14198,120 @@
     <mergeCell ref="D36:D37"/>
     <mergeCell ref="E36:G36"/>
     <mergeCell ref="E37:G37"/>
-    <mergeCell ref="B1:J1"/>
-    <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B4:J4"/>
-    <mergeCell ref="B5:J5"/>
-    <mergeCell ref="B6:J6"/>
-    <mergeCell ref="B7:H7"/>
-    <mergeCell ref="B22:B24"/>
-    <mergeCell ref="C22:G24"/>
-    <mergeCell ref="I22:J24"/>
+    <mergeCell ref="C48:C49"/>
+    <mergeCell ref="D48:G48"/>
+    <mergeCell ref="E49:G49"/>
+    <mergeCell ref="E50:G50"/>
+    <mergeCell ref="E51:G51"/>
+    <mergeCell ref="C52:C53"/>
+    <mergeCell ref="D52:G52"/>
+    <mergeCell ref="E53:G53"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="D42:G42"/>
+    <mergeCell ref="D43:D44"/>
+    <mergeCell ref="E43:G43"/>
+    <mergeCell ref="E44:G44"/>
+    <mergeCell ref="C45:C47"/>
+    <mergeCell ref="D45:G45"/>
+    <mergeCell ref="D46:D47"/>
+    <mergeCell ref="E46:G46"/>
+    <mergeCell ref="E47:G47"/>
+    <mergeCell ref="E58:G58"/>
+    <mergeCell ref="E59:G59"/>
+    <mergeCell ref="C60:C62"/>
+    <mergeCell ref="D60:G60"/>
+    <mergeCell ref="E61:G61"/>
+    <mergeCell ref="E62:G62"/>
+    <mergeCell ref="E54:G54"/>
+    <mergeCell ref="C55:C57"/>
+    <mergeCell ref="D55:G55"/>
+    <mergeCell ref="E56:G56"/>
+    <mergeCell ref="E57:G57"/>
+    <mergeCell ref="F76:G76"/>
+    <mergeCell ref="E80:E81"/>
+    <mergeCell ref="F80:G80"/>
+    <mergeCell ref="G81:I81"/>
+    <mergeCell ref="E84:E85"/>
+    <mergeCell ref="F84:G84"/>
+    <mergeCell ref="E63:G63"/>
+    <mergeCell ref="E64:G64"/>
+    <mergeCell ref="C65:C67"/>
+    <mergeCell ref="D65:G65"/>
+    <mergeCell ref="F66:G66"/>
+    <mergeCell ref="F70:G70"/>
+    <mergeCell ref="E93:G93"/>
+    <mergeCell ref="E94:G94"/>
+    <mergeCell ref="C95:C96"/>
+    <mergeCell ref="D95:G95"/>
+    <mergeCell ref="E96:G96"/>
+    <mergeCell ref="E97:G97"/>
+    <mergeCell ref="C87:C88"/>
+    <mergeCell ref="D87:G87"/>
+    <mergeCell ref="E88:G88"/>
+    <mergeCell ref="E89:G89"/>
+    <mergeCell ref="E90:G90"/>
+    <mergeCell ref="C91:C92"/>
+    <mergeCell ref="D91:G91"/>
+    <mergeCell ref="E92:G92"/>
+    <mergeCell ref="E104:G104"/>
+    <mergeCell ref="C105:G105"/>
+    <mergeCell ref="E98:G98"/>
+    <mergeCell ref="E99:G99"/>
+    <mergeCell ref="E100:G100"/>
+    <mergeCell ref="C101:C103"/>
+    <mergeCell ref="D101:G101"/>
+    <mergeCell ref="E102:G102"/>
+    <mergeCell ref="E103:G103"/>
+    <mergeCell ref="C111:C112"/>
+    <mergeCell ref="D111:G111"/>
+    <mergeCell ref="E112:G112"/>
+    <mergeCell ref="E113:G113"/>
+    <mergeCell ref="C114:C115"/>
+    <mergeCell ref="D114:G114"/>
+    <mergeCell ref="E115:G115"/>
+    <mergeCell ref="C106:G106"/>
+    <mergeCell ref="C107:C108"/>
+    <mergeCell ref="D107:G107"/>
+    <mergeCell ref="E108:G108"/>
+    <mergeCell ref="E109:G109"/>
+    <mergeCell ref="E110:G110"/>
+    <mergeCell ref="E121:G121"/>
+    <mergeCell ref="E122:G122"/>
+    <mergeCell ref="C123:C126"/>
+    <mergeCell ref="D123:G123"/>
+    <mergeCell ref="E124:E125"/>
+    <mergeCell ref="F124:G124"/>
+    <mergeCell ref="E116:G116"/>
+    <mergeCell ref="E117:G117"/>
+    <mergeCell ref="C118:C119"/>
+    <mergeCell ref="D118:G118"/>
+    <mergeCell ref="E119:G119"/>
+    <mergeCell ref="E120:G120"/>
+    <mergeCell ref="E134:G134"/>
+    <mergeCell ref="E135:G135"/>
+    <mergeCell ref="E136:G136"/>
+    <mergeCell ref="E137:G137"/>
+    <mergeCell ref="C138:C139"/>
+    <mergeCell ref="D138:G138"/>
+    <mergeCell ref="E139:G139"/>
+    <mergeCell ref="E129:G129"/>
+    <mergeCell ref="E130:G130"/>
+    <mergeCell ref="C131:C133"/>
+    <mergeCell ref="D131:G131"/>
+    <mergeCell ref="E132:G132"/>
+    <mergeCell ref="E133:G133"/>
+    <mergeCell ref="E151:G151"/>
+    <mergeCell ref="C152:C153"/>
+    <mergeCell ref="D152:G152"/>
+    <mergeCell ref="E153:G153"/>
+    <mergeCell ref="E154:G154"/>
+    <mergeCell ref="F140:G140"/>
+    <mergeCell ref="F141:F142"/>
+    <mergeCell ref="F144:G144"/>
+    <mergeCell ref="F145:F146"/>
+    <mergeCell ref="C149:C150"/>
+    <mergeCell ref="D149:G149"/>
+    <mergeCell ref="E150:G150"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="64" orientation="portrait" r:id="rId1"/>
@@ -14344,15 +14341,15 @@
       <c r="A1" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="320" t="s">
+      <c r="B1" s="357" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="320"/>
-      <c r="D1" s="320"/>
-      <c r="E1" s="320"/>
-      <c r="F1" s="320"/>
-      <c r="G1" s="320"/>
-      <c r="H1" s="320"/>
+      <c r="C1" s="357"/>
+      <c r="D1" s="357"/>
+      <c r="E1" s="357"/>
+      <c r="F1" s="357"/>
+      <c r="G1" s="357"/>
+      <c r="H1" s="357"/>
       <c r="L1" s="51"/>
     </row>
     <row r="2" spans="1:13" ht="15.75" customHeight="1">
@@ -14386,30 +14383,30 @@
       <c r="A3" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="321" t="s">
+      <c r="B3" s="358" t="s">
         <v>167</v>
       </c>
-      <c r="C3" s="321"/>
-      <c r="D3" s="321"/>
-      <c r="E3" s="321"/>
-      <c r="F3" s="321"/>
-      <c r="G3" s="321"/>
-      <c r="H3" s="321"/>
+      <c r="C3" s="358"/>
+      <c r="D3" s="358"/>
+      <c r="E3" s="358"/>
+      <c r="F3" s="358"/>
+      <c r="G3" s="358"/>
+      <c r="H3" s="358"/>
       <c r="L3" s="51"/>
     </row>
     <row r="4" spans="1:13" ht="14.25" customHeight="1">
       <c r="A4" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="322" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="322"/>
-      <c r="D4" s="322"/>
-      <c r="E4" s="322"/>
-      <c r="F4" s="322"/>
-      <c r="G4" s="322"/>
-      <c r="H4" s="322"/>
+      <c r="B4" s="359" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="359"/>
+      <c r="D4" s="359"/>
+      <c r="E4" s="359"/>
+      <c r="F4" s="359"/>
+      <c r="G4" s="359"/>
+      <c r="H4" s="359"/>
       <c r="L4" s="51"/>
       <c r="M4" s="53"/>
     </row>
@@ -14431,40 +14428,40 @@
       <c r="A19" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="B19" s="375" t="s">
+      <c r="B19" s="382" t="s">
         <v>0</v>
       </c>
-      <c r="C19" s="328" t="s">
+      <c r="C19" s="365" t="s">
         <v>51</v>
       </c>
-      <c r="D19" s="329"/>
-      <c r="E19" s="329"/>
-      <c r="F19" s="329"/>
-      <c r="G19" s="330"/>
+      <c r="D19" s="366"/>
+      <c r="E19" s="366"/>
+      <c r="F19" s="366"/>
+      <c r="G19" s="367"/>
       <c r="H19" s="55"/>
     </row>
     <row r="20" spans="1:13" ht="12" customHeight="1">
       <c r="A20" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B20" s="326"/>
-      <c r="C20" s="331"/>
-      <c r="D20" s="332"/>
-      <c r="E20" s="332"/>
-      <c r="F20" s="332"/>
-      <c r="G20" s="333"/>
+      <c r="B20" s="363"/>
+      <c r="C20" s="368"/>
+      <c r="D20" s="369"/>
+      <c r="E20" s="369"/>
+      <c r="F20" s="369"/>
+      <c r="G20" s="370"/>
       <c r="H20" s="55"/>
     </row>
     <row r="21" spans="1:13" ht="24" customHeight="1">
       <c r="A21" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B21" s="327"/>
-      <c r="C21" s="334"/>
-      <c r="D21" s="335"/>
-      <c r="E21" s="335"/>
-      <c r="F21" s="335"/>
-      <c r="G21" s="336"/>
+      <c r="B21" s="364"/>
+      <c r="C21" s="371"/>
+      <c r="D21" s="372"/>
+      <c r="E21" s="372"/>
+      <c r="F21" s="372"/>
+      <c r="G21" s="373"/>
       <c r="H21" s="57" t="s">
         <v>52</v>
       </c>
@@ -14480,17 +14477,17 @@
       <c r="B25" s="57">
         <v>1</v>
       </c>
-      <c r="C25" s="376">
+      <c r="C25" s="383">
         <v>2</v>
       </c>
-      <c r="D25" s="377"/>
+      <c r="D25" s="384"/>
       <c r="E25" s="57">
         <v>3</v>
       </c>
-      <c r="F25" s="376">
+      <c r="F25" s="383">
         <v>4</v>
       </c>
-      <c r="G25" s="377"/>
+      <c r="G25" s="384"/>
       <c r="H25" s="57">
         <v>8</v>
       </c>
@@ -14546,15 +14543,15 @@
       <c r="B29" s="58">
         <v>2</v>
       </c>
-      <c r="C29" s="378" t="s">
+      <c r="C29" s="374" t="s">
         <v>54</v>
       </c>
-      <c r="D29" s="379"/>
-      <c r="E29" s="337" t="s">
+      <c r="D29" s="375"/>
+      <c r="E29" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="F29" s="338"/>
-      <c r="G29" s="339"/>
+      <c r="F29" s="324"/>
+      <c r="G29" s="325"/>
       <c r="H29" s="64"/>
       <c r="I29" s="49"/>
       <c r="M29" s="65"/>
@@ -14566,15 +14563,15 @@
       <c r="B30" s="58">
         <v>3</v>
       </c>
-      <c r="C30" s="380"/>
-      <c r="D30" s="381"/>
+      <c r="C30" s="376"/>
+      <c r="D30" s="377"/>
       <c r="E30" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F30" s="356" t="s">
+      <c r="F30" s="336" t="s">
         <v>56</v>
       </c>
-      <c r="G30" s="358"/>
+      <c r="G30" s="338"/>
       <c r="H30" s="72" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -14589,15 +14586,15 @@
       <c r="B31" s="58">
         <v>4</v>
       </c>
-      <c r="C31" s="380"/>
-      <c r="D31" s="381"/>
+      <c r="C31" s="376"/>
+      <c r="D31" s="377"/>
       <c r="E31" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="F31" s="356" t="s">
+      <c r="F31" s="336" t="s">
         <v>57</v>
       </c>
-      <c r="G31" s="358"/>
+      <c r="G31" s="338"/>
       <c r="H31" s="64"/>
       <c r="I31" s="49"/>
       <c r="M31" s="53"/>
@@ -14609,15 +14606,15 @@
       <c r="B32" s="58">
         <v>5</v>
       </c>
-      <c r="C32" s="380"/>
-      <c r="D32" s="381"/>
+      <c r="C32" s="376"/>
+      <c r="D32" s="377"/>
       <c r="E32" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="F32" s="356" t="s">
+      <c r="F32" s="336" t="s">
         <v>58</v>
       </c>
-      <c r="G32" s="358"/>
+      <c r="G32" s="338"/>
       <c r="H32" s="64"/>
       <c r="I32" s="49"/>
     </row>
@@ -14637,10 +14634,10 @@
       <c r="E33" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F33" s="346" t="s">
+      <c r="F33" s="319" t="s">
         <v>170</v>
       </c>
-      <c r="G33" s="348"/>
+      <c r="G33" s="321"/>
       <c r="H33" s="64"/>
       <c r="I33" s="49"/>
       <c r="J33" s="49"/>
@@ -14661,10 +14658,10 @@
       <c r="E34" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F34" s="346" t="s">
-        <v>44</v>
-      </c>
-      <c r="G34" s="348"/>
+      <c r="F34" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="G34" s="321"/>
       <c r="H34" s="64"/>
       <c r="I34" s="49"/>
       <c r="J34" s="49"/>
@@ -14677,15 +14674,15 @@
       <c r="B35" s="58">
         <v>8</v>
       </c>
-      <c r="C35" s="378" t="s">
+      <c r="C35" s="374" t="s">
         <v>171</v>
       </c>
-      <c r="D35" s="379"/>
-      <c r="E35" s="337" t="s">
+      <c r="D35" s="375"/>
+      <c r="E35" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="F35" s="338"/>
-      <c r="G35" s="339"/>
+      <c r="F35" s="324"/>
+      <c r="G35" s="325"/>
       <c r="H35" s="64"/>
       <c r="I35" s="49"/>
     </row>
@@ -14696,15 +14693,15 @@
       <c r="B36" s="58">
         <v>9</v>
       </c>
-      <c r="C36" s="380"/>
-      <c r="D36" s="381"/>
-      <c r="E36" s="373" t="s">
+      <c r="C36" s="376"/>
+      <c r="D36" s="377"/>
+      <c r="E36" s="330" t="s">
         <v>55</v>
       </c>
-      <c r="F36" s="356" t="s">
+      <c r="F36" s="336" t="s">
         <v>172</v>
       </c>
-      <c r="G36" s="358"/>
+      <c r="G36" s="338"/>
       <c r="H36" s="72" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -14719,13 +14716,13 @@
       <c r="B37" s="58">
         <v>10</v>
       </c>
-      <c r="C37" s="382"/>
-      <c r="D37" s="383"/>
-      <c r="E37" s="374"/>
-      <c r="F37" s="356" t="s">
+      <c r="C37" s="380"/>
+      <c r="D37" s="381"/>
+      <c r="E37" s="331"/>
+      <c r="F37" s="336" t="s">
         <v>173</v>
       </c>
-      <c r="G37" s="358"/>
+      <c r="G37" s="338"/>
       <c r="H37" s="64"/>
       <c r="I37" s="49"/>
     </row>
@@ -14736,15 +14733,15 @@
       <c r="B38" s="58">
         <v>11</v>
       </c>
-      <c r="C38" s="378" t="s">
+      <c r="C38" s="374" t="s">
         <v>174</v>
       </c>
-      <c r="D38" s="379"/>
-      <c r="E38" s="337" t="s">
+      <c r="D38" s="375"/>
+      <c r="E38" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="F38" s="338"/>
-      <c r="G38" s="339"/>
+      <c r="F38" s="324"/>
+      <c r="G38" s="325"/>
       <c r="H38" s="64"/>
       <c r="I38" s="49"/>
     </row>
@@ -14755,15 +14752,15 @@
       <c r="B39" s="58">
         <v>12</v>
       </c>
-      <c r="C39" s="380"/>
-      <c r="D39" s="381"/>
+      <c r="C39" s="376"/>
+      <c r="D39" s="377"/>
       <c r="E39" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F39" s="384" t="s">
-        <v>44</v>
-      </c>
-      <c r="G39" s="385"/>
+      <c r="F39" s="378" t="s">
+        <v>44</v>
+      </c>
+      <c r="G39" s="379"/>
       <c r="H39" s="64"/>
       <c r="I39" s="49"/>
     </row>
@@ -14783,10 +14780,10 @@
       <c r="E40" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F40" s="346" t="s">
-        <v>44</v>
-      </c>
-      <c r="G40" s="348"/>
+      <c r="F40" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="G40" s="321"/>
       <c r="H40" s="64"/>
       <c r="I40" s="49"/>
       <c r="J40" s="49"/>
@@ -14798,15 +14795,15 @@
       <c r="B41" s="58">
         <v>14</v>
       </c>
-      <c r="C41" s="378" t="s">
+      <c r="C41" s="374" t="s">
         <v>175</v>
       </c>
-      <c r="D41" s="379"/>
-      <c r="E41" s="337" t="s">
+      <c r="D41" s="375"/>
+      <c r="E41" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="F41" s="338"/>
-      <c r="G41" s="339"/>
+      <c r="F41" s="324"/>
+      <c r="G41" s="325"/>
       <c r="H41" s="64"/>
       <c r="I41" s="49"/>
     </row>
@@ -14817,15 +14814,15 @@
       <c r="B42" s="58">
         <v>15</v>
       </c>
-      <c r="C42" s="380"/>
-      <c r="D42" s="381"/>
+      <c r="C42" s="376"/>
+      <c r="D42" s="377"/>
       <c r="E42" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F42" s="356" t="s">
+      <c r="F42" s="336" t="s">
         <v>91</v>
       </c>
-      <c r="G42" s="358"/>
+      <c r="G42" s="338"/>
       <c r="H42" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -14848,10 +14845,10 @@
       <c r="E43" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F43" s="346" t="s">
+      <c r="F43" s="319" t="s">
         <v>176</v>
       </c>
-      <c r="G43" s="348"/>
+      <c r="G43" s="321"/>
       <c r="H43" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -14875,10 +14872,10 @@
       <c r="E44" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F44" s="346" t="s">
-        <v>44</v>
-      </c>
-      <c r="G44" s="348"/>
+      <c r="F44" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="G44" s="321"/>
       <c r="H44" s="64"/>
       <c r="I44" s="49"/>
       <c r="J44" s="49"/>
@@ -14890,15 +14887,15 @@
       <c r="B45" s="58">
         <v>18</v>
       </c>
-      <c r="C45" s="378" t="s">
+      <c r="C45" s="374" t="s">
         <v>177</v>
       </c>
-      <c r="D45" s="379"/>
-      <c r="E45" s="337" t="s">
+      <c r="D45" s="375"/>
+      <c r="E45" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="F45" s="338"/>
-      <c r="G45" s="339"/>
+      <c r="F45" s="324"/>
+      <c r="G45" s="325"/>
       <c r="H45" s="64"/>
       <c r="I45" s="49"/>
     </row>
@@ -14909,15 +14906,15 @@
       <c r="B46" s="58">
         <v>19</v>
       </c>
-      <c r="C46" s="380"/>
-      <c r="D46" s="381"/>
+      <c r="C46" s="376"/>
+      <c r="D46" s="377"/>
       <c r="E46" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F46" s="384" t="s">
-        <v>44</v>
-      </c>
-      <c r="G46" s="385"/>
+      <c r="F46" s="378" t="s">
+        <v>44</v>
+      </c>
+      <c r="G46" s="379"/>
       <c r="H46" s="64"/>
       <c r="I46" s="49"/>
     </row>
@@ -14937,8 +14934,8 @@
       <c r="E47" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F47" s="346"/>
-      <c r="G47" s="348"/>
+      <c r="F47" s="319"/>
+      <c r="G47" s="321"/>
       <c r="H47" s="64"/>
       <c r="I47" s="49"/>
       <c r="J47" s="49"/>
@@ -14959,10 +14956,10 @@
       <c r="E48" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F48" s="346" t="s">
+      <c r="F48" s="319" t="s">
         <v>178</v>
       </c>
-      <c r="G48" s="348"/>
+      <c r="G48" s="321"/>
       <c r="H48" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -14986,10 +14983,10 @@
       <c r="E49" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F49" s="346" t="s">
+      <c r="F49" s="319" t="s">
         <v>8</v>
       </c>
-      <c r="G49" s="348"/>
+      <c r="G49" s="321"/>
       <c r="H49" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15004,13 +15001,13 @@
       <c r="B50" s="58">
         <v>24</v>
       </c>
-      <c r="C50" s="337" t="s">
+      <c r="C50" s="323" t="s">
         <v>179</v>
       </c>
-      <c r="D50" s="338"/>
-      <c r="E50" s="338"/>
-      <c r="F50" s="338"/>
-      <c r="G50" s="339"/>
+      <c r="D50" s="324"/>
+      <c r="E50" s="324"/>
+      <c r="F50" s="324"/>
+      <c r="G50" s="325"/>
       <c r="H50" s="64"/>
       <c r="I50" s="49"/>
     </row>
@@ -15021,13 +15018,13 @@
       <c r="B51" s="58">
         <v>25</v>
       </c>
-      <c r="C51" s="337" t="s">
+      <c r="C51" s="323" t="s">
         <v>180</v>
       </c>
-      <c r="D51" s="338"/>
-      <c r="E51" s="338"/>
-      <c r="F51" s="338"/>
-      <c r="G51" s="339"/>
+      <c r="D51" s="324"/>
+      <c r="E51" s="324"/>
+      <c r="F51" s="324"/>
+      <c r="G51" s="325"/>
       <c r="H51" s="64" t="e">
         <f>нак.расх.!G29-зат.осн.про.!H75-зат.осн.про.!H99</f>
         <v>#REF!</v>
@@ -15073,15 +15070,15 @@
       <c r="B53" s="58">
         <v>2</v>
       </c>
-      <c r="C53" s="378" t="s">
+      <c r="C53" s="374" t="s">
         <v>54</v>
       </c>
-      <c r="D53" s="379"/>
-      <c r="E53" s="337" t="s">
+      <c r="D53" s="375"/>
+      <c r="E53" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="F53" s="338"/>
-      <c r="G53" s="339"/>
+      <c r="F53" s="324"/>
+      <c r="G53" s="325"/>
       <c r="H53" s="64"/>
       <c r="I53" s="49"/>
       <c r="M53" s="53" t="e">
@@ -15096,15 +15093,15 @@
       <c r="B54" s="58">
         <v>3</v>
       </c>
-      <c r="C54" s="380"/>
-      <c r="D54" s="381"/>
+      <c r="C54" s="376"/>
+      <c r="D54" s="377"/>
       <c r="E54" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F54" s="356" t="s">
+      <c r="F54" s="336" t="s">
         <v>56</v>
       </c>
-      <c r="G54" s="358"/>
+      <c r="G54" s="338"/>
       <c r="H54" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15118,15 +15115,15 @@
       <c r="B55" s="58">
         <v>4</v>
       </c>
-      <c r="C55" s="380"/>
-      <c r="D55" s="381"/>
+      <c r="C55" s="376"/>
+      <c r="D55" s="377"/>
       <c r="E55" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="F55" s="356" t="s">
+      <c r="F55" s="336" t="s">
         <v>57</v>
       </c>
-      <c r="G55" s="358"/>
+      <c r="G55" s="338"/>
       <c r="H55" s="64"/>
       <c r="I55" s="49"/>
     </row>
@@ -15137,15 +15134,15 @@
       <c r="B56" s="58">
         <v>5</v>
       </c>
-      <c r="C56" s="380"/>
-      <c r="D56" s="381"/>
+      <c r="C56" s="376"/>
+      <c r="D56" s="377"/>
       <c r="E56" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="F56" s="356" t="s">
+      <c r="F56" s="336" t="s">
         <v>58</v>
       </c>
-      <c r="G56" s="358"/>
+      <c r="G56" s="338"/>
       <c r="H56" s="64"/>
       <c r="I56" s="49"/>
     </row>
@@ -15165,10 +15162,10 @@
       <c r="E57" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F57" s="346" t="s">
+      <c r="F57" s="319" t="s">
         <v>170</v>
       </c>
-      <c r="G57" s="348"/>
+      <c r="G57" s="321"/>
       <c r="H57" s="64"/>
       <c r="I57" s="49"/>
       <c r="J57" s="49"/>
@@ -15189,10 +15186,10 @@
       <c r="E58" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F58" s="346" t="s">
-        <v>44</v>
-      </c>
-      <c r="G58" s="348"/>
+      <c r="F58" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="G58" s="321"/>
       <c r="H58" s="64"/>
       <c r="I58" s="49"/>
     </row>
@@ -15203,15 +15200,15 @@
       <c r="B59" s="58">
         <v>8</v>
       </c>
-      <c r="C59" s="378" t="s">
+      <c r="C59" s="374" t="s">
         <v>171</v>
       </c>
-      <c r="D59" s="379"/>
-      <c r="E59" s="337" t="s">
+      <c r="D59" s="375"/>
+      <c r="E59" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="F59" s="338"/>
-      <c r="G59" s="339"/>
+      <c r="F59" s="324"/>
+      <c r="G59" s="325"/>
       <c r="H59" s="64"/>
       <c r="I59" s="49"/>
     </row>
@@ -15222,15 +15219,15 @@
       <c r="B60" s="58">
         <v>9</v>
       </c>
-      <c r="C60" s="380"/>
-      <c r="D60" s="381"/>
-      <c r="E60" s="373" t="s">
+      <c r="C60" s="376"/>
+      <c r="D60" s="377"/>
+      <c r="E60" s="330" t="s">
         <v>55</v>
       </c>
-      <c r="F60" s="356" t="s">
+      <c r="F60" s="336" t="s">
         <v>172</v>
       </c>
-      <c r="G60" s="358"/>
+      <c r="G60" s="338"/>
       <c r="H60" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15244,13 +15241,13 @@
       <c r="B61" s="58">
         <v>10</v>
       </c>
-      <c r="C61" s="382"/>
-      <c r="D61" s="383"/>
-      <c r="E61" s="374"/>
-      <c r="F61" s="356" t="s">
+      <c r="C61" s="380"/>
+      <c r="D61" s="381"/>
+      <c r="E61" s="331"/>
+      <c r="F61" s="336" t="s">
         <v>173</v>
       </c>
-      <c r="G61" s="358"/>
+      <c r="G61" s="338"/>
       <c r="H61" s="64"/>
       <c r="I61" s="49"/>
     </row>
@@ -15261,15 +15258,15 @@
       <c r="B62" s="58">
         <v>11</v>
       </c>
-      <c r="C62" s="378" t="s">
+      <c r="C62" s="374" t="s">
         <v>174</v>
       </c>
-      <c r="D62" s="379"/>
-      <c r="E62" s="337" t="s">
+      <c r="D62" s="375"/>
+      <c r="E62" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="F62" s="338"/>
-      <c r="G62" s="339"/>
+      <c r="F62" s="324"/>
+      <c r="G62" s="325"/>
       <c r="H62" s="64"/>
       <c r="I62" s="49"/>
     </row>
@@ -15280,15 +15277,15 @@
       <c r="B63" s="58">
         <v>12</v>
       </c>
-      <c r="C63" s="380"/>
-      <c r="D63" s="381"/>
+      <c r="C63" s="376"/>
+      <c r="D63" s="377"/>
       <c r="E63" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F63" s="384" t="s">
-        <v>44</v>
-      </c>
-      <c r="G63" s="385"/>
+      <c r="F63" s="378" t="s">
+        <v>44</v>
+      </c>
+      <c r="G63" s="379"/>
       <c r="H63" s="64"/>
       <c r="I63" s="49"/>
       <c r="J63" s="49"/>
@@ -15309,10 +15306,10 @@
       <c r="E64" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F64" s="346" t="s">
-        <v>44</v>
-      </c>
-      <c r="G64" s="348"/>
+      <c r="F64" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="G64" s="321"/>
       <c r="H64" s="64"/>
       <c r="I64" s="49"/>
     </row>
@@ -15323,15 +15320,15 @@
       <c r="B65" s="58">
         <v>14</v>
       </c>
-      <c r="C65" s="378" t="s">
+      <c r="C65" s="374" t="s">
         <v>175</v>
       </c>
-      <c r="D65" s="379"/>
-      <c r="E65" s="337" t="s">
+      <c r="D65" s="375"/>
+      <c r="E65" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="F65" s="338"/>
-      <c r="G65" s="339"/>
+      <c r="F65" s="324"/>
+      <c r="G65" s="325"/>
       <c r="H65" s="64"/>
       <c r="I65" s="49"/>
     </row>
@@ -15342,15 +15339,15 @@
       <c r="B66" s="58">
         <v>15</v>
       </c>
-      <c r="C66" s="380"/>
-      <c r="D66" s="381"/>
+      <c r="C66" s="376"/>
+      <c r="D66" s="377"/>
       <c r="E66" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F66" s="356" t="s">
+      <c r="F66" s="336" t="s">
         <v>91</v>
       </c>
-      <c r="G66" s="358"/>
+      <c r="G66" s="338"/>
       <c r="H66" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15374,10 +15371,10 @@
       <c r="E67" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F67" s="346" t="s">
+      <c r="F67" s="319" t="s">
         <v>176</v>
       </c>
-      <c r="G67" s="348"/>
+      <c r="G67" s="321"/>
       <c r="H67" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15400,10 +15397,10 @@
       <c r="E68" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F68" s="346" t="s">
-        <v>44</v>
-      </c>
-      <c r="G68" s="348"/>
+      <c r="F68" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="G68" s="321"/>
       <c r="H68" s="64"/>
       <c r="I68" s="49"/>
     </row>
@@ -15414,15 +15411,15 @@
       <c r="B69" s="58">
         <v>18</v>
       </c>
-      <c r="C69" s="378" t="s">
+      <c r="C69" s="374" t="s">
         <v>177</v>
       </c>
-      <c r="D69" s="379"/>
-      <c r="E69" s="337" t="s">
+      <c r="D69" s="375"/>
+      <c r="E69" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="F69" s="338"/>
-      <c r="G69" s="339"/>
+      <c r="F69" s="324"/>
+      <c r="G69" s="325"/>
       <c r="H69" s="64"/>
       <c r="I69" s="49"/>
       <c r="J69" s="49"/>
@@ -15434,15 +15431,15 @@
       <c r="B70" s="58">
         <v>19</v>
       </c>
-      <c r="C70" s="380"/>
-      <c r="D70" s="381"/>
+      <c r="C70" s="376"/>
+      <c r="D70" s="377"/>
       <c r="E70" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F70" s="384" t="s">
-        <v>44</v>
-      </c>
-      <c r="G70" s="385"/>
+      <c r="F70" s="378" t="s">
+        <v>44</v>
+      </c>
+      <c r="G70" s="379"/>
       <c r="H70" s="64"/>
       <c r="I70" s="49"/>
     </row>
@@ -15462,8 +15459,8 @@
       <c r="E71" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F71" s="346"/>
-      <c r="G71" s="348"/>
+      <c r="F71" s="319"/>
+      <c r="G71" s="321"/>
       <c r="H71" s="64"/>
       <c r="I71" s="49"/>
     </row>
@@ -15480,10 +15477,10 @@
       <c r="E72" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F72" s="346" t="s">
+      <c r="F72" s="319" t="s">
         <v>178</v>
       </c>
-      <c r="G72" s="348"/>
+      <c r="G72" s="321"/>
       <c r="H72" s="64"/>
       <c r="I72" s="49"/>
       <c r="J72" s="49"/>
@@ -15506,10 +15503,10 @@
       <c r="E73" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F73" s="346" t="s">
+      <c r="F73" s="319" t="s">
         <v>8</v>
       </c>
-      <c r="G73" s="348"/>
+      <c r="G73" s="321"/>
       <c r="H73" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15523,13 +15520,13 @@
       <c r="B74" s="58">
         <v>24</v>
       </c>
-      <c r="C74" s="337" t="s">
+      <c r="C74" s="323" t="s">
         <v>179</v>
       </c>
-      <c r="D74" s="338"/>
-      <c r="E74" s="338"/>
-      <c r="F74" s="338"/>
-      <c r="G74" s="339"/>
+      <c r="D74" s="324"/>
+      <c r="E74" s="324"/>
+      <c r="F74" s="324"/>
+      <c r="G74" s="325"/>
       <c r="H74" s="64"/>
       <c r="I74" s="49"/>
       <c r="J74" s="49"/>
@@ -15540,13 +15537,13 @@
       <c r="B75" s="58">
         <v>25</v>
       </c>
-      <c r="C75" s="337" t="s">
+      <c r="C75" s="323" t="s">
         <v>180</v>
       </c>
-      <c r="D75" s="338"/>
-      <c r="E75" s="338"/>
-      <c r="F75" s="338"/>
-      <c r="G75" s="339"/>
+      <c r="D75" s="324"/>
+      <c r="E75" s="324"/>
+      <c r="F75" s="324"/>
+      <c r="G75" s="325"/>
       <c r="H75" s="64" t="e">
         <f>нак.расх.!G29*4%</f>
         <v>#REF!</v>
@@ -15592,15 +15589,15 @@
       <c r="B77" s="58">
         <v>2</v>
       </c>
-      <c r="C77" s="378" t="s">
+      <c r="C77" s="374" t="s">
         <v>54</v>
       </c>
-      <c r="D77" s="379"/>
-      <c r="E77" s="337" t="s">
+      <c r="D77" s="375"/>
+      <c r="E77" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="F77" s="338"/>
-      <c r="G77" s="339"/>
+      <c r="F77" s="324"/>
+      <c r="G77" s="325"/>
       <c r="H77" s="64"/>
       <c r="M77" s="53" t="e">
         <f>H76-M76</f>
@@ -15611,15 +15608,15 @@
       <c r="B78" s="58">
         <v>3</v>
       </c>
-      <c r="C78" s="380"/>
-      <c r="D78" s="381"/>
+      <c r="C78" s="376"/>
+      <c r="D78" s="377"/>
       <c r="E78" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F78" s="356" t="s">
+      <c r="F78" s="336" t="s">
         <v>56</v>
       </c>
-      <c r="G78" s="358"/>
+      <c r="G78" s="338"/>
       <c r="H78" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15629,30 +15626,30 @@
       <c r="B79" s="58">
         <v>4</v>
       </c>
-      <c r="C79" s="380"/>
-      <c r="D79" s="381"/>
+      <c r="C79" s="376"/>
+      <c r="D79" s="377"/>
       <c r="E79" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="F79" s="356" t="s">
+      <c r="F79" s="336" t="s">
         <v>57</v>
       </c>
-      <c r="G79" s="358"/>
+      <c r="G79" s="338"/>
       <c r="H79" s="64"/>
     </row>
     <row r="80" spans="1:13" ht="15.75" customHeight="1">
       <c r="B80" s="58">
         <v>5</v>
       </c>
-      <c r="C80" s="380"/>
-      <c r="D80" s="381"/>
+      <c r="C80" s="376"/>
+      <c r="D80" s="377"/>
       <c r="E80" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="F80" s="356" t="s">
+      <c r="F80" s="336" t="s">
         <v>58</v>
       </c>
-      <c r="G80" s="358"/>
+      <c r="G80" s="338"/>
       <c r="H80" s="64"/>
     </row>
     <row r="81" spans="2:8" ht="15.75" customHeight="1">
@@ -15668,10 +15665,10 @@
       <c r="E81" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F81" s="346" t="s">
+      <c r="F81" s="319" t="s">
         <v>170</v>
       </c>
-      <c r="G81" s="348"/>
+      <c r="G81" s="321"/>
       <c r="H81" s="64"/>
     </row>
     <row r="82" spans="2:8" ht="15.75" customHeight="1">
@@ -15687,40 +15684,40 @@
       <c r="E82" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F82" s="346" t="s">
-        <v>44</v>
-      </c>
-      <c r="G82" s="348"/>
+      <c r="F82" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="G82" s="321"/>
       <c r="H82" s="64"/>
     </row>
     <row r="83" spans="2:8" ht="15.75" customHeight="1">
       <c r="B83" s="58">
         <v>8</v>
       </c>
-      <c r="C83" s="378" t="s">
+      <c r="C83" s="374" t="s">
         <v>171</v>
       </c>
-      <c r="D83" s="379"/>
-      <c r="E83" s="337" t="s">
+      <c r="D83" s="375"/>
+      <c r="E83" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="F83" s="338"/>
-      <c r="G83" s="339"/>
+      <c r="F83" s="324"/>
+      <c r="G83" s="325"/>
       <c r="H83" s="64"/>
     </row>
     <row r="84" spans="2:8" ht="15.75" customHeight="1">
       <c r="B84" s="58">
         <v>9</v>
       </c>
-      <c r="C84" s="380"/>
-      <c r="D84" s="381"/>
-      <c r="E84" s="373" t="s">
+      <c r="C84" s="376"/>
+      <c r="D84" s="377"/>
+      <c r="E84" s="330" t="s">
         <v>55</v>
       </c>
-      <c r="F84" s="356" t="s">
+      <c r="F84" s="336" t="s">
         <v>172</v>
       </c>
-      <c r="G84" s="358"/>
+      <c r="G84" s="338"/>
       <c r="H84" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15730,43 +15727,43 @@
       <c r="B85" s="58">
         <v>10</v>
       </c>
-      <c r="C85" s="382"/>
-      <c r="D85" s="383"/>
-      <c r="E85" s="374"/>
-      <c r="F85" s="356" t="s">
+      <c r="C85" s="380"/>
+      <c r="D85" s="381"/>
+      <c r="E85" s="331"/>
+      <c r="F85" s="336" t="s">
         <v>173</v>
       </c>
-      <c r="G85" s="358"/>
+      <c r="G85" s="338"/>
       <c r="H85" s="64"/>
     </row>
     <row r="86" spans="2:8" ht="15.75" customHeight="1">
       <c r="B86" s="58">
         <v>11</v>
       </c>
-      <c r="C86" s="378" t="s">
+      <c r="C86" s="374" t="s">
         <v>174</v>
       </c>
-      <c r="D86" s="379"/>
-      <c r="E86" s="337" t="s">
+      <c r="D86" s="375"/>
+      <c r="E86" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="F86" s="338"/>
-      <c r="G86" s="339"/>
+      <c r="F86" s="324"/>
+      <c r="G86" s="325"/>
       <c r="H86" s="64"/>
     </row>
     <row r="87" spans="2:8" ht="15.75" customHeight="1">
       <c r="B87" s="58">
         <v>12</v>
       </c>
-      <c r="C87" s="380"/>
-      <c r="D87" s="381"/>
+      <c r="C87" s="376"/>
+      <c r="D87" s="377"/>
       <c r="E87" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F87" s="384" t="s">
-        <v>44</v>
-      </c>
-      <c r="G87" s="385"/>
+      <c r="F87" s="378" t="s">
+        <v>44</v>
+      </c>
+      <c r="G87" s="379"/>
       <c r="H87" s="64"/>
     </row>
     <row r="88" spans="2:8" ht="15.75" customHeight="1">
@@ -15782,40 +15779,40 @@
       <c r="E88" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F88" s="346" t="s">
-        <v>44</v>
-      </c>
-      <c r="G88" s="348"/>
+      <c r="F88" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="G88" s="321"/>
       <c r="H88" s="64"/>
     </row>
     <row r="89" spans="2:8" ht="15.75" customHeight="1">
       <c r="B89" s="58">
         <v>14</v>
       </c>
-      <c r="C89" s="378" t="s">
+      <c r="C89" s="374" t="s">
         <v>175</v>
       </c>
-      <c r="D89" s="379"/>
-      <c r="E89" s="337" t="s">
+      <c r="D89" s="375"/>
+      <c r="E89" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="F89" s="338"/>
-      <c r="G89" s="339"/>
+      <c r="F89" s="324"/>
+      <c r="G89" s="325"/>
       <c r="H89" s="64"/>
     </row>
     <row r="90" spans="2:8" ht="15.75" customHeight="1">
       <c r="B90" s="58">
         <v>15</v>
       </c>
-      <c r="C90" s="380"/>
-      <c r="D90" s="381"/>
+      <c r="C90" s="376"/>
+      <c r="D90" s="377"/>
       <c r="E90" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F90" s="356" t="s">
+      <c r="F90" s="336" t="s">
         <v>91</v>
       </c>
-      <c r="G90" s="358"/>
+      <c r="G90" s="338"/>
       <c r="H90" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15834,10 +15831,10 @@
       <c r="E91" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F91" s="346" t="s">
+      <c r="F91" s="319" t="s">
         <v>176</v>
       </c>
-      <c r="G91" s="348"/>
+      <c r="G91" s="321"/>
       <c r="H91" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15856,40 +15853,40 @@
       <c r="E92" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F92" s="346" t="s">
-        <v>44</v>
-      </c>
-      <c r="G92" s="348"/>
+      <c r="F92" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="G92" s="321"/>
       <c r="H92" s="64"/>
     </row>
     <row r="93" spans="2:8" ht="15.75" customHeight="1">
       <c r="B93" s="58">
         <v>18</v>
       </c>
-      <c r="C93" s="378" t="s">
+      <c r="C93" s="374" t="s">
         <v>177</v>
       </c>
-      <c r="D93" s="379"/>
-      <c r="E93" s="337" t="s">
+      <c r="D93" s="375"/>
+      <c r="E93" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="F93" s="338"/>
-      <c r="G93" s="339"/>
+      <c r="F93" s="324"/>
+      <c r="G93" s="325"/>
       <c r="H93" s="64"/>
     </row>
     <row r="94" spans="2:8" ht="15.75" customHeight="1">
       <c r="B94" s="58">
         <v>19</v>
       </c>
-      <c r="C94" s="380"/>
-      <c r="D94" s="381"/>
+      <c r="C94" s="376"/>
+      <c r="D94" s="377"/>
       <c r="E94" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F94" s="384" t="s">
-        <v>44</v>
-      </c>
-      <c r="G94" s="385"/>
+      <c r="F94" s="378" t="s">
+        <v>44</v>
+      </c>
+      <c r="G94" s="379"/>
       <c r="H94" s="64"/>
     </row>
     <row r="95" spans="2:8" ht="15.75" customHeight="1">
@@ -15905,8 +15902,8 @@
       <c r="E95" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F95" s="346"/>
-      <c r="G95" s="348"/>
+      <c r="F95" s="319"/>
+      <c r="G95" s="321"/>
       <c r="H95" s="64"/>
     </row>
     <row r="96" spans="2:8" ht="32.25" customHeight="1">
@@ -15922,10 +15919,10 @@
       <c r="E96" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F96" s="346" t="s">
+      <c r="F96" s="319" t="s">
         <v>8</v>
       </c>
-      <c r="G96" s="348"/>
+      <c r="G96" s="321"/>
       <c r="H96" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15944,34 +15941,34 @@
       <c r="E97" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F97" s="346"/>
-      <c r="G97" s="348"/>
+      <c r="F97" s="319"/>
+      <c r="G97" s="321"/>
       <c r="H97" s="64"/>
     </row>
     <row r="98" spans="2:8" ht="15.75" customHeight="1">
       <c r="B98" s="58">
         <v>24</v>
       </c>
-      <c r="C98" s="337" t="s">
+      <c r="C98" s="323" t="s">
         <v>179</v>
       </c>
-      <c r="D98" s="338"/>
-      <c r="E98" s="338"/>
-      <c r="F98" s="338"/>
-      <c r="G98" s="339"/>
+      <c r="D98" s="324"/>
+      <c r="E98" s="324"/>
+      <c r="F98" s="324"/>
+      <c r="G98" s="325"/>
       <c r="H98" s="64"/>
     </row>
     <row r="99" spans="2:8" ht="15.75" customHeight="1">
       <c r="B99" s="58">
         <v>25</v>
       </c>
-      <c r="C99" s="337" t="s">
+      <c r="C99" s="323" t="s">
         <v>180</v>
       </c>
-      <c r="D99" s="338"/>
-      <c r="E99" s="338"/>
-      <c r="F99" s="338"/>
-      <c r="G99" s="339"/>
+      <c r="D99" s="324"/>
+      <c r="E99" s="324"/>
+      <c r="F99" s="324"/>
+      <c r="G99" s="325"/>
       <c r="H99" s="64" t="e">
         <f>нак.расх.!G29*16%</f>
         <v>#REF!</v>
@@ -15979,39 +15976,54 @@
     </row>
   </sheetData>
   <mergeCells count="94">
-    <mergeCell ref="F96:G96"/>
-    <mergeCell ref="F97:G97"/>
-    <mergeCell ref="C98:G98"/>
-    <mergeCell ref="C99:G99"/>
-    <mergeCell ref="F91:G91"/>
-    <mergeCell ref="F92:G92"/>
-    <mergeCell ref="C93:D94"/>
-    <mergeCell ref="E93:G93"/>
-    <mergeCell ref="F94:G94"/>
-    <mergeCell ref="F95:G95"/>
-    <mergeCell ref="C86:D87"/>
-    <mergeCell ref="E86:G86"/>
-    <mergeCell ref="F87:G87"/>
-    <mergeCell ref="F88:G88"/>
-    <mergeCell ref="C89:D90"/>
-    <mergeCell ref="E89:G89"/>
-    <mergeCell ref="F90:G90"/>
-    <mergeCell ref="F81:G81"/>
-    <mergeCell ref="F82:G82"/>
-    <mergeCell ref="C83:D85"/>
-    <mergeCell ref="E83:G83"/>
-    <mergeCell ref="E84:E85"/>
-    <mergeCell ref="F84:G84"/>
-    <mergeCell ref="F85:G85"/>
-    <mergeCell ref="F72:G72"/>
-    <mergeCell ref="F73:G73"/>
-    <mergeCell ref="C74:G74"/>
-    <mergeCell ref="C75:G75"/>
-    <mergeCell ref="C77:D80"/>
-    <mergeCell ref="E77:G77"/>
-    <mergeCell ref="F78:G78"/>
-    <mergeCell ref="F79:G79"/>
-    <mergeCell ref="F80:G80"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="B4:H4"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="C19:G21"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="C29:D32"/>
+    <mergeCell ref="E29:G29"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="C35:D37"/>
+    <mergeCell ref="E35:G35"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="F36:G36"/>
+    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="F47:G47"/>
+    <mergeCell ref="C38:D39"/>
+    <mergeCell ref="E38:G38"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="C41:D42"/>
+    <mergeCell ref="E41:G41"/>
+    <mergeCell ref="F42:G42"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="C45:D46"/>
+    <mergeCell ref="E45:G45"/>
+    <mergeCell ref="F46:G46"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="C53:D56"/>
+    <mergeCell ref="E53:G53"/>
+    <mergeCell ref="F54:G54"/>
+    <mergeCell ref="F55:G55"/>
+    <mergeCell ref="F56:G56"/>
+    <mergeCell ref="F57:G57"/>
+    <mergeCell ref="F58:G58"/>
+    <mergeCell ref="C59:D61"/>
+    <mergeCell ref="E59:G59"/>
+    <mergeCell ref="E60:E61"/>
+    <mergeCell ref="F60:G60"/>
+    <mergeCell ref="F61:G61"/>
     <mergeCell ref="F71:G71"/>
     <mergeCell ref="C62:D63"/>
     <mergeCell ref="E62:G62"/>
@@ -16025,54 +16037,39 @@
     <mergeCell ref="C69:D70"/>
     <mergeCell ref="E69:G69"/>
     <mergeCell ref="F70:G70"/>
-    <mergeCell ref="F57:G57"/>
-    <mergeCell ref="F58:G58"/>
-    <mergeCell ref="C59:D61"/>
-    <mergeCell ref="E59:G59"/>
-    <mergeCell ref="E60:E61"/>
-    <mergeCell ref="F60:G60"/>
-    <mergeCell ref="F61:G61"/>
-    <mergeCell ref="F48:G48"/>
-    <mergeCell ref="F49:G49"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="C53:D56"/>
-    <mergeCell ref="E53:G53"/>
-    <mergeCell ref="F54:G54"/>
-    <mergeCell ref="F55:G55"/>
-    <mergeCell ref="F56:G56"/>
-    <mergeCell ref="F47:G47"/>
-    <mergeCell ref="C38:D39"/>
-    <mergeCell ref="E38:G38"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="C41:D42"/>
-    <mergeCell ref="E41:G41"/>
-    <mergeCell ref="F42:G42"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="F44:G44"/>
-    <mergeCell ref="C45:D46"/>
-    <mergeCell ref="E45:G45"/>
-    <mergeCell ref="F46:G46"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="C35:D37"/>
-    <mergeCell ref="E35:G35"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="F36:G36"/>
-    <mergeCell ref="F37:G37"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="B3:H3"/>
-    <mergeCell ref="B4:H4"/>
-    <mergeCell ref="B19:B21"/>
-    <mergeCell ref="C19:G21"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="C29:D32"/>
-    <mergeCell ref="E29:G29"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="F72:G72"/>
+    <mergeCell ref="F73:G73"/>
+    <mergeCell ref="C74:G74"/>
+    <mergeCell ref="C75:G75"/>
+    <mergeCell ref="C77:D80"/>
+    <mergeCell ref="E77:G77"/>
+    <mergeCell ref="F78:G78"/>
+    <mergeCell ref="F79:G79"/>
+    <mergeCell ref="F80:G80"/>
+    <mergeCell ref="F81:G81"/>
+    <mergeCell ref="F82:G82"/>
+    <mergeCell ref="C83:D85"/>
+    <mergeCell ref="E83:G83"/>
+    <mergeCell ref="E84:E85"/>
+    <mergeCell ref="F84:G84"/>
+    <mergeCell ref="F85:G85"/>
+    <mergeCell ref="C86:D87"/>
+    <mergeCell ref="E86:G86"/>
+    <mergeCell ref="F87:G87"/>
+    <mergeCell ref="F88:G88"/>
+    <mergeCell ref="C89:D90"/>
+    <mergeCell ref="E89:G89"/>
+    <mergeCell ref="F90:G90"/>
+    <mergeCell ref="F96:G96"/>
+    <mergeCell ref="F97:G97"/>
+    <mergeCell ref="C98:G98"/>
+    <mergeCell ref="C99:G99"/>
+    <mergeCell ref="F91:G91"/>
+    <mergeCell ref="F92:G92"/>
+    <mergeCell ref="C93:D94"/>
+    <mergeCell ref="E93:G93"/>
+    <mergeCell ref="F94:G94"/>
+    <mergeCell ref="F95:G95"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="76" orientation="portrait" r:id="rId1"/>
@@ -16101,14 +16098,14 @@
       <c r="A1" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="320" t="s">
+      <c r="B1" s="357" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="320"/>
-      <c r="D1" s="320"/>
-      <c r="E1" s="320"/>
-      <c r="F1" s="320"/>
-      <c r="G1" s="320"/>
+      <c r="C1" s="357"/>
+      <c r="D1" s="357"/>
+      <c r="E1" s="357"/>
+      <c r="F1" s="357"/>
+      <c r="G1" s="357"/>
       <c r="K1" s="51"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" customHeight="1">
@@ -16139,69 +16136,69 @@
       <c r="A3" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="320" t="s">
+      <c r="B3" s="357" t="s">
         <v>182</v>
       </c>
-      <c r="C3" s="320"/>
-      <c r="D3" s="320"/>
-      <c r="E3" s="320"/>
-      <c r="F3" s="320"/>
-      <c r="G3" s="320"/>
+      <c r="C3" s="357"/>
+      <c r="D3" s="357"/>
+      <c r="E3" s="357"/>
+      <c r="F3" s="357"/>
+      <c r="G3" s="357"/>
       <c r="K3" s="51"/>
     </row>
     <row r="4" spans="1:11" ht="14.25" customHeight="1">
       <c r="A4" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="322" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="322"/>
-      <c r="D4" s="322"/>
-      <c r="E4" s="322"/>
-      <c r="F4" s="322"/>
-      <c r="G4" s="322"/>
+      <c r="B4" s="359" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="359"/>
+      <c r="D4" s="359"/>
+      <c r="E4" s="359"/>
+      <c r="F4" s="359"/>
+      <c r="G4" s="359"/>
       <c r="K4" s="51"/>
     </row>
     <row r="5" spans="1:11" ht="24.75" customHeight="1">
       <c r="A5" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="323" t="s">
+      <c r="B5" s="360" t="s">
         <v>47</v>
       </c>
-      <c r="C5" s="323"/>
-      <c r="D5" s="323"/>
-      <c r="E5" s="323"/>
-      <c r="F5" s="323"/>
-      <c r="G5" s="323"/>
+      <c r="C5" s="360"/>
+      <c r="D5" s="360"/>
+      <c r="E5" s="360"/>
+      <c r="F5" s="360"/>
+      <c r="G5" s="360"/>
       <c r="K5" s="51"/>
     </row>
     <row r="6" spans="1:11" ht="12" customHeight="1">
       <c r="A6" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B6" s="323" t="s">
+      <c r="B6" s="360" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="323"/>
-      <c r="D6" s="323"/>
-      <c r="E6" s="323"/>
-      <c r="F6" s="323"/>
-      <c r="G6" s="323"/>
+      <c r="C6" s="360"/>
+      <c r="D6" s="360"/>
+      <c r="E6" s="360"/>
+      <c r="F6" s="360"/>
+      <c r="G6" s="360"/>
       <c r="K6" s="51"/>
     </row>
     <row r="7" spans="1:11" ht="12" customHeight="1">
       <c r="A7" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B7" s="324" t="s">
+      <c r="B7" s="361" t="s">
         <v>183</v>
       </c>
-      <c r="C7" s="324"/>
-      <c r="D7" s="324"/>
-      <c r="E7" s="324"/>
-      <c r="F7" s="324"/>
+      <c r="C7" s="361"/>
+      <c r="D7" s="361"/>
+      <c r="E7" s="361"/>
+      <c r="F7" s="361"/>
       <c r="G7" s="71" t="s">
         <v>50</v>
       </c>
@@ -16225,37 +16222,37 @@
       <c r="A22" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B22" s="325" t="s">
+      <c r="B22" s="362" t="s">
         <v>0</v>
       </c>
-      <c r="C22" s="328" t="s">
+      <c r="C22" s="365" t="s">
         <v>51</v>
       </c>
-      <c r="D22" s="329"/>
-      <c r="E22" s="329"/>
-      <c r="F22" s="330"/>
+      <c r="D22" s="366"/>
+      <c r="E22" s="366"/>
+      <c r="F22" s="367"/>
       <c r="G22" s="55"/>
     </row>
     <row r="23" spans="1:12" ht="12" customHeight="1">
       <c r="A23" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="326"/>
-      <c r="C23" s="331"/>
-      <c r="D23" s="332"/>
-      <c r="E23" s="332"/>
-      <c r="F23" s="333"/>
+      <c r="B23" s="363"/>
+      <c r="C23" s="368"/>
+      <c r="D23" s="369"/>
+      <c r="E23" s="369"/>
+      <c r="F23" s="370"/>
       <c r="G23" s="55"/>
     </row>
     <row r="24" spans="1:12" ht="24" customHeight="1">
       <c r="A24" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B24" s="327"/>
-      <c r="C24" s="334"/>
-      <c r="D24" s="335"/>
-      <c r="E24" s="335"/>
-      <c r="F24" s="336"/>
+      <c r="B24" s="364"/>
+      <c r="C24" s="371"/>
+      <c r="D24" s="372"/>
+      <c r="E24" s="372"/>
+      <c r="F24" s="373"/>
       <c r="G24" s="57" t="s">
         <v>52</v>
       </c>
@@ -16276,10 +16273,10 @@
       <c r="D28" s="57">
         <v>3</v>
       </c>
-      <c r="E28" s="376">
+      <c r="E28" s="383">
         <v>4</v>
       </c>
-      <c r="F28" s="377"/>
+      <c r="F28" s="384"/>
       <c r="G28" s="57">
         <v>8</v>
       </c>
@@ -16291,12 +16288,12 @@
       <c r="B29" s="58">
         <v>1</v>
       </c>
-      <c r="C29" s="337" t="s">
+      <c r="C29" s="323" t="s">
         <v>184</v>
       </c>
-      <c r="D29" s="338"/>
-      <c r="E29" s="338"/>
-      <c r="F29" s="338"/>
+      <c r="D29" s="324"/>
+      <c r="E29" s="324"/>
+      <c r="F29" s="324"/>
       <c r="G29" s="72" t="e">
         <f>SUM(G30:G77)</f>
         <v>#REF!</v>
@@ -16316,11 +16313,11 @@
       <c r="C30" s="73" t="s">
         <v>54</v>
       </c>
-      <c r="D30" s="337" t="s">
+      <c r="D30" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E30" s="338"/>
-      <c r="F30" s="338"/>
+      <c r="E30" s="324"/>
+      <c r="F30" s="324"/>
       <c r="G30" s="74"/>
       <c r="L30" s="53" t="e">
         <f>G29-L29</f>
@@ -16340,10 +16337,10 @@
       <c r="D31" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E31" s="356" t="s">
+      <c r="E31" s="336" t="s">
         <v>56</v>
       </c>
-      <c r="F31" s="357"/>
+      <c r="F31" s="337"/>
       <c r="G31" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16363,10 +16360,10 @@
       <c r="D32" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E32" s="356" t="s">
+      <c r="E32" s="336" t="s">
         <v>57</v>
       </c>
-      <c r="F32" s="357"/>
+      <c r="F32" s="337"/>
       <c r="G32" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16386,10 +16383,10 @@
       <c r="D33" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E33" s="356" t="s">
+      <c r="E33" s="336" t="s">
         <v>58</v>
       </c>
-      <c r="F33" s="357"/>
+      <c r="F33" s="337"/>
       <c r="G33" s="74"/>
     </row>
     <row r="34" spans="1:13" ht="12" customHeight="1">
@@ -16446,10 +16443,10 @@
       <c r="D36" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E36" s="346" t="s">
-        <v>44</v>
-      </c>
-      <c r="F36" s="347"/>
+      <c r="E36" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="F36" s="320"/>
       <c r="G36" s="74"/>
       <c r="H36" s="49"/>
     </row>
@@ -16463,11 +16460,11 @@
       <c r="C37" s="73" t="s">
         <v>171</v>
       </c>
-      <c r="D37" s="337" t="s">
+      <c r="D37" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E37" s="338"/>
-      <c r="F37" s="338"/>
+      <c r="E37" s="324"/>
+      <c r="F37" s="324"/>
       <c r="G37" s="74"/>
     </row>
     <row r="38" spans="1:13" ht="12" customHeight="1">
@@ -16483,10 +16480,10 @@
       <c r="D38" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E38" s="356" t="s">
+      <c r="E38" s="336" t="s">
         <v>172</v>
       </c>
-      <c r="F38" s="357"/>
+      <c r="F38" s="337"/>
       <c r="G38" s="74" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -16506,10 +16503,10 @@
       <c r="D39" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E39" s="356" t="s">
+      <c r="E39" s="336" t="s">
         <v>173</v>
       </c>
-      <c r="F39" s="357"/>
+      <c r="F39" s="337"/>
       <c r="G39" s="74"/>
     </row>
     <row r="40" spans="1:13" ht="12" customHeight="1">
@@ -16519,14 +16516,14 @@
       <c r="B40" s="58">
         <v>26</v>
       </c>
-      <c r="C40" s="340" t="s">
+      <c r="C40" s="332" t="s">
         <v>174</v>
       </c>
-      <c r="D40" s="337" t="s">
+      <c r="D40" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E40" s="338"/>
-      <c r="F40" s="338"/>
+      <c r="E40" s="324"/>
+      <c r="F40" s="324"/>
       <c r="G40" s="74"/>
     </row>
     <row r="41" spans="1:13" ht="12" customHeight="1">
@@ -16536,11 +16533,11 @@
       <c r="B41" s="58">
         <v>27</v>
       </c>
-      <c r="C41" s="341"/>
+      <c r="C41" s="333"/>
       <c r="D41" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E41" s="384" t="s">
+      <c r="E41" s="378" t="s">
         <v>44</v>
       </c>
       <c r="F41" s="386"/>
@@ -16559,10 +16556,10 @@
       <c r="D42" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E42" s="346" t="s">
-        <v>44</v>
-      </c>
-      <c r="F42" s="347"/>
+      <c r="E42" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="F42" s="320"/>
       <c r="G42" s="74"/>
       <c r="H42" s="49"/>
     </row>
@@ -16573,14 +16570,14 @@
       <c r="B43" s="58">
         <v>29</v>
       </c>
-      <c r="C43" s="340" t="s">
+      <c r="C43" s="332" t="s">
         <v>186</v>
       </c>
-      <c r="D43" s="337" t="s">
+      <c r="D43" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E43" s="338"/>
-      <c r="F43" s="338"/>
+      <c r="E43" s="324"/>
+      <c r="F43" s="324"/>
       <c r="G43" s="74"/>
     </row>
     <row r="44" spans="1:13" ht="12" customHeight="1">
@@ -16590,14 +16587,14 @@
       <c r="B44" s="58">
         <v>30</v>
       </c>
-      <c r="C44" s="341"/>
+      <c r="C44" s="333"/>
       <c r="D44" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E44" s="346" t="s">
+      <c r="E44" s="319" t="s">
         <v>128</v>
       </c>
-      <c r="F44" s="347"/>
+      <c r="F44" s="320"/>
       <c r="G44" s="74"/>
     </row>
     <row r="45" spans="1:13" ht="18.75" customHeight="1">
@@ -16607,14 +16604,14 @@
       <c r="B45" s="58">
         <v>31</v>
       </c>
-      <c r="C45" s="342"/>
+      <c r="C45" s="349"/>
       <c r="D45" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E45" s="387" t="s">
+      <c r="E45" s="389" t="s">
         <v>129</v>
       </c>
-      <c r="F45" s="388"/>
+      <c r="F45" s="390"/>
       <c r="G45" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16629,12 +16626,12 @@
       <c r="B46" s="58">
         <v>32</v>
       </c>
-      <c r="C46" s="337" t="s">
+      <c r="C46" s="323" t="s">
         <v>20</v>
       </c>
-      <c r="D46" s="338"/>
-      <c r="E46" s="338"/>
-      <c r="F46" s="338"/>
+      <c r="D46" s="324"/>
+      <c r="E46" s="324"/>
+      <c r="F46" s="324"/>
       <c r="G46" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16651,11 +16648,11 @@
       <c r="C47" s="73" t="s">
         <v>62</v>
       </c>
-      <c r="D47" s="337" t="s">
+      <c r="D47" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E47" s="338"/>
-      <c r="F47" s="338"/>
+      <c r="E47" s="324"/>
+      <c r="F47" s="324"/>
       <c r="G47" s="74"/>
       <c r="L47" s="53"/>
     </row>
@@ -16672,10 +16669,10 @@
       <c r="D48" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E48" s="356" t="s">
+      <c r="E48" s="336" t="s">
         <v>63</v>
       </c>
-      <c r="F48" s="357"/>
+      <c r="F48" s="337"/>
       <c r="G48" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16694,10 +16691,10 @@
       <c r="D49" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E49" s="356" t="s">
+      <c r="E49" s="336" t="s">
         <v>64</v>
       </c>
-      <c r="F49" s="357"/>
+      <c r="F49" s="337"/>
       <c r="G49" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16710,14 +16707,14 @@
       <c r="B50" s="58">
         <v>36</v>
       </c>
-      <c r="C50" s="340" t="s">
+      <c r="C50" s="332" t="s">
         <v>187</v>
       </c>
-      <c r="D50" s="337" t="s">
+      <c r="D50" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E50" s="338"/>
-      <c r="F50" s="338"/>
+      <c r="E50" s="324"/>
+      <c r="F50" s="324"/>
       <c r="G50" s="74"/>
     </row>
     <row r="51" spans="1:8" ht="12" customHeight="1">
@@ -16727,11 +16724,11 @@
       <c r="B51" s="58">
         <v>37</v>
       </c>
-      <c r="C51" s="341"/>
+      <c r="C51" s="333"/>
       <c r="D51" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E51" s="384" t="s">
+      <c r="E51" s="378" t="s">
         <v>44</v>
       </c>
       <c r="F51" s="386"/>
@@ -16750,10 +16747,10 @@
       <c r="D52" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E52" s="346" t="s">
+      <c r="E52" s="319" t="s">
         <v>188</v>
       </c>
-      <c r="F52" s="347"/>
+      <c r="F52" s="320"/>
       <c r="G52" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16767,12 +16764,12 @@
       <c r="B53" s="58">
         <v>43</v>
       </c>
-      <c r="C53" s="337" t="s">
+      <c r="C53" s="323" t="s">
         <v>16</v>
       </c>
-      <c r="D53" s="338"/>
-      <c r="E53" s="338"/>
-      <c r="F53" s="338"/>
+      <c r="D53" s="324"/>
+      <c r="E53" s="324"/>
+      <c r="F53" s="324"/>
       <c r="G53" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16785,12 +16782,12 @@
       <c r="B54" s="58">
         <v>44</v>
       </c>
-      <c r="C54" s="337" t="s">
+      <c r="C54" s="323" t="s">
         <v>14</v>
       </c>
-      <c r="D54" s="338"/>
-      <c r="E54" s="338"/>
-      <c r="F54" s="338"/>
+      <c r="D54" s="324"/>
+      <c r="E54" s="324"/>
+      <c r="F54" s="324"/>
       <c r="G54" s="74"/>
     </row>
     <row r="55" spans="1:8" ht="12" customHeight="1">
@@ -16803,11 +16800,11 @@
       <c r="C55" s="73" t="s">
         <v>137</v>
       </c>
-      <c r="D55" s="337" t="s">
+      <c r="D55" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E55" s="338"/>
-      <c r="F55" s="338"/>
+      <c r="E55" s="324"/>
+      <c r="F55" s="324"/>
       <c r="G55" s="74"/>
     </row>
     <row r="56" spans="1:8" ht="12" customHeight="1">
@@ -16823,7 +16820,7 @@
       <c r="D56" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E56" s="384" t="s">
+      <c r="E56" s="378" t="s">
         <v>44</v>
       </c>
       <c r="F56" s="386"/>
@@ -16842,10 +16839,10 @@
       <c r="D57" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E57" s="346" t="s">
+      <c r="E57" s="319" t="s">
         <v>4</v>
       </c>
-      <c r="F57" s="347"/>
+      <c r="F57" s="320"/>
       <c r="G57" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16865,10 +16862,10 @@
       <c r="D58" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E58" s="346" t="s">
-        <v>44</v>
-      </c>
-      <c r="F58" s="347"/>
+      <c r="E58" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="F58" s="320"/>
       <c r="G58" s="74"/>
       <c r="H58" s="49"/>
     </row>
@@ -16879,12 +16876,12 @@
       <c r="B59" s="58">
         <v>51</v>
       </c>
-      <c r="C59" s="337" t="s">
+      <c r="C59" s="323" t="s">
         <v>189</v>
       </c>
-      <c r="D59" s="338"/>
-      <c r="E59" s="338"/>
-      <c r="F59" s="338"/>
+      <c r="D59" s="324"/>
+      <c r="E59" s="324"/>
+      <c r="F59" s="324"/>
       <c r="G59" s="74"/>
     </row>
     <row r="60" spans="1:8" ht="12" customHeight="1">
@@ -16894,12 +16891,12 @@
       <c r="B60" s="58">
         <v>52</v>
       </c>
-      <c r="C60" s="337" t="s">
+      <c r="C60" s="323" t="s">
         <v>17</v>
       </c>
-      <c r="D60" s="338"/>
-      <c r="E60" s="338"/>
-      <c r="F60" s="338"/>
+      <c r="D60" s="324"/>
+      <c r="E60" s="324"/>
+      <c r="F60" s="324"/>
       <c r="G60" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16912,12 +16909,12 @@
       <c r="B61" s="58">
         <v>53</v>
       </c>
-      <c r="C61" s="337" t="s">
+      <c r="C61" s="323" t="s">
         <v>190</v>
       </c>
-      <c r="D61" s="338"/>
-      <c r="E61" s="338"/>
-      <c r="F61" s="338"/>
+      <c r="D61" s="324"/>
+      <c r="E61" s="324"/>
+      <c r="F61" s="324"/>
       <c r="G61" s="74"/>
     </row>
     <row r="62" spans="1:8" ht="12" customHeight="1">
@@ -16927,12 +16924,12 @@
       <c r="B62" s="58">
         <v>54</v>
       </c>
-      <c r="C62" s="337" t="s">
+      <c r="C62" s="323" t="s">
         <v>191</v>
       </c>
-      <c r="D62" s="338"/>
-      <c r="E62" s="338"/>
-      <c r="F62" s="338"/>
+      <c r="D62" s="324"/>
+      <c r="E62" s="324"/>
+      <c r="F62" s="324"/>
       <c r="G62" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16945,12 +16942,12 @@
       <c r="B63" s="58">
         <v>55</v>
       </c>
-      <c r="C63" s="337" t="s">
+      <c r="C63" s="323" t="s">
         <v>192</v>
       </c>
-      <c r="D63" s="338"/>
-      <c r="E63" s="338"/>
-      <c r="F63" s="338"/>
+      <c r="D63" s="324"/>
+      <c r="E63" s="324"/>
+      <c r="F63" s="324"/>
       <c r="G63" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16963,14 +16960,14 @@
       <c r="B64" s="58">
         <v>56</v>
       </c>
-      <c r="C64" s="340" t="s">
+      <c r="C64" s="332" t="s">
         <v>175</v>
       </c>
-      <c r="D64" s="337" t="s">
+      <c r="D64" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E64" s="338"/>
-      <c r="F64" s="338"/>
+      <c r="E64" s="324"/>
+      <c r="F64" s="324"/>
       <c r="G64" s="74"/>
     </row>
     <row r="65" spans="1:11" ht="12" customHeight="1">
@@ -16980,14 +16977,14 @@
       <c r="B65" s="58">
         <v>57</v>
       </c>
-      <c r="C65" s="341"/>
+      <c r="C65" s="333"/>
       <c r="D65" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E65" s="356" t="s">
+      <c r="E65" s="336" t="s">
         <v>91</v>
       </c>
-      <c r="F65" s="357"/>
+      <c r="F65" s="337"/>
       <c r="G65" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17006,10 +17003,10 @@
       <c r="D66" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E66" s="346" t="s">
+      <c r="E66" s="319" t="s">
         <v>193</v>
       </c>
-      <c r="F66" s="347"/>
+      <c r="F66" s="320"/>
       <c r="G66" s="74"/>
       <c r="H66" s="49"/>
     </row>
@@ -17020,14 +17017,14 @@
       <c r="B67" s="58">
         <v>59</v>
       </c>
-      <c r="C67" s="340" t="s">
+      <c r="C67" s="332" t="s">
         <v>102</v>
       </c>
-      <c r="D67" s="337" t="s">
+      <c r="D67" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E67" s="338"/>
-      <c r="F67" s="338"/>
+      <c r="E67" s="324"/>
+      <c r="F67" s="324"/>
       <c r="G67" s="74"/>
     </row>
     <row r="68" spans="1:11" ht="12" customHeight="1">
@@ -17037,11 +17034,11 @@
       <c r="B68" s="58">
         <v>60</v>
       </c>
-      <c r="C68" s="341"/>
+      <c r="C68" s="333"/>
       <c r="D68" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E68" s="384" t="s">
+      <c r="E68" s="378" t="s">
         <v>44</v>
       </c>
       <c r="F68" s="386"/>
@@ -17060,10 +17057,10 @@
       <c r="D69" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E69" s="346" t="s">
+      <c r="E69" s="319" t="s">
         <v>194</v>
       </c>
-      <c r="F69" s="347"/>
+      <c r="F69" s="320"/>
       <c r="G69" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17083,10 +17080,10 @@
       <c r="D70" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E70" s="346" t="s">
+      <c r="E70" s="319" t="s">
         <v>195</v>
       </c>
-      <c r="F70" s="347"/>
+      <c r="F70" s="320"/>
       <c r="G70" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17106,10 +17103,10 @@
       <c r="D71" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E71" s="389" t="s">
+      <c r="E71" s="387" t="s">
         <v>196</v>
       </c>
-      <c r="F71" s="390"/>
+      <c r="F71" s="388"/>
       <c r="G71" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17121,10 +17118,10 @@
       <c r="B72" s="58"/>
       <c r="C72" s="77"/>
       <c r="D72" s="70"/>
-      <c r="E72" s="389" t="s">
+      <c r="E72" s="387" t="s">
         <v>13</v>
       </c>
-      <c r="F72" s="390"/>
+      <c r="F72" s="388"/>
       <c r="G72" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17136,10 +17133,10 @@
       <c r="B73" s="58"/>
       <c r="C73" s="77"/>
       <c r="D73" s="70"/>
-      <c r="E73" s="389" t="s">
+      <c r="E73" s="387" t="s">
         <v>8</v>
       </c>
-      <c r="F73" s="390"/>
+      <c r="F73" s="388"/>
       <c r="G73" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17159,10 +17156,10 @@
       <c r="D74" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E74" s="346" t="s">
-        <v>44</v>
-      </c>
-      <c r="F74" s="347"/>
+      <c r="E74" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="F74" s="320"/>
       <c r="G74" s="74"/>
       <c r="H74" s="49"/>
     </row>
@@ -17173,14 +17170,14 @@
       <c r="B75" s="58">
         <v>65</v>
       </c>
-      <c r="C75" s="340" t="s">
+      <c r="C75" s="332" t="s">
         <v>197</v>
       </c>
-      <c r="D75" s="337" t="s">
+      <c r="D75" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E75" s="338"/>
-      <c r="F75" s="338"/>
+      <c r="E75" s="324"/>
+      <c r="F75" s="324"/>
       <c r="G75" s="74"/>
     </row>
     <row r="76" spans="1:11" ht="12" customHeight="1">
@@ -17190,11 +17187,11 @@
       <c r="B76" s="58">
         <v>66</v>
       </c>
-      <c r="C76" s="341"/>
+      <c r="C76" s="333"/>
       <c r="D76" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E76" s="384" t="s">
+      <c r="E76" s="378" t="s">
         <v>44</v>
       </c>
       <c r="F76" s="386"/>
@@ -17213,10 +17210,10 @@
       <c r="D77" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E77" s="346" t="s">
+      <c r="E77" s="319" t="s">
         <v>198</v>
       </c>
-      <c r="F77" s="347"/>
+      <c r="F77" s="320"/>
       <c r="G77" s="81" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -17275,13 +17272,13 @@
       <c r="K79" s="51"/>
     </row>
     <row r="80" spans="1:11" ht="15" customHeight="1">
-      <c r="B80" s="391" t="s">
+      <c r="B80" s="385" t="s">
         <v>199</v>
       </c>
-      <c r="C80" s="391"/>
-      <c r="D80" s="391"/>
-      <c r="E80" s="391"/>
-      <c r="F80" s="391"/>
+      <c r="C80" s="385"/>
+      <c r="D80" s="385"/>
+      <c r="E80" s="385"/>
+      <c r="F80" s="385"/>
       <c r="G80" s="83"/>
       <c r="H80" s="83"/>
       <c r="I80" s="82"/>
@@ -17289,13 +17286,13 @@
       <c r="K80" s="51"/>
     </row>
     <row r="81" spans="2:11" ht="15" customHeight="1">
-      <c r="B81" s="391" t="s">
-        <v>44</v>
-      </c>
-      <c r="C81" s="391"/>
-      <c r="D81" s="391"/>
-      <c r="E81" s="391"/>
-      <c r="F81" s="391"/>
+      <c r="B81" s="385" t="s">
+        <v>44</v>
+      </c>
+      <c r="C81" s="385"/>
+      <c r="D81" s="385"/>
+      <c r="E81" s="385"/>
+      <c r="F81" s="385"/>
       <c r="G81" s="84"/>
       <c r="H81" s="84"/>
       <c r="I81" s="83"/>
@@ -17305,14 +17302,14 @@
     <row r="82" spans="2:11" ht="15.75" hidden="1" customHeight="1"/>
     <row r="83" spans="2:11" ht="15.75" hidden="1" customHeight="1"/>
     <row r="84" spans="2:11" ht="15" customHeight="1">
-      <c r="B84" s="391" t="s">
+      <c r="B84" s="385" t="s">
         <v>200</v>
       </c>
-      <c r="C84" s="391"/>
-      <c r="D84" s="391"/>
-      <c r="E84" s="391"/>
-      <c r="F84" s="391"/>
-      <c r="G84" s="391"/>
+      <c r="C84" s="385"/>
+      <c r="D84" s="385"/>
+      <c r="E84" s="385"/>
+      <c r="F84" s="385"/>
+      <c r="G84" s="385"/>
       <c r="H84" s="83"/>
       <c r="I84" s="83"/>
       <c r="J84" s="83"/>
@@ -17341,13 +17338,51 @@
     <row r="105" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="65">
-    <mergeCell ref="B84:G84"/>
-    <mergeCell ref="C75:C76"/>
-    <mergeCell ref="D75:F75"/>
-    <mergeCell ref="E76:F76"/>
-    <mergeCell ref="E77:F77"/>
-    <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="B6:G6"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="B22:B24"/>
+    <mergeCell ref="C22:F24"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="E38:F38"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="D40:F40"/>
+    <mergeCell ref="E41:F41"/>
+    <mergeCell ref="E42:F42"/>
+    <mergeCell ref="C43:C45"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="E44:F44"/>
+    <mergeCell ref="E45:F45"/>
+    <mergeCell ref="C46:F46"/>
+    <mergeCell ref="D47:F47"/>
+    <mergeCell ref="E48:F48"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="D50:F50"/>
+    <mergeCell ref="E51:F51"/>
+    <mergeCell ref="C63:F63"/>
+    <mergeCell ref="E52:F52"/>
+    <mergeCell ref="C53:F53"/>
+    <mergeCell ref="C54:F54"/>
+    <mergeCell ref="D55:F55"/>
+    <mergeCell ref="E56:F56"/>
+    <mergeCell ref="E57:F57"/>
+    <mergeCell ref="E58:F58"/>
+    <mergeCell ref="C59:F59"/>
+    <mergeCell ref="C60:F60"/>
+    <mergeCell ref="C61:F61"/>
+    <mergeCell ref="C62:F62"/>
     <mergeCell ref="E74:F74"/>
     <mergeCell ref="C64:C65"/>
     <mergeCell ref="D64:F64"/>
@@ -17361,51 +17396,13 @@
     <mergeCell ref="E71:F71"/>
     <mergeCell ref="E72:F72"/>
     <mergeCell ref="E73:F73"/>
-    <mergeCell ref="C63:F63"/>
-    <mergeCell ref="E52:F52"/>
-    <mergeCell ref="C53:F53"/>
-    <mergeCell ref="C54:F54"/>
-    <mergeCell ref="D55:F55"/>
-    <mergeCell ref="E56:F56"/>
-    <mergeCell ref="E57:F57"/>
-    <mergeCell ref="E58:F58"/>
-    <mergeCell ref="C59:F59"/>
-    <mergeCell ref="C60:F60"/>
-    <mergeCell ref="C61:F61"/>
-    <mergeCell ref="C62:F62"/>
-    <mergeCell ref="C46:F46"/>
-    <mergeCell ref="D47:F47"/>
-    <mergeCell ref="E48:F48"/>
-    <mergeCell ref="E49:F49"/>
-    <mergeCell ref="C50:C51"/>
-    <mergeCell ref="D50:F50"/>
-    <mergeCell ref="E51:F51"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="D40:F40"/>
-    <mergeCell ref="E41:F41"/>
-    <mergeCell ref="E42:F42"/>
-    <mergeCell ref="C43:C45"/>
-    <mergeCell ref="D43:F43"/>
-    <mergeCell ref="E44:F44"/>
-    <mergeCell ref="E45:F45"/>
-    <mergeCell ref="E39:F39"/>
-    <mergeCell ref="B22:B24"/>
-    <mergeCell ref="C22:F24"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="E36:F36"/>
-    <mergeCell ref="D37:F37"/>
-    <mergeCell ref="E38:F38"/>
-    <mergeCell ref="B7:F7"/>
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="B4:G4"/>
-    <mergeCell ref="B5:G5"/>
-    <mergeCell ref="B6:G6"/>
+    <mergeCell ref="B84:G84"/>
+    <mergeCell ref="C75:C76"/>
+    <mergeCell ref="D75:F75"/>
+    <mergeCell ref="E76:F76"/>
+    <mergeCell ref="E77:F77"/>
+    <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Наименование на государственном языке заполняется автоматически в соответствии с КТРУ" sqref="B76 B49:B50 B95:B96"/>
@@ -17441,79 +17438,79 @@
       <c r="A1" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="431" t="s">
+      <c r="B1" s="399" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="431"/>
-      <c r="D1" s="431"/>
-      <c r="E1" s="431"/>
-      <c r="F1" s="431"/>
-      <c r="G1" s="431"/>
-      <c r="H1" s="431"/>
-      <c r="I1" s="431"/>
+      <c r="C1" s="399"/>
+      <c r="D1" s="399"/>
+      <c r="E1" s="399"/>
+      <c r="F1" s="399"/>
+      <c r="G1" s="399"/>
+      <c r="H1" s="399"/>
+      <c r="I1" s="399"/>
       <c r="M1" s="12"/>
     </row>
     <row r="2" spans="1:13" ht="14.25" customHeight="1">
       <c r="A2" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="432" t="s">
+      <c r="B2" s="400" t="s">
         <v>46</v>
       </c>
-      <c r="C2" s="432"/>
-      <c r="D2" s="432"/>
-      <c r="E2" s="432"/>
-      <c r="F2" s="432"/>
-      <c r="G2" s="432"/>
-      <c r="H2" s="432"/>
-      <c r="I2" s="432"/>
+      <c r="C2" s="400"/>
+      <c r="D2" s="400"/>
+      <c r="E2" s="400"/>
+      <c r="F2" s="400"/>
+      <c r="G2" s="400"/>
+      <c r="H2" s="400"/>
+      <c r="I2" s="400"/>
       <c r="M2" s="12"/>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="433" t="s">
+      <c r="B3" s="401" t="s">
         <v>47</v>
       </c>
-      <c r="C3" s="433"/>
-      <c r="D3" s="433"/>
-      <c r="E3" s="433"/>
-      <c r="F3" s="433"/>
-      <c r="G3" s="433"/>
-      <c r="H3" s="433"/>
-      <c r="I3" s="433"/>
+      <c r="C3" s="401"/>
+      <c r="D3" s="401"/>
+      <c r="E3" s="401"/>
+      <c r="F3" s="401"/>
+      <c r="G3" s="401"/>
+      <c r="H3" s="401"/>
+      <c r="I3" s="401"/>
       <c r="M3" s="12"/>
     </row>
     <row r="4" spans="1:13" ht="30" customHeight="1">
       <c r="A4" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="433" t="s">
+      <c r="B4" s="401" t="s">
         <v>48</v>
       </c>
-      <c r="C4" s="433"/>
-      <c r="D4" s="433"/>
-      <c r="E4" s="433"/>
-      <c r="F4" s="433"/>
-      <c r="G4" s="433"/>
-      <c r="H4" s="433"/>
-      <c r="I4" s="433"/>
+      <c r="C4" s="401"/>
+      <c r="D4" s="401"/>
+      <c r="E4" s="401"/>
+      <c r="F4" s="401"/>
+      <c r="G4" s="401"/>
+      <c r="H4" s="401"/>
+      <c r="I4" s="401"/>
       <c r="M4" s="12"/>
     </row>
     <row r="5" spans="1:13" ht="12" customHeight="1">
       <c r="A5" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="434" t="s">
+      <c r="B5" s="402" t="s">
         <v>49</v>
       </c>
-      <c r="C5" s="434"/>
-      <c r="D5" s="434"/>
-      <c r="E5" s="434"/>
-      <c r="F5" s="434"/>
-      <c r="G5" s="434"/>
-      <c r="H5" s="434"/>
+      <c r="C5" s="402"/>
+      <c r="D5" s="402"/>
+      <c r="E5" s="402"/>
+      <c r="F5" s="402"/>
+      <c r="G5" s="402"/>
+      <c r="H5" s="402"/>
       <c r="I5" s="13" t="s">
         <v>50</v>
       </c>
@@ -17537,18 +17534,18 @@
       <c r="A20" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="B20" s="435" t="s">
+      <c r="B20" s="403" t="s">
         <v>0</v>
       </c>
-      <c r="C20" s="438" t="s">
+      <c r="C20" s="406" t="s">
         <v>51</v>
       </c>
-      <c r="D20" s="439"/>
-      <c r="E20" s="439"/>
-      <c r="F20" s="439"/>
-      <c r="G20" s="439"/>
-      <c r="H20" s="440"/>
-      <c r="I20" s="447" t="s">
+      <c r="D20" s="407"/>
+      <c r="E20" s="407"/>
+      <c r="F20" s="407"/>
+      <c r="G20" s="407"/>
+      <c r="H20" s="408"/>
+      <c r="I20" s="415" t="s">
         <v>52</v>
       </c>
       <c r="J20" s="10"/>
@@ -17561,14 +17558,14 @@
       <c r="A21" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="B21" s="436"/>
-      <c r="C21" s="441"/>
-      <c r="D21" s="442"/>
-      <c r="E21" s="442"/>
-      <c r="F21" s="442"/>
-      <c r="G21" s="442"/>
-      <c r="H21" s="443"/>
-      <c r="I21" s="436"/>
+      <c r="B21" s="404"/>
+      <c r="C21" s="409"/>
+      <c r="D21" s="410"/>
+      <c r="E21" s="410"/>
+      <c r="F21" s="410"/>
+      <c r="G21" s="410"/>
+      <c r="H21" s="411"/>
+      <c r="I21" s="404"/>
       <c r="J21" s="10"/>
       <c r="K21" s="10"/>
       <c r="L21" s="10"/>
@@ -17578,14 +17575,14 @@
       <c r="A22" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="B22" s="437"/>
-      <c r="C22" s="444"/>
-      <c r="D22" s="445"/>
-      <c r="E22" s="445"/>
-      <c r="F22" s="445"/>
-      <c r="G22" s="445"/>
-      <c r="H22" s="446"/>
-      <c r="I22" s="437"/>
+      <c r="B22" s="405"/>
+      <c r="C22" s="412"/>
+      <c r="D22" s="413"/>
+      <c r="E22" s="413"/>
+      <c r="F22" s="413"/>
+      <c r="G22" s="413"/>
+      <c r="H22" s="414"/>
+      <c r="I22" s="405"/>
       <c r="J22" s="10"/>
       <c r="K22" s="10"/>
       <c r="L22" s="10"/>
@@ -17601,10 +17598,10 @@
       <c r="B26" s="18">
         <v>1</v>
       </c>
-      <c r="C26" s="429">
+      <c r="C26" s="391">
         <v>2</v>
       </c>
-      <c r="D26" s="430"/>
+      <c r="D26" s="392"/>
       <c r="E26" s="18">
         <v>3</v>
       </c>
@@ -17628,14 +17625,14 @@
       <c r="B27" s="19">
         <v>1</v>
       </c>
-      <c r="C27" s="395" t="s">
+      <c r="C27" s="393" t="s">
         <v>53</v>
       </c>
-      <c r="D27" s="396"/>
-      <c r="E27" s="396"/>
-      <c r="F27" s="396"/>
-      <c r="G27" s="396"/>
-      <c r="H27" s="397"/>
+      <c r="D27" s="394"/>
+      <c r="E27" s="394"/>
+      <c r="F27" s="394"/>
+      <c r="G27" s="394"/>
+      <c r="H27" s="395"/>
       <c r="I27" s="20"/>
       <c r="N27" s="16"/>
     </row>
@@ -17652,12 +17649,12 @@
       <c r="D28" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="E28" s="395" t="s">
+      <c r="E28" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F28" s="396"/>
-      <c r="G28" s="396"/>
-      <c r="H28" s="397"/>
+      <c r="F28" s="394"/>
+      <c r="G28" s="394"/>
+      <c r="H28" s="395"/>
       <c r="I28" s="20" t="e">
         <f>SUM(I29:I190)</f>
         <v>#REF!</v>
@@ -17683,11 +17680,11 @@
       <c r="E29" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F29" s="402" t="s">
+      <c r="F29" s="396" t="s">
         <v>56</v>
       </c>
-      <c r="G29" s="403"/>
-      <c r="H29" s="404"/>
+      <c r="G29" s="397"/>
+      <c r="H29" s="398"/>
       <c r="I29" s="20" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17713,11 +17710,11 @@
       <c r="E30" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F30" s="402" t="s">
+      <c r="F30" s="396" t="s">
         <v>57</v>
       </c>
-      <c r="G30" s="403"/>
-      <c r="H30" s="404"/>
+      <c r="G30" s="397"/>
+      <c r="H30" s="398"/>
       <c r="I30" s="20" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17740,11 +17737,11 @@
       <c r="E31" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F31" s="402" t="s">
+      <c r="F31" s="396" t="s">
         <v>58</v>
       </c>
-      <c r="G31" s="403"/>
-      <c r="H31" s="404"/>
+      <c r="G31" s="397"/>
+      <c r="H31" s="398"/>
       <c r="I31" s="20"/>
     </row>
     <row r="32" spans="1:14" ht="12" customHeight="1">
@@ -17763,11 +17760,11 @@
       <c r="E32" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F32" s="392" t="s">
+      <c r="F32" s="416" t="s">
         <v>59</v>
       </c>
-      <c r="G32" s="393"/>
-      <c r="H32" s="394"/>
+      <c r="G32" s="417"/>
+      <c r="H32" s="418"/>
       <c r="I32" s="20" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -17793,16 +17790,16 @@
       <c r="B34" s="21">
         <v>7</v>
       </c>
-      <c r="C34" s="398" t="s">
+      <c r="C34" s="419" t="s">
         <v>61</v>
       </c>
-      <c r="D34" s="399"/>
-      <c r="E34" s="395" t="s">
+      <c r="D34" s="420"/>
+      <c r="E34" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F34" s="396"/>
-      <c r="G34" s="396"/>
-      <c r="H34" s="397"/>
+      <c r="F34" s="394"/>
+      <c r="G34" s="394"/>
+      <c r="H34" s="395"/>
       <c r="I34" s="32"/>
     </row>
     <row r="35" spans="1:15" ht="12" customHeight="1">
@@ -17812,16 +17809,16 @@
       <c r="B35" s="21">
         <v>8</v>
       </c>
-      <c r="C35" s="400"/>
-      <c r="D35" s="401"/>
+      <c r="C35" s="421"/>
+      <c r="D35" s="422"/>
       <c r="E35" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F35" s="402" t="s">
-        <v>44</v>
-      </c>
-      <c r="G35" s="403"/>
-      <c r="H35" s="404"/>
+      <c r="F35" s="396" t="s">
+        <v>44</v>
+      </c>
+      <c r="G35" s="397"/>
+      <c r="H35" s="398"/>
       <c r="I35" s="32"/>
     </row>
     <row r="36" spans="1:15" hidden="1">
@@ -17834,16 +17831,16 @@
       <c r="B37" s="21">
         <v>10</v>
       </c>
-      <c r="C37" s="408" t="s">
+      <c r="C37" s="423" t="s">
         <v>62</v>
       </c>
-      <c r="D37" s="409"/>
-      <c r="E37" s="395" t="s">
+      <c r="D37" s="424"/>
+      <c r="E37" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F37" s="396"/>
-      <c r="G37" s="396"/>
-      <c r="H37" s="397"/>
+      <c r="F37" s="394"/>
+      <c r="G37" s="394"/>
+      <c r="H37" s="395"/>
       <c r="I37" s="32"/>
     </row>
     <row r="38" spans="1:15" ht="12" customHeight="1">
@@ -17853,16 +17850,16 @@
       <c r="B38" s="21">
         <v>11</v>
       </c>
-      <c r="C38" s="410"/>
-      <c r="D38" s="411"/>
-      <c r="E38" s="414" t="s">
+      <c r="C38" s="425"/>
+      <c r="D38" s="426"/>
+      <c r="E38" s="429" t="s">
         <v>55</v>
       </c>
-      <c r="F38" s="402" t="s">
+      <c r="F38" s="396" t="s">
         <v>63</v>
       </c>
-      <c r="G38" s="403"/>
-      <c r="H38" s="404"/>
+      <c r="G38" s="397"/>
+      <c r="H38" s="398"/>
       <c r="I38" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17875,14 +17872,14 @@
       <c r="B39" s="21">
         <v>12</v>
       </c>
-      <c r="C39" s="412"/>
-      <c r="D39" s="413"/>
-      <c r="E39" s="415"/>
-      <c r="F39" s="402" t="s">
+      <c r="C39" s="427"/>
+      <c r="D39" s="428"/>
+      <c r="E39" s="430"/>
+      <c r="F39" s="396" t="s">
         <v>64</v>
       </c>
-      <c r="G39" s="403"/>
-      <c r="H39" s="404"/>
+      <c r="G39" s="397"/>
+      <c r="H39" s="398"/>
       <c r="I39" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17895,16 +17892,16 @@
       <c r="B40" s="21">
         <v>13</v>
       </c>
-      <c r="C40" s="398" t="s">
+      <c r="C40" s="419" t="s">
         <v>65</v>
       </c>
-      <c r="D40" s="399"/>
-      <c r="E40" s="395" t="s">
+      <c r="D40" s="420"/>
+      <c r="E40" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F40" s="396"/>
-      <c r="G40" s="396"/>
-      <c r="H40" s="397"/>
+      <c r="F40" s="394"/>
+      <c r="G40" s="394"/>
+      <c r="H40" s="395"/>
       <c r="I40" s="32"/>
     </row>
     <row r="41" spans="1:15" ht="17.25" customHeight="1">
@@ -17914,16 +17911,16 @@
       <c r="B41" s="21">
         <v>14</v>
       </c>
-      <c r="C41" s="400"/>
-      <c r="D41" s="401"/>
+      <c r="C41" s="421"/>
+      <c r="D41" s="422"/>
       <c r="E41" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F41" s="402" t="s">
-        <v>44</v>
-      </c>
-      <c r="G41" s="403"/>
-      <c r="H41" s="404"/>
+      <c r="F41" s="396" t="s">
+        <v>44</v>
+      </c>
+      <c r="G41" s="397"/>
+      <c r="H41" s="398"/>
       <c r="I41" s="32"/>
     </row>
     <row r="42" spans="1:15" ht="12" customHeight="1">
@@ -17942,11 +17939,11 @@
       <c r="E42" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F42" s="392" t="s">
+      <c r="F42" s="416" t="s">
         <v>66</v>
       </c>
-      <c r="G42" s="393"/>
-      <c r="H42" s="394"/>
+      <c r="G42" s="417"/>
+      <c r="H42" s="418"/>
       <c r="I42" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17963,14 +17960,14 @@
       <c r="B44" s="21">
         <v>17</v>
       </c>
-      <c r="C44" s="395" t="s">
+      <c r="C44" s="393" t="s">
         <v>67</v>
       </c>
-      <c r="D44" s="396"/>
-      <c r="E44" s="396"/>
-      <c r="F44" s="396"/>
-      <c r="G44" s="396"/>
-      <c r="H44" s="397"/>
+      <c r="D44" s="394"/>
+      <c r="E44" s="394"/>
+      <c r="F44" s="394"/>
+      <c r="G44" s="394"/>
+      <c r="H44" s="395"/>
       <c r="I44" s="32"/>
     </row>
     <row r="45" spans="1:15" ht="12" customHeight="1">
@@ -17980,16 +17977,16 @@
       <c r="B45" s="21">
         <v>18</v>
       </c>
-      <c r="C45" s="423" t="s">
+      <c r="C45" s="431" t="s">
         <v>68</v>
       </c>
-      <c r="D45" s="424"/>
-      <c r="E45" s="395" t="s">
+      <c r="D45" s="432"/>
+      <c r="E45" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F45" s="396"/>
-      <c r="G45" s="396"/>
-      <c r="H45" s="397"/>
+      <c r="F45" s="394"/>
+      <c r="G45" s="394"/>
+      <c r="H45" s="395"/>
       <c r="I45" s="32"/>
     </row>
     <row r="46" spans="1:15" ht="30" customHeight="1">
@@ -17999,16 +17996,16 @@
       <c r="B46" s="21">
         <v>19</v>
       </c>
-      <c r="C46" s="425"/>
-      <c r="D46" s="426"/>
-      <c r="E46" s="414" t="s">
+      <c r="C46" s="433"/>
+      <c r="D46" s="434"/>
+      <c r="E46" s="429" t="s">
         <v>55</v>
       </c>
-      <c r="F46" s="402" t="s">
+      <c r="F46" s="396" t="s">
         <v>69</v>
       </c>
-      <c r="G46" s="403"/>
-      <c r="H46" s="404"/>
+      <c r="G46" s="397"/>
+      <c r="H46" s="398"/>
       <c r="I46" s="127" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -18023,14 +18020,14 @@
       <c r="B47" s="21">
         <v>20</v>
       </c>
-      <c r="C47" s="425"/>
-      <c r="D47" s="426"/>
-      <c r="E47" s="416"/>
-      <c r="F47" s="402" t="s">
+      <c r="C47" s="433"/>
+      <c r="D47" s="434"/>
+      <c r="E47" s="437"/>
+      <c r="F47" s="396" t="s">
         <v>70</v>
       </c>
-      <c r="G47" s="403"/>
-      <c r="H47" s="404"/>
+      <c r="G47" s="397"/>
+      <c r="H47" s="398"/>
       <c r="I47" s="127" t="e">
         <f>#REF!+#REF!-#REF!</f>
         <v>#REF!</v>
@@ -18045,14 +18042,14 @@
       <c r="B48" s="21">
         <v>21</v>
       </c>
-      <c r="C48" s="425"/>
-      <c r="D48" s="426"/>
-      <c r="E48" s="416"/>
-      <c r="F48" s="402" t="s">
+      <c r="C48" s="433"/>
+      <c r="D48" s="434"/>
+      <c r="E48" s="437"/>
+      <c r="F48" s="396" t="s">
         <v>71</v>
       </c>
-      <c r="G48" s="403"/>
-      <c r="H48" s="404"/>
+      <c r="G48" s="397"/>
+      <c r="H48" s="398"/>
       <c r="I48" s="127" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -18066,14 +18063,14 @@
       <c r="B49" s="21">
         <v>22</v>
       </c>
-      <c r="C49" s="427"/>
-      <c r="D49" s="428"/>
-      <c r="E49" s="415"/>
-      <c r="F49" s="402" t="s">
+      <c r="C49" s="435"/>
+      <c r="D49" s="436"/>
+      <c r="E49" s="430"/>
+      <c r="F49" s="396" t="s">
         <v>72</v>
       </c>
-      <c r="G49" s="403"/>
-      <c r="H49" s="404"/>
+      <c r="G49" s="397"/>
+      <c r="H49" s="398"/>
       <c r="I49" s="34" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -18087,16 +18084,16 @@
       <c r="B50" s="21">
         <v>23</v>
       </c>
-      <c r="C50" s="419" t="s">
+      <c r="C50" s="438" t="s">
         <v>73</v>
       </c>
-      <c r="D50" s="420"/>
-      <c r="E50" s="395" t="s">
+      <c r="D50" s="439"/>
+      <c r="E50" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F50" s="396"/>
-      <c r="G50" s="396"/>
-      <c r="H50" s="397"/>
+      <c r="F50" s="394"/>
+      <c r="G50" s="394"/>
+      <c r="H50" s="395"/>
       <c r="I50" s="32"/>
     </row>
     <row r="51" spans="1:14" ht="12" customHeight="1">
@@ -18106,16 +18103,16 @@
       <c r="B51" s="21">
         <v>24</v>
       </c>
-      <c r="C51" s="421"/>
-      <c r="D51" s="422"/>
+      <c r="C51" s="440"/>
+      <c r="D51" s="441"/>
       <c r="E51" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F51" s="402" t="s">
+      <c r="F51" s="396" t="s">
         <v>23</v>
       </c>
-      <c r="G51" s="403"/>
-      <c r="H51" s="404"/>
+      <c r="G51" s="397"/>
+      <c r="H51" s="398"/>
       <c r="I51" s="36" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -18138,11 +18135,11 @@
       <c r="E52" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F52" s="402" t="s">
+      <c r="F52" s="396" t="s">
         <v>74</v>
       </c>
-      <c r="G52" s="403"/>
-      <c r="H52" s="404"/>
+      <c r="G52" s="397"/>
+      <c r="H52" s="398"/>
       <c r="I52" s="32"/>
       <c r="N52" s="35"/>
     </row>
@@ -18156,16 +18153,16 @@
       <c r="B54" s="21">
         <v>27</v>
       </c>
-      <c r="C54" s="398" t="s">
+      <c r="C54" s="419" t="s">
         <v>75</v>
       </c>
-      <c r="D54" s="399"/>
-      <c r="E54" s="395" t="s">
+      <c r="D54" s="420"/>
+      <c r="E54" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F54" s="396"/>
-      <c r="G54" s="396"/>
-      <c r="H54" s="397"/>
+      <c r="F54" s="394"/>
+      <c r="G54" s="394"/>
+      <c r="H54" s="395"/>
       <c r="I54" s="32"/>
     </row>
     <row r="55" spans="1:14" ht="12" customHeight="1">
@@ -18175,16 +18172,16 @@
       <c r="B55" s="21">
         <v>28</v>
       </c>
-      <c r="C55" s="400"/>
-      <c r="D55" s="401"/>
+      <c r="C55" s="421"/>
+      <c r="D55" s="422"/>
       <c r="E55" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F55" s="402" t="s">
+      <c r="F55" s="396" t="s">
         <v>76</v>
       </c>
-      <c r="G55" s="403"/>
-      <c r="H55" s="404"/>
+      <c r="G55" s="397"/>
+      <c r="H55" s="398"/>
       <c r="I55" s="32"/>
     </row>
     <row r="56" spans="1:14" ht="12" customHeight="1">
@@ -18194,16 +18191,16 @@
       <c r="B56" s="21">
         <v>29</v>
       </c>
-      <c r="C56" s="400"/>
-      <c r="D56" s="401"/>
+      <c r="C56" s="421"/>
+      <c r="D56" s="422"/>
       <c r="E56" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F56" s="402" t="s">
+      <c r="F56" s="396" t="s">
         <v>77</v>
       </c>
-      <c r="G56" s="403"/>
-      <c r="H56" s="404"/>
+      <c r="G56" s="397"/>
+      <c r="H56" s="398"/>
       <c r="I56" s="32"/>
     </row>
     <row r="57" spans="1:14" ht="12" customHeight="1">
@@ -18213,16 +18210,16 @@
       <c r="B57" s="21">
         <v>30</v>
       </c>
-      <c r="C57" s="400"/>
-      <c r="D57" s="401"/>
+      <c r="C57" s="421"/>
+      <c r="D57" s="422"/>
       <c r="E57" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F57" s="402" t="s">
+      <c r="F57" s="396" t="s">
         <v>78</v>
       </c>
-      <c r="G57" s="403"/>
-      <c r="H57" s="404"/>
+      <c r="G57" s="397"/>
+      <c r="H57" s="398"/>
       <c r="I57" s="32"/>
     </row>
     <row r="58" spans="1:14" ht="12" customHeight="1">
@@ -18241,11 +18238,11 @@
       <c r="E58" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F58" s="402" t="s">
+      <c r="F58" s="396" t="s">
         <v>79</v>
       </c>
-      <c r="G58" s="403"/>
-      <c r="H58" s="404"/>
+      <c r="G58" s="397"/>
+      <c r="H58" s="398"/>
       <c r="I58" s="32" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -18261,14 +18258,14 @@
       <c r="B60" s="21">
         <v>33</v>
       </c>
-      <c r="C60" s="395" t="s">
+      <c r="C60" s="393" t="s">
         <v>80</v>
       </c>
-      <c r="D60" s="396"/>
-      <c r="E60" s="396"/>
-      <c r="F60" s="396"/>
-      <c r="G60" s="396"/>
-      <c r="H60" s="397"/>
+      <c r="D60" s="394"/>
+      <c r="E60" s="394"/>
+      <c r="F60" s="394"/>
+      <c r="G60" s="394"/>
+      <c r="H60" s="395"/>
       <c r="I60" s="32"/>
     </row>
     <row r="61" spans="1:14" ht="12" customHeight="1">
@@ -18278,16 +18275,16 @@
       <c r="B61" s="21">
         <v>34</v>
       </c>
-      <c r="C61" s="398" t="s">
+      <c r="C61" s="419" t="s">
         <v>81</v>
       </c>
-      <c r="D61" s="399"/>
-      <c r="E61" s="395" t="s">
+      <c r="D61" s="420"/>
+      <c r="E61" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F61" s="396"/>
-      <c r="G61" s="396"/>
-      <c r="H61" s="397"/>
+      <c r="F61" s="394"/>
+      <c r="G61" s="394"/>
+      <c r="H61" s="395"/>
       <c r="I61" s="32"/>
     </row>
     <row r="62" spans="1:14" ht="12" customHeight="1">
@@ -18297,18 +18294,18 @@
       <c r="B62" s="21">
         <v>35</v>
       </c>
-      <c r="C62" s="400"/>
-      <c r="D62" s="401"/>
+      <c r="C62" s="421"/>
+      <c r="D62" s="422"/>
       <c r="E62" s="26" t="s">
         <v>55</v>
       </c>
       <c r="F62" s="26" t="s">
         <v>82</v>
       </c>
-      <c r="G62" s="417" t="s">
+      <c r="G62" s="442" t="s">
         <v>5</v>
       </c>
-      <c r="H62" s="418"/>
+      <c r="H62" s="443"/>
       <c r="I62" s="32"/>
     </row>
     <row r="63" spans="1:14" ht="12" customHeight="1">
@@ -18318,8 +18315,8 @@
       <c r="B63" s="21">
         <v>36</v>
       </c>
-      <c r="C63" s="400"/>
-      <c r="D63" s="401"/>
+      <c r="C63" s="421"/>
+      <c r="D63" s="422"/>
       <c r="E63" s="27" t="s">
         <v>44</v>
       </c>
@@ -18383,10 +18380,10 @@
       <c r="F66" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="G66" s="417" t="s">
+      <c r="G66" s="442" t="s">
         <v>5</v>
       </c>
-      <c r="H66" s="418"/>
+      <c r="H66" s="443"/>
       <c r="I66" s="32"/>
     </row>
     <row r="67" spans="1:14" ht="12" customHeight="1">
@@ -18465,10 +18462,10 @@
       <c r="F70" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="G70" s="417" t="s">
+      <c r="G70" s="442" t="s">
         <v>5</v>
       </c>
-      <c r="H70" s="418"/>
+      <c r="H70" s="443"/>
       <c r="I70" s="32"/>
     </row>
     <row r="71" spans="1:14" ht="12" customHeight="1">
@@ -18547,10 +18544,10 @@
       <c r="F74" s="26" t="s">
         <v>87</v>
       </c>
-      <c r="G74" s="417" t="s">
+      <c r="G74" s="442" t="s">
         <v>5</v>
       </c>
-      <c r="H74" s="418"/>
+      <c r="H74" s="443"/>
       <c r="I74" s="32"/>
     </row>
     <row r="75" spans="1:14" ht="12" customHeight="1">
@@ -18617,16 +18614,16 @@
       <c r="B78" s="21">
         <v>51</v>
       </c>
-      <c r="C78" s="398" t="s">
+      <c r="C78" s="419" t="s">
         <v>88</v>
       </c>
-      <c r="D78" s="399"/>
-      <c r="E78" s="395" t="s">
+      <c r="D78" s="420"/>
+      <c r="E78" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F78" s="396"/>
-      <c r="G78" s="396"/>
-      <c r="H78" s="397"/>
+      <c r="F78" s="394"/>
+      <c r="G78" s="394"/>
+      <c r="H78" s="395"/>
       <c r="I78" s="32"/>
     </row>
     <row r="79" spans="1:14" ht="12" customHeight="1">
@@ -18636,16 +18633,16 @@
       <c r="B79" s="21">
         <v>52</v>
       </c>
-      <c r="C79" s="400"/>
-      <c r="D79" s="401"/>
+      <c r="C79" s="421"/>
+      <c r="D79" s="422"/>
       <c r="E79" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F79" s="402" t="s">
+      <c r="F79" s="396" t="s">
         <v>89</v>
       </c>
-      <c r="G79" s="403"/>
-      <c r="H79" s="404"/>
+      <c r="G79" s="397"/>
+      <c r="H79" s="398"/>
       <c r="I79" s="32"/>
     </row>
     <row r="80" spans="1:14" ht="12" customHeight="1">
@@ -18664,11 +18661,11 @@
       <c r="E80" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F80" s="402" t="s">
+      <c r="F80" s="396" t="s">
         <v>24</v>
       </c>
-      <c r="G80" s="403"/>
-      <c r="H80" s="404"/>
+      <c r="G80" s="397"/>
+      <c r="H80" s="398"/>
       <c r="I80" s="36" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -18691,11 +18688,11 @@
       <c r="E81" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F81" s="402" t="s">
+      <c r="F81" s="396" t="s">
         <v>90</v>
       </c>
-      <c r="G81" s="403"/>
-      <c r="H81" s="404"/>
+      <c r="G81" s="397"/>
+      <c r="H81" s="398"/>
       <c r="I81" s="32"/>
       <c r="N81" s="35"/>
     </row>
@@ -18715,13 +18712,13 @@
       <c r="E82" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F82" s="414" t="s">
+      <c r="F82" s="429" t="s">
         <v>91</v>
       </c>
-      <c r="G82" s="417" t="s">
+      <c r="G82" s="442" t="s">
         <v>5</v>
       </c>
-      <c r="H82" s="418"/>
+      <c r="H82" s="443"/>
       <c r="I82" s="32"/>
     </row>
     <row r="83" spans="1:14" ht="24" customHeight="1">
@@ -18740,8 +18737,8 @@
       <c r="E83" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F83" s="416"/>
-      <c r="G83" s="414" t="s">
+      <c r="F83" s="437"/>
+      <c r="G83" s="429" t="s">
         <v>55</v>
       </c>
       <c r="H83" s="15" t="s">
@@ -18768,8 +18765,8 @@
       <c r="E84" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F84" s="415"/>
-      <c r="G84" s="415"/>
+      <c r="F84" s="430"/>
+      <c r="G84" s="430"/>
       <c r="H84" s="15" t="s">
         <v>92</v>
       </c>
@@ -18794,11 +18791,11 @@
       <c r="E85" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F85" s="402" t="s">
+      <c r="F85" s="396" t="s">
         <v>9</v>
       </c>
-      <c r="G85" s="403"/>
-      <c r="H85" s="404"/>
+      <c r="G85" s="397"/>
+      <c r="H85" s="398"/>
       <c r="I85" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -18820,11 +18817,11 @@
       <c r="E86" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F86" s="402" t="s">
+      <c r="F86" s="396" t="s">
         <v>10</v>
       </c>
-      <c r="G86" s="403"/>
-      <c r="H86" s="404"/>
+      <c r="G86" s="397"/>
+      <c r="H86" s="398"/>
       <c r="I86" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -18846,11 +18843,11 @@
       <c r="E87" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F87" s="402" t="s">
+      <c r="F87" s="396" t="s">
         <v>11</v>
       </c>
-      <c r="G87" s="403"/>
-      <c r="H87" s="404"/>
+      <c r="G87" s="397"/>
+      <c r="H87" s="398"/>
       <c r="I87" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -18872,11 +18869,11 @@
       <c r="E88" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F88" s="402" t="s">
+      <c r="F88" s="396" t="s">
         <v>93</v>
       </c>
-      <c r="G88" s="403"/>
-      <c r="H88" s="404"/>
+      <c r="G88" s="397"/>
+      <c r="H88" s="398"/>
       <c r="I88" s="32"/>
     </row>
     <row r="89" spans="1:14" ht="12" customHeight="1">
@@ -18895,11 +18892,11 @@
       <c r="E89" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F89" s="392" t="s">
+      <c r="F89" s="416" t="s">
         <v>94</v>
       </c>
-      <c r="G89" s="393"/>
-      <c r="H89" s="394"/>
+      <c r="G89" s="417"/>
+      <c r="H89" s="418"/>
       <c r="I89" s="32"/>
       <c r="J89" s="10"/>
     </row>
@@ -18919,9 +18916,9 @@
       <c r="E90" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F90" s="392"/>
-      <c r="G90" s="393"/>
-      <c r="H90" s="394"/>
+      <c r="F90" s="416"/>
+      <c r="G90" s="417"/>
+      <c r="H90" s="418"/>
       <c r="I90" s="39"/>
       <c r="J90" s="10"/>
     </row>
@@ -18935,16 +18932,16 @@
       <c r="B92" s="21">
         <v>63</v>
       </c>
-      <c r="C92" s="398" t="s">
+      <c r="C92" s="419" t="s">
         <v>95</v>
       </c>
-      <c r="D92" s="399"/>
-      <c r="E92" s="395" t="s">
+      <c r="D92" s="420"/>
+      <c r="E92" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F92" s="396"/>
-      <c r="G92" s="396"/>
-      <c r="H92" s="397"/>
+      <c r="F92" s="394"/>
+      <c r="G92" s="394"/>
+      <c r="H92" s="395"/>
       <c r="I92" s="32"/>
     </row>
     <row r="93" spans="1:14" ht="12" customHeight="1">
@@ -18960,14 +18957,14 @@
       <c r="D93" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="E93" s="414" t="s">
+      <c r="E93" s="429" t="s">
         <v>55</v>
       </c>
-      <c r="F93" s="402" t="s">
-        <v>44</v>
-      </c>
-      <c r="G93" s="403"/>
-      <c r="H93" s="404"/>
+      <c r="F93" s="396" t="s">
+        <v>44</v>
+      </c>
+      <c r="G93" s="397"/>
+      <c r="H93" s="398"/>
       <c r="I93" s="32"/>
     </row>
     <row r="94" spans="1:14" ht="12" customHeight="1">
@@ -18983,12 +18980,12 @@
       <c r="D94" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="E94" s="415"/>
-      <c r="F94" s="392" t="s">
+      <c r="E94" s="430"/>
+      <c r="F94" s="416" t="s">
         <v>96</v>
       </c>
-      <c r="G94" s="393"/>
-      <c r="H94" s="394"/>
+      <c r="G94" s="417"/>
+      <c r="H94" s="418"/>
       <c r="I94" s="32"/>
       <c r="J94" s="10"/>
     </row>
@@ -19002,16 +18999,16 @@
       <c r="B96" s="21">
         <v>66</v>
       </c>
-      <c r="C96" s="398" t="s">
+      <c r="C96" s="419" t="s">
         <v>97</v>
       </c>
-      <c r="D96" s="399"/>
-      <c r="E96" s="395" t="s">
+      <c r="D96" s="420"/>
+      <c r="E96" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F96" s="396"/>
-      <c r="G96" s="396"/>
-      <c r="H96" s="397"/>
+      <c r="F96" s="394"/>
+      <c r="G96" s="394"/>
+      <c r="H96" s="395"/>
       <c r="I96" s="32"/>
     </row>
     <row r="97" spans="1:10" ht="12" customHeight="1">
@@ -19030,11 +19027,11 @@
       <c r="E97" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F97" s="402" t="s">
+      <c r="F97" s="396" t="s">
         <v>98</v>
       </c>
-      <c r="G97" s="403"/>
-      <c r="H97" s="404"/>
+      <c r="G97" s="397"/>
+      <c r="H97" s="398"/>
       <c r="I97" s="32"/>
     </row>
     <row r="98" spans="1:10" ht="12" customHeight="1">
@@ -19053,11 +19050,11 @@
       <c r="E98" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F98" s="402" t="s">
+      <c r="F98" s="396" t="s">
         <v>99</v>
       </c>
-      <c r="G98" s="403"/>
-      <c r="H98" s="404"/>
+      <c r="G98" s="397"/>
+      <c r="H98" s="398"/>
       <c r="I98" s="32"/>
     </row>
     <row r="99" spans="1:10" ht="12" customHeight="1">
@@ -19076,11 +19073,11 @@
       <c r="E99" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F99" s="402" t="s">
+      <c r="F99" s="396" t="s">
         <v>12</v>
       </c>
-      <c r="G99" s="403"/>
-      <c r="H99" s="404"/>
+      <c r="G99" s="397"/>
+      <c r="H99" s="398"/>
       <c r="I99" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19102,11 +19099,11 @@
       <c r="E100" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F100" s="402" t="s">
+      <c r="F100" s="396" t="s">
         <v>100</v>
       </c>
-      <c r="G100" s="403"/>
-      <c r="H100" s="404"/>
+      <c r="G100" s="397"/>
+      <c r="H100" s="398"/>
       <c r="I100" s="32"/>
     </row>
     <row r="101" spans="1:10" ht="12" customHeight="1">
@@ -19125,11 +19122,11 @@
       <c r="E101" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F101" s="392" t="s">
-        <v>44</v>
-      </c>
-      <c r="G101" s="393"/>
-      <c r="H101" s="394"/>
+      <c r="F101" s="416" t="s">
+        <v>44</v>
+      </c>
+      <c r="G101" s="417"/>
+      <c r="H101" s="418"/>
       <c r="I101" s="32"/>
       <c r="J101" s="10"/>
     </row>
@@ -19149,11 +19146,11 @@
       <c r="E102" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F102" s="392" t="s">
-        <v>44</v>
-      </c>
-      <c r="G102" s="393"/>
-      <c r="H102" s="394"/>
+      <c r="F102" s="416" t="s">
+        <v>44</v>
+      </c>
+      <c r="G102" s="417"/>
+      <c r="H102" s="418"/>
       <c r="I102" s="32"/>
       <c r="J102" s="10"/>
     </row>
@@ -19167,14 +19164,14 @@
       <c r="B104" s="21">
         <v>72</v>
       </c>
-      <c r="C104" s="395" t="s">
+      <c r="C104" s="393" t="s">
         <v>19</v>
       </c>
-      <c r="D104" s="396"/>
-      <c r="E104" s="396"/>
-      <c r="F104" s="396"/>
-      <c r="G104" s="396"/>
-      <c r="H104" s="397"/>
+      <c r="D104" s="394"/>
+      <c r="E104" s="394"/>
+      <c r="F104" s="394"/>
+      <c r="G104" s="394"/>
+      <c r="H104" s="395"/>
       <c r="I104" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19187,14 +19184,14 @@
       <c r="B105" s="21">
         <v>73</v>
       </c>
-      <c r="C105" s="395" t="s">
+      <c r="C105" s="393" t="s">
         <v>101</v>
       </c>
-      <c r="D105" s="396"/>
-      <c r="E105" s="396"/>
-      <c r="F105" s="396"/>
-      <c r="G105" s="396"/>
-      <c r="H105" s="397"/>
+      <c r="D105" s="394"/>
+      <c r="E105" s="394"/>
+      <c r="F105" s="394"/>
+      <c r="G105" s="394"/>
+      <c r="H105" s="395"/>
       <c r="I105" s="32"/>
     </row>
     <row r="106" spans="1:10" ht="12" customHeight="1">
@@ -19204,16 +19201,16 @@
       <c r="B106" s="21">
         <v>74</v>
       </c>
-      <c r="C106" s="398" t="s">
+      <c r="C106" s="419" t="s">
         <v>102</v>
       </c>
-      <c r="D106" s="399"/>
-      <c r="E106" s="395" t="s">
+      <c r="D106" s="420"/>
+      <c r="E106" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F106" s="396"/>
-      <c r="G106" s="396"/>
-      <c r="H106" s="397"/>
+      <c r="F106" s="394"/>
+      <c r="G106" s="394"/>
+      <c r="H106" s="395"/>
       <c r="I106" s="32"/>
     </row>
     <row r="107" spans="1:10" ht="18.75" customHeight="1">
@@ -19223,16 +19220,16 @@
       <c r="B107" s="21">
         <v>75</v>
       </c>
-      <c r="C107" s="400"/>
-      <c r="D107" s="401"/>
+      <c r="C107" s="421"/>
+      <c r="D107" s="422"/>
       <c r="E107" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F107" s="402" t="s">
+      <c r="F107" s="396" t="s">
         <v>13</v>
       </c>
-      <c r="G107" s="403"/>
-      <c r="H107" s="404"/>
+      <c r="G107" s="397"/>
+      <c r="H107" s="398"/>
       <c r="I107" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19254,11 +19251,11 @@
       <c r="E108" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F108" s="392" t="s">
+      <c r="F108" s="416" t="s">
         <v>103</v>
       </c>
-      <c r="G108" s="393"/>
-      <c r="H108" s="394"/>
+      <c r="G108" s="417"/>
+      <c r="H108" s="418"/>
       <c r="I108" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19281,11 +19278,11 @@
       <c r="E109" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F109" s="392" t="s">
+      <c r="F109" s="416" t="s">
         <v>104</v>
       </c>
-      <c r="G109" s="393"/>
-      <c r="H109" s="394"/>
+      <c r="G109" s="417"/>
+      <c r="H109" s="418"/>
       <c r="I109" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19308,11 +19305,11 @@
       <c r="E110" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F110" s="392" t="s">
+      <c r="F110" s="416" t="s">
         <v>8</v>
       </c>
-      <c r="G110" s="393"/>
-      <c r="H110" s="394"/>
+      <c r="G110" s="417"/>
+      <c r="H110" s="418"/>
       <c r="I110" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19329,16 +19326,16 @@
       <c r="B112" s="21">
         <v>77</v>
       </c>
-      <c r="C112" s="398" t="s">
+      <c r="C112" s="419" t="s">
         <v>105</v>
       </c>
-      <c r="D112" s="399"/>
-      <c r="E112" s="395" t="s">
+      <c r="D112" s="420"/>
+      <c r="E112" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F112" s="396"/>
-      <c r="G112" s="396"/>
-      <c r="H112" s="397"/>
+      <c r="F112" s="394"/>
+      <c r="G112" s="394"/>
+      <c r="H112" s="395"/>
       <c r="I112" s="32"/>
     </row>
     <row r="113" spans="1:9" ht="12" customHeight="1">
@@ -19357,11 +19354,11 @@
       <c r="E113" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F113" s="402" t="s">
+      <c r="F113" s="396" t="s">
         <v>106</v>
       </c>
-      <c r="G113" s="403"/>
-      <c r="H113" s="404"/>
+      <c r="G113" s="397"/>
+      <c r="H113" s="398"/>
       <c r="I113" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19383,11 +19380,11 @@
       <c r="E114" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F114" s="402" t="s">
+      <c r="F114" s="396" t="s">
         <v>107</v>
       </c>
-      <c r="G114" s="403"/>
-      <c r="H114" s="404"/>
+      <c r="G114" s="397"/>
+      <c r="H114" s="398"/>
       <c r="I114" s="32"/>
     </row>
     <row r="115" spans="1:9" ht="12" customHeight="1">
@@ -19397,14 +19394,14 @@
       <c r="B115" s="21">
         <v>80</v>
       </c>
-      <c r="C115" s="395" t="s">
+      <c r="C115" s="393" t="s">
         <v>108</v>
       </c>
-      <c r="D115" s="396"/>
-      <c r="E115" s="396"/>
-      <c r="F115" s="396"/>
-      <c r="G115" s="396"/>
-      <c r="H115" s="397"/>
+      <c r="D115" s="394"/>
+      <c r="E115" s="394"/>
+      <c r="F115" s="394"/>
+      <c r="G115" s="394"/>
+      <c r="H115" s="395"/>
       <c r="I115" s="32"/>
     </row>
     <row r="116" spans="1:9" ht="12" customHeight="1">
@@ -19414,16 +19411,16 @@
       <c r="B116" s="21">
         <v>81</v>
       </c>
-      <c r="C116" s="398" t="s">
+      <c r="C116" s="419" t="s">
         <v>109</v>
       </c>
-      <c r="D116" s="399"/>
-      <c r="E116" s="395" t="s">
+      <c r="D116" s="420"/>
+      <c r="E116" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F116" s="396"/>
-      <c r="G116" s="396"/>
-      <c r="H116" s="397"/>
+      <c r="F116" s="394"/>
+      <c r="G116" s="394"/>
+      <c r="H116" s="395"/>
       <c r="I116" s="32"/>
     </row>
     <row r="117" spans="1:9" ht="12" customHeight="1">
@@ -19433,16 +19430,16 @@
       <c r="B117" s="21">
         <v>82</v>
       </c>
-      <c r="C117" s="400"/>
-      <c r="D117" s="401"/>
+      <c r="C117" s="421"/>
+      <c r="D117" s="422"/>
       <c r="E117" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F117" s="402" t="s">
+      <c r="F117" s="396" t="s">
         <v>110</v>
       </c>
-      <c r="G117" s="403"/>
-      <c r="H117" s="404"/>
+      <c r="G117" s="397"/>
+      <c r="H117" s="398"/>
       <c r="I117" s="32"/>
     </row>
     <row r="118" spans="1:9" ht="12" customHeight="1">
@@ -19461,11 +19458,11 @@
       <c r="E118" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F118" s="402" t="s">
+      <c r="F118" s="396" t="s">
         <v>111</v>
       </c>
-      <c r="G118" s="403"/>
-      <c r="H118" s="404"/>
+      <c r="G118" s="397"/>
+      <c r="H118" s="398"/>
       <c r="I118" s="32"/>
     </row>
     <row r="119" spans="1:9" hidden="1">
@@ -19478,16 +19475,16 @@
       <c r="B120" s="21">
         <v>85</v>
       </c>
-      <c r="C120" s="398" t="s">
+      <c r="C120" s="419" t="s">
         <v>112</v>
       </c>
-      <c r="D120" s="399"/>
-      <c r="E120" s="395" t="s">
+      <c r="D120" s="420"/>
+      <c r="E120" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F120" s="396"/>
-      <c r="G120" s="396"/>
-      <c r="H120" s="397"/>
+      <c r="F120" s="394"/>
+      <c r="G120" s="394"/>
+      <c r="H120" s="395"/>
       <c r="I120" s="32"/>
     </row>
     <row r="121" spans="1:9" ht="12" customHeight="1">
@@ -19497,16 +19494,16 @@
       <c r="B121" s="21">
         <v>86</v>
       </c>
-      <c r="C121" s="400"/>
-      <c r="D121" s="401"/>
+      <c r="C121" s="421"/>
+      <c r="D121" s="422"/>
       <c r="E121" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F121" s="402" t="s">
+      <c r="F121" s="396" t="s">
         <v>113</v>
       </c>
-      <c r="G121" s="403"/>
-      <c r="H121" s="404"/>
+      <c r="G121" s="397"/>
+      <c r="H121" s="398"/>
       <c r="I121" s="32"/>
     </row>
     <row r="122" spans="1:9" ht="12" customHeight="1">
@@ -19525,11 +19522,11 @@
       <c r="E122" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F122" s="402" t="s">
+      <c r="F122" s="396" t="s">
         <v>111</v>
       </c>
-      <c r="G122" s="403"/>
-      <c r="H122" s="404"/>
+      <c r="G122" s="397"/>
+      <c r="H122" s="398"/>
       <c r="I122" s="32"/>
     </row>
     <row r="123" spans="1:9" ht="12" customHeight="1">
@@ -19548,11 +19545,11 @@
       <c r="E123" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F123" s="402" t="s">
+      <c r="F123" s="396" t="s">
         <v>114</v>
       </c>
-      <c r="G123" s="403"/>
-      <c r="H123" s="404"/>
+      <c r="G123" s="397"/>
+      <c r="H123" s="398"/>
       <c r="I123" s="32"/>
     </row>
     <row r="124" spans="1:9" ht="12" customHeight="1">
@@ -19571,11 +19568,11 @@
       <c r="E124" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F124" s="402" t="s">
+      <c r="F124" s="396" t="s">
         <v>115</v>
       </c>
-      <c r="G124" s="403"/>
-      <c r="H124" s="404"/>
+      <c r="G124" s="397"/>
+      <c r="H124" s="398"/>
       <c r="I124" s="32"/>
     </row>
     <row r="125" spans="1:9" hidden="1">
@@ -19588,14 +19585,14 @@
       <c r="B126" s="21">
         <v>91</v>
       </c>
-      <c r="C126" s="395" t="s">
+      <c r="C126" s="393" t="s">
         <v>116</v>
       </c>
-      <c r="D126" s="396"/>
-      <c r="E126" s="396"/>
-      <c r="F126" s="396"/>
-      <c r="G126" s="396"/>
-      <c r="H126" s="397"/>
+      <c r="D126" s="394"/>
+      <c r="E126" s="394"/>
+      <c r="F126" s="394"/>
+      <c r="G126" s="394"/>
+      <c r="H126" s="395"/>
       <c r="I126" s="32"/>
     </row>
     <row r="127" spans="1:9" ht="12" customHeight="1">
@@ -19605,16 +19602,16 @@
       <c r="B127" s="21">
         <v>92</v>
       </c>
-      <c r="C127" s="398" t="s">
+      <c r="C127" s="419" t="s">
         <v>117</v>
       </c>
-      <c r="D127" s="399"/>
-      <c r="E127" s="395" t="s">
+      <c r="D127" s="420"/>
+      <c r="E127" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F127" s="396"/>
-      <c r="G127" s="396"/>
-      <c r="H127" s="397"/>
+      <c r="F127" s="394"/>
+      <c r="G127" s="394"/>
+      <c r="H127" s="395"/>
       <c r="I127" s="32"/>
     </row>
     <row r="128" spans="1:9" ht="12" customHeight="1">
@@ -19624,16 +19621,16 @@
       <c r="B128" s="21">
         <v>93</v>
       </c>
-      <c r="C128" s="400"/>
-      <c r="D128" s="401"/>
+      <c r="C128" s="421"/>
+      <c r="D128" s="422"/>
       <c r="E128" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F128" s="405" t="s">
-        <v>44</v>
-      </c>
-      <c r="G128" s="406"/>
-      <c r="H128" s="407"/>
+      <c r="F128" s="444" t="s">
+        <v>44</v>
+      </c>
+      <c r="G128" s="445"/>
+      <c r="H128" s="446"/>
       <c r="I128" s="40"/>
     </row>
     <row r="129" spans="1:14" hidden="1">
@@ -19646,14 +19643,14 @@
       <c r="B130" s="21">
         <v>95</v>
       </c>
-      <c r="C130" s="395" t="s">
+      <c r="C130" s="393" t="s">
         <v>118</v>
       </c>
-      <c r="D130" s="396"/>
-      <c r="E130" s="396"/>
-      <c r="F130" s="396"/>
-      <c r="G130" s="396"/>
-      <c r="H130" s="397"/>
+      <c r="D130" s="394"/>
+      <c r="E130" s="394"/>
+      <c r="F130" s="394"/>
+      <c r="G130" s="394"/>
+      <c r="H130" s="395"/>
       <c r="I130" s="32"/>
     </row>
     <row r="131" spans="1:14" ht="12" customHeight="1">
@@ -19663,14 +19660,14 @@
       <c r="B131" s="21">
         <v>96</v>
       </c>
-      <c r="C131" s="395" t="s">
+      <c r="C131" s="393" t="s">
         <v>119</v>
       </c>
-      <c r="D131" s="396"/>
-      <c r="E131" s="396"/>
-      <c r="F131" s="396"/>
-      <c r="G131" s="396"/>
-      <c r="H131" s="397"/>
+      <c r="D131" s="394"/>
+      <c r="E131" s="394"/>
+      <c r="F131" s="394"/>
+      <c r="G131" s="394"/>
+      <c r="H131" s="395"/>
       <c r="I131" s="32"/>
     </row>
     <row r="132" spans="1:14" ht="12" customHeight="1">
@@ -19680,16 +19677,16 @@
       <c r="B132" s="21">
         <v>97</v>
       </c>
-      <c r="C132" s="398" t="s">
+      <c r="C132" s="419" t="s">
         <v>120</v>
       </c>
-      <c r="D132" s="399"/>
-      <c r="E132" s="395" t="s">
+      <c r="D132" s="420"/>
+      <c r="E132" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F132" s="396"/>
-      <c r="G132" s="396"/>
-      <c r="H132" s="397"/>
+      <c r="F132" s="394"/>
+      <c r="G132" s="394"/>
+      <c r="H132" s="395"/>
       <c r="I132" s="32"/>
     </row>
     <row r="133" spans="1:14" ht="12" customHeight="1">
@@ -19699,16 +19696,16 @@
       <c r="B133" s="21">
         <v>98</v>
       </c>
-      <c r="C133" s="400"/>
-      <c r="D133" s="401"/>
+      <c r="C133" s="421"/>
+      <c r="D133" s="422"/>
       <c r="E133" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F133" s="402" t="s">
+      <c r="F133" s="396" t="s">
         <v>121</v>
       </c>
-      <c r="G133" s="403"/>
-      <c r="H133" s="404"/>
+      <c r="G133" s="397"/>
+      <c r="H133" s="398"/>
       <c r="I133" s="32"/>
     </row>
     <row r="134" spans="1:14" ht="12" customHeight="1">
@@ -19718,16 +19715,16 @@
       <c r="B134" s="21">
         <v>99</v>
       </c>
-      <c r="C134" s="400"/>
-      <c r="D134" s="401"/>
+      <c r="C134" s="421"/>
+      <c r="D134" s="422"/>
       <c r="E134" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F134" s="402" t="s">
+      <c r="F134" s="396" t="s">
         <v>122</v>
       </c>
-      <c r="G134" s="403"/>
-      <c r="H134" s="404"/>
+      <c r="G134" s="397"/>
+      <c r="H134" s="398"/>
       <c r="I134" s="32"/>
     </row>
     <row r="135" spans="1:14" ht="12" customHeight="1">
@@ -19737,16 +19734,16 @@
       <c r="B135" s="21">
         <v>100</v>
       </c>
-      <c r="C135" s="400"/>
-      <c r="D135" s="401"/>
+      <c r="C135" s="421"/>
+      <c r="D135" s="422"/>
       <c r="E135" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F135" s="402" t="s">
+      <c r="F135" s="396" t="s">
         <v>123</v>
       </c>
-      <c r="G135" s="403"/>
-      <c r="H135" s="404"/>
+      <c r="G135" s="397"/>
+      <c r="H135" s="398"/>
       <c r="I135" s="32"/>
     </row>
     <row r="136" spans="1:14" ht="12" customHeight="1">
@@ -19765,11 +19762,11 @@
       <c r="E136" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F136" s="402" t="s">
+      <c r="F136" s="396" t="s">
         <v>124</v>
       </c>
-      <c r="G136" s="403"/>
-      <c r="H136" s="404"/>
+      <c r="G136" s="397"/>
+      <c r="H136" s="398"/>
       <c r="I136" s="32"/>
     </row>
     <row r="137" spans="1:14" ht="12" customHeight="1">
@@ -19788,11 +19785,11 @@
       <c r="E137" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F137" s="402" t="s">
+      <c r="F137" s="396" t="s">
         <v>125</v>
       </c>
-      <c r="G137" s="403"/>
-      <c r="H137" s="404"/>
+      <c r="G137" s="397"/>
+      <c r="H137" s="398"/>
       <c r="I137" s="32"/>
     </row>
     <row r="138" spans="1:14" ht="12" customHeight="1">
@@ -19811,11 +19808,11 @@
       <c r="E138" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F138" s="402" t="s">
+      <c r="F138" s="396" t="s">
         <v>126</v>
       </c>
-      <c r="G138" s="403"/>
-      <c r="H138" s="404"/>
+      <c r="G138" s="397"/>
+      <c r="H138" s="398"/>
       <c r="I138" s="32"/>
     </row>
     <row r="139" spans="1:14" hidden="1">
@@ -19828,16 +19825,16 @@
       <c r="B140" s="21">
         <v>105</v>
       </c>
-      <c r="C140" s="408" t="s">
+      <c r="C140" s="423" t="s">
         <v>127</v>
       </c>
-      <c r="D140" s="409"/>
-      <c r="E140" s="395" t="s">
+      <c r="D140" s="424"/>
+      <c r="E140" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F140" s="396"/>
-      <c r="G140" s="396"/>
-      <c r="H140" s="397"/>
+      <c r="F140" s="394"/>
+      <c r="G140" s="394"/>
+      <c r="H140" s="395"/>
       <c r="I140" s="32"/>
     </row>
     <row r="141" spans="1:14" ht="12" customHeight="1">
@@ -19847,16 +19844,16 @@
       <c r="B141" s="21">
         <v>106</v>
       </c>
-      <c r="C141" s="410"/>
-      <c r="D141" s="411"/>
-      <c r="E141" s="414" t="s">
+      <c r="C141" s="425"/>
+      <c r="D141" s="426"/>
+      <c r="E141" s="429" t="s">
         <v>55</v>
       </c>
-      <c r="F141" s="402" t="s">
+      <c r="F141" s="396" t="s">
         <v>128</v>
       </c>
-      <c r="G141" s="403"/>
-      <c r="H141" s="404"/>
+      <c r="G141" s="397"/>
+      <c r="H141" s="398"/>
       <c r="I141" s="32" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -19869,14 +19866,14 @@
       <c r="B142" s="21">
         <v>107</v>
       </c>
-      <c r="C142" s="412"/>
-      <c r="D142" s="413"/>
-      <c r="E142" s="415"/>
-      <c r="F142" s="402" t="s">
+      <c r="C142" s="427"/>
+      <c r="D142" s="428"/>
+      <c r="E142" s="430"/>
+      <c r="F142" s="396" t="s">
         <v>129</v>
       </c>
-      <c r="G142" s="403"/>
-      <c r="H142" s="404"/>
+      <c r="G142" s="397"/>
+      <c r="H142" s="398"/>
       <c r="I142" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19890,14 +19887,14 @@
       <c r="B143" s="21">
         <v>108</v>
       </c>
-      <c r="C143" s="395" t="s">
+      <c r="C143" s="393" t="s">
         <v>22</v>
       </c>
-      <c r="D143" s="396"/>
-      <c r="E143" s="396"/>
-      <c r="F143" s="396"/>
-      <c r="G143" s="396"/>
-      <c r="H143" s="397"/>
+      <c r="D143" s="394"/>
+      <c r="E143" s="394"/>
+      <c r="F143" s="394"/>
+      <c r="G143" s="394"/>
+      <c r="H143" s="395"/>
       <c r="I143" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19917,12 +19914,12 @@
       <c r="D144" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="E144" s="395" t="s">
+      <c r="E144" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F144" s="396"/>
-      <c r="G144" s="396"/>
-      <c r="H144" s="397"/>
+      <c r="F144" s="394"/>
+      <c r="G144" s="394"/>
+      <c r="H144" s="395"/>
       <c r="I144" s="32"/>
     </row>
     <row r="145" spans="1:10" ht="12" customHeight="1">
@@ -19941,11 +19938,11 @@
       <c r="E145" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F145" s="402" t="s">
+      <c r="F145" s="396" t="s">
         <v>131</v>
       </c>
-      <c r="G145" s="403"/>
-      <c r="H145" s="404"/>
+      <c r="G145" s="397"/>
+      <c r="H145" s="398"/>
       <c r="I145" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19967,11 +19964,11 @@
       <c r="E146" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F146" s="402" t="s">
+      <c r="F146" s="396" t="s">
         <v>132</v>
       </c>
-      <c r="G146" s="403"/>
-      <c r="H146" s="404"/>
+      <c r="G146" s="397"/>
+      <c r="H146" s="398"/>
       <c r="I146" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19993,11 +19990,11 @@
       <c r="E147" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F147" s="402" t="s">
+      <c r="F147" s="396" t="s">
         <v>64</v>
       </c>
-      <c r="G147" s="403"/>
-      <c r="H147" s="404"/>
+      <c r="G147" s="397"/>
+      <c r="H147" s="398"/>
       <c r="I147" s="32"/>
     </row>
     <row r="148" spans="1:10" ht="12" customHeight="1">
@@ -20016,11 +20013,11 @@
       <c r="E148" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F148" s="392" t="s">
+      <c r="F148" s="416" t="s">
         <v>133</v>
       </c>
-      <c r="G148" s="393"/>
-      <c r="H148" s="394"/>
+      <c r="G148" s="417"/>
+      <c r="H148" s="418"/>
       <c r="I148" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20043,11 +20040,11 @@
       <c r="E149" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F149" s="392" t="s">
+      <c r="F149" s="416" t="s">
         <v>134</v>
       </c>
-      <c r="G149" s="393"/>
-      <c r="H149" s="394"/>
+      <c r="G149" s="417"/>
+      <c r="H149" s="418"/>
       <c r="I149" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20070,11 +20067,11 @@
       <c r="E150" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F150" s="392" t="s">
+      <c r="F150" s="416" t="s">
         <v>135</v>
       </c>
-      <c r="G150" s="393"/>
-      <c r="H150" s="394"/>
+      <c r="G150" s="417"/>
+      <c r="H150" s="418"/>
       <c r="I150" s="32"/>
       <c r="J150" s="10"/>
     </row>
@@ -20094,11 +20091,11 @@
       <c r="E151" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F151" s="392" t="s">
+      <c r="F151" s="416" t="s">
         <v>136</v>
       </c>
-      <c r="G151" s="393"/>
-      <c r="H151" s="394"/>
+      <c r="G151" s="417"/>
+      <c r="H151" s="418"/>
       <c r="I151" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20115,16 +20112,16 @@
       <c r="B153" s="21">
         <v>114</v>
       </c>
-      <c r="C153" s="398" t="s">
+      <c r="C153" s="419" t="s">
         <v>137</v>
       </c>
-      <c r="D153" s="399"/>
-      <c r="E153" s="395" t="s">
+      <c r="D153" s="420"/>
+      <c r="E153" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F153" s="396"/>
-      <c r="G153" s="396"/>
-      <c r="H153" s="397"/>
+      <c r="F153" s="394"/>
+      <c r="G153" s="394"/>
+      <c r="H153" s="395"/>
       <c r="I153" s="32"/>
     </row>
     <row r="154" spans="1:10" ht="12" customHeight="1">
@@ -20134,16 +20131,16 @@
       <c r="B154" s="21">
         <v>115</v>
       </c>
-      <c r="C154" s="400"/>
-      <c r="D154" s="401"/>
+      <c r="C154" s="421"/>
+      <c r="D154" s="422"/>
       <c r="E154" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F154" s="405" t="s">
-        <v>44</v>
-      </c>
-      <c r="G154" s="406"/>
-      <c r="H154" s="407"/>
+      <c r="F154" s="444" t="s">
+        <v>44</v>
+      </c>
+      <c r="G154" s="445"/>
+      <c r="H154" s="446"/>
       <c r="I154" s="40"/>
     </row>
     <row r="155" spans="1:10" ht="12" customHeight="1">
@@ -20162,11 +20159,11 @@
       <c r="E155" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F155" s="392" t="s">
+      <c r="F155" s="416" t="s">
         <v>4</v>
       </c>
-      <c r="G155" s="393"/>
-      <c r="H155" s="394"/>
+      <c r="G155" s="417"/>
+      <c r="H155" s="418"/>
       <c r="I155" s="32"/>
       <c r="J155" s="10"/>
     </row>
@@ -20186,11 +20183,11 @@
       <c r="E156" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F156" s="392" t="s">
+      <c r="F156" s="416" t="s">
         <v>138</v>
       </c>
-      <c r="G156" s="393"/>
-      <c r="H156" s="394"/>
+      <c r="G156" s="417"/>
+      <c r="H156" s="418"/>
       <c r="I156" s="32"/>
       <c r="J156" s="10"/>
     </row>
@@ -20210,11 +20207,11 @@
       <c r="E157" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F157" s="392" t="s">
+      <c r="F157" s="416" t="s">
         <v>139</v>
       </c>
-      <c r="G157" s="393"/>
-      <c r="H157" s="394"/>
+      <c r="G157" s="417"/>
+      <c r="H157" s="418"/>
       <c r="I157" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20237,9 +20234,9 @@
       <c r="E158" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F158" s="392"/>
-      <c r="G158" s="393"/>
-      <c r="H158" s="394"/>
+      <c r="F158" s="416"/>
+      <c r="G158" s="417"/>
+      <c r="H158" s="418"/>
       <c r="I158" s="32"/>
       <c r="J158" s="10"/>
     </row>
@@ -20253,14 +20250,14 @@
       <c r="B160" s="21">
         <v>117</v>
       </c>
-      <c r="C160" s="395" t="s">
+      <c r="C160" s="393" t="s">
         <v>140</v>
       </c>
-      <c r="D160" s="396"/>
-      <c r="E160" s="396"/>
-      <c r="F160" s="396"/>
-      <c r="G160" s="396"/>
-      <c r="H160" s="397"/>
+      <c r="D160" s="394"/>
+      <c r="E160" s="394"/>
+      <c r="F160" s="394"/>
+      <c r="G160" s="394"/>
+      <c r="H160" s="395"/>
       <c r="I160" s="32"/>
     </row>
     <row r="161" spans="1:9" ht="12" customHeight="1">
@@ -20270,14 +20267,14 @@
       <c r="B161" s="21">
         <v>118</v>
       </c>
-      <c r="C161" s="395" t="s">
+      <c r="C161" s="393" t="s">
         <v>141</v>
       </c>
-      <c r="D161" s="396"/>
-      <c r="E161" s="396"/>
-      <c r="F161" s="396"/>
-      <c r="G161" s="396"/>
-      <c r="H161" s="397"/>
+      <c r="D161" s="394"/>
+      <c r="E161" s="394"/>
+      <c r="F161" s="394"/>
+      <c r="G161" s="394"/>
+      <c r="H161" s="395"/>
       <c r="I161" s="42" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -20290,14 +20287,14 @@
       <c r="B162" s="21">
         <v>119</v>
       </c>
-      <c r="C162" s="395" t="s">
+      <c r="C162" s="393" t="s">
         <v>142</v>
       </c>
-      <c r="D162" s="396"/>
-      <c r="E162" s="396"/>
-      <c r="F162" s="396"/>
-      <c r="G162" s="396"/>
-      <c r="H162" s="397"/>
+      <c r="D162" s="394"/>
+      <c r="E162" s="394"/>
+      <c r="F162" s="394"/>
+      <c r="G162" s="394"/>
+      <c r="H162" s="395"/>
       <c r="I162" s="32"/>
     </row>
     <row r="163" spans="1:9" ht="12" customHeight="1">
@@ -20307,14 +20304,14 @@
       <c r="B163" s="21">
         <v>120</v>
       </c>
-      <c r="C163" s="395" t="s">
+      <c r="C163" s="393" t="s">
         <v>143</v>
       </c>
-      <c r="D163" s="396"/>
-      <c r="E163" s="396"/>
-      <c r="F163" s="396"/>
-      <c r="G163" s="396"/>
-      <c r="H163" s="397"/>
+      <c r="D163" s="394"/>
+      <c r="E163" s="394"/>
+      <c r="F163" s="394"/>
+      <c r="G163" s="394"/>
+      <c r="H163" s="395"/>
       <c r="I163" s="32"/>
     </row>
     <row r="164" spans="1:9" ht="12" customHeight="1">
@@ -20324,14 +20321,14 @@
       <c r="B164" s="21">
         <v>121</v>
       </c>
-      <c r="C164" s="395" t="s">
+      <c r="C164" s="393" t="s">
         <v>144</v>
       </c>
-      <c r="D164" s="396"/>
-      <c r="E164" s="396"/>
-      <c r="F164" s="396"/>
-      <c r="G164" s="396"/>
-      <c r="H164" s="397"/>
+      <c r="D164" s="394"/>
+      <c r="E164" s="394"/>
+      <c r="F164" s="394"/>
+      <c r="G164" s="394"/>
+      <c r="H164" s="395"/>
       <c r="I164" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20344,16 +20341,16 @@
       <c r="B165" s="21">
         <v>122</v>
       </c>
-      <c r="C165" s="398" t="s">
+      <c r="C165" s="419" t="s">
         <v>145</v>
       </c>
-      <c r="D165" s="399"/>
-      <c r="E165" s="395" t="s">
+      <c r="D165" s="420"/>
+      <c r="E165" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F165" s="396"/>
-      <c r="G165" s="396"/>
-      <c r="H165" s="397"/>
+      <c r="F165" s="394"/>
+      <c r="G165" s="394"/>
+      <c r="H165" s="395"/>
       <c r="I165" s="32"/>
     </row>
     <row r="166" spans="1:9" ht="12" customHeight="1">
@@ -20363,16 +20360,16 @@
       <c r="B166" s="21">
         <v>123</v>
       </c>
-      <c r="C166" s="400"/>
-      <c r="D166" s="401"/>
+      <c r="C166" s="421"/>
+      <c r="D166" s="422"/>
       <c r="E166" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F166" s="402" t="s">
+      <c r="F166" s="396" t="s">
         <v>146</v>
       </c>
-      <c r="G166" s="403"/>
-      <c r="H166" s="404"/>
+      <c r="G166" s="397"/>
+      <c r="H166" s="398"/>
       <c r="I166" s="32"/>
     </row>
     <row r="167" spans="1:9" ht="12" customHeight="1">
@@ -20391,11 +20388,11 @@
       <c r="E167" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F167" s="402" t="s">
+      <c r="F167" s="396" t="s">
         <v>147</v>
       </c>
-      <c r="G167" s="403"/>
-      <c r="H167" s="404"/>
+      <c r="G167" s="397"/>
+      <c r="H167" s="398"/>
       <c r="I167" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20417,11 +20414,11 @@
       <c r="E168" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F168" s="402" t="s">
+      <c r="F168" s="396" t="s">
         <v>148</v>
       </c>
-      <c r="G168" s="403"/>
-      <c r="H168" s="404"/>
+      <c r="G168" s="397"/>
+      <c r="H168" s="398"/>
       <c r="I168" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20437,14 +20434,14 @@
       <c r="B170" s="21">
         <v>127</v>
       </c>
-      <c r="C170" s="395" t="s">
+      <c r="C170" s="393" t="s">
         <v>17</v>
       </c>
-      <c r="D170" s="396"/>
-      <c r="E170" s="396"/>
-      <c r="F170" s="396"/>
-      <c r="G170" s="396"/>
-      <c r="H170" s="397"/>
+      <c r="D170" s="394"/>
+      <c r="E170" s="394"/>
+      <c r="F170" s="394"/>
+      <c r="G170" s="394"/>
+      <c r="H170" s="395"/>
       <c r="I170" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20457,14 +20454,14 @@
       <c r="B171" s="21">
         <v>128</v>
       </c>
-      <c r="C171" s="395" t="s">
+      <c r="C171" s="393" t="s">
         <v>149</v>
       </c>
-      <c r="D171" s="396"/>
-      <c r="E171" s="396"/>
-      <c r="F171" s="396"/>
-      <c r="G171" s="396"/>
-      <c r="H171" s="397"/>
+      <c r="D171" s="394"/>
+      <c r="E171" s="394"/>
+      <c r="F171" s="394"/>
+      <c r="G171" s="394"/>
+      <c r="H171" s="395"/>
       <c r="I171" s="32"/>
     </row>
     <row r="172" spans="1:9" ht="12" customHeight="1">
@@ -20474,14 +20471,14 @@
       <c r="B172" s="21">
         <v>129</v>
       </c>
-      <c r="C172" s="395" t="s">
+      <c r="C172" s="393" t="s">
         <v>150</v>
       </c>
-      <c r="D172" s="396"/>
-      <c r="E172" s="396"/>
-      <c r="F172" s="396"/>
-      <c r="G172" s="396"/>
-      <c r="H172" s="397"/>
+      <c r="D172" s="394"/>
+      <c r="E172" s="394"/>
+      <c r="F172" s="394"/>
+      <c r="G172" s="394"/>
+      <c r="H172" s="395"/>
       <c r="I172" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20494,14 +20491,14 @@
       <c r="B173" s="21">
         <v>130</v>
       </c>
-      <c r="C173" s="395" t="s">
+      <c r="C173" s="393" t="s">
         <v>151</v>
       </c>
-      <c r="D173" s="396"/>
-      <c r="E173" s="396"/>
-      <c r="F173" s="396"/>
-      <c r="G173" s="396"/>
-      <c r="H173" s="397"/>
+      <c r="D173" s="394"/>
+      <c r="E173" s="394"/>
+      <c r="F173" s="394"/>
+      <c r="G173" s="394"/>
+      <c r="H173" s="395"/>
       <c r="I173" s="32"/>
     </row>
     <row r="174" spans="1:9" ht="12" customHeight="1">
@@ -20511,14 +20508,14 @@
       <c r="B174" s="21">
         <v>131</v>
       </c>
-      <c r="C174" s="395" t="s">
+      <c r="C174" s="393" t="s">
         <v>152</v>
       </c>
-      <c r="D174" s="396"/>
-      <c r="E174" s="396"/>
-      <c r="F174" s="396"/>
-      <c r="G174" s="396"/>
-      <c r="H174" s="397"/>
+      <c r="D174" s="394"/>
+      <c r="E174" s="394"/>
+      <c r="F174" s="394"/>
+      <c r="G174" s="394"/>
+      <c r="H174" s="395"/>
       <c r="I174" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20531,16 +20528,16 @@
       <c r="B175" s="21">
         <v>132</v>
       </c>
-      <c r="C175" s="398" t="s">
+      <c r="C175" s="419" t="s">
         <v>153</v>
       </c>
-      <c r="D175" s="399"/>
-      <c r="E175" s="395" t="s">
+      <c r="D175" s="420"/>
+      <c r="E175" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F175" s="396"/>
-      <c r="G175" s="396"/>
-      <c r="H175" s="397"/>
+      <c r="F175" s="394"/>
+      <c r="G175" s="394"/>
+      <c r="H175" s="395"/>
       <c r="I175" s="32"/>
     </row>
     <row r="176" spans="1:9" ht="12" customHeight="1">
@@ -20550,16 +20547,16 @@
       <c r="B176" s="21">
         <v>133</v>
       </c>
-      <c r="C176" s="400"/>
-      <c r="D176" s="401"/>
+      <c r="C176" s="421"/>
+      <c r="D176" s="422"/>
       <c r="E176" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F176" s="402" t="s">
+      <c r="F176" s="396" t="s">
         <v>128</v>
       </c>
-      <c r="G176" s="403"/>
-      <c r="H176" s="404"/>
+      <c r="G176" s="397"/>
+      <c r="H176" s="398"/>
       <c r="I176" s="32"/>
     </row>
     <row r="177" spans="1:14" ht="12" customHeight="1">
@@ -20569,16 +20566,16 @@
       <c r="B177" s="21">
         <v>134</v>
       </c>
-      <c r="C177" s="400"/>
-      <c r="D177" s="401"/>
+      <c r="C177" s="421"/>
+      <c r="D177" s="422"/>
       <c r="E177" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F177" s="402" t="s">
+      <c r="F177" s="396" t="s">
         <v>154</v>
       </c>
-      <c r="G177" s="403"/>
-      <c r="H177" s="404"/>
+      <c r="G177" s="397"/>
+      <c r="H177" s="398"/>
       <c r="I177" s="32"/>
     </row>
     <row r="178" spans="1:14" ht="12" customHeight="1">
@@ -20597,11 +20594,11 @@
       <c r="E178" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F178" s="402" t="s">
+      <c r="F178" s="396" t="s">
         <v>155</v>
       </c>
-      <c r="G178" s="403"/>
-      <c r="H178" s="404"/>
+      <c r="G178" s="397"/>
+      <c r="H178" s="398"/>
       <c r="I178" s="32"/>
     </row>
     <row r="179" spans="1:14" hidden="1">
@@ -20614,14 +20611,14 @@
       <c r="B180" s="21">
         <v>137</v>
       </c>
-      <c r="C180" s="395" t="s">
+      <c r="C180" s="393" t="s">
         <v>156</v>
       </c>
-      <c r="D180" s="396"/>
-      <c r="E180" s="396"/>
-      <c r="F180" s="396"/>
-      <c r="G180" s="396"/>
-      <c r="H180" s="397"/>
+      <c r="D180" s="394"/>
+      <c r="E180" s="394"/>
+      <c r="F180" s="394"/>
+      <c r="G180" s="394"/>
+      <c r="H180" s="395"/>
       <c r="I180" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20634,14 +20631,14 @@
       <c r="B181" s="21">
         <v>138</v>
       </c>
-      <c r="C181" s="395" t="s">
+      <c r="C181" s="393" t="s">
         <v>21</v>
       </c>
-      <c r="D181" s="396"/>
-      <c r="E181" s="396"/>
-      <c r="F181" s="396"/>
-      <c r="G181" s="396"/>
-      <c r="H181" s="397"/>
+      <c r="D181" s="394"/>
+      <c r="E181" s="394"/>
+      <c r="F181" s="394"/>
+      <c r="G181" s="394"/>
+      <c r="H181" s="395"/>
       <c r="I181" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20654,16 +20651,16 @@
       <c r="B182" s="21">
         <v>139</v>
       </c>
-      <c r="C182" s="398" t="s">
+      <c r="C182" s="419" t="s">
         <v>157</v>
       </c>
-      <c r="D182" s="399"/>
-      <c r="E182" s="395" t="s">
+      <c r="D182" s="420"/>
+      <c r="E182" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F182" s="396"/>
-      <c r="G182" s="396"/>
-      <c r="H182" s="397"/>
+      <c r="F182" s="394"/>
+      <c r="G182" s="394"/>
+      <c r="H182" s="395"/>
       <c r="I182" s="32"/>
     </row>
     <row r="183" spans="1:14" ht="12" customHeight="1">
@@ -20673,16 +20670,16 @@
       <c r="B183" s="21">
         <v>140</v>
       </c>
-      <c r="C183" s="400"/>
-      <c r="D183" s="401"/>
+      <c r="C183" s="421"/>
+      <c r="D183" s="422"/>
       <c r="E183" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F183" s="402" t="s">
-        <v>44</v>
-      </c>
-      <c r="G183" s="403"/>
-      <c r="H183" s="404"/>
+      <c r="F183" s="396" t="s">
+        <v>44</v>
+      </c>
+      <c r="G183" s="397"/>
+      <c r="H183" s="398"/>
       <c r="I183" s="32"/>
     </row>
     <row r="184" spans="1:14" hidden="1">
@@ -20695,16 +20692,16 @@
       <c r="B185" s="21">
         <v>142</v>
       </c>
-      <c r="C185" s="398" t="s">
+      <c r="C185" s="419" t="s">
         <v>158</v>
       </c>
-      <c r="D185" s="399"/>
-      <c r="E185" s="395" t="s">
+      <c r="D185" s="420"/>
+      <c r="E185" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F185" s="396"/>
-      <c r="G185" s="396"/>
-      <c r="H185" s="397"/>
+      <c r="F185" s="394"/>
+      <c r="G185" s="394"/>
+      <c r="H185" s="395"/>
       <c r="I185" s="32"/>
     </row>
     <row r="186" spans="1:14" ht="12" customHeight="1">
@@ -20714,16 +20711,16 @@
       <c r="B186" s="21">
         <v>143</v>
       </c>
-      <c r="C186" s="400"/>
-      <c r="D186" s="401"/>
+      <c r="C186" s="421"/>
+      <c r="D186" s="422"/>
       <c r="E186" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F186" s="402" t="s">
+      <c r="F186" s="396" t="s">
         <v>159</v>
       </c>
-      <c r="G186" s="403"/>
-      <c r="H186" s="404"/>
+      <c r="G186" s="397"/>
+      <c r="H186" s="398"/>
       <c r="I186" s="32"/>
     </row>
     <row r="187" spans="1:14" ht="12" customHeight="1">
@@ -20733,16 +20730,16 @@
       <c r="B187" s="21">
         <v>144</v>
       </c>
-      <c r="C187" s="400"/>
-      <c r="D187" s="401"/>
+      <c r="C187" s="421"/>
+      <c r="D187" s="422"/>
       <c r="E187" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F187" s="402" t="s">
+      <c r="F187" s="396" t="s">
         <v>160</v>
       </c>
-      <c r="G187" s="403"/>
-      <c r="H187" s="404"/>
+      <c r="G187" s="397"/>
+      <c r="H187" s="398"/>
       <c r="I187" s="32"/>
     </row>
     <row r="188" spans="1:14" ht="12" customHeight="1">
@@ -20761,11 +20758,11 @@
       <c r="E188" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F188" s="392" t="s">
+      <c r="F188" s="416" t="s">
         <v>161</v>
       </c>
-      <c r="G188" s="393"/>
-      <c r="H188" s="394"/>
+      <c r="G188" s="417"/>
+      <c r="H188" s="418"/>
       <c r="I188" s="32"/>
       <c r="J188" s="10"/>
     </row>
@@ -20785,11 +20782,11 @@
       <c r="E189" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F189" s="392" t="s">
+      <c r="F189" s="416" t="s">
         <v>162</v>
       </c>
-      <c r="G189" s="393"/>
-      <c r="H189" s="394"/>
+      <c r="G189" s="417"/>
+      <c r="H189" s="418"/>
       <c r="I189" s="32"/>
       <c r="J189" s="10"/>
     </row>
@@ -20809,11 +20806,11 @@
       <c r="E190" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="F190" s="392" t="s">
+      <c r="F190" s="416" t="s">
         <v>163</v>
       </c>
-      <c r="G190" s="393"/>
-      <c r="H190" s="394"/>
+      <c r="G190" s="417"/>
+      <c r="H190" s="418"/>
       <c r="I190" s="32" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -20876,6 +20873,161 @@
     </row>
   </sheetData>
   <mergeCells count="169">
+    <mergeCell ref="F188:H188"/>
+    <mergeCell ref="F189:H189"/>
+    <mergeCell ref="F190:H190"/>
+    <mergeCell ref="C180:H180"/>
+    <mergeCell ref="C181:H181"/>
+    <mergeCell ref="C182:D183"/>
+    <mergeCell ref="E182:H182"/>
+    <mergeCell ref="F183:H183"/>
+    <mergeCell ref="C185:D187"/>
+    <mergeCell ref="E185:H185"/>
+    <mergeCell ref="F186:H186"/>
+    <mergeCell ref="F187:H187"/>
+    <mergeCell ref="C174:H174"/>
+    <mergeCell ref="C175:D177"/>
+    <mergeCell ref="E175:H175"/>
+    <mergeCell ref="F176:H176"/>
+    <mergeCell ref="F177:H177"/>
+    <mergeCell ref="F178:H178"/>
+    <mergeCell ref="F167:H167"/>
+    <mergeCell ref="F168:H168"/>
+    <mergeCell ref="C170:H170"/>
+    <mergeCell ref="C171:H171"/>
+    <mergeCell ref="C172:H172"/>
+    <mergeCell ref="C173:H173"/>
+    <mergeCell ref="C162:H162"/>
+    <mergeCell ref="C163:H163"/>
+    <mergeCell ref="C164:H164"/>
+    <mergeCell ref="C165:D166"/>
+    <mergeCell ref="E165:H165"/>
+    <mergeCell ref="F166:H166"/>
+    <mergeCell ref="F155:H155"/>
+    <mergeCell ref="F156:H156"/>
+    <mergeCell ref="F157:H157"/>
+    <mergeCell ref="F158:H158"/>
+    <mergeCell ref="C160:H160"/>
+    <mergeCell ref="C161:H161"/>
+    <mergeCell ref="F149:H149"/>
+    <mergeCell ref="F150:H150"/>
+    <mergeCell ref="F151:H151"/>
+    <mergeCell ref="C153:D154"/>
+    <mergeCell ref="E153:H153"/>
+    <mergeCell ref="F154:H154"/>
+    <mergeCell ref="C143:H143"/>
+    <mergeCell ref="E144:H144"/>
+    <mergeCell ref="F145:H145"/>
+    <mergeCell ref="F146:H146"/>
+    <mergeCell ref="F147:H147"/>
+    <mergeCell ref="F148:H148"/>
+    <mergeCell ref="F137:H137"/>
+    <mergeCell ref="F138:H138"/>
+    <mergeCell ref="C140:D142"/>
+    <mergeCell ref="E140:H140"/>
+    <mergeCell ref="E141:E142"/>
+    <mergeCell ref="F141:H141"/>
+    <mergeCell ref="F142:H142"/>
+    <mergeCell ref="C132:D135"/>
+    <mergeCell ref="E132:H132"/>
+    <mergeCell ref="F133:H133"/>
+    <mergeCell ref="F134:H134"/>
+    <mergeCell ref="F135:H135"/>
+    <mergeCell ref="F136:H136"/>
+    <mergeCell ref="C126:H126"/>
+    <mergeCell ref="C127:D128"/>
+    <mergeCell ref="E127:H127"/>
+    <mergeCell ref="F128:H128"/>
+    <mergeCell ref="C130:H130"/>
+    <mergeCell ref="C131:H131"/>
+    <mergeCell ref="C120:D121"/>
+    <mergeCell ref="E120:H120"/>
+    <mergeCell ref="F121:H121"/>
+    <mergeCell ref="F122:H122"/>
+    <mergeCell ref="F123:H123"/>
+    <mergeCell ref="F124:H124"/>
+    <mergeCell ref="F114:H114"/>
+    <mergeCell ref="C115:H115"/>
+    <mergeCell ref="C116:D117"/>
+    <mergeCell ref="E116:H116"/>
+    <mergeCell ref="F117:H117"/>
+    <mergeCell ref="F118:H118"/>
+    <mergeCell ref="F108:H108"/>
+    <mergeCell ref="F109:H109"/>
+    <mergeCell ref="F110:H110"/>
+    <mergeCell ref="C112:D112"/>
+    <mergeCell ref="E112:H112"/>
+    <mergeCell ref="F113:H113"/>
+    <mergeCell ref="F101:H101"/>
+    <mergeCell ref="F102:H102"/>
+    <mergeCell ref="C104:H104"/>
+    <mergeCell ref="C105:H105"/>
+    <mergeCell ref="C106:D107"/>
+    <mergeCell ref="E106:H106"/>
+    <mergeCell ref="F107:H107"/>
+    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="E96:H96"/>
+    <mergeCell ref="F97:H97"/>
+    <mergeCell ref="F98:H98"/>
+    <mergeCell ref="F99:H99"/>
+    <mergeCell ref="F100:H100"/>
+    <mergeCell ref="F88:H88"/>
+    <mergeCell ref="F89:H89"/>
+    <mergeCell ref="F90:H90"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="E92:H92"/>
+    <mergeCell ref="E93:E94"/>
+    <mergeCell ref="F93:H93"/>
+    <mergeCell ref="F94:H94"/>
+    <mergeCell ref="F82:F84"/>
+    <mergeCell ref="G82:H82"/>
+    <mergeCell ref="G83:G84"/>
+    <mergeCell ref="F85:H85"/>
+    <mergeCell ref="F86:H86"/>
+    <mergeCell ref="F87:H87"/>
+    <mergeCell ref="G74:H74"/>
+    <mergeCell ref="C78:D79"/>
+    <mergeCell ref="E78:H78"/>
+    <mergeCell ref="F79:H79"/>
+    <mergeCell ref="F80:H80"/>
+    <mergeCell ref="F81:H81"/>
+    <mergeCell ref="C60:H60"/>
+    <mergeCell ref="C61:D63"/>
+    <mergeCell ref="E61:H61"/>
+    <mergeCell ref="G62:H62"/>
+    <mergeCell ref="G66:H66"/>
+    <mergeCell ref="G70:H70"/>
+    <mergeCell ref="C54:D57"/>
+    <mergeCell ref="E54:H54"/>
+    <mergeCell ref="F55:H55"/>
+    <mergeCell ref="F56:H56"/>
+    <mergeCell ref="F57:H57"/>
+    <mergeCell ref="F58:H58"/>
+    <mergeCell ref="F48:H48"/>
+    <mergeCell ref="F49:H49"/>
+    <mergeCell ref="C50:D51"/>
+    <mergeCell ref="E50:H50"/>
+    <mergeCell ref="F51:H51"/>
+    <mergeCell ref="F52:H52"/>
+    <mergeCell ref="C40:D41"/>
+    <mergeCell ref="E40:H40"/>
+    <mergeCell ref="F41:H41"/>
+    <mergeCell ref="F42:H42"/>
+    <mergeCell ref="C44:H44"/>
+    <mergeCell ref="C45:D49"/>
+    <mergeCell ref="E45:H45"/>
+    <mergeCell ref="E46:E49"/>
+    <mergeCell ref="F46:H46"/>
+    <mergeCell ref="F47:H47"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="C34:D35"/>
+    <mergeCell ref="E34:H34"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="C37:D39"/>
+    <mergeCell ref="E37:H37"/>
+    <mergeCell ref="E38:E39"/>
+    <mergeCell ref="F38:H38"/>
+    <mergeCell ref="F39:H39"/>
     <mergeCell ref="C26:D26"/>
     <mergeCell ref="C27:H27"/>
     <mergeCell ref="E28:H28"/>
@@ -20890,161 +21042,6 @@
     <mergeCell ref="B20:B22"/>
     <mergeCell ref="C20:H22"/>
     <mergeCell ref="I20:I22"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="C34:D35"/>
-    <mergeCell ref="E34:H34"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="C37:D39"/>
-    <mergeCell ref="E37:H37"/>
-    <mergeCell ref="E38:E39"/>
-    <mergeCell ref="F38:H38"/>
-    <mergeCell ref="F39:H39"/>
-    <mergeCell ref="C40:D41"/>
-    <mergeCell ref="E40:H40"/>
-    <mergeCell ref="F41:H41"/>
-    <mergeCell ref="F42:H42"/>
-    <mergeCell ref="C44:H44"/>
-    <mergeCell ref="C45:D49"/>
-    <mergeCell ref="E45:H45"/>
-    <mergeCell ref="E46:E49"/>
-    <mergeCell ref="F46:H46"/>
-    <mergeCell ref="F47:H47"/>
-    <mergeCell ref="C54:D57"/>
-    <mergeCell ref="E54:H54"/>
-    <mergeCell ref="F55:H55"/>
-    <mergeCell ref="F56:H56"/>
-    <mergeCell ref="F57:H57"/>
-    <mergeCell ref="F58:H58"/>
-    <mergeCell ref="F48:H48"/>
-    <mergeCell ref="F49:H49"/>
-    <mergeCell ref="C50:D51"/>
-    <mergeCell ref="E50:H50"/>
-    <mergeCell ref="F51:H51"/>
-    <mergeCell ref="F52:H52"/>
-    <mergeCell ref="G74:H74"/>
-    <mergeCell ref="C78:D79"/>
-    <mergeCell ref="E78:H78"/>
-    <mergeCell ref="F79:H79"/>
-    <mergeCell ref="F80:H80"/>
-    <mergeCell ref="F81:H81"/>
-    <mergeCell ref="C60:H60"/>
-    <mergeCell ref="C61:D63"/>
-    <mergeCell ref="E61:H61"/>
-    <mergeCell ref="G62:H62"/>
-    <mergeCell ref="G66:H66"/>
-    <mergeCell ref="G70:H70"/>
-    <mergeCell ref="F88:H88"/>
-    <mergeCell ref="F89:H89"/>
-    <mergeCell ref="F90:H90"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="E92:H92"/>
-    <mergeCell ref="E93:E94"/>
-    <mergeCell ref="F93:H93"/>
-    <mergeCell ref="F94:H94"/>
-    <mergeCell ref="F82:F84"/>
-    <mergeCell ref="G82:H82"/>
-    <mergeCell ref="G83:G84"/>
-    <mergeCell ref="F85:H85"/>
-    <mergeCell ref="F86:H86"/>
-    <mergeCell ref="F87:H87"/>
-    <mergeCell ref="F101:H101"/>
-    <mergeCell ref="F102:H102"/>
-    <mergeCell ref="C104:H104"/>
-    <mergeCell ref="C105:H105"/>
-    <mergeCell ref="C106:D107"/>
-    <mergeCell ref="E106:H106"/>
-    <mergeCell ref="F107:H107"/>
-    <mergeCell ref="C96:D96"/>
-    <mergeCell ref="E96:H96"/>
-    <mergeCell ref="F97:H97"/>
-    <mergeCell ref="F98:H98"/>
-    <mergeCell ref="F99:H99"/>
-    <mergeCell ref="F100:H100"/>
-    <mergeCell ref="F114:H114"/>
-    <mergeCell ref="C115:H115"/>
-    <mergeCell ref="C116:D117"/>
-    <mergeCell ref="E116:H116"/>
-    <mergeCell ref="F117:H117"/>
-    <mergeCell ref="F118:H118"/>
-    <mergeCell ref="F108:H108"/>
-    <mergeCell ref="F109:H109"/>
-    <mergeCell ref="F110:H110"/>
-    <mergeCell ref="C112:D112"/>
-    <mergeCell ref="E112:H112"/>
-    <mergeCell ref="F113:H113"/>
-    <mergeCell ref="C126:H126"/>
-    <mergeCell ref="C127:D128"/>
-    <mergeCell ref="E127:H127"/>
-    <mergeCell ref="F128:H128"/>
-    <mergeCell ref="C130:H130"/>
-    <mergeCell ref="C131:H131"/>
-    <mergeCell ref="C120:D121"/>
-    <mergeCell ref="E120:H120"/>
-    <mergeCell ref="F121:H121"/>
-    <mergeCell ref="F122:H122"/>
-    <mergeCell ref="F123:H123"/>
-    <mergeCell ref="F124:H124"/>
-    <mergeCell ref="F137:H137"/>
-    <mergeCell ref="F138:H138"/>
-    <mergeCell ref="C140:D142"/>
-    <mergeCell ref="E140:H140"/>
-    <mergeCell ref="E141:E142"/>
-    <mergeCell ref="F141:H141"/>
-    <mergeCell ref="F142:H142"/>
-    <mergeCell ref="C132:D135"/>
-    <mergeCell ref="E132:H132"/>
-    <mergeCell ref="F133:H133"/>
-    <mergeCell ref="F134:H134"/>
-    <mergeCell ref="F135:H135"/>
-    <mergeCell ref="F136:H136"/>
-    <mergeCell ref="F149:H149"/>
-    <mergeCell ref="F150:H150"/>
-    <mergeCell ref="F151:H151"/>
-    <mergeCell ref="C153:D154"/>
-    <mergeCell ref="E153:H153"/>
-    <mergeCell ref="F154:H154"/>
-    <mergeCell ref="C143:H143"/>
-    <mergeCell ref="E144:H144"/>
-    <mergeCell ref="F145:H145"/>
-    <mergeCell ref="F146:H146"/>
-    <mergeCell ref="F147:H147"/>
-    <mergeCell ref="F148:H148"/>
-    <mergeCell ref="C162:H162"/>
-    <mergeCell ref="C163:H163"/>
-    <mergeCell ref="C164:H164"/>
-    <mergeCell ref="C165:D166"/>
-    <mergeCell ref="E165:H165"/>
-    <mergeCell ref="F166:H166"/>
-    <mergeCell ref="F155:H155"/>
-    <mergeCell ref="F156:H156"/>
-    <mergeCell ref="F157:H157"/>
-    <mergeCell ref="F158:H158"/>
-    <mergeCell ref="C160:H160"/>
-    <mergeCell ref="C161:H161"/>
-    <mergeCell ref="C174:H174"/>
-    <mergeCell ref="C175:D177"/>
-    <mergeCell ref="E175:H175"/>
-    <mergeCell ref="F176:H176"/>
-    <mergeCell ref="F177:H177"/>
-    <mergeCell ref="F178:H178"/>
-    <mergeCell ref="F167:H167"/>
-    <mergeCell ref="F168:H168"/>
-    <mergeCell ref="C170:H170"/>
-    <mergeCell ref="C171:H171"/>
-    <mergeCell ref="C172:H172"/>
-    <mergeCell ref="C173:H173"/>
-    <mergeCell ref="F188:H188"/>
-    <mergeCell ref="F189:H189"/>
-    <mergeCell ref="F190:H190"/>
-    <mergeCell ref="C180:H180"/>
-    <mergeCell ref="C181:H181"/>
-    <mergeCell ref="C182:D183"/>
-    <mergeCell ref="E182:H182"/>
-    <mergeCell ref="F183:H183"/>
-    <mergeCell ref="C185:D187"/>
-    <mergeCell ref="E185:H185"/>
-    <mergeCell ref="F186:H186"/>
-    <mergeCell ref="F187:H187"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="55" orientation="portrait" r:id="rId1"/>
@@ -21072,8 +21069,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="F1" s="448"/>
-      <c r="G1" s="448"/>
+      <c r="F1" s="447"/>
+      <c r="G1" s="447"/>
     </row>
     <row r="2" spans="1:10" ht="15.75">
       <c r="A2" s="242" t="s">
@@ -21087,7 +21084,7 @@
     </row>
     <row r="3" spans="1:10" ht="15.75">
       <c r="A3" s="242" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B3" s="236"/>
       <c r="C3" s="236"/>
@@ -21168,7 +21165,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="206" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C7" s="207" t="s">
         <v>269</v>
@@ -21194,7 +21191,7 @@
         <v>307</v>
       </c>
       <c r="J7" s="270" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="30">
@@ -21202,7 +21199,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="206" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C8" s="207" t="s">
         <v>274</v>
@@ -21236,7 +21233,7 @@
         <v>2</v>
       </c>
       <c r="B9" s="206" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C9" s="207" t="s">
         <v>274</v>
@@ -21262,7 +21259,7 @@
         <v>307</v>
       </c>
       <c r="J9" s="270" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -21356,36 +21353,36 @@
       <c r="J12" s="267"/>
     </row>
     <row r="13" spans="1:10" ht="30">
-      <c r="A13" s="213">
+      <c r="A13" s="286">
         <v>1</v>
       </c>
-      <c r="B13" s="210" t="s">
-        <v>429</v>
-      </c>
-      <c r="C13" s="213" t="s">
+      <c r="B13" s="293" t="s">
+        <v>428</v>
+      </c>
+      <c r="C13" s="286" t="s">
         <v>270</v>
       </c>
-      <c r="D13" s="281">
+      <c r="D13" s="287">
         <v>1</v>
       </c>
-      <c r="E13" s="282">
+      <c r="E13" s="288">
         <v>1300000</v>
       </c>
-      <c r="F13" s="283">
+      <c r="F13" s="289">
         <f>IF(E13&gt;0,E13-MIN(E13,4250000)*10%-MIN(E13,1700000)*2%-MAX(0,E13-MIN(E13,4250000)*10%-MIN(E13,1700000)*2%-129750)*10%,0)</f>
         <v>1042575</v>
       </c>
-      <c r="G13" s="281">
+      <c r="G13" s="287">
         <f>D13*E13*12/1000</f>
         <v>15600</v>
       </c>
-      <c r="H13" s="281" t="s">
+      <c r="H13" s="287" t="s">
         <v>305</v>
       </c>
-      <c r="I13" s="284" t="s">
-        <v>309</v>
-      </c>
-      <c r="J13" s="285" t="s">
+      <c r="I13" s="290" t="s">
+        <v>426</v>
+      </c>
+      <c r="J13" s="291" t="s">
         <v>328</v>
       </c>
     </row>
@@ -21394,7 +21391,7 @@
         <v>2</v>
       </c>
       <c r="B14" s="210" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C14" s="194" t="s">
         <v>272</v>
@@ -21428,7 +21425,7 @@
         <v>3</v>
       </c>
       <c r="B15" s="210" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C15" s="213" t="s">
         <v>272</v>
@@ -21462,7 +21459,7 @@
         <v>4</v>
       </c>
       <c r="B16" s="255" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C16" s="249"/>
       <c r="D16" s="251"/>
@@ -21484,7 +21481,7 @@
         <v>5</v>
       </c>
       <c r="B17" s="244" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C17" s="243" t="s">
         <v>271</v>
@@ -21544,7 +21541,7 @@
         <v>1</v>
       </c>
       <c r="B19" s="211" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C19" s="194" t="s">
         <v>272</v>
@@ -21578,7 +21575,7 @@
         <v>2</v>
       </c>
       <c r="B20" s="210" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C20" s="213" t="s">
         <v>272</v>
@@ -21612,7 +21609,7 @@
         <v>3</v>
       </c>
       <c r="B21" s="210" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C21" s="213" t="s">
         <v>272</v>
@@ -21638,7 +21635,7 @@
         <v>309</v>
       </c>
       <c r="J21" s="285" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="22" spans="1:10" s="214" customFormat="1" ht="30">
@@ -21646,7 +21643,7 @@
         <v>4</v>
       </c>
       <c r="B22" s="244" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C22" s="243" t="s">
         <v>272</v>
@@ -21708,7 +21705,7 @@
         <v>1</v>
       </c>
       <c r="B24" s="248" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C24" s="243" t="s">
         <v>270</v>
@@ -21742,7 +21739,7 @@
         <v>2</v>
       </c>
       <c r="B25" s="183" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C25" s="194" t="s">
         <v>272</v>
@@ -21806,36 +21803,36 @@
       </c>
     </row>
     <row r="27" spans="1:10" s="214" customFormat="1" ht="30">
-      <c r="A27" s="286">
+      <c r="A27" s="243">
         <v>4</v>
       </c>
-      <c r="B27" s="287" t="s">
-        <v>435</v>
-      </c>
-      <c r="C27" s="286" t="s">
+      <c r="B27" s="248" t="s">
+        <v>434</v>
+      </c>
+      <c r="C27" s="243" t="s">
         <v>272</v>
       </c>
-      <c r="D27" s="288">
+      <c r="D27" s="245">
         <v>1</v>
       </c>
-      <c r="E27" s="289">
+      <c r="E27" s="246">
         <v>1000000</v>
       </c>
-      <c r="F27" s="290">
+      <c r="F27" s="247">
         <f t="shared" si="4"/>
         <v>804975</v>
       </c>
-      <c r="G27" s="288">
+      <c r="G27" s="245">
         <f t="shared" si="5"/>
         <v>12000</v>
       </c>
-      <c r="H27" s="288" t="s">
+      <c r="H27" s="245" t="s">
         <v>305</v>
       </c>
-      <c r="I27" s="291" t="s">
-        <v>426</v>
-      </c>
-      <c r="J27" s="292" t="s">
+      <c r="I27" s="266" t="s">
+        <v>318</v>
+      </c>
+      <c r="J27" s="271" t="s">
         <v>320</v>
       </c>
     </row>
@@ -21911,8 +21908,8 @@
       <c r="A30" s="213">
         <v>7</v>
       </c>
-      <c r="B30" s="293" t="s">
-        <v>436</v>
+      <c r="B30" s="292" t="s">
+        <v>435</v>
       </c>
       <c r="C30" s="213" t="s">
         <v>271</v>
@@ -21942,36 +21939,36 @@
       </c>
     </row>
     <row r="31" spans="1:10" s="214" customFormat="1" ht="30">
-      <c r="A31" s="286">
+      <c r="A31" s="243">
         <v>8</v>
       </c>
-      <c r="B31" s="294" t="s">
-        <v>437</v>
-      </c>
-      <c r="C31" s="286" t="s">
+      <c r="B31" s="244" t="s">
+        <v>436</v>
+      </c>
+      <c r="C31" s="243" t="s">
         <v>271</v>
       </c>
-      <c r="D31" s="288">
+      <c r="D31" s="245">
         <v>1</v>
       </c>
-      <c r="E31" s="289">
+      <c r="E31" s="246">
         <v>700000</v>
       </c>
-      <c r="F31" s="290">
+      <c r="F31" s="247">
         <f t="shared" si="4"/>
         <v>567375</v>
       </c>
-      <c r="G31" s="288">
+      <c r="G31" s="245">
         <f t="shared" si="5"/>
         <v>8400</v>
       </c>
-      <c r="H31" s="288" t="s">
+      <c r="H31" s="245" t="s">
         <v>305</v>
       </c>
-      <c r="I31" s="291" t="s">
-        <v>426</v>
-      </c>
-      <c r="J31" s="292" t="s">
+      <c r="I31" s="266" t="s">
+        <v>318</v>
+      </c>
+      <c r="J31" s="271" t="s">
         <v>320</v>
       </c>
     </row>
@@ -21980,7 +21977,7 @@
         <v>9</v>
       </c>
       <c r="B32" s="244" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C32" s="243" t="s">
         <v>271</v>
@@ -22014,7 +22011,7 @@
         <v>10</v>
       </c>
       <c r="B33" s="244" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C33" s="243" t="s">
         <v>271</v>
@@ -22160,7 +22157,7 @@
         <v>1</v>
       </c>
       <c r="B38" s="176" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C38" s="193" t="s">
         <v>270</v>
@@ -22272,36 +22269,36 @@
       </c>
     </row>
     <row r="42" spans="1:10" s="212" customFormat="1">
-      <c r="A42" s="295">
+      <c r="A42" s="294">
         <v>5</v>
       </c>
       <c r="B42" s="210" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C42" s="213" t="s">
         <v>271</v>
       </c>
-      <c r="D42" s="296">
+      <c r="D42" s="295">
         <v>1</v>
       </c>
-      <c r="E42" s="297">
+      <c r="E42" s="296">
         <v>700000</v>
       </c>
-      <c r="F42" s="298">
+      <c r="F42" s="297">
         <f>IF(E42&gt;0,E42-MIN(E42,4250000)*10%-MIN(E42,1700000)*2%-MAX(0,E42-MIN(E42,4250000)*10%-MIN(E42,1700000)*2%-129750)*10%,0)</f>
         <v>567375</v>
       </c>
-      <c r="G42" s="296">
+      <c r="G42" s="295">
         <f>D42*E42*12/1000</f>
         <v>8400</v>
       </c>
-      <c r="H42" s="296" t="s">
+      <c r="H42" s="295" t="s">
         <v>305</v>
       </c>
-      <c r="I42" s="299" t="s">
+      <c r="I42" s="298" t="s">
         <v>309</v>
       </c>
-      <c r="J42" s="300" t="s">
+      <c r="J42" s="299" t="s">
         <v>313</v>
       </c>
     </row>
@@ -22310,7 +22307,7 @@
         <v>6</v>
       </c>
       <c r="B43" s="176" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C43" s="194" t="s">
         <v>272</v>
@@ -22344,7 +22341,7 @@
         <v>7</v>
       </c>
       <c r="B44" s="176" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C44" s="195" t="s">
         <v>271</v>
@@ -22578,7 +22575,7 @@
     <row r="52" spans="1:10" ht="45">
       <c r="A52" s="241"/>
       <c r="B52" s="217" t="s">
-        <v>427</v>
+        <v>454</v>
       </c>
       <c r="C52" s="186"/>
       <c r="D52" s="1"/>
@@ -29687,54 +29684,54 @@
       </c>
     </row>
     <row r="3" spans="1:6" ht="30" customHeight="1">
-      <c r="A3" s="450" t="s">
+      <c r="A3" s="449" t="s">
         <v>332</v>
       </c>
-      <c r="B3" s="450"/>
-      <c r="C3" s="450"/>
-      <c r="D3" s="450"/>
-      <c r="E3" s="450"/>
-      <c r="F3" s="450"/>
+      <c r="B3" s="449"/>
+      <c r="C3" s="449"/>
+      <c r="D3" s="449"/>
+      <c r="E3" s="449"/>
+      <c r="F3" s="449"/>
     </row>
     <row r="4" spans="1:6" ht="44.1" customHeight="1">
-      <c r="A4" s="450" t="s">
+      <c r="A4" s="449" t="s">
         <v>333</v>
       </c>
-      <c r="B4" s="450"/>
-      <c r="C4" s="450"/>
-      <c r="D4" s="450"/>
-      <c r="E4" s="450"/>
-      <c r="F4" s="450"/>
+      <c r="B4" s="449"/>
+      <c r="C4" s="449"/>
+      <c r="D4" s="449"/>
+      <c r="E4" s="449"/>
+      <c r="F4" s="449"/>
     </row>
     <row r="5" spans="1:6" ht="44.1" customHeight="1">
-      <c r="A5" s="450" t="s">
+      <c r="A5" s="449" t="s">
         <v>334</v>
       </c>
-      <c r="B5" s="450"/>
-      <c r="C5" s="450"/>
-      <c r="D5" s="450"/>
-      <c r="E5" s="450"/>
-      <c r="F5" s="450"/>
+      <c r="B5" s="449"/>
+      <c r="C5" s="449"/>
+      <c r="D5" s="449"/>
+      <c r="E5" s="449"/>
+      <c r="F5" s="449"/>
     </row>
     <row r="6" spans="1:6" ht="30" customHeight="1">
-      <c r="A6" s="450" t="s">
+      <c r="A6" s="449" t="s">
         <v>335</v>
       </c>
-      <c r="B6" s="450"/>
-      <c r="C6" s="450"/>
-      <c r="D6" s="450"/>
-      <c r="E6" s="450"/>
-      <c r="F6" s="450"/>
+      <c r="B6" s="449"/>
+      <c r="C6" s="449"/>
+      <c r="D6" s="449"/>
+      <c r="E6" s="449"/>
+      <c r="F6" s="449"/>
     </row>
     <row r="7" spans="1:6" ht="30" customHeight="1">
-      <c r="A7" s="450" t="s">
+      <c r="A7" s="449" t="s">
         <v>336</v>
       </c>
-      <c r="B7" s="450"/>
-      <c r="C7" s="450"/>
-      <c r="D7" s="450"/>
-      <c r="E7" s="450"/>
-      <c r="F7" s="450"/>
+      <c r="B7" s="449"/>
+      <c r="C7" s="449"/>
+      <c r="D7" s="449"/>
+      <c r="E7" s="449"/>
+      <c r="F7" s="449"/>
     </row>
     <row r="9" spans="1:6" ht="25.5">
       <c r="A9" s="279" t="s">
@@ -30002,87 +29999,93 @@
       </c>
     </row>
     <row r="24" spans="1:6" ht="27" customHeight="1">
-      <c r="A24" s="449" t="s">
+      <c r="A24" s="448" t="s">
         <v>402</v>
       </c>
-      <c r="B24" s="449"/>
-      <c r="C24" s="449"/>
-      <c r="D24" s="449"/>
-      <c r="E24" s="449"/>
-      <c r="F24" s="449"/>
+      <c r="B24" s="448"/>
+      <c r="C24" s="448"/>
+      <c r="D24" s="448"/>
+      <c r="E24" s="448"/>
+      <c r="F24" s="448"/>
     </row>
     <row r="25" spans="1:6" ht="27" customHeight="1">
-      <c r="A25" s="449" t="s">
+      <c r="A25" s="448" t="s">
         <v>403</v>
       </c>
-      <c r="B25" s="449"/>
-      <c r="C25" s="449"/>
-      <c r="D25" s="449"/>
-      <c r="E25" s="449"/>
-      <c r="F25" s="449"/>
+      <c r="B25" s="448"/>
+      <c r="C25" s="448"/>
+      <c r="D25" s="448"/>
+      <c r="E25" s="448"/>
+      <c r="F25" s="448"/>
     </row>
     <row r="26" spans="1:6" ht="27" customHeight="1">
-      <c r="A26" s="449" t="s">
+      <c r="A26" s="448" t="s">
         <v>404</v>
       </c>
-      <c r="B26" s="449"/>
-      <c r="C26" s="449"/>
-      <c r="D26" s="449"/>
-      <c r="E26" s="449"/>
-      <c r="F26" s="449"/>
+      <c r="B26" s="448"/>
+      <c r="C26" s="448"/>
+      <c r="D26" s="448"/>
+      <c r="E26" s="448"/>
+      <c r="F26" s="448"/>
     </row>
     <row r="27" spans="1:6" ht="27" customHeight="1">
-      <c r="A27" s="449" t="s">
+      <c r="A27" s="448" t="s">
         <v>405</v>
       </c>
-      <c r="B27" s="449"/>
-      <c r="C27" s="449"/>
-      <c r="D27" s="449"/>
-      <c r="E27" s="449"/>
-      <c r="F27" s="449"/>
+      <c r="B27" s="448"/>
+      <c r="C27" s="448"/>
+      <c r="D27" s="448"/>
+      <c r="E27" s="448"/>
+      <c r="F27" s="448"/>
     </row>
     <row r="28" spans="1:6" ht="27" customHeight="1">
-      <c r="A28" s="449" t="s">
+      <c r="A28" s="448" t="s">
         <v>406</v>
       </c>
-      <c r="B28" s="449"/>
-      <c r="C28" s="449"/>
-      <c r="D28" s="449"/>
-      <c r="E28" s="449"/>
-      <c r="F28" s="449"/>
+      <c r="B28" s="448"/>
+      <c r="C28" s="448"/>
+      <c r="D28" s="448"/>
+      <c r="E28" s="448"/>
+      <c r="F28" s="448"/>
     </row>
     <row r="29" spans="1:6" ht="27" customHeight="1">
-      <c r="A29" s="449" t="s">
+      <c r="A29" s="448" t="s">
         <v>407</v>
       </c>
-      <c r="B29" s="449"/>
-      <c r="C29" s="449"/>
-      <c r="D29" s="449"/>
-      <c r="E29" s="449"/>
-      <c r="F29" s="449"/>
+      <c r="B29" s="448"/>
+      <c r="C29" s="448"/>
+      <c r="D29" s="448"/>
+      <c r="E29" s="448"/>
+      <c r="F29" s="448"/>
     </row>
     <row r="30" spans="1:6" ht="27" customHeight="1">
-      <c r="A30" s="449" t="s">
+      <c r="A30" s="448" t="s">
         <v>408</v>
       </c>
-      <c r="B30" s="449"/>
-      <c r="C30" s="449"/>
-      <c r="D30" s="449"/>
-      <c r="E30" s="449"/>
-      <c r="F30" s="449"/>
+      <c r="B30" s="448"/>
+      <c r="C30" s="448"/>
+      <c r="D30" s="448"/>
+      <c r="E30" s="448"/>
+      <c r="F30" s="448"/>
     </row>
     <row r="31" spans="1:6" ht="27" customHeight="1">
-      <c r="A31" s="449" t="s">
+      <c r="A31" s="448" t="s">
         <v>409</v>
       </c>
-      <c r="B31" s="449"/>
-      <c r="C31" s="449"/>
-      <c r="D31" s="449"/>
-      <c r="E31" s="449"/>
-      <c r="F31" s="449"/>
+      <c r="B31" s="448"/>
+      <c r="C31" s="448"/>
+      <c r="D31" s="448"/>
+      <c r="E31" s="448"/>
+      <c r="F31" s="448"/>
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A7:F7"/>
     <mergeCell ref="A31:F31"/>
     <mergeCell ref="A25:F25"/>
     <mergeCell ref="A26:F26"/>
@@ -30090,12 +30093,6 @@
     <mergeCell ref="A28:F28"/>
     <mergeCell ref="A29:F29"/>
     <mergeCell ref="A30:F30"/>
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" verticalDpi="0" r:id="rId1"/>

--- a/TAZA/_документы/ШР ЦАКФ.xlsx
+++ b/TAZA/_документы/ШР ЦАКФ.xlsx
@@ -21522,15 +21522,15 @@
       </c>
       <c r="E18" s="221">
         <f>SUM(E19:E22)</f>
-        <v>3030000</v>
+        <v>3400000</v>
       </c>
       <c r="F18" s="222">
         <f>SUM(F19:F22)</f>
-        <v>2451660</v>
+        <v>2744700</v>
       </c>
       <c r="G18" s="181">
         <f>SUM(G19:G22)</f>
-        <v>36360</v>
+        <v>40800</v>
       </c>
       <c r="H18" s="181"/>
       <c r="I18" s="181"/>
@@ -21584,15 +21584,15 @@
         <v>1</v>
       </c>
       <c r="E20" s="282">
-        <v>615000</v>
+        <v>800000</v>
       </c>
       <c r="F20" s="283">
         <f>IF(E20&gt;0,E20-MIN(E20,4250000)*10%-MIN(E20,1700000)*2%-MAX(0,E20-MIN(E20,4250000)*10%-MIN(E20,1700000)*2%-129750)*10%,0)</f>
-        <v>500055</v>
+        <v>646575</v>
       </c>
       <c r="G20" s="281">
         <f>D20*E20*12/1000</f>
-        <v>7380</v>
+        <v>9600</v>
       </c>
       <c r="H20" s="281" t="s">
         <v>305</v>
@@ -21618,15 +21618,15 @@
         <v>1</v>
       </c>
       <c r="E21" s="282">
-        <v>615000</v>
+        <v>800000</v>
       </c>
       <c r="F21" s="283">
         <f>IF(E21&gt;0,E21-MIN(E21,4250000)*10%-MIN(E21,1700000)*2%-MAX(0,E21-MIN(E21,4250000)*10%-MIN(E21,1700000)*2%-129750)*10%,0)</f>
-        <v>500055</v>
+        <v>646575</v>
       </c>
       <c r="G21" s="281">
         <f>D21*E21*12/1000</f>
-        <v>7380</v>
+        <v>9600</v>
       </c>
       <c r="H21" s="281" t="s">
         <v>305</v>
@@ -22558,15 +22558,15 @@
       </c>
       <c r="E51" s="233">
         <f>E6+E10+E12+E18+E23+E34+E37+E46</f>
-        <v>31423100</v>
+        <v>31793100</v>
       </c>
       <c r="F51" s="235">
         <f>F6+F10+F12+F18+F23+F34+F37+F46</f>
-        <v>25302295.199999999</v>
+        <v>25595335.199999999</v>
       </c>
       <c r="G51" s="234">
         <f>G6+G10+G12+G18+G23+G34+G37+G46</f>
-        <v>361560</v>
+        <v>366000</v>
       </c>
       <c r="H51" s="234"/>
       <c r="I51" s="234"/>

--- a/TAZA/_документы/ШР ЦАКФ.xlsx
+++ b/TAZA/_документы/ШР ЦАКФ.xlsx
@@ -1828,9 +1828,6 @@
     <t>Вывод</t>
   </si>
   <si>
-    <t>ГИД, заместители ГИД, национальный координатор, финансовый директор</t>
-  </si>
-  <si>
     <t>1 400 000 – 1 600 000</t>
   </si>
   <si>
@@ -2428,6 +2425,9 @@
   </si>
   <si>
     <t>*приход с 12.2026 и в 2027 году выделен сиреневым (с 12.2026 – Өміртай А.; остальные – с 02.2027)</t>
+  </si>
+  <si>
+    <t>ГИД, заместители ГИД, руководитель проектного офиса «Таза Қазақстан», финансовый директор</t>
   </si>
 </sst>
 </file>
@@ -5576,6 +5576,42 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5588,48 +5624,90 @@
     <xf numFmtId="0" fontId="45" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="177" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="177" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="177" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="0" xfId="177" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="2" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="39" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="33" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="34" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="35" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="177" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="37" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="38" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="36" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="39" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="39" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="3" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="10" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="46" fillId="3" borderId="37" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -5639,18 +5717,69 @@
     <xf numFmtId="49" fontId="46" fillId="3" borderId="36" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="33" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="34" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="35" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="1" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="32" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="37" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="38" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="36" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="37" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="38" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="39" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="3" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="10" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="2" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="17" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="32" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="37" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="38" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="36" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="46" fillId="3" borderId="33" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -5660,139 +5789,19 @@
     <xf numFmtId="0" fontId="46" fillId="3" borderId="35" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="32" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="46" fillId="3" borderId="39" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="3" borderId="1" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="39" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="37" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="25" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="38" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="37" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="37" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="38" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="36" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="10" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="2" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="17" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="39" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="3" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="39" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="3" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="1" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="10" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="33" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="34" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="35" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="177" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="177" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="177" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="0" xfId="177" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="2" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="39" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="33" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="34" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="35" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="177" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="36" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="33" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5807,43 +5816,145 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="46" fillId="3" borderId="37" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="3" borderId="36" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="25" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="38" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="2" borderId="37" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="2" borderId="38" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="37" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="37" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="36" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="36" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="3" borderId="0" xfId="177" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="38" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="37" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="36" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="2" borderId="37" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="46" fillId="2" borderId="38" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5852,24 +5963,6 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -5920,99 +6013,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -6354,7 +6354,7 @@
         <xdr:cNvPr id="2" name="TextBox 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6412,7 +6412,7 @@
         <xdr:cNvPr id="3" name="TextBox 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6467,7 +6467,7 @@
         <xdr:cNvPr id="4" name="TextBox 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000004000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000004000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10244,26 +10244,26 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="309" t="s">
+      <c r="A2" s="301" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="309"/>
+      <c r="B2" s="301"/>
       <c r="C2" s="132" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="314" t="s">
+      <c r="A3" s="302" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="315"/>
+      <c r="B3" s="303"/>
       <c r="C3" s="133"/>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="314" t="s">
+      <c r="A4" s="302" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="315" t="s">
+      <c r="B4" s="303" t="s">
         <v>27</v>
       </c>
       <c r="C4" s="133"/>
@@ -10276,24 +10276,24 @@
       <c r="C5" s="133"/>
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1">
-      <c r="A6" s="314" t="s">
+      <c r="A6" s="302" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="315"/>
+      <c r="B6" s="303"/>
       <c r="C6" s="134"/>
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1">
-      <c r="A7" s="314" t="s">
+      <c r="A7" s="302" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="315"/>
+      <c r="B7" s="303"/>
       <c r="C7" s="135"/>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="305" t="s">
+      <c r="A8" s="304" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="306"/>
+      <c r="B8" s="305"/>
       <c r="C8" s="131">
         <f>SUM(C3:C7)</f>
         <v>0</v>
@@ -10303,17 +10303,17 @@
       <c r="C9" s="2"/>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="316" t="s">
+      <c r="A10" s="306" t="s">
         <v>31</v>
       </c>
-      <c r="B10" s="316"/>
-      <c r="C10" s="316"/>
+      <c r="B10" s="306"/>
+      <c r="C10" s="306"/>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="309" t="s">
+      <c r="A11" s="301" t="s">
         <v>2</v>
       </c>
-      <c r="B11" s="309"/>
+      <c r="B11" s="301"/>
       <c r="C11" s="132" t="s">
         <v>1</v>
       </c>
@@ -10340,10 +10340,10 @@
       <c r="C14" s="136"/>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="305" t="s">
+      <c r="A15" s="304" t="s">
         <v>35</v>
       </c>
-      <c r="B15" s="306"/>
+      <c r="B15" s="305"/>
       <c r="C15" s="130">
         <f>SUM(C12:C14)</f>
         <v>0</v>
@@ -10373,10 +10373,10 @@
       <c r="C19" s="4"/>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="309" t="s">
+      <c r="A20" s="301" t="s">
         <v>2</v>
       </c>
-      <c r="B20" s="309"/>
+      <c r="B20" s="301"/>
       <c r="C20" s="132" t="s">
         <v>1</v>
       </c>
@@ -10421,17 +10421,17 @@
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="310" t="s">
+      <c r="A26" s="309" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="311"/>
-      <c r="C26" s="312"/>
+      <c r="B26" s="310"/>
+      <c r="C26" s="311"/>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="309" t="s">
+      <c r="A27" s="301" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="309"/>
+      <c r="B27" s="301"/>
       <c r="C27" s="138"/>
     </row>
     <row r="28" spans="1:4">
@@ -10448,17 +10448,17 @@
       <c r="C29" s="6"/>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="313" t="s">
+      <c r="A30" s="312" t="s">
         <v>40</v>
       </c>
-      <c r="B30" s="313"/>
+      <c r="B30" s="312"/>
       <c r="C30" s="2"/>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="309" t="s">
+      <c r="A31" s="301" t="s">
         <v>2</v>
       </c>
-      <c r="B31" s="309"/>
+      <c r="B31" s="301"/>
       <c r="C31" s="132" t="s">
         <v>1</v>
       </c>
@@ -10495,8 +10495,8 @@
       <c r="D35" s="3"/>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="301"/>
-      <c r="B36" s="302"/>
+      <c r="A36" s="313"/>
+      <c r="B36" s="314"/>
       <c r="C36" s="144">
         <f>SUM(C32:C35)</f>
         <v>0</v>
@@ -10508,10 +10508,10 @@
       <c r="C37" s="8"/>
     </row>
     <row r="38" spans="1:4">
-      <c r="A38" s="303" t="s">
+      <c r="A38" s="315" t="s">
         <v>42</v>
       </c>
-      <c r="B38" s="304"/>
+      <c r="B38" s="316"/>
       <c r="C38" s="145">
         <f>C28-C36</f>
         <v>0</v>
@@ -10534,6 +10534,23 @@
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A31:B31"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A3:B3"/>
@@ -10546,23 +10563,6 @@
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A38:B38"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -10830,11 +10830,11 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="1"/>
-      <c r="B19" s="309" t="s">
+      <c r="B19" s="301" t="s">
         <v>259</v>
       </c>
-      <c r="C19" s="309"/>
-      <c r="D19" s="309"/>
+      <c r="C19" s="301"/>
+      <c r="D19" s="301"/>
       <c r="E19" s="162" t="e">
         <f>E15/E18</f>
         <v>#REF!</v>
@@ -10911,17 +10911,17 @@
       <c r="A1" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="357" t="s">
+      <c r="B1" s="319" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="357"/>
-      <c r="D1" s="357"/>
-      <c r="E1" s="357"/>
-      <c r="F1" s="357"/>
-      <c r="G1" s="357"/>
-      <c r="H1" s="357"/>
-      <c r="I1" s="357"/>
-      <c r="J1" s="357"/>
+      <c r="C1" s="319"/>
+      <c r="D1" s="319"/>
+      <c r="E1" s="319"/>
+      <c r="F1" s="319"/>
+      <c r="G1" s="319"/>
+      <c r="H1" s="319"/>
+      <c r="I1" s="319"/>
+      <c r="J1" s="319"/>
       <c r="K1" s="85"/>
       <c r="O1" s="51"/>
     </row>
@@ -10959,17 +10959,17 @@
       <c r="A3" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="358" t="s">
+      <c r="B3" s="320" t="s">
         <v>201</v>
       </c>
-      <c r="C3" s="358"/>
-      <c r="D3" s="358"/>
-      <c r="E3" s="358"/>
-      <c r="F3" s="358"/>
-      <c r="G3" s="358"/>
-      <c r="H3" s="358"/>
-      <c r="I3" s="358"/>
-      <c r="J3" s="358"/>
+      <c r="C3" s="320"/>
+      <c r="D3" s="320"/>
+      <c r="E3" s="320"/>
+      <c r="F3" s="320"/>
+      <c r="G3" s="320"/>
+      <c r="H3" s="320"/>
+      <c r="I3" s="320"/>
+      <c r="J3" s="320"/>
       <c r="K3" s="88"/>
       <c r="O3" s="51"/>
     </row>
@@ -10977,17 +10977,17 @@
       <c r="A4" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="359" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="359"/>
-      <c r="D4" s="359"/>
-      <c r="E4" s="359"/>
-      <c r="F4" s="359"/>
-      <c r="G4" s="359"/>
-      <c r="H4" s="359"/>
-      <c r="I4" s="359"/>
-      <c r="J4" s="359"/>
+      <c r="B4" s="321" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="321"/>
+      <c r="D4" s="321"/>
+      <c r="E4" s="321"/>
+      <c r="F4" s="321"/>
+      <c r="G4" s="321"/>
+      <c r="H4" s="321"/>
+      <c r="I4" s="321"/>
+      <c r="J4" s="321"/>
       <c r="K4" s="89"/>
       <c r="O4" s="51"/>
     </row>
@@ -10995,17 +10995,17 @@
       <c r="A5" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="360" t="s">
+      <c r="B5" s="322" t="s">
         <v>47</v>
       </c>
-      <c r="C5" s="360"/>
-      <c r="D5" s="360"/>
-      <c r="E5" s="360"/>
-      <c r="F5" s="360"/>
-      <c r="G5" s="360"/>
-      <c r="H5" s="360"/>
-      <c r="I5" s="360"/>
-      <c r="J5" s="360"/>
+      <c r="C5" s="322"/>
+      <c r="D5" s="322"/>
+      <c r="E5" s="322"/>
+      <c r="F5" s="322"/>
+      <c r="G5" s="322"/>
+      <c r="H5" s="322"/>
+      <c r="I5" s="322"/>
+      <c r="J5" s="322"/>
       <c r="K5" s="90"/>
       <c r="O5" s="51"/>
     </row>
@@ -11013,17 +11013,17 @@
       <c r="A6" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B6" s="360" t="s">
+      <c r="B6" s="322" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="360"/>
-      <c r="D6" s="360"/>
-      <c r="E6" s="360"/>
-      <c r="F6" s="360"/>
-      <c r="G6" s="360"/>
-      <c r="H6" s="360"/>
-      <c r="I6" s="360"/>
-      <c r="J6" s="360"/>
+      <c r="C6" s="322"/>
+      <c r="D6" s="322"/>
+      <c r="E6" s="322"/>
+      <c r="F6" s="322"/>
+      <c r="G6" s="322"/>
+      <c r="H6" s="322"/>
+      <c r="I6" s="322"/>
+      <c r="J6" s="322"/>
       <c r="K6" s="90"/>
       <c r="O6" s="51"/>
     </row>
@@ -11031,15 +11031,15 @@
       <c r="A7" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B7" s="361" t="s">
+      <c r="B7" s="323" t="s">
         <v>183</v>
       </c>
-      <c r="C7" s="361"/>
-      <c r="D7" s="361"/>
-      <c r="E7" s="361"/>
-      <c r="F7" s="361"/>
-      <c r="G7" s="361"/>
-      <c r="H7" s="361"/>
+      <c r="C7" s="323"/>
+      <c r="D7" s="323"/>
+      <c r="E7" s="323"/>
+      <c r="F7" s="323"/>
+      <c r="G7" s="323"/>
+      <c r="H7" s="323"/>
       <c r="I7" s="91"/>
       <c r="J7" s="71" t="s">
         <v>50</v>
@@ -11065,51 +11065,51 @@
       <c r="A22" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B22" s="362" t="s">
+      <c r="B22" s="324" t="s">
         <v>0</v>
       </c>
-      <c r="C22" s="365" t="s">
+      <c r="C22" s="327" t="s">
         <v>51</v>
       </c>
-      <c r="D22" s="366"/>
-      <c r="E22" s="366"/>
-      <c r="F22" s="366"/>
-      <c r="G22" s="367"/>
+      <c r="D22" s="328"/>
+      <c r="E22" s="328"/>
+      <c r="F22" s="328"/>
+      <c r="G22" s="329"/>
       <c r="H22" s="93"/>
-      <c r="I22" s="366" t="s">
+      <c r="I22" s="328" t="s">
         <v>52</v>
       </c>
-      <c r="J22" s="367"/>
+      <c r="J22" s="329"/>
       <c r="K22" s="94"/>
     </row>
     <row r="23" spans="1:16" ht="12" customHeight="1">
       <c r="A23" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="363"/>
-      <c r="C23" s="368"/>
-      <c r="D23" s="369"/>
-      <c r="E23" s="369"/>
-      <c r="F23" s="369"/>
-      <c r="G23" s="370"/>
+      <c r="B23" s="325"/>
+      <c r="C23" s="330"/>
+      <c r="D23" s="331"/>
+      <c r="E23" s="331"/>
+      <c r="F23" s="331"/>
+      <c r="G23" s="332"/>
       <c r="H23" s="95"/>
-      <c r="I23" s="369"/>
-      <c r="J23" s="370"/>
+      <c r="I23" s="331"/>
+      <c r="J23" s="332"/>
       <c r="K23" s="94"/>
     </row>
     <row r="24" spans="1:16" ht="24" customHeight="1">
       <c r="A24" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B24" s="364"/>
-      <c r="C24" s="371"/>
-      <c r="D24" s="372"/>
-      <c r="E24" s="372"/>
-      <c r="F24" s="372"/>
-      <c r="G24" s="373"/>
+      <c r="B24" s="326"/>
+      <c r="C24" s="333"/>
+      <c r="D24" s="334"/>
+      <c r="E24" s="334"/>
+      <c r="F24" s="334"/>
+      <c r="G24" s="335"/>
       <c r="H24" s="96"/>
-      <c r="I24" s="372"/>
-      <c r="J24" s="373"/>
+      <c r="I24" s="334"/>
+      <c r="J24" s="335"/>
       <c r="K24" s="94"/>
     </row>
     <row r="25" spans="1:16" ht="15.75" hidden="1" customHeight="1"/>
@@ -11151,13 +11151,13 @@
       <c r="B29" s="58">
         <v>1</v>
       </c>
-      <c r="C29" s="323" t="s">
+      <c r="C29" s="336" t="s">
         <v>202</v>
       </c>
-      <c r="D29" s="324"/>
-      <c r="E29" s="324"/>
-      <c r="F29" s="324"/>
-      <c r="G29" s="325"/>
+      <c r="D29" s="337"/>
+      <c r="E29" s="337"/>
+      <c r="F29" s="337"/>
+      <c r="G29" s="338"/>
       <c r="H29" s="97"/>
       <c r="I29" s="97" t="e">
         <f>I35+I44+I46+I47+I50+#REF!+I68+I71+I72+I73+I77+I89+I97+I101+I106+I108+I116+I131+I142+I146+I147+I154+I32+I34+#REF!+#REF!+I151+#REF!+I98+I113+I155</f>
@@ -11174,15 +11174,15 @@
       <c r="B30" s="58">
         <v>2</v>
       </c>
-      <c r="C30" s="332" t="s">
+      <c r="C30" s="339" t="s">
         <v>54</v>
       </c>
-      <c r="D30" s="323" t="s">
+      <c r="D30" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E30" s="324"/>
-      <c r="F30" s="324"/>
-      <c r="G30" s="325"/>
+      <c r="E30" s="337"/>
+      <c r="F30" s="337"/>
+      <c r="G30" s="338"/>
       <c r="H30" s="97"/>
       <c r="I30" s="97"/>
       <c r="J30" s="99" t="e">
@@ -11202,15 +11202,15 @@
       <c r="B31" s="58">
         <v>3</v>
       </c>
-      <c r="C31" s="333"/>
+      <c r="C31" s="340"/>
       <c r="D31" s="342" t="s">
         <v>55</v>
       </c>
-      <c r="E31" s="319" t="s">
+      <c r="E31" s="345" t="s">
         <v>56</v>
       </c>
-      <c r="F31" s="320"/>
-      <c r="G31" s="321"/>
+      <c r="F31" s="346"/>
+      <c r="G31" s="347"/>
       <c r="H31" s="72"/>
       <c r="I31" s="72"/>
       <c r="J31" s="100"/>
@@ -11227,13 +11227,13 @@
       <c r="B32" s="58">
         <v>4</v>
       </c>
-      <c r="C32" s="333"/>
+      <c r="C32" s="340"/>
       <c r="D32" s="343"/>
-      <c r="E32" s="319" t="s">
+      <c r="E32" s="345" t="s">
         <v>57</v>
       </c>
-      <c r="F32" s="320"/>
-      <c r="G32" s="321"/>
+      <c r="F32" s="346"/>
+      <c r="G32" s="347"/>
       <c r="H32" s="72"/>
       <c r="I32" s="72"/>
       <c r="J32" s="81" t="e">
@@ -11253,13 +11253,13 @@
       <c r="B33" s="58">
         <v>5</v>
       </c>
-      <c r="C33" s="333"/>
+      <c r="C33" s="340"/>
       <c r="D33" s="343"/>
-      <c r="E33" s="352" t="s">
+      <c r="E33" s="348" t="s">
         <v>58</v>
       </c>
-      <c r="F33" s="353"/>
-      <c r="G33" s="354"/>
+      <c r="F33" s="349"/>
+      <c r="G33" s="350"/>
       <c r="H33" s="72"/>
       <c r="I33" s="72"/>
       <c r="J33" s="81"/>
@@ -11272,13 +11272,13 @@
       <c r="B34" s="58">
         <v>6</v>
       </c>
-      <c r="C34" s="349"/>
-      <c r="D34" s="351"/>
-      <c r="E34" s="329" t="s">
+      <c r="C34" s="341"/>
+      <c r="D34" s="344"/>
+      <c r="E34" s="352" t="s">
         <v>170</v>
       </c>
-      <c r="F34" s="329"/>
-      <c r="G34" s="329"/>
+      <c r="F34" s="352"/>
+      <c r="G34" s="352"/>
       <c r="H34" s="72"/>
       <c r="I34" s="72"/>
       <c r="J34" s="81" t="e">
@@ -11294,15 +11294,15 @@
       <c r="B35" s="58">
         <v>7</v>
       </c>
-      <c r="C35" s="332" t="s">
+      <c r="C35" s="339" t="s">
         <v>171</v>
       </c>
-      <c r="D35" s="323" t="s">
+      <c r="D35" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E35" s="355"/>
-      <c r="F35" s="355"/>
-      <c r="G35" s="356"/>
+      <c r="E35" s="353"/>
+      <c r="F35" s="353"/>
+      <c r="G35" s="354"/>
       <c r="H35" s="97"/>
       <c r="I35" s="101">
         <f>I36+I37</f>
@@ -11318,15 +11318,15 @@
       <c r="B36" s="58">
         <v>8</v>
       </c>
-      <c r="C36" s="333"/>
+      <c r="C36" s="340"/>
       <c r="D36" s="342" t="s">
         <v>55</v>
       </c>
-      <c r="E36" s="336" t="s">
+      <c r="E36" s="355" t="s">
         <v>172</v>
       </c>
-      <c r="F36" s="337"/>
-      <c r="G36" s="338"/>
+      <c r="F36" s="356"/>
+      <c r="G36" s="357"/>
       <c r="H36" s="72"/>
       <c r="I36" s="72"/>
       <c r="J36" s="81" t="e">
@@ -11343,13 +11343,13 @@
       <c r="B37" s="58">
         <v>9</v>
       </c>
-      <c r="C37" s="349"/>
-      <c r="D37" s="350"/>
-      <c r="E37" s="336" t="s">
+      <c r="C37" s="341"/>
+      <c r="D37" s="351"/>
+      <c r="E37" s="355" t="s">
         <v>173</v>
       </c>
-      <c r="F37" s="337"/>
-      <c r="G37" s="338"/>
+      <c r="F37" s="356"/>
+      <c r="G37" s="357"/>
       <c r="H37" s="72"/>
       <c r="I37" s="72"/>
       <c r="J37" s="81" t="e">
@@ -11366,13 +11366,13 @@
       <c r="B38" s="58">
         <v>10</v>
       </c>
-      <c r="C38" s="323" t="s">
+      <c r="C38" s="336" t="s">
         <v>203</v>
       </c>
-      <c r="D38" s="324"/>
-      <c r="E38" s="324"/>
-      <c r="F38" s="324"/>
-      <c r="G38" s="325"/>
+      <c r="D38" s="337"/>
+      <c r="E38" s="337"/>
+      <c r="F38" s="337"/>
+      <c r="G38" s="338"/>
       <c r="H38" s="97"/>
       <c r="I38" s="97"/>
       <c r="J38" s="102"/>
@@ -11385,15 +11385,15 @@
       <c r="B39" s="58">
         <v>11</v>
       </c>
-      <c r="C39" s="332" t="s">
+      <c r="C39" s="339" t="s">
         <v>186</v>
       </c>
-      <c r="D39" s="323" t="s">
+      <c r="D39" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E39" s="324"/>
-      <c r="F39" s="324"/>
-      <c r="G39" s="325"/>
+      <c r="E39" s="337"/>
+      <c r="F39" s="337"/>
+      <c r="G39" s="338"/>
       <c r="H39" s="97"/>
       <c r="I39" s="97"/>
       <c r="J39" s="102"/>
@@ -11406,15 +11406,15 @@
       <c r="B40" s="58">
         <v>12</v>
       </c>
-      <c r="C40" s="333"/>
+      <c r="C40" s="340"/>
       <c r="D40" s="342" t="s">
         <v>55</v>
       </c>
-      <c r="E40" s="319" t="s">
+      <c r="E40" s="345" t="s">
         <v>128</v>
       </c>
-      <c r="F40" s="320"/>
-      <c r="G40" s="321"/>
+      <c r="F40" s="346"/>
+      <c r="G40" s="347"/>
       <c r="H40" s="72"/>
       <c r="I40" s="72"/>
       <c r="J40" s="81" t="e">
@@ -11430,13 +11430,13 @@
       <c r="B41" s="58">
         <v>13</v>
       </c>
-      <c r="C41" s="349"/>
-      <c r="D41" s="350"/>
-      <c r="E41" s="319" t="s">
+      <c r="C41" s="341"/>
+      <c r="D41" s="351"/>
+      <c r="E41" s="345" t="s">
         <v>129</v>
       </c>
-      <c r="F41" s="320"/>
-      <c r="G41" s="321"/>
+      <c r="F41" s="346"/>
+      <c r="G41" s="347"/>
       <c r="H41" s="72"/>
       <c r="I41" s="72"/>
       <c r="J41" s="81" t="e">
@@ -11452,15 +11452,15 @@
       <c r="B42" s="58">
         <v>14</v>
       </c>
-      <c r="C42" s="332" t="s">
+      <c r="C42" s="339" t="s">
         <v>204</v>
       </c>
-      <c r="D42" s="323" t="s">
+      <c r="D42" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E42" s="324"/>
-      <c r="F42" s="324"/>
-      <c r="G42" s="325"/>
+      <c r="E42" s="337"/>
+      <c r="F42" s="337"/>
+      <c r="G42" s="338"/>
       <c r="H42" s="97"/>
       <c r="I42" s="97"/>
       <c r="J42" s="102"/>
@@ -11473,15 +11473,15 @@
       <c r="B43" s="58">
         <v>15</v>
       </c>
-      <c r="C43" s="333"/>
+      <c r="C43" s="340"/>
       <c r="D43" s="342" t="s">
         <v>55</v>
       </c>
-      <c r="E43" s="319" t="s">
+      <c r="E43" s="345" t="s">
         <v>128</v>
       </c>
-      <c r="F43" s="320"/>
-      <c r="G43" s="321"/>
+      <c r="F43" s="346"/>
+      <c r="G43" s="347"/>
       <c r="H43" s="72"/>
       <c r="I43" s="72"/>
       <c r="J43" s="81" t="e">
@@ -11497,13 +11497,13 @@
       <c r="B44" s="58">
         <v>16</v>
       </c>
-      <c r="C44" s="349"/>
-      <c r="D44" s="350"/>
-      <c r="E44" s="319" t="s">
+      <c r="C44" s="341"/>
+      <c r="D44" s="351"/>
+      <c r="E44" s="345" t="s">
         <v>129</v>
       </c>
-      <c r="F44" s="320"/>
-      <c r="G44" s="321"/>
+      <c r="F44" s="346"/>
+      <c r="G44" s="347"/>
       <c r="H44" s="72"/>
       <c r="I44" s="72"/>
       <c r="J44" s="81" t="e">
@@ -11519,15 +11519,15 @@
       <c r="B45" s="58">
         <v>17</v>
       </c>
-      <c r="C45" s="332" t="s">
+      <c r="C45" s="339" t="s">
         <v>62</v>
       </c>
-      <c r="D45" s="323" t="s">
+      <c r="D45" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E45" s="324"/>
-      <c r="F45" s="324"/>
-      <c r="G45" s="325"/>
+      <c r="E45" s="337"/>
+      <c r="F45" s="337"/>
+      <c r="G45" s="338"/>
       <c r="H45" s="97"/>
       <c r="I45" s="97"/>
       <c r="J45" s="102"/>
@@ -11540,15 +11540,15 @@
       <c r="B46" s="58">
         <v>18</v>
       </c>
-      <c r="C46" s="333"/>
+      <c r="C46" s="340"/>
       <c r="D46" s="342" t="s">
         <v>55</v>
       </c>
-      <c r="E46" s="319" t="s">
+      <c r="E46" s="345" t="s">
         <v>63</v>
       </c>
-      <c r="F46" s="320"/>
-      <c r="G46" s="321"/>
+      <c r="F46" s="346"/>
+      <c r="G46" s="347"/>
       <c r="H46" s="72"/>
       <c r="I46" s="72"/>
       <c r="J46" s="81" t="e">
@@ -11564,13 +11564,13 @@
       <c r="B47" s="58">
         <v>19</v>
       </c>
-      <c r="C47" s="349"/>
-      <c r="D47" s="350"/>
-      <c r="E47" s="319" t="s">
+      <c r="C47" s="341"/>
+      <c r="D47" s="351"/>
+      <c r="E47" s="345" t="s">
         <v>64</v>
       </c>
-      <c r="F47" s="320"/>
-      <c r="G47" s="321"/>
+      <c r="F47" s="346"/>
+      <c r="G47" s="347"/>
       <c r="H47" s="72"/>
       <c r="I47" s="72"/>
       <c r="J47" s="81" t="e">
@@ -11586,15 +11586,15 @@
       <c r="B48" s="58">
         <v>20</v>
       </c>
-      <c r="C48" s="332" t="s">
+      <c r="C48" s="339" t="s">
         <v>205</v>
       </c>
-      <c r="D48" s="323" t="s">
+      <c r="D48" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E48" s="324"/>
-      <c r="F48" s="324"/>
-      <c r="G48" s="325"/>
+      <c r="E48" s="337"/>
+      <c r="F48" s="337"/>
+      <c r="G48" s="338"/>
       <c r="H48" s="97"/>
       <c r="I48" s="97"/>
       <c r="J48" s="102"/>
@@ -11607,15 +11607,15 @@
       <c r="B49" s="58">
         <v>21</v>
       </c>
-      <c r="C49" s="333"/>
+      <c r="C49" s="340"/>
       <c r="D49" s="103" t="s">
         <v>55</v>
       </c>
-      <c r="E49" s="334" t="s">
-        <v>44</v>
-      </c>
-      <c r="F49" s="335"/>
-      <c r="G49" s="335"/>
+      <c r="E49" s="358" t="s">
+        <v>44</v>
+      </c>
+      <c r="F49" s="359"/>
+      <c r="G49" s="359"/>
       <c r="H49" s="104"/>
       <c r="I49" s="104"/>
       <c r="J49" s="81"/>
@@ -11634,11 +11634,11 @@
       <c r="D50" s="106" t="s">
         <v>44</v>
       </c>
-      <c r="E50" s="319" t="s">
+      <c r="E50" s="345" t="s">
         <v>206</v>
       </c>
-      <c r="F50" s="320"/>
-      <c r="G50" s="321"/>
+      <c r="F50" s="346"/>
+      <c r="G50" s="347"/>
       <c r="H50" s="72"/>
       <c r="I50" s="72"/>
       <c r="J50" s="81" t="e">
@@ -11661,11 +11661,11 @@
       <c r="D51" s="106" t="s">
         <v>44</v>
       </c>
-      <c r="E51" s="319" t="s">
-        <v>44</v>
-      </c>
-      <c r="F51" s="320"/>
-      <c r="G51" s="321"/>
+      <c r="E51" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="F51" s="346"/>
+      <c r="G51" s="347"/>
       <c r="H51" s="72"/>
       <c r="I51" s="72"/>
       <c r="J51" s="81"/>
@@ -11679,15 +11679,15 @@
       <c r="B52" s="58">
         <v>24</v>
       </c>
-      <c r="C52" s="332" t="s">
+      <c r="C52" s="339" t="s">
         <v>102</v>
       </c>
-      <c r="D52" s="323" t="s">
+      <c r="D52" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E52" s="324"/>
-      <c r="F52" s="324"/>
-      <c r="G52" s="325"/>
+      <c r="E52" s="337"/>
+      <c r="F52" s="337"/>
+      <c r="G52" s="338"/>
       <c r="H52" s="97"/>
       <c r="I52" s="97"/>
       <c r="J52" s="102"/>
@@ -11700,15 +11700,15 @@
       <c r="B53" s="58">
         <v>25</v>
       </c>
-      <c r="C53" s="333"/>
+      <c r="C53" s="340"/>
       <c r="D53" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E53" s="319" t="s">
+      <c r="E53" s="345" t="s">
         <v>13</v>
       </c>
-      <c r="F53" s="320"/>
-      <c r="G53" s="321"/>
+      <c r="F53" s="346"/>
+      <c r="G53" s="347"/>
       <c r="H53" s="72"/>
       <c r="I53" s="72"/>
       <c r="J53" s="81"/>
@@ -11727,11 +11727,11 @@
       <c r="D54" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E54" s="319" t="s">
+      <c r="E54" s="345" t="s">
         <v>207</v>
       </c>
-      <c r="F54" s="320"/>
-      <c r="G54" s="321"/>
+      <c r="F54" s="346"/>
+      <c r="G54" s="347"/>
       <c r="H54" s="72"/>
       <c r="I54" s="72"/>
       <c r="J54" s="81" t="e">
@@ -11748,15 +11748,15 @@
       <c r="B55" s="58">
         <v>30</v>
       </c>
-      <c r="C55" s="332" t="s">
+      <c r="C55" s="339" t="s">
         <v>16</v>
       </c>
-      <c r="D55" s="323" t="s">
+      <c r="D55" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E55" s="324"/>
-      <c r="F55" s="324"/>
-      <c r="G55" s="325"/>
+      <c r="E55" s="337"/>
+      <c r="F55" s="337"/>
+      <c r="G55" s="338"/>
       <c r="H55" s="97"/>
       <c r="I55" s="97"/>
       <c r="J55" s="102"/>
@@ -11769,15 +11769,15 @@
       <c r="B56" s="58">
         <v>31</v>
       </c>
-      <c r="C56" s="333"/>
+      <c r="C56" s="340"/>
       <c r="D56" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E56" s="319" t="s">
+      <c r="E56" s="345" t="s">
         <v>146</v>
       </c>
-      <c r="F56" s="320"/>
-      <c r="G56" s="321"/>
+      <c r="F56" s="346"/>
+      <c r="G56" s="347"/>
       <c r="H56" s="72"/>
       <c r="I56" s="72"/>
       <c r="J56" s="81"/>
@@ -11790,15 +11790,15 @@
       <c r="B57" s="58">
         <v>32</v>
       </c>
-      <c r="C57" s="333"/>
+      <c r="C57" s="340"/>
       <c r="D57" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E57" s="319" t="s">
+      <c r="E57" s="345" t="s">
         <v>147</v>
       </c>
-      <c r="F57" s="320"/>
-      <c r="G57" s="321"/>
+      <c r="F57" s="346"/>
+      <c r="G57" s="347"/>
       <c r="H57" s="72"/>
       <c r="I57" s="72"/>
       <c r="J57" s="81"/>
@@ -11817,11 +11817,11 @@
       <c r="D58" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E58" s="319" t="s">
+      <c r="E58" s="345" t="s">
         <v>148</v>
       </c>
-      <c r="F58" s="320"/>
-      <c r="G58" s="321"/>
+      <c r="F58" s="346"/>
+      <c r="G58" s="347"/>
       <c r="H58" s="72"/>
       <c r="I58" s="72"/>
       <c r="J58" s="81"/>
@@ -11840,11 +11840,11 @@
       <c r="D59" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E59" s="319" t="s">
-        <v>44</v>
-      </c>
-      <c r="F59" s="320"/>
-      <c r="G59" s="321"/>
+      <c r="E59" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="F59" s="346"/>
+      <c r="G59" s="347"/>
       <c r="H59" s="72"/>
       <c r="I59" s="72"/>
       <c r="J59" s="81"/>
@@ -11858,15 +11858,15 @@
       <c r="B60" s="58">
         <v>35</v>
       </c>
-      <c r="C60" s="332" t="s">
+      <c r="C60" s="339" t="s">
         <v>190</v>
       </c>
-      <c r="D60" s="323" t="s">
+      <c r="D60" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E60" s="324"/>
-      <c r="F60" s="324"/>
-      <c r="G60" s="325"/>
+      <c r="E60" s="337"/>
+      <c r="F60" s="337"/>
+      <c r="G60" s="338"/>
       <c r="H60" s="97"/>
       <c r="I60" s="97"/>
       <c r="J60" s="102"/>
@@ -11879,15 +11879,15 @@
       <c r="B61" s="58">
         <v>36</v>
       </c>
-      <c r="C61" s="333"/>
+      <c r="C61" s="340"/>
       <c r="D61" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E61" s="319" t="s">
+      <c r="E61" s="345" t="s">
         <v>128</v>
       </c>
-      <c r="F61" s="320"/>
-      <c r="G61" s="321"/>
+      <c r="F61" s="346"/>
+      <c r="G61" s="347"/>
       <c r="H61" s="72"/>
       <c r="I61" s="72"/>
       <c r="J61" s="81"/>
@@ -11900,15 +11900,15 @@
       <c r="B62" s="58">
         <v>37</v>
       </c>
-      <c r="C62" s="333"/>
+      <c r="C62" s="340"/>
       <c r="D62" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E62" s="319" t="s">
+      <c r="E62" s="345" t="s">
         <v>154</v>
       </c>
-      <c r="F62" s="320"/>
-      <c r="G62" s="321"/>
+      <c r="F62" s="346"/>
+      <c r="G62" s="347"/>
       <c r="H62" s="72"/>
       <c r="I62" s="72"/>
       <c r="J62" s="81"/>
@@ -11927,11 +11927,11 @@
       <c r="D63" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E63" s="319" t="s">
+      <c r="E63" s="345" t="s">
         <v>208</v>
       </c>
-      <c r="F63" s="320"/>
-      <c r="G63" s="321"/>
+      <c r="F63" s="346"/>
+      <c r="G63" s="347"/>
       <c r="H63" s="72"/>
       <c r="I63" s="72"/>
       <c r="J63" s="81"/>
@@ -11950,11 +11950,11 @@
       <c r="D64" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E64" s="319" t="s">
-        <v>44</v>
-      </c>
-      <c r="F64" s="320"/>
-      <c r="G64" s="321"/>
+      <c r="E64" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="F64" s="346"/>
+      <c r="G64" s="347"/>
       <c r="H64" s="72"/>
       <c r="I64" s="72"/>
       <c r="J64" s="81"/>
@@ -11968,15 +11968,15 @@
       <c r="B65" s="58">
         <v>40</v>
       </c>
-      <c r="C65" s="332" t="s">
+      <c r="C65" s="339" t="s">
         <v>14</v>
       </c>
-      <c r="D65" s="323" t="s">
+      <c r="D65" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E65" s="324"/>
-      <c r="F65" s="324"/>
-      <c r="G65" s="325"/>
+      <c r="E65" s="337"/>
+      <c r="F65" s="337"/>
+      <c r="G65" s="338"/>
       <c r="H65" s="97"/>
       <c r="I65" s="97"/>
       <c r="J65" s="102"/>
@@ -11989,17 +11989,17 @@
       <c r="B66" s="58">
         <v>41</v>
       </c>
-      <c r="C66" s="333"/>
+      <c r="C66" s="340"/>
       <c r="D66" s="66" t="s">
         <v>55</v>
       </c>
       <c r="E66" s="103" t="s">
         <v>209</v>
       </c>
-      <c r="F66" s="323" t="s">
+      <c r="F66" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="G66" s="325"/>
+      <c r="G66" s="338"/>
       <c r="H66" s="97"/>
       <c r="I66" s="97"/>
       <c r="J66" s="102"/>
@@ -12012,7 +12012,7 @@
       <c r="B67" s="58">
         <v>42</v>
       </c>
-      <c r="C67" s="333"/>
+      <c r="C67" s="340"/>
       <c r="D67" s="67" t="s">
         <v>44</v>
       </c>
@@ -12105,10 +12105,10 @@
       <c r="E70" s="103" t="s">
         <v>210</v>
       </c>
-      <c r="F70" s="323" t="s">
+      <c r="F70" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="G70" s="325"/>
+      <c r="G70" s="338"/>
       <c r="H70" s="97"/>
       <c r="I70" s="97"/>
       <c r="J70" s="102"/>
@@ -12277,10 +12277,10 @@
       <c r="E76" s="103" t="s">
         <v>214</v>
       </c>
-      <c r="F76" s="323" t="s">
+      <c r="F76" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="G76" s="325"/>
+      <c r="G76" s="338"/>
       <c r="H76" s="97"/>
       <c r="I76" s="97"/>
       <c r="J76" s="102"/>
@@ -12382,13 +12382,13 @@
       <c r="D80" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E80" s="344" t="s">
+      <c r="E80" s="360" t="s">
         <v>216</v>
       </c>
-      <c r="F80" s="323" t="s">
+      <c r="F80" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="G80" s="325"/>
+      <c r="G80" s="338"/>
       <c r="H80" s="97"/>
       <c r="I80" s="97"/>
       <c r="J80" s="102"/>
@@ -12408,15 +12408,15 @@
       <c r="D81" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E81" s="345"/>
+      <c r="E81" s="361"/>
       <c r="F81" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="G81" s="346" t="s">
+      <c r="G81" s="362" t="s">
         <v>136</v>
       </c>
-      <c r="H81" s="347"/>
-      <c r="I81" s="348"/>
+      <c r="H81" s="363"/>
+      <c r="I81" s="364"/>
       <c r="J81" s="81" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -12495,13 +12495,13 @@
       <c r="D84" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E84" s="344" t="s">
-        <v>44</v>
-      </c>
-      <c r="F84" s="323" t="s">
+      <c r="E84" s="360" t="s">
+        <v>44</v>
+      </c>
+      <c r="F84" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="G84" s="325"/>
+      <c r="G84" s="338"/>
       <c r="H84" s="97"/>
       <c r="I84" s="97"/>
       <c r="J84" s="102"/>
@@ -12521,7 +12521,7 @@
       <c r="D85" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E85" s="345"/>
+      <c r="E85" s="361"/>
       <c r="F85" s="66" t="s">
         <v>55</v>
       </c>
@@ -12570,15 +12570,15 @@
       <c r="B87" s="58">
         <v>62</v>
       </c>
-      <c r="C87" s="332" t="s">
+      <c r="C87" s="339" t="s">
         <v>144</v>
       </c>
-      <c r="D87" s="323" t="s">
+      <c r="D87" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E87" s="324"/>
-      <c r="F87" s="324"/>
-      <c r="G87" s="325"/>
+      <c r="E87" s="337"/>
+      <c r="F87" s="337"/>
+      <c r="G87" s="338"/>
       <c r="H87" s="97"/>
       <c r="I87" s="110"/>
       <c r="J87" s="102"/>
@@ -12591,15 +12591,15 @@
       <c r="B88" s="58">
         <v>63</v>
       </c>
-      <c r="C88" s="333"/>
+      <c r="C88" s="340"/>
       <c r="D88" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E88" s="334" t="s">
-        <v>44</v>
-      </c>
-      <c r="F88" s="335"/>
-      <c r="G88" s="335"/>
+      <c r="E88" s="358" t="s">
+        <v>44</v>
+      </c>
+      <c r="F88" s="359"/>
+      <c r="G88" s="359"/>
       <c r="H88" s="104"/>
       <c r="I88" s="104"/>
       <c r="J88" s="81" t="e">
@@ -12621,11 +12621,11 @@
       <c r="D89" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E89" s="319" t="s">
-        <v>44</v>
-      </c>
-      <c r="F89" s="320"/>
-      <c r="G89" s="321"/>
+      <c r="E89" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="F89" s="346"/>
+      <c r="G89" s="347"/>
       <c r="H89" s="72"/>
       <c r="I89" s="109"/>
       <c r="J89" s="81"/>
@@ -12645,11 +12645,11 @@
       <c r="D90" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E90" s="319" t="s">
-        <v>44</v>
-      </c>
-      <c r="F90" s="320"/>
-      <c r="G90" s="321"/>
+      <c r="E90" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="F90" s="346"/>
+      <c r="G90" s="347"/>
       <c r="H90" s="72"/>
       <c r="I90" s="109"/>
       <c r="J90" s="81"/>
@@ -12663,15 +12663,15 @@
       <c r="B91" s="58">
         <v>66</v>
       </c>
-      <c r="C91" s="332" t="s">
+      <c r="C91" s="339" t="s">
         <v>189</v>
       </c>
-      <c r="D91" s="323" t="s">
+      <c r="D91" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E91" s="324"/>
-      <c r="F91" s="324"/>
-      <c r="G91" s="325"/>
+      <c r="E91" s="337"/>
+      <c r="F91" s="337"/>
+      <c r="G91" s="338"/>
       <c r="H91" s="97"/>
       <c r="I91" s="110"/>
       <c r="J91" s="102"/>
@@ -12684,15 +12684,15 @@
       <c r="B92" s="58">
         <v>67</v>
       </c>
-      <c r="C92" s="333"/>
+      <c r="C92" s="340"/>
       <c r="D92" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E92" s="334" t="s">
-        <v>44</v>
-      </c>
-      <c r="F92" s="335"/>
-      <c r="G92" s="335"/>
+      <c r="E92" s="358" t="s">
+        <v>44</v>
+      </c>
+      <c r="F92" s="359"/>
+      <c r="G92" s="359"/>
       <c r="H92" s="104"/>
       <c r="I92" s="104"/>
       <c r="J92" s="81"/>
@@ -12711,11 +12711,11 @@
       <c r="D93" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E93" s="319" t="s">
-        <v>44</v>
-      </c>
-      <c r="F93" s="320"/>
-      <c r="G93" s="321"/>
+      <c r="E93" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="F93" s="346"/>
+      <c r="G93" s="347"/>
       <c r="H93" s="72"/>
       <c r="I93" s="109"/>
       <c r="J93" s="81"/>
@@ -12735,11 +12735,11 @@
       <c r="D94" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E94" s="319" t="s">
-        <v>44</v>
-      </c>
-      <c r="F94" s="320"/>
-      <c r="G94" s="321"/>
+      <c r="E94" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="F94" s="346"/>
+      <c r="G94" s="347"/>
       <c r="H94" s="72"/>
       <c r="I94" s="109"/>
       <c r="J94" s="81"/>
@@ -12753,15 +12753,15 @@
       <c r="B95" s="58">
         <v>70</v>
       </c>
-      <c r="C95" s="332" t="s">
+      <c r="C95" s="339" t="s">
         <v>137</v>
       </c>
-      <c r="D95" s="323" t="s">
+      <c r="D95" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E95" s="324"/>
-      <c r="F95" s="324"/>
-      <c r="G95" s="325"/>
+      <c r="E95" s="337"/>
+      <c r="F95" s="337"/>
+      <c r="G95" s="338"/>
       <c r="H95" s="97"/>
       <c r="I95" s="110"/>
       <c r="J95" s="102"/>
@@ -12774,15 +12774,15 @@
       <c r="B96" s="58">
         <v>71</v>
       </c>
-      <c r="C96" s="333"/>
+      <c r="C96" s="340"/>
       <c r="D96" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E96" s="334" t="s">
-        <v>44</v>
-      </c>
-      <c r="F96" s="335"/>
-      <c r="G96" s="335"/>
+      <c r="E96" s="358" t="s">
+        <v>44</v>
+      </c>
+      <c r="F96" s="359"/>
+      <c r="G96" s="359"/>
       <c r="H96" s="104"/>
       <c r="I96" s="104"/>
       <c r="J96" s="81"/>
@@ -12801,11 +12801,11 @@
       <c r="D97" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E97" s="319" t="s">
+      <c r="E97" s="345" t="s">
         <v>217</v>
       </c>
-      <c r="F97" s="320"/>
-      <c r="G97" s="321"/>
+      <c r="F97" s="346"/>
+      <c r="G97" s="347"/>
       <c r="H97" s="72"/>
       <c r="I97" s="109"/>
       <c r="J97" s="81" t="e">
@@ -12820,11 +12820,11 @@
       <c r="B98" s="58"/>
       <c r="C98" s="77"/>
       <c r="D98" s="70"/>
-      <c r="E98" s="319" t="s">
+      <c r="E98" s="345" t="s">
         <v>218</v>
       </c>
-      <c r="F98" s="320"/>
-      <c r="G98" s="321"/>
+      <c r="F98" s="346"/>
+      <c r="G98" s="347"/>
       <c r="H98" s="72"/>
       <c r="I98" s="109"/>
       <c r="J98" s="81"/>
@@ -12836,9 +12836,9 @@
       <c r="B99" s="58"/>
       <c r="C99" s="77"/>
       <c r="D99" s="70"/>
-      <c r="E99" s="319"/>
-      <c r="F99" s="320"/>
-      <c r="G99" s="321"/>
+      <c r="E99" s="345"/>
+      <c r="F99" s="346"/>
+      <c r="G99" s="347"/>
       <c r="H99" s="72"/>
       <c r="I99" s="109"/>
       <c r="J99" s="81"/>
@@ -12858,11 +12858,11 @@
       <c r="D100" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E100" s="319" t="s">
-        <v>44</v>
-      </c>
-      <c r="F100" s="320"/>
-      <c r="G100" s="321"/>
+      <c r="E100" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="F100" s="346"/>
+      <c r="G100" s="347"/>
       <c r="H100" s="72"/>
       <c r="I100" s="109"/>
       <c r="J100" s="81"/>
@@ -12876,15 +12876,15 @@
       <c r="B101" s="58">
         <v>75</v>
       </c>
-      <c r="C101" s="332" t="s">
+      <c r="C101" s="339" t="s">
         <v>17</v>
       </c>
-      <c r="D101" s="323" t="s">
+      <c r="D101" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E101" s="324"/>
-      <c r="F101" s="324"/>
-      <c r="G101" s="325"/>
+      <c r="E101" s="337"/>
+      <c r="F101" s="337"/>
+      <c r="G101" s="338"/>
       <c r="H101" s="97"/>
       <c r="I101" s="111">
         <f>I102+I103+I104</f>
@@ -12900,15 +12900,15 @@
       <c r="B102" s="58">
         <v>76</v>
       </c>
-      <c r="C102" s="333"/>
+      <c r="C102" s="340"/>
       <c r="D102" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E102" s="336" t="s">
+      <c r="E102" s="355" t="s">
         <v>219</v>
       </c>
-      <c r="F102" s="337"/>
-      <c r="G102" s="338"/>
+      <c r="F102" s="356"/>
+      <c r="G102" s="357"/>
       <c r="H102" s="72"/>
       <c r="I102" s="109"/>
       <c r="J102" s="81">
@@ -12924,15 +12924,15 @@
       <c r="B103" s="58">
         <v>77</v>
       </c>
-      <c r="C103" s="333"/>
+      <c r="C103" s="340"/>
       <c r="D103" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E103" s="336" t="s">
+      <c r="E103" s="355" t="s">
         <v>220</v>
       </c>
-      <c r="F103" s="337"/>
-      <c r="G103" s="338"/>
+      <c r="F103" s="356"/>
+      <c r="G103" s="357"/>
       <c r="H103" s="72"/>
       <c r="I103" s="72"/>
       <c r="J103" s="81">
@@ -12954,11 +12954,11 @@
       <c r="D104" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E104" s="336" t="s">
+      <c r="E104" s="355" t="s">
         <v>221</v>
       </c>
-      <c r="F104" s="337"/>
-      <c r="G104" s="338"/>
+      <c r="F104" s="356"/>
+      <c r="G104" s="357"/>
       <c r="H104" s="72"/>
       <c r="I104" s="72"/>
       <c r="J104" s="81">
@@ -12974,13 +12974,13 @@
       <c r="B105" s="58">
         <v>83</v>
       </c>
-      <c r="C105" s="323" t="s">
+      <c r="C105" s="336" t="s">
         <v>7</v>
       </c>
-      <c r="D105" s="324"/>
-      <c r="E105" s="324"/>
-      <c r="F105" s="324"/>
-      <c r="G105" s="325"/>
+      <c r="D105" s="337"/>
+      <c r="E105" s="337"/>
+      <c r="F105" s="337"/>
+      <c r="G105" s="338"/>
       <c r="H105" s="97"/>
       <c r="I105" s="97"/>
       <c r="J105" s="102" t="e">
@@ -12996,13 +12996,13 @@
       <c r="B106" s="58">
         <v>84</v>
       </c>
-      <c r="C106" s="323" t="s">
+      <c r="C106" s="336" t="s">
         <v>222</v>
       </c>
-      <c r="D106" s="324"/>
-      <c r="E106" s="324"/>
-      <c r="F106" s="324"/>
-      <c r="G106" s="325"/>
+      <c r="D106" s="337"/>
+      <c r="E106" s="337"/>
+      <c r="F106" s="337"/>
+      <c r="G106" s="338"/>
       <c r="H106" s="97"/>
       <c r="I106" s="101"/>
       <c r="J106" s="102" t="e">
@@ -13018,15 +13018,15 @@
       <c r="B107" s="58">
         <v>85</v>
       </c>
-      <c r="C107" s="332" t="s">
+      <c r="C107" s="339" t="s">
         <v>223</v>
       </c>
-      <c r="D107" s="323" t="s">
+      <c r="D107" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E107" s="324"/>
-      <c r="F107" s="324"/>
-      <c r="G107" s="325"/>
+      <c r="E107" s="337"/>
+      <c r="F107" s="337"/>
+      <c r="G107" s="338"/>
       <c r="H107" s="97"/>
       <c r="I107" s="97"/>
       <c r="J107" s="102"/>
@@ -13039,15 +13039,15 @@
       <c r="B108" s="58">
         <v>86</v>
       </c>
-      <c r="C108" s="333"/>
+      <c r="C108" s="340"/>
       <c r="D108" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E108" s="336" t="s">
+      <c r="E108" s="355" t="s">
         <v>224</v>
       </c>
-      <c r="F108" s="337"/>
-      <c r="G108" s="338"/>
+      <c r="F108" s="356"/>
+      <c r="G108" s="357"/>
       <c r="H108" s="72"/>
       <c r="I108" s="63"/>
       <c r="J108" s="81" t="e">
@@ -13069,11 +13069,11 @@
       <c r="D109" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E109" s="319" t="s">
+      <c r="E109" s="345" t="s">
         <v>225</v>
       </c>
-      <c r="F109" s="320"/>
-      <c r="G109" s="321"/>
+      <c r="F109" s="346"/>
+      <c r="G109" s="347"/>
       <c r="H109" s="72"/>
       <c r="I109" s="63"/>
       <c r="J109" s="81"/>
@@ -13093,11 +13093,11 @@
       <c r="D110" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E110" s="319" t="s">
-        <v>44</v>
-      </c>
-      <c r="F110" s="320"/>
-      <c r="G110" s="321"/>
+      <c r="E110" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="F110" s="346"/>
+      <c r="G110" s="347"/>
       <c r="H110" s="72"/>
       <c r="I110" s="72"/>
       <c r="J110" s="81"/>
@@ -13111,15 +13111,15 @@
       <c r="B111" s="58">
         <v>89</v>
       </c>
-      <c r="C111" s="332" t="s">
+      <c r="C111" s="339" t="s">
         <v>192</v>
       </c>
-      <c r="D111" s="323" t="s">
+      <c r="D111" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E111" s="324"/>
-      <c r="F111" s="324"/>
-      <c r="G111" s="325"/>
+      <c r="E111" s="337"/>
+      <c r="F111" s="337"/>
+      <c r="G111" s="338"/>
       <c r="H111" s="97"/>
       <c r="I111" s="97"/>
       <c r="J111" s="102"/>
@@ -13132,15 +13132,15 @@
       <c r="B112" s="58">
         <v>90</v>
       </c>
-      <c r="C112" s="333"/>
+      <c r="C112" s="340"/>
       <c r="D112" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E112" s="336" t="s">
+      <c r="E112" s="355" t="s">
         <v>226</v>
       </c>
-      <c r="F112" s="337"/>
-      <c r="G112" s="338"/>
+      <c r="F112" s="356"/>
+      <c r="G112" s="357"/>
       <c r="H112" s="72"/>
       <c r="I112" s="72"/>
       <c r="J112" s="81"/>
@@ -13159,11 +13159,11 @@
       <c r="D113" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E113" s="319" t="s">
-        <v>44</v>
-      </c>
-      <c r="F113" s="320"/>
-      <c r="G113" s="321"/>
+      <c r="E113" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="F113" s="346"/>
+      <c r="G113" s="347"/>
       <c r="H113" s="72"/>
       <c r="I113" s="72"/>
       <c r="J113" s="81"/>
@@ -13176,15 +13176,15 @@
       <c r="B114" s="58">
         <v>92</v>
       </c>
-      <c r="C114" s="332" t="s">
+      <c r="C114" s="339" t="s">
         <v>191</v>
       </c>
-      <c r="D114" s="323" t="s">
+      <c r="D114" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E114" s="324"/>
-      <c r="F114" s="324"/>
-      <c r="G114" s="325"/>
+      <c r="E114" s="337"/>
+      <c r="F114" s="337"/>
+      <c r="G114" s="338"/>
       <c r="H114" s="97"/>
       <c r="I114" s="97"/>
       <c r="J114" s="102"/>
@@ -13197,15 +13197,15 @@
       <c r="B115" s="58">
         <v>93</v>
       </c>
-      <c r="C115" s="333"/>
+      <c r="C115" s="340"/>
       <c r="D115" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E115" s="334" t="s">
-        <v>44</v>
-      </c>
-      <c r="F115" s="335"/>
-      <c r="G115" s="335"/>
+      <c r="E115" s="358" t="s">
+        <v>44</v>
+      </c>
+      <c r="F115" s="359"/>
+      <c r="G115" s="359"/>
       <c r="H115" s="104"/>
       <c r="I115" s="104"/>
       <c r="J115" s="112"/>
@@ -13224,11 +13224,11 @@
       <c r="D116" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E116" s="319" t="s">
-        <v>44</v>
-      </c>
-      <c r="F116" s="320"/>
-      <c r="G116" s="321"/>
+      <c r="E116" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="F116" s="346"/>
+      <c r="G116" s="347"/>
       <c r="H116" s="72"/>
       <c r="I116" s="63"/>
       <c r="J116" s="81"/>
@@ -13248,11 +13248,11 @@
       <c r="D117" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E117" s="319" t="s">
-        <v>44</v>
-      </c>
-      <c r="F117" s="320"/>
-      <c r="G117" s="321"/>
+      <c r="E117" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="F117" s="346"/>
+      <c r="G117" s="347"/>
       <c r="H117" s="72"/>
       <c r="I117" s="72"/>
       <c r="J117" s="81"/>
@@ -13266,15 +13266,15 @@
       <c r="B118" s="58">
         <v>96</v>
       </c>
-      <c r="C118" s="332" t="s">
+      <c r="C118" s="339" t="s">
         <v>149</v>
       </c>
-      <c r="D118" s="323" t="s">
+      <c r="D118" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E118" s="324"/>
-      <c r="F118" s="324"/>
-      <c r="G118" s="325"/>
+      <c r="E118" s="337"/>
+      <c r="F118" s="337"/>
+      <c r="G118" s="338"/>
       <c r="H118" s="97"/>
       <c r="I118" s="97"/>
       <c r="J118" s="102"/>
@@ -13287,15 +13287,15 @@
       <c r="B119" s="58">
         <v>97</v>
       </c>
-      <c r="C119" s="333"/>
+      <c r="C119" s="340"/>
       <c r="D119" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E119" s="336" t="s">
+      <c r="E119" s="355" t="s">
         <v>227</v>
       </c>
-      <c r="F119" s="337"/>
-      <c r="G119" s="338"/>
+      <c r="F119" s="356"/>
+      <c r="G119" s="357"/>
       <c r="H119" s="72"/>
       <c r="I119" s="72"/>
       <c r="J119" s="81"/>
@@ -13314,11 +13314,11 @@
       <c r="D120" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E120" s="336" t="s">
+      <c r="E120" s="355" t="s">
         <v>228</v>
       </c>
-      <c r="F120" s="337"/>
-      <c r="G120" s="338"/>
+      <c r="F120" s="356"/>
+      <c r="G120" s="357"/>
       <c r="H120" s="72"/>
       <c r="I120" s="72"/>
       <c r="J120" s="81"/>
@@ -13337,11 +13337,11 @@
       <c r="D121" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E121" s="336" t="s">
+      <c r="E121" s="355" t="s">
         <v>229</v>
       </c>
-      <c r="F121" s="337"/>
-      <c r="G121" s="338"/>
+      <c r="F121" s="356"/>
+      <c r="G121" s="357"/>
       <c r="H121" s="72"/>
       <c r="I121" s="72"/>
       <c r="J121" s="81"/>
@@ -13360,11 +13360,11 @@
       <c r="D122" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E122" s="319" t="s">
-        <v>44</v>
-      </c>
-      <c r="F122" s="320"/>
-      <c r="G122" s="321"/>
+      <c r="E122" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="F122" s="346"/>
+      <c r="G122" s="347"/>
       <c r="H122" s="72"/>
       <c r="I122" s="72"/>
       <c r="J122" s="81"/>
@@ -13378,15 +13378,15 @@
       <c r="B123" s="58">
         <v>101</v>
       </c>
-      <c r="C123" s="332" t="s">
+      <c r="C123" s="339" t="s">
         <v>230</v>
       </c>
-      <c r="D123" s="323" t="s">
+      <c r="D123" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E123" s="324"/>
-      <c r="F123" s="324"/>
-      <c r="G123" s="325"/>
+      <c r="E123" s="337"/>
+      <c r="F123" s="337"/>
+      <c r="G123" s="338"/>
       <c r="H123" s="97"/>
       <c r="I123" s="97"/>
       <c r="J123" s="102"/>
@@ -13399,17 +13399,17 @@
       <c r="B124" s="58">
         <v>102</v>
       </c>
-      <c r="C124" s="333"/>
+      <c r="C124" s="340"/>
       <c r="D124" s="66" t="s">
         <v>55</v>
       </c>
       <c r="E124" s="342" t="s">
         <v>231</v>
       </c>
-      <c r="F124" s="323" t="s">
+      <c r="F124" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="G124" s="325"/>
+      <c r="G124" s="338"/>
       <c r="H124" s="97"/>
       <c r="I124" s="97"/>
       <c r="J124" s="102"/>
@@ -13422,7 +13422,7 @@
       <c r="B125" s="58">
         <v>103</v>
       </c>
-      <c r="C125" s="333"/>
+      <c r="C125" s="340"/>
       <c r="D125" s="67" t="s">
         <v>44</v>
       </c>
@@ -13445,7 +13445,7 @@
       <c r="B126" s="58">
         <v>104</v>
       </c>
-      <c r="C126" s="333"/>
+      <c r="C126" s="340"/>
       <c r="D126" s="67" t="s">
         <v>44</v>
       </c>
@@ -13531,11 +13531,11 @@
       <c r="D129" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E129" s="336" t="s">
+      <c r="E129" s="355" t="s">
         <v>234</v>
       </c>
-      <c r="F129" s="337"/>
-      <c r="G129" s="338"/>
+      <c r="F129" s="356"/>
+      <c r="G129" s="357"/>
       <c r="H129" s="72"/>
       <c r="I129" s="72"/>
       <c r="J129" s="81"/>
@@ -13554,11 +13554,11 @@
       <c r="D130" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E130" s="319" t="s">
-        <v>44</v>
-      </c>
-      <c r="F130" s="320"/>
-      <c r="G130" s="321"/>
+      <c r="E130" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="F130" s="346"/>
+      <c r="G130" s="347"/>
       <c r="H130" s="72"/>
       <c r="I130" s="72"/>
       <c r="J130" s="81"/>
@@ -13572,15 +13572,15 @@
       <c r="B131" s="58">
         <v>109</v>
       </c>
-      <c r="C131" s="332" t="s">
+      <c r="C131" s="339" t="s">
         <v>175</v>
       </c>
-      <c r="D131" s="323" t="s">
+      <c r="D131" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E131" s="324"/>
-      <c r="F131" s="324"/>
-      <c r="G131" s="325"/>
+      <c r="E131" s="337"/>
+      <c r="F131" s="337"/>
+      <c r="G131" s="338"/>
       <c r="H131" s="97"/>
       <c r="I131" s="101">
         <f>SUM(I132:I136)</f>
@@ -13596,15 +13596,15 @@
       <c r="B132" s="58">
         <v>110</v>
       </c>
-      <c r="C132" s="333"/>
+      <c r="C132" s="340"/>
       <c r="D132" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E132" s="336" t="s">
+      <c r="E132" s="355" t="s">
         <v>91</v>
       </c>
-      <c r="F132" s="337"/>
-      <c r="G132" s="338"/>
+      <c r="F132" s="356"/>
+      <c r="G132" s="357"/>
       <c r="H132" s="72"/>
       <c r="I132" s="72"/>
       <c r="J132" s="81" t="e">
@@ -13620,15 +13620,15 @@
       <c r="B133" s="58">
         <v>111</v>
       </c>
-      <c r="C133" s="333"/>
+      <c r="C133" s="340"/>
       <c r="D133" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E133" s="336" t="s">
+      <c r="E133" s="355" t="s">
         <v>235</v>
       </c>
-      <c r="F133" s="337"/>
-      <c r="G133" s="338"/>
+      <c r="F133" s="356"/>
+      <c r="G133" s="357"/>
       <c r="H133" s="72"/>
       <c r="I133" s="72"/>
       <c r="J133" s="81" t="e">
@@ -13650,11 +13650,11 @@
       <c r="D134" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E134" s="336" t="s">
+      <c r="E134" s="355" t="s">
         <v>11</v>
       </c>
-      <c r="F134" s="337"/>
-      <c r="G134" s="338"/>
+      <c r="F134" s="356"/>
+      <c r="G134" s="357"/>
       <c r="H134" s="72"/>
       <c r="I134" s="72"/>
       <c r="J134" s="81" t="e">
@@ -13676,11 +13676,11 @@
       <c r="D135" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E135" s="336" t="s">
+      <c r="E135" s="355" t="s">
         <v>9</v>
       </c>
-      <c r="F135" s="337"/>
-      <c r="G135" s="338"/>
+      <c r="F135" s="356"/>
+      <c r="G135" s="357"/>
       <c r="H135" s="72"/>
       <c r="I135" s="72"/>
       <c r="J135" s="81" t="e">
@@ -13702,11 +13702,11 @@
       <c r="D136" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="E136" s="329" t="s">
+      <c r="E136" s="352" t="s">
         <v>236</v>
       </c>
-      <c r="F136" s="329"/>
-      <c r="G136" s="329"/>
+      <c r="F136" s="352"/>
+      <c r="G136" s="352"/>
       <c r="H136" s="72"/>
       <c r="I136" s="72"/>
       <c r="J136" s="81" t="e">
@@ -13729,11 +13729,11 @@
       <c r="D137" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E137" s="339" t="s">
-        <v>44</v>
-      </c>
-      <c r="F137" s="340"/>
-      <c r="G137" s="341"/>
+      <c r="E137" s="365" t="s">
+        <v>44</v>
+      </c>
+      <c r="F137" s="366"/>
+      <c r="G137" s="367"/>
       <c r="H137" s="115"/>
       <c r="I137" s="115"/>
       <c r="J137" s="116"/>
@@ -13747,15 +13747,15 @@
       <c r="B138" s="58">
         <v>118</v>
       </c>
-      <c r="C138" s="332" t="s">
+      <c r="C138" s="339" t="s">
         <v>237</v>
       </c>
-      <c r="D138" s="323" t="s">
+      <c r="D138" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E138" s="324"/>
-      <c r="F138" s="324"/>
-      <c r="G138" s="325"/>
+      <c r="E138" s="337"/>
+      <c r="F138" s="337"/>
+      <c r="G138" s="338"/>
       <c r="H138" s="97"/>
       <c r="I138" s="117"/>
       <c r="J138" s="118"/>
@@ -13768,15 +13768,15 @@
       <c r="B139" s="58">
         <v>119</v>
       </c>
-      <c r="C139" s="333"/>
+      <c r="C139" s="340"/>
       <c r="D139" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E139" s="336" t="s">
+      <c r="E139" s="355" t="s">
         <v>19</v>
       </c>
-      <c r="F139" s="337"/>
-      <c r="G139" s="338"/>
+      <c r="F139" s="356"/>
+      <c r="G139" s="357"/>
       <c r="H139" s="109"/>
       <c r="I139" s="113"/>
       <c r="J139" s="81" t="e">
@@ -13801,10 +13801,10 @@
       <c r="E140" s="66" t="s">
         <v>95</v>
       </c>
-      <c r="F140" s="323" t="s">
+      <c r="F140" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="G140" s="325"/>
+      <c r="G140" s="338"/>
       <c r="H140" s="110"/>
       <c r="I140" s="97"/>
       <c r="J140" s="102"/>
@@ -13826,7 +13826,7 @@
       <c r="E141" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="F141" s="330" t="s">
+      <c r="F141" s="372" t="s">
         <v>55</v>
       </c>
       <c r="G141" s="108" t="s">
@@ -13853,7 +13853,7 @@
       <c r="E142" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F142" s="331"/>
+      <c r="F142" s="373"/>
       <c r="G142" s="60" t="s">
         <v>238</v>
       </c>
@@ -13904,10 +13904,10 @@
       <c r="E144" s="66" t="s">
         <v>97</v>
       </c>
-      <c r="F144" s="323" t="s">
+      <c r="F144" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="G144" s="325"/>
+      <c r="G144" s="338"/>
       <c r="H144" s="97"/>
       <c r="I144" s="110"/>
       <c r="J144" s="102"/>
@@ -13929,7 +13929,7 @@
       <c r="E145" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="F145" s="330" t="s">
+      <c r="F145" s="372" t="s">
         <v>55</v>
       </c>
       <c r="G145" s="108" t="s">
@@ -13956,7 +13956,7 @@
       <c r="E146" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F146" s="331"/>
+      <c r="F146" s="373"/>
       <c r="G146" s="60" t="s">
         <v>18</v>
       </c>
@@ -14026,15 +14026,15 @@
       <c r="B149" s="58">
         <v>129</v>
       </c>
-      <c r="C149" s="332" t="s">
+      <c r="C149" s="339" t="s">
         <v>239</v>
       </c>
-      <c r="D149" s="323" t="s">
+      <c r="D149" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E149" s="324"/>
-      <c r="F149" s="324"/>
-      <c r="G149" s="325"/>
+      <c r="E149" s="337"/>
+      <c r="F149" s="337"/>
+      <c r="G149" s="338"/>
       <c r="H149" s="97"/>
       <c r="I149" s="110"/>
       <c r="J149" s="102"/>
@@ -14047,15 +14047,15 @@
       <c r="B150" s="121">
         <v>130</v>
       </c>
-      <c r="C150" s="333"/>
+      <c r="C150" s="340"/>
       <c r="D150" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E150" s="334" t="s">
-        <v>44</v>
-      </c>
-      <c r="F150" s="335"/>
-      <c r="G150" s="335"/>
+      <c r="E150" s="358" t="s">
+        <v>44</v>
+      </c>
+      <c r="F150" s="359"/>
+      <c r="G150" s="359"/>
       <c r="H150" s="104"/>
       <c r="I150" s="104"/>
       <c r="J150" s="81"/>
@@ -14074,11 +14074,11 @@
       <c r="D151" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E151" s="319" t="s">
-        <v>44</v>
-      </c>
-      <c r="F151" s="320"/>
-      <c r="G151" s="321"/>
+      <c r="E151" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="F151" s="346"/>
+      <c r="G151" s="347"/>
       <c r="H151" s="72"/>
       <c r="I151" s="109"/>
       <c r="J151" s="81"/>
@@ -14092,15 +14092,15 @@
       <c r="B152" s="58">
         <v>132</v>
       </c>
-      <c r="C152" s="322" t="s">
+      <c r="C152" s="368" t="s">
         <v>240</v>
       </c>
-      <c r="D152" s="323" t="s">
+      <c r="D152" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E152" s="324"/>
-      <c r="F152" s="324"/>
-      <c r="G152" s="325"/>
+      <c r="E152" s="337"/>
+      <c r="F152" s="337"/>
+      <c r="G152" s="338"/>
       <c r="H152" s="97"/>
       <c r="I152" s="110"/>
       <c r="J152" s="102"/>
@@ -14113,15 +14113,15 @@
       <c r="B153" s="58">
         <v>133</v>
       </c>
-      <c r="C153" s="322"/>
+      <c r="C153" s="368"/>
       <c r="D153" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E153" s="326" t="s">
+      <c r="E153" s="369" t="s">
         <v>241</v>
       </c>
-      <c r="F153" s="327"/>
-      <c r="G153" s="328"/>
+      <c r="F153" s="370"/>
+      <c r="G153" s="371"/>
       <c r="H153" s="122"/>
       <c r="I153" s="123"/>
       <c r="J153" s="81"/>
@@ -14140,11 +14140,11 @@
       <c r="D154" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="E154" s="329" t="s">
+      <c r="E154" s="352" t="s">
         <v>198</v>
       </c>
-      <c r="F154" s="329"/>
-      <c r="G154" s="329"/>
+      <c r="F154" s="352"/>
+      <c r="G154" s="352"/>
       <c r="H154" s="72"/>
       <c r="I154" s="120" t="e">
         <f>SUM(#REF!)</f>
@@ -14170,15 +14170,120 @@
     </row>
   </sheetData>
   <mergeCells count="142">
-    <mergeCell ref="B1:J1"/>
-    <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B4:J4"/>
-    <mergeCell ref="B5:J5"/>
-    <mergeCell ref="B6:J6"/>
-    <mergeCell ref="B7:H7"/>
-    <mergeCell ref="B22:B24"/>
-    <mergeCell ref="C22:G24"/>
-    <mergeCell ref="I22:J24"/>
+    <mergeCell ref="E151:G151"/>
+    <mergeCell ref="C152:C153"/>
+    <mergeCell ref="D152:G152"/>
+    <mergeCell ref="E153:G153"/>
+    <mergeCell ref="E154:G154"/>
+    <mergeCell ref="F140:G140"/>
+    <mergeCell ref="F141:F142"/>
+    <mergeCell ref="F144:G144"/>
+    <mergeCell ref="F145:F146"/>
+    <mergeCell ref="C149:C150"/>
+    <mergeCell ref="D149:G149"/>
+    <mergeCell ref="E150:G150"/>
+    <mergeCell ref="E134:G134"/>
+    <mergeCell ref="E135:G135"/>
+    <mergeCell ref="E136:G136"/>
+    <mergeCell ref="E137:G137"/>
+    <mergeCell ref="C138:C139"/>
+    <mergeCell ref="D138:G138"/>
+    <mergeCell ref="E139:G139"/>
+    <mergeCell ref="E129:G129"/>
+    <mergeCell ref="E130:G130"/>
+    <mergeCell ref="C131:C133"/>
+    <mergeCell ref="D131:G131"/>
+    <mergeCell ref="E132:G132"/>
+    <mergeCell ref="E133:G133"/>
+    <mergeCell ref="E121:G121"/>
+    <mergeCell ref="E122:G122"/>
+    <mergeCell ref="C123:C126"/>
+    <mergeCell ref="D123:G123"/>
+    <mergeCell ref="E124:E125"/>
+    <mergeCell ref="F124:G124"/>
+    <mergeCell ref="E116:G116"/>
+    <mergeCell ref="E117:G117"/>
+    <mergeCell ref="C118:C119"/>
+    <mergeCell ref="D118:G118"/>
+    <mergeCell ref="E119:G119"/>
+    <mergeCell ref="E120:G120"/>
+    <mergeCell ref="C111:C112"/>
+    <mergeCell ref="D111:G111"/>
+    <mergeCell ref="E112:G112"/>
+    <mergeCell ref="E113:G113"/>
+    <mergeCell ref="C114:C115"/>
+    <mergeCell ref="D114:G114"/>
+    <mergeCell ref="E115:G115"/>
+    <mergeCell ref="C106:G106"/>
+    <mergeCell ref="C107:C108"/>
+    <mergeCell ref="D107:G107"/>
+    <mergeCell ref="E108:G108"/>
+    <mergeCell ref="E109:G109"/>
+    <mergeCell ref="E110:G110"/>
+    <mergeCell ref="E104:G104"/>
+    <mergeCell ref="C105:G105"/>
+    <mergeCell ref="E98:G98"/>
+    <mergeCell ref="E99:G99"/>
+    <mergeCell ref="E100:G100"/>
+    <mergeCell ref="C101:C103"/>
+    <mergeCell ref="D101:G101"/>
+    <mergeCell ref="E102:G102"/>
+    <mergeCell ref="E103:G103"/>
+    <mergeCell ref="E93:G93"/>
+    <mergeCell ref="E94:G94"/>
+    <mergeCell ref="C95:C96"/>
+    <mergeCell ref="D95:G95"/>
+    <mergeCell ref="E96:G96"/>
+    <mergeCell ref="E97:G97"/>
+    <mergeCell ref="C87:C88"/>
+    <mergeCell ref="D87:G87"/>
+    <mergeCell ref="E88:G88"/>
+    <mergeCell ref="E89:G89"/>
+    <mergeCell ref="E90:G90"/>
+    <mergeCell ref="C91:C92"/>
+    <mergeCell ref="D91:G91"/>
+    <mergeCell ref="E92:G92"/>
+    <mergeCell ref="F76:G76"/>
+    <mergeCell ref="E80:E81"/>
+    <mergeCell ref="F80:G80"/>
+    <mergeCell ref="G81:I81"/>
+    <mergeCell ref="E84:E85"/>
+    <mergeCell ref="F84:G84"/>
+    <mergeCell ref="E63:G63"/>
+    <mergeCell ref="E64:G64"/>
+    <mergeCell ref="C65:C67"/>
+    <mergeCell ref="D65:G65"/>
+    <mergeCell ref="F66:G66"/>
+    <mergeCell ref="F70:G70"/>
+    <mergeCell ref="E58:G58"/>
+    <mergeCell ref="E59:G59"/>
+    <mergeCell ref="C60:C62"/>
+    <mergeCell ref="D60:G60"/>
+    <mergeCell ref="E61:G61"/>
+    <mergeCell ref="E62:G62"/>
+    <mergeCell ref="E54:G54"/>
+    <mergeCell ref="C55:C57"/>
+    <mergeCell ref="D55:G55"/>
+    <mergeCell ref="E56:G56"/>
+    <mergeCell ref="E57:G57"/>
+    <mergeCell ref="C48:C49"/>
+    <mergeCell ref="D48:G48"/>
+    <mergeCell ref="E49:G49"/>
+    <mergeCell ref="E50:G50"/>
+    <mergeCell ref="E51:G51"/>
+    <mergeCell ref="C52:C53"/>
+    <mergeCell ref="D52:G52"/>
+    <mergeCell ref="E53:G53"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="D42:G42"/>
+    <mergeCell ref="D43:D44"/>
+    <mergeCell ref="E43:G43"/>
+    <mergeCell ref="E44:G44"/>
+    <mergeCell ref="C45:C47"/>
+    <mergeCell ref="D45:G45"/>
+    <mergeCell ref="D46:D47"/>
+    <mergeCell ref="E46:G46"/>
+    <mergeCell ref="E47:G47"/>
     <mergeCell ref="C29:G29"/>
     <mergeCell ref="C30:C34"/>
     <mergeCell ref="D30:G30"/>
@@ -14198,120 +14303,15 @@
     <mergeCell ref="D36:D37"/>
     <mergeCell ref="E36:G36"/>
     <mergeCell ref="E37:G37"/>
-    <mergeCell ref="C48:C49"/>
-    <mergeCell ref="D48:G48"/>
-    <mergeCell ref="E49:G49"/>
-    <mergeCell ref="E50:G50"/>
-    <mergeCell ref="E51:G51"/>
-    <mergeCell ref="C52:C53"/>
-    <mergeCell ref="D52:G52"/>
-    <mergeCell ref="E53:G53"/>
-    <mergeCell ref="C42:C44"/>
-    <mergeCell ref="D42:G42"/>
-    <mergeCell ref="D43:D44"/>
-    <mergeCell ref="E43:G43"/>
-    <mergeCell ref="E44:G44"/>
-    <mergeCell ref="C45:C47"/>
-    <mergeCell ref="D45:G45"/>
-    <mergeCell ref="D46:D47"/>
-    <mergeCell ref="E46:G46"/>
-    <mergeCell ref="E47:G47"/>
-    <mergeCell ref="E58:G58"/>
-    <mergeCell ref="E59:G59"/>
-    <mergeCell ref="C60:C62"/>
-    <mergeCell ref="D60:G60"/>
-    <mergeCell ref="E61:G61"/>
-    <mergeCell ref="E62:G62"/>
-    <mergeCell ref="E54:G54"/>
-    <mergeCell ref="C55:C57"/>
-    <mergeCell ref="D55:G55"/>
-    <mergeCell ref="E56:G56"/>
-    <mergeCell ref="E57:G57"/>
-    <mergeCell ref="F76:G76"/>
-    <mergeCell ref="E80:E81"/>
-    <mergeCell ref="F80:G80"/>
-    <mergeCell ref="G81:I81"/>
-    <mergeCell ref="E84:E85"/>
-    <mergeCell ref="F84:G84"/>
-    <mergeCell ref="E63:G63"/>
-    <mergeCell ref="E64:G64"/>
-    <mergeCell ref="C65:C67"/>
-    <mergeCell ref="D65:G65"/>
-    <mergeCell ref="F66:G66"/>
-    <mergeCell ref="F70:G70"/>
-    <mergeCell ref="E93:G93"/>
-    <mergeCell ref="E94:G94"/>
-    <mergeCell ref="C95:C96"/>
-    <mergeCell ref="D95:G95"/>
-    <mergeCell ref="E96:G96"/>
-    <mergeCell ref="E97:G97"/>
-    <mergeCell ref="C87:C88"/>
-    <mergeCell ref="D87:G87"/>
-    <mergeCell ref="E88:G88"/>
-    <mergeCell ref="E89:G89"/>
-    <mergeCell ref="E90:G90"/>
-    <mergeCell ref="C91:C92"/>
-    <mergeCell ref="D91:G91"/>
-    <mergeCell ref="E92:G92"/>
-    <mergeCell ref="E104:G104"/>
-    <mergeCell ref="C105:G105"/>
-    <mergeCell ref="E98:G98"/>
-    <mergeCell ref="E99:G99"/>
-    <mergeCell ref="E100:G100"/>
-    <mergeCell ref="C101:C103"/>
-    <mergeCell ref="D101:G101"/>
-    <mergeCell ref="E102:G102"/>
-    <mergeCell ref="E103:G103"/>
-    <mergeCell ref="C111:C112"/>
-    <mergeCell ref="D111:G111"/>
-    <mergeCell ref="E112:G112"/>
-    <mergeCell ref="E113:G113"/>
-    <mergeCell ref="C114:C115"/>
-    <mergeCell ref="D114:G114"/>
-    <mergeCell ref="E115:G115"/>
-    <mergeCell ref="C106:G106"/>
-    <mergeCell ref="C107:C108"/>
-    <mergeCell ref="D107:G107"/>
-    <mergeCell ref="E108:G108"/>
-    <mergeCell ref="E109:G109"/>
-    <mergeCell ref="E110:G110"/>
-    <mergeCell ref="E121:G121"/>
-    <mergeCell ref="E122:G122"/>
-    <mergeCell ref="C123:C126"/>
-    <mergeCell ref="D123:G123"/>
-    <mergeCell ref="E124:E125"/>
-    <mergeCell ref="F124:G124"/>
-    <mergeCell ref="E116:G116"/>
-    <mergeCell ref="E117:G117"/>
-    <mergeCell ref="C118:C119"/>
-    <mergeCell ref="D118:G118"/>
-    <mergeCell ref="E119:G119"/>
-    <mergeCell ref="E120:G120"/>
-    <mergeCell ref="E134:G134"/>
-    <mergeCell ref="E135:G135"/>
-    <mergeCell ref="E136:G136"/>
-    <mergeCell ref="E137:G137"/>
-    <mergeCell ref="C138:C139"/>
-    <mergeCell ref="D138:G138"/>
-    <mergeCell ref="E139:G139"/>
-    <mergeCell ref="E129:G129"/>
-    <mergeCell ref="E130:G130"/>
-    <mergeCell ref="C131:C133"/>
-    <mergeCell ref="D131:G131"/>
-    <mergeCell ref="E132:G132"/>
-    <mergeCell ref="E133:G133"/>
-    <mergeCell ref="E151:G151"/>
-    <mergeCell ref="C152:C153"/>
-    <mergeCell ref="D152:G152"/>
-    <mergeCell ref="E153:G153"/>
-    <mergeCell ref="E154:G154"/>
-    <mergeCell ref="F140:G140"/>
-    <mergeCell ref="F141:F142"/>
-    <mergeCell ref="F144:G144"/>
-    <mergeCell ref="F145:F146"/>
-    <mergeCell ref="C149:C150"/>
-    <mergeCell ref="D149:G149"/>
-    <mergeCell ref="E150:G150"/>
+    <mergeCell ref="B1:J1"/>
+    <mergeCell ref="B3:J3"/>
+    <mergeCell ref="B4:J4"/>
+    <mergeCell ref="B5:J5"/>
+    <mergeCell ref="B6:J6"/>
+    <mergeCell ref="B7:H7"/>
+    <mergeCell ref="B22:B24"/>
+    <mergeCell ref="C22:G24"/>
+    <mergeCell ref="I22:J24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="64" orientation="portrait" r:id="rId1"/>
@@ -14341,15 +14341,15 @@
       <c r="A1" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="357" t="s">
+      <c r="B1" s="319" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="357"/>
-      <c r="D1" s="357"/>
-      <c r="E1" s="357"/>
-      <c r="F1" s="357"/>
-      <c r="G1" s="357"/>
-      <c r="H1" s="357"/>
+      <c r="C1" s="319"/>
+      <c r="D1" s="319"/>
+      <c r="E1" s="319"/>
+      <c r="F1" s="319"/>
+      <c r="G1" s="319"/>
+      <c r="H1" s="319"/>
       <c r="L1" s="51"/>
     </row>
     <row r="2" spans="1:13" ht="15.75" customHeight="1">
@@ -14383,30 +14383,30 @@
       <c r="A3" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="358" t="s">
+      <c r="B3" s="320" t="s">
         <v>167</v>
       </c>
-      <c r="C3" s="358"/>
-      <c r="D3" s="358"/>
-      <c r="E3" s="358"/>
-      <c r="F3" s="358"/>
-      <c r="G3" s="358"/>
-      <c r="H3" s="358"/>
+      <c r="C3" s="320"/>
+      <c r="D3" s="320"/>
+      <c r="E3" s="320"/>
+      <c r="F3" s="320"/>
+      <c r="G3" s="320"/>
+      <c r="H3" s="320"/>
       <c r="L3" s="51"/>
     </row>
     <row r="4" spans="1:13" ht="14.25" customHeight="1">
       <c r="A4" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="359" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="359"/>
-      <c r="D4" s="359"/>
-      <c r="E4" s="359"/>
-      <c r="F4" s="359"/>
-      <c r="G4" s="359"/>
-      <c r="H4" s="359"/>
+      <c r="B4" s="321" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="321"/>
+      <c r="D4" s="321"/>
+      <c r="E4" s="321"/>
+      <c r="F4" s="321"/>
+      <c r="G4" s="321"/>
+      <c r="H4" s="321"/>
       <c r="L4" s="51"/>
       <c r="M4" s="53"/>
     </row>
@@ -14428,40 +14428,40 @@
       <c r="A19" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="B19" s="382" t="s">
+      <c r="B19" s="374" t="s">
         <v>0</v>
       </c>
-      <c r="C19" s="365" t="s">
+      <c r="C19" s="327" t="s">
         <v>51</v>
       </c>
-      <c r="D19" s="366"/>
-      <c r="E19" s="366"/>
-      <c r="F19" s="366"/>
-      <c r="G19" s="367"/>
+      <c r="D19" s="328"/>
+      <c r="E19" s="328"/>
+      <c r="F19" s="328"/>
+      <c r="G19" s="329"/>
       <c r="H19" s="55"/>
     </row>
     <row r="20" spans="1:13" ht="12" customHeight="1">
       <c r="A20" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B20" s="363"/>
-      <c r="C20" s="368"/>
-      <c r="D20" s="369"/>
-      <c r="E20" s="369"/>
-      <c r="F20" s="369"/>
-      <c r="G20" s="370"/>
+      <c r="B20" s="325"/>
+      <c r="C20" s="330"/>
+      <c r="D20" s="331"/>
+      <c r="E20" s="331"/>
+      <c r="F20" s="331"/>
+      <c r="G20" s="332"/>
       <c r="H20" s="55"/>
     </row>
     <row r="21" spans="1:13" ht="24" customHeight="1">
       <c r="A21" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B21" s="364"/>
-      <c r="C21" s="371"/>
-      <c r="D21" s="372"/>
-      <c r="E21" s="372"/>
-      <c r="F21" s="372"/>
-      <c r="G21" s="373"/>
+      <c r="B21" s="326"/>
+      <c r="C21" s="333"/>
+      <c r="D21" s="334"/>
+      <c r="E21" s="334"/>
+      <c r="F21" s="334"/>
+      <c r="G21" s="335"/>
       <c r="H21" s="57" t="s">
         <v>52</v>
       </c>
@@ -14477,17 +14477,17 @@
       <c r="B25" s="57">
         <v>1</v>
       </c>
-      <c r="C25" s="383">
+      <c r="C25" s="375">
         <v>2</v>
       </c>
-      <c r="D25" s="384"/>
+      <c r="D25" s="376"/>
       <c r="E25" s="57">
         <v>3</v>
       </c>
-      <c r="F25" s="383">
+      <c r="F25" s="375">
         <v>4</v>
       </c>
-      <c r="G25" s="384"/>
+      <c r="G25" s="376"/>
       <c r="H25" s="57">
         <v>8</v>
       </c>
@@ -14543,15 +14543,15 @@
       <c r="B29" s="58">
         <v>2</v>
       </c>
-      <c r="C29" s="374" t="s">
+      <c r="C29" s="377" t="s">
         <v>54</v>
       </c>
-      <c r="D29" s="375"/>
-      <c r="E29" s="323" t="s">
+      <c r="D29" s="378"/>
+      <c r="E29" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="F29" s="324"/>
-      <c r="G29" s="325"/>
+      <c r="F29" s="337"/>
+      <c r="G29" s="338"/>
       <c r="H29" s="64"/>
       <c r="I29" s="49"/>
       <c r="M29" s="65"/>
@@ -14563,15 +14563,15 @@
       <c r="B30" s="58">
         <v>3</v>
       </c>
-      <c r="C30" s="376"/>
-      <c r="D30" s="377"/>
+      <c r="C30" s="379"/>
+      <c r="D30" s="380"/>
       <c r="E30" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F30" s="336" t="s">
+      <c r="F30" s="355" t="s">
         <v>56</v>
       </c>
-      <c r="G30" s="338"/>
+      <c r="G30" s="357"/>
       <c r="H30" s="72" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -14586,15 +14586,15 @@
       <c r="B31" s="58">
         <v>4</v>
       </c>
-      <c r="C31" s="376"/>
-      <c r="D31" s="377"/>
+      <c r="C31" s="379"/>
+      <c r="D31" s="380"/>
       <c r="E31" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="F31" s="336" t="s">
+      <c r="F31" s="355" t="s">
         <v>57</v>
       </c>
-      <c r="G31" s="338"/>
+      <c r="G31" s="357"/>
       <c r="H31" s="64"/>
       <c r="I31" s="49"/>
       <c r="M31" s="53"/>
@@ -14606,15 +14606,15 @@
       <c r="B32" s="58">
         <v>5</v>
       </c>
-      <c r="C32" s="376"/>
-      <c r="D32" s="377"/>
+      <c r="C32" s="379"/>
+      <c r="D32" s="380"/>
       <c r="E32" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="F32" s="336" t="s">
+      <c r="F32" s="355" t="s">
         <v>58</v>
       </c>
-      <c r="G32" s="338"/>
+      <c r="G32" s="357"/>
       <c r="H32" s="64"/>
       <c r="I32" s="49"/>
     </row>
@@ -14634,10 +14634,10 @@
       <c r="E33" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F33" s="319" t="s">
+      <c r="F33" s="345" t="s">
         <v>170</v>
       </c>
-      <c r="G33" s="321"/>
+      <c r="G33" s="347"/>
       <c r="H33" s="64"/>
       <c r="I33" s="49"/>
       <c r="J33" s="49"/>
@@ -14658,10 +14658,10 @@
       <c r="E34" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F34" s="319" t="s">
-        <v>44</v>
-      </c>
-      <c r="G34" s="321"/>
+      <c r="F34" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="G34" s="347"/>
       <c r="H34" s="64"/>
       <c r="I34" s="49"/>
       <c r="J34" s="49"/>
@@ -14674,15 +14674,15 @@
       <c r="B35" s="58">
         <v>8</v>
       </c>
-      <c r="C35" s="374" t="s">
+      <c r="C35" s="377" t="s">
         <v>171</v>
       </c>
-      <c r="D35" s="375"/>
-      <c r="E35" s="323" t="s">
+      <c r="D35" s="378"/>
+      <c r="E35" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="F35" s="324"/>
-      <c r="G35" s="325"/>
+      <c r="F35" s="337"/>
+      <c r="G35" s="338"/>
       <c r="H35" s="64"/>
       <c r="I35" s="49"/>
     </row>
@@ -14693,15 +14693,15 @@
       <c r="B36" s="58">
         <v>9</v>
       </c>
-      <c r="C36" s="376"/>
-      <c r="D36" s="377"/>
-      <c r="E36" s="330" t="s">
+      <c r="C36" s="379"/>
+      <c r="D36" s="380"/>
+      <c r="E36" s="372" t="s">
         <v>55</v>
       </c>
-      <c r="F36" s="336" t="s">
+      <c r="F36" s="355" t="s">
         <v>172</v>
       </c>
-      <c r="G36" s="338"/>
+      <c r="G36" s="357"/>
       <c r="H36" s="72" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -14716,13 +14716,13 @@
       <c r="B37" s="58">
         <v>10</v>
       </c>
-      <c r="C37" s="380"/>
-      <c r="D37" s="381"/>
-      <c r="E37" s="331"/>
-      <c r="F37" s="336" t="s">
+      <c r="C37" s="381"/>
+      <c r="D37" s="382"/>
+      <c r="E37" s="373"/>
+      <c r="F37" s="355" t="s">
         <v>173</v>
       </c>
-      <c r="G37" s="338"/>
+      <c r="G37" s="357"/>
       <c r="H37" s="64"/>
       <c r="I37" s="49"/>
     </row>
@@ -14733,15 +14733,15 @@
       <c r="B38" s="58">
         <v>11</v>
       </c>
-      <c r="C38" s="374" t="s">
+      <c r="C38" s="377" t="s">
         <v>174</v>
       </c>
-      <c r="D38" s="375"/>
-      <c r="E38" s="323" t="s">
+      <c r="D38" s="378"/>
+      <c r="E38" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="F38" s="324"/>
-      <c r="G38" s="325"/>
+      <c r="F38" s="337"/>
+      <c r="G38" s="338"/>
       <c r="H38" s="64"/>
       <c r="I38" s="49"/>
     </row>
@@ -14752,15 +14752,15 @@
       <c r="B39" s="58">
         <v>12</v>
       </c>
-      <c r="C39" s="376"/>
-      <c r="D39" s="377"/>
+      <c r="C39" s="379"/>
+      <c r="D39" s="380"/>
       <c r="E39" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F39" s="378" t="s">
-        <v>44</v>
-      </c>
-      <c r="G39" s="379"/>
+      <c r="F39" s="383" t="s">
+        <v>44</v>
+      </c>
+      <c r="G39" s="384"/>
       <c r="H39" s="64"/>
       <c r="I39" s="49"/>
     </row>
@@ -14780,10 +14780,10 @@
       <c r="E40" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F40" s="319" t="s">
-        <v>44</v>
-      </c>
-      <c r="G40" s="321"/>
+      <c r="F40" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="G40" s="347"/>
       <c r="H40" s="64"/>
       <c r="I40" s="49"/>
       <c r="J40" s="49"/>
@@ -14795,15 +14795,15 @@
       <c r="B41" s="58">
         <v>14</v>
       </c>
-      <c r="C41" s="374" t="s">
+      <c r="C41" s="377" t="s">
         <v>175</v>
       </c>
-      <c r="D41" s="375"/>
-      <c r="E41" s="323" t="s">
+      <c r="D41" s="378"/>
+      <c r="E41" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="F41" s="324"/>
-      <c r="G41" s="325"/>
+      <c r="F41" s="337"/>
+      <c r="G41" s="338"/>
       <c r="H41" s="64"/>
       <c r="I41" s="49"/>
     </row>
@@ -14814,15 +14814,15 @@
       <c r="B42" s="58">
         <v>15</v>
       </c>
-      <c r="C42" s="376"/>
-      <c r="D42" s="377"/>
+      <c r="C42" s="379"/>
+      <c r="D42" s="380"/>
       <c r="E42" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F42" s="336" t="s">
+      <c r="F42" s="355" t="s">
         <v>91</v>
       </c>
-      <c r="G42" s="338"/>
+      <c r="G42" s="357"/>
       <c r="H42" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -14845,10 +14845,10 @@
       <c r="E43" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F43" s="319" t="s">
+      <c r="F43" s="345" t="s">
         <v>176</v>
       </c>
-      <c r="G43" s="321"/>
+      <c r="G43" s="347"/>
       <c r="H43" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -14872,10 +14872,10 @@
       <c r="E44" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F44" s="319" t="s">
-        <v>44</v>
-      </c>
-      <c r="G44" s="321"/>
+      <c r="F44" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="G44" s="347"/>
       <c r="H44" s="64"/>
       <c r="I44" s="49"/>
       <c r="J44" s="49"/>
@@ -14887,15 +14887,15 @@
       <c r="B45" s="58">
         <v>18</v>
       </c>
-      <c r="C45" s="374" t="s">
+      <c r="C45" s="377" t="s">
         <v>177</v>
       </c>
-      <c r="D45" s="375"/>
-      <c r="E45" s="323" t="s">
+      <c r="D45" s="378"/>
+      <c r="E45" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="F45" s="324"/>
-      <c r="G45" s="325"/>
+      <c r="F45" s="337"/>
+      <c r="G45" s="338"/>
       <c r="H45" s="64"/>
       <c r="I45" s="49"/>
     </row>
@@ -14906,15 +14906,15 @@
       <c r="B46" s="58">
         <v>19</v>
       </c>
-      <c r="C46" s="376"/>
-      <c r="D46" s="377"/>
+      <c r="C46" s="379"/>
+      <c r="D46" s="380"/>
       <c r="E46" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F46" s="378" t="s">
-        <v>44</v>
-      </c>
-      <c r="G46" s="379"/>
+      <c r="F46" s="383" t="s">
+        <v>44</v>
+      </c>
+      <c r="G46" s="384"/>
       <c r="H46" s="64"/>
       <c r="I46" s="49"/>
     </row>
@@ -14934,8 +14934,8 @@
       <c r="E47" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F47" s="319"/>
-      <c r="G47" s="321"/>
+      <c r="F47" s="345"/>
+      <c r="G47" s="347"/>
       <c r="H47" s="64"/>
       <c r="I47" s="49"/>
       <c r="J47" s="49"/>
@@ -14956,10 +14956,10 @@
       <c r="E48" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F48" s="319" t="s">
+      <c r="F48" s="345" t="s">
         <v>178</v>
       </c>
-      <c r="G48" s="321"/>
+      <c r="G48" s="347"/>
       <c r="H48" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -14983,10 +14983,10 @@
       <c r="E49" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F49" s="319" t="s">
+      <c r="F49" s="345" t="s">
         <v>8</v>
       </c>
-      <c r="G49" s="321"/>
+      <c r="G49" s="347"/>
       <c r="H49" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15001,13 +15001,13 @@
       <c r="B50" s="58">
         <v>24</v>
       </c>
-      <c r="C50" s="323" t="s">
+      <c r="C50" s="336" t="s">
         <v>179</v>
       </c>
-      <c r="D50" s="324"/>
-      <c r="E50" s="324"/>
-      <c r="F50" s="324"/>
-      <c r="G50" s="325"/>
+      <c r="D50" s="337"/>
+      <c r="E50" s="337"/>
+      <c r="F50" s="337"/>
+      <c r="G50" s="338"/>
       <c r="H50" s="64"/>
       <c r="I50" s="49"/>
     </row>
@@ -15018,13 +15018,13 @@
       <c r="B51" s="58">
         <v>25</v>
       </c>
-      <c r="C51" s="323" t="s">
+      <c r="C51" s="336" t="s">
         <v>180</v>
       </c>
-      <c r="D51" s="324"/>
-      <c r="E51" s="324"/>
-      <c r="F51" s="324"/>
-      <c r="G51" s="325"/>
+      <c r="D51" s="337"/>
+      <c r="E51" s="337"/>
+      <c r="F51" s="337"/>
+      <c r="G51" s="338"/>
       <c r="H51" s="64" t="e">
         <f>нак.расх.!G29-зат.осн.про.!H75-зат.осн.про.!H99</f>
         <v>#REF!</v>
@@ -15070,15 +15070,15 @@
       <c r="B53" s="58">
         <v>2</v>
       </c>
-      <c r="C53" s="374" t="s">
+      <c r="C53" s="377" t="s">
         <v>54</v>
       </c>
-      <c r="D53" s="375"/>
-      <c r="E53" s="323" t="s">
+      <c r="D53" s="378"/>
+      <c r="E53" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="F53" s="324"/>
-      <c r="G53" s="325"/>
+      <c r="F53" s="337"/>
+      <c r="G53" s="338"/>
       <c r="H53" s="64"/>
       <c r="I53" s="49"/>
       <c r="M53" s="53" t="e">
@@ -15093,15 +15093,15 @@
       <c r="B54" s="58">
         <v>3</v>
       </c>
-      <c r="C54" s="376"/>
-      <c r="D54" s="377"/>
+      <c r="C54" s="379"/>
+      <c r="D54" s="380"/>
       <c r="E54" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F54" s="336" t="s">
+      <c r="F54" s="355" t="s">
         <v>56</v>
       </c>
-      <c r="G54" s="338"/>
+      <c r="G54" s="357"/>
       <c r="H54" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15115,15 +15115,15 @@
       <c r="B55" s="58">
         <v>4</v>
       </c>
-      <c r="C55" s="376"/>
-      <c r="D55" s="377"/>
+      <c r="C55" s="379"/>
+      <c r="D55" s="380"/>
       <c r="E55" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="F55" s="336" t="s">
+      <c r="F55" s="355" t="s">
         <v>57</v>
       </c>
-      <c r="G55" s="338"/>
+      <c r="G55" s="357"/>
       <c r="H55" s="64"/>
       <c r="I55" s="49"/>
     </row>
@@ -15134,15 +15134,15 @@
       <c r="B56" s="58">
         <v>5</v>
       </c>
-      <c r="C56" s="376"/>
-      <c r="D56" s="377"/>
+      <c r="C56" s="379"/>
+      <c r="D56" s="380"/>
       <c r="E56" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="F56" s="336" t="s">
+      <c r="F56" s="355" t="s">
         <v>58</v>
       </c>
-      <c r="G56" s="338"/>
+      <c r="G56" s="357"/>
       <c r="H56" s="64"/>
       <c r="I56" s="49"/>
     </row>
@@ -15162,10 +15162,10 @@
       <c r="E57" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F57" s="319" t="s">
+      <c r="F57" s="345" t="s">
         <v>170</v>
       </c>
-      <c r="G57" s="321"/>
+      <c r="G57" s="347"/>
       <c r="H57" s="64"/>
       <c r="I57" s="49"/>
       <c r="J57" s="49"/>
@@ -15186,10 +15186,10 @@
       <c r="E58" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F58" s="319" t="s">
-        <v>44</v>
-      </c>
-      <c r="G58" s="321"/>
+      <c r="F58" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="G58" s="347"/>
       <c r="H58" s="64"/>
       <c r="I58" s="49"/>
     </row>
@@ -15200,15 +15200,15 @@
       <c r="B59" s="58">
         <v>8</v>
       </c>
-      <c r="C59" s="374" t="s">
+      <c r="C59" s="377" t="s">
         <v>171</v>
       </c>
-      <c r="D59" s="375"/>
-      <c r="E59" s="323" t="s">
+      <c r="D59" s="378"/>
+      <c r="E59" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="F59" s="324"/>
-      <c r="G59" s="325"/>
+      <c r="F59" s="337"/>
+      <c r="G59" s="338"/>
       <c r="H59" s="64"/>
       <c r="I59" s="49"/>
     </row>
@@ -15219,15 +15219,15 @@
       <c r="B60" s="58">
         <v>9</v>
       </c>
-      <c r="C60" s="376"/>
-      <c r="D60" s="377"/>
-      <c r="E60" s="330" t="s">
+      <c r="C60" s="379"/>
+      <c r="D60" s="380"/>
+      <c r="E60" s="372" t="s">
         <v>55</v>
       </c>
-      <c r="F60" s="336" t="s">
+      <c r="F60" s="355" t="s">
         <v>172</v>
       </c>
-      <c r="G60" s="338"/>
+      <c r="G60" s="357"/>
       <c r="H60" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15241,13 +15241,13 @@
       <c r="B61" s="58">
         <v>10</v>
       </c>
-      <c r="C61" s="380"/>
-      <c r="D61" s="381"/>
-      <c r="E61" s="331"/>
-      <c r="F61" s="336" t="s">
+      <c r="C61" s="381"/>
+      <c r="D61" s="382"/>
+      <c r="E61" s="373"/>
+      <c r="F61" s="355" t="s">
         <v>173</v>
       </c>
-      <c r="G61" s="338"/>
+      <c r="G61" s="357"/>
       <c r="H61" s="64"/>
       <c r="I61" s="49"/>
     </row>
@@ -15258,15 +15258,15 @@
       <c r="B62" s="58">
         <v>11</v>
       </c>
-      <c r="C62" s="374" t="s">
+      <c r="C62" s="377" t="s">
         <v>174</v>
       </c>
-      <c r="D62" s="375"/>
-      <c r="E62" s="323" t="s">
+      <c r="D62" s="378"/>
+      <c r="E62" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="F62" s="324"/>
-      <c r="G62" s="325"/>
+      <c r="F62" s="337"/>
+      <c r="G62" s="338"/>
       <c r="H62" s="64"/>
       <c r="I62" s="49"/>
     </row>
@@ -15277,15 +15277,15 @@
       <c r="B63" s="58">
         <v>12</v>
       </c>
-      <c r="C63" s="376"/>
-      <c r="D63" s="377"/>
+      <c r="C63" s="379"/>
+      <c r="D63" s="380"/>
       <c r="E63" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F63" s="378" t="s">
-        <v>44</v>
-      </c>
-      <c r="G63" s="379"/>
+      <c r="F63" s="383" t="s">
+        <v>44</v>
+      </c>
+      <c r="G63" s="384"/>
       <c r="H63" s="64"/>
       <c r="I63" s="49"/>
       <c r="J63" s="49"/>
@@ -15306,10 +15306,10 @@
       <c r="E64" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F64" s="319" t="s">
-        <v>44</v>
-      </c>
-      <c r="G64" s="321"/>
+      <c r="F64" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="G64" s="347"/>
       <c r="H64" s="64"/>
       <c r="I64" s="49"/>
     </row>
@@ -15320,15 +15320,15 @@
       <c r="B65" s="58">
         <v>14</v>
       </c>
-      <c r="C65" s="374" t="s">
+      <c r="C65" s="377" t="s">
         <v>175</v>
       </c>
-      <c r="D65" s="375"/>
-      <c r="E65" s="323" t="s">
+      <c r="D65" s="378"/>
+      <c r="E65" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="F65" s="324"/>
-      <c r="G65" s="325"/>
+      <c r="F65" s="337"/>
+      <c r="G65" s="338"/>
       <c r="H65" s="64"/>
       <c r="I65" s="49"/>
     </row>
@@ -15339,15 +15339,15 @@
       <c r="B66" s="58">
         <v>15</v>
       </c>
-      <c r="C66" s="376"/>
-      <c r="D66" s="377"/>
+      <c r="C66" s="379"/>
+      <c r="D66" s="380"/>
       <c r="E66" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F66" s="336" t="s">
+      <c r="F66" s="355" t="s">
         <v>91</v>
       </c>
-      <c r="G66" s="338"/>
+      <c r="G66" s="357"/>
       <c r="H66" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15371,10 +15371,10 @@
       <c r="E67" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F67" s="319" t="s">
+      <c r="F67" s="345" t="s">
         <v>176</v>
       </c>
-      <c r="G67" s="321"/>
+      <c r="G67" s="347"/>
       <c r="H67" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15397,10 +15397,10 @@
       <c r="E68" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F68" s="319" t="s">
-        <v>44</v>
-      </c>
-      <c r="G68" s="321"/>
+      <c r="F68" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="G68" s="347"/>
       <c r="H68" s="64"/>
       <c r="I68" s="49"/>
     </row>
@@ -15411,15 +15411,15 @@
       <c r="B69" s="58">
         <v>18</v>
       </c>
-      <c r="C69" s="374" t="s">
+      <c r="C69" s="377" t="s">
         <v>177</v>
       </c>
-      <c r="D69" s="375"/>
-      <c r="E69" s="323" t="s">
+      <c r="D69" s="378"/>
+      <c r="E69" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="F69" s="324"/>
-      <c r="G69" s="325"/>
+      <c r="F69" s="337"/>
+      <c r="G69" s="338"/>
       <c r="H69" s="64"/>
       <c r="I69" s="49"/>
       <c r="J69" s="49"/>
@@ -15431,15 +15431,15 @@
       <c r="B70" s="58">
         <v>19</v>
       </c>
-      <c r="C70" s="376"/>
-      <c r="D70" s="377"/>
+      <c r="C70" s="379"/>
+      <c r="D70" s="380"/>
       <c r="E70" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F70" s="378" t="s">
-        <v>44</v>
-      </c>
-      <c r="G70" s="379"/>
+      <c r="F70" s="383" t="s">
+        <v>44</v>
+      </c>
+      <c r="G70" s="384"/>
       <c r="H70" s="64"/>
       <c r="I70" s="49"/>
     </row>
@@ -15459,8 +15459,8 @@
       <c r="E71" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F71" s="319"/>
-      <c r="G71" s="321"/>
+      <c r="F71" s="345"/>
+      <c r="G71" s="347"/>
       <c r="H71" s="64"/>
       <c r="I71" s="49"/>
     </row>
@@ -15477,10 +15477,10 @@
       <c r="E72" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F72" s="319" t="s">
+      <c r="F72" s="345" t="s">
         <v>178</v>
       </c>
-      <c r="G72" s="321"/>
+      <c r="G72" s="347"/>
       <c r="H72" s="64"/>
       <c r="I72" s="49"/>
       <c r="J72" s="49"/>
@@ -15503,10 +15503,10 @@
       <c r="E73" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F73" s="319" t="s">
+      <c r="F73" s="345" t="s">
         <v>8</v>
       </c>
-      <c r="G73" s="321"/>
+      <c r="G73" s="347"/>
       <c r="H73" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15520,13 +15520,13 @@
       <c r="B74" s="58">
         <v>24</v>
       </c>
-      <c r="C74" s="323" t="s">
+      <c r="C74" s="336" t="s">
         <v>179</v>
       </c>
-      <c r="D74" s="324"/>
-      <c r="E74" s="324"/>
-      <c r="F74" s="324"/>
-      <c r="G74" s="325"/>
+      <c r="D74" s="337"/>
+      <c r="E74" s="337"/>
+      <c r="F74" s="337"/>
+      <c r="G74" s="338"/>
       <c r="H74" s="64"/>
       <c r="I74" s="49"/>
       <c r="J74" s="49"/>
@@ -15537,13 +15537,13 @@
       <c r="B75" s="58">
         <v>25</v>
       </c>
-      <c r="C75" s="323" t="s">
+      <c r="C75" s="336" t="s">
         <v>180</v>
       </c>
-      <c r="D75" s="324"/>
-      <c r="E75" s="324"/>
-      <c r="F75" s="324"/>
-      <c r="G75" s="325"/>
+      <c r="D75" s="337"/>
+      <c r="E75" s="337"/>
+      <c r="F75" s="337"/>
+      <c r="G75" s="338"/>
       <c r="H75" s="64" t="e">
         <f>нак.расх.!G29*4%</f>
         <v>#REF!</v>
@@ -15589,15 +15589,15 @@
       <c r="B77" s="58">
         <v>2</v>
       </c>
-      <c r="C77" s="374" t="s">
+      <c r="C77" s="377" t="s">
         <v>54</v>
       </c>
-      <c r="D77" s="375"/>
-      <c r="E77" s="323" t="s">
+      <c r="D77" s="378"/>
+      <c r="E77" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="F77" s="324"/>
-      <c r="G77" s="325"/>
+      <c r="F77" s="337"/>
+      <c r="G77" s="338"/>
       <c r="H77" s="64"/>
       <c r="M77" s="53" t="e">
         <f>H76-M76</f>
@@ -15608,15 +15608,15 @@
       <c r="B78" s="58">
         <v>3</v>
       </c>
-      <c r="C78" s="376"/>
-      <c r="D78" s="377"/>
+      <c r="C78" s="379"/>
+      <c r="D78" s="380"/>
       <c r="E78" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F78" s="336" t="s">
+      <c r="F78" s="355" t="s">
         <v>56</v>
       </c>
-      <c r="G78" s="338"/>
+      <c r="G78" s="357"/>
       <c r="H78" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15626,30 +15626,30 @@
       <c r="B79" s="58">
         <v>4</v>
       </c>
-      <c r="C79" s="376"/>
-      <c r="D79" s="377"/>
+      <c r="C79" s="379"/>
+      <c r="D79" s="380"/>
       <c r="E79" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="F79" s="336" t="s">
+      <c r="F79" s="355" t="s">
         <v>57</v>
       </c>
-      <c r="G79" s="338"/>
+      <c r="G79" s="357"/>
       <c r="H79" s="64"/>
     </row>
     <row r="80" spans="1:13" ht="15.75" customHeight="1">
       <c r="B80" s="58">
         <v>5</v>
       </c>
-      <c r="C80" s="376"/>
-      <c r="D80" s="377"/>
+      <c r="C80" s="379"/>
+      <c r="D80" s="380"/>
       <c r="E80" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="F80" s="336" t="s">
+      <c r="F80" s="355" t="s">
         <v>58</v>
       </c>
-      <c r="G80" s="338"/>
+      <c r="G80" s="357"/>
       <c r="H80" s="64"/>
     </row>
     <row r="81" spans="2:8" ht="15.75" customHeight="1">
@@ -15665,10 +15665,10 @@
       <c r="E81" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F81" s="319" t="s">
+      <c r="F81" s="345" t="s">
         <v>170</v>
       </c>
-      <c r="G81" s="321"/>
+      <c r="G81" s="347"/>
       <c r="H81" s="64"/>
     </row>
     <row r="82" spans="2:8" ht="15.75" customHeight="1">
@@ -15684,40 +15684,40 @@
       <c r="E82" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F82" s="319" t="s">
-        <v>44</v>
-      </c>
-      <c r="G82" s="321"/>
+      <c r="F82" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="G82" s="347"/>
       <c r="H82" s="64"/>
     </row>
     <row r="83" spans="2:8" ht="15.75" customHeight="1">
       <c r="B83" s="58">
         <v>8</v>
       </c>
-      <c r="C83" s="374" t="s">
+      <c r="C83" s="377" t="s">
         <v>171</v>
       </c>
-      <c r="D83" s="375"/>
-      <c r="E83" s="323" t="s">
+      <c r="D83" s="378"/>
+      <c r="E83" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="F83" s="324"/>
-      <c r="G83" s="325"/>
+      <c r="F83" s="337"/>
+      <c r="G83" s="338"/>
       <c r="H83" s="64"/>
     </row>
     <row r="84" spans="2:8" ht="15.75" customHeight="1">
       <c r="B84" s="58">
         <v>9</v>
       </c>
-      <c r="C84" s="376"/>
-      <c r="D84" s="377"/>
-      <c r="E84" s="330" t="s">
+      <c r="C84" s="379"/>
+      <c r="D84" s="380"/>
+      <c r="E84" s="372" t="s">
         <v>55</v>
       </c>
-      <c r="F84" s="336" t="s">
+      <c r="F84" s="355" t="s">
         <v>172</v>
       </c>
-      <c r="G84" s="338"/>
+      <c r="G84" s="357"/>
       <c r="H84" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15727,43 +15727,43 @@
       <c r="B85" s="58">
         <v>10</v>
       </c>
-      <c r="C85" s="380"/>
-      <c r="D85" s="381"/>
-      <c r="E85" s="331"/>
-      <c r="F85" s="336" t="s">
+      <c r="C85" s="381"/>
+      <c r="D85" s="382"/>
+      <c r="E85" s="373"/>
+      <c r="F85" s="355" t="s">
         <v>173</v>
       </c>
-      <c r="G85" s="338"/>
+      <c r="G85" s="357"/>
       <c r="H85" s="64"/>
     </row>
     <row r="86" spans="2:8" ht="15.75" customHeight="1">
       <c r="B86" s="58">
         <v>11</v>
       </c>
-      <c r="C86" s="374" t="s">
+      <c r="C86" s="377" t="s">
         <v>174</v>
       </c>
-      <c r="D86" s="375"/>
-      <c r="E86" s="323" t="s">
+      <c r="D86" s="378"/>
+      <c r="E86" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="F86" s="324"/>
-      <c r="G86" s="325"/>
+      <c r="F86" s="337"/>
+      <c r="G86" s="338"/>
       <c r="H86" s="64"/>
     </row>
     <row r="87" spans="2:8" ht="15.75" customHeight="1">
       <c r="B87" s="58">
         <v>12</v>
       </c>
-      <c r="C87" s="376"/>
-      <c r="D87" s="377"/>
+      <c r="C87" s="379"/>
+      <c r="D87" s="380"/>
       <c r="E87" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F87" s="378" t="s">
-        <v>44</v>
-      </c>
-      <c r="G87" s="379"/>
+      <c r="F87" s="383" t="s">
+        <v>44</v>
+      </c>
+      <c r="G87" s="384"/>
       <c r="H87" s="64"/>
     </row>
     <row r="88" spans="2:8" ht="15.75" customHeight="1">
@@ -15779,40 +15779,40 @@
       <c r="E88" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F88" s="319" t="s">
-        <v>44</v>
-      </c>
-      <c r="G88" s="321"/>
+      <c r="F88" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="G88" s="347"/>
       <c r="H88" s="64"/>
     </row>
     <row r="89" spans="2:8" ht="15.75" customHeight="1">
       <c r="B89" s="58">
         <v>14</v>
       </c>
-      <c r="C89" s="374" t="s">
+      <c r="C89" s="377" t="s">
         <v>175</v>
       </c>
-      <c r="D89" s="375"/>
-      <c r="E89" s="323" t="s">
+      <c r="D89" s="378"/>
+      <c r="E89" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="F89" s="324"/>
-      <c r="G89" s="325"/>
+      <c r="F89" s="337"/>
+      <c r="G89" s="338"/>
       <c r="H89" s="64"/>
     </row>
     <row r="90" spans="2:8" ht="15.75" customHeight="1">
       <c r="B90" s="58">
         <v>15</v>
       </c>
-      <c r="C90" s="376"/>
-      <c r="D90" s="377"/>
+      <c r="C90" s="379"/>
+      <c r="D90" s="380"/>
       <c r="E90" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F90" s="336" t="s">
+      <c r="F90" s="355" t="s">
         <v>91</v>
       </c>
-      <c r="G90" s="338"/>
+      <c r="G90" s="357"/>
       <c r="H90" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15831,10 +15831,10 @@
       <c r="E91" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F91" s="319" t="s">
+      <c r="F91" s="345" t="s">
         <v>176</v>
       </c>
-      <c r="G91" s="321"/>
+      <c r="G91" s="347"/>
       <c r="H91" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15853,40 +15853,40 @@
       <c r="E92" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F92" s="319" t="s">
-        <v>44</v>
-      </c>
-      <c r="G92" s="321"/>
+      <c r="F92" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="G92" s="347"/>
       <c r="H92" s="64"/>
     </row>
     <row r="93" spans="2:8" ht="15.75" customHeight="1">
       <c r="B93" s="58">
         <v>18</v>
       </c>
-      <c r="C93" s="374" t="s">
+      <c r="C93" s="377" t="s">
         <v>177</v>
       </c>
-      <c r="D93" s="375"/>
-      <c r="E93" s="323" t="s">
+      <c r="D93" s="378"/>
+      <c r="E93" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="F93" s="324"/>
-      <c r="G93" s="325"/>
+      <c r="F93" s="337"/>
+      <c r="G93" s="338"/>
       <c r="H93" s="64"/>
     </row>
     <row r="94" spans="2:8" ht="15.75" customHeight="1">
       <c r="B94" s="58">
         <v>19</v>
       </c>
-      <c r="C94" s="376"/>
-      <c r="D94" s="377"/>
+      <c r="C94" s="379"/>
+      <c r="D94" s="380"/>
       <c r="E94" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F94" s="378" t="s">
-        <v>44</v>
-      </c>
-      <c r="G94" s="379"/>
+      <c r="F94" s="383" t="s">
+        <v>44</v>
+      </c>
+      <c r="G94" s="384"/>
       <c r="H94" s="64"/>
     </row>
     <row r="95" spans="2:8" ht="15.75" customHeight="1">
@@ -15902,8 +15902,8 @@
       <c r="E95" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F95" s="319"/>
-      <c r="G95" s="321"/>
+      <c r="F95" s="345"/>
+      <c r="G95" s="347"/>
       <c r="H95" s="64"/>
     </row>
     <row r="96" spans="2:8" ht="32.25" customHeight="1">
@@ -15919,10 +15919,10 @@
       <c r="E96" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F96" s="319" t="s">
+      <c r="F96" s="345" t="s">
         <v>8</v>
       </c>
-      <c r="G96" s="321"/>
+      <c r="G96" s="347"/>
       <c r="H96" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15941,34 +15941,34 @@
       <c r="E97" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F97" s="319"/>
-      <c r="G97" s="321"/>
+      <c r="F97" s="345"/>
+      <c r="G97" s="347"/>
       <c r="H97" s="64"/>
     </row>
     <row r="98" spans="2:8" ht="15.75" customHeight="1">
       <c r="B98" s="58">
         <v>24</v>
       </c>
-      <c r="C98" s="323" t="s">
+      <c r="C98" s="336" t="s">
         <v>179</v>
       </c>
-      <c r="D98" s="324"/>
-      <c r="E98" s="324"/>
-      <c r="F98" s="324"/>
-      <c r="G98" s="325"/>
+      <c r="D98" s="337"/>
+      <c r="E98" s="337"/>
+      <c r="F98" s="337"/>
+      <c r="G98" s="338"/>
       <c r="H98" s="64"/>
     </row>
     <row r="99" spans="2:8" ht="15.75" customHeight="1">
       <c r="B99" s="58">
         <v>25</v>
       </c>
-      <c r="C99" s="323" t="s">
+      <c r="C99" s="336" t="s">
         <v>180</v>
       </c>
-      <c r="D99" s="324"/>
-      <c r="E99" s="324"/>
-      <c r="F99" s="324"/>
-      <c r="G99" s="325"/>
+      <c r="D99" s="337"/>
+      <c r="E99" s="337"/>
+      <c r="F99" s="337"/>
+      <c r="G99" s="338"/>
       <c r="H99" s="64" t="e">
         <f>нак.расх.!G29*16%</f>
         <v>#REF!</v>
@@ -15976,6 +15976,87 @@
     </row>
   </sheetData>
   <mergeCells count="94">
+    <mergeCell ref="F96:G96"/>
+    <mergeCell ref="F97:G97"/>
+    <mergeCell ref="C98:G98"/>
+    <mergeCell ref="C99:G99"/>
+    <mergeCell ref="F91:G91"/>
+    <mergeCell ref="F92:G92"/>
+    <mergeCell ref="C93:D94"/>
+    <mergeCell ref="E93:G93"/>
+    <mergeCell ref="F94:G94"/>
+    <mergeCell ref="F95:G95"/>
+    <mergeCell ref="C86:D87"/>
+    <mergeCell ref="E86:G86"/>
+    <mergeCell ref="F87:G87"/>
+    <mergeCell ref="F88:G88"/>
+    <mergeCell ref="C89:D90"/>
+    <mergeCell ref="E89:G89"/>
+    <mergeCell ref="F90:G90"/>
+    <mergeCell ref="F81:G81"/>
+    <mergeCell ref="F82:G82"/>
+    <mergeCell ref="C83:D85"/>
+    <mergeCell ref="E83:G83"/>
+    <mergeCell ref="E84:E85"/>
+    <mergeCell ref="F84:G84"/>
+    <mergeCell ref="F85:G85"/>
+    <mergeCell ref="F72:G72"/>
+    <mergeCell ref="F73:G73"/>
+    <mergeCell ref="C74:G74"/>
+    <mergeCell ref="C75:G75"/>
+    <mergeCell ref="C77:D80"/>
+    <mergeCell ref="E77:G77"/>
+    <mergeCell ref="F78:G78"/>
+    <mergeCell ref="F79:G79"/>
+    <mergeCell ref="F80:G80"/>
+    <mergeCell ref="F71:G71"/>
+    <mergeCell ref="C62:D63"/>
+    <mergeCell ref="E62:G62"/>
+    <mergeCell ref="F63:G63"/>
+    <mergeCell ref="F64:G64"/>
+    <mergeCell ref="C65:D66"/>
+    <mergeCell ref="E65:G65"/>
+    <mergeCell ref="F66:G66"/>
+    <mergeCell ref="F67:G67"/>
+    <mergeCell ref="F68:G68"/>
+    <mergeCell ref="C69:D70"/>
+    <mergeCell ref="E69:G69"/>
+    <mergeCell ref="F70:G70"/>
+    <mergeCell ref="F57:G57"/>
+    <mergeCell ref="F58:G58"/>
+    <mergeCell ref="C59:D61"/>
+    <mergeCell ref="E59:G59"/>
+    <mergeCell ref="E60:E61"/>
+    <mergeCell ref="F60:G60"/>
+    <mergeCell ref="F61:G61"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="C53:D56"/>
+    <mergeCell ref="E53:G53"/>
+    <mergeCell ref="F54:G54"/>
+    <mergeCell ref="F55:G55"/>
+    <mergeCell ref="F56:G56"/>
+    <mergeCell ref="F47:G47"/>
+    <mergeCell ref="C38:D39"/>
+    <mergeCell ref="E38:G38"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="C41:D42"/>
+    <mergeCell ref="E41:G41"/>
+    <mergeCell ref="F42:G42"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="C45:D46"/>
+    <mergeCell ref="E45:G45"/>
+    <mergeCell ref="F46:G46"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="C35:D37"/>
+    <mergeCell ref="E35:G35"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="F36:G36"/>
+    <mergeCell ref="F37:G37"/>
     <mergeCell ref="F33:G33"/>
     <mergeCell ref="B1:H1"/>
     <mergeCell ref="B3:H3"/>
@@ -15989,87 +16070,6 @@
     <mergeCell ref="F30:G30"/>
     <mergeCell ref="F31:G31"/>
     <mergeCell ref="F32:G32"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="C35:D37"/>
-    <mergeCell ref="E35:G35"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="F36:G36"/>
-    <mergeCell ref="F37:G37"/>
-    <mergeCell ref="F47:G47"/>
-    <mergeCell ref="C38:D39"/>
-    <mergeCell ref="E38:G38"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="C41:D42"/>
-    <mergeCell ref="E41:G41"/>
-    <mergeCell ref="F42:G42"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="F44:G44"/>
-    <mergeCell ref="C45:D46"/>
-    <mergeCell ref="E45:G45"/>
-    <mergeCell ref="F46:G46"/>
-    <mergeCell ref="F48:G48"/>
-    <mergeCell ref="F49:G49"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="C53:D56"/>
-    <mergeCell ref="E53:G53"/>
-    <mergeCell ref="F54:G54"/>
-    <mergeCell ref="F55:G55"/>
-    <mergeCell ref="F56:G56"/>
-    <mergeCell ref="F57:G57"/>
-    <mergeCell ref="F58:G58"/>
-    <mergeCell ref="C59:D61"/>
-    <mergeCell ref="E59:G59"/>
-    <mergeCell ref="E60:E61"/>
-    <mergeCell ref="F60:G60"/>
-    <mergeCell ref="F61:G61"/>
-    <mergeCell ref="F71:G71"/>
-    <mergeCell ref="C62:D63"/>
-    <mergeCell ref="E62:G62"/>
-    <mergeCell ref="F63:G63"/>
-    <mergeCell ref="F64:G64"/>
-    <mergeCell ref="C65:D66"/>
-    <mergeCell ref="E65:G65"/>
-    <mergeCell ref="F66:G66"/>
-    <mergeCell ref="F67:G67"/>
-    <mergeCell ref="F68:G68"/>
-    <mergeCell ref="C69:D70"/>
-    <mergeCell ref="E69:G69"/>
-    <mergeCell ref="F70:G70"/>
-    <mergeCell ref="F72:G72"/>
-    <mergeCell ref="F73:G73"/>
-    <mergeCell ref="C74:G74"/>
-    <mergeCell ref="C75:G75"/>
-    <mergeCell ref="C77:D80"/>
-    <mergeCell ref="E77:G77"/>
-    <mergeCell ref="F78:G78"/>
-    <mergeCell ref="F79:G79"/>
-    <mergeCell ref="F80:G80"/>
-    <mergeCell ref="F81:G81"/>
-    <mergeCell ref="F82:G82"/>
-    <mergeCell ref="C83:D85"/>
-    <mergeCell ref="E83:G83"/>
-    <mergeCell ref="E84:E85"/>
-    <mergeCell ref="F84:G84"/>
-    <mergeCell ref="F85:G85"/>
-    <mergeCell ref="C86:D87"/>
-    <mergeCell ref="E86:G86"/>
-    <mergeCell ref="F87:G87"/>
-    <mergeCell ref="F88:G88"/>
-    <mergeCell ref="C89:D90"/>
-    <mergeCell ref="E89:G89"/>
-    <mergeCell ref="F90:G90"/>
-    <mergeCell ref="F96:G96"/>
-    <mergeCell ref="F97:G97"/>
-    <mergeCell ref="C98:G98"/>
-    <mergeCell ref="C99:G99"/>
-    <mergeCell ref="F91:G91"/>
-    <mergeCell ref="F92:G92"/>
-    <mergeCell ref="C93:D94"/>
-    <mergeCell ref="E93:G93"/>
-    <mergeCell ref="F94:G94"/>
-    <mergeCell ref="F95:G95"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="76" orientation="portrait" r:id="rId1"/>
@@ -16098,14 +16098,14 @@
       <c r="A1" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="357" t="s">
+      <c r="B1" s="319" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="357"/>
-      <c r="D1" s="357"/>
-      <c r="E1" s="357"/>
-      <c r="F1" s="357"/>
-      <c r="G1" s="357"/>
+      <c r="C1" s="319"/>
+      <c r="D1" s="319"/>
+      <c r="E1" s="319"/>
+      <c r="F1" s="319"/>
+      <c r="G1" s="319"/>
       <c r="K1" s="51"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" customHeight="1">
@@ -16136,69 +16136,69 @@
       <c r="A3" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="357" t="s">
+      <c r="B3" s="319" t="s">
         <v>182</v>
       </c>
-      <c r="C3" s="357"/>
-      <c r="D3" s="357"/>
-      <c r="E3" s="357"/>
-      <c r="F3" s="357"/>
-      <c r="G3" s="357"/>
+      <c r="C3" s="319"/>
+      <c r="D3" s="319"/>
+      <c r="E3" s="319"/>
+      <c r="F3" s="319"/>
+      <c r="G3" s="319"/>
       <c r="K3" s="51"/>
     </row>
     <row r="4" spans="1:11" ht="14.25" customHeight="1">
       <c r="A4" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="359" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="359"/>
-      <c r="D4" s="359"/>
-      <c r="E4" s="359"/>
-      <c r="F4" s="359"/>
-      <c r="G4" s="359"/>
+      <c r="B4" s="321" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="321"/>
+      <c r="D4" s="321"/>
+      <c r="E4" s="321"/>
+      <c r="F4" s="321"/>
+      <c r="G4" s="321"/>
       <c r="K4" s="51"/>
     </row>
     <row r="5" spans="1:11" ht="24.75" customHeight="1">
       <c r="A5" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="360" t="s">
+      <c r="B5" s="322" t="s">
         <v>47</v>
       </c>
-      <c r="C5" s="360"/>
-      <c r="D5" s="360"/>
-      <c r="E5" s="360"/>
-      <c r="F5" s="360"/>
-      <c r="G5" s="360"/>
+      <c r="C5" s="322"/>
+      <c r="D5" s="322"/>
+      <c r="E5" s="322"/>
+      <c r="F5" s="322"/>
+      <c r="G5" s="322"/>
       <c r="K5" s="51"/>
     </row>
     <row r="6" spans="1:11" ht="12" customHeight="1">
       <c r="A6" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B6" s="360" t="s">
+      <c r="B6" s="322" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="360"/>
-      <c r="D6" s="360"/>
-      <c r="E6" s="360"/>
-      <c r="F6" s="360"/>
-      <c r="G6" s="360"/>
+      <c r="C6" s="322"/>
+      <c r="D6" s="322"/>
+      <c r="E6" s="322"/>
+      <c r="F6" s="322"/>
+      <c r="G6" s="322"/>
       <c r="K6" s="51"/>
     </row>
     <row r="7" spans="1:11" ht="12" customHeight="1">
       <c r="A7" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B7" s="361" t="s">
+      <c r="B7" s="323" t="s">
         <v>183</v>
       </c>
-      <c r="C7" s="361"/>
-      <c r="D7" s="361"/>
-      <c r="E7" s="361"/>
-      <c r="F7" s="361"/>
+      <c r="C7" s="323"/>
+      <c r="D7" s="323"/>
+      <c r="E7" s="323"/>
+      <c r="F7" s="323"/>
       <c r="G7" s="71" t="s">
         <v>50</v>
       </c>
@@ -16222,37 +16222,37 @@
       <c r="A22" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B22" s="362" t="s">
+      <c r="B22" s="324" t="s">
         <v>0</v>
       </c>
-      <c r="C22" s="365" t="s">
+      <c r="C22" s="327" t="s">
         <v>51</v>
       </c>
-      <c r="D22" s="366"/>
-      <c r="E22" s="366"/>
-      <c r="F22" s="367"/>
+      <c r="D22" s="328"/>
+      <c r="E22" s="328"/>
+      <c r="F22" s="329"/>
       <c r="G22" s="55"/>
     </row>
     <row r="23" spans="1:12" ht="12" customHeight="1">
       <c r="A23" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="363"/>
-      <c r="C23" s="368"/>
-      <c r="D23" s="369"/>
-      <c r="E23" s="369"/>
-      <c r="F23" s="370"/>
+      <c r="B23" s="325"/>
+      <c r="C23" s="330"/>
+      <c r="D23" s="331"/>
+      <c r="E23" s="331"/>
+      <c r="F23" s="332"/>
       <c r="G23" s="55"/>
     </row>
     <row r="24" spans="1:12" ht="24" customHeight="1">
       <c r="A24" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B24" s="364"/>
-      <c r="C24" s="371"/>
-      <c r="D24" s="372"/>
-      <c r="E24" s="372"/>
-      <c r="F24" s="373"/>
+      <c r="B24" s="326"/>
+      <c r="C24" s="333"/>
+      <c r="D24" s="334"/>
+      <c r="E24" s="334"/>
+      <c r="F24" s="335"/>
       <c r="G24" s="57" t="s">
         <v>52</v>
       </c>
@@ -16273,10 +16273,10 @@
       <c r="D28" s="57">
         <v>3</v>
       </c>
-      <c r="E28" s="383">
+      <c r="E28" s="375">
         <v>4</v>
       </c>
-      <c r="F28" s="384"/>
+      <c r="F28" s="376"/>
       <c r="G28" s="57">
         <v>8</v>
       </c>
@@ -16288,12 +16288,12 @@
       <c r="B29" s="58">
         <v>1</v>
       </c>
-      <c r="C29" s="323" t="s">
+      <c r="C29" s="336" t="s">
         <v>184</v>
       </c>
-      <c r="D29" s="324"/>
-      <c r="E29" s="324"/>
-      <c r="F29" s="324"/>
+      <c r="D29" s="337"/>
+      <c r="E29" s="337"/>
+      <c r="F29" s="337"/>
       <c r="G29" s="72" t="e">
         <f>SUM(G30:G77)</f>
         <v>#REF!</v>
@@ -16313,11 +16313,11 @@
       <c r="C30" s="73" t="s">
         <v>54</v>
       </c>
-      <c r="D30" s="323" t="s">
+      <c r="D30" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E30" s="324"/>
-      <c r="F30" s="324"/>
+      <c r="E30" s="337"/>
+      <c r="F30" s="337"/>
       <c r="G30" s="74"/>
       <c r="L30" s="53" t="e">
         <f>G29-L29</f>
@@ -16337,10 +16337,10 @@
       <c r="D31" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E31" s="336" t="s">
+      <c r="E31" s="355" t="s">
         <v>56</v>
       </c>
-      <c r="F31" s="337"/>
+      <c r="F31" s="356"/>
       <c r="G31" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16360,10 +16360,10 @@
       <c r="D32" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E32" s="336" t="s">
+      <c r="E32" s="355" t="s">
         <v>57</v>
       </c>
-      <c r="F32" s="337"/>
+      <c r="F32" s="356"/>
       <c r="G32" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16383,10 +16383,10 @@
       <c r="D33" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E33" s="336" t="s">
+      <c r="E33" s="355" t="s">
         <v>58</v>
       </c>
-      <c r="F33" s="337"/>
+      <c r="F33" s="356"/>
       <c r="G33" s="74"/>
     </row>
     <row r="34" spans="1:13" ht="12" customHeight="1">
@@ -16443,10 +16443,10 @@
       <c r="D36" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E36" s="319" t="s">
-        <v>44</v>
-      </c>
-      <c r="F36" s="320"/>
+      <c r="E36" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="F36" s="346"/>
       <c r="G36" s="74"/>
       <c r="H36" s="49"/>
     </row>
@@ -16460,11 +16460,11 @@
       <c r="C37" s="73" t="s">
         <v>171</v>
       </c>
-      <c r="D37" s="323" t="s">
+      <c r="D37" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E37" s="324"/>
-      <c r="F37" s="324"/>
+      <c r="E37" s="337"/>
+      <c r="F37" s="337"/>
       <c r="G37" s="74"/>
     </row>
     <row r="38" spans="1:13" ht="12" customHeight="1">
@@ -16480,10 +16480,10 @@
       <c r="D38" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E38" s="336" t="s">
+      <c r="E38" s="355" t="s">
         <v>172</v>
       </c>
-      <c r="F38" s="337"/>
+      <c r="F38" s="356"/>
       <c r="G38" s="74" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -16503,10 +16503,10 @@
       <c r="D39" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E39" s="336" t="s">
+      <c r="E39" s="355" t="s">
         <v>173</v>
       </c>
-      <c r="F39" s="337"/>
+      <c r="F39" s="356"/>
       <c r="G39" s="74"/>
     </row>
     <row r="40" spans="1:13" ht="12" customHeight="1">
@@ -16516,14 +16516,14 @@
       <c r="B40" s="58">
         <v>26</v>
       </c>
-      <c r="C40" s="332" t="s">
+      <c r="C40" s="339" t="s">
         <v>174</v>
       </c>
-      <c r="D40" s="323" t="s">
+      <c r="D40" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E40" s="324"/>
-      <c r="F40" s="324"/>
+      <c r="E40" s="337"/>
+      <c r="F40" s="337"/>
       <c r="G40" s="74"/>
     </row>
     <row r="41" spans="1:13" ht="12" customHeight="1">
@@ -16533,14 +16533,14 @@
       <c r="B41" s="58">
         <v>27</v>
       </c>
-      <c r="C41" s="333"/>
+      <c r="C41" s="340"/>
       <c r="D41" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E41" s="378" t="s">
-        <v>44</v>
-      </c>
-      <c r="F41" s="386"/>
+      <c r="E41" s="383" t="s">
+        <v>44</v>
+      </c>
+      <c r="F41" s="385"/>
       <c r="G41" s="74"/>
     </row>
     <row r="42" spans="1:13" ht="12" customHeight="1">
@@ -16556,10 +16556,10 @@
       <c r="D42" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E42" s="319" t="s">
-        <v>44</v>
-      </c>
-      <c r="F42" s="320"/>
+      <c r="E42" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="F42" s="346"/>
       <c r="G42" s="74"/>
       <c r="H42" s="49"/>
     </row>
@@ -16570,14 +16570,14 @@
       <c r="B43" s="58">
         <v>29</v>
       </c>
-      <c r="C43" s="332" t="s">
+      <c r="C43" s="339" t="s">
         <v>186</v>
       </c>
-      <c r="D43" s="323" t="s">
+      <c r="D43" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E43" s="324"/>
-      <c r="F43" s="324"/>
+      <c r="E43" s="337"/>
+      <c r="F43" s="337"/>
       <c r="G43" s="74"/>
     </row>
     <row r="44" spans="1:13" ht="12" customHeight="1">
@@ -16587,14 +16587,14 @@
       <c r="B44" s="58">
         <v>30</v>
       </c>
-      <c r="C44" s="333"/>
+      <c r="C44" s="340"/>
       <c r="D44" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E44" s="319" t="s">
+      <c r="E44" s="345" t="s">
         <v>128</v>
       </c>
-      <c r="F44" s="320"/>
+      <c r="F44" s="346"/>
       <c r="G44" s="74"/>
     </row>
     <row r="45" spans="1:13" ht="18.75" customHeight="1">
@@ -16604,14 +16604,14 @@
       <c r="B45" s="58">
         <v>31</v>
       </c>
-      <c r="C45" s="349"/>
+      <c r="C45" s="341"/>
       <c r="D45" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E45" s="389" t="s">
+      <c r="E45" s="386" t="s">
         <v>129</v>
       </c>
-      <c r="F45" s="390"/>
+      <c r="F45" s="387"/>
       <c r="G45" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16626,12 +16626,12 @@
       <c r="B46" s="58">
         <v>32</v>
       </c>
-      <c r="C46" s="323" t="s">
+      <c r="C46" s="336" t="s">
         <v>20</v>
       </c>
-      <c r="D46" s="324"/>
-      <c r="E46" s="324"/>
-      <c r="F46" s="324"/>
+      <c r="D46" s="337"/>
+      <c r="E46" s="337"/>
+      <c r="F46" s="337"/>
       <c r="G46" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16648,11 +16648,11 @@
       <c r="C47" s="73" t="s">
         <v>62</v>
       </c>
-      <c r="D47" s="323" t="s">
+      <c r="D47" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E47" s="324"/>
-      <c r="F47" s="324"/>
+      <c r="E47" s="337"/>
+      <c r="F47" s="337"/>
       <c r="G47" s="74"/>
       <c r="L47" s="53"/>
     </row>
@@ -16669,10 +16669,10 @@
       <c r="D48" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E48" s="336" t="s">
+      <c r="E48" s="355" t="s">
         <v>63</v>
       </c>
-      <c r="F48" s="337"/>
+      <c r="F48" s="356"/>
       <c r="G48" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16691,10 +16691,10 @@
       <c r="D49" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E49" s="336" t="s">
+      <c r="E49" s="355" t="s">
         <v>64</v>
       </c>
-      <c r="F49" s="337"/>
+      <c r="F49" s="356"/>
       <c r="G49" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16707,14 +16707,14 @@
       <c r="B50" s="58">
         <v>36</v>
       </c>
-      <c r="C50" s="332" t="s">
+      <c r="C50" s="339" t="s">
         <v>187</v>
       </c>
-      <c r="D50" s="323" t="s">
+      <c r="D50" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E50" s="324"/>
-      <c r="F50" s="324"/>
+      <c r="E50" s="337"/>
+      <c r="F50" s="337"/>
       <c r="G50" s="74"/>
     </row>
     <row r="51" spans="1:8" ht="12" customHeight="1">
@@ -16724,14 +16724,14 @@
       <c r="B51" s="58">
         <v>37</v>
       </c>
-      <c r="C51" s="333"/>
+      <c r="C51" s="340"/>
       <c r="D51" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E51" s="378" t="s">
-        <v>44</v>
-      </c>
-      <c r="F51" s="386"/>
+      <c r="E51" s="383" t="s">
+        <v>44</v>
+      </c>
+      <c r="F51" s="385"/>
       <c r="G51" s="74"/>
     </row>
     <row r="52" spans="1:8" ht="24.75" customHeight="1">
@@ -16747,10 +16747,10 @@
       <c r="D52" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E52" s="319" t="s">
+      <c r="E52" s="345" t="s">
         <v>188</v>
       </c>
-      <c r="F52" s="320"/>
+      <c r="F52" s="346"/>
       <c r="G52" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16764,12 +16764,12 @@
       <c r="B53" s="58">
         <v>43</v>
       </c>
-      <c r="C53" s="323" t="s">
+      <c r="C53" s="336" t="s">
         <v>16</v>
       </c>
-      <c r="D53" s="324"/>
-      <c r="E53" s="324"/>
-      <c r="F53" s="324"/>
+      <c r="D53" s="337"/>
+      <c r="E53" s="337"/>
+      <c r="F53" s="337"/>
       <c r="G53" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16782,12 +16782,12 @@
       <c r="B54" s="58">
         <v>44</v>
       </c>
-      <c r="C54" s="323" t="s">
+      <c r="C54" s="336" t="s">
         <v>14</v>
       </c>
-      <c r="D54" s="324"/>
-      <c r="E54" s="324"/>
-      <c r="F54" s="324"/>
+      <c r="D54" s="337"/>
+      <c r="E54" s="337"/>
+      <c r="F54" s="337"/>
       <c r="G54" s="74"/>
     </row>
     <row r="55" spans="1:8" ht="12" customHeight="1">
@@ -16800,11 +16800,11 @@
       <c r="C55" s="73" t="s">
         <v>137</v>
       </c>
-      <c r="D55" s="323" t="s">
+      <c r="D55" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E55" s="324"/>
-      <c r="F55" s="324"/>
+      <c r="E55" s="337"/>
+      <c r="F55" s="337"/>
       <c r="G55" s="74"/>
     </row>
     <row r="56" spans="1:8" ht="12" customHeight="1">
@@ -16820,10 +16820,10 @@
       <c r="D56" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E56" s="378" t="s">
-        <v>44</v>
-      </c>
-      <c r="F56" s="386"/>
+      <c r="E56" s="383" t="s">
+        <v>44</v>
+      </c>
+      <c r="F56" s="385"/>
       <c r="G56" s="74"/>
     </row>
     <row r="57" spans="1:8" ht="24.75" customHeight="1">
@@ -16839,10 +16839,10 @@
       <c r="D57" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E57" s="319" t="s">
+      <c r="E57" s="345" t="s">
         <v>4</v>
       </c>
-      <c r="F57" s="320"/>
+      <c r="F57" s="346"/>
       <c r="G57" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16862,10 +16862,10 @@
       <c r="D58" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E58" s="319" t="s">
-        <v>44</v>
-      </c>
-      <c r="F58" s="320"/>
+      <c r="E58" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="F58" s="346"/>
       <c r="G58" s="74"/>
       <c r="H58" s="49"/>
     </row>
@@ -16876,12 +16876,12 @@
       <c r="B59" s="58">
         <v>51</v>
       </c>
-      <c r="C59" s="323" t="s">
+      <c r="C59" s="336" t="s">
         <v>189</v>
       </c>
-      <c r="D59" s="324"/>
-      <c r="E59" s="324"/>
-      <c r="F59" s="324"/>
+      <c r="D59" s="337"/>
+      <c r="E59" s="337"/>
+      <c r="F59" s="337"/>
       <c r="G59" s="74"/>
     </row>
     <row r="60" spans="1:8" ht="12" customHeight="1">
@@ -16891,12 +16891,12 @@
       <c r="B60" s="58">
         <v>52</v>
       </c>
-      <c r="C60" s="323" t="s">
+      <c r="C60" s="336" t="s">
         <v>17</v>
       </c>
-      <c r="D60" s="324"/>
-      <c r="E60" s="324"/>
-      <c r="F60" s="324"/>
+      <c r="D60" s="337"/>
+      <c r="E60" s="337"/>
+      <c r="F60" s="337"/>
       <c r="G60" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16909,12 +16909,12 @@
       <c r="B61" s="58">
         <v>53</v>
       </c>
-      <c r="C61" s="323" t="s">
+      <c r="C61" s="336" t="s">
         <v>190</v>
       </c>
-      <c r="D61" s="324"/>
-      <c r="E61" s="324"/>
-      <c r="F61" s="324"/>
+      <c r="D61" s="337"/>
+      <c r="E61" s="337"/>
+      <c r="F61" s="337"/>
       <c r="G61" s="74"/>
     </row>
     <row r="62" spans="1:8" ht="12" customHeight="1">
@@ -16924,12 +16924,12 @@
       <c r="B62" s="58">
         <v>54</v>
       </c>
-      <c r="C62" s="323" t="s">
+      <c r="C62" s="336" t="s">
         <v>191</v>
       </c>
-      <c r="D62" s="324"/>
-      <c r="E62" s="324"/>
-      <c r="F62" s="324"/>
+      <c r="D62" s="337"/>
+      <c r="E62" s="337"/>
+      <c r="F62" s="337"/>
       <c r="G62" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16942,12 +16942,12 @@
       <c r="B63" s="58">
         <v>55</v>
       </c>
-      <c r="C63" s="323" t="s">
+      <c r="C63" s="336" t="s">
         <v>192</v>
       </c>
-      <c r="D63" s="324"/>
-      <c r="E63" s="324"/>
-      <c r="F63" s="324"/>
+      <c r="D63" s="337"/>
+      <c r="E63" s="337"/>
+      <c r="F63" s="337"/>
       <c r="G63" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16960,14 +16960,14 @@
       <c r="B64" s="58">
         <v>56</v>
       </c>
-      <c r="C64" s="332" t="s">
+      <c r="C64" s="339" t="s">
         <v>175</v>
       </c>
-      <c r="D64" s="323" t="s">
+      <c r="D64" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E64" s="324"/>
-      <c r="F64" s="324"/>
+      <c r="E64" s="337"/>
+      <c r="F64" s="337"/>
       <c r="G64" s="74"/>
     </row>
     <row r="65" spans="1:11" ht="12" customHeight="1">
@@ -16977,14 +16977,14 @@
       <c r="B65" s="58">
         <v>57</v>
       </c>
-      <c r="C65" s="333"/>
+      <c r="C65" s="340"/>
       <c r="D65" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E65" s="336" t="s">
+      <c r="E65" s="355" t="s">
         <v>91</v>
       </c>
-      <c r="F65" s="337"/>
+      <c r="F65" s="356"/>
       <c r="G65" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17003,10 +17003,10 @@
       <c r="D66" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E66" s="319" t="s">
+      <c r="E66" s="345" t="s">
         <v>193</v>
       </c>
-      <c r="F66" s="320"/>
+      <c r="F66" s="346"/>
       <c r="G66" s="74"/>
       <c r="H66" s="49"/>
     </row>
@@ -17017,14 +17017,14 @@
       <c r="B67" s="58">
         <v>59</v>
       </c>
-      <c r="C67" s="332" t="s">
+      <c r="C67" s="339" t="s">
         <v>102</v>
       </c>
-      <c r="D67" s="323" t="s">
+      <c r="D67" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E67" s="324"/>
-      <c r="F67" s="324"/>
+      <c r="E67" s="337"/>
+      <c r="F67" s="337"/>
       <c r="G67" s="74"/>
     </row>
     <row r="68" spans="1:11" ht="12" customHeight="1">
@@ -17034,14 +17034,14 @@
       <c r="B68" s="58">
         <v>60</v>
       </c>
-      <c r="C68" s="333"/>
+      <c r="C68" s="340"/>
       <c r="D68" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E68" s="378" t="s">
-        <v>44</v>
-      </c>
-      <c r="F68" s="386"/>
+      <c r="E68" s="383" t="s">
+        <v>44</v>
+      </c>
+      <c r="F68" s="385"/>
       <c r="G68" s="74"/>
     </row>
     <row r="69" spans="1:11" ht="12" customHeight="1">
@@ -17057,10 +17057,10 @@
       <c r="D69" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E69" s="319" t="s">
+      <c r="E69" s="345" t="s">
         <v>194</v>
       </c>
-      <c r="F69" s="320"/>
+      <c r="F69" s="346"/>
       <c r="G69" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17080,10 +17080,10 @@
       <c r="D70" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E70" s="319" t="s">
+      <c r="E70" s="345" t="s">
         <v>195</v>
       </c>
-      <c r="F70" s="320"/>
+      <c r="F70" s="346"/>
       <c r="G70" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17103,10 +17103,10 @@
       <c r="D71" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E71" s="387" t="s">
+      <c r="E71" s="388" t="s">
         <v>196</v>
       </c>
-      <c r="F71" s="388"/>
+      <c r="F71" s="389"/>
       <c r="G71" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17118,10 +17118,10 @@
       <c r="B72" s="58"/>
       <c r="C72" s="77"/>
       <c r="D72" s="70"/>
-      <c r="E72" s="387" t="s">
+      <c r="E72" s="388" t="s">
         <v>13</v>
       </c>
-      <c r="F72" s="388"/>
+      <c r="F72" s="389"/>
       <c r="G72" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17133,10 +17133,10 @@
       <c r="B73" s="58"/>
       <c r="C73" s="77"/>
       <c r="D73" s="70"/>
-      <c r="E73" s="387" t="s">
+      <c r="E73" s="388" t="s">
         <v>8</v>
       </c>
-      <c r="F73" s="388"/>
+      <c r="F73" s="389"/>
       <c r="G73" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17156,10 +17156,10 @@
       <c r="D74" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E74" s="319" t="s">
-        <v>44</v>
-      </c>
-      <c r="F74" s="320"/>
+      <c r="E74" s="345" t="s">
+        <v>44</v>
+      </c>
+      <c r="F74" s="346"/>
       <c r="G74" s="74"/>
       <c r="H74" s="49"/>
     </row>
@@ -17170,14 +17170,14 @@
       <c r="B75" s="58">
         <v>65</v>
       </c>
-      <c r="C75" s="332" t="s">
+      <c r="C75" s="339" t="s">
         <v>197</v>
       </c>
-      <c r="D75" s="323" t="s">
+      <c r="D75" s="336" t="s">
         <v>5</v>
       </c>
-      <c r="E75" s="324"/>
-      <c r="F75" s="324"/>
+      <c r="E75" s="337"/>
+      <c r="F75" s="337"/>
       <c r="G75" s="74"/>
     </row>
     <row r="76" spans="1:11" ht="12" customHeight="1">
@@ -17187,14 +17187,14 @@
       <c r="B76" s="58">
         <v>66</v>
       </c>
-      <c r="C76" s="333"/>
+      <c r="C76" s="340"/>
       <c r="D76" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E76" s="378" t="s">
-        <v>44</v>
-      </c>
-      <c r="F76" s="386"/>
+      <c r="E76" s="383" t="s">
+        <v>44</v>
+      </c>
+      <c r="F76" s="385"/>
       <c r="G76" s="74"/>
     </row>
     <row r="77" spans="1:11" ht="12" customHeight="1">
@@ -17210,10 +17210,10 @@
       <c r="D77" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E77" s="319" t="s">
+      <c r="E77" s="345" t="s">
         <v>198</v>
       </c>
-      <c r="F77" s="320"/>
+      <c r="F77" s="346"/>
       <c r="G77" s="81" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -17272,13 +17272,13 @@
       <c r="K79" s="51"/>
     </row>
     <row r="80" spans="1:11" ht="15" customHeight="1">
-      <c r="B80" s="385" t="s">
+      <c r="B80" s="390" t="s">
         <v>199</v>
       </c>
-      <c r="C80" s="385"/>
-      <c r="D80" s="385"/>
-      <c r="E80" s="385"/>
-      <c r="F80" s="385"/>
+      <c r="C80" s="390"/>
+      <c r="D80" s="390"/>
+      <c r="E80" s="390"/>
+      <c r="F80" s="390"/>
       <c r="G80" s="83"/>
       <c r="H80" s="83"/>
       <c r="I80" s="82"/>
@@ -17286,13 +17286,13 @@
       <c r="K80" s="51"/>
     </row>
     <row r="81" spans="2:11" ht="15" customHeight="1">
-      <c r="B81" s="385" t="s">
-        <v>44</v>
-      </c>
-      <c r="C81" s="385"/>
-      <c r="D81" s="385"/>
-      <c r="E81" s="385"/>
-      <c r="F81" s="385"/>
+      <c r="B81" s="390" t="s">
+        <v>44</v>
+      </c>
+      <c r="C81" s="390"/>
+      <c r="D81" s="390"/>
+      <c r="E81" s="390"/>
+      <c r="F81" s="390"/>
       <c r="G81" s="84"/>
       <c r="H81" s="84"/>
       <c r="I81" s="83"/>
@@ -17302,14 +17302,14 @@
     <row r="82" spans="2:11" ht="15.75" hidden="1" customHeight="1"/>
     <row r="83" spans="2:11" ht="15.75" hidden="1" customHeight="1"/>
     <row r="84" spans="2:11" ht="15" customHeight="1">
-      <c r="B84" s="385" t="s">
+      <c r="B84" s="390" t="s">
         <v>200</v>
       </c>
-      <c r="C84" s="385"/>
-      <c r="D84" s="385"/>
-      <c r="E84" s="385"/>
-      <c r="F84" s="385"/>
-      <c r="G84" s="385"/>
+      <c r="C84" s="390"/>
+      <c r="D84" s="390"/>
+      <c r="E84" s="390"/>
+      <c r="F84" s="390"/>
+      <c r="G84" s="390"/>
       <c r="H84" s="83"/>
       <c r="I84" s="83"/>
       <c r="J84" s="83"/>
@@ -17338,51 +17338,13 @@
     <row r="105" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="65">
-    <mergeCell ref="B7:F7"/>
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="B4:G4"/>
-    <mergeCell ref="B5:G5"/>
-    <mergeCell ref="B6:G6"/>
-    <mergeCell ref="E39:F39"/>
-    <mergeCell ref="B22:B24"/>
-    <mergeCell ref="C22:F24"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="E36:F36"/>
-    <mergeCell ref="D37:F37"/>
-    <mergeCell ref="E38:F38"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="D40:F40"/>
-    <mergeCell ref="E41:F41"/>
-    <mergeCell ref="E42:F42"/>
-    <mergeCell ref="C43:C45"/>
-    <mergeCell ref="D43:F43"/>
-    <mergeCell ref="E44:F44"/>
-    <mergeCell ref="E45:F45"/>
-    <mergeCell ref="C46:F46"/>
-    <mergeCell ref="D47:F47"/>
-    <mergeCell ref="E48:F48"/>
-    <mergeCell ref="E49:F49"/>
-    <mergeCell ref="C50:C51"/>
-    <mergeCell ref="D50:F50"/>
-    <mergeCell ref="E51:F51"/>
-    <mergeCell ref="C63:F63"/>
-    <mergeCell ref="E52:F52"/>
-    <mergeCell ref="C53:F53"/>
-    <mergeCell ref="C54:F54"/>
-    <mergeCell ref="D55:F55"/>
-    <mergeCell ref="E56:F56"/>
-    <mergeCell ref="E57:F57"/>
-    <mergeCell ref="E58:F58"/>
-    <mergeCell ref="C59:F59"/>
-    <mergeCell ref="C60:F60"/>
-    <mergeCell ref="C61:F61"/>
-    <mergeCell ref="C62:F62"/>
+    <mergeCell ref="B84:G84"/>
+    <mergeCell ref="C75:C76"/>
+    <mergeCell ref="D75:F75"/>
+    <mergeCell ref="E76:F76"/>
+    <mergeCell ref="E77:F77"/>
+    <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
     <mergeCell ref="E74:F74"/>
     <mergeCell ref="C64:C65"/>
     <mergeCell ref="D64:F64"/>
@@ -17396,13 +17358,51 @@
     <mergeCell ref="E71:F71"/>
     <mergeCell ref="E72:F72"/>
     <mergeCell ref="E73:F73"/>
-    <mergeCell ref="B84:G84"/>
-    <mergeCell ref="C75:C76"/>
-    <mergeCell ref="D75:F75"/>
-    <mergeCell ref="E76:F76"/>
-    <mergeCell ref="E77:F77"/>
-    <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="C63:F63"/>
+    <mergeCell ref="E52:F52"/>
+    <mergeCell ref="C53:F53"/>
+    <mergeCell ref="C54:F54"/>
+    <mergeCell ref="D55:F55"/>
+    <mergeCell ref="E56:F56"/>
+    <mergeCell ref="E57:F57"/>
+    <mergeCell ref="E58:F58"/>
+    <mergeCell ref="C59:F59"/>
+    <mergeCell ref="C60:F60"/>
+    <mergeCell ref="C61:F61"/>
+    <mergeCell ref="C62:F62"/>
+    <mergeCell ref="C46:F46"/>
+    <mergeCell ref="D47:F47"/>
+    <mergeCell ref="E48:F48"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="D50:F50"/>
+    <mergeCell ref="E51:F51"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="D40:F40"/>
+    <mergeCell ref="E41:F41"/>
+    <mergeCell ref="E42:F42"/>
+    <mergeCell ref="C43:C45"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="E44:F44"/>
+    <mergeCell ref="E45:F45"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="B22:B24"/>
+    <mergeCell ref="C22:F24"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="E38:F38"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="B6:G6"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Наименование на государственном языке заполняется автоматически в соответствии с КТРУ" sqref="B76 B49:B50 B95:B96"/>
@@ -17438,79 +17438,79 @@
       <c r="A1" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="399" t="s">
+      <c r="B1" s="430" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="399"/>
-      <c r="D1" s="399"/>
-      <c r="E1" s="399"/>
-      <c r="F1" s="399"/>
-      <c r="G1" s="399"/>
-      <c r="H1" s="399"/>
-      <c r="I1" s="399"/>
+      <c r="C1" s="430"/>
+      <c r="D1" s="430"/>
+      <c r="E1" s="430"/>
+      <c r="F1" s="430"/>
+      <c r="G1" s="430"/>
+      <c r="H1" s="430"/>
+      <c r="I1" s="430"/>
       <c r="M1" s="12"/>
     </row>
     <row r="2" spans="1:13" ht="14.25" customHeight="1">
       <c r="A2" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="400" t="s">
+      <c r="B2" s="431" t="s">
         <v>46</v>
       </c>
-      <c r="C2" s="400"/>
-      <c r="D2" s="400"/>
-      <c r="E2" s="400"/>
-      <c r="F2" s="400"/>
-      <c r="G2" s="400"/>
-      <c r="H2" s="400"/>
-      <c r="I2" s="400"/>
+      <c r="C2" s="431"/>
+      <c r="D2" s="431"/>
+      <c r="E2" s="431"/>
+      <c r="F2" s="431"/>
+      <c r="G2" s="431"/>
+      <c r="H2" s="431"/>
+      <c r="I2" s="431"/>
       <c r="M2" s="12"/>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="401" t="s">
+      <c r="B3" s="432" t="s">
         <v>47</v>
       </c>
-      <c r="C3" s="401"/>
-      <c r="D3" s="401"/>
-      <c r="E3" s="401"/>
-      <c r="F3" s="401"/>
-      <c r="G3" s="401"/>
-      <c r="H3" s="401"/>
-      <c r="I3" s="401"/>
+      <c r="C3" s="432"/>
+      <c r="D3" s="432"/>
+      <c r="E3" s="432"/>
+      <c r="F3" s="432"/>
+      <c r="G3" s="432"/>
+      <c r="H3" s="432"/>
+      <c r="I3" s="432"/>
       <c r="M3" s="12"/>
     </row>
     <row r="4" spans="1:13" ht="30" customHeight="1">
       <c r="A4" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="401" t="s">
+      <c r="B4" s="432" t="s">
         <v>48</v>
       </c>
-      <c r="C4" s="401"/>
-      <c r="D4" s="401"/>
-      <c r="E4" s="401"/>
-      <c r="F4" s="401"/>
-      <c r="G4" s="401"/>
-      <c r="H4" s="401"/>
-      <c r="I4" s="401"/>
+      <c r="C4" s="432"/>
+      <c r="D4" s="432"/>
+      <c r="E4" s="432"/>
+      <c r="F4" s="432"/>
+      <c r="G4" s="432"/>
+      <c r="H4" s="432"/>
+      <c r="I4" s="432"/>
       <c r="M4" s="12"/>
     </row>
     <row r="5" spans="1:13" ht="12" customHeight="1">
       <c r="A5" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="402" t="s">
+      <c r="B5" s="433" t="s">
         <v>49</v>
       </c>
-      <c r="C5" s="402"/>
-      <c r="D5" s="402"/>
-      <c r="E5" s="402"/>
-      <c r="F5" s="402"/>
-      <c r="G5" s="402"/>
-      <c r="H5" s="402"/>
+      <c r="C5" s="433"/>
+      <c r="D5" s="433"/>
+      <c r="E5" s="433"/>
+      <c r="F5" s="433"/>
+      <c r="G5" s="433"/>
+      <c r="H5" s="433"/>
       <c r="I5" s="13" t="s">
         <v>50</v>
       </c>
@@ -17534,18 +17534,18 @@
       <c r="A20" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="B20" s="403" t="s">
+      <c r="B20" s="434" t="s">
         <v>0</v>
       </c>
-      <c r="C20" s="406" t="s">
+      <c r="C20" s="437" t="s">
         <v>51</v>
       </c>
-      <c r="D20" s="407"/>
-      <c r="E20" s="407"/>
-      <c r="F20" s="407"/>
-      <c r="G20" s="407"/>
-      <c r="H20" s="408"/>
-      <c r="I20" s="415" t="s">
+      <c r="D20" s="438"/>
+      <c r="E20" s="438"/>
+      <c r="F20" s="438"/>
+      <c r="G20" s="438"/>
+      <c r="H20" s="439"/>
+      <c r="I20" s="446" t="s">
         <v>52</v>
       </c>
       <c r="J20" s="10"/>
@@ -17558,14 +17558,14 @@
       <c r="A21" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="B21" s="404"/>
-      <c r="C21" s="409"/>
-      <c r="D21" s="410"/>
-      <c r="E21" s="410"/>
-      <c r="F21" s="410"/>
-      <c r="G21" s="410"/>
-      <c r="H21" s="411"/>
-      <c r="I21" s="404"/>
+      <c r="B21" s="435"/>
+      <c r="C21" s="440"/>
+      <c r="D21" s="441"/>
+      <c r="E21" s="441"/>
+      <c r="F21" s="441"/>
+      <c r="G21" s="441"/>
+      <c r="H21" s="442"/>
+      <c r="I21" s="435"/>
       <c r="J21" s="10"/>
       <c r="K21" s="10"/>
       <c r="L21" s="10"/>
@@ -17575,14 +17575,14 @@
       <c r="A22" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="B22" s="405"/>
-      <c r="C22" s="412"/>
-      <c r="D22" s="413"/>
-      <c r="E22" s="413"/>
-      <c r="F22" s="413"/>
-      <c r="G22" s="413"/>
-      <c r="H22" s="414"/>
-      <c r="I22" s="405"/>
+      <c r="B22" s="436"/>
+      <c r="C22" s="443"/>
+      <c r="D22" s="444"/>
+      <c r="E22" s="444"/>
+      <c r="F22" s="444"/>
+      <c r="G22" s="444"/>
+      <c r="H22" s="445"/>
+      <c r="I22" s="436"/>
       <c r="J22" s="10"/>
       <c r="K22" s="10"/>
       <c r="L22" s="10"/>
@@ -17598,10 +17598,10 @@
       <c r="B26" s="18">
         <v>1</v>
       </c>
-      <c r="C26" s="391">
+      <c r="C26" s="428">
         <v>2</v>
       </c>
-      <c r="D26" s="392"/>
+      <c r="D26" s="429"/>
       <c r="E26" s="18">
         <v>3</v>
       </c>
@@ -17625,14 +17625,14 @@
       <c r="B27" s="19">
         <v>1</v>
       </c>
-      <c r="C27" s="393" t="s">
+      <c r="C27" s="394" t="s">
         <v>53</v>
       </c>
-      <c r="D27" s="394"/>
-      <c r="E27" s="394"/>
-      <c r="F27" s="394"/>
-      <c r="G27" s="394"/>
-      <c r="H27" s="395"/>
+      <c r="D27" s="395"/>
+      <c r="E27" s="395"/>
+      <c r="F27" s="395"/>
+      <c r="G27" s="395"/>
+      <c r="H27" s="396"/>
       <c r="I27" s="20"/>
       <c r="N27" s="16"/>
     </row>
@@ -17649,12 +17649,12 @@
       <c r="D28" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="E28" s="393" t="s">
+      <c r="E28" s="394" t="s">
         <v>5</v>
       </c>
-      <c r="F28" s="394"/>
-      <c r="G28" s="394"/>
-      <c r="H28" s="395"/>
+      <c r="F28" s="395"/>
+      <c r="G28" s="395"/>
+      <c r="H28" s="396"/>
       <c r="I28" s="20" t="e">
         <f>SUM(I29:I190)</f>
         <v>#REF!</v>
@@ -17680,11 +17680,11 @@
       <c r="E29" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F29" s="396" t="s">
+      <c r="F29" s="401" t="s">
         <v>56</v>
       </c>
-      <c r="G29" s="397"/>
-      <c r="H29" s="398"/>
+      <c r="G29" s="402"/>
+      <c r="H29" s="403"/>
       <c r="I29" s="20" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17710,11 +17710,11 @@
       <c r="E30" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F30" s="396" t="s">
+      <c r="F30" s="401" t="s">
         <v>57</v>
       </c>
-      <c r="G30" s="397"/>
-      <c r="H30" s="398"/>
+      <c r="G30" s="402"/>
+      <c r="H30" s="403"/>
       <c r="I30" s="20" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17737,11 +17737,11 @@
       <c r="E31" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F31" s="396" t="s">
+      <c r="F31" s="401" t="s">
         <v>58</v>
       </c>
-      <c r="G31" s="397"/>
-      <c r="H31" s="398"/>
+      <c r="G31" s="402"/>
+      <c r="H31" s="403"/>
       <c r="I31" s="20"/>
     </row>
     <row r="32" spans="1:14" ht="12" customHeight="1">
@@ -17760,11 +17760,11 @@
       <c r="E32" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F32" s="416" t="s">
+      <c r="F32" s="391" t="s">
         <v>59</v>
       </c>
-      <c r="G32" s="417"/>
-      <c r="H32" s="418"/>
+      <c r="G32" s="392"/>
+      <c r="H32" s="393"/>
       <c r="I32" s="20" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -17790,16 +17790,16 @@
       <c r="B34" s="21">
         <v>7</v>
       </c>
-      <c r="C34" s="419" t="s">
+      <c r="C34" s="397" t="s">
         <v>61</v>
       </c>
-      <c r="D34" s="420"/>
-      <c r="E34" s="393" t="s">
+      <c r="D34" s="398"/>
+      <c r="E34" s="394" t="s">
         <v>5</v>
       </c>
-      <c r="F34" s="394"/>
-      <c r="G34" s="394"/>
-      <c r="H34" s="395"/>
+      <c r="F34" s="395"/>
+      <c r="G34" s="395"/>
+      <c r="H34" s="396"/>
       <c r="I34" s="32"/>
     </row>
     <row r="35" spans="1:15" ht="12" customHeight="1">
@@ -17809,16 +17809,16 @@
       <c r="B35" s="21">
         <v>8</v>
       </c>
-      <c r="C35" s="421"/>
-      <c r="D35" s="422"/>
+      <c r="C35" s="399"/>
+      <c r="D35" s="400"/>
       <c r="E35" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F35" s="396" t="s">
-        <v>44</v>
-      </c>
-      <c r="G35" s="397"/>
-      <c r="H35" s="398"/>
+      <c r="F35" s="401" t="s">
+        <v>44</v>
+      </c>
+      <c r="G35" s="402"/>
+      <c r="H35" s="403"/>
       <c r="I35" s="32"/>
     </row>
     <row r="36" spans="1:15" hidden="1">
@@ -17831,16 +17831,16 @@
       <c r="B37" s="21">
         <v>10</v>
       </c>
-      <c r="C37" s="423" t="s">
+      <c r="C37" s="407" t="s">
         <v>62</v>
       </c>
-      <c r="D37" s="424"/>
-      <c r="E37" s="393" t="s">
+      <c r="D37" s="408"/>
+      <c r="E37" s="394" t="s">
         <v>5</v>
       </c>
-      <c r="F37" s="394"/>
-      <c r="G37" s="394"/>
-      <c r="H37" s="395"/>
+      <c r="F37" s="395"/>
+      <c r="G37" s="395"/>
+      <c r="H37" s="396"/>
       <c r="I37" s="32"/>
     </row>
     <row r="38" spans="1:15" ht="12" customHeight="1">
@@ -17850,16 +17850,16 @@
       <c r="B38" s="21">
         <v>11</v>
       </c>
-      <c r="C38" s="425"/>
-      <c r="D38" s="426"/>
-      <c r="E38" s="429" t="s">
+      <c r="C38" s="409"/>
+      <c r="D38" s="410"/>
+      <c r="E38" s="413" t="s">
         <v>55</v>
       </c>
-      <c r="F38" s="396" t="s">
+      <c r="F38" s="401" t="s">
         <v>63</v>
       </c>
-      <c r="G38" s="397"/>
-      <c r="H38" s="398"/>
+      <c r="G38" s="402"/>
+      <c r="H38" s="403"/>
       <c r="I38" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17872,14 +17872,14 @@
       <c r="B39" s="21">
         <v>12</v>
       </c>
-      <c r="C39" s="427"/>
-      <c r="D39" s="428"/>
-      <c r="E39" s="430"/>
-      <c r="F39" s="396" t="s">
+      <c r="C39" s="411"/>
+      <c r="D39" s="412"/>
+      <c r="E39" s="414"/>
+      <c r="F39" s="401" t="s">
         <v>64</v>
       </c>
-      <c r="G39" s="397"/>
-      <c r="H39" s="398"/>
+      <c r="G39" s="402"/>
+      <c r="H39" s="403"/>
       <c r="I39" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17892,16 +17892,16 @@
       <c r="B40" s="21">
         <v>13</v>
       </c>
-      <c r="C40" s="419" t="s">
+      <c r="C40" s="397" t="s">
         <v>65</v>
       </c>
-      <c r="D40" s="420"/>
-      <c r="E40" s="393" t="s">
+      <c r="D40" s="398"/>
+      <c r="E40" s="394" t="s">
         <v>5</v>
       </c>
-      <c r="F40" s="394"/>
-      <c r="G40" s="394"/>
-      <c r="H40" s="395"/>
+      <c r="F40" s="395"/>
+      <c r="G40" s="395"/>
+      <c r="H40" s="396"/>
       <c r="I40" s="32"/>
     </row>
     <row r="41" spans="1:15" ht="17.25" customHeight="1">
@@ -17911,16 +17911,16 @@
       <c r="B41" s="21">
         <v>14</v>
       </c>
-      <c r="C41" s="421"/>
-      <c r="D41" s="422"/>
+      <c r="C41" s="399"/>
+      <c r="D41" s="400"/>
       <c r="E41" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F41" s="396" t="s">
-        <v>44</v>
-      </c>
-      <c r="G41" s="397"/>
-      <c r="H41" s="398"/>
+      <c r="F41" s="401" t="s">
+        <v>44</v>
+      </c>
+      <c r="G41" s="402"/>
+      <c r="H41" s="403"/>
       <c r="I41" s="32"/>
     </row>
     <row r="42" spans="1:15" ht="12" customHeight="1">
@@ -17939,11 +17939,11 @@
       <c r="E42" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F42" s="416" t="s">
+      <c r="F42" s="391" t="s">
         <v>66</v>
       </c>
-      <c r="G42" s="417"/>
-      <c r="H42" s="418"/>
+      <c r="G42" s="392"/>
+      <c r="H42" s="393"/>
       <c r="I42" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17960,14 +17960,14 @@
       <c r="B44" s="21">
         <v>17</v>
       </c>
-      <c r="C44" s="393" t="s">
+      <c r="C44" s="394" t="s">
         <v>67</v>
       </c>
-      <c r="D44" s="394"/>
-      <c r="E44" s="394"/>
-      <c r="F44" s="394"/>
-      <c r="G44" s="394"/>
-      <c r="H44" s="395"/>
+      <c r="D44" s="395"/>
+      <c r="E44" s="395"/>
+      <c r="F44" s="395"/>
+      <c r="G44" s="395"/>
+      <c r="H44" s="396"/>
       <c r="I44" s="32"/>
     </row>
     <row r="45" spans="1:15" ht="12" customHeight="1">
@@ -17977,16 +17977,16 @@
       <c r="B45" s="21">
         <v>18</v>
       </c>
-      <c r="C45" s="431" t="s">
+      <c r="C45" s="422" t="s">
         <v>68</v>
       </c>
-      <c r="D45" s="432"/>
-      <c r="E45" s="393" t="s">
+      <c r="D45" s="423"/>
+      <c r="E45" s="394" t="s">
         <v>5</v>
       </c>
-      <c r="F45" s="394"/>
-      <c r="G45" s="394"/>
-      <c r="H45" s="395"/>
+      <c r="F45" s="395"/>
+      <c r="G45" s="395"/>
+      <c r="H45" s="396"/>
       <c r="I45" s="32"/>
     </row>
     <row r="46" spans="1:15" ht="30" customHeight="1">
@@ -17996,16 +17996,16 @@
       <c r="B46" s="21">
         <v>19</v>
       </c>
-      <c r="C46" s="433"/>
-      <c r="D46" s="434"/>
-      <c r="E46" s="429" t="s">
+      <c r="C46" s="424"/>
+      <c r="D46" s="425"/>
+      <c r="E46" s="413" t="s">
         <v>55</v>
       </c>
-      <c r="F46" s="396" t="s">
+      <c r="F46" s="401" t="s">
         <v>69</v>
       </c>
-      <c r="G46" s="397"/>
-      <c r="H46" s="398"/>
+      <c r="G46" s="402"/>
+      <c r="H46" s="403"/>
       <c r="I46" s="127" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -18020,14 +18020,14 @@
       <c r="B47" s="21">
         <v>20</v>
       </c>
-      <c r="C47" s="433"/>
-      <c r="D47" s="434"/>
-      <c r="E47" s="437"/>
-      <c r="F47" s="396" t="s">
+      <c r="C47" s="424"/>
+      <c r="D47" s="425"/>
+      <c r="E47" s="415"/>
+      <c r="F47" s="401" t="s">
         <v>70</v>
       </c>
-      <c r="G47" s="397"/>
-      <c r="H47" s="398"/>
+      <c r="G47" s="402"/>
+      <c r="H47" s="403"/>
       <c r="I47" s="127" t="e">
         <f>#REF!+#REF!-#REF!</f>
         <v>#REF!</v>
@@ -18042,14 +18042,14 @@
       <c r="B48" s="21">
         <v>21</v>
       </c>
-      <c r="C48" s="433"/>
-      <c r="D48" s="434"/>
-      <c r="E48" s="437"/>
-      <c r="F48" s="396" t="s">
+      <c r="C48" s="424"/>
+      <c r="D48" s="425"/>
+      <c r="E48" s="415"/>
+      <c r="F48" s="401" t="s">
         <v>71</v>
       </c>
-      <c r="G48" s="397"/>
-      <c r="H48" s="398"/>
+      <c r="G48" s="402"/>
+      <c r="H48" s="403"/>
       <c r="I48" s="127" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -18063,14 +18063,14 @@
       <c r="B49" s="21">
         <v>22</v>
       </c>
-      <c r="C49" s="435"/>
-      <c r="D49" s="436"/>
-      <c r="E49" s="430"/>
-      <c r="F49" s="396" t="s">
+      <c r="C49" s="426"/>
+      <c r="D49" s="427"/>
+      <c r="E49" s="414"/>
+      <c r="F49" s="401" t="s">
         <v>72</v>
       </c>
-      <c r="G49" s="397"/>
-      <c r="H49" s="398"/>
+      <c r="G49" s="402"/>
+      <c r="H49" s="403"/>
       <c r="I49" s="34" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -18084,16 +18084,16 @@
       <c r="B50" s="21">
         <v>23</v>
       </c>
-      <c r="C50" s="438" t="s">
+      <c r="C50" s="418" t="s">
         <v>73</v>
       </c>
-      <c r="D50" s="439"/>
-      <c r="E50" s="393" t="s">
+      <c r="D50" s="419"/>
+      <c r="E50" s="394" t="s">
         <v>5</v>
       </c>
-      <c r="F50" s="394"/>
-      <c r="G50" s="394"/>
-      <c r="H50" s="395"/>
+      <c r="F50" s="395"/>
+      <c r="G50" s="395"/>
+      <c r="H50" s="396"/>
       <c r="I50" s="32"/>
     </row>
     <row r="51" spans="1:14" ht="12" customHeight="1">
@@ -18103,16 +18103,16 @@
       <c r="B51" s="21">
         <v>24</v>
       </c>
-      <c r="C51" s="440"/>
-      <c r="D51" s="441"/>
+      <c r="C51" s="420"/>
+      <c r="D51" s="421"/>
       <c r="E51" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F51" s="396" t="s">
+      <c r="F51" s="401" t="s">
         <v>23</v>
       </c>
-      <c r="G51" s="397"/>
-      <c r="H51" s="398"/>
+      <c r="G51" s="402"/>
+      <c r="H51" s="403"/>
       <c r="I51" s="36" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -18135,11 +18135,11 @@
       <c r="E52" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F52" s="396" t="s">
+      <c r="F52" s="401" t="s">
         <v>74</v>
       </c>
-      <c r="G52" s="397"/>
-      <c r="H52" s="398"/>
+      <c r="G52" s="402"/>
+      <c r="H52" s="403"/>
       <c r="I52" s="32"/>
       <c r="N52" s="35"/>
     </row>
@@ -18153,16 +18153,16 @@
       <c r="B54" s="21">
         <v>27</v>
       </c>
-      <c r="C54" s="419" t="s">
+      <c r="C54" s="397" t="s">
         <v>75</v>
       </c>
-      <c r="D54" s="420"/>
-      <c r="E54" s="393" t="s">
+      <c r="D54" s="398"/>
+      <c r="E54" s="394" t="s">
         <v>5</v>
       </c>
-      <c r="F54" s="394"/>
-      <c r="G54" s="394"/>
-      <c r="H54" s="395"/>
+      <c r="F54" s="395"/>
+      <c r="G54" s="395"/>
+      <c r="H54" s="396"/>
       <c r="I54" s="32"/>
     </row>
     <row r="55" spans="1:14" ht="12" customHeight="1">
@@ -18172,16 +18172,16 @@
       <c r="B55" s="21">
         <v>28</v>
       </c>
-      <c r="C55" s="421"/>
-      <c r="D55" s="422"/>
+      <c r="C55" s="399"/>
+      <c r="D55" s="400"/>
       <c r="E55" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F55" s="396" t="s">
+      <c r="F55" s="401" t="s">
         <v>76</v>
       </c>
-      <c r="G55" s="397"/>
-      <c r="H55" s="398"/>
+      <c r="G55" s="402"/>
+      <c r="H55" s="403"/>
       <c r="I55" s="32"/>
     </row>
     <row r="56" spans="1:14" ht="12" customHeight="1">
@@ -18191,16 +18191,16 @@
       <c r="B56" s="21">
         <v>29</v>
       </c>
-      <c r="C56" s="421"/>
-      <c r="D56" s="422"/>
+      <c r="C56" s="399"/>
+      <c r="D56" s="400"/>
       <c r="E56" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F56" s="396" t="s">
+      <c r="F56" s="401" t="s">
         <v>77</v>
       </c>
-      <c r="G56" s="397"/>
-      <c r="H56" s="398"/>
+      <c r="G56" s="402"/>
+      <c r="H56" s="403"/>
       <c r="I56" s="32"/>
     </row>
     <row r="57" spans="1:14" ht="12" customHeight="1">
@@ -18210,16 +18210,16 @@
       <c r="B57" s="21">
         <v>30</v>
       </c>
-      <c r="C57" s="421"/>
-      <c r="D57" s="422"/>
+      <c r="C57" s="399"/>
+      <c r="D57" s="400"/>
       <c r="E57" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F57" s="396" t="s">
+      <c r="F57" s="401" t="s">
         <v>78</v>
       </c>
-      <c r="G57" s="397"/>
-      <c r="H57" s="398"/>
+      <c r="G57" s="402"/>
+      <c r="H57" s="403"/>
       <c r="I57" s="32"/>
     </row>
     <row r="58" spans="1:14" ht="12" customHeight="1">
@@ -18238,11 +18238,11 @@
       <c r="E58" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F58" s="396" t="s">
+      <c r="F58" s="401" t="s">
         <v>79</v>
       </c>
-      <c r="G58" s="397"/>
-      <c r="H58" s="398"/>
+      <c r="G58" s="402"/>
+      <c r="H58" s="403"/>
       <c r="I58" s="32" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -18258,14 +18258,14 @@
       <c r="B60" s="21">
         <v>33</v>
       </c>
-      <c r="C60" s="393" t="s">
+      <c r="C60" s="394" t="s">
         <v>80</v>
       </c>
-      <c r="D60" s="394"/>
-      <c r="E60" s="394"/>
-      <c r="F60" s="394"/>
-      <c r="G60" s="394"/>
-      <c r="H60" s="395"/>
+      <c r="D60" s="395"/>
+      <c r="E60" s="395"/>
+      <c r="F60" s="395"/>
+      <c r="G60" s="395"/>
+      <c r="H60" s="396"/>
       <c r="I60" s="32"/>
     </row>
     <row r="61" spans="1:14" ht="12" customHeight="1">
@@ -18275,16 +18275,16 @@
       <c r="B61" s="21">
         <v>34</v>
       </c>
-      <c r="C61" s="419" t="s">
+      <c r="C61" s="397" t="s">
         <v>81</v>
       </c>
-      <c r="D61" s="420"/>
-      <c r="E61" s="393" t="s">
+      <c r="D61" s="398"/>
+      <c r="E61" s="394" t="s">
         <v>5</v>
       </c>
-      <c r="F61" s="394"/>
-      <c r="G61" s="394"/>
-      <c r="H61" s="395"/>
+      <c r="F61" s="395"/>
+      <c r="G61" s="395"/>
+      <c r="H61" s="396"/>
       <c r="I61" s="32"/>
     </row>
     <row r="62" spans="1:14" ht="12" customHeight="1">
@@ -18294,18 +18294,18 @@
       <c r="B62" s="21">
         <v>35</v>
       </c>
-      <c r="C62" s="421"/>
-      <c r="D62" s="422"/>
+      <c r="C62" s="399"/>
+      <c r="D62" s="400"/>
       <c r="E62" s="26" t="s">
         <v>55</v>
       </c>
       <c r="F62" s="26" t="s">
         <v>82</v>
       </c>
-      <c r="G62" s="442" t="s">
+      <c r="G62" s="416" t="s">
         <v>5</v>
       </c>
-      <c r="H62" s="443"/>
+      <c r="H62" s="417"/>
       <c r="I62" s="32"/>
     </row>
     <row r="63" spans="1:14" ht="12" customHeight="1">
@@ -18315,8 +18315,8 @@
       <c r="B63" s="21">
         <v>36</v>
       </c>
-      <c r="C63" s="421"/>
-      <c r="D63" s="422"/>
+      <c r="C63" s="399"/>
+      <c r="D63" s="400"/>
       <c r="E63" s="27" t="s">
         <v>44</v>
       </c>
@@ -18380,10 +18380,10 @@
       <c r="F66" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="G66" s="442" t="s">
+      <c r="G66" s="416" t="s">
         <v>5</v>
       </c>
-      <c r="H66" s="443"/>
+      <c r="H66" s="417"/>
       <c r="I66" s="32"/>
     </row>
     <row r="67" spans="1:14" ht="12" customHeight="1">
@@ -18462,10 +18462,10 @@
       <c r="F70" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="G70" s="442" t="s">
+      <c r="G70" s="416" t="s">
         <v>5</v>
       </c>
-      <c r="H70" s="443"/>
+      <c r="H70" s="417"/>
       <c r="I70" s="32"/>
     </row>
     <row r="71" spans="1:14" ht="12" customHeight="1">
@@ -18544,10 +18544,10 @@
       <c r="F74" s="26" t="s">
         <v>87</v>
       </c>
-      <c r="G74" s="442" t="s">
+      <c r="G74" s="416" t="s">
         <v>5</v>
       </c>
-      <c r="H74" s="443"/>
+      <c r="H74" s="417"/>
       <c r="I74" s="32"/>
     </row>
     <row r="75" spans="1:14" ht="12" customHeight="1">
@@ -18614,16 +18614,16 @@
       <c r="B78" s="21">
         <v>51</v>
       </c>
-      <c r="C78" s="419" t="s">
+      <c r="C78" s="397" t="s">
         <v>88</v>
       </c>
-      <c r="D78" s="420"/>
-      <c r="E78" s="393" t="s">
+      <c r="D78" s="398"/>
+      <c r="E78" s="394" t="s">
         <v>5</v>
       </c>
-      <c r="F78" s="394"/>
-      <c r="G78" s="394"/>
-      <c r="H78" s="395"/>
+      <c r="F78" s="395"/>
+      <c r="G78" s="395"/>
+      <c r="H78" s="396"/>
       <c r="I78" s="32"/>
     </row>
     <row r="79" spans="1:14" ht="12" customHeight="1">
@@ -18633,16 +18633,16 @@
       <c r="B79" s="21">
         <v>52</v>
       </c>
-      <c r="C79" s="421"/>
-      <c r="D79" s="422"/>
+      <c r="C79" s="399"/>
+      <c r="D79" s="400"/>
       <c r="E79" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F79" s="396" t="s">
+      <c r="F79" s="401" t="s">
         <v>89</v>
       </c>
-      <c r="G79" s="397"/>
-      <c r="H79" s="398"/>
+      <c r="G79" s="402"/>
+      <c r="H79" s="403"/>
       <c r="I79" s="32"/>
     </row>
     <row r="80" spans="1:14" ht="12" customHeight="1">
@@ -18661,11 +18661,11 @@
       <c r="E80" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F80" s="396" t="s">
+      <c r="F80" s="401" t="s">
         <v>24</v>
       </c>
-      <c r="G80" s="397"/>
-      <c r="H80" s="398"/>
+      <c r="G80" s="402"/>
+      <c r="H80" s="403"/>
       <c r="I80" s="36" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -18688,11 +18688,11 @@
       <c r="E81" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F81" s="396" t="s">
+      <c r="F81" s="401" t="s">
         <v>90</v>
       </c>
-      <c r="G81" s="397"/>
-      <c r="H81" s="398"/>
+      <c r="G81" s="402"/>
+      <c r="H81" s="403"/>
       <c r="I81" s="32"/>
       <c r="N81" s="35"/>
     </row>
@@ -18712,13 +18712,13 @@
       <c r="E82" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F82" s="429" t="s">
+      <c r="F82" s="413" t="s">
         <v>91</v>
       </c>
-      <c r="G82" s="442" t="s">
+      <c r="G82" s="416" t="s">
         <v>5</v>
       </c>
-      <c r="H82" s="443"/>
+      <c r="H82" s="417"/>
       <c r="I82" s="32"/>
     </row>
     <row r="83" spans="1:14" ht="24" customHeight="1">
@@ -18737,8 +18737,8 @@
       <c r="E83" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F83" s="437"/>
-      <c r="G83" s="429" t="s">
+      <c r="F83" s="415"/>
+      <c r="G83" s="413" t="s">
         <v>55</v>
       </c>
       <c r="H83" s="15" t="s">
@@ -18765,8 +18765,8 @@
       <c r="E84" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F84" s="430"/>
-      <c r="G84" s="430"/>
+      <c r="F84" s="414"/>
+      <c r="G84" s="414"/>
       <c r="H84" s="15" t="s">
         <v>92</v>
       </c>
@@ -18791,11 +18791,11 @@
       <c r="E85" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F85" s="396" t="s">
+      <c r="F85" s="401" t="s">
         <v>9</v>
       </c>
-      <c r="G85" s="397"/>
-      <c r="H85" s="398"/>
+      <c r="G85" s="402"/>
+      <c r="H85" s="403"/>
       <c r="I85" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -18817,11 +18817,11 @@
       <c r="E86" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F86" s="396" t="s">
+      <c r="F86" s="401" t="s">
         <v>10</v>
       </c>
-      <c r="G86" s="397"/>
-      <c r="H86" s="398"/>
+      <c r="G86" s="402"/>
+      <c r="H86" s="403"/>
       <c r="I86" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -18843,11 +18843,11 @@
       <c r="E87" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F87" s="396" t="s">
+      <c r="F87" s="401" t="s">
         <v>11</v>
       </c>
-      <c r="G87" s="397"/>
-      <c r="H87" s="398"/>
+      <c r="G87" s="402"/>
+      <c r="H87" s="403"/>
       <c r="I87" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -18869,11 +18869,11 @@
       <c r="E88" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F88" s="396" t="s">
+      <c r="F88" s="401" t="s">
         <v>93</v>
       </c>
-      <c r="G88" s="397"/>
-      <c r="H88" s="398"/>
+      <c r="G88" s="402"/>
+      <c r="H88" s="403"/>
       <c r="I88" s="32"/>
     </row>
     <row r="89" spans="1:14" ht="12" customHeight="1">
@@ -18892,11 +18892,11 @@
       <c r="E89" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F89" s="416" t="s">
+      <c r="F89" s="391" t="s">
         <v>94</v>
       </c>
-      <c r="G89" s="417"/>
-      <c r="H89" s="418"/>
+      <c r="G89" s="392"/>
+      <c r="H89" s="393"/>
       <c r="I89" s="32"/>
       <c r="J89" s="10"/>
     </row>
@@ -18916,9 +18916,9 @@
       <c r="E90" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F90" s="416"/>
-      <c r="G90" s="417"/>
-      <c r="H90" s="418"/>
+      <c r="F90" s="391"/>
+      <c r="G90" s="392"/>
+      <c r="H90" s="393"/>
       <c r="I90" s="39"/>
       <c r="J90" s="10"/>
     </row>
@@ -18932,16 +18932,16 @@
       <c r="B92" s="21">
         <v>63</v>
       </c>
-      <c r="C92" s="419" t="s">
+      <c r="C92" s="397" t="s">
         <v>95</v>
       </c>
-      <c r="D92" s="420"/>
-      <c r="E92" s="393" t="s">
+      <c r="D92" s="398"/>
+      <c r="E92" s="394" t="s">
         <v>5</v>
       </c>
-      <c r="F92" s="394"/>
-      <c r="G92" s="394"/>
-      <c r="H92" s="395"/>
+      <c r="F92" s="395"/>
+      <c r="G92" s="395"/>
+      <c r="H92" s="396"/>
       <c r="I92" s="32"/>
     </row>
     <row r="93" spans="1:14" ht="12" customHeight="1">
@@ -18957,14 +18957,14 @@
       <c r="D93" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="E93" s="429" t="s">
+      <c r="E93" s="413" t="s">
         <v>55</v>
       </c>
-      <c r="F93" s="396" t="s">
-        <v>44</v>
-      </c>
-      <c r="G93" s="397"/>
-      <c r="H93" s="398"/>
+      <c r="F93" s="401" t="s">
+        <v>44</v>
+      </c>
+      <c r="G93" s="402"/>
+      <c r="H93" s="403"/>
       <c r="I93" s="32"/>
     </row>
     <row r="94" spans="1:14" ht="12" customHeight="1">
@@ -18980,12 +18980,12 @@
       <c r="D94" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="E94" s="430"/>
-      <c r="F94" s="416" t="s">
+      <c r="E94" s="414"/>
+      <c r="F94" s="391" t="s">
         <v>96</v>
       </c>
-      <c r="G94" s="417"/>
-      <c r="H94" s="418"/>
+      <c r="G94" s="392"/>
+      <c r="H94" s="393"/>
       <c r="I94" s="32"/>
       <c r="J94" s="10"/>
     </row>
@@ -18999,16 +18999,16 @@
       <c r="B96" s="21">
         <v>66</v>
       </c>
-      <c r="C96" s="419" t="s">
+      <c r="C96" s="397" t="s">
         <v>97</v>
       </c>
-      <c r="D96" s="420"/>
-      <c r="E96" s="393" t="s">
+      <c r="D96" s="398"/>
+      <c r="E96" s="394" t="s">
         <v>5</v>
       </c>
-      <c r="F96" s="394"/>
-      <c r="G96" s="394"/>
-      <c r="H96" s="395"/>
+      <c r="F96" s="395"/>
+      <c r="G96" s="395"/>
+      <c r="H96" s="396"/>
       <c r="I96" s="32"/>
     </row>
     <row r="97" spans="1:10" ht="12" customHeight="1">
@@ -19027,11 +19027,11 @@
       <c r="E97" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F97" s="396" t="s">
+      <c r="F97" s="401" t="s">
         <v>98</v>
       </c>
-      <c r="G97" s="397"/>
-      <c r="H97" s="398"/>
+      <c r="G97" s="402"/>
+      <c r="H97" s="403"/>
       <c r="I97" s="32"/>
     </row>
     <row r="98" spans="1:10" ht="12" customHeight="1">
@@ -19050,11 +19050,11 @@
       <c r="E98" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F98" s="396" t="s">
+      <c r="F98" s="401" t="s">
         <v>99</v>
       </c>
-      <c r="G98" s="397"/>
-      <c r="H98" s="398"/>
+      <c r="G98" s="402"/>
+      <c r="H98" s="403"/>
       <c r="I98" s="32"/>
     </row>
     <row r="99" spans="1:10" ht="12" customHeight="1">
@@ -19073,11 +19073,11 @@
       <c r="E99" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F99" s="396" t="s">
+      <c r="F99" s="401" t="s">
         <v>12</v>
       </c>
-      <c r="G99" s="397"/>
-      <c r="H99" s="398"/>
+      <c r="G99" s="402"/>
+      <c r="H99" s="403"/>
       <c r="I99" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19099,11 +19099,11 @@
       <c r="E100" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F100" s="396" t="s">
+      <c r="F100" s="401" t="s">
         <v>100</v>
       </c>
-      <c r="G100" s="397"/>
-      <c r="H100" s="398"/>
+      <c r="G100" s="402"/>
+      <c r="H100" s="403"/>
       <c r="I100" s="32"/>
     </row>
     <row r="101" spans="1:10" ht="12" customHeight="1">
@@ -19122,11 +19122,11 @@
       <c r="E101" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F101" s="416" t="s">
-        <v>44</v>
-      </c>
-      <c r="G101" s="417"/>
-      <c r="H101" s="418"/>
+      <c r="F101" s="391" t="s">
+        <v>44</v>
+      </c>
+      <c r="G101" s="392"/>
+      <c r="H101" s="393"/>
       <c r="I101" s="32"/>
       <c r="J101" s="10"/>
     </row>
@@ -19146,11 +19146,11 @@
       <c r="E102" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F102" s="416" t="s">
-        <v>44</v>
-      </c>
-      <c r="G102" s="417"/>
-      <c r="H102" s="418"/>
+      <c r="F102" s="391" t="s">
+        <v>44</v>
+      </c>
+      <c r="G102" s="392"/>
+      <c r="H102" s="393"/>
       <c r="I102" s="32"/>
       <c r="J102" s="10"/>
     </row>
@@ -19164,14 +19164,14 @@
       <c r="B104" s="21">
         <v>72</v>
       </c>
-      <c r="C104" s="393" t="s">
+      <c r="C104" s="394" t="s">
         <v>19</v>
       </c>
-      <c r="D104" s="394"/>
-      <c r="E104" s="394"/>
-      <c r="F104" s="394"/>
-      <c r="G104" s="394"/>
-      <c r="H104" s="395"/>
+      <c r="D104" s="395"/>
+      <c r="E104" s="395"/>
+      <c r="F104" s="395"/>
+      <c r="G104" s="395"/>
+      <c r="H104" s="396"/>
       <c r="I104" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19184,14 +19184,14 @@
       <c r="B105" s="21">
         <v>73</v>
       </c>
-      <c r="C105" s="393" t="s">
+      <c r="C105" s="394" t="s">
         <v>101</v>
       </c>
-      <c r="D105" s="394"/>
-      <c r="E105" s="394"/>
-      <c r="F105" s="394"/>
-      <c r="G105" s="394"/>
-      <c r="H105" s="395"/>
+      <c r="D105" s="395"/>
+      <c r="E105" s="395"/>
+      <c r="F105" s="395"/>
+      <c r="G105" s="395"/>
+      <c r="H105" s="396"/>
       <c r="I105" s="32"/>
     </row>
     <row r="106" spans="1:10" ht="12" customHeight="1">
@@ -19201,16 +19201,16 @@
       <c r="B106" s="21">
         <v>74</v>
       </c>
-      <c r="C106" s="419" t="s">
+      <c r="C106" s="397" t="s">
         <v>102</v>
       </c>
-      <c r="D106" s="420"/>
-      <c r="E106" s="393" t="s">
+      <c r="D106" s="398"/>
+      <c r="E106" s="394" t="s">
         <v>5</v>
       </c>
-      <c r="F106" s="394"/>
-      <c r="G106" s="394"/>
-      <c r="H106" s="395"/>
+      <c r="F106" s="395"/>
+      <c r="G106" s="395"/>
+      <c r="H106" s="396"/>
       <c r="I106" s="32"/>
     </row>
     <row r="107" spans="1:10" ht="18.75" customHeight="1">
@@ -19220,16 +19220,16 @@
       <c r="B107" s="21">
         <v>75</v>
       </c>
-      <c r="C107" s="421"/>
-      <c r="D107" s="422"/>
+      <c r="C107" s="399"/>
+      <c r="D107" s="400"/>
       <c r="E107" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F107" s="396" t="s">
+      <c r="F107" s="401" t="s">
         <v>13</v>
       </c>
-      <c r="G107" s="397"/>
-      <c r="H107" s="398"/>
+      <c r="G107" s="402"/>
+      <c r="H107" s="403"/>
       <c r="I107" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19251,11 +19251,11 @@
       <c r="E108" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F108" s="416" t="s">
+      <c r="F108" s="391" t="s">
         <v>103</v>
       </c>
-      <c r="G108" s="417"/>
-      <c r="H108" s="418"/>
+      <c r="G108" s="392"/>
+      <c r="H108" s="393"/>
       <c r="I108" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19278,11 +19278,11 @@
       <c r="E109" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F109" s="416" t="s">
+      <c r="F109" s="391" t="s">
         <v>104</v>
       </c>
-      <c r="G109" s="417"/>
-      <c r="H109" s="418"/>
+      <c r="G109" s="392"/>
+      <c r="H109" s="393"/>
       <c r="I109" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19305,11 +19305,11 @@
       <c r="E110" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F110" s="416" t="s">
+      <c r="F110" s="391" t="s">
         <v>8</v>
       </c>
-      <c r="G110" s="417"/>
-      <c r="H110" s="418"/>
+      <c r="G110" s="392"/>
+      <c r="H110" s="393"/>
       <c r="I110" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19326,16 +19326,16 @@
       <c r="B112" s="21">
         <v>77</v>
       </c>
-      <c r="C112" s="419" t="s">
+      <c r="C112" s="397" t="s">
         <v>105</v>
       </c>
-      <c r="D112" s="420"/>
-      <c r="E112" s="393" t="s">
+      <c r="D112" s="398"/>
+      <c r="E112" s="394" t="s">
         <v>5</v>
       </c>
-      <c r="F112" s="394"/>
-      <c r="G112" s="394"/>
-      <c r="H112" s="395"/>
+      <c r="F112" s="395"/>
+      <c r="G112" s="395"/>
+      <c r="H112" s="396"/>
       <c r="I112" s="32"/>
     </row>
     <row r="113" spans="1:9" ht="12" customHeight="1">
@@ -19354,11 +19354,11 @@
       <c r="E113" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F113" s="396" t="s">
+      <c r="F113" s="401" t="s">
         <v>106</v>
       </c>
-      <c r="G113" s="397"/>
-      <c r="H113" s="398"/>
+      <c r="G113" s="402"/>
+      <c r="H113" s="403"/>
       <c r="I113" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19380,11 +19380,11 @@
       <c r="E114" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F114" s="396" t="s">
+      <c r="F114" s="401" t="s">
         <v>107</v>
       </c>
-      <c r="G114" s="397"/>
-      <c r="H114" s="398"/>
+      <c r="G114" s="402"/>
+      <c r="H114" s="403"/>
       <c r="I114" s="32"/>
     </row>
     <row r="115" spans="1:9" ht="12" customHeight="1">
@@ -19394,14 +19394,14 @@
       <c r="B115" s="21">
         <v>80</v>
       </c>
-      <c r="C115" s="393" t="s">
+      <c r="C115" s="394" t="s">
         <v>108</v>
       </c>
-      <c r="D115" s="394"/>
-      <c r="E115" s="394"/>
-      <c r="F115" s="394"/>
-      <c r="G115" s="394"/>
-      <c r="H115" s="395"/>
+      <c r="D115" s="395"/>
+      <c r="E115" s="395"/>
+      <c r="F115" s="395"/>
+      <c r="G115" s="395"/>
+      <c r="H115" s="396"/>
       <c r="I115" s="32"/>
     </row>
     <row r="116" spans="1:9" ht="12" customHeight="1">
@@ -19411,16 +19411,16 @@
       <c r="B116" s="21">
         <v>81</v>
       </c>
-      <c r="C116" s="419" t="s">
+      <c r="C116" s="397" t="s">
         <v>109</v>
       </c>
-      <c r="D116" s="420"/>
-      <c r="E116" s="393" t="s">
+      <c r="D116" s="398"/>
+      <c r="E116" s="394" t="s">
         <v>5</v>
       </c>
-      <c r="F116" s="394"/>
-      <c r="G116" s="394"/>
-      <c r="H116" s="395"/>
+      <c r="F116" s="395"/>
+      <c r="G116" s="395"/>
+      <c r="H116" s="396"/>
       <c r="I116" s="32"/>
     </row>
     <row r="117" spans="1:9" ht="12" customHeight="1">
@@ -19430,16 +19430,16 @@
       <c r="B117" s="21">
         <v>82</v>
       </c>
-      <c r="C117" s="421"/>
-      <c r="D117" s="422"/>
+      <c r="C117" s="399"/>
+      <c r="D117" s="400"/>
       <c r="E117" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F117" s="396" t="s">
+      <c r="F117" s="401" t="s">
         <v>110</v>
       </c>
-      <c r="G117" s="397"/>
-      <c r="H117" s="398"/>
+      <c r="G117" s="402"/>
+      <c r="H117" s="403"/>
       <c r="I117" s="32"/>
     </row>
     <row r="118" spans="1:9" ht="12" customHeight="1">
@@ -19458,11 +19458,11 @@
       <c r="E118" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F118" s="396" t="s">
+      <c r="F118" s="401" t="s">
         <v>111</v>
       </c>
-      <c r="G118" s="397"/>
-      <c r="H118" s="398"/>
+      <c r="G118" s="402"/>
+      <c r="H118" s="403"/>
       <c r="I118" s="32"/>
     </row>
     <row r="119" spans="1:9" hidden="1">
@@ -19475,16 +19475,16 @@
       <c r="B120" s="21">
         <v>85</v>
       </c>
-      <c r="C120" s="419" t="s">
+      <c r="C120" s="397" t="s">
         <v>112</v>
       </c>
-      <c r="D120" s="420"/>
-      <c r="E120" s="393" t="s">
+      <c r="D120" s="398"/>
+      <c r="E120" s="394" t="s">
         <v>5</v>
       </c>
-      <c r="F120" s="394"/>
-      <c r="G120" s="394"/>
-      <c r="H120" s="395"/>
+      <c r="F120" s="395"/>
+      <c r="G120" s="395"/>
+      <c r="H120" s="396"/>
       <c r="I120" s="32"/>
     </row>
     <row r="121" spans="1:9" ht="12" customHeight="1">
@@ -19494,16 +19494,16 @@
       <c r="B121" s="21">
         <v>86</v>
       </c>
-      <c r="C121" s="421"/>
-      <c r="D121" s="422"/>
+      <c r="C121" s="399"/>
+      <c r="D121" s="400"/>
       <c r="E121" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F121" s="396" t="s">
+      <c r="F121" s="401" t="s">
         <v>113</v>
       </c>
-      <c r="G121" s="397"/>
-      <c r="H121" s="398"/>
+      <c r="G121" s="402"/>
+      <c r="H121" s="403"/>
       <c r="I121" s="32"/>
     </row>
     <row r="122" spans="1:9" ht="12" customHeight="1">
@@ -19522,11 +19522,11 @@
       <c r="E122" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F122" s="396" t="s">
+      <c r="F122" s="401" t="s">
         <v>111</v>
       </c>
-      <c r="G122" s="397"/>
-      <c r="H122" s="398"/>
+      <c r="G122" s="402"/>
+      <c r="H122" s="403"/>
       <c r="I122" s="32"/>
     </row>
     <row r="123" spans="1:9" ht="12" customHeight="1">
@@ -19545,11 +19545,11 @@
       <c r="E123" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F123" s="396" t="s">
+      <c r="F123" s="401" t="s">
         <v>114</v>
       </c>
-      <c r="G123" s="397"/>
-      <c r="H123" s="398"/>
+      <c r="G123" s="402"/>
+      <c r="H123" s="403"/>
       <c r="I123" s="32"/>
     </row>
     <row r="124" spans="1:9" ht="12" customHeight="1">
@@ -19568,11 +19568,11 @@
       <c r="E124" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F124" s="396" t="s">
+      <c r="F124" s="401" t="s">
         <v>115</v>
       </c>
-      <c r="G124" s="397"/>
-      <c r="H124" s="398"/>
+      <c r="G124" s="402"/>
+      <c r="H124" s="403"/>
       <c r="I124" s="32"/>
     </row>
     <row r="125" spans="1:9" hidden="1">
@@ -19585,14 +19585,14 @@
       <c r="B126" s="21">
         <v>91</v>
       </c>
-      <c r="C126" s="393" t="s">
+      <c r="C126" s="394" t="s">
         <v>116</v>
       </c>
-      <c r="D126" s="394"/>
-      <c r="E126" s="394"/>
-      <c r="F126" s="394"/>
-      <c r="G126" s="394"/>
-      <c r="H126" s="395"/>
+      <c r="D126" s="395"/>
+      <c r="E126" s="395"/>
+      <c r="F126" s="395"/>
+      <c r="G126" s="395"/>
+      <c r="H126" s="396"/>
       <c r="I126" s="32"/>
     </row>
     <row r="127" spans="1:9" ht="12" customHeight="1">
@@ -19602,16 +19602,16 @@
       <c r="B127" s="21">
         <v>92</v>
       </c>
-      <c r="C127" s="419" t="s">
+      <c r="C127" s="397" t="s">
         <v>117</v>
       </c>
-      <c r="D127" s="420"/>
-      <c r="E127" s="393" t="s">
+      <c r="D127" s="398"/>
+      <c r="E127" s="394" t="s">
         <v>5</v>
       </c>
-      <c r="F127" s="394"/>
-      <c r="G127" s="394"/>
-      <c r="H127" s="395"/>
+      <c r="F127" s="395"/>
+      <c r="G127" s="395"/>
+      <c r="H127" s="396"/>
       <c r="I127" s="32"/>
     </row>
     <row r="128" spans="1:9" ht="12" customHeight="1">
@@ -19621,16 +19621,16 @@
       <c r="B128" s="21">
         <v>93</v>
       </c>
-      <c r="C128" s="421"/>
-      <c r="D128" s="422"/>
+      <c r="C128" s="399"/>
+      <c r="D128" s="400"/>
       <c r="E128" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F128" s="444" t="s">
-        <v>44</v>
-      </c>
-      <c r="G128" s="445"/>
-      <c r="H128" s="446"/>
+      <c r="F128" s="404" t="s">
+        <v>44</v>
+      </c>
+      <c r="G128" s="405"/>
+      <c r="H128" s="406"/>
       <c r="I128" s="40"/>
     </row>
     <row r="129" spans="1:14" hidden="1">
@@ -19643,14 +19643,14 @@
       <c r="B130" s="21">
         <v>95</v>
       </c>
-      <c r="C130" s="393" t="s">
+      <c r="C130" s="394" t="s">
         <v>118</v>
       </c>
-      <c r="D130" s="394"/>
-      <c r="E130" s="394"/>
-      <c r="F130" s="394"/>
-      <c r="G130" s="394"/>
-      <c r="H130" s="395"/>
+      <c r="D130" s="395"/>
+      <c r="E130" s="395"/>
+      <c r="F130" s="395"/>
+      <c r="G130" s="395"/>
+      <c r="H130" s="396"/>
       <c r="I130" s="32"/>
     </row>
     <row r="131" spans="1:14" ht="12" customHeight="1">
@@ -19660,14 +19660,14 @@
       <c r="B131" s="21">
         <v>96</v>
       </c>
-      <c r="C131" s="393" t="s">
+      <c r="C131" s="394" t="s">
         <v>119</v>
       </c>
-      <c r="D131" s="394"/>
-      <c r="E131" s="394"/>
-      <c r="F131" s="394"/>
-      <c r="G131" s="394"/>
-      <c r="H131" s="395"/>
+      <c r="D131" s="395"/>
+      <c r="E131" s="395"/>
+      <c r="F131" s="395"/>
+      <c r="G131" s="395"/>
+      <c r="H131" s="396"/>
       <c r="I131" s="32"/>
     </row>
     <row r="132" spans="1:14" ht="12" customHeight="1">
@@ -19677,16 +19677,16 @@
       <c r="B132" s="21">
         <v>97</v>
       </c>
-      <c r="C132" s="419" t="s">
+      <c r="C132" s="397" t="s">
         <v>120</v>
       </c>
-      <c r="D132" s="420"/>
-      <c r="E132" s="393" t="s">
+      <c r="D132" s="398"/>
+      <c r="E132" s="394" t="s">
         <v>5</v>
       </c>
-      <c r="F132" s="394"/>
-      <c r="G132" s="394"/>
-      <c r="H132" s="395"/>
+      <c r="F132" s="395"/>
+      <c r="G132" s="395"/>
+      <c r="H132" s="396"/>
       <c r="I132" s="32"/>
     </row>
     <row r="133" spans="1:14" ht="12" customHeight="1">
@@ -19696,16 +19696,16 @@
       <c r="B133" s="21">
         <v>98</v>
       </c>
-      <c r="C133" s="421"/>
-      <c r="D133" s="422"/>
+      <c r="C133" s="399"/>
+      <c r="D133" s="400"/>
       <c r="E133" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F133" s="396" t="s">
+      <c r="F133" s="401" t="s">
         <v>121</v>
       </c>
-      <c r="G133" s="397"/>
-      <c r="H133" s="398"/>
+      <c r="G133" s="402"/>
+      <c r="H133" s="403"/>
       <c r="I133" s="32"/>
     </row>
     <row r="134" spans="1:14" ht="12" customHeight="1">
@@ -19715,16 +19715,16 @@
       <c r="B134" s="21">
         <v>99</v>
       </c>
-      <c r="C134" s="421"/>
-      <c r="D134" s="422"/>
+      <c r="C134" s="399"/>
+      <c r="D134" s="400"/>
       <c r="E134" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F134" s="396" t="s">
+      <c r="F134" s="401" t="s">
         <v>122</v>
       </c>
-      <c r="G134" s="397"/>
-      <c r="H134" s="398"/>
+      <c r="G134" s="402"/>
+      <c r="H134" s="403"/>
       <c r="I134" s="32"/>
     </row>
     <row r="135" spans="1:14" ht="12" customHeight="1">
@@ -19734,16 +19734,16 @@
       <c r="B135" s="21">
         <v>100</v>
       </c>
-      <c r="C135" s="421"/>
-      <c r="D135" s="422"/>
+      <c r="C135" s="399"/>
+      <c r="D135" s="400"/>
       <c r="E135" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F135" s="396" t="s">
+      <c r="F135" s="401" t="s">
         <v>123</v>
       </c>
-      <c r="G135" s="397"/>
-      <c r="H135" s="398"/>
+      <c r="G135" s="402"/>
+      <c r="H135" s="403"/>
       <c r="I135" s="32"/>
     </row>
     <row r="136" spans="1:14" ht="12" customHeight="1">
@@ -19762,11 +19762,11 @@
       <c r="E136" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F136" s="396" t="s">
+      <c r="F136" s="401" t="s">
         <v>124</v>
       </c>
-      <c r="G136" s="397"/>
-      <c r="H136" s="398"/>
+      <c r="G136" s="402"/>
+      <c r="H136" s="403"/>
       <c r="I136" s="32"/>
     </row>
     <row r="137" spans="1:14" ht="12" customHeight="1">
@@ -19785,11 +19785,11 @@
       <c r="E137" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F137" s="396" t="s">
+      <c r="F137" s="401" t="s">
         <v>125</v>
       </c>
-      <c r="G137" s="397"/>
-      <c r="H137" s="398"/>
+      <c r="G137" s="402"/>
+      <c r="H137" s="403"/>
       <c r="I137" s="32"/>
     </row>
     <row r="138" spans="1:14" ht="12" customHeight="1">
@@ -19808,11 +19808,11 @@
       <c r="E138" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F138" s="396" t="s">
+      <c r="F138" s="401" t="s">
         <v>126</v>
       </c>
-      <c r="G138" s="397"/>
-      <c r="H138" s="398"/>
+      <c r="G138" s="402"/>
+      <c r="H138" s="403"/>
       <c r="I138" s="32"/>
     </row>
     <row r="139" spans="1:14" hidden="1">
@@ -19825,16 +19825,16 @@
       <c r="B140" s="21">
         <v>105</v>
       </c>
-      <c r="C140" s="423" t="s">
+      <c r="C140" s="407" t="s">
         <v>127</v>
       </c>
-      <c r="D140" s="424"/>
-      <c r="E140" s="393" t="s">
+      <c r="D140" s="408"/>
+      <c r="E140" s="394" t="s">
         <v>5</v>
       </c>
-      <c r="F140" s="394"/>
-      <c r="G140" s="394"/>
-      <c r="H140" s="395"/>
+      <c r="F140" s="395"/>
+      <c r="G140" s="395"/>
+      <c r="H140" s="396"/>
       <c r="I140" s="32"/>
     </row>
     <row r="141" spans="1:14" ht="12" customHeight="1">
@@ -19844,16 +19844,16 @@
       <c r="B141" s="21">
         <v>106</v>
       </c>
-      <c r="C141" s="425"/>
-      <c r="D141" s="426"/>
-      <c r="E141" s="429" t="s">
+      <c r="C141" s="409"/>
+      <c r="D141" s="410"/>
+      <c r="E141" s="413" t="s">
         <v>55</v>
       </c>
-      <c r="F141" s="396" t="s">
+      <c r="F141" s="401" t="s">
         <v>128</v>
       </c>
-      <c r="G141" s="397"/>
-      <c r="H141" s="398"/>
+      <c r="G141" s="402"/>
+      <c r="H141" s="403"/>
       <c r="I141" s="32" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -19866,14 +19866,14 @@
       <c r="B142" s="21">
         <v>107</v>
       </c>
-      <c r="C142" s="427"/>
-      <c r="D142" s="428"/>
-      <c r="E142" s="430"/>
-      <c r="F142" s="396" t="s">
+      <c r="C142" s="411"/>
+      <c r="D142" s="412"/>
+      <c r="E142" s="414"/>
+      <c r="F142" s="401" t="s">
         <v>129</v>
       </c>
-      <c r="G142" s="397"/>
-      <c r="H142" s="398"/>
+      <c r="G142" s="402"/>
+      <c r="H142" s="403"/>
       <c r="I142" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19887,14 +19887,14 @@
       <c r="B143" s="21">
         <v>108</v>
       </c>
-      <c r="C143" s="393" t="s">
+      <c r="C143" s="394" t="s">
         <v>22</v>
       </c>
-      <c r="D143" s="394"/>
-      <c r="E143" s="394"/>
-      <c r="F143" s="394"/>
-      <c r="G143" s="394"/>
-      <c r="H143" s="395"/>
+      <c r="D143" s="395"/>
+      <c r="E143" s="395"/>
+      <c r="F143" s="395"/>
+      <c r="G143" s="395"/>
+      <c r="H143" s="396"/>
       <c r="I143" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19914,12 +19914,12 @@
       <c r="D144" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="E144" s="393" t="s">
+      <c r="E144" s="394" t="s">
         <v>5</v>
       </c>
-      <c r="F144" s="394"/>
-      <c r="G144" s="394"/>
-      <c r="H144" s="395"/>
+      <c r="F144" s="395"/>
+      <c r="G144" s="395"/>
+      <c r="H144" s="396"/>
       <c r="I144" s="32"/>
     </row>
     <row r="145" spans="1:10" ht="12" customHeight="1">
@@ -19938,11 +19938,11 @@
       <c r="E145" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F145" s="396" t="s">
+      <c r="F145" s="401" t="s">
         <v>131</v>
       </c>
-      <c r="G145" s="397"/>
-      <c r="H145" s="398"/>
+      <c r="G145" s="402"/>
+      <c r="H145" s="403"/>
       <c r="I145" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19964,11 +19964,11 @@
       <c r="E146" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F146" s="396" t="s">
+      <c r="F146" s="401" t="s">
         <v>132</v>
       </c>
-      <c r="G146" s="397"/>
-      <c r="H146" s="398"/>
+      <c r="G146" s="402"/>
+      <c r="H146" s="403"/>
       <c r="I146" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19990,11 +19990,11 @@
       <c r="E147" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F147" s="396" t="s">
+      <c r="F147" s="401" t="s">
         <v>64</v>
       </c>
-      <c r="G147" s="397"/>
-      <c r="H147" s="398"/>
+      <c r="G147" s="402"/>
+      <c r="H147" s="403"/>
       <c r="I147" s="32"/>
     </row>
     <row r="148" spans="1:10" ht="12" customHeight="1">
@@ -20013,11 +20013,11 @@
       <c r="E148" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F148" s="416" t="s">
+      <c r="F148" s="391" t="s">
         <v>133</v>
       </c>
-      <c r="G148" s="417"/>
-      <c r="H148" s="418"/>
+      <c r="G148" s="392"/>
+      <c r="H148" s="393"/>
       <c r="I148" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20040,11 +20040,11 @@
       <c r="E149" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F149" s="416" t="s">
+      <c r="F149" s="391" t="s">
         <v>134</v>
       </c>
-      <c r="G149" s="417"/>
-      <c r="H149" s="418"/>
+      <c r="G149" s="392"/>
+      <c r="H149" s="393"/>
       <c r="I149" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20067,11 +20067,11 @@
       <c r="E150" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F150" s="416" t="s">
+      <c r="F150" s="391" t="s">
         <v>135</v>
       </c>
-      <c r="G150" s="417"/>
-      <c r="H150" s="418"/>
+      <c r="G150" s="392"/>
+      <c r="H150" s="393"/>
       <c r="I150" s="32"/>
       <c r="J150" s="10"/>
     </row>
@@ -20091,11 +20091,11 @@
       <c r="E151" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F151" s="416" t="s">
+      <c r="F151" s="391" t="s">
         <v>136</v>
       </c>
-      <c r="G151" s="417"/>
-      <c r="H151" s="418"/>
+      <c r="G151" s="392"/>
+      <c r="H151" s="393"/>
       <c r="I151" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20112,16 +20112,16 @@
       <c r="B153" s="21">
         <v>114</v>
       </c>
-      <c r="C153" s="419" t="s">
+      <c r="C153" s="397" t="s">
         <v>137</v>
       </c>
-      <c r="D153" s="420"/>
-      <c r="E153" s="393" t="s">
+      <c r="D153" s="398"/>
+      <c r="E153" s="394" t="s">
         <v>5</v>
       </c>
-      <c r="F153" s="394"/>
-      <c r="G153" s="394"/>
-      <c r="H153" s="395"/>
+      <c r="F153" s="395"/>
+      <c r="G153" s="395"/>
+      <c r="H153" s="396"/>
       <c r="I153" s="32"/>
     </row>
     <row r="154" spans="1:10" ht="12" customHeight="1">
@@ -20131,16 +20131,16 @@
       <c r="B154" s="21">
         <v>115</v>
       </c>
-      <c r="C154" s="421"/>
-      <c r="D154" s="422"/>
+      <c r="C154" s="399"/>
+      <c r="D154" s="400"/>
       <c r="E154" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F154" s="444" t="s">
-        <v>44</v>
-      </c>
-      <c r="G154" s="445"/>
-      <c r="H154" s="446"/>
+      <c r="F154" s="404" t="s">
+        <v>44</v>
+      </c>
+      <c r="G154" s="405"/>
+      <c r="H154" s="406"/>
       <c r="I154" s="40"/>
     </row>
     <row r="155" spans="1:10" ht="12" customHeight="1">
@@ -20159,11 +20159,11 @@
       <c r="E155" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F155" s="416" t="s">
+      <c r="F155" s="391" t="s">
         <v>4</v>
       </c>
-      <c r="G155" s="417"/>
-      <c r="H155" s="418"/>
+      <c r="G155" s="392"/>
+      <c r="H155" s="393"/>
       <c r="I155" s="32"/>
       <c r="J155" s="10"/>
     </row>
@@ -20183,11 +20183,11 @@
       <c r="E156" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F156" s="416" t="s">
+      <c r="F156" s="391" t="s">
         <v>138</v>
       </c>
-      <c r="G156" s="417"/>
-      <c r="H156" s="418"/>
+      <c r="G156" s="392"/>
+      <c r="H156" s="393"/>
       <c r="I156" s="32"/>
       <c r="J156" s="10"/>
     </row>
@@ -20207,11 +20207,11 @@
       <c r="E157" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F157" s="416" t="s">
+      <c r="F157" s="391" t="s">
         <v>139</v>
       </c>
-      <c r="G157" s="417"/>
-      <c r="H157" s="418"/>
+      <c r="G157" s="392"/>
+      <c r="H157" s="393"/>
       <c r="I157" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20234,9 +20234,9 @@
       <c r="E158" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F158" s="416"/>
-      <c r="G158" s="417"/>
-      <c r="H158" s="418"/>
+      <c r="F158" s="391"/>
+      <c r="G158" s="392"/>
+      <c r="H158" s="393"/>
       <c r="I158" s="32"/>
       <c r="J158" s="10"/>
     </row>
@@ -20250,14 +20250,14 @@
       <c r="B160" s="21">
         <v>117</v>
       </c>
-      <c r="C160" s="393" t="s">
+      <c r="C160" s="394" t="s">
         <v>140</v>
       </c>
-      <c r="D160" s="394"/>
-      <c r="E160" s="394"/>
-      <c r="F160" s="394"/>
-      <c r="G160" s="394"/>
-      <c r="H160" s="395"/>
+      <c r="D160" s="395"/>
+      <c r="E160" s="395"/>
+      <c r="F160" s="395"/>
+      <c r="G160" s="395"/>
+      <c r="H160" s="396"/>
       <c r="I160" s="32"/>
     </row>
     <row r="161" spans="1:9" ht="12" customHeight="1">
@@ -20267,14 +20267,14 @@
       <c r="B161" s="21">
         <v>118</v>
       </c>
-      <c r="C161" s="393" t="s">
+      <c r="C161" s="394" t="s">
         <v>141</v>
       </c>
-      <c r="D161" s="394"/>
-      <c r="E161" s="394"/>
-      <c r="F161" s="394"/>
-      <c r="G161" s="394"/>
-      <c r="H161" s="395"/>
+      <c r="D161" s="395"/>
+      <c r="E161" s="395"/>
+      <c r="F161" s="395"/>
+      <c r="G161" s="395"/>
+      <c r="H161" s="396"/>
       <c r="I161" s="42" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -20287,14 +20287,14 @@
       <c r="B162" s="21">
         <v>119</v>
       </c>
-      <c r="C162" s="393" t="s">
+      <c r="C162" s="394" t="s">
         <v>142</v>
       </c>
-      <c r="D162" s="394"/>
-      <c r="E162" s="394"/>
-      <c r="F162" s="394"/>
-      <c r="G162" s="394"/>
-      <c r="H162" s="395"/>
+      <c r="D162" s="395"/>
+      <c r="E162" s="395"/>
+      <c r="F162" s="395"/>
+      <c r="G162" s="395"/>
+      <c r="H162" s="396"/>
       <c r="I162" s="32"/>
     </row>
     <row r="163" spans="1:9" ht="12" customHeight="1">
@@ -20304,14 +20304,14 @@
       <c r="B163" s="21">
         <v>120</v>
       </c>
-      <c r="C163" s="393" t="s">
+      <c r="C163" s="394" t="s">
         <v>143</v>
       </c>
-      <c r="D163" s="394"/>
-      <c r="E163" s="394"/>
-      <c r="F163" s="394"/>
-      <c r="G163" s="394"/>
-      <c r="H163" s="395"/>
+      <c r="D163" s="395"/>
+      <c r="E163" s="395"/>
+      <c r="F163" s="395"/>
+      <c r="G163" s="395"/>
+      <c r="H163" s="396"/>
       <c r="I163" s="32"/>
     </row>
     <row r="164" spans="1:9" ht="12" customHeight="1">
@@ -20321,14 +20321,14 @@
       <c r="B164" s="21">
         <v>121</v>
       </c>
-      <c r="C164" s="393" t="s">
+      <c r="C164" s="394" t="s">
         <v>144</v>
       </c>
-      <c r="D164" s="394"/>
-      <c r="E164" s="394"/>
-      <c r="F164" s="394"/>
-      <c r="G164" s="394"/>
-      <c r="H164" s="395"/>
+      <c r="D164" s="395"/>
+      <c r="E164" s="395"/>
+      <c r="F164" s="395"/>
+      <c r="G164" s="395"/>
+      <c r="H164" s="396"/>
       <c r="I164" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20341,16 +20341,16 @@
       <c r="B165" s="21">
         <v>122</v>
       </c>
-      <c r="C165" s="419" t="s">
+      <c r="C165" s="397" t="s">
         <v>145</v>
       </c>
-      <c r="D165" s="420"/>
-      <c r="E165" s="393" t="s">
+      <c r="D165" s="398"/>
+      <c r="E165" s="394" t="s">
         <v>5</v>
       </c>
-      <c r="F165" s="394"/>
-      <c r="G165" s="394"/>
-      <c r="H165" s="395"/>
+      <c r="F165" s="395"/>
+      <c r="G165" s="395"/>
+      <c r="H165" s="396"/>
       <c r="I165" s="32"/>
     </row>
     <row r="166" spans="1:9" ht="12" customHeight="1">
@@ -20360,16 +20360,16 @@
       <c r="B166" s="21">
         <v>123</v>
       </c>
-      <c r="C166" s="421"/>
-      <c r="D166" s="422"/>
+      <c r="C166" s="399"/>
+      <c r="D166" s="400"/>
       <c r="E166" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F166" s="396" t="s">
+      <c r="F166" s="401" t="s">
         <v>146</v>
       </c>
-      <c r="G166" s="397"/>
-      <c r="H166" s="398"/>
+      <c r="G166" s="402"/>
+      <c r="H166" s="403"/>
       <c r="I166" s="32"/>
     </row>
     <row r="167" spans="1:9" ht="12" customHeight="1">
@@ -20388,11 +20388,11 @@
       <c r="E167" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F167" s="396" t="s">
+      <c r="F167" s="401" t="s">
         <v>147</v>
       </c>
-      <c r="G167" s="397"/>
-      <c r="H167" s="398"/>
+      <c r="G167" s="402"/>
+      <c r="H167" s="403"/>
       <c r="I167" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20414,11 +20414,11 @@
       <c r="E168" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F168" s="396" t="s">
+      <c r="F168" s="401" t="s">
         <v>148</v>
       </c>
-      <c r="G168" s="397"/>
-      <c r="H168" s="398"/>
+      <c r="G168" s="402"/>
+      <c r="H168" s="403"/>
       <c r="I168" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20434,14 +20434,14 @@
       <c r="B170" s="21">
         <v>127</v>
       </c>
-      <c r="C170" s="393" t="s">
+      <c r="C170" s="394" t="s">
         <v>17</v>
       </c>
-      <c r="D170" s="394"/>
-      <c r="E170" s="394"/>
-      <c r="F170" s="394"/>
-      <c r="G170" s="394"/>
-      <c r="H170" s="395"/>
+      <c r="D170" s="395"/>
+      <c r="E170" s="395"/>
+      <c r="F170" s="395"/>
+      <c r="G170" s="395"/>
+      <c r="H170" s="396"/>
       <c r="I170" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20454,14 +20454,14 @@
       <c r="B171" s="21">
         <v>128</v>
       </c>
-      <c r="C171" s="393" t="s">
+      <c r="C171" s="394" t="s">
         <v>149</v>
       </c>
-      <c r="D171" s="394"/>
-      <c r="E171" s="394"/>
-      <c r="F171" s="394"/>
-      <c r="G171" s="394"/>
-      <c r="H171" s="395"/>
+      <c r="D171" s="395"/>
+      <c r="E171" s="395"/>
+      <c r="F171" s="395"/>
+      <c r="G171" s="395"/>
+      <c r="H171" s="396"/>
       <c r="I171" s="32"/>
     </row>
     <row r="172" spans="1:9" ht="12" customHeight="1">
@@ -20471,14 +20471,14 @@
       <c r="B172" s="21">
         <v>129</v>
       </c>
-      <c r="C172" s="393" t="s">
+      <c r="C172" s="394" t="s">
         <v>150</v>
       </c>
-      <c r="D172" s="394"/>
-      <c r="E172" s="394"/>
-      <c r="F172" s="394"/>
-      <c r="G172" s="394"/>
-      <c r="H172" s="395"/>
+      <c r="D172" s="395"/>
+      <c r="E172" s="395"/>
+      <c r="F172" s="395"/>
+      <c r="G172" s="395"/>
+      <c r="H172" s="396"/>
       <c r="I172" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20491,14 +20491,14 @@
       <c r="B173" s="21">
         <v>130</v>
       </c>
-      <c r="C173" s="393" t="s">
+      <c r="C173" s="394" t="s">
         <v>151</v>
       </c>
-      <c r="D173" s="394"/>
-      <c r="E173" s="394"/>
-      <c r="F173" s="394"/>
-      <c r="G173" s="394"/>
-      <c r="H173" s="395"/>
+      <c r="D173" s="395"/>
+      <c r="E173" s="395"/>
+      <c r="F173" s="395"/>
+      <c r="G173" s="395"/>
+      <c r="H173" s="396"/>
       <c r="I173" s="32"/>
     </row>
     <row r="174" spans="1:9" ht="12" customHeight="1">
@@ -20508,14 +20508,14 @@
       <c r="B174" s="21">
         <v>131</v>
       </c>
-      <c r="C174" s="393" t="s">
+      <c r="C174" s="394" t="s">
         <v>152</v>
       </c>
-      <c r="D174" s="394"/>
-      <c r="E174" s="394"/>
-      <c r="F174" s="394"/>
-      <c r="G174" s="394"/>
-      <c r="H174" s="395"/>
+      <c r="D174" s="395"/>
+      <c r="E174" s="395"/>
+      <c r="F174" s="395"/>
+      <c r="G174" s="395"/>
+      <c r="H174" s="396"/>
       <c r="I174" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20528,16 +20528,16 @@
       <c r="B175" s="21">
         <v>132</v>
       </c>
-      <c r="C175" s="419" t="s">
+      <c r="C175" s="397" t="s">
         <v>153</v>
       </c>
-      <c r="D175" s="420"/>
-      <c r="E175" s="393" t="s">
+      <c r="D175" s="398"/>
+      <c r="E175" s="394" t="s">
         <v>5</v>
       </c>
-      <c r="F175" s="394"/>
-      <c r="G175" s="394"/>
-      <c r="H175" s="395"/>
+      <c r="F175" s="395"/>
+      <c r="G175" s="395"/>
+      <c r="H175" s="396"/>
       <c r="I175" s="32"/>
     </row>
     <row r="176" spans="1:9" ht="12" customHeight="1">
@@ -20547,16 +20547,16 @@
       <c r="B176" s="21">
         <v>133</v>
       </c>
-      <c r="C176" s="421"/>
-      <c r="D176" s="422"/>
+      <c r="C176" s="399"/>
+      <c r="D176" s="400"/>
       <c r="E176" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F176" s="396" t="s">
+      <c r="F176" s="401" t="s">
         <v>128</v>
       </c>
-      <c r="G176" s="397"/>
-      <c r="H176" s="398"/>
+      <c r="G176" s="402"/>
+      <c r="H176" s="403"/>
       <c r="I176" s="32"/>
     </row>
     <row r="177" spans="1:14" ht="12" customHeight="1">
@@ -20566,16 +20566,16 @@
       <c r="B177" s="21">
         <v>134</v>
       </c>
-      <c r="C177" s="421"/>
-      <c r="D177" s="422"/>
+      <c r="C177" s="399"/>
+      <c r="D177" s="400"/>
       <c r="E177" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F177" s="396" t="s">
+      <c r="F177" s="401" t="s">
         <v>154</v>
       </c>
-      <c r="G177" s="397"/>
-      <c r="H177" s="398"/>
+      <c r="G177" s="402"/>
+      <c r="H177" s="403"/>
       <c r="I177" s="32"/>
     </row>
     <row r="178" spans="1:14" ht="12" customHeight="1">
@@ -20594,11 +20594,11 @@
       <c r="E178" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F178" s="396" t="s">
+      <c r="F178" s="401" t="s">
         <v>155</v>
       </c>
-      <c r="G178" s="397"/>
-      <c r="H178" s="398"/>
+      <c r="G178" s="402"/>
+      <c r="H178" s="403"/>
       <c r="I178" s="32"/>
     </row>
     <row r="179" spans="1:14" hidden="1">
@@ -20611,14 +20611,14 @@
       <c r="B180" s="21">
         <v>137</v>
       </c>
-      <c r="C180" s="393" t="s">
+      <c r="C180" s="394" t="s">
         <v>156</v>
       </c>
-      <c r="D180" s="394"/>
-      <c r="E180" s="394"/>
-      <c r="F180" s="394"/>
-      <c r="G180" s="394"/>
-      <c r="H180" s="395"/>
+      <c r="D180" s="395"/>
+      <c r="E180" s="395"/>
+      <c r="F180" s="395"/>
+      <c r="G180" s="395"/>
+      <c r="H180" s="396"/>
       <c r="I180" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20631,14 +20631,14 @@
       <c r="B181" s="21">
         <v>138</v>
       </c>
-      <c r="C181" s="393" t="s">
+      <c r="C181" s="394" t="s">
         <v>21</v>
       </c>
-      <c r="D181" s="394"/>
-      <c r="E181" s="394"/>
-      <c r="F181" s="394"/>
-      <c r="G181" s="394"/>
-      <c r="H181" s="395"/>
+      <c r="D181" s="395"/>
+      <c r="E181" s="395"/>
+      <c r="F181" s="395"/>
+      <c r="G181" s="395"/>
+      <c r="H181" s="396"/>
       <c r="I181" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20651,16 +20651,16 @@
       <c r="B182" s="21">
         <v>139</v>
       </c>
-      <c r="C182" s="419" t="s">
+      <c r="C182" s="397" t="s">
         <v>157</v>
       </c>
-      <c r="D182" s="420"/>
-      <c r="E182" s="393" t="s">
+      <c r="D182" s="398"/>
+      <c r="E182" s="394" t="s">
         <v>5</v>
       </c>
-      <c r="F182" s="394"/>
-      <c r="G182" s="394"/>
-      <c r="H182" s="395"/>
+      <c r="F182" s="395"/>
+      <c r="G182" s="395"/>
+      <c r="H182" s="396"/>
       <c r="I182" s="32"/>
     </row>
     <row r="183" spans="1:14" ht="12" customHeight="1">
@@ -20670,16 +20670,16 @@
       <c r="B183" s="21">
         <v>140</v>
       </c>
-      <c r="C183" s="421"/>
-      <c r="D183" s="422"/>
+      <c r="C183" s="399"/>
+      <c r="D183" s="400"/>
       <c r="E183" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F183" s="396" t="s">
-        <v>44</v>
-      </c>
-      <c r="G183" s="397"/>
-      <c r="H183" s="398"/>
+      <c r="F183" s="401" t="s">
+        <v>44</v>
+      </c>
+      <c r="G183" s="402"/>
+      <c r="H183" s="403"/>
       <c r="I183" s="32"/>
     </row>
     <row r="184" spans="1:14" hidden="1">
@@ -20692,16 +20692,16 @@
       <c r="B185" s="21">
         <v>142</v>
       </c>
-      <c r="C185" s="419" t="s">
+      <c r="C185" s="397" t="s">
         <v>158</v>
       </c>
-      <c r="D185" s="420"/>
-      <c r="E185" s="393" t="s">
+      <c r="D185" s="398"/>
+      <c r="E185" s="394" t="s">
         <v>5</v>
       </c>
-      <c r="F185" s="394"/>
-      <c r="G185" s="394"/>
-      <c r="H185" s="395"/>
+      <c r="F185" s="395"/>
+      <c r="G185" s="395"/>
+      <c r="H185" s="396"/>
       <c r="I185" s="32"/>
     </row>
     <row r="186" spans="1:14" ht="12" customHeight="1">
@@ -20711,16 +20711,16 @@
       <c r="B186" s="21">
         <v>143</v>
       </c>
-      <c r="C186" s="421"/>
-      <c r="D186" s="422"/>
+      <c r="C186" s="399"/>
+      <c r="D186" s="400"/>
       <c r="E186" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F186" s="396" t="s">
+      <c r="F186" s="401" t="s">
         <v>159</v>
       </c>
-      <c r="G186" s="397"/>
-      <c r="H186" s="398"/>
+      <c r="G186" s="402"/>
+      <c r="H186" s="403"/>
       <c r="I186" s="32"/>
     </row>
     <row r="187" spans="1:14" ht="12" customHeight="1">
@@ -20730,16 +20730,16 @@
       <c r="B187" s="21">
         <v>144</v>
       </c>
-      <c r="C187" s="421"/>
-      <c r="D187" s="422"/>
+      <c r="C187" s="399"/>
+      <c r="D187" s="400"/>
       <c r="E187" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F187" s="396" t="s">
+      <c r="F187" s="401" t="s">
         <v>160</v>
       </c>
-      <c r="G187" s="397"/>
-      <c r="H187" s="398"/>
+      <c r="G187" s="402"/>
+      <c r="H187" s="403"/>
       <c r="I187" s="32"/>
     </row>
     <row r="188" spans="1:14" ht="12" customHeight="1">
@@ -20758,11 +20758,11 @@
       <c r="E188" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F188" s="416" t="s">
+      <c r="F188" s="391" t="s">
         <v>161</v>
       </c>
-      <c r="G188" s="417"/>
-      <c r="H188" s="418"/>
+      <c r="G188" s="392"/>
+      <c r="H188" s="393"/>
       <c r="I188" s="32"/>
       <c r="J188" s="10"/>
     </row>
@@ -20782,11 +20782,11 @@
       <c r="E189" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F189" s="416" t="s">
+      <c r="F189" s="391" t="s">
         <v>162</v>
       </c>
-      <c r="G189" s="417"/>
-      <c r="H189" s="418"/>
+      <c r="G189" s="392"/>
+      <c r="H189" s="393"/>
       <c r="I189" s="32"/>
       <c r="J189" s="10"/>
     </row>
@@ -20806,11 +20806,11 @@
       <c r="E190" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="F190" s="416" t="s">
+      <c r="F190" s="391" t="s">
         <v>163</v>
       </c>
-      <c r="G190" s="417"/>
-      <c r="H190" s="418"/>
+      <c r="G190" s="392"/>
+      <c r="H190" s="393"/>
       <c r="I190" s="32" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -20873,104 +20873,63 @@
     </row>
   </sheetData>
   <mergeCells count="169">
-    <mergeCell ref="F188:H188"/>
-    <mergeCell ref="F189:H189"/>
-    <mergeCell ref="F190:H190"/>
-    <mergeCell ref="C180:H180"/>
-    <mergeCell ref="C181:H181"/>
-    <mergeCell ref="C182:D183"/>
-    <mergeCell ref="E182:H182"/>
-    <mergeCell ref="F183:H183"/>
-    <mergeCell ref="C185:D187"/>
-    <mergeCell ref="E185:H185"/>
-    <mergeCell ref="F186:H186"/>
-    <mergeCell ref="F187:H187"/>
-    <mergeCell ref="C174:H174"/>
-    <mergeCell ref="C175:D177"/>
-    <mergeCell ref="E175:H175"/>
-    <mergeCell ref="F176:H176"/>
-    <mergeCell ref="F177:H177"/>
-    <mergeCell ref="F178:H178"/>
-    <mergeCell ref="F167:H167"/>
-    <mergeCell ref="F168:H168"/>
-    <mergeCell ref="C170:H170"/>
-    <mergeCell ref="C171:H171"/>
-    <mergeCell ref="C172:H172"/>
-    <mergeCell ref="C173:H173"/>
-    <mergeCell ref="C162:H162"/>
-    <mergeCell ref="C163:H163"/>
-    <mergeCell ref="C164:H164"/>
-    <mergeCell ref="C165:D166"/>
-    <mergeCell ref="E165:H165"/>
-    <mergeCell ref="F166:H166"/>
-    <mergeCell ref="F155:H155"/>
-    <mergeCell ref="F156:H156"/>
-    <mergeCell ref="F157:H157"/>
-    <mergeCell ref="F158:H158"/>
-    <mergeCell ref="C160:H160"/>
-    <mergeCell ref="C161:H161"/>
-    <mergeCell ref="F149:H149"/>
-    <mergeCell ref="F150:H150"/>
-    <mergeCell ref="F151:H151"/>
-    <mergeCell ref="C153:D154"/>
-    <mergeCell ref="E153:H153"/>
-    <mergeCell ref="F154:H154"/>
-    <mergeCell ref="C143:H143"/>
-    <mergeCell ref="E144:H144"/>
-    <mergeCell ref="F145:H145"/>
-    <mergeCell ref="F146:H146"/>
-    <mergeCell ref="F147:H147"/>
-    <mergeCell ref="F148:H148"/>
-    <mergeCell ref="F137:H137"/>
-    <mergeCell ref="F138:H138"/>
-    <mergeCell ref="C140:D142"/>
-    <mergeCell ref="E140:H140"/>
-    <mergeCell ref="E141:E142"/>
-    <mergeCell ref="F141:H141"/>
-    <mergeCell ref="F142:H142"/>
-    <mergeCell ref="C132:D135"/>
-    <mergeCell ref="E132:H132"/>
-    <mergeCell ref="F133:H133"/>
-    <mergeCell ref="F134:H134"/>
-    <mergeCell ref="F135:H135"/>
-    <mergeCell ref="F136:H136"/>
-    <mergeCell ref="C126:H126"/>
-    <mergeCell ref="C127:D128"/>
-    <mergeCell ref="E127:H127"/>
-    <mergeCell ref="F128:H128"/>
-    <mergeCell ref="C130:H130"/>
-    <mergeCell ref="C131:H131"/>
-    <mergeCell ref="C120:D121"/>
-    <mergeCell ref="E120:H120"/>
-    <mergeCell ref="F121:H121"/>
-    <mergeCell ref="F122:H122"/>
-    <mergeCell ref="F123:H123"/>
-    <mergeCell ref="F124:H124"/>
-    <mergeCell ref="F114:H114"/>
-    <mergeCell ref="C115:H115"/>
-    <mergeCell ref="C116:D117"/>
-    <mergeCell ref="E116:H116"/>
-    <mergeCell ref="F117:H117"/>
-    <mergeCell ref="F118:H118"/>
-    <mergeCell ref="F108:H108"/>
-    <mergeCell ref="F109:H109"/>
-    <mergeCell ref="F110:H110"/>
-    <mergeCell ref="C112:D112"/>
-    <mergeCell ref="E112:H112"/>
-    <mergeCell ref="F113:H113"/>
-    <mergeCell ref="F101:H101"/>
-    <mergeCell ref="F102:H102"/>
-    <mergeCell ref="C104:H104"/>
-    <mergeCell ref="C105:H105"/>
-    <mergeCell ref="C106:D107"/>
-    <mergeCell ref="E106:H106"/>
-    <mergeCell ref="F107:H107"/>
-    <mergeCell ref="C96:D96"/>
-    <mergeCell ref="E96:H96"/>
-    <mergeCell ref="F97:H97"/>
-    <mergeCell ref="F98:H98"/>
-    <mergeCell ref="F99:H99"/>
-    <mergeCell ref="F100:H100"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:H27"/>
+    <mergeCell ref="E28:H28"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B3:I3"/>
+    <mergeCell ref="B4:I4"/>
+    <mergeCell ref="B5:H5"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="C20:H22"/>
+    <mergeCell ref="I20:I22"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="C34:D35"/>
+    <mergeCell ref="E34:H34"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="C37:D39"/>
+    <mergeCell ref="E37:H37"/>
+    <mergeCell ref="E38:E39"/>
+    <mergeCell ref="F38:H38"/>
+    <mergeCell ref="F39:H39"/>
+    <mergeCell ref="C40:D41"/>
+    <mergeCell ref="E40:H40"/>
+    <mergeCell ref="F41:H41"/>
+    <mergeCell ref="F42:H42"/>
+    <mergeCell ref="C44:H44"/>
+    <mergeCell ref="C45:D49"/>
+    <mergeCell ref="E45:H45"/>
+    <mergeCell ref="E46:E49"/>
+    <mergeCell ref="F46:H46"/>
+    <mergeCell ref="F47:H47"/>
+    <mergeCell ref="C54:D57"/>
+    <mergeCell ref="E54:H54"/>
+    <mergeCell ref="F55:H55"/>
+    <mergeCell ref="F56:H56"/>
+    <mergeCell ref="F57:H57"/>
+    <mergeCell ref="F58:H58"/>
+    <mergeCell ref="F48:H48"/>
+    <mergeCell ref="F49:H49"/>
+    <mergeCell ref="C50:D51"/>
+    <mergeCell ref="E50:H50"/>
+    <mergeCell ref="F51:H51"/>
+    <mergeCell ref="F52:H52"/>
+    <mergeCell ref="G74:H74"/>
+    <mergeCell ref="C78:D79"/>
+    <mergeCell ref="E78:H78"/>
+    <mergeCell ref="F79:H79"/>
+    <mergeCell ref="F80:H80"/>
+    <mergeCell ref="F81:H81"/>
+    <mergeCell ref="C60:H60"/>
+    <mergeCell ref="C61:D63"/>
+    <mergeCell ref="E61:H61"/>
+    <mergeCell ref="G62:H62"/>
+    <mergeCell ref="G66:H66"/>
+    <mergeCell ref="G70:H70"/>
     <mergeCell ref="F88:H88"/>
     <mergeCell ref="F89:H89"/>
     <mergeCell ref="F90:H90"/>
@@ -20985,63 +20944,104 @@
     <mergeCell ref="F85:H85"/>
     <mergeCell ref="F86:H86"/>
     <mergeCell ref="F87:H87"/>
-    <mergeCell ref="G74:H74"/>
-    <mergeCell ref="C78:D79"/>
-    <mergeCell ref="E78:H78"/>
-    <mergeCell ref="F79:H79"/>
-    <mergeCell ref="F80:H80"/>
-    <mergeCell ref="F81:H81"/>
-    <mergeCell ref="C60:H60"/>
-    <mergeCell ref="C61:D63"/>
-    <mergeCell ref="E61:H61"/>
-    <mergeCell ref="G62:H62"/>
-    <mergeCell ref="G66:H66"/>
-    <mergeCell ref="G70:H70"/>
-    <mergeCell ref="C54:D57"/>
-    <mergeCell ref="E54:H54"/>
-    <mergeCell ref="F55:H55"/>
-    <mergeCell ref="F56:H56"/>
-    <mergeCell ref="F57:H57"/>
-    <mergeCell ref="F58:H58"/>
-    <mergeCell ref="F48:H48"/>
-    <mergeCell ref="F49:H49"/>
-    <mergeCell ref="C50:D51"/>
-    <mergeCell ref="E50:H50"/>
-    <mergeCell ref="F51:H51"/>
-    <mergeCell ref="F52:H52"/>
-    <mergeCell ref="C40:D41"/>
-    <mergeCell ref="E40:H40"/>
-    <mergeCell ref="F41:H41"/>
-    <mergeCell ref="F42:H42"/>
-    <mergeCell ref="C44:H44"/>
-    <mergeCell ref="C45:D49"/>
-    <mergeCell ref="E45:H45"/>
-    <mergeCell ref="E46:E49"/>
-    <mergeCell ref="F46:H46"/>
-    <mergeCell ref="F47:H47"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="C34:D35"/>
-    <mergeCell ref="E34:H34"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="C37:D39"/>
-    <mergeCell ref="E37:H37"/>
-    <mergeCell ref="E38:E39"/>
-    <mergeCell ref="F38:H38"/>
-    <mergeCell ref="F39:H39"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:H27"/>
-    <mergeCell ref="E28:H28"/>
-    <mergeCell ref="F29:H29"/>
-    <mergeCell ref="F30:H30"/>
-    <mergeCell ref="F31:H31"/>
-    <mergeCell ref="B1:I1"/>
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="B3:I3"/>
-    <mergeCell ref="B4:I4"/>
-    <mergeCell ref="B5:H5"/>
-    <mergeCell ref="B20:B22"/>
-    <mergeCell ref="C20:H22"/>
-    <mergeCell ref="I20:I22"/>
+    <mergeCell ref="F101:H101"/>
+    <mergeCell ref="F102:H102"/>
+    <mergeCell ref="C104:H104"/>
+    <mergeCell ref="C105:H105"/>
+    <mergeCell ref="C106:D107"/>
+    <mergeCell ref="E106:H106"/>
+    <mergeCell ref="F107:H107"/>
+    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="E96:H96"/>
+    <mergeCell ref="F97:H97"/>
+    <mergeCell ref="F98:H98"/>
+    <mergeCell ref="F99:H99"/>
+    <mergeCell ref="F100:H100"/>
+    <mergeCell ref="F114:H114"/>
+    <mergeCell ref="C115:H115"/>
+    <mergeCell ref="C116:D117"/>
+    <mergeCell ref="E116:H116"/>
+    <mergeCell ref="F117:H117"/>
+    <mergeCell ref="F118:H118"/>
+    <mergeCell ref="F108:H108"/>
+    <mergeCell ref="F109:H109"/>
+    <mergeCell ref="F110:H110"/>
+    <mergeCell ref="C112:D112"/>
+    <mergeCell ref="E112:H112"/>
+    <mergeCell ref="F113:H113"/>
+    <mergeCell ref="C126:H126"/>
+    <mergeCell ref="C127:D128"/>
+    <mergeCell ref="E127:H127"/>
+    <mergeCell ref="F128:H128"/>
+    <mergeCell ref="C130:H130"/>
+    <mergeCell ref="C131:H131"/>
+    <mergeCell ref="C120:D121"/>
+    <mergeCell ref="E120:H120"/>
+    <mergeCell ref="F121:H121"/>
+    <mergeCell ref="F122:H122"/>
+    <mergeCell ref="F123:H123"/>
+    <mergeCell ref="F124:H124"/>
+    <mergeCell ref="F137:H137"/>
+    <mergeCell ref="F138:H138"/>
+    <mergeCell ref="C140:D142"/>
+    <mergeCell ref="E140:H140"/>
+    <mergeCell ref="E141:E142"/>
+    <mergeCell ref="F141:H141"/>
+    <mergeCell ref="F142:H142"/>
+    <mergeCell ref="C132:D135"/>
+    <mergeCell ref="E132:H132"/>
+    <mergeCell ref="F133:H133"/>
+    <mergeCell ref="F134:H134"/>
+    <mergeCell ref="F135:H135"/>
+    <mergeCell ref="F136:H136"/>
+    <mergeCell ref="F149:H149"/>
+    <mergeCell ref="F150:H150"/>
+    <mergeCell ref="F151:H151"/>
+    <mergeCell ref="C153:D154"/>
+    <mergeCell ref="E153:H153"/>
+    <mergeCell ref="F154:H154"/>
+    <mergeCell ref="C143:H143"/>
+    <mergeCell ref="E144:H144"/>
+    <mergeCell ref="F145:H145"/>
+    <mergeCell ref="F146:H146"/>
+    <mergeCell ref="F147:H147"/>
+    <mergeCell ref="F148:H148"/>
+    <mergeCell ref="C162:H162"/>
+    <mergeCell ref="C163:H163"/>
+    <mergeCell ref="C164:H164"/>
+    <mergeCell ref="C165:D166"/>
+    <mergeCell ref="E165:H165"/>
+    <mergeCell ref="F166:H166"/>
+    <mergeCell ref="F155:H155"/>
+    <mergeCell ref="F156:H156"/>
+    <mergeCell ref="F157:H157"/>
+    <mergeCell ref="F158:H158"/>
+    <mergeCell ref="C160:H160"/>
+    <mergeCell ref="C161:H161"/>
+    <mergeCell ref="C174:H174"/>
+    <mergeCell ref="C175:D177"/>
+    <mergeCell ref="E175:H175"/>
+    <mergeCell ref="F176:H176"/>
+    <mergeCell ref="F177:H177"/>
+    <mergeCell ref="F178:H178"/>
+    <mergeCell ref="F167:H167"/>
+    <mergeCell ref="F168:H168"/>
+    <mergeCell ref="C170:H170"/>
+    <mergeCell ref="C171:H171"/>
+    <mergeCell ref="C172:H172"/>
+    <mergeCell ref="C173:H173"/>
+    <mergeCell ref="F188:H188"/>
+    <mergeCell ref="F189:H189"/>
+    <mergeCell ref="F190:H190"/>
+    <mergeCell ref="C180:H180"/>
+    <mergeCell ref="C181:H181"/>
+    <mergeCell ref="C182:D183"/>
+    <mergeCell ref="E182:H182"/>
+    <mergeCell ref="F183:H183"/>
+    <mergeCell ref="C185:D187"/>
+    <mergeCell ref="E185:H185"/>
+    <mergeCell ref="F186:H186"/>
+    <mergeCell ref="F187:H187"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="55" orientation="portrait" r:id="rId1"/>
@@ -21084,7 +21084,7 @@
     </row>
     <row r="3" spans="1:10" ht="15.75">
       <c r="A3" s="242" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B3" s="236"/>
       <c r="C3" s="236"/>
@@ -21165,7 +21165,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="206" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C7" s="207" t="s">
         <v>269</v>
@@ -21191,7 +21191,7 @@
         <v>307</v>
       </c>
       <c r="J7" s="270" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="30">
@@ -21199,7 +21199,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="206" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C8" s="207" t="s">
         <v>274</v>
@@ -21233,7 +21233,7 @@
         <v>2</v>
       </c>
       <c r="B9" s="206" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C9" s="207" t="s">
         <v>274</v>
@@ -21259,7 +21259,7 @@
         <v>307</v>
       </c>
       <c r="J9" s="270" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -21295,7 +21295,7 @@
         <v>1</v>
       </c>
       <c r="B11" s="206" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C11" s="207" t="s">
         <v>274</v>
@@ -21357,7 +21357,7 @@
         <v>1</v>
       </c>
       <c r="B13" s="293" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C13" s="286" t="s">
         <v>270</v>
@@ -21380,7 +21380,7 @@
         <v>305</v>
       </c>
       <c r="I13" s="290" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="J13" s="291" t="s">
         <v>328</v>
@@ -21391,7 +21391,7 @@
         <v>2</v>
       </c>
       <c r="B14" s="210" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C14" s="194" t="s">
         <v>272</v>
@@ -21425,7 +21425,7 @@
         <v>3</v>
       </c>
       <c r="B15" s="210" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C15" s="213" t="s">
         <v>272</v>
@@ -21459,7 +21459,7 @@
         <v>4</v>
       </c>
       <c r="B16" s="255" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C16" s="249"/>
       <c r="D16" s="251"/>
@@ -21473,7 +21473,7 @@
         <v>309</v>
       </c>
       <c r="J16" s="272" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="17" spans="1:10" s="214" customFormat="1" ht="30">
@@ -21481,7 +21481,7 @@
         <v>5</v>
       </c>
       <c r="B17" s="244" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C17" s="243" t="s">
         <v>271</v>
@@ -21513,7 +21513,7 @@
     <row r="18" spans="1:10" ht="42.75">
       <c r="A18" s="202"/>
       <c r="B18" s="203" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C18" s="204"/>
       <c r="D18" s="181">
@@ -21541,7 +21541,7 @@
         <v>1</v>
       </c>
       <c r="B19" s="211" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C19" s="194" t="s">
         <v>272</v>
@@ -21567,7 +21567,7 @@
         <v>309</v>
       </c>
       <c r="J19" s="270" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="20" spans="1:10" s="214" customFormat="1" ht="30">
@@ -21575,7 +21575,7 @@
         <v>2</v>
       </c>
       <c r="B20" s="210" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C20" s="213" t="s">
         <v>272</v>
@@ -21609,7 +21609,7 @@
         <v>3</v>
       </c>
       <c r="B21" s="210" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C21" s="213" t="s">
         <v>272</v>
@@ -21635,7 +21635,7 @@
         <v>309</v>
       </c>
       <c r="J21" s="285" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="22" spans="1:10" s="214" customFormat="1" ht="30">
@@ -21643,7 +21643,7 @@
         <v>4</v>
       </c>
       <c r="B22" s="244" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C22" s="243" t="s">
         <v>272</v>
@@ -21705,7 +21705,7 @@
         <v>1</v>
       </c>
       <c r="B24" s="248" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C24" s="243" t="s">
         <v>270</v>
@@ -21739,7 +21739,7 @@
         <v>2</v>
       </c>
       <c r="B25" s="183" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C25" s="194" t="s">
         <v>272</v>
@@ -21773,7 +21773,7 @@
         <v>3</v>
       </c>
       <c r="B26" s="183" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C26" s="194" t="s">
         <v>272</v>
@@ -21799,7 +21799,7 @@
         <v>309</v>
       </c>
       <c r="J26" s="270" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="27" spans="1:10" s="214" customFormat="1" ht="30">
@@ -21807,7 +21807,7 @@
         <v>4</v>
       </c>
       <c r="B27" s="248" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C27" s="243" t="s">
         <v>272</v>
@@ -21841,7 +21841,7 @@
         <v>5</v>
       </c>
       <c r="B28" s="183" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C28" s="194" t="s">
         <v>272</v>
@@ -21867,7 +21867,7 @@
         <v>309</v>
       </c>
       <c r="J28" s="270" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="30">
@@ -21875,7 +21875,7 @@
         <v>6</v>
       </c>
       <c r="B29" s="183" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C29" s="194" t="s">
         <v>272</v>
@@ -21901,7 +21901,7 @@
         <v>309</v>
       </c>
       <c r="J29" s="270" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="30">
@@ -21909,7 +21909,7 @@
         <v>7</v>
       </c>
       <c r="B30" s="292" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C30" s="213" t="s">
         <v>271</v>
@@ -21943,7 +21943,7 @@
         <v>8</v>
       </c>
       <c r="B31" s="244" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C31" s="243" t="s">
         <v>271</v>
@@ -21977,7 +21977,7 @@
         <v>9</v>
       </c>
       <c r="B32" s="244" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C32" s="243" t="s">
         <v>271</v>
@@ -22011,7 +22011,7 @@
         <v>10</v>
       </c>
       <c r="B33" s="244" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C33" s="243" t="s">
         <v>271</v>
@@ -22073,7 +22073,7 @@
         <v>1</v>
       </c>
       <c r="B35" s="183" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C35" s="192" t="s">
         <v>270</v>
@@ -22099,7 +22099,7 @@
         <v>309</v>
       </c>
       <c r="J35" s="270" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="30">
@@ -22157,7 +22157,7 @@
         <v>1</v>
       </c>
       <c r="B38" s="176" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C38" s="193" t="s">
         <v>270</v>
@@ -22191,7 +22191,7 @@
         <v>2</v>
       </c>
       <c r="B39" s="210" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C39" s="194" t="s">
         <v>272</v>
@@ -22217,7 +22217,7 @@
         <v>309</v>
       </c>
       <c r="J39" s="273" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="40" spans="1:10" s="212" customFormat="1" ht="30">
@@ -22273,7 +22273,7 @@
         <v>5</v>
       </c>
       <c r="B42" s="210" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C42" s="213" t="s">
         <v>271</v>
@@ -22307,7 +22307,7 @@
         <v>6</v>
       </c>
       <c r="B43" s="176" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C43" s="194" t="s">
         <v>272</v>
@@ -22341,7 +22341,7 @@
         <v>7</v>
       </c>
       <c r="B44" s="176" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C44" s="195" t="s">
         <v>271</v>
@@ -22575,7 +22575,7 @@
     <row r="52" spans="1:10" ht="45">
       <c r="A52" s="241"/>
       <c r="B52" s="217" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C52" s="186"/>
       <c r="D52" s="1"/>
@@ -29755,252 +29755,252 @@
     </row>
     <row r="10" spans="1:6" ht="51">
       <c r="A10" s="278" t="s">
+        <v>454</v>
+      </c>
+      <c r="B10" s="280" t="s">
         <v>343</v>
       </c>
-      <c r="B10" s="280" t="s">
+      <c r="C10" s="280" t="s">
         <v>344</v>
       </c>
-      <c r="C10" s="280" t="s">
+      <c r="D10" s="278" t="s">
         <v>345</v>
       </c>
-      <c r="D10" s="278" t="s">
+      <c r="E10" s="278" t="s">
         <v>346</v>
       </c>
-      <c r="E10" s="278" t="s">
+      <c r="F10" s="278" t="s">
         <v>347</v>
-      </c>
-      <c r="F10" s="278" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="76.5">
       <c r="A11" s="278" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B11" s="280" t="s">
+        <v>348</v>
+      </c>
+      <c r="C11" s="280" t="s">
         <v>349</v>
       </c>
-      <c r="C11" s="280" t="s">
+      <c r="D11" s="278" t="s">
         <v>350</v>
       </c>
-      <c r="D11" s="278" t="s">
+      <c r="E11" s="278" t="s">
         <v>351</v>
       </c>
-      <c r="E11" s="278" t="s">
+      <c r="F11" s="278" t="s">
         <v>352</v>
-      </c>
-      <c r="F11" s="278" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="51">
       <c r="A12" s="278" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B12" s="280" t="s">
+        <v>353</v>
+      </c>
+      <c r="C12" s="280" t="s">
         <v>354</v>
       </c>
-      <c r="C12" s="280" t="s">
+      <c r="D12" s="278" t="s">
         <v>355</v>
       </c>
-      <c r="D12" s="278" t="s">
+      <c r="E12" s="278" t="s">
         <v>356</v>
       </c>
-      <c r="E12" s="278" t="s">
+      <c r="F12" s="278" t="s">
         <v>357</v>
-      </c>
-      <c r="F12" s="278" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="63.75">
       <c r="A13" s="278" t="s">
+        <v>358</v>
+      </c>
+      <c r="B13" s="280" t="s">
         <v>359</v>
       </c>
-      <c r="B13" s="280" t="s">
+      <c r="C13" s="280" t="s">
         <v>360</v>
       </c>
-      <c r="C13" s="280" t="s">
+      <c r="D13" s="278" t="s">
         <v>361</v>
       </c>
-      <c r="D13" s="278" t="s">
+      <c r="E13" s="278" t="s">
         <v>362</v>
       </c>
-      <c r="E13" s="278" t="s">
+      <c r="F13" s="278" t="s">
         <v>363</v>
-      </c>
-      <c r="F13" s="278" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="51">
       <c r="A14" s="278" t="s">
+        <v>364</v>
+      </c>
+      <c r="B14" s="280" t="s">
         <v>365</v>
       </c>
-      <c r="B14" s="280" t="s">
+      <c r="C14" s="280" t="s">
         <v>366</v>
       </c>
-      <c r="C14" s="280" t="s">
+      <c r="D14" s="278" t="s">
         <v>367</v>
       </c>
-      <c r="D14" s="278" t="s">
+      <c r="E14" s="278" t="s">
         <v>368</v>
       </c>
-      <c r="E14" s="278" t="s">
+      <c r="F14" s="278" t="s">
         <v>369</v>
-      </c>
-      <c r="F14" s="278" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="51">
       <c r="A15" s="278" t="s">
+        <v>370</v>
+      </c>
+      <c r="B15" s="280" t="s">
         <v>371</v>
       </c>
-      <c r="B15" s="280" t="s">
+      <c r="C15" s="280" t="s">
         <v>372</v>
       </c>
-      <c r="C15" s="280" t="s">
+      <c r="D15" s="278" t="s">
         <v>373</v>
       </c>
-      <c r="D15" s="278" t="s">
+      <c r="E15" s="278" t="s">
         <v>374</v>
       </c>
-      <c r="E15" s="278" t="s">
+      <c r="F15" s="278" t="s">
         <v>375</v>
-      </c>
-      <c r="F15" s="278" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="51">
       <c r="A16" s="278" t="s">
+        <v>376</v>
+      </c>
+      <c r="B16" s="280" t="s">
+        <v>359</v>
+      </c>
+      <c r="C16" s="280" t="s">
         <v>377</v>
       </c>
-      <c r="B16" s="280" t="s">
-        <v>360</v>
-      </c>
-      <c r="C16" s="280" t="s">
+      <c r="D16" s="278" t="s">
         <v>378</v>
       </c>
-      <c r="D16" s="278" t="s">
+      <c r="E16" s="278" t="s">
         <v>379</v>
       </c>
-      <c r="E16" s="278" t="s">
+      <c r="F16" s="278" t="s">
         <v>380</v>
-      </c>
-      <c r="F16" s="278" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="25.5">
       <c r="A17" s="278" t="s">
+        <v>381</v>
+      </c>
+      <c r="B17" s="280" t="s">
+        <v>359</v>
+      </c>
+      <c r="C17" s="280" t="s">
+        <v>377</v>
+      </c>
+      <c r="D17" s="278" t="s">
         <v>382</v>
       </c>
-      <c r="B17" s="280" t="s">
-        <v>360</v>
-      </c>
-      <c r="C17" s="280" t="s">
-        <v>378</v>
-      </c>
-      <c r="D17" s="278" t="s">
+      <c r="E17" s="278" t="s">
+        <v>356</v>
+      </c>
+      <c r="F17" s="278" t="s">
         <v>383</v>
-      </c>
-      <c r="E17" s="278" t="s">
-        <v>357</v>
-      </c>
-      <c r="F17" s="278" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="38.25">
       <c r="A18" s="278" t="s">
+        <v>384</v>
+      </c>
+      <c r="B18" s="280" t="s">
+        <v>359</v>
+      </c>
+      <c r="C18" s="280" t="s">
+        <v>377</v>
+      </c>
+      <c r="D18" s="278" t="s">
         <v>385</v>
       </c>
-      <c r="B18" s="280" t="s">
-        <v>360</v>
-      </c>
-      <c r="C18" s="280" t="s">
-        <v>378</v>
-      </c>
-      <c r="D18" s="278" t="s">
+      <c r="E18" s="278" t="s">
         <v>386</v>
       </c>
-      <c r="E18" s="278" t="s">
+      <c r="F18" s="278" t="s">
         <v>387</v>
-      </c>
-      <c r="F18" s="278" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="38.25">
       <c r="A19" s="278" t="s">
+        <v>388</v>
+      </c>
+      <c r="B19" s="280" t="s">
+        <v>371</v>
+      </c>
+      <c r="C19" s="280" t="s">
+        <v>377</v>
+      </c>
+      <c r="D19" s="278" t="s">
         <v>389</v>
       </c>
-      <c r="B19" s="280" t="s">
-        <v>372</v>
-      </c>
-      <c r="C19" s="280" t="s">
-        <v>378</v>
-      </c>
-      <c r="D19" s="278" t="s">
+      <c r="E19" s="278" t="s">
         <v>390</v>
       </c>
-      <c r="E19" s="278" t="s">
+      <c r="F19" s="278" t="s">
         <v>391</v>
-      </c>
-      <c r="F19" s="278" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="51">
       <c r="A20" s="278" t="s">
+        <v>392</v>
+      </c>
+      <c r="B20" s="280" t="s">
+        <v>371</v>
+      </c>
+      <c r="C20" s="280" t="s">
+        <v>377</v>
+      </c>
+      <c r="D20" s="278" t="s">
         <v>393</v>
       </c>
-      <c r="B20" s="280" t="s">
-        <v>372</v>
-      </c>
-      <c r="C20" s="280" t="s">
-        <v>378</v>
-      </c>
-      <c r="D20" s="278" t="s">
+      <c r="E20" s="278" t="s">
         <v>394</v>
       </c>
-      <c r="E20" s="278" t="s">
+      <c r="F20" s="278" t="s">
         <v>395</v>
-      </c>
-      <c r="F20" s="278" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="25.5">
       <c r="A21" s="278" t="s">
+        <v>396</v>
+      </c>
+      <c r="B21" s="280" t="s">
+        <v>371</v>
+      </c>
+      <c r="C21" s="280" t="s">
+        <v>377</v>
+      </c>
+      <c r="D21" s="278" t="s">
         <v>397</v>
       </c>
-      <c r="B21" s="280" t="s">
-        <v>372</v>
-      </c>
-      <c r="C21" s="280" t="s">
-        <v>378</v>
-      </c>
-      <c r="D21" s="278" t="s">
+      <c r="E21" s="278" t="s">
         <v>398</v>
       </c>
-      <c r="E21" s="278" t="s">
+      <c r="F21" s="278" t="s">
         <v>399</v>
-      </c>
-      <c r="F21" s="278" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="276" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="27" customHeight="1">
       <c r="A24" s="448" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B24" s="448"/>
       <c r="C24" s="448"/>
@@ -30010,7 +30010,7 @@
     </row>
     <row r="25" spans="1:6" ht="27" customHeight="1">
       <c r="A25" s="448" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B25" s="448"/>
       <c r="C25" s="448"/>
@@ -30020,7 +30020,7 @@
     </row>
     <row r="26" spans="1:6" ht="27" customHeight="1">
       <c r="A26" s="448" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B26" s="448"/>
       <c r="C26" s="448"/>
@@ -30030,7 +30030,7 @@
     </row>
     <row r="27" spans="1:6" ht="27" customHeight="1">
       <c r="A27" s="448" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B27" s="448"/>
       <c r="C27" s="448"/>
@@ -30040,7 +30040,7 @@
     </row>
     <row r="28" spans="1:6" ht="27" customHeight="1">
       <c r="A28" s="448" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B28" s="448"/>
       <c r="C28" s="448"/>
@@ -30050,7 +30050,7 @@
     </row>
     <row r="29" spans="1:6" ht="27" customHeight="1">
       <c r="A29" s="448" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B29" s="448"/>
       <c r="C29" s="448"/>
@@ -30060,7 +30060,7 @@
     </row>
     <row r="30" spans="1:6" ht="27" customHeight="1">
       <c r="A30" s="448" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B30" s="448"/>
       <c r="C30" s="448"/>
@@ -30070,7 +30070,7 @@
     </row>
     <row r="31" spans="1:6" ht="27" customHeight="1">
       <c r="A31" s="448" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B31" s="448"/>
       <c r="C31" s="448"/>
@@ -30080,12 +30080,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A7:F7"/>
     <mergeCell ref="A31:F31"/>
     <mergeCell ref="A25:F25"/>
     <mergeCell ref="A26:F26"/>
@@ -30093,6 +30087,12 @@
     <mergeCell ref="A28:F28"/>
     <mergeCell ref="A29:F29"/>
     <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" verticalDpi="0" r:id="rId1"/>

--- a/TAZA/_документы/ШР ЦАКФ.xlsx
+++ b/TAZA/_документы/ШР ЦАКФ.xlsx
@@ -301,7 +301,7 @@
     <definedName name="nfn">#REF!</definedName>
     <definedName name="Print_Area" localSheetId="5">'выбытие денег '!$A$1:$N$195</definedName>
     <definedName name="Print_Area" localSheetId="4">нак.расх.!$A$1:$L$95</definedName>
-    <definedName name="Print_Area" localSheetId="6">ФОТ!$A$1:$J$55</definedName>
+    <definedName name="Print_Area" localSheetId="6">ФОТ!$A$1:$J$56</definedName>
     <definedName name="Profit_Loss" localSheetId="2">#REF!</definedName>
     <definedName name="Profit_Loss" localSheetId="5">#REF!</definedName>
     <definedName name="Profit_Loss" localSheetId="3">#REF!</definedName>
@@ -590,8 +590,8 @@
     <definedName name="пппп">#REF!</definedName>
     <definedName name="прейс">#REF!</definedName>
     <definedName name="прейск">#REF!</definedName>
-    <definedName name="принтареа2" localSheetId="6">ФОТ!$A$1:$G$54</definedName>
-    <definedName name="принтареа3" localSheetId="6">ФОТ!$A$1:$G$55</definedName>
+    <definedName name="принтареа2" localSheetId="6">ФОТ!$A$1:$G$55</definedName>
+    <definedName name="принтареа3" localSheetId="6">ФОТ!$A$1:$G$56</definedName>
     <definedName name="про" localSheetId="2">#REF!</definedName>
     <definedName name="про" localSheetId="5">#REF!</definedName>
     <definedName name="про" localSheetId="3">#REF!</definedName>
@@ -772,7 +772,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1890" uniqueCount="455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1895" uniqueCount="458">
   <si>
     <t>№ п/п</t>
   </si>
@@ -2400,12 +2400,6 @@
     <t>Стратегия и научное направление Фонда, аналитические и экспертные материалы, международные партнёры; поручения ГИД</t>
   </si>
   <si>
-    <t>Главный исполнительный директор Фонда, Руководитель Проектного офиса для Центральной Азии / Қаражан</t>
-  </si>
-  <si>
-    <t>Общее руководство Фондом и проектом, представительство, утверждение планов, бюджета и отчётов; руководство Проектным офисом для Центральной Азии</t>
-  </si>
-  <si>
     <t>Молодёжь, волонтёры, НПО, школы и вузы; экспертиза молодёжных и общественных проектов</t>
   </si>
   <si>
@@ -2428,6 +2422,21 @@
   </si>
   <si>
     <t>ГИД, заместители ГИД, руководитель проектного офиса «Таза Қазақстан», финансовый директор</t>
+  </si>
+  <si>
+    <t>Главный исполнительный директор Фонда / Қаражан</t>
+  </si>
+  <si>
+    <t>Общее руководство Фондом и проектом, представительство, утверждение планов, бюджета и отчётов; до назначения Руководителя Проектного офиса для Центральной Азии исполняет его обязанности без оклада и доплаты</t>
+  </si>
+  <si>
+    <t>Руководитель Проектного офиса для Центральной Азии / вакансия (обязанности исполняет ГИД)</t>
+  </si>
+  <si>
+    <t>вакансия</t>
+  </si>
+  <si>
+    <t>Руководство Проектным офисом для Центральной Азии; до назначения Руководителя обязанности исполняет ГИД без оклада и доплаты</t>
   </si>
 </sst>
 </file>
@@ -21053,7 +21062,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J935"/>
+  <dimension ref="A1:J936"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -21084,7 +21093,7 @@
     </row>
     <row r="3" spans="1:10" ht="15.75">
       <c r="A3" s="242" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="B3" s="236"/>
       <c r="C3" s="236"/>
@@ -21160,12 +21169,12 @@
       <c r="I6" s="181"/>
       <c r="J6" s="181"/>
     </row>
-    <row r="7" spans="1:10" ht="45">
+    <row r="7" spans="1:10" ht="60">
       <c r="A7" s="205">
         <v>1</v>
       </c>
       <c r="B7" s="206" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="C7" s="207" t="s">
         <v>269</v>
@@ -21191,7 +21200,7 @@
         <v>307</v>
       </c>
       <c r="J7" s="270" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="30">
@@ -21517,20 +21526,20 @@
       </c>
       <c r="C18" s="204"/>
       <c r="D18" s="181">
-        <f>SUM(D19:D22)</f>
-        <v>4</v>
+        <f>SUM(D19:D23)</f>
+        <v>5</v>
       </c>
       <c r="E18" s="221">
-        <f>SUM(E19:E22)</f>
-        <v>3400000</v>
+        <f>SUM(E19:E23)</f>
+        <v>4800000</v>
       </c>
       <c r="F18" s="222">
-        <f>SUM(F19:F22)</f>
-        <v>2744700</v>
+        <f>SUM(F19:F23)</f>
+        <v>3866475</v>
       </c>
       <c r="G18" s="181">
-        <f>SUM(G19:G22)</f>
-        <v>40800</v>
+        <f>SUM(G19:G23)</f>
+        <v>57600</v>
       </c>
       <c r="H18" s="181"/>
       <c r="I18" s="181"/>
@@ -21541,67 +21550,67 @@
         <v>1</v>
       </c>
       <c r="B19" s="211" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="C19" s="194" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="D19" s="177">
         <v>1</v>
       </c>
       <c r="E19" s="223">
-        <v>1000000</v>
+        <v>1400000</v>
       </c>
       <c r="F19" s="224">
         <f>IF(E19&gt;0,E19-MIN(E19,4250000)*10%-MIN(E19,1700000)*2%-MAX(0,E19-MIN(E19,4250000)*10%-MIN(E19,1700000)*2%-129750)*10%,0)</f>
-        <v>804975</v>
+        <v>1121775</v>
       </c>
       <c r="G19" s="177">
         <f>D19*E19*12/1000</f>
-        <v>12000</v>
+        <v>16800</v>
       </c>
       <c r="H19" s="177" t="s">
         <v>305</v>
       </c>
       <c r="I19" s="264" t="s">
+        <v>456</v>
+      </c>
+      <c r="J19" s="270" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="45">
+      <c r="A20" s="196">
+        <v>2</v>
+      </c>
+      <c r="B20" s="211" t="s">
+        <v>447</v>
+      </c>
+      <c r="C20" s="194" t="s">
+        <v>272</v>
+      </c>
+      <c r="D20" s="177">
+        <v>1</v>
+      </c>
+      <c r="E20" s="223">
+        <v>1000000</v>
+      </c>
+      <c r="F20" s="224">
+        <f>IF(E20&gt;0,E20-MIN(E20,4250000)*10%-MIN(E20,1700000)*2%-MAX(0,E20-MIN(E20,4250000)*10%-MIN(E20,1700000)*2%-129750)*10%,0)</f>
+        <v>804975</v>
+      </c>
+      <c r="G20" s="177">
+        <f>D20*E20*12/1000</f>
+        <v>12000</v>
+      </c>
+      <c r="H20" s="177" t="s">
+        <v>305</v>
+      </c>
+      <c r="I20" s="264" t="s">
         <v>309</v>
       </c>
-      <c r="J19" s="270" t="s">
+      <c r="J20" s="270" t="s">
         <v>409</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" s="214" customFormat="1" ht="30">
-      <c r="A20" s="213">
-        <v>2</v>
-      </c>
-      <c r="B20" s="210" t="s">
-        <v>450</v>
-      </c>
-      <c r="C20" s="213" t="s">
-        <v>272</v>
-      </c>
-      <c r="D20" s="281">
-        <v>1</v>
-      </c>
-      <c r="E20" s="282">
-        <v>800000</v>
-      </c>
-      <c r="F20" s="283">
-        <f>IF(E20&gt;0,E20-MIN(E20,4250000)*10%-MIN(E20,1700000)*2%-MAX(0,E20-MIN(E20,4250000)*10%-MIN(E20,1700000)*2%-129750)*10%,0)</f>
-        <v>646575</v>
-      </c>
-      <c r="G20" s="281">
-        <f>D20*E20*12/1000</f>
-        <v>9600</v>
-      </c>
-      <c r="H20" s="281" t="s">
-        <v>305</v>
-      </c>
-      <c r="I20" s="284" t="s">
-        <v>309</v>
-      </c>
-      <c r="J20" s="285" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="21" spans="1:10" s="214" customFormat="1" ht="30">
@@ -21609,7 +21618,7 @@
         <v>3</v>
       </c>
       <c r="B21" s="210" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="C21" s="213" t="s">
         <v>272</v>
@@ -21635,247 +21644,247 @@
         <v>309</v>
       </c>
       <c r="J21" s="285" t="s">
-        <v>447</v>
+        <v>324</v>
       </c>
     </row>
     <row r="22" spans="1:10" s="214" customFormat="1" ht="30">
-      <c r="A22" s="243">
+      <c r="A22" s="213">
         <v>4</v>
       </c>
-      <c r="B22" s="244" t="s">
-        <v>452</v>
-      </c>
-      <c r="C22" s="243" t="s">
+      <c r="B22" s="210" t="s">
+        <v>449</v>
+      </c>
+      <c r="C22" s="213" t="s">
         <v>272</v>
       </c>
-      <c r="D22" s="245">
+      <c r="D22" s="281">
         <v>1</v>
       </c>
-      <c r="E22" s="246">
+      <c r="E22" s="282">
         <v>800000</v>
       </c>
-      <c r="F22" s="247">
+      <c r="F22" s="283">
         <f>IF(E22&gt;0,E22-MIN(E22,4250000)*10%-MIN(E22,1700000)*2%-MAX(0,E22-MIN(E22,4250000)*10%-MIN(E22,1700000)*2%-129750)*10%,0)</f>
         <v>646575</v>
       </c>
-      <c r="G22" s="245">
+      <c r="G22" s="281">
         <f>D22*E22*12/1000</f>
         <v>9600</v>
       </c>
-      <c r="H22" s="245" t="s">
+      <c r="H22" s="281" t="s">
         <v>305</v>
       </c>
-      <c r="I22" s="266" t="s">
+      <c r="I22" s="284" t="s">
+        <v>309</v>
+      </c>
+      <c r="J22" s="285" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" s="214" customFormat="1" ht="30">
+      <c r="A23" s="243">
+        <v>5</v>
+      </c>
+      <c r="B23" s="244" t="s">
+        <v>450</v>
+      </c>
+      <c r="C23" s="243" t="s">
+        <v>272</v>
+      </c>
+      <c r="D23" s="245">
+        <v>1</v>
+      </c>
+      <c r="E23" s="246">
+        <v>800000</v>
+      </c>
+      <c r="F23" s="247">
+        <f>IF(E23&gt;0,E23-MIN(E23,4250000)*10%-MIN(E23,1700000)*2%-MAX(0,E23-MIN(E23,4250000)*10%-MIN(E23,1700000)*2%-129750)*10%,0)</f>
+        <v>646575</v>
+      </c>
+      <c r="G23" s="245">
+        <f>D23*E23*12/1000</f>
+        <v>9600</v>
+      </c>
+      <c r="H23" s="245" t="s">
+        <v>305</v>
+      </c>
+      <c r="I23" s="266" t="s">
         <v>318</v>
       </c>
-      <c r="J22" s="271" t="s">
+      <c r="J23" s="271" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="28.5">
-      <c r="A23" s="171" t="s">
+    <row r="24" spans="1:10" ht="28.5">
+      <c r="A24" s="171" t="s">
         <v>280</v>
       </c>
-      <c r="B23" s="180" t="s">
+      <c r="B24" s="180" t="s">
         <v>277</v>
       </c>
-      <c r="C23" s="179"/>
-      <c r="D23" s="181">
-        <f>SUM(D24:D33)</f>
+      <c r="C24" s="179"/>
+      <c r="D24" s="181">
+        <f>SUM(D25:D34)</f>
         <v>10</v>
       </c>
-      <c r="E23" s="221">
-        <f t="shared" ref="E23:G23" si="3">SUM(E24:E33)</f>
+      <c r="E24" s="221">
+        <f t="shared" ref="E24:G24" si="3">SUM(E25:E34)</f>
         <v>9200000</v>
       </c>
-      <c r="F23" s="222">
-        <f>SUM(F24:F33)</f>
+      <c r="F24" s="222">
+        <f>SUM(F25:F34)</f>
         <v>7416150</v>
       </c>
-      <c r="G23" s="181">
+      <c r="G24" s="181">
         <f t="shared" si="3"/>
         <v>110400</v>
       </c>
-      <c r="H23" s="181"/>
-      <c r="I23" s="181"/>
-      <c r="J23" s="267"/>
-    </row>
-    <row r="24" spans="1:10" s="214" customFormat="1" ht="30">
-      <c r="A24" s="243">
+      <c r="H24" s="181"/>
+      <c r="I24" s="181"/>
+      <c r="J24" s="267"/>
+    </row>
+    <row r="25" spans="1:10" s="214" customFormat="1" ht="30">
+      <c r="A25" s="243">
         <v>1</v>
       </c>
-      <c r="B24" s="248" t="s">
+      <c r="B25" s="248" t="s">
         <v>432</v>
       </c>
-      <c r="C24" s="243" t="s">
+      <c r="C25" s="243" t="s">
         <v>270</v>
       </c>
-      <c r="D24" s="245">
+      <c r="D25" s="245">
         <v>1</v>
       </c>
-      <c r="E24" s="246">
+      <c r="E25" s="246">
         <v>1300000</v>
       </c>
-      <c r="F24" s="247">
-        <f t="shared" ref="F24:F33" si="4">IF(E24&gt;0,E24-MIN(E24,4250000)*10%-MIN(E24,1700000)*2%-MAX(0,E24-MIN(E24,4250000)*10%-MIN(E24,1700000)*2%-129750)*10%,0)</f>
+      <c r="F25" s="247">
+        <f t="shared" ref="F25:F34" si="4">IF(E25&gt;0,E25-MIN(E25,4250000)*10%-MIN(E25,1700000)*2%-MAX(0,E25-MIN(E25,4250000)*10%-MIN(E25,1700000)*2%-129750)*10%,0)</f>
         <v>1042575</v>
       </c>
-      <c r="G24" s="245">
-        <f t="shared" ref="G24:G33" si="5">D24*E24*12/1000</f>
+      <c r="G25" s="245">
+        <f t="shared" ref="G25:G34" si="5">D25*E25*12/1000</f>
         <v>15600</v>
       </c>
-      <c r="H24" s="245" t="s">
+      <c r="H25" s="245" t="s">
         <v>305</v>
       </c>
-      <c r="I24" s="266" t="s">
+      <c r="I25" s="266" t="s">
         <v>318</v>
       </c>
-      <c r="J24" s="271" t="s">
+      <c r="J25" s="271" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="30">
-      <c r="A25" s="182">
+    <row r="26" spans="1:10" ht="30">
+      <c r="A26" s="182">
         <v>2</v>
       </c>
-      <c r="B25" s="183" t="s">
+      <c r="B26" s="183" t="s">
         <v>442</v>
       </c>
-      <c r="C25" s="194" t="s">
+      <c r="C26" s="194" t="s">
         <v>272</v>
       </c>
-      <c r="D25" s="177">
+      <c r="D26" s="177">
         <v>1</v>
       </c>
-      <c r="E25" s="223">
+      <c r="E26" s="223">
         <v>1100000</v>
       </c>
-      <c r="F25" s="224">
+      <c r="F26" s="224">
         <f t="shared" si="4"/>
         <v>884175</v>
       </c>
-      <c r="G25" s="177">
+      <c r="G26" s="177">
         <f t="shared" si="5"/>
         <v>13200</v>
       </c>
-      <c r="H25" s="177" t="s">
+      <c r="H26" s="177" t="s">
         <v>305</v>
       </c>
-      <c r="I25" s="264" t="s">
+      <c r="I26" s="264" t="s">
         <v>309</v>
       </c>
-      <c r="J25" s="270" t="s">
+      <c r="J26" s="270" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="30">
-      <c r="A26" s="213">
+    <row r="27" spans="1:10" ht="30">
+      <c r="A27" s="213">
         <v>3</v>
       </c>
-      <c r="B26" s="183" t="s">
+      <c r="B27" s="183" t="s">
         <v>422</v>
       </c>
-      <c r="C26" s="194" t="s">
+      <c r="C27" s="194" t="s">
         <v>272</v>
       </c>
-      <c r="D26" s="177">
+      <c r="D27" s="177">
         <v>1</v>
       </c>
-      <c r="E26" s="223">
+      <c r="E27" s="223">
         <v>1000000</v>
       </c>
-      <c r="F26" s="224">
+      <c r="F27" s="224">
         <f t="shared" si="4"/>
         <v>804975</v>
       </c>
-      <c r="G26" s="177">
+      <c r="G27" s="177">
         <f t="shared" si="5"/>
         <v>12000</v>
       </c>
-      <c r="H26" s="177" t="s">
+      <c r="H27" s="177" t="s">
         <v>305</v>
       </c>
-      <c r="I26" s="264" t="s">
+      <c r="I27" s="264" t="s">
         <v>309</v>
       </c>
-      <c r="J26" s="270" t="s">
+      <c r="J27" s="270" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="27" spans="1:10" s="214" customFormat="1" ht="30">
-      <c r="A27" s="243">
+    <row r="28" spans="1:10" s="214" customFormat="1" ht="30">
+      <c r="A28" s="243">
         <v>4</v>
       </c>
-      <c r="B27" s="248" t="s">
+      <c r="B28" s="248" t="s">
         <v>433</v>
       </c>
-      <c r="C27" s="243" t="s">
+      <c r="C28" s="243" t="s">
         <v>272</v>
       </c>
-      <c r="D27" s="245">
+      <c r="D28" s="245">
         <v>1</v>
       </c>
-      <c r="E27" s="246">
+      <c r="E28" s="246">
         <v>1000000</v>
       </c>
-      <c r="F27" s="247">
+      <c r="F28" s="247">
         <f t="shared" si="4"/>
         <v>804975</v>
       </c>
-      <c r="G27" s="245">
+      <c r="G28" s="245">
         <f t="shared" si="5"/>
         <v>12000</v>
       </c>
-      <c r="H27" s="245" t="s">
+      <c r="H28" s="245" t="s">
         <v>305</v>
       </c>
-      <c r="I27" s="266" t="s">
+      <c r="I28" s="266" t="s">
         <v>318</v>
       </c>
-      <c r="J27" s="271" t="s">
+      <c r="J28" s="271" t="s">
         <v>320</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" ht="30">
-      <c r="A28" s="182">
-        <v>5</v>
-      </c>
-      <c r="B28" s="183" t="s">
-        <v>420</v>
-      </c>
-      <c r="C28" s="194" t="s">
-        <v>272</v>
-      </c>
-      <c r="D28" s="177">
-        <v>1</v>
-      </c>
-      <c r="E28" s="223">
-        <v>1000000</v>
-      </c>
-      <c r="F28" s="224">
-        <f t="shared" si="4"/>
-        <v>804975</v>
-      </c>
-      <c r="G28" s="177">
-        <f t="shared" si="5"/>
-        <v>12000</v>
-      </c>
-      <c r="H28" s="177" t="s">
-        <v>305</v>
-      </c>
-      <c r="I28" s="264" t="s">
-        <v>309</v>
-      </c>
-      <c r="J28" s="270" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="30">
       <c r="A29" s="182">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B29" s="183" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C29" s="194" t="s">
         <v>272</v>
@@ -21901,83 +21910,83 @@
         <v>309</v>
       </c>
       <c r="J29" s="270" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="30">
+      <c r="A30" s="182">
+        <v>6</v>
+      </c>
+      <c r="B30" s="183" t="s">
+        <v>421</v>
+      </c>
+      <c r="C30" s="194" t="s">
+        <v>272</v>
+      </c>
+      <c r="D30" s="177">
+        <v>1</v>
+      </c>
+      <c r="E30" s="223">
+        <v>1000000</v>
+      </c>
+      <c r="F30" s="224">
+        <f t="shared" si="4"/>
+        <v>804975</v>
+      </c>
+      <c r="G30" s="177">
+        <f t="shared" si="5"/>
+        <v>12000</v>
+      </c>
+      <c r="H30" s="177" t="s">
+        <v>305</v>
+      </c>
+      <c r="I30" s="264" t="s">
+        <v>309</v>
+      </c>
+      <c r="J30" s="270" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="30">
-      <c r="A30" s="213">
+    <row r="31" spans="1:10" ht="30">
+      <c r="A31" s="213">
         <v>7</v>
       </c>
-      <c r="B30" s="292" t="s">
+      <c r="B31" s="292" t="s">
         <v>434</v>
       </c>
-      <c r="C30" s="213" t="s">
+      <c r="C31" s="213" t="s">
         <v>271</v>
       </c>
-      <c r="D30" s="281">
+      <c r="D31" s="281">
         <v>1</v>
       </c>
-      <c r="E30" s="282">
+      <c r="E31" s="282">
         <v>700000</v>
       </c>
-      <c r="F30" s="283">
+      <c r="F31" s="283">
         <f t="shared" si="4"/>
         <v>567375</v>
       </c>
-      <c r="G30" s="281">
+      <c r="G31" s="281">
         <f t="shared" si="5"/>
         <v>8400</v>
       </c>
-      <c r="H30" s="281" t="s">
+      <c r="H31" s="281" t="s">
         <v>305</v>
       </c>
-      <c r="I30" s="284" t="s">
+      <c r="I31" s="284" t="s">
         <v>309</v>
       </c>
-      <c r="J30" s="285" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" s="214" customFormat="1" ht="30">
-      <c r="A31" s="243">
-        <v>8</v>
-      </c>
-      <c r="B31" s="244" t="s">
-        <v>435</v>
-      </c>
-      <c r="C31" s="243" t="s">
-        <v>271</v>
-      </c>
-      <c r="D31" s="245">
-        <v>1</v>
-      </c>
-      <c r="E31" s="246">
-        <v>700000</v>
-      </c>
-      <c r="F31" s="247">
-        <f t="shared" si="4"/>
-        <v>567375</v>
-      </c>
-      <c r="G31" s="245">
-        <f t="shared" si="5"/>
-        <v>8400</v>
-      </c>
-      <c r="H31" s="245" t="s">
-        <v>305</v>
-      </c>
-      <c r="I31" s="266" t="s">
-        <v>318</v>
-      </c>
-      <c r="J31" s="271" t="s">
+      <c r="J31" s="285" t="s">
         <v>320</v>
       </c>
     </row>
     <row r="32" spans="1:10" s="214" customFormat="1" ht="30">
       <c r="A32" s="243">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B32" s="244" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C32" s="243" t="s">
         <v>271</v>
@@ -22003,15 +22012,15 @@
         <v>318</v>
       </c>
       <c r="J32" s="271" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="33" spans="1:10" s="214" customFormat="1" ht="30">
       <c r="A33" s="243">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B33" s="244" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C33" s="243" t="s">
         <v>271</v>
@@ -22037,178 +22046,178 @@
         <v>318</v>
       </c>
       <c r="J33" s="271" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" s="214" customFormat="1" ht="30">
+      <c r="A34" s="243">
+        <v>10</v>
+      </c>
+      <c r="B34" s="244" t="s">
+        <v>437</v>
+      </c>
+      <c r="C34" s="243" t="s">
+        <v>271</v>
+      </c>
+      <c r="D34" s="245">
+        <v>1</v>
+      </c>
+      <c r="E34" s="246">
+        <v>700000</v>
+      </c>
+      <c r="F34" s="247">
+        <f t="shared" si="4"/>
+        <v>567375</v>
+      </c>
+      <c r="G34" s="245">
+        <f t="shared" si="5"/>
+        <v>8400</v>
+      </c>
+      <c r="H34" s="245" t="s">
+        <v>305</v>
+      </c>
+      <c r="I34" s="266" t="s">
+        <v>318</v>
+      </c>
+      <c r="J34" s="271" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="34" spans="1:10" s="166" customFormat="1">
-      <c r="A34" s="171" t="s">
+    <row r="35" spans="1:10" s="166" customFormat="1">
+      <c r="A35" s="171" t="s">
         <v>281</v>
       </c>
-      <c r="B34" s="184" t="s">
+      <c r="B35" s="184" t="s">
         <v>278</v>
       </c>
-      <c r="C34" s="187"/>
-      <c r="D34" s="185">
-        <f t="shared" ref="D34:G34" si="6">SUM(D35:D36)</f>
+      <c r="C35" s="187"/>
+      <c r="D35" s="185">
+        <f t="shared" ref="D35:G35" si="6">SUM(D36:D37)</f>
         <v>1</v>
       </c>
-      <c r="E34" s="225">
+      <c r="E35" s="225">
         <f t="shared" si="6"/>
         <v>1300000</v>
       </c>
-      <c r="F34" s="226">
+      <c r="F35" s="226">
         <f t="shared" si="6"/>
         <v>1042575</v>
       </c>
-      <c r="G34" s="185">
+      <c r="G35" s="185">
         <f t="shared" si="6"/>
         <v>15600</v>
       </c>
-      <c r="H34" s="185"/>
-      <c r="I34" s="185"/>
-      <c r="J34" s="268"/>
-    </row>
-    <row r="35" spans="1:10" ht="30">
-      <c r="A35" s="182">
+      <c r="H35" s="185"/>
+      <c r="I35" s="185"/>
+      <c r="J35" s="268"/>
+    </row>
+    <row r="36" spans="1:10" ht="30">
+      <c r="A36" s="182">
         <v>1</v>
       </c>
-      <c r="B35" s="183" t="s">
+      <c r="B36" s="183" t="s">
         <v>419</v>
       </c>
-      <c r="C35" s="192" t="s">
+      <c r="C36" s="192" t="s">
         <v>270</v>
       </c>
-      <c r="D35" s="177">
+      <c r="D36" s="177">
         <v>1</v>
       </c>
-      <c r="E35" s="223">
+      <c r="E36" s="223">
         <v>1300000</v>
       </c>
-      <c r="F35" s="224">
-        <f>IF(E35&gt;0,E35-MIN(E35,4250000)*10%-MIN(E35,1700000)*2%-MAX(0,E35-MIN(E35,4250000)*10%-MIN(E35,1700000)*2%-129750)*10%,0)</f>
+      <c r="F36" s="224">
+        <f>IF(E36&gt;0,E36-MIN(E36,4250000)*10%-MIN(E36,1700000)*2%-MAX(0,E36-MIN(E36,4250000)*10%-MIN(E36,1700000)*2%-129750)*10%,0)</f>
         <v>1042575</v>
       </c>
-      <c r="G35" s="177">
-        <f>D35*E35*12/1000</f>
+      <c r="G36" s="177">
+        <f>D36*E36*12/1000</f>
         <v>15600</v>
       </c>
-      <c r="H35" s="177" t="s">
+      <c r="H36" s="177" t="s">
         <v>305</v>
       </c>
-      <c r="I35" s="264" t="s">
+      <c r="I36" s="264" t="s">
         <v>309</v>
       </c>
-      <c r="J35" s="270" t="s">
+      <c r="J36" s="270" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="30">
-      <c r="A36" s="249">
+    <row r="37" spans="1:10" ht="30">
+      <c r="A37" s="249">
         <v>2</v>
       </c>
-      <c r="B36" s="250" t="s">
+      <c r="B37" s="250" t="s">
         <v>295</v>
       </c>
-      <c r="C36" s="249"/>
-      <c r="D36" s="251"/>
-      <c r="E36" s="252"/>
-      <c r="F36" s="253"/>
-      <c r="G36" s="251"/>
-      <c r="H36" s="251" t="s">
+      <c r="C37" s="249"/>
+      <c r="D37" s="251"/>
+      <c r="E37" s="252"/>
+      <c r="F37" s="253"/>
+      <c r="G37" s="251"/>
+      <c r="H37" s="251" t="s">
         <v>302</v>
       </c>
-      <c r="I36" s="263" t="s">
+      <c r="I37" s="263" t="s">
         <v>309</v>
       </c>
-      <c r="J36" s="272" t="s">
+      <c r="J37" s="272" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="37" spans="1:10">
-      <c r="A37" s="171" t="s">
+    <row r="38" spans="1:10">
+      <c r="A38" s="171" t="s">
         <v>266</v>
       </c>
-      <c r="B37" s="172" t="s">
+      <c r="B38" s="172" t="s">
         <v>275</v>
       </c>
-      <c r="C37" s="188"/>
-      <c r="D37" s="173">
-        <f t="shared" ref="D37:G37" si="7">SUM(D38:D45)</f>
+      <c r="C38" s="188"/>
+      <c r="D38" s="173">
+        <f t="shared" ref="D38:G38" si="7">SUM(D39:D46)</f>
         <v>5</v>
       </c>
-      <c r="E37" s="227">
+      <c r="E38" s="227">
         <f t="shared" si="7"/>
         <v>4700000</v>
       </c>
-      <c r="F37" s="228">
-        <f>SUM(F38:F45)</f>
+      <c r="F38" s="228">
+        <f>SUM(F39:F46)</f>
         <v>3787275</v>
       </c>
-      <c r="G37" s="173">
+      <c r="G38" s="173">
         <f t="shared" si="7"/>
         <v>56400</v>
       </c>
-      <c r="H37" s="173"/>
-      <c r="I37" s="173"/>
-      <c r="J37" s="269"/>
-    </row>
-    <row r="38" spans="1:10" ht="30">
-      <c r="A38" s="168">
-        <v>1</v>
-      </c>
-      <c r="B38" s="176" t="s">
-        <v>438</v>
-      </c>
-      <c r="C38" s="193" t="s">
-        <v>270</v>
-      </c>
-      <c r="D38" s="170">
-        <v>1</v>
-      </c>
-      <c r="E38" s="229">
-        <v>1300000</v>
-      </c>
-      <c r="F38" s="230">
-        <f>IF(E38&gt;0,E38-MIN(E38,4250000)*10%-MIN(E38,1700000)*2%-MAX(0,E38-MIN(E38,4250000)*10%-MIN(E38,1700000)*2%-129750)*10%,0)</f>
-        <v>1042575</v>
-      </c>
-      <c r="G38" s="170">
-        <f>D38*E38*12/1000</f>
-        <v>15600</v>
-      </c>
-      <c r="H38" s="170" t="s">
-        <v>305</v>
-      </c>
-      <c r="I38" s="265" t="s">
-        <v>309</v>
-      </c>
-      <c r="J38" s="273" t="s">
-        <v>316</v>
-      </c>
+      <c r="H38" s="173"/>
+      <c r="I38" s="173"/>
+      <c r="J38" s="269"/>
     </row>
     <row r="39" spans="1:10" ht="30">
       <c r="A39" s="168">
-        <v>2</v>
-      </c>
-      <c r="B39" s="210" t="s">
-        <v>418</v>
-      </c>
-      <c r="C39" s="194" t="s">
-        <v>272</v>
+        <v>1</v>
+      </c>
+      <c r="B39" s="176" t="s">
+        <v>438</v>
+      </c>
+      <c r="C39" s="193" t="s">
+        <v>270</v>
       </c>
       <c r="D39" s="170">
         <v>1</v>
       </c>
       <c r="E39" s="229">
-        <v>1000000</v>
+        <v>1300000</v>
       </c>
       <c r="F39" s="230">
         <f>IF(E39&gt;0,E39-MIN(E39,4250000)*10%-MIN(E39,1700000)*2%-MAX(0,E39-MIN(E39,4250000)*10%-MIN(E39,1700000)*2%-129750)*10%,0)</f>
-        <v>804975</v>
+        <v>1042575</v>
       </c>
       <c r="G39" s="170">
         <f>D39*E39*12/1000</f>
-        <v>12000</v>
+        <v>15600</v>
       </c>
       <c r="H39" s="170" t="s">
         <v>305</v>
@@ -22217,42 +22226,52 @@
         <v>309</v>
       </c>
       <c r="J39" s="273" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="30">
+      <c r="A40" s="168">
+        <v>2</v>
+      </c>
+      <c r="B40" s="210" t="s">
+        <v>418</v>
+      </c>
+      <c r="C40" s="194" t="s">
+        <v>272</v>
+      </c>
+      <c r="D40" s="170">
+        <v>1</v>
+      </c>
+      <c r="E40" s="229">
+        <v>1000000</v>
+      </c>
+      <c r="F40" s="230">
+        <f>IF(E40&gt;0,E40-MIN(E40,4250000)*10%-MIN(E40,1700000)*2%-MAX(0,E40-MIN(E40,4250000)*10%-MIN(E40,1700000)*2%-129750)*10%,0)</f>
+        <v>804975</v>
+      </c>
+      <c r="G40" s="170">
+        <f>D40*E40*12/1000</f>
+        <v>12000</v>
+      </c>
+      <c r="H40" s="170" t="s">
+        <v>305</v>
+      </c>
+      <c r="I40" s="265" t="s">
+        <v>309</v>
+      </c>
+      <c r="J40" s="273" t="s">
         <v>416</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" s="212" customFormat="1" ht="30">
-      <c r="A40" s="254">
-        <v>3</v>
-      </c>
-      <c r="B40" s="255" t="s">
-        <v>292</v>
-      </c>
-      <c r="C40" s="249" t="s">
-        <v>272</v>
-      </c>
-      <c r="D40" s="256"/>
-      <c r="E40" s="257"/>
-      <c r="F40" s="258"/>
-      <c r="G40" s="256"/>
-      <c r="H40" s="256" t="s">
-        <v>302</v>
-      </c>
-      <c r="I40" s="262" t="s">
-        <v>309</v>
-      </c>
-      <c r="J40" s="274" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="41" spans="1:10" s="212" customFormat="1" ht="30">
       <c r="A41" s="254">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B41" s="255" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C41" s="249" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D41" s="256"/>
       <c r="E41" s="257"/>
@@ -22265,358 +22284,374 @@
         <v>309</v>
       </c>
       <c r="J41" s="274" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" s="212" customFormat="1" ht="30">
+      <c r="A42" s="254">
+        <v>4</v>
+      </c>
+      <c r="B42" s="255" t="s">
+        <v>293</v>
+      </c>
+      <c r="C42" s="249" t="s">
+        <v>271</v>
+      </c>
+      <c r="D42" s="256"/>
+      <c r="E42" s="257"/>
+      <c r="F42" s="258"/>
+      <c r="G42" s="256"/>
+      <c r="H42" s="256" t="s">
+        <v>302</v>
+      </c>
+      <c r="I42" s="262" t="s">
+        <v>309</v>
+      </c>
+      <c r="J42" s="274" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="42" spans="1:10" s="212" customFormat="1">
-      <c r="A42" s="294">
+    <row r="43" spans="1:10" s="212" customFormat="1">
+      <c r="A43" s="294">
         <v>5</v>
       </c>
-      <c r="B42" s="210" t="s">
+      <c r="B43" s="210" t="s">
         <v>439</v>
       </c>
-      <c r="C42" s="213" t="s">
+      <c r="C43" s="213" t="s">
         <v>271</v>
       </c>
-      <c r="D42" s="295">
+      <c r="D43" s="295">
         <v>1</v>
       </c>
-      <c r="E42" s="296">
+      <c r="E43" s="296">
         <v>700000</v>
       </c>
-      <c r="F42" s="297">
-        <f>IF(E42&gt;0,E42-MIN(E42,4250000)*10%-MIN(E42,1700000)*2%-MAX(0,E42-MIN(E42,4250000)*10%-MIN(E42,1700000)*2%-129750)*10%,0)</f>
+      <c r="F43" s="297">
+        <f>IF(E43&gt;0,E43-MIN(E43,4250000)*10%-MIN(E43,1700000)*2%-MAX(0,E43-MIN(E43,4250000)*10%-MIN(E43,1700000)*2%-129750)*10%,0)</f>
         <v>567375</v>
       </c>
-      <c r="G42" s="295">
-        <f>D42*E42*12/1000</f>
+      <c r="G43" s="295">
+        <f>D43*E43*12/1000</f>
         <v>8400</v>
       </c>
-      <c r="H42" s="295" t="s">
+      <c r="H43" s="295" t="s">
         <v>305</v>
       </c>
-      <c r="I42" s="298" t="s">
+      <c r="I43" s="298" t="s">
         <v>309</v>
       </c>
-      <c r="J42" s="299" t="s">
+      <c r="J43" s="299" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="30">
-      <c r="A43" s="168">
+    <row r="44" spans="1:10" ht="30">
+      <c r="A44" s="168">
         <v>6</v>
       </c>
-      <c r="B43" s="176" t="s">
+      <c r="B44" s="176" t="s">
         <v>440</v>
       </c>
-      <c r="C43" s="194" t="s">
+      <c r="C44" s="194" t="s">
         <v>272</v>
-      </c>
-      <c r="D43" s="177">
-        <v>1</v>
-      </c>
-      <c r="E43" s="229">
-        <v>1000000</v>
-      </c>
-      <c r="F43" s="230">
-        <f>IF(E43&gt;0,E43-MIN(E43,4250000)*10%-MIN(E43,1700000)*2%-MAX(0,E43-MIN(E43,4250000)*10%-MIN(E43,1700000)*2%-129750)*10%,0)</f>
-        <v>804975</v>
-      </c>
-      <c r="G43" s="170">
-        <f>D43*E43*12/1000</f>
-        <v>12000</v>
-      </c>
-      <c r="H43" s="170" t="s">
-        <v>305</v>
-      </c>
-      <c r="I43" s="265" t="s">
-        <v>309</v>
-      </c>
-      <c r="J43" s="273" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" ht="30">
-      <c r="A44" s="182">
-        <v>7</v>
-      </c>
-      <c r="B44" s="176" t="s">
-        <v>441</v>
-      </c>
-      <c r="C44" s="195" t="s">
-        <v>271</v>
       </c>
       <c r="D44" s="177">
         <v>1</v>
       </c>
-      <c r="E44" s="223">
+      <c r="E44" s="229">
+        <v>1000000</v>
+      </c>
+      <c r="F44" s="230">
+        <f>IF(E44&gt;0,E44-MIN(E44,4250000)*10%-MIN(E44,1700000)*2%-MAX(0,E44-MIN(E44,4250000)*10%-MIN(E44,1700000)*2%-129750)*10%,0)</f>
+        <v>804975</v>
+      </c>
+      <c r="G44" s="170">
+        <f>D44*E44*12/1000</f>
+        <v>12000</v>
+      </c>
+      <c r="H44" s="170" t="s">
+        <v>305</v>
+      </c>
+      <c r="I44" s="265" t="s">
+        <v>309</v>
+      </c>
+      <c r="J44" s="273" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" ht="30">
+      <c r="A45" s="182">
+        <v>7</v>
+      </c>
+      <c r="B45" s="176" t="s">
+        <v>441</v>
+      </c>
+      <c r="C45" s="195" t="s">
+        <v>271</v>
+      </c>
+      <c r="D45" s="177">
+        <v>1</v>
+      </c>
+      <c r="E45" s="223">
         <v>700000</v>
       </c>
-      <c r="F44" s="224">
-        <f>IF(E44&gt;0,E44-MIN(E44,4250000)*10%-MIN(E44,1700000)*2%-MAX(0,E44-MIN(E44,4250000)*10%-MIN(E44,1700000)*2%-129750)*10%,0)</f>
+      <c r="F45" s="224">
+        <f>IF(E45&gt;0,E45-MIN(E45,4250000)*10%-MIN(E45,1700000)*2%-MAX(0,E45-MIN(E45,4250000)*10%-MIN(E45,1700000)*2%-129750)*10%,0)</f>
         <v>567375</v>
       </c>
-      <c r="G44" s="177">
-        <f>D44*E44*12/1000</f>
+      <c r="G45" s="177">
+        <f>D45*E45*12/1000</f>
         <v>8400</v>
       </c>
-      <c r="H44" s="177" t="s">
+      <c r="H45" s="177" t="s">
         <v>305</v>
       </c>
-      <c r="I44" s="264" t="s">
+      <c r="I45" s="264" t="s">
         <v>309</v>
       </c>
-      <c r="J44" s="270" t="s">
+      <c r="J45" s="270" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="45" spans="1:10" s="212" customFormat="1" ht="30">
-      <c r="A45" s="254">
+    <row r="46" spans="1:10" s="212" customFormat="1" ht="30">
+      <c r="A46" s="254">
         <v>8</v>
       </c>
-      <c r="B45" s="255" t="s">
+      <c r="B46" s="255" t="s">
         <v>294</v>
       </c>
-      <c r="C45" s="249" t="s">
+      <c r="C46" s="249" t="s">
         <v>271</v>
       </c>
-      <c r="D45" s="256">
+      <c r="D46" s="256">
         <v>0</v>
       </c>
-      <c r="E45" s="257"/>
-      <c r="F45" s="258"/>
-      <c r="G45" s="256"/>
-      <c r="H45" s="256" t="s">
+      <c r="E46" s="257"/>
+      <c r="F46" s="258"/>
+      <c r="G46" s="256"/>
+      <c r="H46" s="256" t="s">
         <v>302</v>
       </c>
-      <c r="I45" s="262" t="s">
+      <c r="I46" s="262" t="s">
         <v>309</v>
       </c>
-      <c r="J45" s="274" t="s">
+      <c r="J46" s="274" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="46" spans="1:10">
-      <c r="A46" s="167" t="s">
+    <row r="47" spans="1:10">
+      <c r="A47" s="167" t="s">
         <v>267</v>
       </c>
-      <c r="B46" s="167" t="s">
+      <c r="B47" s="167" t="s">
         <v>291</v>
       </c>
-      <c r="C46" s="167"/>
-      <c r="D46" s="167">
-        <f t="shared" ref="D46:G46" si="8">SUM(D47:D50)</f>
+      <c r="C47" s="167"/>
+      <c r="D47" s="167">
+        <f t="shared" ref="D47:G47" si="8">SUM(D48:D51)</f>
         <v>2</v>
       </c>
-      <c r="E46" s="231">
+      <c r="E47" s="231">
         <f t="shared" si="8"/>
         <v>3393100</v>
       </c>
-      <c r="F46" s="232">
+      <c r="F47" s="232">
         <f t="shared" si="8"/>
         <v>2739235.2</v>
       </c>
-      <c r="G46" s="167">
+      <c r="G47" s="167">
         <f t="shared" si="8"/>
         <v>25200</v>
       </c>
-      <c r="H46" s="167"/>
-      <c r="I46" s="167"/>
-      <c r="J46" s="269"/>
-    </row>
-    <row r="47" spans="1:10" ht="30">
-      <c r="A47" s="168">
+      <c r="H47" s="167"/>
+      <c r="I47" s="167"/>
+      <c r="J47" s="269"/>
+    </row>
+    <row r="48" spans="1:10" ht="30">
+      <c r="A48" s="168">
         <v>1</v>
       </c>
-      <c r="B47" s="169" t="s">
+      <c r="B48" s="169" t="s">
         <v>283</v>
       </c>
-      <c r="C47" s="193" t="s">
+      <c r="C48" s="193" t="s">
         <v>270</v>
-      </c>
-      <c r="D47" s="170">
-        <v>1</v>
-      </c>
-      <c r="E47" s="229">
-        <v>1400000</v>
-      </c>
-      <c r="F47" s="230">
-        <f>IF(E47&gt;0,E47-MIN(E47,4250000)*10%-MIN(E47,1700000)*2%-MAX(0,E47-MIN(E47,4250000)*10%-MIN(E47,1700000)*2%-129750)*10%,0)</f>
-        <v>1121775</v>
-      </c>
-      <c r="G47" s="170">
-        <f>D47*E47*12/1000</f>
-        <v>16800</v>
-      </c>
-      <c r="H47" s="170" t="s">
-        <v>305</v>
-      </c>
-      <c r="I47" s="265" t="s">
-        <v>307</v>
-      </c>
-      <c r="J47" s="273" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10">
-      <c r="A48" s="196">
-        <v>2</v>
-      </c>
-      <c r="B48" s="215" t="s">
-        <v>284</v>
-      </c>
-      <c r="C48" s="194" t="s">
-        <v>272</v>
       </c>
       <c r="D48" s="170">
         <v>1</v>
       </c>
-      <c r="E48" s="223">
+      <c r="E48" s="229">
+        <v>1400000</v>
+      </c>
+      <c r="F48" s="230">
+        <f>IF(E48&gt;0,E48-MIN(E48,4250000)*10%-MIN(E48,1700000)*2%-MAX(0,E48-MIN(E48,4250000)*10%-MIN(E48,1700000)*2%-129750)*10%,0)</f>
+        <v>1121775</v>
+      </c>
+      <c r="G48" s="170">
+        <f>D48*E48*12/1000</f>
+        <v>16800</v>
+      </c>
+      <c r="H48" s="170" t="s">
+        <v>305</v>
+      </c>
+      <c r="I48" s="265" t="s">
+        <v>307</v>
+      </c>
+      <c r="J48" s="273" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10">
+      <c r="A49" s="196">
+        <v>2</v>
+      </c>
+      <c r="B49" s="215" t="s">
+        <v>284</v>
+      </c>
+      <c r="C49" s="194" t="s">
+        <v>272</v>
+      </c>
+      <c r="D49" s="170">
+        <v>1</v>
+      </c>
+      <c r="E49" s="223">
         <v>700000</v>
       </c>
-      <c r="F48" s="224">
-        <f>IF(E48&gt;0,E48-MIN(E48,4250000)*10%-MIN(E48,1700000)*2%-MAX(0,E48-MIN(E48,4250000)*10%-MIN(E48,1700000)*2%-129750)*10%,0)</f>
+      <c r="F49" s="224">
+        <f>IF(E49&gt;0,E49-MIN(E49,4250000)*10%-MIN(E49,1700000)*2%-MAX(0,E49-MIN(E49,4250000)*10%-MIN(E49,1700000)*2%-129750)*10%,0)</f>
         <v>567375</v>
       </c>
-      <c r="G48" s="177">
-        <f>D48*E48*12/1000</f>
+      <c r="G49" s="177">
+        <f>D49*E49*12/1000</f>
         <v>8400</v>
       </c>
-      <c r="H48" s="177" t="s">
+      <c r="H49" s="177" t="s">
         <v>305</v>
       </c>
-      <c r="I48" s="264" t="s">
+      <c r="I49" s="264" t="s">
         <v>309</v>
       </c>
-      <c r="J48" s="270" t="s">
+      <c r="J49" s="270" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="49" spans="1:10">
-      <c r="A49" s="259">
+    <row r="50" spans="1:10">
+      <c r="A50" s="259">
         <v>3</v>
       </c>
-      <c r="B49" s="260" t="s">
+      <c r="B50" s="260" t="s">
         <v>285</v>
       </c>
-      <c r="C49" s="249"/>
-      <c r="D49" s="256"/>
-      <c r="E49" s="252">
+      <c r="C50" s="249"/>
+      <c r="D50" s="256"/>
+      <c r="E50" s="252">
         <v>867500</v>
       </c>
-      <c r="F49" s="253">
-        <f>IF(E49&gt;0,E49-MIN(E49,4250000)*10%-MIN(E49,1700000)*2%-MAX(0,E49-MIN(E49,4250000)*10%-MIN(E49,1700000)*2%-129750)*10%,0)</f>
+      <c r="F50" s="253">
+        <f>IF(E50&gt;0,E50-MIN(E50,4250000)*10%-MIN(E50,1700000)*2%-MAX(0,E50-MIN(E50,4250000)*10%-MIN(E50,1700000)*2%-129750)*10%,0)</f>
         <v>700035</v>
       </c>
-      <c r="G49" s="251"/>
-      <c r="H49" s="251" t="s">
+      <c r="G50" s="251"/>
+      <c r="H50" s="251" t="s">
         <v>302</v>
       </c>
-      <c r="I49" s="263" t="s">
+      <c r="I50" s="263" t="s">
         <v>309</v>
       </c>
-      <c r="J49" s="272" t="s">
+      <c r="J50" s="272" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="30">
-      <c r="A50" s="259">
+    <row r="51" spans="1:10" ht="30">
+      <c r="A51" s="259">
         <v>4</v>
       </c>
-      <c r="B50" s="260" t="s">
+      <c r="B51" s="260" t="s">
         <v>286</v>
       </c>
-      <c r="C50" s="249"/>
-      <c r="D50" s="251"/>
-      <c r="E50" s="257">
+      <c r="C51" s="249"/>
+      <c r="D51" s="251"/>
+      <c r="E51" s="257">
         <v>425600</v>
       </c>
-      <c r="F50" s="258">
-        <f>IF(E50&gt;0,E50-MIN(E50,4250000)*10%-MIN(E50,1700000)*2%-MAX(0,E50-MIN(E50,4250000)*10%-MIN(E50,1700000)*2%-129750)*10%,0)</f>
+      <c r="F51" s="258">
+        <f>IF(E51&gt;0,E51-MIN(E51,4250000)*10%-MIN(E51,1700000)*2%-MAX(0,E51-MIN(E51,4250000)*10%-MIN(E51,1700000)*2%-129750)*10%,0)</f>
         <v>350050.2</v>
       </c>
-      <c r="G50" s="256"/>
-      <c r="H50" s="256" t="s">
+      <c r="G51" s="256"/>
+      <c r="H51" s="256" t="s">
         <v>302</v>
       </c>
-      <c r="I50" s="262" t="s">
+      <c r="I51" s="262" t="s">
         <v>309</v>
       </c>
-      <c r="J50" s="274" t="s">
+      <c r="J51" s="274" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A51" s="197"/>
-      <c r="B51" s="198" t="s">
+    <row r="52" spans="1:10" ht="15.75" thickBot="1">
+      <c r="A52" s="197"/>
+      <c r="B52" s="198" t="s">
         <v>290</v>
       </c>
-      <c r="C51" s="189"/>
-      <c r="D51" s="174">
-        <f>D6+D10+D12+D18+D23+D34+D37+D46</f>
-        <v>30</v>
-      </c>
-      <c r="E51" s="233">
-        <f>E6+E10+E12+E18+E23+E34+E37+E46</f>
-        <v>31793100</v>
-      </c>
-      <c r="F51" s="235">
-        <f>F6+F10+F12+F18+F23+F34+F37+F46</f>
-        <v>25595335.199999999</v>
-      </c>
-      <c r="G51" s="234">
-        <f>G6+G10+G12+G18+G23+G34+G37+G46</f>
-        <v>366000</v>
-      </c>
-      <c r="H51" s="234"/>
-      <c r="I51" s="234"/>
-      <c r="J51" s="234"/>
-    </row>
-    <row r="52" spans="1:10" ht="45">
-      <c r="A52" s="241"/>
-      <c r="B52" s="217" t="s">
-        <v>453</v>
-      </c>
-      <c r="C52" s="186"/>
-      <c r="D52" s="1"/>
-      <c r="E52" s="175"/>
-      <c r="G52" s="165"/>
-    </row>
-    <row r="53" spans="1:10">
+      <c r="C52" s="189"/>
+      <c r="D52" s="174">
+        <f>D6+D10+D12+D18+D24+D35+D38+D47</f>
+        <v>31</v>
+      </c>
+      <c r="E52" s="233">
+        <f>E6+E10+E12+E18+E24+E35+E38+E47</f>
+        <v>33193100</v>
+      </c>
+      <c r="F52" s="235">
+        <f>F6+F10+F12+F18+F24+F35+F38+F47</f>
+        <v>26717110.199999999</v>
+      </c>
+      <c r="G52" s="234">
+        <f>G6+G10+G12+G18+G24+G35+G38+G47</f>
+        <v>382800</v>
+      </c>
+      <c r="H52" s="234"/>
+      <c r="I52" s="234"/>
+      <c r="J52" s="234"/>
+    </row>
+    <row r="53" spans="1:10" ht="45">
       <c r="A53" s="241"/>
-      <c r="B53" s="261" t="s">
-        <v>296</v>
-      </c>
-      <c r="C53" s="190"/>
-      <c r="D53" s="129"/>
-      <c r="E53" s="129"/>
-      <c r="G53" s="1"/>
+      <c r="B53" s="217" t="s">
+        <v>451</v>
+      </c>
+      <c r="C53" s="186"/>
+      <c r="D53" s="1"/>
+      <c r="E53" s="175"/>
+      <c r="G53" s="165"/>
     </row>
     <row r="54" spans="1:10">
       <c r="A54" s="241"/>
-      <c r="B54" s="216" t="str">
-        <f>"Всего в штате по таблице (столбец D) — "&amp;D51&amp;" чел."</f>
-        <v>Всего в штате по таблице (столбец D) — 30 чел.</v>
+      <c r="B54" s="261" t="s">
+        <v>296</v>
       </c>
       <c r="C54" s="190"/>
       <c r="D54" s="129"/>
       <c r="E54" s="129"/>
       <c r="G54" s="1"/>
     </row>
-    <row r="55" spans="1:10" ht="43.5">
+    <row r="55" spans="1:10">
       <c r="A55" s="241"/>
-      <c r="B55" s="240" t="str">
-        <f>"Состав: проектный офис — "&amp;(D10+D12+D23+D34+D37)&amp;" чел.; Фонд с Проектным офисом для Центральной Азии — "&amp;(D6+D18+D46)&amp;" чел."</f>
-        <v>Состав: проектный офис — 21 чел.; Фонд с Проектным офисом для Центральной Азии — 9 чел.</v>
-      </c>
-      <c r="C55" s="186"/>
-      <c r="D55" s="1"/>
-      <c r="E55" s="1"/>
+      <c r="B55" s="216" t="str">
+        <f>"Всего в штате по таблице (столбец D) — "&amp;D52&amp;" чел."</f>
+        <v>Всего в штате по таблице (столбец D) — 31 чел.</v>
+      </c>
+      <c r="C55" s="190"/>
+      <c r="D55" s="129"/>
+      <c r="E55" s="129"/>
       <c r="G55" s="1"/>
     </row>
-    <row r="56" spans="1:10">
-      <c r="A56" s="1"/>
-      <c r="B56" s="217"/>
+    <row r="56" spans="1:10" ht="43.5">
+      <c r="A56" s="241"/>
+      <c r="B56" s="240" t="str">
+        <f>"Состав: проектный офис — "&amp;(D10+D12+D24+D35+D38)&amp;" чел.; Фонд с Проектным офисом для Центральной Азии — "&amp;(D6+D18+D47)&amp;" чел."</f>
+        <v>Состав: проектный офис — 21 чел.; Фонд с Проектным офисом для Центральной Азии — 10 чел.</v>
+      </c>
       <c r="C56" s="186"/>
       <c r="D56" s="1"/>
       <c r="E56" s="1"/>
@@ -22624,7 +22659,7 @@
     </row>
     <row r="57" spans="1:10">
       <c r="A57" s="1"/>
-      <c r="B57" s="209"/>
+      <c r="B57" s="217"/>
       <c r="C57" s="186"/>
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
@@ -29653,6 +29688,14 @@
       <c r="D935" s="1"/>
       <c r="E935" s="1"/>
       <c r="G935" s="1"/>
+    </row>
+    <row r="936" spans="1:7">
+      <c r="A936" s="1"/>
+      <c r="B936" s="209"/>
+      <c r="C936" s="186"/>
+      <c r="D936" s="1"/>
+      <c r="E936" s="1"/>
+      <c r="G936" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -29755,7 +29798,7 @@
     </row>
     <row r="10" spans="1:6" ht="51">
       <c r="A10" s="278" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="B10" s="280" t="s">
         <v>343</v>

--- a/TAZA/_документы/ШР ЦАКФ.xlsx
+++ b/TAZA/_документы/ШР ЦАКФ.xlsx
@@ -2409,15 +2409,6 @@
     <t>Заместитель руководителя Проектного офиса для Центральной Азии</t>
   </si>
   <si>
-    <t>Менеджер проектов – эколог / Загирова Анастасия</t>
-  </si>
-  <si>
-    <t>Менеджер проектов – эколог / Абулхан А.</t>
-  </si>
-  <si>
-    <t>Менеджер проектов – эколог (отходы, вода, воздух) / вакансия</t>
-  </si>
-  <si>
     <t>*приход с 12.2026 и в 2027 году выделен сиреневым (с 12.2026 – Өміртай А.; остальные – с 02.2027)</t>
   </si>
   <si>
@@ -2437,6 +2428,15 @@
   </si>
   <si>
     <t>Руководство Проектным офисом для Центральной Азии; до назначения Руководителя обязанности исполняет ГИД без оклада и доплаты</t>
+  </si>
+  <si>
+    <t>Менеджер проектов / Загирова Анастасия</t>
+  </si>
+  <si>
+    <t>Менеджер проектов / Абулхан А.</t>
+  </si>
+  <si>
+    <t>Менеджер проектов / вакансия</t>
   </si>
 </sst>
 </file>
@@ -5585,60 +5585,174 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="37" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="38" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="36" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="32" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="37" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="38" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="36" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="33" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="34" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="35" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="32" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="39" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="1" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="39" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="37" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="38" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="37" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="38" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="36" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="10" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="2" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="17" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="39" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="3" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="39" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="3" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="1" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="10" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="33" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="34" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="35" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="177" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -5690,119 +5804,29 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="37" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="38" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="36" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="39" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="33" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="35" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="39" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="3" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="37" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="36" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="10" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="37" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="38" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="36" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="33" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="34" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="35" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="1" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="32" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="37" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="38" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="36" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="37" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="38" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="39" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="3" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="10" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="2" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="17" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="32" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="33" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="34" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="35" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="39" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="1" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="25" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -5813,47 +5837,98 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="36" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="33" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="35" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="37" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="36" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="0" xfId="177" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="3" borderId="38" xfId="177" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="37" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="3" borderId="36" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="46" fillId="2" borderId="37" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="46" fillId="2" borderId="38" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="37" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="36" xfId="177" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="0" xfId="177" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="46" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -5864,15 +5939,6 @@
     <xf numFmtId="49" fontId="46" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -5885,13 +5951,67 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5902,126 +6022,6 @@
     </xf>
     <xf numFmtId="0" fontId="46" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -6363,7 +6363,7 @@
         <xdr:cNvPr id="2" name="TextBox 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6421,7 +6421,7 @@
         <xdr:cNvPr id="3" name="TextBox 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000003000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6476,7 +6476,7 @@
         <xdr:cNvPr id="4" name="TextBox 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000004000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000004000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10253,26 +10253,26 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="301" t="s">
+      <c r="A2" s="309" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="301"/>
+      <c r="B2" s="309"/>
       <c r="C2" s="132" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="302" t="s">
+      <c r="A3" s="314" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="303"/>
+      <c r="B3" s="315"/>
       <c r="C3" s="133"/>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="302" t="s">
+      <c r="A4" s="314" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="303" t="s">
+      <c r="B4" s="315" t="s">
         <v>27</v>
       </c>
       <c r="C4" s="133"/>
@@ -10285,24 +10285,24 @@
       <c r="C5" s="133"/>
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1">
-      <c r="A6" s="302" t="s">
+      <c r="A6" s="314" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="303"/>
+      <c r="B6" s="315"/>
       <c r="C6" s="134"/>
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1">
-      <c r="A7" s="302" t="s">
+      <c r="A7" s="314" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="303"/>
+      <c r="B7" s="315"/>
       <c r="C7" s="135"/>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="304" t="s">
+      <c r="A8" s="305" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="305"/>
+      <c r="B8" s="306"/>
       <c r="C8" s="131">
         <f>SUM(C3:C7)</f>
         <v>0</v>
@@ -10312,17 +10312,17 @@
       <c r="C9" s="2"/>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="306" t="s">
+      <c r="A10" s="316" t="s">
         <v>31</v>
       </c>
-      <c r="B10" s="306"/>
-      <c r="C10" s="306"/>
+      <c r="B10" s="316"/>
+      <c r="C10" s="316"/>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="301" t="s">
+      <c r="A11" s="309" t="s">
         <v>2</v>
       </c>
-      <c r="B11" s="301"/>
+      <c r="B11" s="309"/>
       <c r="C11" s="132" t="s">
         <v>1</v>
       </c>
@@ -10349,10 +10349,10 @@
       <c r="C14" s="136"/>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="304" t="s">
+      <c r="A15" s="305" t="s">
         <v>35</v>
       </c>
-      <c r="B15" s="305"/>
+      <c r="B15" s="306"/>
       <c r="C15" s="130">
         <f>SUM(C12:C14)</f>
         <v>0</v>
@@ -10382,10 +10382,10 @@
       <c r="C19" s="4"/>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="301" t="s">
+      <c r="A20" s="309" t="s">
         <v>2</v>
       </c>
-      <c r="B20" s="301"/>
+      <c r="B20" s="309"/>
       <c r="C20" s="132" t="s">
         <v>1</v>
       </c>
@@ -10430,17 +10430,17 @@
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="309" t="s">
+      <c r="A26" s="310" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="310"/>
-      <c r="C26" s="311"/>
+      <c r="B26" s="311"/>
+      <c r="C26" s="312"/>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="301" t="s">
+      <c r="A27" s="309" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="301"/>
+      <c r="B27" s="309"/>
       <c r="C27" s="138"/>
     </row>
     <row r="28" spans="1:4">
@@ -10457,17 +10457,17 @@
       <c r="C29" s="6"/>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="312" t="s">
+      <c r="A30" s="313" t="s">
         <v>40</v>
       </c>
-      <c r="B30" s="312"/>
+      <c r="B30" s="313"/>
       <c r="C30" s="2"/>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="301" t="s">
+      <c r="A31" s="309" t="s">
         <v>2</v>
       </c>
-      <c r="B31" s="301"/>
+      <c r="B31" s="309"/>
       <c r="C31" s="132" t="s">
         <v>1</v>
       </c>
@@ -10504,8 +10504,8 @@
       <c r="D35" s="3"/>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="313"/>
-      <c r="B36" s="314"/>
+      <c r="A36" s="301"/>
+      <c r="B36" s="302"/>
       <c r="C36" s="144">
         <f>SUM(C32:C35)</f>
         <v>0</v>
@@ -10517,10 +10517,10 @@
       <c r="C37" s="8"/>
     </row>
     <row r="38" spans="1:4">
-      <c r="A38" s="315" t="s">
+      <c r="A38" s="303" t="s">
         <v>42</v>
       </c>
-      <c r="B38" s="316"/>
+      <c r="B38" s="304"/>
       <c r="C38" s="145">
         <f>C28-C36</f>
         <v>0</v>
@@ -10543,11 +10543,18 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A13:B13"/>
     <mergeCell ref="A32:B32"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="A17:B17"/>
@@ -10560,18 +10567,11 @@
     <mergeCell ref="A27:B27"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A38:B38"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -10839,11 +10839,11 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="1"/>
-      <c r="B19" s="301" t="s">
+      <c r="B19" s="309" t="s">
         <v>259</v>
       </c>
-      <c r="C19" s="301"/>
-      <c r="D19" s="301"/>
+      <c r="C19" s="309"/>
+      <c r="D19" s="309"/>
       <c r="E19" s="162" t="e">
         <f>E15/E18</f>
         <v>#REF!</v>
@@ -10920,17 +10920,17 @@
       <c r="A1" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="319" t="s">
+      <c r="B1" s="357" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="319"/>
-      <c r="D1" s="319"/>
-      <c r="E1" s="319"/>
-      <c r="F1" s="319"/>
-      <c r="G1" s="319"/>
-      <c r="H1" s="319"/>
-      <c r="I1" s="319"/>
-      <c r="J1" s="319"/>
+      <c r="C1" s="357"/>
+      <c r="D1" s="357"/>
+      <c r="E1" s="357"/>
+      <c r="F1" s="357"/>
+      <c r="G1" s="357"/>
+      <c r="H1" s="357"/>
+      <c r="I1" s="357"/>
+      <c r="J1" s="357"/>
       <c r="K1" s="85"/>
       <c r="O1" s="51"/>
     </row>
@@ -10968,17 +10968,17 @@
       <c r="A3" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="320" t="s">
+      <c r="B3" s="358" t="s">
         <v>201</v>
       </c>
-      <c r="C3" s="320"/>
-      <c r="D3" s="320"/>
-      <c r="E3" s="320"/>
-      <c r="F3" s="320"/>
-      <c r="G3" s="320"/>
-      <c r="H3" s="320"/>
-      <c r="I3" s="320"/>
-      <c r="J3" s="320"/>
+      <c r="C3" s="358"/>
+      <c r="D3" s="358"/>
+      <c r="E3" s="358"/>
+      <c r="F3" s="358"/>
+      <c r="G3" s="358"/>
+      <c r="H3" s="358"/>
+      <c r="I3" s="358"/>
+      <c r="J3" s="358"/>
       <c r="K3" s="88"/>
       <c r="O3" s="51"/>
     </row>
@@ -10986,17 +10986,17 @@
       <c r="A4" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="321" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="321"/>
-      <c r="D4" s="321"/>
-      <c r="E4" s="321"/>
-      <c r="F4" s="321"/>
-      <c r="G4" s="321"/>
-      <c r="H4" s="321"/>
-      <c r="I4" s="321"/>
-      <c r="J4" s="321"/>
+      <c r="B4" s="359" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="359"/>
+      <c r="D4" s="359"/>
+      <c r="E4" s="359"/>
+      <c r="F4" s="359"/>
+      <c r="G4" s="359"/>
+      <c r="H4" s="359"/>
+      <c r="I4" s="359"/>
+      <c r="J4" s="359"/>
       <c r="K4" s="89"/>
       <c r="O4" s="51"/>
     </row>
@@ -11004,17 +11004,17 @@
       <c r="A5" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="322" t="s">
+      <c r="B5" s="360" t="s">
         <v>47</v>
       </c>
-      <c r="C5" s="322"/>
-      <c r="D5" s="322"/>
-      <c r="E5" s="322"/>
-      <c r="F5" s="322"/>
-      <c r="G5" s="322"/>
-      <c r="H5" s="322"/>
-      <c r="I5" s="322"/>
-      <c r="J5" s="322"/>
+      <c r="C5" s="360"/>
+      <c r="D5" s="360"/>
+      <c r="E5" s="360"/>
+      <c r="F5" s="360"/>
+      <c r="G5" s="360"/>
+      <c r="H5" s="360"/>
+      <c r="I5" s="360"/>
+      <c r="J5" s="360"/>
       <c r="K5" s="90"/>
       <c r="O5" s="51"/>
     </row>
@@ -11022,17 +11022,17 @@
       <c r="A6" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B6" s="322" t="s">
+      <c r="B6" s="360" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="322"/>
-      <c r="D6" s="322"/>
-      <c r="E6" s="322"/>
-      <c r="F6" s="322"/>
-      <c r="G6" s="322"/>
-      <c r="H6" s="322"/>
-      <c r="I6" s="322"/>
-      <c r="J6" s="322"/>
+      <c r="C6" s="360"/>
+      <c r="D6" s="360"/>
+      <c r="E6" s="360"/>
+      <c r="F6" s="360"/>
+      <c r="G6" s="360"/>
+      <c r="H6" s="360"/>
+      <c r="I6" s="360"/>
+      <c r="J6" s="360"/>
       <c r="K6" s="90"/>
       <c r="O6" s="51"/>
     </row>
@@ -11040,15 +11040,15 @@
       <c r="A7" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B7" s="323" t="s">
+      <c r="B7" s="361" t="s">
         <v>183</v>
       </c>
-      <c r="C7" s="323"/>
-      <c r="D7" s="323"/>
-      <c r="E7" s="323"/>
-      <c r="F7" s="323"/>
-      <c r="G7" s="323"/>
-      <c r="H7" s="323"/>
+      <c r="C7" s="361"/>
+      <c r="D7" s="361"/>
+      <c r="E7" s="361"/>
+      <c r="F7" s="361"/>
+      <c r="G7" s="361"/>
+      <c r="H7" s="361"/>
       <c r="I7" s="91"/>
       <c r="J7" s="71" t="s">
         <v>50</v>
@@ -11074,51 +11074,51 @@
       <c r="A22" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B22" s="324" t="s">
+      <c r="B22" s="362" t="s">
         <v>0</v>
       </c>
-      <c r="C22" s="327" t="s">
+      <c r="C22" s="365" t="s">
         <v>51</v>
       </c>
-      <c r="D22" s="328"/>
-      <c r="E22" s="328"/>
-      <c r="F22" s="328"/>
-      <c r="G22" s="329"/>
+      <c r="D22" s="366"/>
+      <c r="E22" s="366"/>
+      <c r="F22" s="366"/>
+      <c r="G22" s="367"/>
       <c r="H22" s="93"/>
-      <c r="I22" s="328" t="s">
+      <c r="I22" s="366" t="s">
         <v>52</v>
       </c>
-      <c r="J22" s="329"/>
+      <c r="J22" s="367"/>
       <c r="K22" s="94"/>
     </row>
     <row r="23" spans="1:16" ht="12" customHeight="1">
       <c r="A23" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="325"/>
-      <c r="C23" s="330"/>
-      <c r="D23" s="331"/>
-      <c r="E23" s="331"/>
-      <c r="F23" s="331"/>
-      <c r="G23" s="332"/>
+      <c r="B23" s="363"/>
+      <c r="C23" s="368"/>
+      <c r="D23" s="369"/>
+      <c r="E23" s="369"/>
+      <c r="F23" s="369"/>
+      <c r="G23" s="370"/>
       <c r="H23" s="95"/>
-      <c r="I23" s="331"/>
-      <c r="J23" s="332"/>
+      <c r="I23" s="369"/>
+      <c r="J23" s="370"/>
       <c r="K23" s="94"/>
     </row>
     <row r="24" spans="1:16" ht="24" customHeight="1">
       <c r="A24" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B24" s="326"/>
-      <c r="C24" s="333"/>
-      <c r="D24" s="334"/>
-      <c r="E24" s="334"/>
-      <c r="F24" s="334"/>
-      <c r="G24" s="335"/>
+      <c r="B24" s="364"/>
+      <c r="C24" s="371"/>
+      <c r="D24" s="372"/>
+      <c r="E24" s="372"/>
+      <c r="F24" s="372"/>
+      <c r="G24" s="373"/>
       <c r="H24" s="96"/>
-      <c r="I24" s="334"/>
-      <c r="J24" s="335"/>
+      <c r="I24" s="372"/>
+      <c r="J24" s="373"/>
       <c r="K24" s="94"/>
     </row>
     <row r="25" spans="1:16" ht="15.75" hidden="1" customHeight="1"/>
@@ -11160,13 +11160,13 @@
       <c r="B29" s="58">
         <v>1</v>
       </c>
-      <c r="C29" s="336" t="s">
+      <c r="C29" s="323" t="s">
         <v>202</v>
       </c>
-      <c r="D29" s="337"/>
-      <c r="E29" s="337"/>
-      <c r="F29" s="337"/>
-      <c r="G29" s="338"/>
+      <c r="D29" s="324"/>
+      <c r="E29" s="324"/>
+      <c r="F29" s="324"/>
+      <c r="G29" s="325"/>
       <c r="H29" s="97"/>
       <c r="I29" s="97" t="e">
         <f>I35+I44+I46+I47+I50+#REF!+I68+I71+I72+I73+I77+I89+I97+I101+I106+I108+I116+I131+I142+I146+I147+I154+I32+I34+#REF!+#REF!+I151+#REF!+I98+I113+I155</f>
@@ -11183,15 +11183,15 @@
       <c r="B30" s="58">
         <v>2</v>
       </c>
-      <c r="C30" s="339" t="s">
+      <c r="C30" s="332" t="s">
         <v>54</v>
       </c>
-      <c r="D30" s="336" t="s">
+      <c r="D30" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E30" s="337"/>
-      <c r="F30" s="337"/>
-      <c r="G30" s="338"/>
+      <c r="E30" s="324"/>
+      <c r="F30" s="324"/>
+      <c r="G30" s="325"/>
       <c r="H30" s="97"/>
       <c r="I30" s="97"/>
       <c r="J30" s="99" t="e">
@@ -11211,15 +11211,15 @@
       <c r="B31" s="58">
         <v>3</v>
       </c>
-      <c r="C31" s="340"/>
+      <c r="C31" s="333"/>
       <c r="D31" s="342" t="s">
         <v>55</v>
       </c>
-      <c r="E31" s="345" t="s">
+      <c r="E31" s="319" t="s">
         <v>56</v>
       </c>
-      <c r="F31" s="346"/>
-      <c r="G31" s="347"/>
+      <c r="F31" s="320"/>
+      <c r="G31" s="321"/>
       <c r="H31" s="72"/>
       <c r="I31" s="72"/>
       <c r="J31" s="100"/>
@@ -11236,13 +11236,13 @@
       <c r="B32" s="58">
         <v>4</v>
       </c>
-      <c r="C32" s="340"/>
+      <c r="C32" s="333"/>
       <c r="D32" s="343"/>
-      <c r="E32" s="345" t="s">
+      <c r="E32" s="319" t="s">
         <v>57</v>
       </c>
-      <c r="F32" s="346"/>
-      <c r="G32" s="347"/>
+      <c r="F32" s="320"/>
+      <c r="G32" s="321"/>
       <c r="H32" s="72"/>
       <c r="I32" s="72"/>
       <c r="J32" s="81" t="e">
@@ -11262,13 +11262,13 @@
       <c r="B33" s="58">
         <v>5</v>
       </c>
-      <c r="C33" s="340"/>
+      <c r="C33" s="333"/>
       <c r="D33" s="343"/>
-      <c r="E33" s="348" t="s">
+      <c r="E33" s="352" t="s">
         <v>58</v>
       </c>
-      <c r="F33" s="349"/>
-      <c r="G33" s="350"/>
+      <c r="F33" s="353"/>
+      <c r="G33" s="354"/>
       <c r="H33" s="72"/>
       <c r="I33" s="72"/>
       <c r="J33" s="81"/>
@@ -11281,13 +11281,13 @@
       <c r="B34" s="58">
         <v>6</v>
       </c>
-      <c r="C34" s="341"/>
-      <c r="D34" s="344"/>
-      <c r="E34" s="352" t="s">
+      <c r="C34" s="349"/>
+      <c r="D34" s="351"/>
+      <c r="E34" s="329" t="s">
         <v>170</v>
       </c>
-      <c r="F34" s="352"/>
-      <c r="G34" s="352"/>
+      <c r="F34" s="329"/>
+      <c r="G34" s="329"/>
       <c r="H34" s="72"/>
       <c r="I34" s="72"/>
       <c r="J34" s="81" t="e">
@@ -11303,15 +11303,15 @@
       <c r="B35" s="58">
         <v>7</v>
       </c>
-      <c r="C35" s="339" t="s">
+      <c r="C35" s="332" t="s">
         <v>171</v>
       </c>
-      <c r="D35" s="336" t="s">
+      <c r="D35" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E35" s="353"/>
-      <c r="F35" s="353"/>
-      <c r="G35" s="354"/>
+      <c r="E35" s="355"/>
+      <c r="F35" s="355"/>
+      <c r="G35" s="356"/>
       <c r="H35" s="97"/>
       <c r="I35" s="101">
         <f>I36+I37</f>
@@ -11327,15 +11327,15 @@
       <c r="B36" s="58">
         <v>8</v>
       </c>
-      <c r="C36" s="340"/>
+      <c r="C36" s="333"/>
       <c r="D36" s="342" t="s">
         <v>55</v>
       </c>
-      <c r="E36" s="355" t="s">
+      <c r="E36" s="336" t="s">
         <v>172</v>
       </c>
-      <c r="F36" s="356"/>
-      <c r="G36" s="357"/>
+      <c r="F36" s="337"/>
+      <c r="G36" s="338"/>
       <c r="H36" s="72"/>
       <c r="I36" s="72"/>
       <c r="J36" s="81" t="e">
@@ -11352,13 +11352,13 @@
       <c r="B37" s="58">
         <v>9</v>
       </c>
-      <c r="C37" s="341"/>
-      <c r="D37" s="351"/>
-      <c r="E37" s="355" t="s">
+      <c r="C37" s="349"/>
+      <c r="D37" s="350"/>
+      <c r="E37" s="336" t="s">
         <v>173</v>
       </c>
-      <c r="F37" s="356"/>
-      <c r="G37" s="357"/>
+      <c r="F37" s="337"/>
+      <c r="G37" s="338"/>
       <c r="H37" s="72"/>
       <c r="I37" s="72"/>
       <c r="J37" s="81" t="e">
@@ -11375,13 +11375,13 @@
       <c r="B38" s="58">
         <v>10</v>
       </c>
-      <c r="C38" s="336" t="s">
+      <c r="C38" s="323" t="s">
         <v>203</v>
       </c>
-      <c r="D38" s="337"/>
-      <c r="E38" s="337"/>
-      <c r="F38" s="337"/>
-      <c r="G38" s="338"/>
+      <c r="D38" s="324"/>
+      <c r="E38" s="324"/>
+      <c r="F38" s="324"/>
+      <c r="G38" s="325"/>
       <c r="H38" s="97"/>
       <c r="I38" s="97"/>
       <c r="J38" s="102"/>
@@ -11394,15 +11394,15 @@
       <c r="B39" s="58">
         <v>11</v>
       </c>
-      <c r="C39" s="339" t="s">
+      <c r="C39" s="332" t="s">
         <v>186</v>
       </c>
-      <c r="D39" s="336" t="s">
+      <c r="D39" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E39" s="337"/>
-      <c r="F39" s="337"/>
-      <c r="G39" s="338"/>
+      <c r="E39" s="324"/>
+      <c r="F39" s="324"/>
+      <c r="G39" s="325"/>
       <c r="H39" s="97"/>
       <c r="I39" s="97"/>
       <c r="J39" s="102"/>
@@ -11415,15 +11415,15 @@
       <c r="B40" s="58">
         <v>12</v>
       </c>
-      <c r="C40" s="340"/>
+      <c r="C40" s="333"/>
       <c r="D40" s="342" t="s">
         <v>55</v>
       </c>
-      <c r="E40" s="345" t="s">
+      <c r="E40" s="319" t="s">
         <v>128</v>
       </c>
-      <c r="F40" s="346"/>
-      <c r="G40" s="347"/>
+      <c r="F40" s="320"/>
+      <c r="G40" s="321"/>
       <c r="H40" s="72"/>
       <c r="I40" s="72"/>
       <c r="J40" s="81" t="e">
@@ -11439,13 +11439,13 @@
       <c r="B41" s="58">
         <v>13</v>
       </c>
-      <c r="C41" s="341"/>
-      <c r="D41" s="351"/>
-      <c r="E41" s="345" t="s">
+      <c r="C41" s="349"/>
+      <c r="D41" s="350"/>
+      <c r="E41" s="319" t="s">
         <v>129</v>
       </c>
-      <c r="F41" s="346"/>
-      <c r="G41" s="347"/>
+      <c r="F41" s="320"/>
+      <c r="G41" s="321"/>
       <c r="H41" s="72"/>
       <c r="I41" s="72"/>
       <c r="J41" s="81" t="e">
@@ -11461,15 +11461,15 @@
       <c r="B42" s="58">
         <v>14</v>
       </c>
-      <c r="C42" s="339" t="s">
+      <c r="C42" s="332" t="s">
         <v>204</v>
       </c>
-      <c r="D42" s="336" t="s">
+      <c r="D42" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E42" s="337"/>
-      <c r="F42" s="337"/>
-      <c r="G42" s="338"/>
+      <c r="E42" s="324"/>
+      <c r="F42" s="324"/>
+      <c r="G42" s="325"/>
       <c r="H42" s="97"/>
       <c r="I42" s="97"/>
       <c r="J42" s="102"/>
@@ -11482,15 +11482,15 @@
       <c r="B43" s="58">
         <v>15</v>
       </c>
-      <c r="C43" s="340"/>
+      <c r="C43" s="333"/>
       <c r="D43" s="342" t="s">
         <v>55</v>
       </c>
-      <c r="E43" s="345" t="s">
+      <c r="E43" s="319" t="s">
         <v>128</v>
       </c>
-      <c r="F43" s="346"/>
-      <c r="G43" s="347"/>
+      <c r="F43" s="320"/>
+      <c r="G43" s="321"/>
       <c r="H43" s="72"/>
       <c r="I43" s="72"/>
       <c r="J43" s="81" t="e">
@@ -11506,13 +11506,13 @@
       <c r="B44" s="58">
         <v>16</v>
       </c>
-      <c r="C44" s="341"/>
-      <c r="D44" s="351"/>
-      <c r="E44" s="345" t="s">
+      <c r="C44" s="349"/>
+      <c r="D44" s="350"/>
+      <c r="E44" s="319" t="s">
         <v>129</v>
       </c>
-      <c r="F44" s="346"/>
-      <c r="G44" s="347"/>
+      <c r="F44" s="320"/>
+      <c r="G44" s="321"/>
       <c r="H44" s="72"/>
       <c r="I44" s="72"/>
       <c r="J44" s="81" t="e">
@@ -11528,15 +11528,15 @@
       <c r="B45" s="58">
         <v>17</v>
       </c>
-      <c r="C45" s="339" t="s">
+      <c r="C45" s="332" t="s">
         <v>62</v>
       </c>
-      <c r="D45" s="336" t="s">
+      <c r="D45" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E45" s="337"/>
-      <c r="F45" s="337"/>
-      <c r="G45" s="338"/>
+      <c r="E45" s="324"/>
+      <c r="F45" s="324"/>
+      <c r="G45" s="325"/>
       <c r="H45" s="97"/>
       <c r="I45" s="97"/>
       <c r="J45" s="102"/>
@@ -11549,15 +11549,15 @@
       <c r="B46" s="58">
         <v>18</v>
       </c>
-      <c r="C46" s="340"/>
+      <c r="C46" s="333"/>
       <c r="D46" s="342" t="s">
         <v>55</v>
       </c>
-      <c r="E46" s="345" t="s">
+      <c r="E46" s="319" t="s">
         <v>63</v>
       </c>
-      <c r="F46" s="346"/>
-      <c r="G46" s="347"/>
+      <c r="F46" s="320"/>
+      <c r="G46" s="321"/>
       <c r="H46" s="72"/>
       <c r="I46" s="72"/>
       <c r="J46" s="81" t="e">
@@ -11573,13 +11573,13 @@
       <c r="B47" s="58">
         <v>19</v>
       </c>
-      <c r="C47" s="341"/>
-      <c r="D47" s="351"/>
-      <c r="E47" s="345" t="s">
+      <c r="C47" s="349"/>
+      <c r="D47" s="350"/>
+      <c r="E47" s="319" t="s">
         <v>64</v>
       </c>
-      <c r="F47" s="346"/>
-      <c r="G47" s="347"/>
+      <c r="F47" s="320"/>
+      <c r="G47" s="321"/>
       <c r="H47" s="72"/>
       <c r="I47" s="72"/>
       <c r="J47" s="81" t="e">
@@ -11595,15 +11595,15 @@
       <c r="B48" s="58">
         <v>20</v>
       </c>
-      <c r="C48" s="339" t="s">
+      <c r="C48" s="332" t="s">
         <v>205</v>
       </c>
-      <c r="D48" s="336" t="s">
+      <c r="D48" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E48" s="337"/>
-      <c r="F48" s="337"/>
-      <c r="G48" s="338"/>
+      <c r="E48" s="324"/>
+      <c r="F48" s="324"/>
+      <c r="G48" s="325"/>
       <c r="H48" s="97"/>
       <c r="I48" s="97"/>
       <c r="J48" s="102"/>
@@ -11616,15 +11616,15 @@
       <c r="B49" s="58">
         <v>21</v>
       </c>
-      <c r="C49" s="340"/>
+      <c r="C49" s="333"/>
       <c r="D49" s="103" t="s">
         <v>55</v>
       </c>
-      <c r="E49" s="358" t="s">
-        <v>44</v>
-      </c>
-      <c r="F49" s="359"/>
-      <c r="G49" s="359"/>
+      <c r="E49" s="334" t="s">
+        <v>44</v>
+      </c>
+      <c r="F49" s="335"/>
+      <c r="G49" s="335"/>
       <c r="H49" s="104"/>
       <c r="I49" s="104"/>
       <c r="J49" s="81"/>
@@ -11643,11 +11643,11 @@
       <c r="D50" s="106" t="s">
         <v>44</v>
       </c>
-      <c r="E50" s="345" t="s">
+      <c r="E50" s="319" t="s">
         <v>206</v>
       </c>
-      <c r="F50" s="346"/>
-      <c r="G50" s="347"/>
+      <c r="F50" s="320"/>
+      <c r="G50" s="321"/>
       <c r="H50" s="72"/>
       <c r="I50" s="72"/>
       <c r="J50" s="81" t="e">
@@ -11670,11 +11670,11 @@
       <c r="D51" s="106" t="s">
         <v>44</v>
       </c>
-      <c r="E51" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="F51" s="346"/>
-      <c r="G51" s="347"/>
+      <c r="E51" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="F51" s="320"/>
+      <c r="G51" s="321"/>
       <c r="H51" s="72"/>
       <c r="I51" s="72"/>
       <c r="J51" s="81"/>
@@ -11688,15 +11688,15 @@
       <c r="B52" s="58">
         <v>24</v>
       </c>
-      <c r="C52" s="339" t="s">
+      <c r="C52" s="332" t="s">
         <v>102</v>
       </c>
-      <c r="D52" s="336" t="s">
+      <c r="D52" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E52" s="337"/>
-      <c r="F52" s="337"/>
-      <c r="G52" s="338"/>
+      <c r="E52" s="324"/>
+      <c r="F52" s="324"/>
+      <c r="G52" s="325"/>
       <c r="H52" s="97"/>
       <c r="I52" s="97"/>
       <c r="J52" s="102"/>
@@ -11709,15 +11709,15 @@
       <c r="B53" s="58">
         <v>25</v>
       </c>
-      <c r="C53" s="340"/>
+      <c r="C53" s="333"/>
       <c r="D53" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E53" s="345" t="s">
+      <c r="E53" s="319" t="s">
         <v>13</v>
       </c>
-      <c r="F53" s="346"/>
-      <c r="G53" s="347"/>
+      <c r="F53" s="320"/>
+      <c r="G53" s="321"/>
       <c r="H53" s="72"/>
       <c r="I53" s="72"/>
       <c r="J53" s="81"/>
@@ -11736,11 +11736,11 @@
       <c r="D54" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E54" s="345" t="s">
+      <c r="E54" s="319" t="s">
         <v>207</v>
       </c>
-      <c r="F54" s="346"/>
-      <c r="G54" s="347"/>
+      <c r="F54" s="320"/>
+      <c r="G54" s="321"/>
       <c r="H54" s="72"/>
       <c r="I54" s="72"/>
       <c r="J54" s="81" t="e">
@@ -11757,15 +11757,15 @@
       <c r="B55" s="58">
         <v>30</v>
       </c>
-      <c r="C55" s="339" t="s">
+      <c r="C55" s="332" t="s">
         <v>16</v>
       </c>
-      <c r="D55" s="336" t="s">
+      <c r="D55" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E55" s="337"/>
-      <c r="F55" s="337"/>
-      <c r="G55" s="338"/>
+      <c r="E55" s="324"/>
+      <c r="F55" s="324"/>
+      <c r="G55" s="325"/>
       <c r="H55" s="97"/>
       <c r="I55" s="97"/>
       <c r="J55" s="102"/>
@@ -11778,15 +11778,15 @@
       <c r="B56" s="58">
         <v>31</v>
       </c>
-      <c r="C56" s="340"/>
+      <c r="C56" s="333"/>
       <c r="D56" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E56" s="345" t="s">
+      <c r="E56" s="319" t="s">
         <v>146</v>
       </c>
-      <c r="F56" s="346"/>
-      <c r="G56" s="347"/>
+      <c r="F56" s="320"/>
+      <c r="G56" s="321"/>
       <c r="H56" s="72"/>
       <c r="I56" s="72"/>
       <c r="J56" s="81"/>
@@ -11799,15 +11799,15 @@
       <c r="B57" s="58">
         <v>32</v>
       </c>
-      <c r="C57" s="340"/>
+      <c r="C57" s="333"/>
       <c r="D57" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E57" s="345" t="s">
+      <c r="E57" s="319" t="s">
         <v>147</v>
       </c>
-      <c r="F57" s="346"/>
-      <c r="G57" s="347"/>
+      <c r="F57" s="320"/>
+      <c r="G57" s="321"/>
       <c r="H57" s="72"/>
       <c r="I57" s="72"/>
       <c r="J57" s="81"/>
@@ -11826,11 +11826,11 @@
       <c r="D58" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E58" s="345" t="s">
+      <c r="E58" s="319" t="s">
         <v>148</v>
       </c>
-      <c r="F58" s="346"/>
-      <c r="G58" s="347"/>
+      <c r="F58" s="320"/>
+      <c r="G58" s="321"/>
       <c r="H58" s="72"/>
       <c r="I58" s="72"/>
       <c r="J58" s="81"/>
@@ -11849,11 +11849,11 @@
       <c r="D59" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E59" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="F59" s="346"/>
-      <c r="G59" s="347"/>
+      <c r="E59" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="F59" s="320"/>
+      <c r="G59" s="321"/>
       <c r="H59" s="72"/>
       <c r="I59" s="72"/>
       <c r="J59" s="81"/>
@@ -11867,15 +11867,15 @@
       <c r="B60" s="58">
         <v>35</v>
       </c>
-      <c r="C60" s="339" t="s">
+      <c r="C60" s="332" t="s">
         <v>190</v>
       </c>
-      <c r="D60" s="336" t="s">
+      <c r="D60" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E60" s="337"/>
-      <c r="F60" s="337"/>
-      <c r="G60" s="338"/>
+      <c r="E60" s="324"/>
+      <c r="F60" s="324"/>
+      <c r="G60" s="325"/>
       <c r="H60" s="97"/>
       <c r="I60" s="97"/>
       <c r="J60" s="102"/>
@@ -11888,15 +11888,15 @@
       <c r="B61" s="58">
         <v>36</v>
       </c>
-      <c r="C61" s="340"/>
+      <c r="C61" s="333"/>
       <c r="D61" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E61" s="345" t="s">
+      <c r="E61" s="319" t="s">
         <v>128</v>
       </c>
-      <c r="F61" s="346"/>
-      <c r="G61" s="347"/>
+      <c r="F61" s="320"/>
+      <c r="G61" s="321"/>
       <c r="H61" s="72"/>
       <c r="I61" s="72"/>
       <c r="J61" s="81"/>
@@ -11909,15 +11909,15 @@
       <c r="B62" s="58">
         <v>37</v>
       </c>
-      <c r="C62" s="340"/>
+      <c r="C62" s="333"/>
       <c r="D62" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E62" s="345" t="s">
+      <c r="E62" s="319" t="s">
         <v>154</v>
       </c>
-      <c r="F62" s="346"/>
-      <c r="G62" s="347"/>
+      <c r="F62" s="320"/>
+      <c r="G62" s="321"/>
       <c r="H62" s="72"/>
       <c r="I62" s="72"/>
       <c r="J62" s="81"/>
@@ -11936,11 +11936,11 @@
       <c r="D63" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E63" s="345" t="s">
+      <c r="E63" s="319" t="s">
         <v>208</v>
       </c>
-      <c r="F63" s="346"/>
-      <c r="G63" s="347"/>
+      <c r="F63" s="320"/>
+      <c r="G63" s="321"/>
       <c r="H63" s="72"/>
       <c r="I63" s="72"/>
       <c r="J63" s="81"/>
@@ -11959,11 +11959,11 @@
       <c r="D64" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E64" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="F64" s="346"/>
-      <c r="G64" s="347"/>
+      <c r="E64" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="F64" s="320"/>
+      <c r="G64" s="321"/>
       <c r="H64" s="72"/>
       <c r="I64" s="72"/>
       <c r="J64" s="81"/>
@@ -11977,15 +11977,15 @@
       <c r="B65" s="58">
         <v>40</v>
       </c>
-      <c r="C65" s="339" t="s">
+      <c r="C65" s="332" t="s">
         <v>14</v>
       </c>
-      <c r="D65" s="336" t="s">
+      <c r="D65" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E65" s="337"/>
-      <c r="F65" s="337"/>
-      <c r="G65" s="338"/>
+      <c r="E65" s="324"/>
+      <c r="F65" s="324"/>
+      <c r="G65" s="325"/>
       <c r="H65" s="97"/>
       <c r="I65" s="97"/>
       <c r="J65" s="102"/>
@@ -11998,17 +11998,17 @@
       <c r="B66" s="58">
         <v>41</v>
       </c>
-      <c r="C66" s="340"/>
+      <c r="C66" s="333"/>
       <c r="D66" s="66" t="s">
         <v>55</v>
       </c>
       <c r="E66" s="103" t="s">
         <v>209</v>
       </c>
-      <c r="F66" s="336" t="s">
+      <c r="F66" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="G66" s="338"/>
+      <c r="G66" s="325"/>
       <c r="H66" s="97"/>
       <c r="I66" s="97"/>
       <c r="J66" s="102"/>
@@ -12021,7 +12021,7 @@
       <c r="B67" s="58">
         <v>42</v>
       </c>
-      <c r="C67" s="340"/>
+      <c r="C67" s="333"/>
       <c r="D67" s="67" t="s">
         <v>44</v>
       </c>
@@ -12114,10 +12114,10 @@
       <c r="E70" s="103" t="s">
         <v>210</v>
       </c>
-      <c r="F70" s="336" t="s">
+      <c r="F70" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="G70" s="338"/>
+      <c r="G70" s="325"/>
       <c r="H70" s="97"/>
       <c r="I70" s="97"/>
       <c r="J70" s="102"/>
@@ -12286,10 +12286,10 @@
       <c r="E76" s="103" t="s">
         <v>214</v>
       </c>
-      <c r="F76" s="336" t="s">
+      <c r="F76" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="G76" s="338"/>
+      <c r="G76" s="325"/>
       <c r="H76" s="97"/>
       <c r="I76" s="97"/>
       <c r="J76" s="102"/>
@@ -12391,13 +12391,13 @@
       <c r="D80" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E80" s="360" t="s">
+      <c r="E80" s="344" t="s">
         <v>216</v>
       </c>
-      <c r="F80" s="336" t="s">
+      <c r="F80" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="G80" s="338"/>
+      <c r="G80" s="325"/>
       <c r="H80" s="97"/>
       <c r="I80" s="97"/>
       <c r="J80" s="102"/>
@@ -12417,15 +12417,15 @@
       <c r="D81" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E81" s="361"/>
+      <c r="E81" s="345"/>
       <c r="F81" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="G81" s="362" t="s">
+      <c r="G81" s="346" t="s">
         <v>136</v>
       </c>
-      <c r="H81" s="363"/>
-      <c r="I81" s="364"/>
+      <c r="H81" s="347"/>
+      <c r="I81" s="348"/>
       <c r="J81" s="81" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -12504,13 +12504,13 @@
       <c r="D84" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E84" s="360" t="s">
-        <v>44</v>
-      </c>
-      <c r="F84" s="336" t="s">
+      <c r="E84" s="344" t="s">
+        <v>44</v>
+      </c>
+      <c r="F84" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="G84" s="338"/>
+      <c r="G84" s="325"/>
       <c r="H84" s="97"/>
       <c r="I84" s="97"/>
       <c r="J84" s="102"/>
@@ -12530,7 +12530,7 @@
       <c r="D85" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E85" s="361"/>
+      <c r="E85" s="345"/>
       <c r="F85" s="66" t="s">
         <v>55</v>
       </c>
@@ -12579,15 +12579,15 @@
       <c r="B87" s="58">
         <v>62</v>
       </c>
-      <c r="C87" s="339" t="s">
+      <c r="C87" s="332" t="s">
         <v>144</v>
       </c>
-      <c r="D87" s="336" t="s">
+      <c r="D87" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E87" s="337"/>
-      <c r="F87" s="337"/>
-      <c r="G87" s="338"/>
+      <c r="E87" s="324"/>
+      <c r="F87" s="324"/>
+      <c r="G87" s="325"/>
       <c r="H87" s="97"/>
       <c r="I87" s="110"/>
       <c r="J87" s="102"/>
@@ -12600,15 +12600,15 @@
       <c r="B88" s="58">
         <v>63</v>
       </c>
-      <c r="C88" s="340"/>
+      <c r="C88" s="333"/>
       <c r="D88" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E88" s="358" t="s">
-        <v>44</v>
-      </c>
-      <c r="F88" s="359"/>
-      <c r="G88" s="359"/>
+      <c r="E88" s="334" t="s">
+        <v>44</v>
+      </c>
+      <c r="F88" s="335"/>
+      <c r="G88" s="335"/>
       <c r="H88" s="104"/>
       <c r="I88" s="104"/>
       <c r="J88" s="81" t="e">
@@ -12630,11 +12630,11 @@
       <c r="D89" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E89" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="F89" s="346"/>
-      <c r="G89" s="347"/>
+      <c r="E89" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="F89" s="320"/>
+      <c r="G89" s="321"/>
       <c r="H89" s="72"/>
       <c r="I89" s="109"/>
       <c r="J89" s="81"/>
@@ -12654,11 +12654,11 @@
       <c r="D90" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E90" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="F90" s="346"/>
-      <c r="G90" s="347"/>
+      <c r="E90" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="F90" s="320"/>
+      <c r="G90" s="321"/>
       <c r="H90" s="72"/>
       <c r="I90" s="109"/>
       <c r="J90" s="81"/>
@@ -12672,15 +12672,15 @@
       <c r="B91" s="58">
         <v>66</v>
       </c>
-      <c r="C91" s="339" t="s">
+      <c r="C91" s="332" t="s">
         <v>189</v>
       </c>
-      <c r="D91" s="336" t="s">
+      <c r="D91" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E91" s="337"/>
-      <c r="F91" s="337"/>
-      <c r="G91" s="338"/>
+      <c r="E91" s="324"/>
+      <c r="F91" s="324"/>
+      <c r="G91" s="325"/>
       <c r="H91" s="97"/>
       <c r="I91" s="110"/>
       <c r="J91" s="102"/>
@@ -12693,15 +12693,15 @@
       <c r="B92" s="58">
         <v>67</v>
       </c>
-      <c r="C92" s="340"/>
+      <c r="C92" s="333"/>
       <c r="D92" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E92" s="358" t="s">
-        <v>44</v>
-      </c>
-      <c r="F92" s="359"/>
-      <c r="G92" s="359"/>
+      <c r="E92" s="334" t="s">
+        <v>44</v>
+      </c>
+      <c r="F92" s="335"/>
+      <c r="G92" s="335"/>
       <c r="H92" s="104"/>
       <c r="I92" s="104"/>
       <c r="J92" s="81"/>
@@ -12720,11 +12720,11 @@
       <c r="D93" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E93" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="F93" s="346"/>
-      <c r="G93" s="347"/>
+      <c r="E93" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="F93" s="320"/>
+      <c r="G93" s="321"/>
       <c r="H93" s="72"/>
       <c r="I93" s="109"/>
       <c r="J93" s="81"/>
@@ -12744,11 +12744,11 @@
       <c r="D94" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E94" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="F94" s="346"/>
-      <c r="G94" s="347"/>
+      <c r="E94" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="F94" s="320"/>
+      <c r="G94" s="321"/>
       <c r="H94" s="72"/>
       <c r="I94" s="109"/>
       <c r="J94" s="81"/>
@@ -12762,15 +12762,15 @@
       <c r="B95" s="58">
         <v>70</v>
       </c>
-      <c r="C95" s="339" t="s">
+      <c r="C95" s="332" t="s">
         <v>137</v>
       </c>
-      <c r="D95" s="336" t="s">
+      <c r="D95" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E95" s="337"/>
-      <c r="F95" s="337"/>
-      <c r="G95" s="338"/>
+      <c r="E95" s="324"/>
+      <c r="F95" s="324"/>
+      <c r="G95" s="325"/>
       <c r="H95" s="97"/>
       <c r="I95" s="110"/>
       <c r="J95" s="102"/>
@@ -12783,15 +12783,15 @@
       <c r="B96" s="58">
         <v>71</v>
       </c>
-      <c r="C96" s="340"/>
+      <c r="C96" s="333"/>
       <c r="D96" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E96" s="358" t="s">
-        <v>44</v>
-      </c>
-      <c r="F96" s="359"/>
-      <c r="G96" s="359"/>
+      <c r="E96" s="334" t="s">
+        <v>44</v>
+      </c>
+      <c r="F96" s="335"/>
+      <c r="G96" s="335"/>
       <c r="H96" s="104"/>
       <c r="I96" s="104"/>
       <c r="J96" s="81"/>
@@ -12810,11 +12810,11 @@
       <c r="D97" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E97" s="345" t="s">
+      <c r="E97" s="319" t="s">
         <v>217</v>
       </c>
-      <c r="F97" s="346"/>
-      <c r="G97" s="347"/>
+      <c r="F97" s="320"/>
+      <c r="G97" s="321"/>
       <c r="H97" s="72"/>
       <c r="I97" s="109"/>
       <c r="J97" s="81" t="e">
@@ -12829,11 +12829,11 @@
       <c r="B98" s="58"/>
       <c r="C98" s="77"/>
       <c r="D98" s="70"/>
-      <c r="E98" s="345" t="s">
+      <c r="E98" s="319" t="s">
         <v>218</v>
       </c>
-      <c r="F98" s="346"/>
-      <c r="G98" s="347"/>
+      <c r="F98" s="320"/>
+      <c r="G98" s="321"/>
       <c r="H98" s="72"/>
       <c r="I98" s="109"/>
       <c r="J98" s="81"/>
@@ -12845,9 +12845,9 @@
       <c r="B99" s="58"/>
       <c r="C99" s="77"/>
       <c r="D99" s="70"/>
-      <c r="E99" s="345"/>
-      <c r="F99" s="346"/>
-      <c r="G99" s="347"/>
+      <c r="E99" s="319"/>
+      <c r="F99" s="320"/>
+      <c r="G99" s="321"/>
       <c r="H99" s="72"/>
       <c r="I99" s="109"/>
       <c r="J99" s="81"/>
@@ -12867,11 +12867,11 @@
       <c r="D100" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E100" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="F100" s="346"/>
-      <c r="G100" s="347"/>
+      <c r="E100" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="F100" s="320"/>
+      <c r="G100" s="321"/>
       <c r="H100" s="72"/>
       <c r="I100" s="109"/>
       <c r="J100" s="81"/>
@@ -12885,15 +12885,15 @@
       <c r="B101" s="58">
         <v>75</v>
       </c>
-      <c r="C101" s="339" t="s">
+      <c r="C101" s="332" t="s">
         <v>17</v>
       </c>
-      <c r="D101" s="336" t="s">
+      <c r="D101" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E101" s="337"/>
-      <c r="F101" s="337"/>
-      <c r="G101" s="338"/>
+      <c r="E101" s="324"/>
+      <c r="F101" s="324"/>
+      <c r="G101" s="325"/>
       <c r="H101" s="97"/>
       <c r="I101" s="111">
         <f>I102+I103+I104</f>
@@ -12909,15 +12909,15 @@
       <c r="B102" s="58">
         <v>76</v>
       </c>
-      <c r="C102" s="340"/>
+      <c r="C102" s="333"/>
       <c r="D102" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E102" s="355" t="s">
+      <c r="E102" s="336" t="s">
         <v>219</v>
       </c>
-      <c r="F102" s="356"/>
-      <c r="G102" s="357"/>
+      <c r="F102" s="337"/>
+      <c r="G102" s="338"/>
       <c r="H102" s="72"/>
       <c r="I102" s="109"/>
       <c r="J102" s="81">
@@ -12933,15 +12933,15 @@
       <c r="B103" s="58">
         <v>77</v>
       </c>
-      <c r="C103" s="340"/>
+      <c r="C103" s="333"/>
       <c r="D103" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E103" s="355" t="s">
+      <c r="E103" s="336" t="s">
         <v>220</v>
       </c>
-      <c r="F103" s="356"/>
-      <c r="G103" s="357"/>
+      <c r="F103" s="337"/>
+      <c r="G103" s="338"/>
       <c r="H103" s="72"/>
       <c r="I103" s="72"/>
       <c r="J103" s="81">
@@ -12963,11 +12963,11 @@
       <c r="D104" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E104" s="355" t="s">
+      <c r="E104" s="336" t="s">
         <v>221</v>
       </c>
-      <c r="F104" s="356"/>
-      <c r="G104" s="357"/>
+      <c r="F104" s="337"/>
+      <c r="G104" s="338"/>
       <c r="H104" s="72"/>
       <c r="I104" s="72"/>
       <c r="J104" s="81">
@@ -12983,13 +12983,13 @@
       <c r="B105" s="58">
         <v>83</v>
       </c>
-      <c r="C105" s="336" t="s">
+      <c r="C105" s="323" t="s">
         <v>7</v>
       </c>
-      <c r="D105" s="337"/>
-      <c r="E105" s="337"/>
-      <c r="F105" s="337"/>
-      <c r="G105" s="338"/>
+      <c r="D105" s="324"/>
+      <c r="E105" s="324"/>
+      <c r="F105" s="324"/>
+      <c r="G105" s="325"/>
       <c r="H105" s="97"/>
       <c r="I105" s="97"/>
       <c r="J105" s="102" t="e">
@@ -13005,13 +13005,13 @@
       <c r="B106" s="58">
         <v>84</v>
       </c>
-      <c r="C106" s="336" t="s">
+      <c r="C106" s="323" t="s">
         <v>222</v>
       </c>
-      <c r="D106" s="337"/>
-      <c r="E106" s="337"/>
-      <c r="F106" s="337"/>
-      <c r="G106" s="338"/>
+      <c r="D106" s="324"/>
+      <c r="E106" s="324"/>
+      <c r="F106" s="324"/>
+      <c r="G106" s="325"/>
       <c r="H106" s="97"/>
       <c r="I106" s="101"/>
       <c r="J106" s="102" t="e">
@@ -13027,15 +13027,15 @@
       <c r="B107" s="58">
         <v>85</v>
       </c>
-      <c r="C107" s="339" t="s">
+      <c r="C107" s="332" t="s">
         <v>223</v>
       </c>
-      <c r="D107" s="336" t="s">
+      <c r="D107" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E107" s="337"/>
-      <c r="F107" s="337"/>
-      <c r="G107" s="338"/>
+      <c r="E107" s="324"/>
+      <c r="F107" s="324"/>
+      <c r="G107" s="325"/>
       <c r="H107" s="97"/>
       <c r="I107" s="97"/>
       <c r="J107" s="102"/>
@@ -13048,15 +13048,15 @@
       <c r="B108" s="58">
         <v>86</v>
       </c>
-      <c r="C108" s="340"/>
+      <c r="C108" s="333"/>
       <c r="D108" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E108" s="355" t="s">
+      <c r="E108" s="336" t="s">
         <v>224</v>
       </c>
-      <c r="F108" s="356"/>
-      <c r="G108" s="357"/>
+      <c r="F108" s="337"/>
+      <c r="G108" s="338"/>
       <c r="H108" s="72"/>
       <c r="I108" s="63"/>
       <c r="J108" s="81" t="e">
@@ -13078,11 +13078,11 @@
       <c r="D109" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E109" s="345" t="s">
+      <c r="E109" s="319" t="s">
         <v>225</v>
       </c>
-      <c r="F109" s="346"/>
-      <c r="G109" s="347"/>
+      <c r="F109" s="320"/>
+      <c r="G109" s="321"/>
       <c r="H109" s="72"/>
       <c r="I109" s="63"/>
       <c r="J109" s="81"/>
@@ -13102,11 +13102,11 @@
       <c r="D110" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E110" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="F110" s="346"/>
-      <c r="G110" s="347"/>
+      <c r="E110" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="F110" s="320"/>
+      <c r="G110" s="321"/>
       <c r="H110" s="72"/>
       <c r="I110" s="72"/>
       <c r="J110" s="81"/>
@@ -13120,15 +13120,15 @@
       <c r="B111" s="58">
         <v>89</v>
       </c>
-      <c r="C111" s="339" t="s">
+      <c r="C111" s="332" t="s">
         <v>192</v>
       </c>
-      <c r="D111" s="336" t="s">
+      <c r="D111" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E111" s="337"/>
-      <c r="F111" s="337"/>
-      <c r="G111" s="338"/>
+      <c r="E111" s="324"/>
+      <c r="F111" s="324"/>
+      <c r="G111" s="325"/>
       <c r="H111" s="97"/>
       <c r="I111" s="97"/>
       <c r="J111" s="102"/>
@@ -13141,15 +13141,15 @@
       <c r="B112" s="58">
         <v>90</v>
       </c>
-      <c r="C112" s="340"/>
+      <c r="C112" s="333"/>
       <c r="D112" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E112" s="355" t="s">
+      <c r="E112" s="336" t="s">
         <v>226</v>
       </c>
-      <c r="F112" s="356"/>
-      <c r="G112" s="357"/>
+      <c r="F112" s="337"/>
+      <c r="G112" s="338"/>
       <c r="H112" s="72"/>
       <c r="I112" s="72"/>
       <c r="J112" s="81"/>
@@ -13168,11 +13168,11 @@
       <c r="D113" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E113" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="F113" s="346"/>
-      <c r="G113" s="347"/>
+      <c r="E113" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="F113" s="320"/>
+      <c r="G113" s="321"/>
       <c r="H113" s="72"/>
       <c r="I113" s="72"/>
       <c r="J113" s="81"/>
@@ -13185,15 +13185,15 @@
       <c r="B114" s="58">
         <v>92</v>
       </c>
-      <c r="C114" s="339" t="s">
+      <c r="C114" s="332" t="s">
         <v>191</v>
       </c>
-      <c r="D114" s="336" t="s">
+      <c r="D114" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E114" s="337"/>
-      <c r="F114" s="337"/>
-      <c r="G114" s="338"/>
+      <c r="E114" s="324"/>
+      <c r="F114" s="324"/>
+      <c r="G114" s="325"/>
       <c r="H114" s="97"/>
       <c r="I114" s="97"/>
       <c r="J114" s="102"/>
@@ -13206,15 +13206,15 @@
       <c r="B115" s="58">
         <v>93</v>
       </c>
-      <c r="C115" s="340"/>
+      <c r="C115" s="333"/>
       <c r="D115" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E115" s="358" t="s">
-        <v>44</v>
-      </c>
-      <c r="F115" s="359"/>
-      <c r="G115" s="359"/>
+      <c r="E115" s="334" t="s">
+        <v>44</v>
+      </c>
+      <c r="F115" s="335"/>
+      <c r="G115" s="335"/>
       <c r="H115" s="104"/>
       <c r="I115" s="104"/>
       <c r="J115" s="112"/>
@@ -13233,11 +13233,11 @@
       <c r="D116" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E116" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="F116" s="346"/>
-      <c r="G116" s="347"/>
+      <c r="E116" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="F116" s="320"/>
+      <c r="G116" s="321"/>
       <c r="H116" s="72"/>
       <c r="I116" s="63"/>
       <c r="J116" s="81"/>
@@ -13257,11 +13257,11 @@
       <c r="D117" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E117" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="F117" s="346"/>
-      <c r="G117" s="347"/>
+      <c r="E117" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="F117" s="320"/>
+      <c r="G117" s="321"/>
       <c r="H117" s="72"/>
       <c r="I117" s="72"/>
       <c r="J117" s="81"/>
@@ -13275,15 +13275,15 @@
       <c r="B118" s="58">
         <v>96</v>
       </c>
-      <c r="C118" s="339" t="s">
+      <c r="C118" s="332" t="s">
         <v>149</v>
       </c>
-      <c r="D118" s="336" t="s">
+      <c r="D118" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E118" s="337"/>
-      <c r="F118" s="337"/>
-      <c r="G118" s="338"/>
+      <c r="E118" s="324"/>
+      <c r="F118" s="324"/>
+      <c r="G118" s="325"/>
       <c r="H118" s="97"/>
       <c r="I118" s="97"/>
       <c r="J118" s="102"/>
@@ -13296,15 +13296,15 @@
       <c r="B119" s="58">
         <v>97</v>
       </c>
-      <c r="C119" s="340"/>
+      <c r="C119" s="333"/>
       <c r="D119" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E119" s="355" t="s">
+      <c r="E119" s="336" t="s">
         <v>227</v>
       </c>
-      <c r="F119" s="356"/>
-      <c r="G119" s="357"/>
+      <c r="F119" s="337"/>
+      <c r="G119" s="338"/>
       <c r="H119" s="72"/>
       <c r="I119" s="72"/>
       <c r="J119" s="81"/>
@@ -13323,11 +13323,11 @@
       <c r="D120" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E120" s="355" t="s">
+      <c r="E120" s="336" t="s">
         <v>228</v>
       </c>
-      <c r="F120" s="356"/>
-      <c r="G120" s="357"/>
+      <c r="F120" s="337"/>
+      <c r="G120" s="338"/>
       <c r="H120" s="72"/>
       <c r="I120" s="72"/>
       <c r="J120" s="81"/>
@@ -13346,11 +13346,11 @@
       <c r="D121" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E121" s="355" t="s">
+      <c r="E121" s="336" t="s">
         <v>229</v>
       </c>
-      <c r="F121" s="356"/>
-      <c r="G121" s="357"/>
+      <c r="F121" s="337"/>
+      <c r="G121" s="338"/>
       <c r="H121" s="72"/>
       <c r="I121" s="72"/>
       <c r="J121" s="81"/>
@@ -13369,11 +13369,11 @@
       <c r="D122" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E122" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="F122" s="346"/>
-      <c r="G122" s="347"/>
+      <c r="E122" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="F122" s="320"/>
+      <c r="G122" s="321"/>
       <c r="H122" s="72"/>
       <c r="I122" s="72"/>
       <c r="J122" s="81"/>
@@ -13387,15 +13387,15 @@
       <c r="B123" s="58">
         <v>101</v>
       </c>
-      <c r="C123" s="339" t="s">
+      <c r="C123" s="332" t="s">
         <v>230</v>
       </c>
-      <c r="D123" s="336" t="s">
+      <c r="D123" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E123" s="337"/>
-      <c r="F123" s="337"/>
-      <c r="G123" s="338"/>
+      <c r="E123" s="324"/>
+      <c r="F123" s="324"/>
+      <c r="G123" s="325"/>
       <c r="H123" s="97"/>
       <c r="I123" s="97"/>
       <c r="J123" s="102"/>
@@ -13408,17 +13408,17 @@
       <c r="B124" s="58">
         <v>102</v>
       </c>
-      <c r="C124" s="340"/>
+      <c r="C124" s="333"/>
       <c r="D124" s="66" t="s">
         <v>55</v>
       </c>
       <c r="E124" s="342" t="s">
         <v>231</v>
       </c>
-      <c r="F124" s="336" t="s">
+      <c r="F124" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="G124" s="338"/>
+      <c r="G124" s="325"/>
       <c r="H124" s="97"/>
       <c r="I124" s="97"/>
       <c r="J124" s="102"/>
@@ -13431,7 +13431,7 @@
       <c r="B125" s="58">
         <v>103</v>
       </c>
-      <c r="C125" s="340"/>
+      <c r="C125" s="333"/>
       <c r="D125" s="67" t="s">
         <v>44</v>
       </c>
@@ -13454,7 +13454,7 @@
       <c r="B126" s="58">
         <v>104</v>
       </c>
-      <c r="C126" s="340"/>
+      <c r="C126" s="333"/>
       <c r="D126" s="67" t="s">
         <v>44</v>
       </c>
@@ -13540,11 +13540,11 @@
       <c r="D129" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E129" s="355" t="s">
+      <c r="E129" s="336" t="s">
         <v>234</v>
       </c>
-      <c r="F129" s="356"/>
-      <c r="G129" s="357"/>
+      <c r="F129" s="337"/>
+      <c r="G129" s="338"/>
       <c r="H129" s="72"/>
       <c r="I129" s="72"/>
       <c r="J129" s="81"/>
@@ -13563,11 +13563,11 @@
       <c r="D130" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E130" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="F130" s="346"/>
-      <c r="G130" s="347"/>
+      <c r="E130" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="F130" s="320"/>
+      <c r="G130" s="321"/>
       <c r="H130" s="72"/>
       <c r="I130" s="72"/>
       <c r="J130" s="81"/>
@@ -13581,15 +13581,15 @@
       <c r="B131" s="58">
         <v>109</v>
       </c>
-      <c r="C131" s="339" t="s">
+      <c r="C131" s="332" t="s">
         <v>175</v>
       </c>
-      <c r="D131" s="336" t="s">
+      <c r="D131" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E131" s="337"/>
-      <c r="F131" s="337"/>
-      <c r="G131" s="338"/>
+      <c r="E131" s="324"/>
+      <c r="F131" s="324"/>
+      <c r="G131" s="325"/>
       <c r="H131" s="97"/>
       <c r="I131" s="101">
         <f>SUM(I132:I136)</f>
@@ -13605,15 +13605,15 @@
       <c r="B132" s="58">
         <v>110</v>
       </c>
-      <c r="C132" s="340"/>
+      <c r="C132" s="333"/>
       <c r="D132" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E132" s="355" t="s">
+      <c r="E132" s="336" t="s">
         <v>91</v>
       </c>
-      <c r="F132" s="356"/>
-      <c r="G132" s="357"/>
+      <c r="F132" s="337"/>
+      <c r="G132" s="338"/>
       <c r="H132" s="72"/>
       <c r="I132" s="72"/>
       <c r="J132" s="81" t="e">
@@ -13629,15 +13629,15 @@
       <c r="B133" s="58">
         <v>111</v>
       </c>
-      <c r="C133" s="340"/>
+      <c r="C133" s="333"/>
       <c r="D133" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E133" s="355" t="s">
+      <c r="E133" s="336" t="s">
         <v>235</v>
       </c>
-      <c r="F133" s="356"/>
-      <c r="G133" s="357"/>
+      <c r="F133" s="337"/>
+      <c r="G133" s="338"/>
       <c r="H133" s="72"/>
       <c r="I133" s="72"/>
       <c r="J133" s="81" t="e">
@@ -13659,11 +13659,11 @@
       <c r="D134" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E134" s="355" t="s">
+      <c r="E134" s="336" t="s">
         <v>11</v>
       </c>
-      <c r="F134" s="356"/>
-      <c r="G134" s="357"/>
+      <c r="F134" s="337"/>
+      <c r="G134" s="338"/>
       <c r="H134" s="72"/>
       <c r="I134" s="72"/>
       <c r="J134" s="81" t="e">
@@ -13685,11 +13685,11 @@
       <c r="D135" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E135" s="355" t="s">
+      <c r="E135" s="336" t="s">
         <v>9</v>
       </c>
-      <c r="F135" s="356"/>
-      <c r="G135" s="357"/>
+      <c r="F135" s="337"/>
+      <c r="G135" s="338"/>
       <c r="H135" s="72"/>
       <c r="I135" s="72"/>
       <c r="J135" s="81" t="e">
@@ -13711,11 +13711,11 @@
       <c r="D136" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="E136" s="352" t="s">
+      <c r="E136" s="329" t="s">
         <v>236</v>
       </c>
-      <c r="F136" s="352"/>
-      <c r="G136" s="352"/>
+      <c r="F136" s="329"/>
+      <c r="G136" s="329"/>
       <c r="H136" s="72"/>
       <c r="I136" s="72"/>
       <c r="J136" s="81" t="e">
@@ -13738,11 +13738,11 @@
       <c r="D137" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E137" s="365" t="s">
-        <v>44</v>
-      </c>
-      <c r="F137" s="366"/>
-      <c r="G137" s="367"/>
+      <c r="E137" s="339" t="s">
+        <v>44</v>
+      </c>
+      <c r="F137" s="340"/>
+      <c r="G137" s="341"/>
       <c r="H137" s="115"/>
       <c r="I137" s="115"/>
       <c r="J137" s="116"/>
@@ -13756,15 +13756,15 @@
       <c r="B138" s="58">
         <v>118</v>
       </c>
-      <c r="C138" s="339" t="s">
+      <c r="C138" s="332" t="s">
         <v>237</v>
       </c>
-      <c r="D138" s="336" t="s">
+      <c r="D138" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E138" s="337"/>
-      <c r="F138" s="337"/>
-      <c r="G138" s="338"/>
+      <c r="E138" s="324"/>
+      <c r="F138" s="324"/>
+      <c r="G138" s="325"/>
       <c r="H138" s="97"/>
       <c r="I138" s="117"/>
       <c r="J138" s="118"/>
@@ -13777,15 +13777,15 @@
       <c r="B139" s="58">
         <v>119</v>
       </c>
-      <c r="C139" s="340"/>
+      <c r="C139" s="333"/>
       <c r="D139" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E139" s="355" t="s">
+      <c r="E139" s="336" t="s">
         <v>19</v>
       </c>
-      <c r="F139" s="356"/>
-      <c r="G139" s="357"/>
+      <c r="F139" s="337"/>
+      <c r="G139" s="338"/>
       <c r="H139" s="109"/>
       <c r="I139" s="113"/>
       <c r="J139" s="81" t="e">
@@ -13810,10 +13810,10 @@
       <c r="E140" s="66" t="s">
         <v>95</v>
       </c>
-      <c r="F140" s="336" t="s">
+      <c r="F140" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="G140" s="338"/>
+      <c r="G140" s="325"/>
       <c r="H140" s="110"/>
       <c r="I140" s="97"/>
       <c r="J140" s="102"/>
@@ -13835,7 +13835,7 @@
       <c r="E141" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="F141" s="372" t="s">
+      <c r="F141" s="330" t="s">
         <v>55</v>
       </c>
       <c r="G141" s="108" t="s">
@@ -13862,7 +13862,7 @@
       <c r="E142" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F142" s="373"/>
+      <c r="F142" s="331"/>
       <c r="G142" s="60" t="s">
         <v>238</v>
       </c>
@@ -13913,10 +13913,10 @@
       <c r="E144" s="66" t="s">
         <v>97</v>
       </c>
-      <c r="F144" s="336" t="s">
+      <c r="F144" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="G144" s="338"/>
+      <c r="G144" s="325"/>
       <c r="H144" s="97"/>
       <c r="I144" s="110"/>
       <c r="J144" s="102"/>
@@ -13938,7 +13938,7 @@
       <c r="E145" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="F145" s="372" t="s">
+      <c r="F145" s="330" t="s">
         <v>55</v>
       </c>
       <c r="G145" s="108" t="s">
@@ -13965,7 +13965,7 @@
       <c r="E146" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F146" s="373"/>
+      <c r="F146" s="331"/>
       <c r="G146" s="60" t="s">
         <v>18</v>
       </c>
@@ -14035,15 +14035,15 @@
       <c r="B149" s="58">
         <v>129</v>
       </c>
-      <c r="C149" s="339" t="s">
+      <c r="C149" s="332" t="s">
         <v>239</v>
       </c>
-      <c r="D149" s="336" t="s">
+      <c r="D149" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E149" s="337"/>
-      <c r="F149" s="337"/>
-      <c r="G149" s="338"/>
+      <c r="E149" s="324"/>
+      <c r="F149" s="324"/>
+      <c r="G149" s="325"/>
       <c r="H149" s="97"/>
       <c r="I149" s="110"/>
       <c r="J149" s="102"/>
@@ -14056,15 +14056,15 @@
       <c r="B150" s="121">
         <v>130</v>
       </c>
-      <c r="C150" s="340"/>
+      <c r="C150" s="333"/>
       <c r="D150" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E150" s="358" t="s">
-        <v>44</v>
-      </c>
-      <c r="F150" s="359"/>
-      <c r="G150" s="359"/>
+      <c r="E150" s="334" t="s">
+        <v>44</v>
+      </c>
+      <c r="F150" s="335"/>
+      <c r="G150" s="335"/>
       <c r="H150" s="104"/>
       <c r="I150" s="104"/>
       <c r="J150" s="81"/>
@@ -14083,11 +14083,11 @@
       <c r="D151" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E151" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="F151" s="346"/>
-      <c r="G151" s="347"/>
+      <c r="E151" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="F151" s="320"/>
+      <c r="G151" s="321"/>
       <c r="H151" s="72"/>
       <c r="I151" s="109"/>
       <c r="J151" s="81"/>
@@ -14101,15 +14101,15 @@
       <c r="B152" s="58">
         <v>132</v>
       </c>
-      <c r="C152" s="368" t="s">
+      <c r="C152" s="322" t="s">
         <v>240</v>
       </c>
-      <c r="D152" s="336" t="s">
+      <c r="D152" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E152" s="337"/>
-      <c r="F152" s="337"/>
-      <c r="G152" s="338"/>
+      <c r="E152" s="324"/>
+      <c r="F152" s="324"/>
+      <c r="G152" s="325"/>
       <c r="H152" s="97"/>
       <c r="I152" s="110"/>
       <c r="J152" s="102"/>
@@ -14122,15 +14122,15 @@
       <c r="B153" s="58">
         <v>133</v>
       </c>
-      <c r="C153" s="368"/>
+      <c r="C153" s="322"/>
       <c r="D153" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E153" s="369" t="s">
+      <c r="E153" s="326" t="s">
         <v>241</v>
       </c>
-      <c r="F153" s="370"/>
-      <c r="G153" s="371"/>
+      <c r="F153" s="327"/>
+      <c r="G153" s="328"/>
       <c r="H153" s="122"/>
       <c r="I153" s="123"/>
       <c r="J153" s="81"/>
@@ -14149,11 +14149,11 @@
       <c r="D154" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="E154" s="352" t="s">
+      <c r="E154" s="329" t="s">
         <v>198</v>
       </c>
-      <c r="F154" s="352"/>
-      <c r="G154" s="352"/>
+      <c r="F154" s="329"/>
+      <c r="G154" s="329"/>
       <c r="H154" s="72"/>
       <c r="I154" s="120" t="e">
         <f>SUM(#REF!)</f>
@@ -14179,120 +14179,15 @@
     </row>
   </sheetData>
   <mergeCells count="142">
-    <mergeCell ref="E151:G151"/>
-    <mergeCell ref="C152:C153"/>
-    <mergeCell ref="D152:G152"/>
-    <mergeCell ref="E153:G153"/>
-    <mergeCell ref="E154:G154"/>
-    <mergeCell ref="F140:G140"/>
-    <mergeCell ref="F141:F142"/>
-    <mergeCell ref="F144:G144"/>
-    <mergeCell ref="F145:F146"/>
-    <mergeCell ref="C149:C150"/>
-    <mergeCell ref="D149:G149"/>
-    <mergeCell ref="E150:G150"/>
-    <mergeCell ref="E134:G134"/>
-    <mergeCell ref="E135:G135"/>
-    <mergeCell ref="E136:G136"/>
-    <mergeCell ref="E137:G137"/>
-    <mergeCell ref="C138:C139"/>
-    <mergeCell ref="D138:G138"/>
-    <mergeCell ref="E139:G139"/>
-    <mergeCell ref="E129:G129"/>
-    <mergeCell ref="E130:G130"/>
-    <mergeCell ref="C131:C133"/>
-    <mergeCell ref="D131:G131"/>
-    <mergeCell ref="E132:G132"/>
-    <mergeCell ref="E133:G133"/>
-    <mergeCell ref="E121:G121"/>
-    <mergeCell ref="E122:G122"/>
-    <mergeCell ref="C123:C126"/>
-    <mergeCell ref="D123:G123"/>
-    <mergeCell ref="E124:E125"/>
-    <mergeCell ref="F124:G124"/>
-    <mergeCell ref="E116:G116"/>
-    <mergeCell ref="E117:G117"/>
-    <mergeCell ref="C118:C119"/>
-    <mergeCell ref="D118:G118"/>
-    <mergeCell ref="E119:G119"/>
-    <mergeCell ref="E120:G120"/>
-    <mergeCell ref="C111:C112"/>
-    <mergeCell ref="D111:G111"/>
-    <mergeCell ref="E112:G112"/>
-    <mergeCell ref="E113:G113"/>
-    <mergeCell ref="C114:C115"/>
-    <mergeCell ref="D114:G114"/>
-    <mergeCell ref="E115:G115"/>
-    <mergeCell ref="C106:G106"/>
-    <mergeCell ref="C107:C108"/>
-    <mergeCell ref="D107:G107"/>
-    <mergeCell ref="E108:G108"/>
-    <mergeCell ref="E109:G109"/>
-    <mergeCell ref="E110:G110"/>
-    <mergeCell ref="E104:G104"/>
-    <mergeCell ref="C105:G105"/>
-    <mergeCell ref="E98:G98"/>
-    <mergeCell ref="E99:G99"/>
-    <mergeCell ref="E100:G100"/>
-    <mergeCell ref="C101:C103"/>
-    <mergeCell ref="D101:G101"/>
-    <mergeCell ref="E102:G102"/>
-    <mergeCell ref="E103:G103"/>
-    <mergeCell ref="E93:G93"/>
-    <mergeCell ref="E94:G94"/>
-    <mergeCell ref="C95:C96"/>
-    <mergeCell ref="D95:G95"/>
-    <mergeCell ref="E96:G96"/>
-    <mergeCell ref="E97:G97"/>
-    <mergeCell ref="C87:C88"/>
-    <mergeCell ref="D87:G87"/>
-    <mergeCell ref="E88:G88"/>
-    <mergeCell ref="E89:G89"/>
-    <mergeCell ref="E90:G90"/>
-    <mergeCell ref="C91:C92"/>
-    <mergeCell ref="D91:G91"/>
-    <mergeCell ref="E92:G92"/>
-    <mergeCell ref="F76:G76"/>
-    <mergeCell ref="E80:E81"/>
-    <mergeCell ref="F80:G80"/>
-    <mergeCell ref="G81:I81"/>
-    <mergeCell ref="E84:E85"/>
-    <mergeCell ref="F84:G84"/>
-    <mergeCell ref="E63:G63"/>
-    <mergeCell ref="E64:G64"/>
-    <mergeCell ref="C65:C67"/>
-    <mergeCell ref="D65:G65"/>
-    <mergeCell ref="F66:G66"/>
-    <mergeCell ref="F70:G70"/>
-    <mergeCell ref="E58:G58"/>
-    <mergeCell ref="E59:G59"/>
-    <mergeCell ref="C60:C62"/>
-    <mergeCell ref="D60:G60"/>
-    <mergeCell ref="E61:G61"/>
-    <mergeCell ref="E62:G62"/>
-    <mergeCell ref="E54:G54"/>
-    <mergeCell ref="C55:C57"/>
-    <mergeCell ref="D55:G55"/>
-    <mergeCell ref="E56:G56"/>
-    <mergeCell ref="E57:G57"/>
-    <mergeCell ref="C48:C49"/>
-    <mergeCell ref="D48:G48"/>
-    <mergeCell ref="E49:G49"/>
-    <mergeCell ref="E50:G50"/>
-    <mergeCell ref="E51:G51"/>
-    <mergeCell ref="C52:C53"/>
-    <mergeCell ref="D52:G52"/>
-    <mergeCell ref="E53:G53"/>
-    <mergeCell ref="C42:C44"/>
-    <mergeCell ref="D42:G42"/>
-    <mergeCell ref="D43:D44"/>
-    <mergeCell ref="E43:G43"/>
-    <mergeCell ref="E44:G44"/>
-    <mergeCell ref="C45:C47"/>
-    <mergeCell ref="D45:G45"/>
-    <mergeCell ref="D46:D47"/>
-    <mergeCell ref="E46:G46"/>
-    <mergeCell ref="E47:G47"/>
+    <mergeCell ref="B1:J1"/>
+    <mergeCell ref="B3:J3"/>
+    <mergeCell ref="B4:J4"/>
+    <mergeCell ref="B5:J5"/>
+    <mergeCell ref="B6:J6"/>
+    <mergeCell ref="B7:H7"/>
+    <mergeCell ref="B22:B24"/>
+    <mergeCell ref="C22:G24"/>
+    <mergeCell ref="I22:J24"/>
     <mergeCell ref="C29:G29"/>
     <mergeCell ref="C30:C34"/>
     <mergeCell ref="D30:G30"/>
@@ -14312,15 +14207,120 @@
     <mergeCell ref="D36:D37"/>
     <mergeCell ref="E36:G36"/>
     <mergeCell ref="E37:G37"/>
-    <mergeCell ref="B1:J1"/>
-    <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B4:J4"/>
-    <mergeCell ref="B5:J5"/>
-    <mergeCell ref="B6:J6"/>
-    <mergeCell ref="B7:H7"/>
-    <mergeCell ref="B22:B24"/>
-    <mergeCell ref="C22:G24"/>
-    <mergeCell ref="I22:J24"/>
+    <mergeCell ref="C48:C49"/>
+    <mergeCell ref="D48:G48"/>
+    <mergeCell ref="E49:G49"/>
+    <mergeCell ref="E50:G50"/>
+    <mergeCell ref="E51:G51"/>
+    <mergeCell ref="C52:C53"/>
+    <mergeCell ref="D52:G52"/>
+    <mergeCell ref="E53:G53"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="D42:G42"/>
+    <mergeCell ref="D43:D44"/>
+    <mergeCell ref="E43:G43"/>
+    <mergeCell ref="E44:G44"/>
+    <mergeCell ref="C45:C47"/>
+    <mergeCell ref="D45:G45"/>
+    <mergeCell ref="D46:D47"/>
+    <mergeCell ref="E46:G46"/>
+    <mergeCell ref="E47:G47"/>
+    <mergeCell ref="E58:G58"/>
+    <mergeCell ref="E59:G59"/>
+    <mergeCell ref="C60:C62"/>
+    <mergeCell ref="D60:G60"/>
+    <mergeCell ref="E61:G61"/>
+    <mergeCell ref="E62:G62"/>
+    <mergeCell ref="E54:G54"/>
+    <mergeCell ref="C55:C57"/>
+    <mergeCell ref="D55:G55"/>
+    <mergeCell ref="E56:G56"/>
+    <mergeCell ref="E57:G57"/>
+    <mergeCell ref="F76:G76"/>
+    <mergeCell ref="E80:E81"/>
+    <mergeCell ref="F80:G80"/>
+    <mergeCell ref="G81:I81"/>
+    <mergeCell ref="E84:E85"/>
+    <mergeCell ref="F84:G84"/>
+    <mergeCell ref="E63:G63"/>
+    <mergeCell ref="E64:G64"/>
+    <mergeCell ref="C65:C67"/>
+    <mergeCell ref="D65:G65"/>
+    <mergeCell ref="F66:G66"/>
+    <mergeCell ref="F70:G70"/>
+    <mergeCell ref="E93:G93"/>
+    <mergeCell ref="E94:G94"/>
+    <mergeCell ref="C95:C96"/>
+    <mergeCell ref="D95:G95"/>
+    <mergeCell ref="E96:G96"/>
+    <mergeCell ref="E97:G97"/>
+    <mergeCell ref="C87:C88"/>
+    <mergeCell ref="D87:G87"/>
+    <mergeCell ref="E88:G88"/>
+    <mergeCell ref="E89:G89"/>
+    <mergeCell ref="E90:G90"/>
+    <mergeCell ref="C91:C92"/>
+    <mergeCell ref="D91:G91"/>
+    <mergeCell ref="E92:G92"/>
+    <mergeCell ref="E104:G104"/>
+    <mergeCell ref="C105:G105"/>
+    <mergeCell ref="E98:G98"/>
+    <mergeCell ref="E99:G99"/>
+    <mergeCell ref="E100:G100"/>
+    <mergeCell ref="C101:C103"/>
+    <mergeCell ref="D101:G101"/>
+    <mergeCell ref="E102:G102"/>
+    <mergeCell ref="E103:G103"/>
+    <mergeCell ref="C111:C112"/>
+    <mergeCell ref="D111:G111"/>
+    <mergeCell ref="E112:G112"/>
+    <mergeCell ref="E113:G113"/>
+    <mergeCell ref="C114:C115"/>
+    <mergeCell ref="D114:G114"/>
+    <mergeCell ref="E115:G115"/>
+    <mergeCell ref="C106:G106"/>
+    <mergeCell ref="C107:C108"/>
+    <mergeCell ref="D107:G107"/>
+    <mergeCell ref="E108:G108"/>
+    <mergeCell ref="E109:G109"/>
+    <mergeCell ref="E110:G110"/>
+    <mergeCell ref="E121:G121"/>
+    <mergeCell ref="E122:G122"/>
+    <mergeCell ref="C123:C126"/>
+    <mergeCell ref="D123:G123"/>
+    <mergeCell ref="E124:E125"/>
+    <mergeCell ref="F124:G124"/>
+    <mergeCell ref="E116:G116"/>
+    <mergeCell ref="E117:G117"/>
+    <mergeCell ref="C118:C119"/>
+    <mergeCell ref="D118:G118"/>
+    <mergeCell ref="E119:G119"/>
+    <mergeCell ref="E120:G120"/>
+    <mergeCell ref="E134:G134"/>
+    <mergeCell ref="E135:G135"/>
+    <mergeCell ref="E136:G136"/>
+    <mergeCell ref="E137:G137"/>
+    <mergeCell ref="C138:C139"/>
+    <mergeCell ref="D138:G138"/>
+    <mergeCell ref="E139:G139"/>
+    <mergeCell ref="E129:G129"/>
+    <mergeCell ref="E130:G130"/>
+    <mergeCell ref="C131:C133"/>
+    <mergeCell ref="D131:G131"/>
+    <mergeCell ref="E132:G132"/>
+    <mergeCell ref="E133:G133"/>
+    <mergeCell ref="E151:G151"/>
+    <mergeCell ref="C152:C153"/>
+    <mergeCell ref="D152:G152"/>
+    <mergeCell ref="E153:G153"/>
+    <mergeCell ref="E154:G154"/>
+    <mergeCell ref="F140:G140"/>
+    <mergeCell ref="F141:F142"/>
+    <mergeCell ref="F144:G144"/>
+    <mergeCell ref="F145:F146"/>
+    <mergeCell ref="C149:C150"/>
+    <mergeCell ref="D149:G149"/>
+    <mergeCell ref="E150:G150"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="64" orientation="portrait" r:id="rId1"/>
@@ -14350,15 +14350,15 @@
       <c r="A1" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="319" t="s">
+      <c r="B1" s="357" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="319"/>
-      <c r="D1" s="319"/>
-      <c r="E1" s="319"/>
-      <c r="F1" s="319"/>
-      <c r="G1" s="319"/>
-      <c r="H1" s="319"/>
+      <c r="C1" s="357"/>
+      <c r="D1" s="357"/>
+      <c r="E1" s="357"/>
+      <c r="F1" s="357"/>
+      <c r="G1" s="357"/>
+      <c r="H1" s="357"/>
       <c r="L1" s="51"/>
     </row>
     <row r="2" spans="1:13" ht="15.75" customHeight="1">
@@ -14392,30 +14392,30 @@
       <c r="A3" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="320" t="s">
+      <c r="B3" s="358" t="s">
         <v>167</v>
       </c>
-      <c r="C3" s="320"/>
-      <c r="D3" s="320"/>
-      <c r="E3" s="320"/>
-      <c r="F3" s="320"/>
-      <c r="G3" s="320"/>
-      <c r="H3" s="320"/>
+      <c r="C3" s="358"/>
+      <c r="D3" s="358"/>
+      <c r="E3" s="358"/>
+      <c r="F3" s="358"/>
+      <c r="G3" s="358"/>
+      <c r="H3" s="358"/>
       <c r="L3" s="51"/>
     </row>
     <row r="4" spans="1:13" ht="14.25" customHeight="1">
       <c r="A4" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="321" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="321"/>
-      <c r="D4" s="321"/>
-      <c r="E4" s="321"/>
-      <c r="F4" s="321"/>
-      <c r="G4" s="321"/>
-      <c r="H4" s="321"/>
+      <c r="B4" s="359" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="359"/>
+      <c r="D4" s="359"/>
+      <c r="E4" s="359"/>
+      <c r="F4" s="359"/>
+      <c r="G4" s="359"/>
+      <c r="H4" s="359"/>
       <c r="L4" s="51"/>
       <c r="M4" s="53"/>
     </row>
@@ -14437,40 +14437,40 @@
       <c r="A19" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="B19" s="374" t="s">
+      <c r="B19" s="382" t="s">
         <v>0</v>
       </c>
-      <c r="C19" s="327" t="s">
+      <c r="C19" s="365" t="s">
         <v>51</v>
       </c>
-      <c r="D19" s="328"/>
-      <c r="E19" s="328"/>
-      <c r="F19" s="328"/>
-      <c r="G19" s="329"/>
+      <c r="D19" s="366"/>
+      <c r="E19" s="366"/>
+      <c r="F19" s="366"/>
+      <c r="G19" s="367"/>
       <c r="H19" s="55"/>
     </row>
     <row r="20" spans="1:13" ht="12" customHeight="1">
       <c r="A20" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B20" s="325"/>
-      <c r="C20" s="330"/>
-      <c r="D20" s="331"/>
-      <c r="E20" s="331"/>
-      <c r="F20" s="331"/>
-      <c r="G20" s="332"/>
+      <c r="B20" s="363"/>
+      <c r="C20" s="368"/>
+      <c r="D20" s="369"/>
+      <c r="E20" s="369"/>
+      <c r="F20" s="369"/>
+      <c r="G20" s="370"/>
       <c r="H20" s="55"/>
     </row>
     <row r="21" spans="1:13" ht="24" customHeight="1">
       <c r="A21" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B21" s="326"/>
-      <c r="C21" s="333"/>
-      <c r="D21" s="334"/>
-      <c r="E21" s="334"/>
-      <c r="F21" s="334"/>
-      <c r="G21" s="335"/>
+      <c r="B21" s="364"/>
+      <c r="C21" s="371"/>
+      <c r="D21" s="372"/>
+      <c r="E21" s="372"/>
+      <c r="F21" s="372"/>
+      <c r="G21" s="373"/>
       <c r="H21" s="57" t="s">
         <v>52</v>
       </c>
@@ -14486,17 +14486,17 @@
       <c r="B25" s="57">
         <v>1</v>
       </c>
-      <c r="C25" s="375">
+      <c r="C25" s="383">
         <v>2</v>
       </c>
-      <c r="D25" s="376"/>
+      <c r="D25" s="384"/>
       <c r="E25" s="57">
         <v>3</v>
       </c>
-      <c r="F25" s="375">
+      <c r="F25" s="383">
         <v>4</v>
       </c>
-      <c r="G25" s="376"/>
+      <c r="G25" s="384"/>
       <c r="H25" s="57">
         <v>8</v>
       </c>
@@ -14552,15 +14552,15 @@
       <c r="B29" s="58">
         <v>2</v>
       </c>
-      <c r="C29" s="377" t="s">
+      <c r="C29" s="374" t="s">
         <v>54</v>
       </c>
-      <c r="D29" s="378"/>
-      <c r="E29" s="336" t="s">
+      <c r="D29" s="375"/>
+      <c r="E29" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="F29" s="337"/>
-      <c r="G29" s="338"/>
+      <c r="F29" s="324"/>
+      <c r="G29" s="325"/>
       <c r="H29" s="64"/>
       <c r="I29" s="49"/>
       <c r="M29" s="65"/>
@@ -14572,15 +14572,15 @@
       <c r="B30" s="58">
         <v>3</v>
       </c>
-      <c r="C30" s="379"/>
-      <c r="D30" s="380"/>
+      <c r="C30" s="376"/>
+      <c r="D30" s="377"/>
       <c r="E30" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F30" s="355" t="s">
+      <c r="F30" s="336" t="s">
         <v>56</v>
       </c>
-      <c r="G30" s="357"/>
+      <c r="G30" s="338"/>
       <c r="H30" s="72" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -14595,15 +14595,15 @@
       <c r="B31" s="58">
         <v>4</v>
       </c>
-      <c r="C31" s="379"/>
-      <c r="D31" s="380"/>
+      <c r="C31" s="376"/>
+      <c r="D31" s="377"/>
       <c r="E31" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="F31" s="355" t="s">
+      <c r="F31" s="336" t="s">
         <v>57</v>
       </c>
-      <c r="G31" s="357"/>
+      <c r="G31" s="338"/>
       <c r="H31" s="64"/>
       <c r="I31" s="49"/>
       <c r="M31" s="53"/>
@@ -14615,15 +14615,15 @@
       <c r="B32" s="58">
         <v>5</v>
       </c>
-      <c r="C32" s="379"/>
-      <c r="D32" s="380"/>
+      <c r="C32" s="376"/>
+      <c r="D32" s="377"/>
       <c r="E32" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="F32" s="355" t="s">
+      <c r="F32" s="336" t="s">
         <v>58</v>
       </c>
-      <c r="G32" s="357"/>
+      <c r="G32" s="338"/>
       <c r="H32" s="64"/>
       <c r="I32" s="49"/>
     </row>
@@ -14643,10 +14643,10 @@
       <c r="E33" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F33" s="345" t="s">
+      <c r="F33" s="319" t="s">
         <v>170</v>
       </c>
-      <c r="G33" s="347"/>
+      <c r="G33" s="321"/>
       <c r="H33" s="64"/>
       <c r="I33" s="49"/>
       <c r="J33" s="49"/>
@@ -14667,10 +14667,10 @@
       <c r="E34" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F34" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="G34" s="347"/>
+      <c r="F34" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="G34" s="321"/>
       <c r="H34" s="64"/>
       <c r="I34" s="49"/>
       <c r="J34" s="49"/>
@@ -14683,15 +14683,15 @@
       <c r="B35" s="58">
         <v>8</v>
       </c>
-      <c r="C35" s="377" t="s">
+      <c r="C35" s="374" t="s">
         <v>171</v>
       </c>
-      <c r="D35" s="378"/>
-      <c r="E35" s="336" t="s">
+      <c r="D35" s="375"/>
+      <c r="E35" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="F35" s="337"/>
-      <c r="G35" s="338"/>
+      <c r="F35" s="324"/>
+      <c r="G35" s="325"/>
       <c r="H35" s="64"/>
       <c r="I35" s="49"/>
     </row>
@@ -14702,15 +14702,15 @@
       <c r="B36" s="58">
         <v>9</v>
       </c>
-      <c r="C36" s="379"/>
-      <c r="D36" s="380"/>
-      <c r="E36" s="372" t="s">
+      <c r="C36" s="376"/>
+      <c r="D36" s="377"/>
+      <c r="E36" s="330" t="s">
         <v>55</v>
       </c>
-      <c r="F36" s="355" t="s">
+      <c r="F36" s="336" t="s">
         <v>172</v>
       </c>
-      <c r="G36" s="357"/>
+      <c r="G36" s="338"/>
       <c r="H36" s="72" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -14725,13 +14725,13 @@
       <c r="B37" s="58">
         <v>10</v>
       </c>
-      <c r="C37" s="381"/>
-      <c r="D37" s="382"/>
-      <c r="E37" s="373"/>
-      <c r="F37" s="355" t="s">
+      <c r="C37" s="380"/>
+      <c r="D37" s="381"/>
+      <c r="E37" s="331"/>
+      <c r="F37" s="336" t="s">
         <v>173</v>
       </c>
-      <c r="G37" s="357"/>
+      <c r="G37" s="338"/>
       <c r="H37" s="64"/>
       <c r="I37" s="49"/>
     </row>
@@ -14742,15 +14742,15 @@
       <c r="B38" s="58">
         <v>11</v>
       </c>
-      <c r="C38" s="377" t="s">
+      <c r="C38" s="374" t="s">
         <v>174</v>
       </c>
-      <c r="D38" s="378"/>
-      <c r="E38" s="336" t="s">
+      <c r="D38" s="375"/>
+      <c r="E38" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="F38" s="337"/>
-      <c r="G38" s="338"/>
+      <c r="F38" s="324"/>
+      <c r="G38" s="325"/>
       <c r="H38" s="64"/>
       <c r="I38" s="49"/>
     </row>
@@ -14761,15 +14761,15 @@
       <c r="B39" s="58">
         <v>12</v>
       </c>
-      <c r="C39" s="379"/>
-      <c r="D39" s="380"/>
+      <c r="C39" s="376"/>
+      <c r="D39" s="377"/>
       <c r="E39" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F39" s="383" t="s">
-        <v>44</v>
-      </c>
-      <c r="G39" s="384"/>
+      <c r="F39" s="378" t="s">
+        <v>44</v>
+      </c>
+      <c r="G39" s="379"/>
       <c r="H39" s="64"/>
       <c r="I39" s="49"/>
     </row>
@@ -14789,10 +14789,10 @@
       <c r="E40" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F40" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="G40" s="347"/>
+      <c r="F40" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="G40" s="321"/>
       <c r="H40" s="64"/>
       <c r="I40" s="49"/>
       <c r="J40" s="49"/>
@@ -14804,15 +14804,15 @@
       <c r="B41" s="58">
         <v>14</v>
       </c>
-      <c r="C41" s="377" t="s">
+      <c r="C41" s="374" t="s">
         <v>175</v>
       </c>
-      <c r="D41" s="378"/>
-      <c r="E41" s="336" t="s">
+      <c r="D41" s="375"/>
+      <c r="E41" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="F41" s="337"/>
-      <c r="G41" s="338"/>
+      <c r="F41" s="324"/>
+      <c r="G41" s="325"/>
       <c r="H41" s="64"/>
       <c r="I41" s="49"/>
     </row>
@@ -14823,15 +14823,15 @@
       <c r="B42" s="58">
         <v>15</v>
       </c>
-      <c r="C42" s="379"/>
-      <c r="D42" s="380"/>
+      <c r="C42" s="376"/>
+      <c r="D42" s="377"/>
       <c r="E42" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F42" s="355" t="s">
+      <c r="F42" s="336" t="s">
         <v>91</v>
       </c>
-      <c r="G42" s="357"/>
+      <c r="G42" s="338"/>
       <c r="H42" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -14854,10 +14854,10 @@
       <c r="E43" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F43" s="345" t="s">
+      <c r="F43" s="319" t="s">
         <v>176</v>
       </c>
-      <c r="G43" s="347"/>
+      <c r="G43" s="321"/>
       <c r="H43" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -14881,10 +14881,10 @@
       <c r="E44" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F44" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="G44" s="347"/>
+      <c r="F44" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="G44" s="321"/>
       <c r="H44" s="64"/>
       <c r="I44" s="49"/>
       <c r="J44" s="49"/>
@@ -14896,15 +14896,15 @@
       <c r="B45" s="58">
         <v>18</v>
       </c>
-      <c r="C45" s="377" t="s">
+      <c r="C45" s="374" t="s">
         <v>177</v>
       </c>
-      <c r="D45" s="378"/>
-      <c r="E45" s="336" t="s">
+      <c r="D45" s="375"/>
+      <c r="E45" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="F45" s="337"/>
-      <c r="G45" s="338"/>
+      <c r="F45" s="324"/>
+      <c r="G45" s="325"/>
       <c r="H45" s="64"/>
       <c r="I45" s="49"/>
     </row>
@@ -14915,15 +14915,15 @@
       <c r="B46" s="58">
         <v>19</v>
       </c>
-      <c r="C46" s="379"/>
-      <c r="D46" s="380"/>
+      <c r="C46" s="376"/>
+      <c r="D46" s="377"/>
       <c r="E46" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F46" s="383" t="s">
-        <v>44</v>
-      </c>
-      <c r="G46" s="384"/>
+      <c r="F46" s="378" t="s">
+        <v>44</v>
+      </c>
+      <c r="G46" s="379"/>
       <c r="H46" s="64"/>
       <c r="I46" s="49"/>
     </row>
@@ -14943,8 +14943,8 @@
       <c r="E47" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F47" s="345"/>
-      <c r="G47" s="347"/>
+      <c r="F47" s="319"/>
+      <c r="G47" s="321"/>
       <c r="H47" s="64"/>
       <c r="I47" s="49"/>
       <c r="J47" s="49"/>
@@ -14965,10 +14965,10 @@
       <c r="E48" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F48" s="345" t="s">
+      <c r="F48" s="319" t="s">
         <v>178</v>
       </c>
-      <c r="G48" s="347"/>
+      <c r="G48" s="321"/>
       <c r="H48" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -14992,10 +14992,10 @@
       <c r="E49" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F49" s="345" t="s">
+      <c r="F49" s="319" t="s">
         <v>8</v>
       </c>
-      <c r="G49" s="347"/>
+      <c r="G49" s="321"/>
       <c r="H49" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15010,13 +15010,13 @@
       <c r="B50" s="58">
         <v>24</v>
       </c>
-      <c r="C50" s="336" t="s">
+      <c r="C50" s="323" t="s">
         <v>179</v>
       </c>
-      <c r="D50" s="337"/>
-      <c r="E50" s="337"/>
-      <c r="F50" s="337"/>
-      <c r="G50" s="338"/>
+      <c r="D50" s="324"/>
+      <c r="E50" s="324"/>
+      <c r="F50" s="324"/>
+      <c r="G50" s="325"/>
       <c r="H50" s="64"/>
       <c r="I50" s="49"/>
     </row>
@@ -15027,13 +15027,13 @@
       <c r="B51" s="58">
         <v>25</v>
       </c>
-      <c r="C51" s="336" t="s">
+      <c r="C51" s="323" t="s">
         <v>180</v>
       </c>
-      <c r="D51" s="337"/>
-      <c r="E51" s="337"/>
-      <c r="F51" s="337"/>
-      <c r="G51" s="338"/>
+      <c r="D51" s="324"/>
+      <c r="E51" s="324"/>
+      <c r="F51" s="324"/>
+      <c r="G51" s="325"/>
       <c r="H51" s="64" t="e">
         <f>нак.расх.!G29-зат.осн.про.!H75-зат.осн.про.!H99</f>
         <v>#REF!</v>
@@ -15079,15 +15079,15 @@
       <c r="B53" s="58">
         <v>2</v>
       </c>
-      <c r="C53" s="377" t="s">
+      <c r="C53" s="374" t="s">
         <v>54</v>
       </c>
-      <c r="D53" s="378"/>
-      <c r="E53" s="336" t="s">
+      <c r="D53" s="375"/>
+      <c r="E53" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="F53" s="337"/>
-      <c r="G53" s="338"/>
+      <c r="F53" s="324"/>
+      <c r="G53" s="325"/>
       <c r="H53" s="64"/>
       <c r="I53" s="49"/>
       <c r="M53" s="53" t="e">
@@ -15102,15 +15102,15 @@
       <c r="B54" s="58">
         <v>3</v>
       </c>
-      <c r="C54" s="379"/>
-      <c r="D54" s="380"/>
+      <c r="C54" s="376"/>
+      <c r="D54" s="377"/>
       <c r="E54" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F54" s="355" t="s">
+      <c r="F54" s="336" t="s">
         <v>56</v>
       </c>
-      <c r="G54" s="357"/>
+      <c r="G54" s="338"/>
       <c r="H54" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15124,15 +15124,15 @@
       <c r="B55" s="58">
         <v>4</v>
       </c>
-      <c r="C55" s="379"/>
-      <c r="D55" s="380"/>
+      <c r="C55" s="376"/>
+      <c r="D55" s="377"/>
       <c r="E55" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="F55" s="355" t="s">
+      <c r="F55" s="336" t="s">
         <v>57</v>
       </c>
-      <c r="G55" s="357"/>
+      <c r="G55" s="338"/>
       <c r="H55" s="64"/>
       <c r="I55" s="49"/>
     </row>
@@ -15143,15 +15143,15 @@
       <c r="B56" s="58">
         <v>5</v>
       </c>
-      <c r="C56" s="379"/>
-      <c r="D56" s="380"/>
+      <c r="C56" s="376"/>
+      <c r="D56" s="377"/>
       <c r="E56" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="F56" s="355" t="s">
+      <c r="F56" s="336" t="s">
         <v>58</v>
       </c>
-      <c r="G56" s="357"/>
+      <c r="G56" s="338"/>
       <c r="H56" s="64"/>
       <c r="I56" s="49"/>
     </row>
@@ -15171,10 +15171,10 @@
       <c r="E57" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F57" s="345" t="s">
+      <c r="F57" s="319" t="s">
         <v>170</v>
       </c>
-      <c r="G57" s="347"/>
+      <c r="G57" s="321"/>
       <c r="H57" s="64"/>
       <c r="I57" s="49"/>
       <c r="J57" s="49"/>
@@ -15195,10 +15195,10 @@
       <c r="E58" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F58" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="G58" s="347"/>
+      <c r="F58" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="G58" s="321"/>
       <c r="H58" s="64"/>
       <c r="I58" s="49"/>
     </row>
@@ -15209,15 +15209,15 @@
       <c r="B59" s="58">
         <v>8</v>
       </c>
-      <c r="C59" s="377" t="s">
+      <c r="C59" s="374" t="s">
         <v>171</v>
       </c>
-      <c r="D59" s="378"/>
-      <c r="E59" s="336" t="s">
+      <c r="D59" s="375"/>
+      <c r="E59" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="F59" s="337"/>
-      <c r="G59" s="338"/>
+      <c r="F59" s="324"/>
+      <c r="G59" s="325"/>
       <c r="H59" s="64"/>
       <c r="I59" s="49"/>
     </row>
@@ -15228,15 +15228,15 @@
       <c r="B60" s="58">
         <v>9</v>
       </c>
-      <c r="C60" s="379"/>
-      <c r="D60" s="380"/>
-      <c r="E60" s="372" t="s">
+      <c r="C60" s="376"/>
+      <c r="D60" s="377"/>
+      <c r="E60" s="330" t="s">
         <v>55</v>
       </c>
-      <c r="F60" s="355" t="s">
+      <c r="F60" s="336" t="s">
         <v>172</v>
       </c>
-      <c r="G60" s="357"/>
+      <c r="G60" s="338"/>
       <c r="H60" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15250,13 +15250,13 @@
       <c r="B61" s="58">
         <v>10</v>
       </c>
-      <c r="C61" s="381"/>
-      <c r="D61" s="382"/>
-      <c r="E61" s="373"/>
-      <c r="F61" s="355" t="s">
+      <c r="C61" s="380"/>
+      <c r="D61" s="381"/>
+      <c r="E61" s="331"/>
+      <c r="F61" s="336" t="s">
         <v>173</v>
       </c>
-      <c r="G61" s="357"/>
+      <c r="G61" s="338"/>
       <c r="H61" s="64"/>
       <c r="I61" s="49"/>
     </row>
@@ -15267,15 +15267,15 @@
       <c r="B62" s="58">
         <v>11</v>
       </c>
-      <c r="C62" s="377" t="s">
+      <c r="C62" s="374" t="s">
         <v>174</v>
       </c>
-      <c r="D62" s="378"/>
-      <c r="E62" s="336" t="s">
+      <c r="D62" s="375"/>
+      <c r="E62" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="F62" s="337"/>
-      <c r="G62" s="338"/>
+      <c r="F62" s="324"/>
+      <c r="G62" s="325"/>
       <c r="H62" s="64"/>
       <c r="I62" s="49"/>
     </row>
@@ -15286,15 +15286,15 @@
       <c r="B63" s="58">
         <v>12</v>
       </c>
-      <c r="C63" s="379"/>
-      <c r="D63" s="380"/>
+      <c r="C63" s="376"/>
+      <c r="D63" s="377"/>
       <c r="E63" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F63" s="383" t="s">
-        <v>44</v>
-      </c>
-      <c r="G63" s="384"/>
+      <c r="F63" s="378" t="s">
+        <v>44</v>
+      </c>
+      <c r="G63" s="379"/>
       <c r="H63" s="64"/>
       <c r="I63" s="49"/>
       <c r="J63" s="49"/>
@@ -15315,10 +15315,10 @@
       <c r="E64" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F64" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="G64" s="347"/>
+      <c r="F64" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="G64" s="321"/>
       <c r="H64" s="64"/>
       <c r="I64" s="49"/>
     </row>
@@ -15329,15 +15329,15 @@
       <c r="B65" s="58">
         <v>14</v>
       </c>
-      <c r="C65" s="377" t="s">
+      <c r="C65" s="374" t="s">
         <v>175</v>
       </c>
-      <c r="D65" s="378"/>
-      <c r="E65" s="336" t="s">
+      <c r="D65" s="375"/>
+      <c r="E65" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="F65" s="337"/>
-      <c r="G65" s="338"/>
+      <c r="F65" s="324"/>
+      <c r="G65" s="325"/>
       <c r="H65" s="64"/>
       <c r="I65" s="49"/>
     </row>
@@ -15348,15 +15348,15 @@
       <c r="B66" s="58">
         <v>15</v>
       </c>
-      <c r="C66" s="379"/>
-      <c r="D66" s="380"/>
+      <c r="C66" s="376"/>
+      <c r="D66" s="377"/>
       <c r="E66" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F66" s="355" t="s">
+      <c r="F66" s="336" t="s">
         <v>91</v>
       </c>
-      <c r="G66" s="357"/>
+      <c r="G66" s="338"/>
       <c r="H66" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15380,10 +15380,10 @@
       <c r="E67" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F67" s="345" t="s">
+      <c r="F67" s="319" t="s">
         <v>176</v>
       </c>
-      <c r="G67" s="347"/>
+      <c r="G67" s="321"/>
       <c r="H67" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15406,10 +15406,10 @@
       <c r="E68" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F68" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="G68" s="347"/>
+      <c r="F68" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="G68" s="321"/>
       <c r="H68" s="64"/>
       <c r="I68" s="49"/>
     </row>
@@ -15420,15 +15420,15 @@
       <c r="B69" s="58">
         <v>18</v>
       </c>
-      <c r="C69" s="377" t="s">
+      <c r="C69" s="374" t="s">
         <v>177</v>
       </c>
-      <c r="D69" s="378"/>
-      <c r="E69" s="336" t="s">
+      <c r="D69" s="375"/>
+      <c r="E69" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="F69" s="337"/>
-      <c r="G69" s="338"/>
+      <c r="F69" s="324"/>
+      <c r="G69" s="325"/>
       <c r="H69" s="64"/>
       <c r="I69" s="49"/>
       <c r="J69" s="49"/>
@@ -15440,15 +15440,15 @@
       <c r="B70" s="58">
         <v>19</v>
       </c>
-      <c r="C70" s="379"/>
-      <c r="D70" s="380"/>
+      <c r="C70" s="376"/>
+      <c r="D70" s="377"/>
       <c r="E70" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F70" s="383" t="s">
-        <v>44</v>
-      </c>
-      <c r="G70" s="384"/>
+      <c r="F70" s="378" t="s">
+        <v>44</v>
+      </c>
+      <c r="G70" s="379"/>
       <c r="H70" s="64"/>
       <c r="I70" s="49"/>
     </row>
@@ -15468,8 +15468,8 @@
       <c r="E71" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F71" s="345"/>
-      <c r="G71" s="347"/>
+      <c r="F71" s="319"/>
+      <c r="G71" s="321"/>
       <c r="H71" s="64"/>
       <c r="I71" s="49"/>
     </row>
@@ -15486,10 +15486,10 @@
       <c r="E72" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F72" s="345" t="s">
+      <c r="F72" s="319" t="s">
         <v>178</v>
       </c>
-      <c r="G72" s="347"/>
+      <c r="G72" s="321"/>
       <c r="H72" s="64"/>
       <c r="I72" s="49"/>
       <c r="J72" s="49"/>
@@ -15512,10 +15512,10 @@
       <c r="E73" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F73" s="345" t="s">
+      <c r="F73" s="319" t="s">
         <v>8</v>
       </c>
-      <c r="G73" s="347"/>
+      <c r="G73" s="321"/>
       <c r="H73" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15529,13 +15529,13 @@
       <c r="B74" s="58">
         <v>24</v>
       </c>
-      <c r="C74" s="336" t="s">
+      <c r="C74" s="323" t="s">
         <v>179</v>
       </c>
-      <c r="D74" s="337"/>
-      <c r="E74" s="337"/>
-      <c r="F74" s="337"/>
-      <c r="G74" s="338"/>
+      <c r="D74" s="324"/>
+      <c r="E74" s="324"/>
+      <c r="F74" s="324"/>
+      <c r="G74" s="325"/>
       <c r="H74" s="64"/>
       <c r="I74" s="49"/>
       <c r="J74" s="49"/>
@@ -15546,13 +15546,13 @@
       <c r="B75" s="58">
         <v>25</v>
       </c>
-      <c r="C75" s="336" t="s">
+      <c r="C75" s="323" t="s">
         <v>180</v>
       </c>
-      <c r="D75" s="337"/>
-      <c r="E75" s="337"/>
-      <c r="F75" s="337"/>
-      <c r="G75" s="338"/>
+      <c r="D75" s="324"/>
+      <c r="E75" s="324"/>
+      <c r="F75" s="324"/>
+      <c r="G75" s="325"/>
       <c r="H75" s="64" t="e">
         <f>нак.расх.!G29*4%</f>
         <v>#REF!</v>
@@ -15598,15 +15598,15 @@
       <c r="B77" s="58">
         <v>2</v>
       </c>
-      <c r="C77" s="377" t="s">
+      <c r="C77" s="374" t="s">
         <v>54</v>
       </c>
-      <c r="D77" s="378"/>
-      <c r="E77" s="336" t="s">
+      <c r="D77" s="375"/>
+      <c r="E77" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="F77" s="337"/>
-      <c r="G77" s="338"/>
+      <c r="F77" s="324"/>
+      <c r="G77" s="325"/>
       <c r="H77" s="64"/>
       <c r="M77" s="53" t="e">
         <f>H76-M76</f>
@@ -15617,15 +15617,15 @@
       <c r="B78" s="58">
         <v>3</v>
       </c>
-      <c r="C78" s="379"/>
-      <c r="D78" s="380"/>
+      <c r="C78" s="376"/>
+      <c r="D78" s="377"/>
       <c r="E78" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F78" s="355" t="s">
+      <c r="F78" s="336" t="s">
         <v>56</v>
       </c>
-      <c r="G78" s="357"/>
+      <c r="G78" s="338"/>
       <c r="H78" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15635,30 +15635,30 @@
       <c r="B79" s="58">
         <v>4</v>
       </c>
-      <c r="C79" s="379"/>
-      <c r="D79" s="380"/>
+      <c r="C79" s="376"/>
+      <c r="D79" s="377"/>
       <c r="E79" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="F79" s="355" t="s">
+      <c r="F79" s="336" t="s">
         <v>57</v>
       </c>
-      <c r="G79" s="357"/>
+      <c r="G79" s="338"/>
       <c r="H79" s="64"/>
     </row>
     <row r="80" spans="1:13" ht="15.75" customHeight="1">
       <c r="B80" s="58">
         <v>5</v>
       </c>
-      <c r="C80" s="379"/>
-      <c r="D80" s="380"/>
+      <c r="C80" s="376"/>
+      <c r="D80" s="377"/>
       <c r="E80" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="F80" s="355" t="s">
+      <c r="F80" s="336" t="s">
         <v>58</v>
       </c>
-      <c r="G80" s="357"/>
+      <c r="G80" s="338"/>
       <c r="H80" s="64"/>
     </row>
     <row r="81" spans="2:8" ht="15.75" customHeight="1">
@@ -15674,10 +15674,10 @@
       <c r="E81" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F81" s="345" t="s">
+      <c r="F81" s="319" t="s">
         <v>170</v>
       </c>
-      <c r="G81" s="347"/>
+      <c r="G81" s="321"/>
       <c r="H81" s="64"/>
     </row>
     <row r="82" spans="2:8" ht="15.75" customHeight="1">
@@ -15693,40 +15693,40 @@
       <c r="E82" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F82" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="G82" s="347"/>
+      <c r="F82" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="G82" s="321"/>
       <c r="H82" s="64"/>
     </row>
     <row r="83" spans="2:8" ht="15.75" customHeight="1">
       <c r="B83" s="58">
         <v>8</v>
       </c>
-      <c r="C83" s="377" t="s">
+      <c r="C83" s="374" t="s">
         <v>171</v>
       </c>
-      <c r="D83" s="378"/>
-      <c r="E83" s="336" t="s">
+      <c r="D83" s="375"/>
+      <c r="E83" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="F83" s="337"/>
-      <c r="G83" s="338"/>
+      <c r="F83" s="324"/>
+      <c r="G83" s="325"/>
       <c r="H83" s="64"/>
     </row>
     <row r="84" spans="2:8" ht="15.75" customHeight="1">
       <c r="B84" s="58">
         <v>9</v>
       </c>
-      <c r="C84" s="379"/>
-      <c r="D84" s="380"/>
-      <c r="E84" s="372" t="s">
+      <c r="C84" s="376"/>
+      <c r="D84" s="377"/>
+      <c r="E84" s="330" t="s">
         <v>55</v>
       </c>
-      <c r="F84" s="355" t="s">
+      <c r="F84" s="336" t="s">
         <v>172</v>
       </c>
-      <c r="G84" s="357"/>
+      <c r="G84" s="338"/>
       <c r="H84" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15736,43 +15736,43 @@
       <c r="B85" s="58">
         <v>10</v>
       </c>
-      <c r="C85" s="381"/>
-      <c r="D85" s="382"/>
-      <c r="E85" s="373"/>
-      <c r="F85" s="355" t="s">
+      <c r="C85" s="380"/>
+      <c r="D85" s="381"/>
+      <c r="E85" s="331"/>
+      <c r="F85" s="336" t="s">
         <v>173</v>
       </c>
-      <c r="G85" s="357"/>
+      <c r="G85" s="338"/>
       <c r="H85" s="64"/>
     </row>
     <row r="86" spans="2:8" ht="15.75" customHeight="1">
       <c r="B86" s="58">
         <v>11</v>
       </c>
-      <c r="C86" s="377" t="s">
+      <c r="C86" s="374" t="s">
         <v>174</v>
       </c>
-      <c r="D86" s="378"/>
-      <c r="E86" s="336" t="s">
+      <c r="D86" s="375"/>
+      <c r="E86" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="F86" s="337"/>
-      <c r="G86" s="338"/>
+      <c r="F86" s="324"/>
+      <c r="G86" s="325"/>
       <c r="H86" s="64"/>
     </row>
     <row r="87" spans="2:8" ht="15.75" customHeight="1">
       <c r="B87" s="58">
         <v>12</v>
       </c>
-      <c r="C87" s="379"/>
-      <c r="D87" s="380"/>
+      <c r="C87" s="376"/>
+      <c r="D87" s="377"/>
       <c r="E87" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F87" s="383" t="s">
-        <v>44</v>
-      </c>
-      <c r="G87" s="384"/>
+      <c r="F87" s="378" t="s">
+        <v>44</v>
+      </c>
+      <c r="G87" s="379"/>
       <c r="H87" s="64"/>
     </row>
     <row r="88" spans="2:8" ht="15.75" customHeight="1">
@@ -15788,40 +15788,40 @@
       <c r="E88" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F88" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="G88" s="347"/>
+      <c r="F88" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="G88" s="321"/>
       <c r="H88" s="64"/>
     </row>
     <row r="89" spans="2:8" ht="15.75" customHeight="1">
       <c r="B89" s="58">
         <v>14</v>
       </c>
-      <c r="C89" s="377" t="s">
+      <c r="C89" s="374" t="s">
         <v>175</v>
       </c>
-      <c r="D89" s="378"/>
-      <c r="E89" s="336" t="s">
+      <c r="D89" s="375"/>
+      <c r="E89" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="F89" s="337"/>
-      <c r="G89" s="338"/>
+      <c r="F89" s="324"/>
+      <c r="G89" s="325"/>
       <c r="H89" s="64"/>
     </row>
     <row r="90" spans="2:8" ht="15.75" customHeight="1">
       <c r="B90" s="58">
         <v>15</v>
       </c>
-      <c r="C90" s="379"/>
-      <c r="D90" s="380"/>
+      <c r="C90" s="376"/>
+      <c r="D90" s="377"/>
       <c r="E90" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F90" s="355" t="s">
+      <c r="F90" s="336" t="s">
         <v>91</v>
       </c>
-      <c r="G90" s="357"/>
+      <c r="G90" s="338"/>
       <c r="H90" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15840,10 +15840,10 @@
       <c r="E91" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F91" s="345" t="s">
+      <c r="F91" s="319" t="s">
         <v>176</v>
       </c>
-      <c r="G91" s="347"/>
+      <c r="G91" s="321"/>
       <c r="H91" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15862,40 +15862,40 @@
       <c r="E92" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F92" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="G92" s="347"/>
+      <c r="F92" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="G92" s="321"/>
       <c r="H92" s="64"/>
     </row>
     <row r="93" spans="2:8" ht="15.75" customHeight="1">
       <c r="B93" s="58">
         <v>18</v>
       </c>
-      <c r="C93" s="377" t="s">
+      <c r="C93" s="374" t="s">
         <v>177</v>
       </c>
-      <c r="D93" s="378"/>
-      <c r="E93" s="336" t="s">
+      <c r="D93" s="375"/>
+      <c r="E93" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="F93" s="337"/>
-      <c r="G93" s="338"/>
+      <c r="F93" s="324"/>
+      <c r="G93" s="325"/>
       <c r="H93" s="64"/>
     </row>
     <row r="94" spans="2:8" ht="15.75" customHeight="1">
       <c r="B94" s="58">
         <v>19</v>
       </c>
-      <c r="C94" s="379"/>
-      <c r="D94" s="380"/>
+      <c r="C94" s="376"/>
+      <c r="D94" s="377"/>
       <c r="E94" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F94" s="383" t="s">
-        <v>44</v>
-      </c>
-      <c r="G94" s="384"/>
+      <c r="F94" s="378" t="s">
+        <v>44</v>
+      </c>
+      <c r="G94" s="379"/>
       <c r="H94" s="64"/>
     </row>
     <row r="95" spans="2:8" ht="15.75" customHeight="1">
@@ -15911,8 +15911,8 @@
       <c r="E95" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F95" s="345"/>
-      <c r="G95" s="347"/>
+      <c r="F95" s="319"/>
+      <c r="G95" s="321"/>
       <c r="H95" s="64"/>
     </row>
     <row r="96" spans="2:8" ht="32.25" customHeight="1">
@@ -15928,10 +15928,10 @@
       <c r="E96" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F96" s="345" t="s">
+      <c r="F96" s="319" t="s">
         <v>8</v>
       </c>
-      <c r="G96" s="347"/>
+      <c r="G96" s="321"/>
       <c r="H96" s="64" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -15950,34 +15950,34 @@
       <c r="E97" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="F97" s="345"/>
-      <c r="G97" s="347"/>
+      <c r="F97" s="319"/>
+      <c r="G97" s="321"/>
       <c r="H97" s="64"/>
     </row>
     <row r="98" spans="2:8" ht="15.75" customHeight="1">
       <c r="B98" s="58">
         <v>24</v>
       </c>
-      <c r="C98" s="336" t="s">
+      <c r="C98" s="323" t="s">
         <v>179</v>
       </c>
-      <c r="D98" s="337"/>
-      <c r="E98" s="337"/>
-      <c r="F98" s="337"/>
-      <c r="G98" s="338"/>
+      <c r="D98" s="324"/>
+      <c r="E98" s="324"/>
+      <c r="F98" s="324"/>
+      <c r="G98" s="325"/>
       <c r="H98" s="64"/>
     </row>
     <row r="99" spans="2:8" ht="15.75" customHeight="1">
       <c r="B99" s="58">
         <v>25</v>
       </c>
-      <c r="C99" s="336" t="s">
+      <c r="C99" s="323" t="s">
         <v>180</v>
       </c>
-      <c r="D99" s="337"/>
-      <c r="E99" s="337"/>
-      <c r="F99" s="337"/>
-      <c r="G99" s="338"/>
+      <c r="D99" s="324"/>
+      <c r="E99" s="324"/>
+      <c r="F99" s="324"/>
+      <c r="G99" s="325"/>
       <c r="H99" s="64" t="e">
         <f>нак.расх.!G29*16%</f>
         <v>#REF!</v>
@@ -15985,39 +15985,54 @@
     </row>
   </sheetData>
   <mergeCells count="94">
-    <mergeCell ref="F96:G96"/>
-    <mergeCell ref="F97:G97"/>
-    <mergeCell ref="C98:G98"/>
-    <mergeCell ref="C99:G99"/>
-    <mergeCell ref="F91:G91"/>
-    <mergeCell ref="F92:G92"/>
-    <mergeCell ref="C93:D94"/>
-    <mergeCell ref="E93:G93"/>
-    <mergeCell ref="F94:G94"/>
-    <mergeCell ref="F95:G95"/>
-    <mergeCell ref="C86:D87"/>
-    <mergeCell ref="E86:G86"/>
-    <mergeCell ref="F87:G87"/>
-    <mergeCell ref="F88:G88"/>
-    <mergeCell ref="C89:D90"/>
-    <mergeCell ref="E89:G89"/>
-    <mergeCell ref="F90:G90"/>
-    <mergeCell ref="F81:G81"/>
-    <mergeCell ref="F82:G82"/>
-    <mergeCell ref="C83:D85"/>
-    <mergeCell ref="E83:G83"/>
-    <mergeCell ref="E84:E85"/>
-    <mergeCell ref="F84:G84"/>
-    <mergeCell ref="F85:G85"/>
-    <mergeCell ref="F72:G72"/>
-    <mergeCell ref="F73:G73"/>
-    <mergeCell ref="C74:G74"/>
-    <mergeCell ref="C75:G75"/>
-    <mergeCell ref="C77:D80"/>
-    <mergeCell ref="E77:G77"/>
-    <mergeCell ref="F78:G78"/>
-    <mergeCell ref="F79:G79"/>
-    <mergeCell ref="F80:G80"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="B4:H4"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="C19:G21"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="C29:D32"/>
+    <mergeCell ref="E29:G29"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="C35:D37"/>
+    <mergeCell ref="E35:G35"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="F36:G36"/>
+    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="F47:G47"/>
+    <mergeCell ref="C38:D39"/>
+    <mergeCell ref="E38:G38"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="C41:D42"/>
+    <mergeCell ref="E41:G41"/>
+    <mergeCell ref="F42:G42"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="C45:D46"/>
+    <mergeCell ref="E45:G45"/>
+    <mergeCell ref="F46:G46"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="C53:D56"/>
+    <mergeCell ref="E53:G53"/>
+    <mergeCell ref="F54:G54"/>
+    <mergeCell ref="F55:G55"/>
+    <mergeCell ref="F56:G56"/>
+    <mergeCell ref="F57:G57"/>
+    <mergeCell ref="F58:G58"/>
+    <mergeCell ref="C59:D61"/>
+    <mergeCell ref="E59:G59"/>
+    <mergeCell ref="E60:E61"/>
+    <mergeCell ref="F60:G60"/>
+    <mergeCell ref="F61:G61"/>
     <mergeCell ref="F71:G71"/>
     <mergeCell ref="C62:D63"/>
     <mergeCell ref="E62:G62"/>
@@ -16031,54 +16046,39 @@
     <mergeCell ref="C69:D70"/>
     <mergeCell ref="E69:G69"/>
     <mergeCell ref="F70:G70"/>
-    <mergeCell ref="F57:G57"/>
-    <mergeCell ref="F58:G58"/>
-    <mergeCell ref="C59:D61"/>
-    <mergeCell ref="E59:G59"/>
-    <mergeCell ref="E60:E61"/>
-    <mergeCell ref="F60:G60"/>
-    <mergeCell ref="F61:G61"/>
-    <mergeCell ref="F48:G48"/>
-    <mergeCell ref="F49:G49"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="C53:D56"/>
-    <mergeCell ref="E53:G53"/>
-    <mergeCell ref="F54:G54"/>
-    <mergeCell ref="F55:G55"/>
-    <mergeCell ref="F56:G56"/>
-    <mergeCell ref="F47:G47"/>
-    <mergeCell ref="C38:D39"/>
-    <mergeCell ref="E38:G38"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="C41:D42"/>
-    <mergeCell ref="E41:G41"/>
-    <mergeCell ref="F42:G42"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="F44:G44"/>
-    <mergeCell ref="C45:D46"/>
-    <mergeCell ref="E45:G45"/>
-    <mergeCell ref="F46:G46"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="C35:D37"/>
-    <mergeCell ref="E35:G35"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="F36:G36"/>
-    <mergeCell ref="F37:G37"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="B3:H3"/>
-    <mergeCell ref="B4:H4"/>
-    <mergeCell ref="B19:B21"/>
-    <mergeCell ref="C19:G21"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="C29:D32"/>
-    <mergeCell ref="E29:G29"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="F72:G72"/>
+    <mergeCell ref="F73:G73"/>
+    <mergeCell ref="C74:G74"/>
+    <mergeCell ref="C75:G75"/>
+    <mergeCell ref="C77:D80"/>
+    <mergeCell ref="E77:G77"/>
+    <mergeCell ref="F78:G78"/>
+    <mergeCell ref="F79:G79"/>
+    <mergeCell ref="F80:G80"/>
+    <mergeCell ref="F81:G81"/>
+    <mergeCell ref="F82:G82"/>
+    <mergeCell ref="C83:D85"/>
+    <mergeCell ref="E83:G83"/>
+    <mergeCell ref="E84:E85"/>
+    <mergeCell ref="F84:G84"/>
+    <mergeCell ref="F85:G85"/>
+    <mergeCell ref="C86:D87"/>
+    <mergeCell ref="E86:G86"/>
+    <mergeCell ref="F87:G87"/>
+    <mergeCell ref="F88:G88"/>
+    <mergeCell ref="C89:D90"/>
+    <mergeCell ref="E89:G89"/>
+    <mergeCell ref="F90:G90"/>
+    <mergeCell ref="F96:G96"/>
+    <mergeCell ref="F97:G97"/>
+    <mergeCell ref="C98:G98"/>
+    <mergeCell ref="C99:G99"/>
+    <mergeCell ref="F91:G91"/>
+    <mergeCell ref="F92:G92"/>
+    <mergeCell ref="C93:D94"/>
+    <mergeCell ref="E93:G93"/>
+    <mergeCell ref="F94:G94"/>
+    <mergeCell ref="F95:G95"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="76" orientation="portrait" r:id="rId1"/>
@@ -16107,14 +16107,14 @@
       <c r="A1" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="319" t="s">
+      <c r="B1" s="357" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="319"/>
-      <c r="D1" s="319"/>
-      <c r="E1" s="319"/>
-      <c r="F1" s="319"/>
-      <c r="G1" s="319"/>
+      <c r="C1" s="357"/>
+      <c r="D1" s="357"/>
+      <c r="E1" s="357"/>
+      <c r="F1" s="357"/>
+      <c r="G1" s="357"/>
       <c r="K1" s="51"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" customHeight="1">
@@ -16145,69 +16145,69 @@
       <c r="A3" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="319" t="s">
+      <c r="B3" s="357" t="s">
         <v>182</v>
       </c>
-      <c r="C3" s="319"/>
-      <c r="D3" s="319"/>
-      <c r="E3" s="319"/>
-      <c r="F3" s="319"/>
-      <c r="G3" s="319"/>
+      <c r="C3" s="357"/>
+      <c r="D3" s="357"/>
+      <c r="E3" s="357"/>
+      <c r="F3" s="357"/>
+      <c r="G3" s="357"/>
       <c r="K3" s="51"/>
     </row>
     <row r="4" spans="1:11" ht="14.25" customHeight="1">
       <c r="A4" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="321" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="321"/>
-      <c r="D4" s="321"/>
-      <c r="E4" s="321"/>
-      <c r="F4" s="321"/>
-      <c r="G4" s="321"/>
+      <c r="B4" s="359" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="359"/>
+      <c r="D4" s="359"/>
+      <c r="E4" s="359"/>
+      <c r="F4" s="359"/>
+      <c r="G4" s="359"/>
       <c r="K4" s="51"/>
     </row>
     <row r="5" spans="1:11" ht="24.75" customHeight="1">
       <c r="A5" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="322" t="s">
+      <c r="B5" s="360" t="s">
         <v>47</v>
       </c>
-      <c r="C5" s="322"/>
-      <c r="D5" s="322"/>
-      <c r="E5" s="322"/>
-      <c r="F5" s="322"/>
-      <c r="G5" s="322"/>
+      <c r="C5" s="360"/>
+      <c r="D5" s="360"/>
+      <c r="E5" s="360"/>
+      <c r="F5" s="360"/>
+      <c r="G5" s="360"/>
       <c r="K5" s="51"/>
     </row>
     <row r="6" spans="1:11" ht="12" customHeight="1">
       <c r="A6" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B6" s="322" t="s">
+      <c r="B6" s="360" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="322"/>
-      <c r="D6" s="322"/>
-      <c r="E6" s="322"/>
-      <c r="F6" s="322"/>
-      <c r="G6" s="322"/>
+      <c r="C6" s="360"/>
+      <c r="D6" s="360"/>
+      <c r="E6" s="360"/>
+      <c r="F6" s="360"/>
+      <c r="G6" s="360"/>
       <c r="K6" s="51"/>
     </row>
     <row r="7" spans="1:11" ht="12" customHeight="1">
       <c r="A7" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="B7" s="323" t="s">
+      <c r="B7" s="361" t="s">
         <v>183</v>
       </c>
-      <c r="C7" s="323"/>
-      <c r="D7" s="323"/>
-      <c r="E7" s="323"/>
-      <c r="F7" s="323"/>
+      <c r="C7" s="361"/>
+      <c r="D7" s="361"/>
+      <c r="E7" s="361"/>
+      <c r="F7" s="361"/>
       <c r="G7" s="71" t="s">
         <v>50</v>
       </c>
@@ -16231,37 +16231,37 @@
       <c r="A22" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B22" s="324" t="s">
+      <c r="B22" s="362" t="s">
         <v>0</v>
       </c>
-      <c r="C22" s="327" t="s">
+      <c r="C22" s="365" t="s">
         <v>51</v>
       </c>
-      <c r="D22" s="328"/>
-      <c r="E22" s="328"/>
-      <c r="F22" s="329"/>
+      <c r="D22" s="366"/>
+      <c r="E22" s="366"/>
+      <c r="F22" s="367"/>
       <c r="G22" s="55"/>
     </row>
     <row r="23" spans="1:12" ht="12" customHeight="1">
       <c r="A23" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="325"/>
-      <c r="C23" s="330"/>
-      <c r="D23" s="331"/>
-      <c r="E23" s="331"/>
-      <c r="F23" s="332"/>
+      <c r="B23" s="363"/>
+      <c r="C23" s="368"/>
+      <c r="D23" s="369"/>
+      <c r="E23" s="369"/>
+      <c r="F23" s="370"/>
       <c r="G23" s="55"/>
     </row>
     <row r="24" spans="1:12" ht="24" customHeight="1">
       <c r="A24" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B24" s="326"/>
-      <c r="C24" s="333"/>
-      <c r="D24" s="334"/>
-      <c r="E24" s="334"/>
-      <c r="F24" s="335"/>
+      <c r="B24" s="364"/>
+      <c r="C24" s="371"/>
+      <c r="D24" s="372"/>
+      <c r="E24" s="372"/>
+      <c r="F24" s="373"/>
       <c r="G24" s="57" t="s">
         <v>52</v>
       </c>
@@ -16282,10 +16282,10 @@
       <c r="D28" s="57">
         <v>3</v>
       </c>
-      <c r="E28" s="375">
+      <c r="E28" s="383">
         <v>4</v>
       </c>
-      <c r="F28" s="376"/>
+      <c r="F28" s="384"/>
       <c r="G28" s="57">
         <v>8</v>
       </c>
@@ -16297,12 +16297,12 @@
       <c r="B29" s="58">
         <v>1</v>
       </c>
-      <c r="C29" s="336" t="s">
+      <c r="C29" s="323" t="s">
         <v>184</v>
       </c>
-      <c r="D29" s="337"/>
-      <c r="E29" s="337"/>
-      <c r="F29" s="337"/>
+      <c r="D29" s="324"/>
+      <c r="E29" s="324"/>
+      <c r="F29" s="324"/>
       <c r="G29" s="72" t="e">
         <f>SUM(G30:G77)</f>
         <v>#REF!</v>
@@ -16322,11 +16322,11 @@
       <c r="C30" s="73" t="s">
         <v>54</v>
       </c>
-      <c r="D30" s="336" t="s">
+      <c r="D30" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E30" s="337"/>
-      <c r="F30" s="337"/>
+      <c r="E30" s="324"/>
+      <c r="F30" s="324"/>
       <c r="G30" s="74"/>
       <c r="L30" s="53" t="e">
         <f>G29-L29</f>
@@ -16346,10 +16346,10 @@
       <c r="D31" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E31" s="355" t="s">
+      <c r="E31" s="336" t="s">
         <v>56</v>
       </c>
-      <c r="F31" s="356"/>
+      <c r="F31" s="337"/>
       <c r="G31" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16369,10 +16369,10 @@
       <c r="D32" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E32" s="355" t="s">
+      <c r="E32" s="336" t="s">
         <v>57</v>
       </c>
-      <c r="F32" s="356"/>
+      <c r="F32" s="337"/>
       <c r="G32" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16392,10 +16392,10 @@
       <c r="D33" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E33" s="355" t="s">
+      <c r="E33" s="336" t="s">
         <v>58</v>
       </c>
-      <c r="F33" s="356"/>
+      <c r="F33" s="337"/>
       <c r="G33" s="74"/>
     </row>
     <row r="34" spans="1:13" ht="12" customHeight="1">
@@ -16452,10 +16452,10 @@
       <c r="D36" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E36" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="F36" s="346"/>
+      <c r="E36" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="F36" s="320"/>
       <c r="G36" s="74"/>
       <c r="H36" s="49"/>
     </row>
@@ -16469,11 +16469,11 @@
       <c r="C37" s="73" t="s">
         <v>171</v>
       </c>
-      <c r="D37" s="336" t="s">
+      <c r="D37" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E37" s="337"/>
-      <c r="F37" s="337"/>
+      <c r="E37" s="324"/>
+      <c r="F37" s="324"/>
       <c r="G37" s="74"/>
     </row>
     <row r="38" spans="1:13" ht="12" customHeight="1">
@@ -16489,10 +16489,10 @@
       <c r="D38" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E38" s="355" t="s">
+      <c r="E38" s="336" t="s">
         <v>172</v>
       </c>
-      <c r="F38" s="356"/>
+      <c r="F38" s="337"/>
       <c r="G38" s="74" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -16512,10 +16512,10 @@
       <c r="D39" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E39" s="355" t="s">
+      <c r="E39" s="336" t="s">
         <v>173</v>
       </c>
-      <c r="F39" s="356"/>
+      <c r="F39" s="337"/>
       <c r="G39" s="74"/>
     </row>
     <row r="40" spans="1:13" ht="12" customHeight="1">
@@ -16525,14 +16525,14 @@
       <c r="B40" s="58">
         <v>26</v>
       </c>
-      <c r="C40" s="339" t="s">
+      <c r="C40" s="332" t="s">
         <v>174</v>
       </c>
-      <c r="D40" s="336" t="s">
+      <c r="D40" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E40" s="337"/>
-      <c r="F40" s="337"/>
+      <c r="E40" s="324"/>
+      <c r="F40" s="324"/>
       <c r="G40" s="74"/>
     </row>
     <row r="41" spans="1:13" ht="12" customHeight="1">
@@ -16542,14 +16542,14 @@
       <c r="B41" s="58">
         <v>27</v>
       </c>
-      <c r="C41" s="340"/>
+      <c r="C41" s="333"/>
       <c r="D41" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E41" s="383" t="s">
-        <v>44</v>
-      </c>
-      <c r="F41" s="385"/>
+      <c r="E41" s="378" t="s">
+        <v>44</v>
+      </c>
+      <c r="F41" s="386"/>
       <c r="G41" s="74"/>
     </row>
     <row r="42" spans="1:13" ht="12" customHeight="1">
@@ -16565,10 +16565,10 @@
       <c r="D42" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E42" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="F42" s="346"/>
+      <c r="E42" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="F42" s="320"/>
       <c r="G42" s="74"/>
       <c r="H42" s="49"/>
     </row>
@@ -16579,14 +16579,14 @@
       <c r="B43" s="58">
         <v>29</v>
       </c>
-      <c r="C43" s="339" t="s">
+      <c r="C43" s="332" t="s">
         <v>186</v>
       </c>
-      <c r="D43" s="336" t="s">
+      <c r="D43" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E43" s="337"/>
-      <c r="F43" s="337"/>
+      <c r="E43" s="324"/>
+      <c r="F43" s="324"/>
       <c r="G43" s="74"/>
     </row>
     <row r="44" spans="1:13" ht="12" customHeight="1">
@@ -16596,14 +16596,14 @@
       <c r="B44" s="58">
         <v>30</v>
       </c>
-      <c r="C44" s="340"/>
+      <c r="C44" s="333"/>
       <c r="D44" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E44" s="345" t="s">
+      <c r="E44" s="319" t="s">
         <v>128</v>
       </c>
-      <c r="F44" s="346"/>
+      <c r="F44" s="320"/>
       <c r="G44" s="74"/>
     </row>
     <row r="45" spans="1:13" ht="18.75" customHeight="1">
@@ -16613,14 +16613,14 @@
       <c r="B45" s="58">
         <v>31</v>
       </c>
-      <c r="C45" s="341"/>
+      <c r="C45" s="349"/>
       <c r="D45" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E45" s="386" t="s">
+      <c r="E45" s="389" t="s">
         <v>129</v>
       </c>
-      <c r="F45" s="387"/>
+      <c r="F45" s="390"/>
       <c r="G45" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16635,12 +16635,12 @@
       <c r="B46" s="58">
         <v>32</v>
       </c>
-      <c r="C46" s="336" t="s">
+      <c r="C46" s="323" t="s">
         <v>20</v>
       </c>
-      <c r="D46" s="337"/>
-      <c r="E46" s="337"/>
-      <c r="F46" s="337"/>
+      <c r="D46" s="324"/>
+      <c r="E46" s="324"/>
+      <c r="F46" s="324"/>
       <c r="G46" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16657,11 +16657,11 @@
       <c r="C47" s="73" t="s">
         <v>62</v>
       </c>
-      <c r="D47" s="336" t="s">
+      <c r="D47" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E47" s="337"/>
-      <c r="F47" s="337"/>
+      <c r="E47" s="324"/>
+      <c r="F47" s="324"/>
       <c r="G47" s="74"/>
       <c r="L47" s="53"/>
     </row>
@@ -16678,10 +16678,10 @@
       <c r="D48" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E48" s="355" t="s">
+      <c r="E48" s="336" t="s">
         <v>63</v>
       </c>
-      <c r="F48" s="356"/>
+      <c r="F48" s="337"/>
       <c r="G48" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16700,10 +16700,10 @@
       <c r="D49" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E49" s="355" t="s">
+      <c r="E49" s="336" t="s">
         <v>64</v>
       </c>
-      <c r="F49" s="356"/>
+      <c r="F49" s="337"/>
       <c r="G49" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16716,14 +16716,14 @@
       <c r="B50" s="58">
         <v>36</v>
       </c>
-      <c r="C50" s="339" t="s">
+      <c r="C50" s="332" t="s">
         <v>187</v>
       </c>
-      <c r="D50" s="336" t="s">
+      <c r="D50" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E50" s="337"/>
-      <c r="F50" s="337"/>
+      <c r="E50" s="324"/>
+      <c r="F50" s="324"/>
       <c r="G50" s="74"/>
     </row>
     <row r="51" spans="1:8" ht="12" customHeight="1">
@@ -16733,14 +16733,14 @@
       <c r="B51" s="58">
         <v>37</v>
       </c>
-      <c r="C51" s="340"/>
+      <c r="C51" s="333"/>
       <c r="D51" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E51" s="383" t="s">
-        <v>44</v>
-      </c>
-      <c r="F51" s="385"/>
+      <c r="E51" s="378" t="s">
+        <v>44</v>
+      </c>
+      <c r="F51" s="386"/>
       <c r="G51" s="74"/>
     </row>
     <row r="52" spans="1:8" ht="24.75" customHeight="1">
@@ -16756,10 +16756,10 @@
       <c r="D52" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E52" s="345" t="s">
+      <c r="E52" s="319" t="s">
         <v>188</v>
       </c>
-      <c r="F52" s="346"/>
+      <c r="F52" s="320"/>
       <c r="G52" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16773,12 +16773,12 @@
       <c r="B53" s="58">
         <v>43</v>
       </c>
-      <c r="C53" s="336" t="s">
+      <c r="C53" s="323" t="s">
         <v>16</v>
       </c>
-      <c r="D53" s="337"/>
-      <c r="E53" s="337"/>
-      <c r="F53" s="337"/>
+      <c r="D53" s="324"/>
+      <c r="E53" s="324"/>
+      <c r="F53" s="324"/>
       <c r="G53" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16791,12 +16791,12 @@
       <c r="B54" s="58">
         <v>44</v>
       </c>
-      <c r="C54" s="336" t="s">
+      <c r="C54" s="323" t="s">
         <v>14</v>
       </c>
-      <c r="D54" s="337"/>
-      <c r="E54" s="337"/>
-      <c r="F54" s="337"/>
+      <c r="D54" s="324"/>
+      <c r="E54" s="324"/>
+      <c r="F54" s="324"/>
       <c r="G54" s="74"/>
     </row>
     <row r="55" spans="1:8" ht="12" customHeight="1">
@@ -16809,11 +16809,11 @@
       <c r="C55" s="73" t="s">
         <v>137</v>
       </c>
-      <c r="D55" s="336" t="s">
+      <c r="D55" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E55" s="337"/>
-      <c r="F55" s="337"/>
+      <c r="E55" s="324"/>
+      <c r="F55" s="324"/>
       <c r="G55" s="74"/>
     </row>
     <row r="56" spans="1:8" ht="12" customHeight="1">
@@ -16829,10 +16829,10 @@
       <c r="D56" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E56" s="383" t="s">
-        <v>44</v>
-      </c>
-      <c r="F56" s="385"/>
+      <c r="E56" s="378" t="s">
+        <v>44</v>
+      </c>
+      <c r="F56" s="386"/>
       <c r="G56" s="74"/>
     </row>
     <row r="57" spans="1:8" ht="24.75" customHeight="1">
@@ -16848,10 +16848,10 @@
       <c r="D57" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E57" s="345" t="s">
+      <c r="E57" s="319" t="s">
         <v>4</v>
       </c>
-      <c r="F57" s="346"/>
+      <c r="F57" s="320"/>
       <c r="G57" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16871,10 +16871,10 @@
       <c r="D58" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E58" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="F58" s="346"/>
+      <c r="E58" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="F58" s="320"/>
       <c r="G58" s="74"/>
       <c r="H58" s="49"/>
     </row>
@@ -16885,12 +16885,12 @@
       <c r="B59" s="58">
         <v>51</v>
       </c>
-      <c r="C59" s="336" t="s">
+      <c r="C59" s="323" t="s">
         <v>189</v>
       </c>
-      <c r="D59" s="337"/>
-      <c r="E59" s="337"/>
-      <c r="F59" s="337"/>
+      <c r="D59" s="324"/>
+      <c r="E59" s="324"/>
+      <c r="F59" s="324"/>
       <c r="G59" s="74"/>
     </row>
     <row r="60" spans="1:8" ht="12" customHeight="1">
@@ -16900,12 +16900,12 @@
       <c r="B60" s="58">
         <v>52</v>
       </c>
-      <c r="C60" s="336" t="s">
+      <c r="C60" s="323" t="s">
         <v>17</v>
       </c>
-      <c r="D60" s="337"/>
-      <c r="E60" s="337"/>
-      <c r="F60" s="337"/>
+      <c r="D60" s="324"/>
+      <c r="E60" s="324"/>
+      <c r="F60" s="324"/>
       <c r="G60" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16918,12 +16918,12 @@
       <c r="B61" s="58">
         <v>53</v>
       </c>
-      <c r="C61" s="336" t="s">
+      <c r="C61" s="323" t="s">
         <v>190</v>
       </c>
-      <c r="D61" s="337"/>
-      <c r="E61" s="337"/>
-      <c r="F61" s="337"/>
+      <c r="D61" s="324"/>
+      <c r="E61" s="324"/>
+      <c r="F61" s="324"/>
       <c r="G61" s="74"/>
     </row>
     <row r="62" spans="1:8" ht="12" customHeight="1">
@@ -16933,12 +16933,12 @@
       <c r="B62" s="58">
         <v>54</v>
       </c>
-      <c r="C62" s="336" t="s">
+      <c r="C62" s="323" t="s">
         <v>191</v>
       </c>
-      <c r="D62" s="337"/>
-      <c r="E62" s="337"/>
-      <c r="F62" s="337"/>
+      <c r="D62" s="324"/>
+      <c r="E62" s="324"/>
+      <c r="F62" s="324"/>
       <c r="G62" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16951,12 +16951,12 @@
       <c r="B63" s="58">
         <v>55</v>
       </c>
-      <c r="C63" s="336" t="s">
+      <c r="C63" s="323" t="s">
         <v>192</v>
       </c>
-      <c r="D63" s="337"/>
-      <c r="E63" s="337"/>
-      <c r="F63" s="337"/>
+      <c r="D63" s="324"/>
+      <c r="E63" s="324"/>
+      <c r="F63" s="324"/>
       <c r="G63" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -16969,14 +16969,14 @@
       <c r="B64" s="58">
         <v>56</v>
       </c>
-      <c r="C64" s="339" t="s">
+      <c r="C64" s="332" t="s">
         <v>175</v>
       </c>
-      <c r="D64" s="336" t="s">
+      <c r="D64" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E64" s="337"/>
-      <c r="F64" s="337"/>
+      <c r="E64" s="324"/>
+      <c r="F64" s="324"/>
       <c r="G64" s="74"/>
     </row>
     <row r="65" spans="1:11" ht="12" customHeight="1">
@@ -16986,14 +16986,14 @@
       <c r="B65" s="58">
         <v>57</v>
       </c>
-      <c r="C65" s="340"/>
+      <c r="C65" s="333"/>
       <c r="D65" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E65" s="355" t="s">
+      <c r="E65" s="336" t="s">
         <v>91</v>
       </c>
-      <c r="F65" s="356"/>
+      <c r="F65" s="337"/>
       <c r="G65" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17012,10 +17012,10 @@
       <c r="D66" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E66" s="345" t="s">
+      <c r="E66" s="319" t="s">
         <v>193</v>
       </c>
-      <c r="F66" s="346"/>
+      <c r="F66" s="320"/>
       <c r="G66" s="74"/>
       <c r="H66" s="49"/>
     </row>
@@ -17026,14 +17026,14 @@
       <c r="B67" s="58">
         <v>59</v>
       </c>
-      <c r="C67" s="339" t="s">
+      <c r="C67" s="332" t="s">
         <v>102</v>
       </c>
-      <c r="D67" s="336" t="s">
+      <c r="D67" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E67" s="337"/>
-      <c r="F67" s="337"/>
+      <c r="E67" s="324"/>
+      <c r="F67" s="324"/>
       <c r="G67" s="74"/>
     </row>
     <row r="68" spans="1:11" ht="12" customHeight="1">
@@ -17043,14 +17043,14 @@
       <c r="B68" s="58">
         <v>60</v>
       </c>
-      <c r="C68" s="340"/>
+      <c r="C68" s="333"/>
       <c r="D68" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E68" s="383" t="s">
-        <v>44</v>
-      </c>
-      <c r="F68" s="385"/>
+      <c r="E68" s="378" t="s">
+        <v>44</v>
+      </c>
+      <c r="F68" s="386"/>
       <c r="G68" s="74"/>
     </row>
     <row r="69" spans="1:11" ht="12" customHeight="1">
@@ -17066,10 +17066,10 @@
       <c r="D69" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E69" s="345" t="s">
+      <c r="E69" s="319" t="s">
         <v>194</v>
       </c>
-      <c r="F69" s="346"/>
+      <c r="F69" s="320"/>
       <c r="G69" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17089,10 +17089,10 @@
       <c r="D70" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E70" s="345" t="s">
+      <c r="E70" s="319" t="s">
         <v>195</v>
       </c>
-      <c r="F70" s="346"/>
+      <c r="F70" s="320"/>
       <c r="G70" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17112,10 +17112,10 @@
       <c r="D71" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E71" s="388" t="s">
+      <c r="E71" s="387" t="s">
         <v>196</v>
       </c>
-      <c r="F71" s="389"/>
+      <c r="F71" s="388"/>
       <c r="G71" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17127,10 +17127,10 @@
       <c r="B72" s="58"/>
       <c r="C72" s="77"/>
       <c r="D72" s="70"/>
-      <c r="E72" s="388" t="s">
+      <c r="E72" s="387" t="s">
         <v>13</v>
       </c>
-      <c r="F72" s="389"/>
+      <c r="F72" s="388"/>
       <c r="G72" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17142,10 +17142,10 @@
       <c r="B73" s="58"/>
       <c r="C73" s="77"/>
       <c r="D73" s="70"/>
-      <c r="E73" s="388" t="s">
+      <c r="E73" s="387" t="s">
         <v>8</v>
       </c>
-      <c r="F73" s="389"/>
+      <c r="F73" s="388"/>
       <c r="G73" s="74" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17165,10 +17165,10 @@
       <c r="D74" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E74" s="345" t="s">
-        <v>44</v>
-      </c>
-      <c r="F74" s="346"/>
+      <c r="E74" s="319" t="s">
+        <v>44</v>
+      </c>
+      <c r="F74" s="320"/>
       <c r="G74" s="74"/>
       <c r="H74" s="49"/>
     </row>
@@ -17179,14 +17179,14 @@
       <c r="B75" s="58">
         <v>65</v>
       </c>
-      <c r="C75" s="339" t="s">
+      <c r="C75" s="332" t="s">
         <v>197</v>
       </c>
-      <c r="D75" s="336" t="s">
+      <c r="D75" s="323" t="s">
         <v>5</v>
       </c>
-      <c r="E75" s="337"/>
-      <c r="F75" s="337"/>
+      <c r="E75" s="324"/>
+      <c r="F75" s="324"/>
       <c r="G75" s="74"/>
     </row>
     <row r="76" spans="1:11" ht="12" customHeight="1">
@@ -17196,14 +17196,14 @@
       <c r="B76" s="58">
         <v>66</v>
       </c>
-      <c r="C76" s="340"/>
+      <c r="C76" s="333"/>
       <c r="D76" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="E76" s="383" t="s">
-        <v>44</v>
-      </c>
-      <c r="F76" s="385"/>
+      <c r="E76" s="378" t="s">
+        <v>44</v>
+      </c>
+      <c r="F76" s="386"/>
       <c r="G76" s="74"/>
     </row>
     <row r="77" spans="1:11" ht="12" customHeight="1">
@@ -17219,10 +17219,10 @@
       <c r="D77" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E77" s="345" t="s">
+      <c r="E77" s="319" t="s">
         <v>198</v>
       </c>
-      <c r="F77" s="346"/>
+      <c r="F77" s="320"/>
       <c r="G77" s="81" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -17281,13 +17281,13 @@
       <c r="K79" s="51"/>
     </row>
     <row r="80" spans="1:11" ht="15" customHeight="1">
-      <c r="B80" s="390" t="s">
+      <c r="B80" s="385" t="s">
         <v>199</v>
       </c>
-      <c r="C80" s="390"/>
-      <c r="D80" s="390"/>
-      <c r="E80" s="390"/>
-      <c r="F80" s="390"/>
+      <c r="C80" s="385"/>
+      <c r="D80" s="385"/>
+      <c r="E80" s="385"/>
+      <c r="F80" s="385"/>
       <c r="G80" s="83"/>
       <c r="H80" s="83"/>
       <c r="I80" s="82"/>
@@ -17295,13 +17295,13 @@
       <c r="K80" s="51"/>
     </row>
     <row r="81" spans="2:11" ht="15" customHeight="1">
-      <c r="B81" s="390" t="s">
-        <v>44</v>
-      </c>
-      <c r="C81" s="390"/>
-      <c r="D81" s="390"/>
-      <c r="E81" s="390"/>
-      <c r="F81" s="390"/>
+      <c r="B81" s="385" t="s">
+        <v>44</v>
+      </c>
+      <c r="C81" s="385"/>
+      <c r="D81" s="385"/>
+      <c r="E81" s="385"/>
+      <c r="F81" s="385"/>
       <c r="G81" s="84"/>
       <c r="H81" s="84"/>
       <c r="I81" s="83"/>
@@ -17311,14 +17311,14 @@
     <row r="82" spans="2:11" ht="15.75" hidden="1" customHeight="1"/>
     <row r="83" spans="2:11" ht="15.75" hidden="1" customHeight="1"/>
     <row r="84" spans="2:11" ht="15" customHeight="1">
-      <c r="B84" s="390" t="s">
+      <c r="B84" s="385" t="s">
         <v>200</v>
       </c>
-      <c r="C84" s="390"/>
-      <c r="D84" s="390"/>
-      <c r="E84" s="390"/>
-      <c r="F84" s="390"/>
-      <c r="G84" s="390"/>
+      <c r="C84" s="385"/>
+      <c r="D84" s="385"/>
+      <c r="E84" s="385"/>
+      <c r="F84" s="385"/>
+      <c r="G84" s="385"/>
       <c r="H84" s="83"/>
       <c r="I84" s="83"/>
       <c r="J84" s="83"/>
@@ -17347,13 +17347,51 @@
     <row r="105" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="65">
-    <mergeCell ref="B84:G84"/>
-    <mergeCell ref="C75:C76"/>
-    <mergeCell ref="D75:F75"/>
-    <mergeCell ref="E76:F76"/>
-    <mergeCell ref="E77:F77"/>
-    <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="B6:G6"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="B22:B24"/>
+    <mergeCell ref="C22:F24"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="E38:F38"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="D40:F40"/>
+    <mergeCell ref="E41:F41"/>
+    <mergeCell ref="E42:F42"/>
+    <mergeCell ref="C43:C45"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="E44:F44"/>
+    <mergeCell ref="E45:F45"/>
+    <mergeCell ref="C46:F46"/>
+    <mergeCell ref="D47:F47"/>
+    <mergeCell ref="E48:F48"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="D50:F50"/>
+    <mergeCell ref="E51:F51"/>
+    <mergeCell ref="C63:F63"/>
+    <mergeCell ref="E52:F52"/>
+    <mergeCell ref="C53:F53"/>
+    <mergeCell ref="C54:F54"/>
+    <mergeCell ref="D55:F55"/>
+    <mergeCell ref="E56:F56"/>
+    <mergeCell ref="E57:F57"/>
+    <mergeCell ref="E58:F58"/>
+    <mergeCell ref="C59:F59"/>
+    <mergeCell ref="C60:F60"/>
+    <mergeCell ref="C61:F61"/>
+    <mergeCell ref="C62:F62"/>
     <mergeCell ref="E74:F74"/>
     <mergeCell ref="C64:C65"/>
     <mergeCell ref="D64:F64"/>
@@ -17367,51 +17405,13 @@
     <mergeCell ref="E71:F71"/>
     <mergeCell ref="E72:F72"/>
     <mergeCell ref="E73:F73"/>
-    <mergeCell ref="C63:F63"/>
-    <mergeCell ref="E52:F52"/>
-    <mergeCell ref="C53:F53"/>
-    <mergeCell ref="C54:F54"/>
-    <mergeCell ref="D55:F55"/>
-    <mergeCell ref="E56:F56"/>
-    <mergeCell ref="E57:F57"/>
-    <mergeCell ref="E58:F58"/>
-    <mergeCell ref="C59:F59"/>
-    <mergeCell ref="C60:F60"/>
-    <mergeCell ref="C61:F61"/>
-    <mergeCell ref="C62:F62"/>
-    <mergeCell ref="C46:F46"/>
-    <mergeCell ref="D47:F47"/>
-    <mergeCell ref="E48:F48"/>
-    <mergeCell ref="E49:F49"/>
-    <mergeCell ref="C50:C51"/>
-    <mergeCell ref="D50:F50"/>
-    <mergeCell ref="E51:F51"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="D40:F40"/>
-    <mergeCell ref="E41:F41"/>
-    <mergeCell ref="E42:F42"/>
-    <mergeCell ref="C43:C45"/>
-    <mergeCell ref="D43:F43"/>
-    <mergeCell ref="E44:F44"/>
-    <mergeCell ref="E45:F45"/>
-    <mergeCell ref="E39:F39"/>
-    <mergeCell ref="B22:B24"/>
-    <mergeCell ref="C22:F24"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="E36:F36"/>
-    <mergeCell ref="D37:F37"/>
-    <mergeCell ref="E38:F38"/>
-    <mergeCell ref="B7:F7"/>
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="B4:G4"/>
-    <mergeCell ref="B5:G5"/>
-    <mergeCell ref="B6:G6"/>
+    <mergeCell ref="B84:G84"/>
+    <mergeCell ref="C75:C76"/>
+    <mergeCell ref="D75:F75"/>
+    <mergeCell ref="E76:F76"/>
+    <mergeCell ref="E77:F77"/>
+    <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Наименование на государственном языке заполняется автоматически в соответствии с КТРУ" sqref="B76 B49:B50 B95:B96"/>
@@ -17447,79 +17447,79 @@
       <c r="A1" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="430" t="s">
+      <c r="B1" s="399" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="430"/>
-      <c r="D1" s="430"/>
-      <c r="E1" s="430"/>
-      <c r="F1" s="430"/>
-      <c r="G1" s="430"/>
-      <c r="H1" s="430"/>
-      <c r="I1" s="430"/>
+      <c r="C1" s="399"/>
+      <c r="D1" s="399"/>
+      <c r="E1" s="399"/>
+      <c r="F1" s="399"/>
+      <c r="G1" s="399"/>
+      <c r="H1" s="399"/>
+      <c r="I1" s="399"/>
       <c r="M1" s="12"/>
     </row>
     <row r="2" spans="1:13" ht="14.25" customHeight="1">
       <c r="A2" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="431" t="s">
+      <c r="B2" s="400" t="s">
         <v>46</v>
       </c>
-      <c r="C2" s="431"/>
-      <c r="D2" s="431"/>
-      <c r="E2" s="431"/>
-      <c r="F2" s="431"/>
-      <c r="G2" s="431"/>
-      <c r="H2" s="431"/>
-      <c r="I2" s="431"/>
+      <c r="C2" s="400"/>
+      <c r="D2" s="400"/>
+      <c r="E2" s="400"/>
+      <c r="F2" s="400"/>
+      <c r="G2" s="400"/>
+      <c r="H2" s="400"/>
+      <c r="I2" s="400"/>
       <c r="M2" s="12"/>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="432" t="s">
+      <c r="B3" s="401" t="s">
         <v>47</v>
       </c>
-      <c r="C3" s="432"/>
-      <c r="D3" s="432"/>
-      <c r="E3" s="432"/>
-      <c r="F3" s="432"/>
-      <c r="G3" s="432"/>
-      <c r="H3" s="432"/>
-      <c r="I3" s="432"/>
+      <c r="C3" s="401"/>
+      <c r="D3" s="401"/>
+      <c r="E3" s="401"/>
+      <c r="F3" s="401"/>
+      <c r="G3" s="401"/>
+      <c r="H3" s="401"/>
+      <c r="I3" s="401"/>
       <c r="M3" s="12"/>
     </row>
     <row r="4" spans="1:13" ht="30" customHeight="1">
       <c r="A4" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="432" t="s">
+      <c r="B4" s="401" t="s">
         <v>48</v>
       </c>
-      <c r="C4" s="432"/>
-      <c r="D4" s="432"/>
-      <c r="E4" s="432"/>
-      <c r="F4" s="432"/>
-      <c r="G4" s="432"/>
-      <c r="H4" s="432"/>
-      <c r="I4" s="432"/>
+      <c r="C4" s="401"/>
+      <c r="D4" s="401"/>
+      <c r="E4" s="401"/>
+      <c r="F4" s="401"/>
+      <c r="G4" s="401"/>
+      <c r="H4" s="401"/>
+      <c r="I4" s="401"/>
       <c r="M4" s="12"/>
     </row>
     <row r="5" spans="1:13" ht="12" customHeight="1">
       <c r="A5" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="433" t="s">
+      <c r="B5" s="402" t="s">
         <v>49</v>
       </c>
-      <c r="C5" s="433"/>
-      <c r="D5" s="433"/>
-      <c r="E5" s="433"/>
-      <c r="F5" s="433"/>
-      <c r="G5" s="433"/>
-      <c r="H5" s="433"/>
+      <c r="C5" s="402"/>
+      <c r="D5" s="402"/>
+      <c r="E5" s="402"/>
+      <c r="F5" s="402"/>
+      <c r="G5" s="402"/>
+      <c r="H5" s="402"/>
       <c r="I5" s="13" t="s">
         <v>50</v>
       </c>
@@ -17543,18 +17543,18 @@
       <c r="A20" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="B20" s="434" t="s">
+      <c r="B20" s="403" t="s">
         <v>0</v>
       </c>
-      <c r="C20" s="437" t="s">
+      <c r="C20" s="406" t="s">
         <v>51</v>
       </c>
-      <c r="D20" s="438"/>
-      <c r="E20" s="438"/>
-      <c r="F20" s="438"/>
-      <c r="G20" s="438"/>
-      <c r="H20" s="439"/>
-      <c r="I20" s="446" t="s">
+      <c r="D20" s="407"/>
+      <c r="E20" s="407"/>
+      <c r="F20" s="407"/>
+      <c r="G20" s="407"/>
+      <c r="H20" s="408"/>
+      <c r="I20" s="415" t="s">
         <v>52</v>
       </c>
       <c r="J20" s="10"/>
@@ -17567,14 +17567,14 @@
       <c r="A21" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="B21" s="435"/>
-      <c r="C21" s="440"/>
-      <c r="D21" s="441"/>
-      <c r="E21" s="441"/>
-      <c r="F21" s="441"/>
-      <c r="G21" s="441"/>
-      <c r="H21" s="442"/>
-      <c r="I21" s="435"/>
+      <c r="B21" s="404"/>
+      <c r="C21" s="409"/>
+      <c r="D21" s="410"/>
+      <c r="E21" s="410"/>
+      <c r="F21" s="410"/>
+      <c r="G21" s="410"/>
+      <c r="H21" s="411"/>
+      <c r="I21" s="404"/>
       <c r="J21" s="10"/>
       <c r="K21" s="10"/>
       <c r="L21" s="10"/>
@@ -17584,14 +17584,14 @@
       <c r="A22" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="B22" s="436"/>
-      <c r="C22" s="443"/>
-      <c r="D22" s="444"/>
-      <c r="E22" s="444"/>
-      <c r="F22" s="444"/>
-      <c r="G22" s="444"/>
-      <c r="H22" s="445"/>
-      <c r="I22" s="436"/>
+      <c r="B22" s="405"/>
+      <c r="C22" s="412"/>
+      <c r="D22" s="413"/>
+      <c r="E22" s="413"/>
+      <c r="F22" s="413"/>
+      <c r="G22" s="413"/>
+      <c r="H22" s="414"/>
+      <c r="I22" s="405"/>
       <c r="J22" s="10"/>
       <c r="K22" s="10"/>
       <c r="L22" s="10"/>
@@ -17607,10 +17607,10 @@
       <c r="B26" s="18">
         <v>1</v>
       </c>
-      <c r="C26" s="428">
+      <c r="C26" s="391">
         <v>2</v>
       </c>
-      <c r="D26" s="429"/>
+      <c r="D26" s="392"/>
       <c r="E26" s="18">
         <v>3</v>
       </c>
@@ -17634,14 +17634,14 @@
       <c r="B27" s="19">
         <v>1</v>
       </c>
-      <c r="C27" s="394" t="s">
+      <c r="C27" s="393" t="s">
         <v>53</v>
       </c>
-      <c r="D27" s="395"/>
-      <c r="E27" s="395"/>
-      <c r="F27" s="395"/>
-      <c r="G27" s="395"/>
-      <c r="H27" s="396"/>
+      <c r="D27" s="394"/>
+      <c r="E27" s="394"/>
+      <c r="F27" s="394"/>
+      <c r="G27" s="394"/>
+      <c r="H27" s="395"/>
       <c r="I27" s="20"/>
       <c r="N27" s="16"/>
     </row>
@@ -17658,12 +17658,12 @@
       <c r="D28" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="E28" s="394" t="s">
+      <c r="E28" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F28" s="395"/>
-      <c r="G28" s="395"/>
-      <c r="H28" s="396"/>
+      <c r="F28" s="394"/>
+      <c r="G28" s="394"/>
+      <c r="H28" s="395"/>
       <c r="I28" s="20" t="e">
         <f>SUM(I29:I190)</f>
         <v>#REF!</v>
@@ -17689,11 +17689,11 @@
       <c r="E29" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F29" s="401" t="s">
+      <c r="F29" s="396" t="s">
         <v>56</v>
       </c>
-      <c r="G29" s="402"/>
-      <c r="H29" s="403"/>
+      <c r="G29" s="397"/>
+      <c r="H29" s="398"/>
       <c r="I29" s="20" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17719,11 +17719,11 @@
       <c r="E30" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F30" s="401" t="s">
+      <c r="F30" s="396" t="s">
         <v>57</v>
       </c>
-      <c r="G30" s="402"/>
-      <c r="H30" s="403"/>
+      <c r="G30" s="397"/>
+      <c r="H30" s="398"/>
       <c r="I30" s="20" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17746,11 +17746,11 @@
       <c r="E31" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F31" s="401" t="s">
+      <c r="F31" s="396" t="s">
         <v>58</v>
       </c>
-      <c r="G31" s="402"/>
-      <c r="H31" s="403"/>
+      <c r="G31" s="397"/>
+      <c r="H31" s="398"/>
       <c r="I31" s="20"/>
     </row>
     <row r="32" spans="1:14" ht="12" customHeight="1">
@@ -17769,11 +17769,11 @@
       <c r="E32" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F32" s="391" t="s">
+      <c r="F32" s="416" t="s">
         <v>59</v>
       </c>
-      <c r="G32" s="392"/>
-      <c r="H32" s="393"/>
+      <c r="G32" s="417"/>
+      <c r="H32" s="418"/>
       <c r="I32" s="20" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -17799,16 +17799,16 @@
       <c r="B34" s="21">
         <v>7</v>
       </c>
-      <c r="C34" s="397" t="s">
+      <c r="C34" s="419" t="s">
         <v>61</v>
       </c>
-      <c r="D34" s="398"/>
-      <c r="E34" s="394" t="s">
+      <c r="D34" s="420"/>
+      <c r="E34" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F34" s="395"/>
-      <c r="G34" s="395"/>
-      <c r="H34" s="396"/>
+      <c r="F34" s="394"/>
+      <c r="G34" s="394"/>
+      <c r="H34" s="395"/>
       <c r="I34" s="32"/>
     </row>
     <row r="35" spans="1:15" ht="12" customHeight="1">
@@ -17818,16 +17818,16 @@
       <c r="B35" s="21">
         <v>8</v>
       </c>
-      <c r="C35" s="399"/>
-      <c r="D35" s="400"/>
+      <c r="C35" s="421"/>
+      <c r="D35" s="422"/>
       <c r="E35" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F35" s="401" t="s">
-        <v>44</v>
-      </c>
-      <c r="G35" s="402"/>
-      <c r="H35" s="403"/>
+      <c r="F35" s="396" t="s">
+        <v>44</v>
+      </c>
+      <c r="G35" s="397"/>
+      <c r="H35" s="398"/>
       <c r="I35" s="32"/>
     </row>
     <row r="36" spans="1:15" hidden="1">
@@ -17840,16 +17840,16 @@
       <c r="B37" s="21">
         <v>10</v>
       </c>
-      <c r="C37" s="407" t="s">
+      <c r="C37" s="423" t="s">
         <v>62</v>
       </c>
-      <c r="D37" s="408"/>
-      <c r="E37" s="394" t="s">
+      <c r="D37" s="424"/>
+      <c r="E37" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F37" s="395"/>
-      <c r="G37" s="395"/>
-      <c r="H37" s="396"/>
+      <c r="F37" s="394"/>
+      <c r="G37" s="394"/>
+      <c r="H37" s="395"/>
       <c r="I37" s="32"/>
     </row>
     <row r="38" spans="1:15" ht="12" customHeight="1">
@@ -17859,16 +17859,16 @@
       <c r="B38" s="21">
         <v>11</v>
       </c>
-      <c r="C38" s="409"/>
-      <c r="D38" s="410"/>
-      <c r="E38" s="413" t="s">
+      <c r="C38" s="425"/>
+      <c r="D38" s="426"/>
+      <c r="E38" s="429" t="s">
         <v>55</v>
       </c>
-      <c r="F38" s="401" t="s">
+      <c r="F38" s="396" t="s">
         <v>63</v>
       </c>
-      <c r="G38" s="402"/>
-      <c r="H38" s="403"/>
+      <c r="G38" s="397"/>
+      <c r="H38" s="398"/>
       <c r="I38" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17881,14 +17881,14 @@
       <c r="B39" s="21">
         <v>12</v>
       </c>
-      <c r="C39" s="411"/>
-      <c r="D39" s="412"/>
-      <c r="E39" s="414"/>
-      <c r="F39" s="401" t="s">
+      <c r="C39" s="427"/>
+      <c r="D39" s="428"/>
+      <c r="E39" s="430"/>
+      <c r="F39" s="396" t="s">
         <v>64</v>
       </c>
-      <c r="G39" s="402"/>
-      <c r="H39" s="403"/>
+      <c r="G39" s="397"/>
+      <c r="H39" s="398"/>
       <c r="I39" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17901,16 +17901,16 @@
       <c r="B40" s="21">
         <v>13</v>
       </c>
-      <c r="C40" s="397" t="s">
+      <c r="C40" s="419" t="s">
         <v>65</v>
       </c>
-      <c r="D40" s="398"/>
-      <c r="E40" s="394" t="s">
+      <c r="D40" s="420"/>
+      <c r="E40" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F40" s="395"/>
-      <c r="G40" s="395"/>
-      <c r="H40" s="396"/>
+      <c r="F40" s="394"/>
+      <c r="G40" s="394"/>
+      <c r="H40" s="395"/>
       <c r="I40" s="32"/>
     </row>
     <row r="41" spans="1:15" ht="17.25" customHeight="1">
@@ -17920,16 +17920,16 @@
       <c r="B41" s="21">
         <v>14</v>
       </c>
-      <c r="C41" s="399"/>
-      <c r="D41" s="400"/>
+      <c r="C41" s="421"/>
+      <c r="D41" s="422"/>
       <c r="E41" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F41" s="401" t="s">
-        <v>44</v>
-      </c>
-      <c r="G41" s="402"/>
-      <c r="H41" s="403"/>
+      <c r="F41" s="396" t="s">
+        <v>44</v>
+      </c>
+      <c r="G41" s="397"/>
+      <c r="H41" s="398"/>
       <c r="I41" s="32"/>
     </row>
     <row r="42" spans="1:15" ht="12" customHeight="1">
@@ -17948,11 +17948,11 @@
       <c r="E42" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F42" s="391" t="s">
+      <c r="F42" s="416" t="s">
         <v>66</v>
       </c>
-      <c r="G42" s="392"/>
-      <c r="H42" s="393"/>
+      <c r="G42" s="417"/>
+      <c r="H42" s="418"/>
       <c r="I42" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -17969,14 +17969,14 @@
       <c r="B44" s="21">
         <v>17</v>
       </c>
-      <c r="C44" s="394" t="s">
+      <c r="C44" s="393" t="s">
         <v>67</v>
       </c>
-      <c r="D44" s="395"/>
-      <c r="E44" s="395"/>
-      <c r="F44" s="395"/>
-      <c r="G44" s="395"/>
-      <c r="H44" s="396"/>
+      <c r="D44" s="394"/>
+      <c r="E44" s="394"/>
+      <c r="F44" s="394"/>
+      <c r="G44" s="394"/>
+      <c r="H44" s="395"/>
       <c r="I44" s="32"/>
     </row>
     <row r="45" spans="1:15" ht="12" customHeight="1">
@@ -17986,16 +17986,16 @@
       <c r="B45" s="21">
         <v>18</v>
       </c>
-      <c r="C45" s="422" t="s">
+      <c r="C45" s="431" t="s">
         <v>68</v>
       </c>
-      <c r="D45" s="423"/>
-      <c r="E45" s="394" t="s">
+      <c r="D45" s="432"/>
+      <c r="E45" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F45" s="395"/>
-      <c r="G45" s="395"/>
-      <c r="H45" s="396"/>
+      <c r="F45" s="394"/>
+      <c r="G45" s="394"/>
+      <c r="H45" s="395"/>
       <c r="I45" s="32"/>
     </row>
     <row r="46" spans="1:15" ht="30" customHeight="1">
@@ -18005,16 +18005,16 @@
       <c r="B46" s="21">
         <v>19</v>
       </c>
-      <c r="C46" s="424"/>
-      <c r="D46" s="425"/>
-      <c r="E46" s="413" t="s">
+      <c r="C46" s="433"/>
+      <c r="D46" s="434"/>
+      <c r="E46" s="429" t="s">
         <v>55</v>
       </c>
-      <c r="F46" s="401" t="s">
+      <c r="F46" s="396" t="s">
         <v>69</v>
       </c>
-      <c r="G46" s="402"/>
-      <c r="H46" s="403"/>
+      <c r="G46" s="397"/>
+      <c r="H46" s="398"/>
       <c r="I46" s="127" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -18029,14 +18029,14 @@
       <c r="B47" s="21">
         <v>20</v>
       </c>
-      <c r="C47" s="424"/>
-      <c r="D47" s="425"/>
-      <c r="E47" s="415"/>
-      <c r="F47" s="401" t="s">
+      <c r="C47" s="433"/>
+      <c r="D47" s="434"/>
+      <c r="E47" s="437"/>
+      <c r="F47" s="396" t="s">
         <v>70</v>
       </c>
-      <c r="G47" s="402"/>
-      <c r="H47" s="403"/>
+      <c r="G47" s="397"/>
+      <c r="H47" s="398"/>
       <c r="I47" s="127" t="e">
         <f>#REF!+#REF!-#REF!</f>
         <v>#REF!</v>
@@ -18051,14 +18051,14 @@
       <c r="B48" s="21">
         <v>21</v>
       </c>
-      <c r="C48" s="424"/>
-      <c r="D48" s="425"/>
-      <c r="E48" s="415"/>
-      <c r="F48" s="401" t="s">
+      <c r="C48" s="433"/>
+      <c r="D48" s="434"/>
+      <c r="E48" s="437"/>
+      <c r="F48" s="396" t="s">
         <v>71</v>
       </c>
-      <c r="G48" s="402"/>
-      <c r="H48" s="403"/>
+      <c r="G48" s="397"/>
+      <c r="H48" s="398"/>
       <c r="I48" s="127" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -18072,14 +18072,14 @@
       <c r="B49" s="21">
         <v>22</v>
       </c>
-      <c r="C49" s="426"/>
-      <c r="D49" s="427"/>
-      <c r="E49" s="414"/>
-      <c r="F49" s="401" t="s">
+      <c r="C49" s="435"/>
+      <c r="D49" s="436"/>
+      <c r="E49" s="430"/>
+      <c r="F49" s="396" t="s">
         <v>72</v>
       </c>
-      <c r="G49" s="402"/>
-      <c r="H49" s="403"/>
+      <c r="G49" s="397"/>
+      <c r="H49" s="398"/>
       <c r="I49" s="34" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -18093,16 +18093,16 @@
       <c r="B50" s="21">
         <v>23</v>
       </c>
-      <c r="C50" s="418" t="s">
+      <c r="C50" s="438" t="s">
         <v>73</v>
       </c>
-      <c r="D50" s="419"/>
-      <c r="E50" s="394" t="s">
+      <c r="D50" s="439"/>
+      <c r="E50" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F50" s="395"/>
-      <c r="G50" s="395"/>
-      <c r="H50" s="396"/>
+      <c r="F50" s="394"/>
+      <c r="G50" s="394"/>
+      <c r="H50" s="395"/>
       <c r="I50" s="32"/>
     </row>
     <row r="51" spans="1:14" ht="12" customHeight="1">
@@ -18112,16 +18112,16 @@
       <c r="B51" s="21">
         <v>24</v>
       </c>
-      <c r="C51" s="420"/>
-      <c r="D51" s="421"/>
+      <c r="C51" s="440"/>
+      <c r="D51" s="441"/>
       <c r="E51" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F51" s="401" t="s">
+      <c r="F51" s="396" t="s">
         <v>23</v>
       </c>
-      <c r="G51" s="402"/>
-      <c r="H51" s="403"/>
+      <c r="G51" s="397"/>
+      <c r="H51" s="398"/>
       <c r="I51" s="36" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -18144,11 +18144,11 @@
       <c r="E52" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F52" s="401" t="s">
+      <c r="F52" s="396" t="s">
         <v>74</v>
       </c>
-      <c r="G52" s="402"/>
-      <c r="H52" s="403"/>
+      <c r="G52" s="397"/>
+      <c r="H52" s="398"/>
       <c r="I52" s="32"/>
       <c r="N52" s="35"/>
     </row>
@@ -18162,16 +18162,16 @@
       <c r="B54" s="21">
         <v>27</v>
       </c>
-      <c r="C54" s="397" t="s">
+      <c r="C54" s="419" t="s">
         <v>75</v>
       </c>
-      <c r="D54" s="398"/>
-      <c r="E54" s="394" t="s">
+      <c r="D54" s="420"/>
+      <c r="E54" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F54" s="395"/>
-      <c r="G54" s="395"/>
-      <c r="H54" s="396"/>
+      <c r="F54" s="394"/>
+      <c r="G54" s="394"/>
+      <c r="H54" s="395"/>
       <c r="I54" s="32"/>
     </row>
     <row r="55" spans="1:14" ht="12" customHeight="1">
@@ -18181,16 +18181,16 @@
       <c r="B55" s="21">
         <v>28</v>
       </c>
-      <c r="C55" s="399"/>
-      <c r="D55" s="400"/>
+      <c r="C55" s="421"/>
+      <c r="D55" s="422"/>
       <c r="E55" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F55" s="401" t="s">
+      <c r="F55" s="396" t="s">
         <v>76</v>
       </c>
-      <c r="G55" s="402"/>
-      <c r="H55" s="403"/>
+      <c r="G55" s="397"/>
+      <c r="H55" s="398"/>
       <c r="I55" s="32"/>
     </row>
     <row r="56" spans="1:14" ht="12" customHeight="1">
@@ -18200,16 +18200,16 @@
       <c r="B56" s="21">
         <v>29</v>
       </c>
-      <c r="C56" s="399"/>
-      <c r="D56" s="400"/>
+      <c r="C56" s="421"/>
+      <c r="D56" s="422"/>
       <c r="E56" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F56" s="401" t="s">
+      <c r="F56" s="396" t="s">
         <v>77</v>
       </c>
-      <c r="G56" s="402"/>
-      <c r="H56" s="403"/>
+      <c r="G56" s="397"/>
+      <c r="H56" s="398"/>
       <c r="I56" s="32"/>
     </row>
     <row r="57" spans="1:14" ht="12" customHeight="1">
@@ -18219,16 +18219,16 @@
       <c r="B57" s="21">
         <v>30</v>
       </c>
-      <c r="C57" s="399"/>
-      <c r="D57" s="400"/>
+      <c r="C57" s="421"/>
+      <c r="D57" s="422"/>
       <c r="E57" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F57" s="401" t="s">
+      <c r="F57" s="396" t="s">
         <v>78</v>
       </c>
-      <c r="G57" s="402"/>
-      <c r="H57" s="403"/>
+      <c r="G57" s="397"/>
+      <c r="H57" s="398"/>
       <c r="I57" s="32"/>
     </row>
     <row r="58" spans="1:14" ht="12" customHeight="1">
@@ -18247,11 +18247,11 @@
       <c r="E58" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F58" s="401" t="s">
+      <c r="F58" s="396" t="s">
         <v>79</v>
       </c>
-      <c r="G58" s="402"/>
-      <c r="H58" s="403"/>
+      <c r="G58" s="397"/>
+      <c r="H58" s="398"/>
       <c r="I58" s="32" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -18267,14 +18267,14 @@
       <c r="B60" s="21">
         <v>33</v>
       </c>
-      <c r="C60" s="394" t="s">
+      <c r="C60" s="393" t="s">
         <v>80</v>
       </c>
-      <c r="D60" s="395"/>
-      <c r="E60" s="395"/>
-      <c r="F60" s="395"/>
-      <c r="G60" s="395"/>
-      <c r="H60" s="396"/>
+      <c r="D60" s="394"/>
+      <c r="E60" s="394"/>
+      <c r="F60" s="394"/>
+      <c r="G60" s="394"/>
+      <c r="H60" s="395"/>
       <c r="I60" s="32"/>
     </row>
     <row r="61" spans="1:14" ht="12" customHeight="1">
@@ -18284,16 +18284,16 @@
       <c r="B61" s="21">
         <v>34</v>
       </c>
-      <c r="C61" s="397" t="s">
+      <c r="C61" s="419" t="s">
         <v>81</v>
       </c>
-      <c r="D61" s="398"/>
-      <c r="E61" s="394" t="s">
+      <c r="D61" s="420"/>
+      <c r="E61" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F61" s="395"/>
-      <c r="G61" s="395"/>
-      <c r="H61" s="396"/>
+      <c r="F61" s="394"/>
+      <c r="G61" s="394"/>
+      <c r="H61" s="395"/>
       <c r="I61" s="32"/>
     </row>
     <row r="62" spans="1:14" ht="12" customHeight="1">
@@ -18303,18 +18303,18 @@
       <c r="B62" s="21">
         <v>35</v>
       </c>
-      <c r="C62" s="399"/>
-      <c r="D62" s="400"/>
+      <c r="C62" s="421"/>
+      <c r="D62" s="422"/>
       <c r="E62" s="26" t="s">
         <v>55</v>
       </c>
       <c r="F62" s="26" t="s">
         <v>82</v>
       </c>
-      <c r="G62" s="416" t="s">
+      <c r="G62" s="442" t="s">
         <v>5</v>
       </c>
-      <c r="H62" s="417"/>
+      <c r="H62" s="443"/>
       <c r="I62" s="32"/>
     </row>
     <row r="63" spans="1:14" ht="12" customHeight="1">
@@ -18324,8 +18324,8 @@
       <c r="B63" s="21">
         <v>36</v>
       </c>
-      <c r="C63" s="399"/>
-      <c r="D63" s="400"/>
+      <c r="C63" s="421"/>
+      <c r="D63" s="422"/>
       <c r="E63" s="27" t="s">
         <v>44</v>
       </c>
@@ -18389,10 +18389,10 @@
       <c r="F66" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="G66" s="416" t="s">
+      <c r="G66" s="442" t="s">
         <v>5</v>
       </c>
-      <c r="H66" s="417"/>
+      <c r="H66" s="443"/>
       <c r="I66" s="32"/>
     </row>
     <row r="67" spans="1:14" ht="12" customHeight="1">
@@ -18471,10 +18471,10 @@
       <c r="F70" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="G70" s="416" t="s">
+      <c r="G70" s="442" t="s">
         <v>5</v>
       </c>
-      <c r="H70" s="417"/>
+      <c r="H70" s="443"/>
       <c r="I70" s="32"/>
     </row>
     <row r="71" spans="1:14" ht="12" customHeight="1">
@@ -18553,10 +18553,10 @@
       <c r="F74" s="26" t="s">
         <v>87</v>
       </c>
-      <c r="G74" s="416" t="s">
+      <c r="G74" s="442" t="s">
         <v>5</v>
       </c>
-      <c r="H74" s="417"/>
+      <c r="H74" s="443"/>
       <c r="I74" s="32"/>
     </row>
     <row r="75" spans="1:14" ht="12" customHeight="1">
@@ -18623,16 +18623,16 @@
       <c r="B78" s="21">
         <v>51</v>
       </c>
-      <c r="C78" s="397" t="s">
+      <c r="C78" s="419" t="s">
         <v>88</v>
       </c>
-      <c r="D78" s="398"/>
-      <c r="E78" s="394" t="s">
+      <c r="D78" s="420"/>
+      <c r="E78" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F78" s="395"/>
-      <c r="G78" s="395"/>
-      <c r="H78" s="396"/>
+      <c r="F78" s="394"/>
+      <c r="G78" s="394"/>
+      <c r="H78" s="395"/>
       <c r="I78" s="32"/>
     </row>
     <row r="79" spans="1:14" ht="12" customHeight="1">
@@ -18642,16 +18642,16 @@
       <c r="B79" s="21">
         <v>52</v>
       </c>
-      <c r="C79" s="399"/>
-      <c r="D79" s="400"/>
+      <c r="C79" s="421"/>
+      <c r="D79" s="422"/>
       <c r="E79" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F79" s="401" t="s">
+      <c r="F79" s="396" t="s">
         <v>89</v>
       </c>
-      <c r="G79" s="402"/>
-      <c r="H79" s="403"/>
+      <c r="G79" s="397"/>
+      <c r="H79" s="398"/>
       <c r="I79" s="32"/>
     </row>
     <row r="80" spans="1:14" ht="12" customHeight="1">
@@ -18670,11 +18670,11 @@
       <c r="E80" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F80" s="401" t="s">
+      <c r="F80" s="396" t="s">
         <v>24</v>
       </c>
-      <c r="G80" s="402"/>
-      <c r="H80" s="403"/>
+      <c r="G80" s="397"/>
+      <c r="H80" s="398"/>
       <c r="I80" s="36" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -18697,11 +18697,11 @@
       <c r="E81" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F81" s="401" t="s">
+      <c r="F81" s="396" t="s">
         <v>90</v>
       </c>
-      <c r="G81" s="402"/>
-      <c r="H81" s="403"/>
+      <c r="G81" s="397"/>
+      <c r="H81" s="398"/>
       <c r="I81" s="32"/>
       <c r="N81" s="35"/>
     </row>
@@ -18721,13 +18721,13 @@
       <c r="E82" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F82" s="413" t="s">
+      <c r="F82" s="429" t="s">
         <v>91</v>
       </c>
-      <c r="G82" s="416" t="s">
+      <c r="G82" s="442" t="s">
         <v>5</v>
       </c>
-      <c r="H82" s="417"/>
+      <c r="H82" s="443"/>
       <c r="I82" s="32"/>
     </row>
     <row r="83" spans="1:14" ht="24" customHeight="1">
@@ -18746,8 +18746,8 @@
       <c r="E83" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F83" s="415"/>
-      <c r="G83" s="413" t="s">
+      <c r="F83" s="437"/>
+      <c r="G83" s="429" t="s">
         <v>55</v>
       </c>
       <c r="H83" s="15" t="s">
@@ -18774,8 +18774,8 @@
       <c r="E84" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F84" s="414"/>
-      <c r="G84" s="414"/>
+      <c r="F84" s="430"/>
+      <c r="G84" s="430"/>
       <c r="H84" s="15" t="s">
         <v>92</v>
       </c>
@@ -18800,11 +18800,11 @@
       <c r="E85" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F85" s="401" t="s">
+      <c r="F85" s="396" t="s">
         <v>9</v>
       </c>
-      <c r="G85" s="402"/>
-      <c r="H85" s="403"/>
+      <c r="G85" s="397"/>
+      <c r="H85" s="398"/>
       <c r="I85" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -18826,11 +18826,11 @@
       <c r="E86" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F86" s="401" t="s">
+      <c r="F86" s="396" t="s">
         <v>10</v>
       </c>
-      <c r="G86" s="402"/>
-      <c r="H86" s="403"/>
+      <c r="G86" s="397"/>
+      <c r="H86" s="398"/>
       <c r="I86" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -18852,11 +18852,11 @@
       <c r="E87" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F87" s="401" t="s">
+      <c r="F87" s="396" t="s">
         <v>11</v>
       </c>
-      <c r="G87" s="402"/>
-      <c r="H87" s="403"/>
+      <c r="G87" s="397"/>
+      <c r="H87" s="398"/>
       <c r="I87" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -18878,11 +18878,11 @@
       <c r="E88" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F88" s="401" t="s">
+      <c r="F88" s="396" t="s">
         <v>93</v>
       </c>
-      <c r="G88" s="402"/>
-      <c r="H88" s="403"/>
+      <c r="G88" s="397"/>
+      <c r="H88" s="398"/>
       <c r="I88" s="32"/>
     </row>
     <row r="89" spans="1:14" ht="12" customHeight="1">
@@ -18901,11 +18901,11 @@
       <c r="E89" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F89" s="391" t="s">
+      <c r="F89" s="416" t="s">
         <v>94</v>
       </c>
-      <c r="G89" s="392"/>
-      <c r="H89" s="393"/>
+      <c r="G89" s="417"/>
+      <c r="H89" s="418"/>
       <c r="I89" s="32"/>
       <c r="J89" s="10"/>
     </row>
@@ -18925,9 +18925,9 @@
       <c r="E90" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F90" s="391"/>
-      <c r="G90" s="392"/>
-      <c r="H90" s="393"/>
+      <c r="F90" s="416"/>
+      <c r="G90" s="417"/>
+      <c r="H90" s="418"/>
       <c r="I90" s="39"/>
       <c r="J90" s="10"/>
     </row>
@@ -18941,16 +18941,16 @@
       <c r="B92" s="21">
         <v>63</v>
       </c>
-      <c r="C92" s="397" t="s">
+      <c r="C92" s="419" t="s">
         <v>95</v>
       </c>
-      <c r="D92" s="398"/>
-      <c r="E92" s="394" t="s">
+      <c r="D92" s="420"/>
+      <c r="E92" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F92" s="395"/>
-      <c r="G92" s="395"/>
-      <c r="H92" s="396"/>
+      <c r="F92" s="394"/>
+      <c r="G92" s="394"/>
+      <c r="H92" s="395"/>
       <c r="I92" s="32"/>
     </row>
     <row r="93" spans="1:14" ht="12" customHeight="1">
@@ -18966,14 +18966,14 @@
       <c r="D93" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="E93" s="413" t="s">
+      <c r="E93" s="429" t="s">
         <v>55</v>
       </c>
-      <c r="F93" s="401" t="s">
-        <v>44</v>
-      </c>
-      <c r="G93" s="402"/>
-      <c r="H93" s="403"/>
+      <c r="F93" s="396" t="s">
+        <v>44</v>
+      </c>
+      <c r="G93" s="397"/>
+      <c r="H93" s="398"/>
       <c r="I93" s="32"/>
     </row>
     <row r="94" spans="1:14" ht="12" customHeight="1">
@@ -18989,12 +18989,12 @@
       <c r="D94" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="E94" s="414"/>
-      <c r="F94" s="391" t="s">
+      <c r="E94" s="430"/>
+      <c r="F94" s="416" t="s">
         <v>96</v>
       </c>
-      <c r="G94" s="392"/>
-      <c r="H94" s="393"/>
+      <c r="G94" s="417"/>
+      <c r="H94" s="418"/>
       <c r="I94" s="32"/>
       <c r="J94" s="10"/>
     </row>
@@ -19008,16 +19008,16 @@
       <c r="B96" s="21">
         <v>66</v>
       </c>
-      <c r="C96" s="397" t="s">
+      <c r="C96" s="419" t="s">
         <v>97</v>
       </c>
-      <c r="D96" s="398"/>
-      <c r="E96" s="394" t="s">
+      <c r="D96" s="420"/>
+      <c r="E96" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F96" s="395"/>
-      <c r="G96" s="395"/>
-      <c r="H96" s="396"/>
+      <c r="F96" s="394"/>
+      <c r="G96" s="394"/>
+      <c r="H96" s="395"/>
       <c r="I96" s="32"/>
     </row>
     <row r="97" spans="1:10" ht="12" customHeight="1">
@@ -19036,11 +19036,11 @@
       <c r="E97" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F97" s="401" t="s">
+      <c r="F97" s="396" t="s">
         <v>98</v>
       </c>
-      <c r="G97" s="402"/>
-      <c r="H97" s="403"/>
+      <c r="G97" s="397"/>
+      <c r="H97" s="398"/>
       <c r="I97" s="32"/>
     </row>
     <row r="98" spans="1:10" ht="12" customHeight="1">
@@ -19059,11 +19059,11 @@
       <c r="E98" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F98" s="401" t="s">
+      <c r="F98" s="396" t="s">
         <v>99</v>
       </c>
-      <c r="G98" s="402"/>
-      <c r="H98" s="403"/>
+      <c r="G98" s="397"/>
+      <c r="H98" s="398"/>
       <c r="I98" s="32"/>
     </row>
     <row r="99" spans="1:10" ht="12" customHeight="1">
@@ -19082,11 +19082,11 @@
       <c r="E99" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F99" s="401" t="s">
+      <c r="F99" s="396" t="s">
         <v>12</v>
       </c>
-      <c r="G99" s="402"/>
-      <c r="H99" s="403"/>
+      <c r="G99" s="397"/>
+      <c r="H99" s="398"/>
       <c r="I99" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19108,11 +19108,11 @@
       <c r="E100" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F100" s="401" t="s">
+      <c r="F100" s="396" t="s">
         <v>100</v>
       </c>
-      <c r="G100" s="402"/>
-      <c r="H100" s="403"/>
+      <c r="G100" s="397"/>
+      <c r="H100" s="398"/>
       <c r="I100" s="32"/>
     </row>
     <row r="101" spans="1:10" ht="12" customHeight="1">
@@ -19131,11 +19131,11 @@
       <c r="E101" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F101" s="391" t="s">
-        <v>44</v>
-      </c>
-      <c r="G101" s="392"/>
-      <c r="H101" s="393"/>
+      <c r="F101" s="416" t="s">
+        <v>44</v>
+      </c>
+      <c r="G101" s="417"/>
+      <c r="H101" s="418"/>
       <c r="I101" s="32"/>
       <c r="J101" s="10"/>
     </row>
@@ -19155,11 +19155,11 @@
       <c r="E102" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F102" s="391" t="s">
-        <v>44</v>
-      </c>
-      <c r="G102" s="392"/>
-      <c r="H102" s="393"/>
+      <c r="F102" s="416" t="s">
+        <v>44</v>
+      </c>
+      <c r="G102" s="417"/>
+      <c r="H102" s="418"/>
       <c r="I102" s="32"/>
       <c r="J102" s="10"/>
     </row>
@@ -19173,14 +19173,14 @@
       <c r="B104" s="21">
         <v>72</v>
       </c>
-      <c r="C104" s="394" t="s">
+      <c r="C104" s="393" t="s">
         <v>19</v>
       </c>
-      <c r="D104" s="395"/>
-      <c r="E104" s="395"/>
-      <c r="F104" s="395"/>
-      <c r="G104" s="395"/>
-      <c r="H104" s="396"/>
+      <c r="D104" s="394"/>
+      <c r="E104" s="394"/>
+      <c r="F104" s="394"/>
+      <c r="G104" s="394"/>
+      <c r="H104" s="395"/>
       <c r="I104" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19193,14 +19193,14 @@
       <c r="B105" s="21">
         <v>73</v>
       </c>
-      <c r="C105" s="394" t="s">
+      <c r="C105" s="393" t="s">
         <v>101</v>
       </c>
-      <c r="D105" s="395"/>
-      <c r="E105" s="395"/>
-      <c r="F105" s="395"/>
-      <c r="G105" s="395"/>
-      <c r="H105" s="396"/>
+      <c r="D105" s="394"/>
+      <c r="E105" s="394"/>
+      <c r="F105" s="394"/>
+      <c r="G105" s="394"/>
+      <c r="H105" s="395"/>
       <c r="I105" s="32"/>
     </row>
     <row r="106" spans="1:10" ht="12" customHeight="1">
@@ -19210,16 +19210,16 @@
       <c r="B106" s="21">
         <v>74</v>
       </c>
-      <c r="C106" s="397" t="s">
+      <c r="C106" s="419" t="s">
         <v>102</v>
       </c>
-      <c r="D106" s="398"/>
-      <c r="E106" s="394" t="s">
+      <c r="D106" s="420"/>
+      <c r="E106" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F106" s="395"/>
-      <c r="G106" s="395"/>
-      <c r="H106" s="396"/>
+      <c r="F106" s="394"/>
+      <c r="G106" s="394"/>
+      <c r="H106" s="395"/>
       <c r="I106" s="32"/>
     </row>
     <row r="107" spans="1:10" ht="18.75" customHeight="1">
@@ -19229,16 +19229,16 @@
       <c r="B107" s="21">
         <v>75</v>
       </c>
-      <c r="C107" s="399"/>
-      <c r="D107" s="400"/>
+      <c r="C107" s="421"/>
+      <c r="D107" s="422"/>
       <c r="E107" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F107" s="401" t="s">
+      <c r="F107" s="396" t="s">
         <v>13</v>
       </c>
-      <c r="G107" s="402"/>
-      <c r="H107" s="403"/>
+      <c r="G107" s="397"/>
+      <c r="H107" s="398"/>
       <c r="I107" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19260,11 +19260,11 @@
       <c r="E108" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F108" s="391" t="s">
+      <c r="F108" s="416" t="s">
         <v>103</v>
       </c>
-      <c r="G108" s="392"/>
-      <c r="H108" s="393"/>
+      <c r="G108" s="417"/>
+      <c r="H108" s="418"/>
       <c r="I108" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19287,11 +19287,11 @@
       <c r="E109" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F109" s="391" t="s">
+      <c r="F109" s="416" t="s">
         <v>104</v>
       </c>
-      <c r="G109" s="392"/>
-      <c r="H109" s="393"/>
+      <c r="G109" s="417"/>
+      <c r="H109" s="418"/>
       <c r="I109" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19314,11 +19314,11 @@
       <c r="E110" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F110" s="391" t="s">
+      <c r="F110" s="416" t="s">
         <v>8</v>
       </c>
-      <c r="G110" s="392"/>
-      <c r="H110" s="393"/>
+      <c r="G110" s="417"/>
+      <c r="H110" s="418"/>
       <c r="I110" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19335,16 +19335,16 @@
       <c r="B112" s="21">
         <v>77</v>
       </c>
-      <c r="C112" s="397" t="s">
+      <c r="C112" s="419" t="s">
         <v>105</v>
       </c>
-      <c r="D112" s="398"/>
-      <c r="E112" s="394" t="s">
+      <c r="D112" s="420"/>
+      <c r="E112" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F112" s="395"/>
-      <c r="G112" s="395"/>
-      <c r="H112" s="396"/>
+      <c r="F112" s="394"/>
+      <c r="G112" s="394"/>
+      <c r="H112" s="395"/>
       <c r="I112" s="32"/>
     </row>
     <row r="113" spans="1:9" ht="12" customHeight="1">
@@ -19363,11 +19363,11 @@
       <c r="E113" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F113" s="401" t="s">
+      <c r="F113" s="396" t="s">
         <v>106</v>
       </c>
-      <c r="G113" s="402"/>
-      <c r="H113" s="403"/>
+      <c r="G113" s="397"/>
+      <c r="H113" s="398"/>
       <c r="I113" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19389,11 +19389,11 @@
       <c r="E114" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F114" s="401" t="s">
+      <c r="F114" s="396" t="s">
         <v>107</v>
       </c>
-      <c r="G114" s="402"/>
-      <c r="H114" s="403"/>
+      <c r="G114" s="397"/>
+      <c r="H114" s="398"/>
       <c r="I114" s="32"/>
     </row>
     <row r="115" spans="1:9" ht="12" customHeight="1">
@@ -19403,14 +19403,14 @@
       <c r="B115" s="21">
         <v>80</v>
       </c>
-      <c r="C115" s="394" t="s">
+      <c r="C115" s="393" t="s">
         <v>108</v>
       </c>
-      <c r="D115" s="395"/>
-      <c r="E115" s="395"/>
-      <c r="F115" s="395"/>
-      <c r="G115" s="395"/>
-      <c r="H115" s="396"/>
+      <c r="D115" s="394"/>
+      <c r="E115" s="394"/>
+      <c r="F115" s="394"/>
+      <c r="G115" s="394"/>
+      <c r="H115" s="395"/>
       <c r="I115" s="32"/>
     </row>
     <row r="116" spans="1:9" ht="12" customHeight="1">
@@ -19420,16 +19420,16 @@
       <c r="B116" s="21">
         <v>81</v>
       </c>
-      <c r="C116" s="397" t="s">
+      <c r="C116" s="419" t="s">
         <v>109</v>
       </c>
-      <c r="D116" s="398"/>
-      <c r="E116" s="394" t="s">
+      <c r="D116" s="420"/>
+      <c r="E116" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F116" s="395"/>
-      <c r="G116" s="395"/>
-      <c r="H116" s="396"/>
+      <c r="F116" s="394"/>
+      <c r="G116" s="394"/>
+      <c r="H116" s="395"/>
       <c r="I116" s="32"/>
     </row>
     <row r="117" spans="1:9" ht="12" customHeight="1">
@@ -19439,16 +19439,16 @@
       <c r="B117" s="21">
         <v>82</v>
       </c>
-      <c r="C117" s="399"/>
-      <c r="D117" s="400"/>
+      <c r="C117" s="421"/>
+      <c r="D117" s="422"/>
       <c r="E117" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F117" s="401" t="s">
+      <c r="F117" s="396" t="s">
         <v>110</v>
       </c>
-      <c r="G117" s="402"/>
-      <c r="H117" s="403"/>
+      <c r="G117" s="397"/>
+      <c r="H117" s="398"/>
       <c r="I117" s="32"/>
     </row>
     <row r="118" spans="1:9" ht="12" customHeight="1">
@@ -19467,11 +19467,11 @@
       <c r="E118" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F118" s="401" t="s">
+      <c r="F118" s="396" t="s">
         <v>111</v>
       </c>
-      <c r="G118" s="402"/>
-      <c r="H118" s="403"/>
+      <c r="G118" s="397"/>
+      <c r="H118" s="398"/>
       <c r="I118" s="32"/>
     </row>
     <row r="119" spans="1:9" hidden="1">
@@ -19484,16 +19484,16 @@
       <c r="B120" s="21">
         <v>85</v>
       </c>
-      <c r="C120" s="397" t="s">
+      <c r="C120" s="419" t="s">
         <v>112</v>
       </c>
-      <c r="D120" s="398"/>
-      <c r="E120" s="394" t="s">
+      <c r="D120" s="420"/>
+      <c r="E120" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F120" s="395"/>
-      <c r="G120" s="395"/>
-      <c r="H120" s="396"/>
+      <c r="F120" s="394"/>
+      <c r="G120" s="394"/>
+      <c r="H120" s="395"/>
       <c r="I120" s="32"/>
     </row>
     <row r="121" spans="1:9" ht="12" customHeight="1">
@@ -19503,16 +19503,16 @@
       <c r="B121" s="21">
         <v>86</v>
       </c>
-      <c r="C121" s="399"/>
-      <c r="D121" s="400"/>
+      <c r="C121" s="421"/>
+      <c r="D121" s="422"/>
       <c r="E121" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F121" s="401" t="s">
+      <c r="F121" s="396" t="s">
         <v>113</v>
       </c>
-      <c r="G121" s="402"/>
-      <c r="H121" s="403"/>
+      <c r="G121" s="397"/>
+      <c r="H121" s="398"/>
       <c r="I121" s="32"/>
     </row>
     <row r="122" spans="1:9" ht="12" customHeight="1">
@@ -19531,11 +19531,11 @@
       <c r="E122" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F122" s="401" t="s">
+      <c r="F122" s="396" t="s">
         <v>111</v>
       </c>
-      <c r="G122" s="402"/>
-      <c r="H122" s="403"/>
+      <c r="G122" s="397"/>
+      <c r="H122" s="398"/>
       <c r="I122" s="32"/>
     </row>
     <row r="123" spans="1:9" ht="12" customHeight="1">
@@ -19554,11 +19554,11 @@
       <c r="E123" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F123" s="401" t="s">
+      <c r="F123" s="396" t="s">
         <v>114</v>
       </c>
-      <c r="G123" s="402"/>
-      <c r="H123" s="403"/>
+      <c r="G123" s="397"/>
+      <c r="H123" s="398"/>
       <c r="I123" s="32"/>
     </row>
     <row r="124" spans="1:9" ht="12" customHeight="1">
@@ -19577,11 +19577,11 @@
       <c r="E124" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F124" s="401" t="s">
+      <c r="F124" s="396" t="s">
         <v>115</v>
       </c>
-      <c r="G124" s="402"/>
-      <c r="H124" s="403"/>
+      <c r="G124" s="397"/>
+      <c r="H124" s="398"/>
       <c r="I124" s="32"/>
     </row>
     <row r="125" spans="1:9" hidden="1">
@@ -19594,14 +19594,14 @@
       <c r="B126" s="21">
         <v>91</v>
       </c>
-      <c r="C126" s="394" t="s">
+      <c r="C126" s="393" t="s">
         <v>116</v>
       </c>
-      <c r="D126" s="395"/>
-      <c r="E126" s="395"/>
-      <c r="F126" s="395"/>
-      <c r="G126" s="395"/>
-      <c r="H126" s="396"/>
+      <c r="D126" s="394"/>
+      <c r="E126" s="394"/>
+      <c r="F126" s="394"/>
+      <c r="G126" s="394"/>
+      <c r="H126" s="395"/>
       <c r="I126" s="32"/>
     </row>
     <row r="127" spans="1:9" ht="12" customHeight="1">
@@ -19611,16 +19611,16 @@
       <c r="B127" s="21">
         <v>92</v>
       </c>
-      <c r="C127" s="397" t="s">
+      <c r="C127" s="419" t="s">
         <v>117</v>
       </c>
-      <c r="D127" s="398"/>
-      <c r="E127" s="394" t="s">
+      <c r="D127" s="420"/>
+      <c r="E127" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F127" s="395"/>
-      <c r="G127" s="395"/>
-      <c r="H127" s="396"/>
+      <c r="F127" s="394"/>
+      <c r="G127" s="394"/>
+      <c r="H127" s="395"/>
       <c r="I127" s="32"/>
     </row>
     <row r="128" spans="1:9" ht="12" customHeight="1">
@@ -19630,16 +19630,16 @@
       <c r="B128" s="21">
         <v>93</v>
       </c>
-      <c r="C128" s="399"/>
-      <c r="D128" s="400"/>
+      <c r="C128" s="421"/>
+      <c r="D128" s="422"/>
       <c r="E128" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F128" s="404" t="s">
-        <v>44</v>
-      </c>
-      <c r="G128" s="405"/>
-      <c r="H128" s="406"/>
+      <c r="F128" s="444" t="s">
+        <v>44</v>
+      </c>
+      <c r="G128" s="445"/>
+      <c r="H128" s="446"/>
       <c r="I128" s="40"/>
     </row>
     <row r="129" spans="1:14" hidden="1">
@@ -19652,14 +19652,14 @@
       <c r="B130" s="21">
         <v>95</v>
       </c>
-      <c r="C130" s="394" t="s">
+      <c r="C130" s="393" t="s">
         <v>118</v>
       </c>
-      <c r="D130" s="395"/>
-      <c r="E130" s="395"/>
-      <c r="F130" s="395"/>
-      <c r="G130" s="395"/>
-      <c r="H130" s="396"/>
+      <c r="D130" s="394"/>
+      <c r="E130" s="394"/>
+      <c r="F130" s="394"/>
+      <c r="G130" s="394"/>
+      <c r="H130" s="395"/>
       <c r="I130" s="32"/>
     </row>
     <row r="131" spans="1:14" ht="12" customHeight="1">
@@ -19669,14 +19669,14 @@
       <c r="B131" s="21">
         <v>96</v>
       </c>
-      <c r="C131" s="394" t="s">
+      <c r="C131" s="393" t="s">
         <v>119</v>
       </c>
-      <c r="D131" s="395"/>
-      <c r="E131" s="395"/>
-      <c r="F131" s="395"/>
-      <c r="G131" s="395"/>
-      <c r="H131" s="396"/>
+      <c r="D131" s="394"/>
+      <c r="E131" s="394"/>
+      <c r="F131" s="394"/>
+      <c r="G131" s="394"/>
+      <c r="H131" s="395"/>
       <c r="I131" s="32"/>
     </row>
     <row r="132" spans="1:14" ht="12" customHeight="1">
@@ -19686,16 +19686,16 @@
       <c r="B132" s="21">
         <v>97</v>
       </c>
-      <c r="C132" s="397" t="s">
+      <c r="C132" s="419" t="s">
         <v>120</v>
       </c>
-      <c r="D132" s="398"/>
-      <c r="E132" s="394" t="s">
+      <c r="D132" s="420"/>
+      <c r="E132" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F132" s="395"/>
-      <c r="G132" s="395"/>
-      <c r="H132" s="396"/>
+      <c r="F132" s="394"/>
+      <c r="G132" s="394"/>
+      <c r="H132" s="395"/>
       <c r="I132" s="32"/>
     </row>
     <row r="133" spans="1:14" ht="12" customHeight="1">
@@ -19705,16 +19705,16 @@
       <c r="B133" s="21">
         <v>98</v>
       </c>
-      <c r="C133" s="399"/>
-      <c r="D133" s="400"/>
+      <c r="C133" s="421"/>
+      <c r="D133" s="422"/>
       <c r="E133" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F133" s="401" t="s">
+      <c r="F133" s="396" t="s">
         <v>121</v>
       </c>
-      <c r="G133" s="402"/>
-      <c r="H133" s="403"/>
+      <c r="G133" s="397"/>
+      <c r="H133" s="398"/>
       <c r="I133" s="32"/>
     </row>
     <row r="134" spans="1:14" ht="12" customHeight="1">
@@ -19724,16 +19724,16 @@
       <c r="B134" s="21">
         <v>99</v>
       </c>
-      <c r="C134" s="399"/>
-      <c r="D134" s="400"/>
+      <c r="C134" s="421"/>
+      <c r="D134" s="422"/>
       <c r="E134" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F134" s="401" t="s">
+      <c r="F134" s="396" t="s">
         <v>122</v>
       </c>
-      <c r="G134" s="402"/>
-      <c r="H134" s="403"/>
+      <c r="G134" s="397"/>
+      <c r="H134" s="398"/>
       <c r="I134" s="32"/>
     </row>
     <row r="135" spans="1:14" ht="12" customHeight="1">
@@ -19743,16 +19743,16 @@
       <c r="B135" s="21">
         <v>100</v>
       </c>
-      <c r="C135" s="399"/>
-      <c r="D135" s="400"/>
+      <c r="C135" s="421"/>
+      <c r="D135" s="422"/>
       <c r="E135" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F135" s="401" t="s">
+      <c r="F135" s="396" t="s">
         <v>123</v>
       </c>
-      <c r="G135" s="402"/>
-      <c r="H135" s="403"/>
+      <c r="G135" s="397"/>
+      <c r="H135" s="398"/>
       <c r="I135" s="32"/>
     </row>
     <row r="136" spans="1:14" ht="12" customHeight="1">
@@ -19771,11 +19771,11 @@
       <c r="E136" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F136" s="401" t="s">
+      <c r="F136" s="396" t="s">
         <v>124</v>
       </c>
-      <c r="G136" s="402"/>
-      <c r="H136" s="403"/>
+      <c r="G136" s="397"/>
+      <c r="H136" s="398"/>
       <c r="I136" s="32"/>
     </row>
     <row r="137" spans="1:14" ht="12" customHeight="1">
@@ -19794,11 +19794,11 @@
       <c r="E137" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F137" s="401" t="s">
+      <c r="F137" s="396" t="s">
         <v>125</v>
       </c>
-      <c r="G137" s="402"/>
-      <c r="H137" s="403"/>
+      <c r="G137" s="397"/>
+      <c r="H137" s="398"/>
       <c r="I137" s="32"/>
     </row>
     <row r="138" spans="1:14" ht="12" customHeight="1">
@@ -19817,11 +19817,11 @@
       <c r="E138" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F138" s="401" t="s">
+      <c r="F138" s="396" t="s">
         <v>126</v>
       </c>
-      <c r="G138" s="402"/>
-      <c r="H138" s="403"/>
+      <c r="G138" s="397"/>
+      <c r="H138" s="398"/>
       <c r="I138" s="32"/>
     </row>
     <row r="139" spans="1:14" hidden="1">
@@ -19834,16 +19834,16 @@
       <c r="B140" s="21">
         <v>105</v>
       </c>
-      <c r="C140" s="407" t="s">
+      <c r="C140" s="423" t="s">
         <v>127</v>
       </c>
-      <c r="D140" s="408"/>
-      <c r="E140" s="394" t="s">
+      <c r="D140" s="424"/>
+      <c r="E140" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F140" s="395"/>
-      <c r="G140" s="395"/>
-      <c r="H140" s="396"/>
+      <c r="F140" s="394"/>
+      <c r="G140" s="394"/>
+      <c r="H140" s="395"/>
       <c r="I140" s="32"/>
     </row>
     <row r="141" spans="1:14" ht="12" customHeight="1">
@@ -19853,16 +19853,16 @@
       <c r="B141" s="21">
         <v>106</v>
       </c>
-      <c r="C141" s="409"/>
-      <c r="D141" s="410"/>
-      <c r="E141" s="413" t="s">
+      <c r="C141" s="425"/>
+      <c r="D141" s="426"/>
+      <c r="E141" s="429" t="s">
         <v>55</v>
       </c>
-      <c r="F141" s="401" t="s">
+      <c r="F141" s="396" t="s">
         <v>128</v>
       </c>
-      <c r="G141" s="402"/>
-      <c r="H141" s="403"/>
+      <c r="G141" s="397"/>
+      <c r="H141" s="398"/>
       <c r="I141" s="32" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -19875,14 +19875,14 @@
       <c r="B142" s="21">
         <v>107</v>
       </c>
-      <c r="C142" s="411"/>
-      <c r="D142" s="412"/>
-      <c r="E142" s="414"/>
-      <c r="F142" s="401" t="s">
+      <c r="C142" s="427"/>
+      <c r="D142" s="428"/>
+      <c r="E142" s="430"/>
+      <c r="F142" s="396" t="s">
         <v>129</v>
       </c>
-      <c r="G142" s="402"/>
-      <c r="H142" s="403"/>
+      <c r="G142" s="397"/>
+      <c r="H142" s="398"/>
       <c r="I142" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19896,14 +19896,14 @@
       <c r="B143" s="21">
         <v>108</v>
       </c>
-      <c r="C143" s="394" t="s">
+      <c r="C143" s="393" t="s">
         <v>22</v>
       </c>
-      <c r="D143" s="395"/>
-      <c r="E143" s="395"/>
-      <c r="F143" s="395"/>
-      <c r="G143" s="395"/>
-      <c r="H143" s="396"/>
+      <c r="D143" s="394"/>
+      <c r="E143" s="394"/>
+      <c r="F143" s="394"/>
+      <c r="G143" s="394"/>
+      <c r="H143" s="395"/>
       <c r="I143" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19923,12 +19923,12 @@
       <c r="D144" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="E144" s="394" t="s">
+      <c r="E144" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F144" s="395"/>
-      <c r="G144" s="395"/>
-      <c r="H144" s="396"/>
+      <c r="F144" s="394"/>
+      <c r="G144" s="394"/>
+      <c r="H144" s="395"/>
       <c r="I144" s="32"/>
     </row>
     <row r="145" spans="1:10" ht="12" customHeight="1">
@@ -19947,11 +19947,11 @@
       <c r="E145" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F145" s="401" t="s">
+      <c r="F145" s="396" t="s">
         <v>131</v>
       </c>
-      <c r="G145" s="402"/>
-      <c r="H145" s="403"/>
+      <c r="G145" s="397"/>
+      <c r="H145" s="398"/>
       <c r="I145" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19973,11 +19973,11 @@
       <c r="E146" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F146" s="401" t="s">
+      <c r="F146" s="396" t="s">
         <v>132</v>
       </c>
-      <c r="G146" s="402"/>
-      <c r="H146" s="403"/>
+      <c r="G146" s="397"/>
+      <c r="H146" s="398"/>
       <c r="I146" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -19999,11 +19999,11 @@
       <c r="E147" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F147" s="401" t="s">
+      <c r="F147" s="396" t="s">
         <v>64</v>
       </c>
-      <c r="G147" s="402"/>
-      <c r="H147" s="403"/>
+      <c r="G147" s="397"/>
+      <c r="H147" s="398"/>
       <c r="I147" s="32"/>
     </row>
     <row r="148" spans="1:10" ht="12" customHeight="1">
@@ -20022,11 +20022,11 @@
       <c r="E148" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F148" s="391" t="s">
+      <c r="F148" s="416" t="s">
         <v>133</v>
       </c>
-      <c r="G148" s="392"/>
-      <c r="H148" s="393"/>
+      <c r="G148" s="417"/>
+      <c r="H148" s="418"/>
       <c r="I148" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20049,11 +20049,11 @@
       <c r="E149" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F149" s="391" t="s">
+      <c r="F149" s="416" t="s">
         <v>134</v>
       </c>
-      <c r="G149" s="392"/>
-      <c r="H149" s="393"/>
+      <c r="G149" s="417"/>
+      <c r="H149" s="418"/>
       <c r="I149" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20076,11 +20076,11 @@
       <c r="E150" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F150" s="391" t="s">
+      <c r="F150" s="416" t="s">
         <v>135</v>
       </c>
-      <c r="G150" s="392"/>
-      <c r="H150" s="393"/>
+      <c r="G150" s="417"/>
+      <c r="H150" s="418"/>
       <c r="I150" s="32"/>
       <c r="J150" s="10"/>
     </row>
@@ -20100,11 +20100,11 @@
       <c r="E151" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F151" s="391" t="s">
+      <c r="F151" s="416" t="s">
         <v>136</v>
       </c>
-      <c r="G151" s="392"/>
-      <c r="H151" s="393"/>
+      <c r="G151" s="417"/>
+      <c r="H151" s="418"/>
       <c r="I151" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20121,16 +20121,16 @@
       <c r="B153" s="21">
         <v>114</v>
       </c>
-      <c r="C153" s="397" t="s">
+      <c r="C153" s="419" t="s">
         <v>137</v>
       </c>
-      <c r="D153" s="398"/>
-      <c r="E153" s="394" t="s">
+      <c r="D153" s="420"/>
+      <c r="E153" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F153" s="395"/>
-      <c r="G153" s="395"/>
-      <c r="H153" s="396"/>
+      <c r="F153" s="394"/>
+      <c r="G153" s="394"/>
+      <c r="H153" s="395"/>
       <c r="I153" s="32"/>
     </row>
     <row r="154" spans="1:10" ht="12" customHeight="1">
@@ -20140,16 +20140,16 @@
       <c r="B154" s="21">
         <v>115</v>
       </c>
-      <c r="C154" s="399"/>
-      <c r="D154" s="400"/>
+      <c r="C154" s="421"/>
+      <c r="D154" s="422"/>
       <c r="E154" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F154" s="404" t="s">
-        <v>44</v>
-      </c>
-      <c r="G154" s="405"/>
-      <c r="H154" s="406"/>
+      <c r="F154" s="444" t="s">
+        <v>44</v>
+      </c>
+      <c r="G154" s="445"/>
+      <c r="H154" s="446"/>
       <c r="I154" s="40"/>
     </row>
     <row r="155" spans="1:10" ht="12" customHeight="1">
@@ -20168,11 +20168,11 @@
       <c r="E155" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F155" s="391" t="s">
+      <c r="F155" s="416" t="s">
         <v>4</v>
       </c>
-      <c r="G155" s="392"/>
-      <c r="H155" s="393"/>
+      <c r="G155" s="417"/>
+      <c r="H155" s="418"/>
       <c r="I155" s="32"/>
       <c r="J155" s="10"/>
     </row>
@@ -20192,11 +20192,11 @@
       <c r="E156" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F156" s="391" t="s">
+      <c r="F156" s="416" t="s">
         <v>138</v>
       </c>
-      <c r="G156" s="392"/>
-      <c r="H156" s="393"/>
+      <c r="G156" s="417"/>
+      <c r="H156" s="418"/>
       <c r="I156" s="32"/>
       <c r="J156" s="10"/>
     </row>
@@ -20216,11 +20216,11 @@
       <c r="E157" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F157" s="391" t="s">
+      <c r="F157" s="416" t="s">
         <v>139</v>
       </c>
-      <c r="G157" s="392"/>
-      <c r="H157" s="393"/>
+      <c r="G157" s="417"/>
+      <c r="H157" s="418"/>
       <c r="I157" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20243,9 +20243,9 @@
       <c r="E158" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F158" s="391"/>
-      <c r="G158" s="392"/>
-      <c r="H158" s="393"/>
+      <c r="F158" s="416"/>
+      <c r="G158" s="417"/>
+      <c r="H158" s="418"/>
       <c r="I158" s="32"/>
       <c r="J158" s="10"/>
     </row>
@@ -20259,14 +20259,14 @@
       <c r="B160" s="21">
         <v>117</v>
       </c>
-      <c r="C160" s="394" t="s">
+      <c r="C160" s="393" t="s">
         <v>140</v>
       </c>
-      <c r="D160" s="395"/>
-      <c r="E160" s="395"/>
-      <c r="F160" s="395"/>
-      <c r="G160" s="395"/>
-      <c r="H160" s="396"/>
+      <c r="D160" s="394"/>
+      <c r="E160" s="394"/>
+      <c r="F160" s="394"/>
+      <c r="G160" s="394"/>
+      <c r="H160" s="395"/>
       <c r="I160" s="32"/>
     </row>
     <row r="161" spans="1:9" ht="12" customHeight="1">
@@ -20276,14 +20276,14 @@
       <c r="B161" s="21">
         <v>118</v>
       </c>
-      <c r="C161" s="394" t="s">
+      <c r="C161" s="393" t="s">
         <v>141</v>
       </c>
-      <c r="D161" s="395"/>
-      <c r="E161" s="395"/>
-      <c r="F161" s="395"/>
-      <c r="G161" s="395"/>
-      <c r="H161" s="396"/>
+      <c r="D161" s="394"/>
+      <c r="E161" s="394"/>
+      <c r="F161" s="394"/>
+      <c r="G161" s="394"/>
+      <c r="H161" s="395"/>
       <c r="I161" s="42" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -20296,14 +20296,14 @@
       <c r="B162" s="21">
         <v>119</v>
       </c>
-      <c r="C162" s="394" t="s">
+      <c r="C162" s="393" t="s">
         <v>142</v>
       </c>
-      <c r="D162" s="395"/>
-      <c r="E162" s="395"/>
-      <c r="F162" s="395"/>
-      <c r="G162" s="395"/>
-      <c r="H162" s="396"/>
+      <c r="D162" s="394"/>
+      <c r="E162" s="394"/>
+      <c r="F162" s="394"/>
+      <c r="G162" s="394"/>
+      <c r="H162" s="395"/>
       <c r="I162" s="32"/>
     </row>
     <row r="163" spans="1:9" ht="12" customHeight="1">
@@ -20313,14 +20313,14 @@
       <c r="B163" s="21">
         <v>120</v>
       </c>
-      <c r="C163" s="394" t="s">
+      <c r="C163" s="393" t="s">
         <v>143</v>
       </c>
-      <c r="D163" s="395"/>
-      <c r="E163" s="395"/>
-      <c r="F163" s="395"/>
-      <c r="G163" s="395"/>
-      <c r="H163" s="396"/>
+      <c r="D163" s="394"/>
+      <c r="E163" s="394"/>
+      <c r="F163" s="394"/>
+      <c r="G163" s="394"/>
+      <c r="H163" s="395"/>
       <c r="I163" s="32"/>
     </row>
     <row r="164" spans="1:9" ht="12" customHeight="1">
@@ -20330,14 +20330,14 @@
       <c r="B164" s="21">
         <v>121</v>
       </c>
-      <c r="C164" s="394" t="s">
+      <c r="C164" s="393" t="s">
         <v>144</v>
       </c>
-      <c r="D164" s="395"/>
-      <c r="E164" s="395"/>
-      <c r="F164" s="395"/>
-      <c r="G164" s="395"/>
-      <c r="H164" s="396"/>
+      <c r="D164" s="394"/>
+      <c r="E164" s="394"/>
+      <c r="F164" s="394"/>
+      <c r="G164" s="394"/>
+      <c r="H164" s="395"/>
       <c r="I164" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20350,16 +20350,16 @@
       <c r="B165" s="21">
         <v>122</v>
       </c>
-      <c r="C165" s="397" t="s">
+      <c r="C165" s="419" t="s">
         <v>145</v>
       </c>
-      <c r="D165" s="398"/>
-      <c r="E165" s="394" t="s">
+      <c r="D165" s="420"/>
+      <c r="E165" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F165" s="395"/>
-      <c r="G165" s="395"/>
-      <c r="H165" s="396"/>
+      <c r="F165" s="394"/>
+      <c r="G165" s="394"/>
+      <c r="H165" s="395"/>
       <c r="I165" s="32"/>
     </row>
     <row r="166" spans="1:9" ht="12" customHeight="1">
@@ -20369,16 +20369,16 @@
       <c r="B166" s="21">
         <v>123</v>
       </c>
-      <c r="C166" s="399"/>
-      <c r="D166" s="400"/>
+      <c r="C166" s="421"/>
+      <c r="D166" s="422"/>
       <c r="E166" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F166" s="401" t="s">
+      <c r="F166" s="396" t="s">
         <v>146</v>
       </c>
-      <c r="G166" s="402"/>
-      <c r="H166" s="403"/>
+      <c r="G166" s="397"/>
+      <c r="H166" s="398"/>
       <c r="I166" s="32"/>
     </row>
     <row r="167" spans="1:9" ht="12" customHeight="1">
@@ -20397,11 +20397,11 @@
       <c r="E167" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F167" s="401" t="s">
+      <c r="F167" s="396" t="s">
         <v>147</v>
       </c>
-      <c r="G167" s="402"/>
-      <c r="H167" s="403"/>
+      <c r="G167" s="397"/>
+      <c r="H167" s="398"/>
       <c r="I167" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20423,11 +20423,11 @@
       <c r="E168" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F168" s="401" t="s">
+      <c r="F168" s="396" t="s">
         <v>148</v>
       </c>
-      <c r="G168" s="402"/>
-      <c r="H168" s="403"/>
+      <c r="G168" s="397"/>
+      <c r="H168" s="398"/>
       <c r="I168" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20443,14 +20443,14 @@
       <c r="B170" s="21">
         <v>127</v>
       </c>
-      <c r="C170" s="394" t="s">
+      <c r="C170" s="393" t="s">
         <v>17</v>
       </c>
-      <c r="D170" s="395"/>
-      <c r="E170" s="395"/>
-      <c r="F170" s="395"/>
-      <c r="G170" s="395"/>
-      <c r="H170" s="396"/>
+      <c r="D170" s="394"/>
+      <c r="E170" s="394"/>
+      <c r="F170" s="394"/>
+      <c r="G170" s="394"/>
+      <c r="H170" s="395"/>
       <c r="I170" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20463,14 +20463,14 @@
       <c r="B171" s="21">
         <v>128</v>
       </c>
-      <c r="C171" s="394" t="s">
+      <c r="C171" s="393" t="s">
         <v>149</v>
       </c>
-      <c r="D171" s="395"/>
-      <c r="E171" s="395"/>
-      <c r="F171" s="395"/>
-      <c r="G171" s="395"/>
-      <c r="H171" s="396"/>
+      <c r="D171" s="394"/>
+      <c r="E171" s="394"/>
+      <c r="F171" s="394"/>
+      <c r="G171" s="394"/>
+      <c r="H171" s="395"/>
       <c r="I171" s="32"/>
     </row>
     <row r="172" spans="1:9" ht="12" customHeight="1">
@@ -20480,14 +20480,14 @@
       <c r="B172" s="21">
         <v>129</v>
       </c>
-      <c r="C172" s="394" t="s">
+      <c r="C172" s="393" t="s">
         <v>150</v>
       </c>
-      <c r="D172" s="395"/>
-      <c r="E172" s="395"/>
-      <c r="F172" s="395"/>
-      <c r="G172" s="395"/>
-      <c r="H172" s="396"/>
+      <c r="D172" s="394"/>
+      <c r="E172" s="394"/>
+      <c r="F172" s="394"/>
+      <c r="G172" s="394"/>
+      <c r="H172" s="395"/>
       <c r="I172" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20500,14 +20500,14 @@
       <c r="B173" s="21">
         <v>130</v>
       </c>
-      <c r="C173" s="394" t="s">
+      <c r="C173" s="393" t="s">
         <v>151</v>
       </c>
-      <c r="D173" s="395"/>
-      <c r="E173" s="395"/>
-      <c r="F173" s="395"/>
-      <c r="G173" s="395"/>
-      <c r="H173" s="396"/>
+      <c r="D173" s="394"/>
+      <c r="E173" s="394"/>
+      <c r="F173" s="394"/>
+      <c r="G173" s="394"/>
+      <c r="H173" s="395"/>
       <c r="I173" s="32"/>
     </row>
     <row r="174" spans="1:9" ht="12" customHeight="1">
@@ -20517,14 +20517,14 @@
       <c r="B174" s="21">
         <v>131</v>
       </c>
-      <c r="C174" s="394" t="s">
+      <c r="C174" s="393" t="s">
         <v>152</v>
       </c>
-      <c r="D174" s="395"/>
-      <c r="E174" s="395"/>
-      <c r="F174" s="395"/>
-      <c r="G174" s="395"/>
-      <c r="H174" s="396"/>
+      <c r="D174" s="394"/>
+      <c r="E174" s="394"/>
+      <c r="F174" s="394"/>
+      <c r="G174" s="394"/>
+      <c r="H174" s="395"/>
       <c r="I174" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20537,16 +20537,16 @@
       <c r="B175" s="21">
         <v>132</v>
       </c>
-      <c r="C175" s="397" t="s">
+      <c r="C175" s="419" t="s">
         <v>153</v>
       </c>
-      <c r="D175" s="398"/>
-      <c r="E175" s="394" t="s">
+      <c r="D175" s="420"/>
+      <c r="E175" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F175" s="395"/>
-      <c r="G175" s="395"/>
-      <c r="H175" s="396"/>
+      <c r="F175" s="394"/>
+      <c r="G175" s="394"/>
+      <c r="H175" s="395"/>
       <c r="I175" s="32"/>
     </row>
     <row r="176" spans="1:9" ht="12" customHeight="1">
@@ -20556,16 +20556,16 @@
       <c r="B176" s="21">
         <v>133</v>
       </c>
-      <c r="C176" s="399"/>
-      <c r="D176" s="400"/>
+      <c r="C176" s="421"/>
+      <c r="D176" s="422"/>
       <c r="E176" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F176" s="401" t="s">
+      <c r="F176" s="396" t="s">
         <v>128</v>
       </c>
-      <c r="G176" s="402"/>
-      <c r="H176" s="403"/>
+      <c r="G176" s="397"/>
+      <c r="H176" s="398"/>
       <c r="I176" s="32"/>
     </row>
     <row r="177" spans="1:14" ht="12" customHeight="1">
@@ -20575,16 +20575,16 @@
       <c r="B177" s="21">
         <v>134</v>
       </c>
-      <c r="C177" s="399"/>
-      <c r="D177" s="400"/>
+      <c r="C177" s="421"/>
+      <c r="D177" s="422"/>
       <c r="E177" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F177" s="401" t="s">
+      <c r="F177" s="396" t="s">
         <v>154</v>
       </c>
-      <c r="G177" s="402"/>
-      <c r="H177" s="403"/>
+      <c r="G177" s="397"/>
+      <c r="H177" s="398"/>
       <c r="I177" s="32"/>
     </row>
     <row r="178" spans="1:14" ht="12" customHeight="1">
@@ -20603,11 +20603,11 @@
       <c r="E178" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F178" s="401" t="s">
+      <c r="F178" s="396" t="s">
         <v>155</v>
       </c>
-      <c r="G178" s="402"/>
-      <c r="H178" s="403"/>
+      <c r="G178" s="397"/>
+      <c r="H178" s="398"/>
       <c r="I178" s="32"/>
     </row>
     <row r="179" spans="1:14" hidden="1">
@@ -20620,14 +20620,14 @@
       <c r="B180" s="21">
         <v>137</v>
       </c>
-      <c r="C180" s="394" t="s">
+      <c r="C180" s="393" t="s">
         <v>156</v>
       </c>
-      <c r="D180" s="395"/>
-      <c r="E180" s="395"/>
-      <c r="F180" s="395"/>
-      <c r="G180" s="395"/>
-      <c r="H180" s="396"/>
+      <c r="D180" s="394"/>
+      <c r="E180" s="394"/>
+      <c r="F180" s="394"/>
+      <c r="G180" s="394"/>
+      <c r="H180" s="395"/>
       <c r="I180" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20640,14 +20640,14 @@
       <c r="B181" s="21">
         <v>138</v>
       </c>
-      <c r="C181" s="394" t="s">
+      <c r="C181" s="393" t="s">
         <v>21</v>
       </c>
-      <c r="D181" s="395"/>
-      <c r="E181" s="395"/>
-      <c r="F181" s="395"/>
-      <c r="G181" s="395"/>
-      <c r="H181" s="396"/>
+      <c r="D181" s="394"/>
+      <c r="E181" s="394"/>
+      <c r="F181" s="394"/>
+      <c r="G181" s="394"/>
+      <c r="H181" s="395"/>
       <c r="I181" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -20660,16 +20660,16 @@
       <c r="B182" s="21">
         <v>139</v>
       </c>
-      <c r="C182" s="397" t="s">
+      <c r="C182" s="419" t="s">
         <v>157</v>
       </c>
-      <c r="D182" s="398"/>
-      <c r="E182" s="394" t="s">
+      <c r="D182" s="420"/>
+      <c r="E182" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F182" s="395"/>
-      <c r="G182" s="395"/>
-      <c r="H182" s="396"/>
+      <c r="F182" s="394"/>
+      <c r="G182" s="394"/>
+      <c r="H182" s="395"/>
       <c r="I182" s="32"/>
     </row>
     <row r="183" spans="1:14" ht="12" customHeight="1">
@@ -20679,16 +20679,16 @@
       <c r="B183" s="21">
         <v>140</v>
       </c>
-      <c r="C183" s="399"/>
-      <c r="D183" s="400"/>
+      <c r="C183" s="421"/>
+      <c r="D183" s="422"/>
       <c r="E183" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F183" s="401" t="s">
-        <v>44</v>
-      </c>
-      <c r="G183" s="402"/>
-      <c r="H183" s="403"/>
+      <c r="F183" s="396" t="s">
+        <v>44</v>
+      </c>
+      <c r="G183" s="397"/>
+      <c r="H183" s="398"/>
       <c r="I183" s="32"/>
     </row>
     <row r="184" spans="1:14" hidden="1">
@@ -20701,16 +20701,16 @@
       <c r="B185" s="21">
         <v>142</v>
       </c>
-      <c r="C185" s="397" t="s">
+      <c r="C185" s="419" t="s">
         <v>158</v>
       </c>
-      <c r="D185" s="398"/>
-      <c r="E185" s="394" t="s">
+      <c r="D185" s="420"/>
+      <c r="E185" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="F185" s="395"/>
-      <c r="G185" s="395"/>
-      <c r="H185" s="396"/>
+      <c r="F185" s="394"/>
+      <c r="G185" s="394"/>
+      <c r="H185" s="395"/>
       <c r="I185" s="32"/>
     </row>
     <row r="186" spans="1:14" ht="12" customHeight="1">
@@ -20720,16 +20720,16 @@
       <c r="B186" s="21">
         <v>143</v>
       </c>
-      <c r="C186" s="399"/>
-      <c r="D186" s="400"/>
+      <c r="C186" s="421"/>
+      <c r="D186" s="422"/>
       <c r="E186" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F186" s="401" t="s">
+      <c r="F186" s="396" t="s">
         <v>159</v>
       </c>
-      <c r="G186" s="402"/>
-      <c r="H186" s="403"/>
+      <c r="G186" s="397"/>
+      <c r="H186" s="398"/>
       <c r="I186" s="32"/>
     </row>
     <row r="187" spans="1:14" ht="12" customHeight="1">
@@ -20739,16 +20739,16 @@
       <c r="B187" s="21">
         <v>144</v>
       </c>
-      <c r="C187" s="399"/>
-      <c r="D187" s="400"/>
+      <c r="C187" s="421"/>
+      <c r="D187" s="422"/>
       <c r="E187" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F187" s="401" t="s">
+      <c r="F187" s="396" t="s">
         <v>160</v>
       </c>
-      <c r="G187" s="402"/>
-      <c r="H187" s="403"/>
+      <c r="G187" s="397"/>
+      <c r="H187" s="398"/>
       <c r="I187" s="32"/>
     </row>
     <row r="188" spans="1:14" ht="12" customHeight="1">
@@ -20767,11 +20767,11 @@
       <c r="E188" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F188" s="391" t="s">
+      <c r="F188" s="416" t="s">
         <v>161</v>
       </c>
-      <c r="G188" s="392"/>
-      <c r="H188" s="393"/>
+      <c r="G188" s="417"/>
+      <c r="H188" s="418"/>
       <c r="I188" s="32"/>
       <c r="J188" s="10"/>
     </row>
@@ -20791,11 +20791,11 @@
       <c r="E189" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F189" s="391" t="s">
+      <c r="F189" s="416" t="s">
         <v>162</v>
       </c>
-      <c r="G189" s="392"/>
-      <c r="H189" s="393"/>
+      <c r="G189" s="417"/>
+      <c r="H189" s="418"/>
       <c r="I189" s="32"/>
       <c r="J189" s="10"/>
     </row>
@@ -20815,11 +20815,11 @@
       <c r="E190" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="F190" s="391" t="s">
+      <c r="F190" s="416" t="s">
         <v>163</v>
       </c>
-      <c r="G190" s="392"/>
-      <c r="H190" s="393"/>
+      <c r="G190" s="417"/>
+      <c r="H190" s="418"/>
       <c r="I190" s="32" t="e">
         <f>#REF!+#REF!</f>
         <v>#REF!</v>
@@ -20882,6 +20882,161 @@
     </row>
   </sheetData>
   <mergeCells count="169">
+    <mergeCell ref="F188:H188"/>
+    <mergeCell ref="F189:H189"/>
+    <mergeCell ref="F190:H190"/>
+    <mergeCell ref="C180:H180"/>
+    <mergeCell ref="C181:H181"/>
+    <mergeCell ref="C182:D183"/>
+    <mergeCell ref="E182:H182"/>
+    <mergeCell ref="F183:H183"/>
+    <mergeCell ref="C185:D187"/>
+    <mergeCell ref="E185:H185"/>
+    <mergeCell ref="F186:H186"/>
+    <mergeCell ref="F187:H187"/>
+    <mergeCell ref="C174:H174"/>
+    <mergeCell ref="C175:D177"/>
+    <mergeCell ref="E175:H175"/>
+    <mergeCell ref="F176:H176"/>
+    <mergeCell ref="F177:H177"/>
+    <mergeCell ref="F178:H178"/>
+    <mergeCell ref="F167:H167"/>
+    <mergeCell ref="F168:H168"/>
+    <mergeCell ref="C170:H170"/>
+    <mergeCell ref="C171:H171"/>
+    <mergeCell ref="C172:H172"/>
+    <mergeCell ref="C173:H173"/>
+    <mergeCell ref="C162:H162"/>
+    <mergeCell ref="C163:H163"/>
+    <mergeCell ref="C164:H164"/>
+    <mergeCell ref="C165:D166"/>
+    <mergeCell ref="E165:H165"/>
+    <mergeCell ref="F166:H166"/>
+    <mergeCell ref="F155:H155"/>
+    <mergeCell ref="F156:H156"/>
+    <mergeCell ref="F157:H157"/>
+    <mergeCell ref="F158:H158"/>
+    <mergeCell ref="C160:H160"/>
+    <mergeCell ref="C161:H161"/>
+    <mergeCell ref="F149:H149"/>
+    <mergeCell ref="F150:H150"/>
+    <mergeCell ref="F151:H151"/>
+    <mergeCell ref="C153:D154"/>
+    <mergeCell ref="E153:H153"/>
+    <mergeCell ref="F154:H154"/>
+    <mergeCell ref="C143:H143"/>
+    <mergeCell ref="E144:H144"/>
+    <mergeCell ref="F145:H145"/>
+    <mergeCell ref="F146:H146"/>
+    <mergeCell ref="F147:H147"/>
+    <mergeCell ref="F148:H148"/>
+    <mergeCell ref="F137:H137"/>
+    <mergeCell ref="F138:H138"/>
+    <mergeCell ref="C140:D142"/>
+    <mergeCell ref="E140:H140"/>
+    <mergeCell ref="E141:E142"/>
+    <mergeCell ref="F141:H141"/>
+    <mergeCell ref="F142:H142"/>
+    <mergeCell ref="C132:D135"/>
+    <mergeCell ref="E132:H132"/>
+    <mergeCell ref="F133:H133"/>
+    <mergeCell ref="F134:H134"/>
+    <mergeCell ref="F135:H135"/>
+    <mergeCell ref="F136:H136"/>
+    <mergeCell ref="C126:H126"/>
+    <mergeCell ref="C127:D128"/>
+    <mergeCell ref="E127:H127"/>
+    <mergeCell ref="F128:H128"/>
+    <mergeCell ref="C130:H130"/>
+    <mergeCell ref="C131:H131"/>
+    <mergeCell ref="C120:D121"/>
+    <mergeCell ref="E120:H120"/>
+    <mergeCell ref="F121:H121"/>
+    <mergeCell ref="F122:H122"/>
+    <mergeCell ref="F123:H123"/>
+    <mergeCell ref="F124:H124"/>
+    <mergeCell ref="F114:H114"/>
+    <mergeCell ref="C115:H115"/>
+    <mergeCell ref="C116:D117"/>
+    <mergeCell ref="E116:H116"/>
+    <mergeCell ref="F117:H117"/>
+    <mergeCell ref="F118:H118"/>
+    <mergeCell ref="F108:H108"/>
+    <mergeCell ref="F109:H109"/>
+    <mergeCell ref="F110:H110"/>
+    <mergeCell ref="C112:D112"/>
+    <mergeCell ref="E112:H112"/>
+    <mergeCell ref="F113:H113"/>
+    <mergeCell ref="F101:H101"/>
+    <mergeCell ref="F102:H102"/>
+    <mergeCell ref="C104:H104"/>
+    <mergeCell ref="C105:H105"/>
+    <mergeCell ref="C106:D107"/>
+    <mergeCell ref="E106:H106"/>
+    <mergeCell ref="F107:H107"/>
+    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="E96:H96"/>
+    <mergeCell ref="F97:H97"/>
+    <mergeCell ref="F98:H98"/>
+    <mergeCell ref="F99:H99"/>
+    <mergeCell ref="F100:H100"/>
+    <mergeCell ref="F88:H88"/>
+    <mergeCell ref="F89:H89"/>
+    <mergeCell ref="F90:H90"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="E92:H92"/>
+    <mergeCell ref="E93:E94"/>
+    <mergeCell ref="F93:H93"/>
+    <mergeCell ref="F94:H94"/>
+    <mergeCell ref="F82:F84"/>
+    <mergeCell ref="G82:H82"/>
+    <mergeCell ref="G83:G84"/>
+    <mergeCell ref="F85:H85"/>
+    <mergeCell ref="F86:H86"/>
+    <mergeCell ref="F87:H87"/>
+    <mergeCell ref="G74:H74"/>
+    <mergeCell ref="C78:D79"/>
+    <mergeCell ref="E78:H78"/>
+    <mergeCell ref="F79:H79"/>
+    <mergeCell ref="F80:H80"/>
+    <mergeCell ref="F81:H81"/>
+    <mergeCell ref="C60:H60"/>
+    <mergeCell ref="C61:D63"/>
+    <mergeCell ref="E61:H61"/>
+    <mergeCell ref="G62:H62"/>
+    <mergeCell ref="G66:H66"/>
+    <mergeCell ref="G70:H70"/>
+    <mergeCell ref="C54:D57"/>
+    <mergeCell ref="E54:H54"/>
+    <mergeCell ref="F55:H55"/>
+    <mergeCell ref="F56:H56"/>
+    <mergeCell ref="F57:H57"/>
+    <mergeCell ref="F58:H58"/>
+    <mergeCell ref="F48:H48"/>
+    <mergeCell ref="F49:H49"/>
+    <mergeCell ref="C50:D51"/>
+    <mergeCell ref="E50:H50"/>
+    <mergeCell ref="F51:H51"/>
+    <mergeCell ref="F52:H52"/>
+    <mergeCell ref="C40:D41"/>
+    <mergeCell ref="E40:H40"/>
+    <mergeCell ref="F41:H41"/>
+    <mergeCell ref="F42:H42"/>
+    <mergeCell ref="C44:H44"/>
+    <mergeCell ref="C45:D49"/>
+    <mergeCell ref="E45:H45"/>
+    <mergeCell ref="E46:E49"/>
+    <mergeCell ref="F46:H46"/>
+    <mergeCell ref="F47:H47"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="C34:D35"/>
+    <mergeCell ref="E34:H34"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="C37:D39"/>
+    <mergeCell ref="E37:H37"/>
+    <mergeCell ref="E38:E39"/>
+    <mergeCell ref="F38:H38"/>
+    <mergeCell ref="F39:H39"/>
     <mergeCell ref="C26:D26"/>
     <mergeCell ref="C27:H27"/>
     <mergeCell ref="E28:H28"/>
@@ -20896,161 +21051,6 @@
     <mergeCell ref="B20:B22"/>
     <mergeCell ref="C20:H22"/>
     <mergeCell ref="I20:I22"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="C34:D35"/>
-    <mergeCell ref="E34:H34"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="C37:D39"/>
-    <mergeCell ref="E37:H37"/>
-    <mergeCell ref="E38:E39"/>
-    <mergeCell ref="F38:H38"/>
-    <mergeCell ref="F39:H39"/>
-    <mergeCell ref="C40:D41"/>
-    <mergeCell ref="E40:H40"/>
-    <mergeCell ref="F41:H41"/>
-    <mergeCell ref="F42:H42"/>
-    <mergeCell ref="C44:H44"/>
-    <mergeCell ref="C45:D49"/>
-    <mergeCell ref="E45:H45"/>
-    <mergeCell ref="E46:E49"/>
-    <mergeCell ref="F46:H46"/>
-    <mergeCell ref="F47:H47"/>
-    <mergeCell ref="C54:D57"/>
-    <mergeCell ref="E54:H54"/>
-    <mergeCell ref="F55:H55"/>
-    <mergeCell ref="F56:H56"/>
-    <mergeCell ref="F57:H57"/>
-    <mergeCell ref="F58:H58"/>
-    <mergeCell ref="F48:H48"/>
-    <mergeCell ref="F49:H49"/>
-    <mergeCell ref="C50:D51"/>
-    <mergeCell ref="E50:H50"/>
-    <mergeCell ref="F51:H51"/>
-    <mergeCell ref="F52:H52"/>
-    <mergeCell ref="G74:H74"/>
-    <mergeCell ref="C78:D79"/>
-    <mergeCell ref="E78:H78"/>
-    <mergeCell ref="F79:H79"/>
-    <mergeCell ref="F80:H80"/>
-    <mergeCell ref="F81:H81"/>
-    <mergeCell ref="C60:H60"/>
-    <mergeCell ref="C61:D63"/>
-    <mergeCell ref="E61:H61"/>
-    <mergeCell ref="G62:H62"/>
-    <mergeCell ref="G66:H66"/>
-    <mergeCell ref="G70:H70"/>
-    <mergeCell ref="F88:H88"/>
-    <mergeCell ref="F89:H89"/>
-    <mergeCell ref="F90:H90"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="E92:H92"/>
-    <mergeCell ref="E93:E94"/>
-    <mergeCell ref="F93:H93"/>
-    <mergeCell ref="F94:H94"/>
-    <mergeCell ref="F82:F84"/>
-    <mergeCell ref="G82:H82"/>
-    <mergeCell ref="G83:G84"/>
-    <mergeCell ref="F85:H85"/>
-    <mergeCell ref="F86:H86"/>
-    <mergeCell ref="F87:H87"/>
-    <mergeCell ref="F101:H101"/>
-    <mergeCell ref="F102:H102"/>
-    <mergeCell ref="C104:H104"/>
-    <mergeCell ref="C105:H105"/>
-    <mergeCell ref="C106:D107"/>
-    <mergeCell ref="E106:H106"/>
-    <mergeCell ref="F107:H107"/>
-    <mergeCell ref="C96:D96"/>
-    <mergeCell ref="E96:H96"/>
-    <mergeCell ref="F97:H97"/>
-    <mergeCell ref="F98:H98"/>
-    <mergeCell ref="F99:H99"/>
-    <mergeCell ref="F100:H100"/>
-    <mergeCell ref="F114:H114"/>
-    <mergeCell ref="C115:H115"/>
-    <mergeCell ref="C116:D117"/>
-    <mergeCell ref="E116:H116"/>
-    <mergeCell ref="F117:H117"/>
-    <mergeCell ref="F118:H118"/>
-    <mergeCell ref="F108:H108"/>
-    <mergeCell ref="F109:H109"/>
-    <mergeCell ref="F110:H110"/>
-    <mergeCell ref="C112:D112"/>
-    <mergeCell ref="E112:H112"/>
-    <mergeCell ref="F113:H113"/>
-    <mergeCell ref="C126:H126"/>
-    <mergeCell ref="C127:D128"/>
-    <mergeCell ref="E127:H127"/>
-    <mergeCell ref="F128:H128"/>
-    <mergeCell ref="C130:H130"/>
-    <mergeCell ref="C131:H131"/>
-    <mergeCell ref="C120:D121"/>
-    <mergeCell ref="E120:H120"/>
-    <mergeCell ref="F121:H121"/>
-    <mergeCell ref="F122:H122"/>
-    <mergeCell ref="F123:H123"/>
-    <mergeCell ref="F124:H124"/>
-    <mergeCell ref="F137:H137"/>
-    <mergeCell ref="F138:H138"/>
-    <mergeCell ref="C140:D142"/>
-    <mergeCell ref="E140:H140"/>
-    <mergeCell ref="E141:E142"/>
-    <mergeCell ref="F141:H141"/>
-    <mergeCell ref="F142:H142"/>
-    <mergeCell ref="C132:D135"/>
-    <mergeCell ref="E132:H132"/>
-    <mergeCell ref="F133:H133"/>
-    <mergeCell ref="F134:H134"/>
-    <mergeCell ref="F135:H135"/>
-    <mergeCell ref="F136:H136"/>
-    <mergeCell ref="F149:H149"/>
-    <mergeCell ref="F150:H150"/>
-    <mergeCell ref="F151:H151"/>
-    <mergeCell ref="C153:D154"/>
-    <mergeCell ref="E153:H153"/>
-    <mergeCell ref="F154:H154"/>
-    <mergeCell ref="C143:H143"/>
-    <mergeCell ref="E144:H144"/>
-    <mergeCell ref="F145:H145"/>
-    <mergeCell ref="F146:H146"/>
-    <mergeCell ref="F147:H147"/>
-    <mergeCell ref="F148:H148"/>
-    <mergeCell ref="C162:H162"/>
-    <mergeCell ref="C163:H163"/>
-    <mergeCell ref="C164:H164"/>
-    <mergeCell ref="C165:D166"/>
-    <mergeCell ref="E165:H165"/>
-    <mergeCell ref="F166:H166"/>
-    <mergeCell ref="F155:H155"/>
-    <mergeCell ref="F156:H156"/>
-    <mergeCell ref="F157:H157"/>
-    <mergeCell ref="F158:H158"/>
-    <mergeCell ref="C160:H160"/>
-    <mergeCell ref="C161:H161"/>
-    <mergeCell ref="C174:H174"/>
-    <mergeCell ref="C175:D177"/>
-    <mergeCell ref="E175:H175"/>
-    <mergeCell ref="F176:H176"/>
-    <mergeCell ref="F177:H177"/>
-    <mergeCell ref="F178:H178"/>
-    <mergeCell ref="F167:H167"/>
-    <mergeCell ref="F168:H168"/>
-    <mergeCell ref="C170:H170"/>
-    <mergeCell ref="C171:H171"/>
-    <mergeCell ref="C172:H172"/>
-    <mergeCell ref="C173:H173"/>
-    <mergeCell ref="F188:H188"/>
-    <mergeCell ref="F189:H189"/>
-    <mergeCell ref="F190:H190"/>
-    <mergeCell ref="C180:H180"/>
-    <mergeCell ref="C181:H181"/>
-    <mergeCell ref="C182:D183"/>
-    <mergeCell ref="E182:H182"/>
-    <mergeCell ref="F183:H183"/>
-    <mergeCell ref="C185:D187"/>
-    <mergeCell ref="E185:H185"/>
-    <mergeCell ref="F186:H186"/>
-    <mergeCell ref="F187:H187"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="55" orientation="portrait" r:id="rId1"/>
@@ -21174,7 +21174,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="206" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="C7" s="207" t="s">
         <v>269</v>
@@ -21200,7 +21200,7 @@
         <v>307</v>
       </c>
       <c r="J7" s="270" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="30">
@@ -21550,7 +21550,7 @@
         <v>1</v>
       </c>
       <c r="B19" s="211" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="C19" s="194" t="s">
         <v>274</v>
@@ -21573,10 +21573,10 @@
         <v>305</v>
       </c>
       <c r="I19" s="264" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="J19" s="270" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="45">
@@ -21618,7 +21618,7 @@
         <v>3</v>
       </c>
       <c r="B21" s="210" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="C21" s="213" t="s">
         <v>272</v>
@@ -21652,7 +21652,7 @@
         <v>4</v>
       </c>
       <c r="B22" s="210" t="s">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c r="C22" s="213" t="s">
         <v>272</v>
@@ -21686,7 +21686,7 @@
         <v>5</v>
       </c>
       <c r="B23" s="244" t="s">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c r="C23" s="243" t="s">
         <v>272</v>
@@ -22618,7 +22618,7 @@
     <row r="53" spans="1:10" ht="45">
       <c r="A53" s="241"/>
       <c r="B53" s="217" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="C53" s="186"/>
       <c r="D53" s="1"/>
@@ -29798,7 +29798,7 @@
     </row>
     <row r="10" spans="1:6" ht="51">
       <c r="A10" s="278" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="B10" s="280" t="s">
         <v>343</v>
@@ -30123,6 +30123,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A7:F7"/>
     <mergeCell ref="A31:F31"/>
     <mergeCell ref="A25:F25"/>
     <mergeCell ref="A26:F26"/>
@@ -30130,12 +30136,6 @@
     <mergeCell ref="A28:F28"/>
     <mergeCell ref="A29:F29"/>
     <mergeCell ref="A30:F30"/>
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" verticalDpi="0" r:id="rId1"/>
